--- a/Assets/02Script/Table/EventTable.xlsx
+++ b/Assets/02Script/Table/EventTable.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="66">
   <si>
     <t>EventID</t>
   </si>
@@ -37,7 +37,7 @@
     <t>E002</t>
   </si>
   <si>
-    <t>Tutorial</t>
+    <t>Tutorial_Timeline</t>
   </si>
   <si>
     <t>Conversation</t>
@@ -46,13 +46,16 @@
     <t>E003</t>
   </si>
   <si>
+    <t>Tutorial_Conversation</t>
+  </si>
+  <si>
     <t>Order</t>
   </si>
   <si>
     <t>Text</t>
   </si>
   <si>
-    <t>"몽령"이라고 알아?</t>
+    <t>&lt;color=red&gt;"몽령"&lt;/color&gt;이라고 알아?</t>
   </si>
   <si>
     <t>삶의 의지가 없을 때 나타나는 귀신인데.</t>
@@ -61,7 +64,8 @@
     <t>삶에 미련을 놓는 순간 몽령이 찾아온대.</t>
   </si>
   <si>
-    <t>몽령은 너를 꿈속에 가두고 본인이 몸을 차지하려 하려고 할 거야.</t>
+    <t>&lt;color=red&gt;몽령&lt;/color&gt;은 너를 꿈속에 가두고 
+본인이 몸을 차지하려 하려고 할 거야.</t>
   </si>
   <si>
     <t>그러니까 무슨 일이 있어도.</t>
@@ -70,7 +74,7 @@
     <t>절대.. 삶의 의지를 놓아선 안돼.</t>
   </si>
   <si>
-    <t>만약.. 아주 만약 꿈속에서 몽령을 마주치게 된다면.</t>
+    <t>만약.. 아주 만약 꿈속에서 &lt;color=red&gt;몽령&lt;/color&gt;을 마주치게 된다면.</t>
   </si>
   <si>
     <t>살고 싶다는 마음을 가지고 뛰어.</t>
@@ -112,10 +116,10 @@
     <t>어렸을 때 엄마랑 자주 오던 공원이랑 똑같네..</t>
   </si>
   <si>
-    <t>엄마 보고싶다..</t>
-  </si>
-  <si>
-    <t>.....</t>
+    <t>엄마 보고 싶다..</t>
+  </si>
+  <si>
+    <t>.......</t>
   </si>
   <si>
     <t>Enemy</t>
@@ -130,58 +134,68 @@
     <t>엄마..?</t>
   </si>
   <si>
-    <t>...아</t>
+    <t>...아...</t>
   </si>
   <si>
     <t>엄마 맞아?</t>
   </si>
   <si>
-    <t>서린아.. 이리와</t>
+    <t>ㅅㅓ린ㅇㅏ.. 이ㄹㅣ 와...</t>
   </si>
   <si>
     <t>엄마!!</t>
   </si>
   <si>
-    <t>보고싶었어요</t>
-  </si>
-  <si>
-    <t>......ㄴ...ㅏ...도.....ㄱㅡ...래ㅆ.....다ㄴ.....다...</t>
-  </si>
-  <si>
-    <t>엄마?</t>
-  </si>
-  <si>
-    <t>어디갔었어요....한참 찾았잖아요.</t>
+    <t>보고 싶었어요..</t>
   </si>
   <si>
     <t>.................................</t>
   </si>
   <si>
-    <t>엄마...?</t>
+    <t>Extra</t>
+  </si>
+  <si>
+    <t>엄마</t>
+  </si>
+  <si>
+    <t>엄마...왜 말을 안하세요..?</t>
+  </si>
+  <si>
+    <t>......ㄴ...ㅏ...도.....
+ㄱㅡ...래ㅆ.....다ㄴ.....다...</t>
+  </si>
+  <si>
+    <t>뭐라고요? 잘 안 들려요</t>
+  </si>
+  <si>
+    <t>....................................</t>
   </si>
   <si>
     <t>....ㄱ......ㅏ....자.....</t>
   </si>
   <si>
-    <t>어딜 가자는거에요?</t>
+    <t>네....?</t>
+  </si>
+  <si>
+    <t>......ㄴㅏ....ㄹ....ㅏㅇ.....가....자....</t>
+  </si>
+  <si>
+    <t>어디를 가자는 거예요?</t>
+  </si>
+  <si>
+    <t>엄마? 왜 그래?</t>
   </si>
   <si>
     <t>........ㅇ....ㅓ.....ㅅㅓ.....가....자니까...!!!!!!</t>
   </si>
   <si>
-    <t>꺄악!!!!</t>
-  </si>
-  <si>
-    <t>왜....왜그러는거야?</t>
-  </si>
-  <si>
-    <t>......ㄴㅏ....ㄹ....ㅏㅇ.....가....자....</t>
-  </si>
-  <si>
-    <t>&lt;i&gt;그러고보니 엄마는 오래전에 돌아가셨어,,&lt;/i&gt;</t>
-  </si>
-  <si>
-    <t>&lt;i&gt;그럼 여기 있는건 누구지?&lt;/i&gt;</t>
+    <t>꺄아아악!!!!!!!!!!!!!!!!!!!!!!!!</t>
+  </si>
+  <si>
+    <t>&lt;i&gt;그러고 보니 엄마는 오래전에 돌아가셨어,,&lt;/i&gt;</t>
+  </si>
+  <si>
+    <t>&lt;i&gt;그럼 여기 있는 건 누구지?&lt;/i&gt;</t>
   </si>
   <si>
     <t>C001</t>
@@ -196,17 +210,19 @@
     <t>Choice2</t>
   </si>
   <si>
-    <t>엄마는 오래전에 돌아가셨어… 넌 엄마가 아니야.</t>
-  </si>
-  <si>
-    <t>엄마가 나한테 이럴리가 없어, 당신...누구야?</t>
+    <t xml:space="preserve"> 당신은 엄마가 아니야.
+너..누구야?</t>
+  </si>
+  <si>
+    <t>엄마 나야 서린이...
+왜 그러는 거야...?</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -216,6 +232,11 @@
     <font>
       <color theme="1"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <color rgb="FF434343"/>
@@ -252,7 +273,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="26">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -262,39 +283,48 @@
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
+    <xf borderId="0" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
     <xf borderId="0" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
     </xf>
@@ -302,10 +332,22 @@
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
@@ -343,7 +385,7 @@
       <border/>
     </dxf>
   </dxfs>
-  <tableStyles count="2">
+  <tableStyles count="3">
     <tableStyle count="2" pivot="0" name="Narration-style">
       <tableStyleElement dxfId="1" type="firstRowStripe"/>
       <tableStyleElement dxfId="2" type="secondRowStripe"/>
@@ -351,6 +393,10 @@
     <tableStyle count="2" pivot="0" name="Dialog-style">
       <tableStyleElement dxfId="2" type="firstRowStripe"/>
       <tableStyleElement dxfId="1" type="secondRowStripe"/>
+    </tableStyle>
+    <tableStyle count="2" pivot="0" name="Dialog-style 2">
+      <tableStyleElement dxfId="1" type="firstRowStripe"/>
+      <tableStyleElement dxfId="2" type="secondRowStripe"/>
     </tableStyle>
   </tableStyles>
 </styleSheet>
@@ -382,7 +428,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="C2:H25" displayName="Table_2" name="Table_2" id="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="C2:H28" displayName="Table_2" name="Table_2" id="2">
   <tableColumns count="6">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -392,6 +438,20 @@
     <tableColumn name="Column6" id="6"/>
   </tableColumns>
   <tableStyleInfo name="Dialog-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="L19:Q25" displayName="Table_3" name="Table_3" id="3">
+  <tableColumns count="6">
+    <tableColumn name="Column1" id="1"/>
+    <tableColumn name="Column2" id="2"/>
+    <tableColumn name="Column3" id="3"/>
+    <tableColumn name="Column4" id="4"/>
+    <tableColumn name="Column5" id="5"/>
+    <tableColumn name="Column6" id="6"/>
+  </tableColumns>
+  <tableStyleInfo name="Dialog-style 2" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
 </table>
 </file>
 
@@ -595,6 +655,9 @@
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="2" max="2" width="20.0"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
@@ -624,10 +687,10 @@
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="4" t="s">
         <v>8</v>
       </c>
       <c r="D3" s="2"/>
@@ -636,8 +699,8 @@
       <c r="A4" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>7</v>
+      <c r="B4" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>8</v>
@@ -664,10 +727,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2">
@@ -677,8 +740,8 @@
       <c r="B2" s="2">
         <v>1.0</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>12</v>
+      <c r="C2" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="3">
@@ -688,8 +751,8 @@
       <c r="B3" s="2">
         <v>2.0</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>13</v>
+      <c r="C3" s="6" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="4">
@@ -699,8 +762,8 @@
       <c r="B4" s="2">
         <v>3.0</v>
       </c>
-      <c r="C4" s="4" t="s">
-        <v>14</v>
+      <c r="C4" s="7" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="5">
@@ -710,8 +773,8 @@
       <c r="B5" s="2">
         <v>4.0</v>
       </c>
-      <c r="C5" s="4" t="s">
-        <v>15</v>
+      <c r="C5" s="8" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="6">
@@ -721,8 +784,8 @@
       <c r="B6" s="2">
         <v>5.0</v>
       </c>
-      <c r="C6" s="4" t="s">
-        <v>16</v>
+      <c r="C6" s="7" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="7">
@@ -732,8 +795,8 @@
       <c r="B7" s="2">
         <v>6.0</v>
       </c>
-      <c r="C7" s="4" t="s">
-        <v>17</v>
+      <c r="C7" s="7" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="8">
@@ -743,8 +806,8 @@
       <c r="B8" s="2">
         <v>7.0</v>
       </c>
-      <c r="C8" s="4" t="s">
-        <v>18</v>
+      <c r="C8" s="8" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="9">
@@ -754,8 +817,8 @@
       <c r="B9" s="2">
         <v>8.0</v>
       </c>
-      <c r="C9" s="5" t="s">
-        <v>19</v>
+      <c r="C9" s="8" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="10">
@@ -765,8 +828,8 @@
       <c r="B10" s="2">
         <v>9.0</v>
       </c>
-      <c r="C10" s="4" t="s">
-        <v>20</v>
+      <c r="C10" s="7" t="s">
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -785,594 +848,721 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
     <col customWidth="1" min="3" max="3" width="30.13"/>
+    <col customWidth="1" min="12" max="12" width="36.75"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="8">
+      <c r="B2" s="10">
         <v>2001.0</v>
       </c>
-      <c r="C2" s="9" t="s">
-        <v>28</v>
-      </c>
-      <c r="D2" s="10">
+      <c r="C2" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="D2" s="12">
         <v>2002.0</v>
       </c>
-      <c r="E2" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="F2" s="9" t="s">
+      <c r="E2" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="G2" s="11"/>
-      <c r="H2" s="11"/>
+      <c r="F2" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="G2" s="13"/>
+      <c r="H2" s="13"/>
     </row>
     <row r="3">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="8">
+      <c r="B3" s="10">
         <v>2002.0</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="7" t="s">
+        <v>32</v>
+      </c>
+      <c r="D3" s="14">
+        <v>2003.0</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="F3" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="D3" s="12">
+      <c r="G3" s="15"/>
+      <c r="H3" s="15"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="B4" s="10">
         <v>2003.0</v>
       </c>
-      <c r="E3" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="F3" s="4" t="s">
+      <c r="C4" s="16" t="s">
+        <v>33</v>
+      </c>
+      <c r="D4" s="12">
+        <v>2004.0</v>
+      </c>
+      <c r="E4" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="G3" s="13"/>
-      <c r="H3" s="13"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="7" t="s">
+      <c r="F4" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="G4" s="13"/>
+      <c r="H4" s="13"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="8">
-        <v>2003.0</v>
-      </c>
-      <c r="C4" s="9" t="s">
-        <v>32</v>
-      </c>
-      <c r="D4" s="10">
+      <c r="B5" s="10">
         <v>2004.0</v>
       </c>
-      <c r="E4" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="F4" s="9" t="s">
+      <c r="C5" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="D5" s="14">
+        <v>2005.0</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="F5" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="G5" s="15"/>
+      <c r="H5" s="15"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="B6" s="10">
+        <v>2005.0</v>
+      </c>
+      <c r="C6" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="D6" s="12">
+        <v>2006.0</v>
+      </c>
+      <c r="E6" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="G4" s="11"/>
-      <c r="H4" s="11"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="7" t="s">
+      <c r="F6" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="G6" s="13"/>
+      <c r="H6" s="13"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="8">
-        <v>2004.0</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="D5" s="12">
-        <v>2005.0</v>
-      </c>
-      <c r="E5" s="4" t="s">
+      <c r="B7" s="10">
+        <v>2006.0</v>
+      </c>
+      <c r="C7" s="8" t="s">
         <v>34</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="D7" s="14">
+        <v>2007.0</v>
+      </c>
+      <c r="E7" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="G5" s="13"/>
-      <c r="H5" s="13"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="7" t="s">
+      <c r="F7" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="G7" s="15"/>
+      <c r="H7" s="15"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="8">
-        <v>2005.0</v>
-      </c>
-      <c r="C6" s="9" t="s">
+      <c r="B8" s="10">
+        <v>2007.0</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="D8" s="12">
+        <v>2008.0</v>
+      </c>
+      <c r="E8" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="F8" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="G8" s="13"/>
+      <c r="H8" s="13"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9" s="10">
+        <v>2008.0</v>
+      </c>
+      <c r="C9" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="D9" s="14">
+        <v>2009.0</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="F9" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="D6" s="10">
-        <v>2006.0</v>
-      </c>
-      <c r="E6" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="F6" s="9" t="s">
+      <c r="G9" s="15"/>
+      <c r="H9" s="15"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="B10" s="10">
+        <v>2009.0</v>
+      </c>
+      <c r="C10" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="D10" s="12">
+        <v>2010.0</v>
+      </c>
+      <c r="E10" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="G6" s="11"/>
-      <c r="H6" s="11"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="7" t="s">
+      <c r="F10" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="G10" s="13"/>
+      <c r="H10" s="13"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="8">
-        <v>2006.0</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="D7" s="12">
-        <v>2007.0</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="F7" s="4" t="s">
+      <c r="B11" s="10">
+        <v>2010.0</v>
+      </c>
+      <c r="C11" s="8" t="s">
+        <v>41</v>
+      </c>
+      <c r="D11" s="14">
+        <v>2011.0</v>
+      </c>
+      <c r="E11" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="G7" s="13"/>
-      <c r="H7" s="13"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="7" t="s">
+      <c r="F11" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="G11" s="15"/>
+      <c r="H11" s="15"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="9" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="8">
-        <v>2007.0</v>
-      </c>
-      <c r="C8" s="9" t="s">
-        <v>37</v>
-      </c>
-      <c r="D8" s="10">
-        <v>2008.0</v>
-      </c>
-      <c r="E8" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="F8" s="9" t="s">
+      <c r="B12" s="10">
+        <v>2011.0</v>
+      </c>
+      <c r="C12" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="D12" s="12">
+        <v>-1.0</v>
+      </c>
+      <c r="E12" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="G8" s="11"/>
-      <c r="H8" s="11"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B9" s="8">
-        <v>2008.0</v>
-      </c>
-      <c r="C9" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="D9" s="12">
-        <v>2009.0</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="F9" s="4" t="s">
+      <c r="F12" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="G12" s="13"/>
+      <c r="H12" s="13"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="B13" s="18">
+        <v>3001.0</v>
+      </c>
+      <c r="C13" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="D13" s="20">
+        <v>3002.0</v>
+      </c>
+      <c r="E13" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G13" s="15"/>
+      <c r="H13" s="21">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="B14" s="18">
+        <v>3002.0</v>
+      </c>
+      <c r="C14" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="D14" s="22">
+        <v>3003.0</v>
+      </c>
+      <c r="E14" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="F14" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="G14" s="13"/>
+      <c r="H14" s="24">
+        <v>5.0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="B15" s="18">
+        <v>3003.0</v>
+      </c>
+      <c r="C15" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="D15" s="20">
+        <v>3004.0</v>
+      </c>
+      <c r="E15" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G15" s="15"/>
+      <c r="H15" s="21">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="B16" s="18">
+        <v>3004.0</v>
+      </c>
+      <c r="C16" s="23" t="s">
+        <v>48</v>
+      </c>
+      <c r="D16" s="22">
+        <v>3005.0</v>
+      </c>
+      <c r="E16" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="F16" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="G16" s="13"/>
+      <c r="H16" s="24">
+        <v>5.0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="B17" s="18">
+        <v>3005.0</v>
+      </c>
+      <c r="C17" s="19" t="s">
+        <v>49</v>
+      </c>
+      <c r="D17" s="20">
+        <v>3006.0</v>
+      </c>
+      <c r="E17" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G17" s="15"/>
+      <c r="H17" s="20">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="B18" s="18">
+        <v>3006.0</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="D18" s="22">
+        <v>3007.0</v>
+      </c>
+      <c r="E18" s="23" t="s">
+        <v>45</v>
+      </c>
+      <c r="F18" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="G18" s="13"/>
+      <c r="H18" s="24">
+        <v>5.0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="B19" s="18">
+        <v>3007.0</v>
+      </c>
+      <c r="C19" s="13" t="s">
+        <v>51</v>
+      </c>
+      <c r="D19" s="20">
+        <v>3008.0</v>
+      </c>
+      <c r="E19" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="F19" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="G19" s="15"/>
+      <c r="H19" s="21">
+        <v>6.0</v>
+      </c>
+      <c r="J19" s="17"/>
+      <c r="K19" s="18"/>
+      <c r="L19" s="15"/>
+      <c r="M19" s="20"/>
+      <c r="N19" s="15"/>
+      <c r="O19" s="7"/>
+      <c r="P19" s="15"/>
+      <c r="Q19" s="20"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="B20" s="18">
+        <v>3008.0</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="D20" s="22">
+        <v>3009.0</v>
+      </c>
+      <c r="E20" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="F20" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="G20" s="13"/>
+      <c r="H20" s="24">
+        <v>2.0</v>
+      </c>
+      <c r="J20" s="17"/>
+      <c r="K20" s="18"/>
+      <c r="L20" s="13"/>
+      <c r="M20" s="22"/>
+      <c r="N20" s="13"/>
+      <c r="O20" s="16"/>
+      <c r="P20" s="13"/>
+      <c r="Q20" s="22"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="B21" s="18">
+        <v>3009.0</v>
+      </c>
+      <c r="C21" s="15" t="s">
+        <v>53</v>
+      </c>
+      <c r="D21" s="20">
+        <v>3010.0</v>
+      </c>
+      <c r="E21" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="G9" s="13"/>
-      <c r="H9" s="13"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B10" s="8">
-        <v>2009.0</v>
-      </c>
-      <c r="C10" s="9" t="s">
-        <v>39</v>
-      </c>
-      <c r="D10" s="10">
-        <v>2010.0</v>
-      </c>
-      <c r="E10" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="F10" s="9" t="s">
+      <c r="F21" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="G21" s="15"/>
+      <c r="H21" s="21">
+        <v>6.0</v>
+      </c>
+      <c r="J21" s="17"/>
+      <c r="K21" s="18"/>
+      <c r="L21" s="15"/>
+      <c r="M21" s="20"/>
+      <c r="N21" s="15"/>
+      <c r="O21" s="7"/>
+      <c r="P21" s="15"/>
+      <c r="Q21" s="20"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="B22" s="18">
+        <v>3010.0</v>
+      </c>
+      <c r="C22" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="D22" s="22">
+        <v>3011.0</v>
+      </c>
+      <c r="E22" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="G10" s="11"/>
-      <c r="H10" s="11"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B11" s="8">
-        <v>2010.0</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="D11" s="12">
-        <v>2011.0</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="F11" s="4" t="s">
+      <c r="F22" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="G22" s="13"/>
+      <c r="H22" s="22">
+        <v>2.0</v>
+      </c>
+      <c r="J22" s="17"/>
+      <c r="K22" s="18"/>
+      <c r="L22" s="13"/>
+      <c r="M22" s="22"/>
+      <c r="N22" s="13"/>
+      <c r="O22" s="11"/>
+      <c r="P22" s="13"/>
+      <c r="Q22" s="22"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="B23" s="18">
+        <v>3011.0</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="D23" s="20">
+        <v>3012.0</v>
+      </c>
+      <c r="E23" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="G11" s="13"/>
-      <c r="H11" s="13"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B12" s="8">
-        <v>2011.0</v>
-      </c>
-      <c r="C12" s="9" t="s">
-        <v>41</v>
-      </c>
-      <c r="D12" s="10">
+      <c r="F23" s="8" t="s">
+        <v>46</v>
+      </c>
+      <c r="G23" s="15"/>
+      <c r="H23" s="21">
+        <v>5.0</v>
+      </c>
+      <c r="J23" s="17"/>
+      <c r="K23" s="18"/>
+      <c r="L23" s="15"/>
+      <c r="M23" s="20"/>
+      <c r="N23" s="15"/>
+      <c r="O23" s="8"/>
+      <c r="P23" s="15"/>
+      <c r="Q23" s="20"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="B24" s="17">
+        <v>3012.0</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="D24" s="22">
+        <v>3013.0</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="H24" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="J24" s="17"/>
+      <c r="K24" s="18"/>
+      <c r="L24" s="13"/>
+      <c r="M24" s="22"/>
+      <c r="N24" s="13"/>
+      <c r="O24" s="11"/>
+      <c r="P24" s="13"/>
+      <c r="Q24" s="22"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="B25" s="18">
+        <v>3013.0</v>
+      </c>
+      <c r="C25" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="D25" s="20">
+        <v>3014.0</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="H25" s="4">
+        <v>7.0</v>
+      </c>
+      <c r="J25" s="17"/>
+      <c r="K25" s="18"/>
+      <c r="L25" s="15"/>
+      <c r="M25" s="14"/>
+      <c r="N25" s="15"/>
+      <c r="O25" s="7"/>
+      <c r="P25" s="15"/>
+      <c r="Q25" s="20"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="B26" s="17">
+        <v>3014.0</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="D26" s="22">
+        <v>3015.0</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="H26" s="4">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="B27" s="18">
+        <v>3015.0</v>
+      </c>
+      <c r="C27" s="23" t="s">
+        <v>58</v>
+      </c>
+      <c r="D27" s="20">
+        <v>3016.0</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="F27" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="G27" s="13"/>
+      <c r="H27" s="22">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="B28" s="17">
+        <v>3016.0</v>
+      </c>
+      <c r="C28" s="19" t="s">
+        <v>59</v>
+      </c>
+      <c r="D28" s="14">
         <v>-1.0</v>
       </c>
-      <c r="E12" s="9" t="s">
-        <v>29</v>
-      </c>
-      <c r="F12" s="9" t="s">
+      <c r="E28" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="G12" s="11"/>
-      <c r="H12" s="11"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="B13" s="15">
-        <v>3001.0</v>
-      </c>
-      <c r="C13" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="D13" s="16">
-        <v>3002.0</v>
-      </c>
-      <c r="E13" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="G13" s="13"/>
-      <c r="H13" s="16">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="B14" s="15">
-        <v>3002.0</v>
-      </c>
-      <c r="C14" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="D14" s="17">
-        <v>3003.0</v>
-      </c>
-      <c r="E14" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="F14" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="G14" s="11"/>
-      <c r="H14" s="17">
-        <v>-1.0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="B15" s="15">
-        <v>3003.0</v>
-      </c>
-      <c r="C15" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="D15" s="16">
-        <v>3004.0</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="G15" s="13"/>
-      <c r="H15" s="16">
-        <v>1.0</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="B16" s="15">
-        <v>3004.0</v>
-      </c>
-      <c r="C16" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="D16" s="17">
-        <v>3005.0</v>
-      </c>
-      <c r="E16" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="F16" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="G16" s="11"/>
-      <c r="H16" s="17">
-        <v>-1.0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="B17" s="15">
-        <v>3005.0</v>
-      </c>
-      <c r="C17" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="D17" s="16">
-        <v>3006.0</v>
-      </c>
-      <c r="E17" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="F17" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="G17" s="13"/>
-      <c r="H17" s="16">
-        <v>2.0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="B18" s="15">
-        <v>3006.0</v>
-      </c>
-      <c r="C18" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="D18" s="17">
-        <v>3007.0</v>
-      </c>
-      <c r="E18" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="F18" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="G18" s="11"/>
-      <c r="H18" s="17">
-        <v>-1.0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="B19" s="15">
-        <v>3007.0</v>
-      </c>
-      <c r="C19" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="D19" s="16">
-        <v>3008.0</v>
-      </c>
-      <c r="E19" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="F19" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="G19" s="13"/>
-      <c r="H19" s="16">
-        <v>2.0</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="B20" s="15">
-        <v>3008.0</v>
-      </c>
-      <c r="C20" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="D20" s="17">
-        <v>3009.0</v>
-      </c>
-      <c r="E20" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="F20" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="G20" s="11"/>
-      <c r="H20" s="17">
-        <v>-1.0</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="B21" s="15">
-        <v>3009.0</v>
-      </c>
-      <c r="C21" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="D21" s="16">
-        <v>3010.0</v>
-      </c>
-      <c r="E21" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="F21" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="G21" s="13"/>
-      <c r="H21" s="16">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="B22" s="15">
-        <v>3010.0</v>
-      </c>
-      <c r="C22" s="11" t="s">
-        <v>52</v>
-      </c>
-      <c r="D22" s="17">
-        <v>3011.0</v>
-      </c>
-      <c r="E22" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="F22" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="G22" s="11"/>
-      <c r="H22" s="17">
-        <v>2.0</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="B23" s="15">
-        <v>3011.0</v>
-      </c>
-      <c r="C23" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="D23" s="16">
-        <v>3012.0</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="F23" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="G23" s="13"/>
-      <c r="H23" s="16">
-        <v>-1.0</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="B24" s="15">
-        <v>3012.0</v>
-      </c>
-      <c r="C24" s="11" t="s">
-        <v>54</v>
-      </c>
-      <c r="D24" s="17">
-        <v>3013.0</v>
-      </c>
-      <c r="E24" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="F24" s="9" t="s">
-        <v>30</v>
-      </c>
-      <c r="G24" s="11"/>
-      <c r="H24" s="17">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="14" t="s">
-        <v>9</v>
-      </c>
-      <c r="B25" s="15">
-        <v>3013.0</v>
-      </c>
-      <c r="C25" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="D25" s="12">
-        <v>-1.0</v>
-      </c>
-      <c r="E25" s="13" t="s">
-        <v>29</v>
-      </c>
-      <c r="F25" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="G25" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="H25" s="16">
+      <c r="F28" s="7" t="s">
+        <v>31</v>
+      </c>
+      <c r="G28" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="H28" s="20">
         <v>0.0</v>
       </c>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
-  <tableParts count="1">
-    <tablePart r:id="rId3"/>
+  <tableParts count="2">
+    <tablePart r:id="rId4"/>
+    <tablePart r:id="rId5"/>
   </tableParts>
 </worksheet>
 </file>
@@ -1384,34 +1574,34 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col customWidth="1" min="2" max="2" width="34.75"/>
-    <col customWidth="1" min="3" max="3" width="32.88"/>
+    <col customWidth="1" min="2" max="2" width="23.63"/>
+    <col customWidth="1" min="3" max="3" width="24.38"/>
     <col customWidth="1" min="4" max="4" width="31.63"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="18" t="s">
-        <v>56</v>
-      </c>
-      <c r="B2" s="15" t="s">
+      <c r="A2" s="25" t="s">
         <v>60</v>
       </c>
-      <c r="C2" s="15" t="s">
-        <v>61</v>
+      <c r="B2" s="17" t="s">
+        <v>64</v>
+      </c>
+      <c r="C2" s="17" t="s">
+        <v>65</v>
       </c>
       <c r="D2" s="1"/>
     </row>

--- a/Assets/02Script/Table/EventTable.xlsx
+++ b/Assets/02Script/Table/EventTable.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="77">
   <si>
     <t>EventID</t>
   </si>
@@ -49,6 +49,18 @@
     <t>Tutorial_Conversation</t>
   </si>
   <si>
+    <t>E004</t>
+  </si>
+  <si>
+    <t>Tutorial_Dead</t>
+  </si>
+  <si>
+    <t>E005</t>
+  </si>
+  <si>
+    <t>RealGame_Start</t>
+  </si>
+  <si>
     <t>Order</t>
   </si>
   <si>
@@ -64,7 +76,7 @@
     <t>삶에 미련을 놓는 순간 몽령이 찾아온대.</t>
   </si>
   <si>
-    <t>&lt;color=red&gt;몽령&lt;/color&gt;은 너를 꿈속에 가두고 
+    <t>몽령은 너를 꿈속에 가두고 
 본인이 몸을 차지하려 하려고 할 거야.</t>
   </si>
   <si>
@@ -74,7 +86,8 @@
     <t>절대.. 삶의 의지를 놓아선 안돼.</t>
   </si>
   <si>
-    <t>만약.. 아주 만약 꿈속에서 &lt;color=red&gt;몽령&lt;/color&gt;을 마주치게 된다면.</t>
+    <t>만약.. 아주 만약.... 
+꿈속에서 몽령을 마주치게 된다면.</t>
   </si>
   <si>
     <t>살고 싶다는 마음을 가지고 뛰어.</t>
@@ -199,6 +212,27 @@
   </si>
   <si>
     <t>C001</t>
+  </si>
+  <si>
+    <t>.....</t>
+  </si>
+  <si>
+    <t>...........</t>
+  </si>
+  <si>
+    <t>꺄아아아아악!</t>
+  </si>
+  <si>
+    <t>뭐...뭐였지????</t>
+  </si>
+  <si>
+    <t>아까 거기잖아...</t>
+  </si>
+  <si>
+    <t>다시 돌아온건가?</t>
+  </si>
+  <si>
+    <t>&lt;i&gt;아까 그 괴물이 다시 나타날지도 모르니 우선 움직여볼까&lt;/i&gt;</t>
   </si>
   <si>
     <t>Choice0</t>
@@ -273,7 +307,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="37">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -316,6 +350,9 @@
     <xf borderId="0" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
+    <xf borderId="0" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
     <xf borderId="0" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -344,10 +381,38 @@
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="right" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
@@ -428,7 +493,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="C2:H28" displayName="Table_2" name="Table_2" id="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="C2:H36" displayName="Table_2" name="Table_2" id="2">
   <tableColumns count="6">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -707,6 +772,28 @@
       </c>
       <c r="D4" s="2"/>
     </row>
+    <row r="5">
+      <c r="A5" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -727,10 +814,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2">
@@ -741,7 +828,7 @@
         <v>1.0</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3">
@@ -752,7 +839,7 @@
         <v>2.0</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4">
@@ -763,7 +850,7 @@
         <v>3.0</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>15</v>
+        <v>19</v>
       </c>
     </row>
     <row r="5">
@@ -774,7 +861,7 @@
         <v>4.0</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6">
@@ -785,7 +872,7 @@
         <v>5.0</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7">
@@ -796,7 +883,7 @@
         <v>6.0</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>18</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8">
@@ -807,7 +894,7 @@
         <v>7.0</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9">
@@ -818,7 +905,7 @@
         <v>8.0</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10">
@@ -829,7 +916,7 @@
         <v>9.0</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -856,25 +943,25 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>28</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2">
@@ -885,19 +972,21 @@
         <v>2001.0</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>29</v>
+        <v>33</v>
       </c>
       <c r="D2" s="12">
         <v>2002.0</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="G2" s="13"/>
-      <c r="H2" s="13"/>
+      <c r="H2" s="14">
+        <v>-1.0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="9" t="s">
@@ -907,19 +996,21 @@
         <v>2002.0</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>32</v>
-      </c>
-      <c r="D3" s="14">
+        <v>36</v>
+      </c>
+      <c r="D3" s="15">
         <v>2003.0</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="G3" s="15"/>
-      <c r="H3" s="15"/>
+        <v>35</v>
+      </c>
+      <c r="G3" s="16"/>
+      <c r="H3" s="14">
+        <v>-1.0</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="9" t="s">
@@ -928,20 +1019,22 @@
       <c r="B4" s="10">
         <v>2003.0</v>
       </c>
-      <c r="C4" s="16" t="s">
-        <v>33</v>
+      <c r="C4" s="17" t="s">
+        <v>37</v>
       </c>
       <c r="D4" s="12">
         <v>2004.0</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="G4" s="13"/>
-      <c r="H4" s="13"/>
+      <c r="H4" s="14">
+        <v>-1.0</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="9" t="s">
@@ -951,19 +1044,21 @@
         <v>2004.0</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="D5" s="14">
+        <v>38</v>
+      </c>
+      <c r="D5" s="15">
         <v>2005.0</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="G5" s="15"/>
-      <c r="H5" s="15"/>
+        <v>40</v>
+      </c>
+      <c r="G5" s="16"/>
+      <c r="H5" s="14">
+        <v>-1.0</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="9" t="s">
@@ -973,19 +1068,21 @@
         <v>2005.0</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="D6" s="12">
         <v>2006.0</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="G6" s="13"/>
-      <c r="H6" s="13"/>
+      <c r="H6" s="14">
+        <v>-1.0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="9" t="s">
@@ -995,19 +1092,21 @@
         <v>2006.0</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="D7" s="14">
+        <v>38</v>
+      </c>
+      <c r="D7" s="15">
         <v>2007.0</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="G7" s="15"/>
-      <c r="H7" s="15"/>
+        <v>40</v>
+      </c>
+      <c r="G7" s="16"/>
+      <c r="H7" s="14">
+        <v>-1.0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="9" t="s">
@@ -1017,19 +1116,21 @@
         <v>2007.0</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="D8" s="12">
         <v>2008.0</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="G8" s="13"/>
-      <c r="H8" s="13"/>
+      <c r="H8" s="14">
+        <v>-1.0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="9" t="s">
@@ -1039,19 +1140,21 @@
         <v>2008.0</v>
       </c>
       <c r="C9" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="D9" s="15">
+        <v>2009.0</v>
+      </c>
+      <c r="E9" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="D9" s="14">
-        <v>2009.0</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>35</v>
-      </c>
       <c r="F9" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="G9" s="15"/>
-      <c r="H9" s="15"/>
+        <v>40</v>
+      </c>
+      <c r="G9" s="16"/>
+      <c r="H9" s="14">
+        <v>-1.0</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="9" t="s">
@@ -1061,19 +1164,21 @@
         <v>2009.0</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="D10" s="12">
         <v>2010.0</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="G10" s="13"/>
-      <c r="H10" s="13"/>
+      <c r="H10" s="14">
+        <v>-1.0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="9" t="s">
@@ -1083,19 +1188,21 @@
         <v>2010.0</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>41</v>
-      </c>
-      <c r="D11" s="14">
+        <v>45</v>
+      </c>
+      <c r="D11" s="15">
         <v>2011.0</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="G11" s="15"/>
-      <c r="H11" s="15"/>
+        <v>40</v>
+      </c>
+      <c r="G11" s="16"/>
+      <c r="H11" s="14">
+        <v>-1.0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="9" t="s">
@@ -1105,62 +1212,64 @@
         <v>2011.0</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="D12" s="12">
         <v>-1.0</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="G12" s="13"/>
-      <c r="H12" s="13"/>
+      <c r="H12" s="14">
+        <v>-1.0</v>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="17" t="s">
+      <c r="A13" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="18">
+      <c r="B13" s="19">
         <v>3001.0</v>
       </c>
-      <c r="C13" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="D13" s="20">
+      <c r="C13" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="D13" s="21">
         <v>3002.0</v>
       </c>
-      <c r="E13" s="15" t="s">
-        <v>30</v>
+      <c r="E13" s="16" t="s">
+        <v>34</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="G13" s="15"/>
-      <c r="H13" s="21">
+        <v>35</v>
+      </c>
+      <c r="G13" s="16"/>
+      <c r="H13" s="22">
         <v>4.0</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="17" t="s">
+      <c r="A14" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="18">
+      <c r="B14" s="19">
         <v>3002.0</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>44</v>
-      </c>
-      <c r="D14" s="22">
+        <v>48</v>
+      </c>
+      <c r="D14" s="23">
         <v>3003.0</v>
       </c>
-      <c r="E14" s="23" t="s">
-        <v>45</v>
-      </c>
-      <c r="F14" s="16" t="s">
-        <v>46</v>
+      <c r="E14" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="F14" s="17" t="s">
+        <v>50</v>
       </c>
       <c r="G14" s="13"/>
       <c r="H14" s="24">
@@ -1168,47 +1277,47 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="17" t="s">
+      <c r="A15" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="B15" s="18">
+      <c r="B15" s="19">
         <v>3003.0</v>
       </c>
-      <c r="C15" s="19" t="s">
-        <v>47</v>
-      </c>
-      <c r="D15" s="20">
+      <c r="C15" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="D15" s="21">
         <v>3004.0</v>
       </c>
-      <c r="E15" s="15" t="s">
-        <v>30</v>
+      <c r="E15" s="16" t="s">
+        <v>34</v>
       </c>
       <c r="F15" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="G15" s="15"/>
-      <c r="H15" s="21">
+        <v>35</v>
+      </c>
+      <c r="G15" s="16"/>
+      <c r="H15" s="22">
         <v>2.0</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="17" t="s">
+      <c r="A16" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="B16" s="18">
+      <c r="B16" s="19">
         <v>3004.0</v>
       </c>
-      <c r="C16" s="23" t="s">
-        <v>48</v>
-      </c>
-      <c r="D16" s="22">
+      <c r="C16" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="D16" s="23">
         <v>3005.0</v>
       </c>
-      <c r="E16" s="23" t="s">
-        <v>45</v>
-      </c>
-      <c r="F16" s="16" t="s">
-        <v>46</v>
+      <c r="E16" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="F16" s="17" t="s">
+        <v>50</v>
       </c>
       <c r="G16" s="13"/>
       <c r="H16" s="24">
@@ -1216,47 +1325,47 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="17" t="s">
+      <c r="A17" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="B17" s="18">
+      <c r="B17" s="19">
         <v>3005.0</v>
       </c>
-      <c r="C17" s="19" t="s">
+      <c r="C17" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="D17" s="21">
+        <v>3006.0</v>
+      </c>
+      <c r="E17" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="G17" s="16"/>
+      <c r="H17" s="21">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="B18" s="19">
+        <v>3006.0</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D18" s="23">
+        <v>3007.0</v>
+      </c>
+      <c r="E18" s="14" t="s">
         <v>49</v>
       </c>
-      <c r="D17" s="20">
-        <v>3006.0</v>
-      </c>
-      <c r="E17" s="15" t="s">
-        <v>30</v>
-      </c>
-      <c r="F17" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="G17" s="15"/>
-      <c r="H17" s="20">
-        <v>2.0</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="B18" s="18">
-        <v>3006.0</v>
-      </c>
-      <c r="C18" s="4" t="s">
+      <c r="F18" s="17" t="s">
         <v>50</v>
-      </c>
-      <c r="D18" s="22">
-        <v>3007.0</v>
-      </c>
-      <c r="E18" s="23" t="s">
-        <v>45</v>
-      </c>
-      <c r="F18" s="16" t="s">
-        <v>46</v>
       </c>
       <c r="G18" s="13"/>
       <c r="H18" s="24">
@@ -1264,298 +1373,486 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="17" t="s">
+      <c r="A19" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="B19" s="18">
+      <c r="B19" s="19">
         <v>3007.0</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="D19" s="20">
+        <v>55</v>
+      </c>
+      <c r="D19" s="21">
         <v>3008.0</v>
       </c>
-      <c r="E19" s="19" t="s">
-        <v>45</v>
+      <c r="E19" s="20" t="s">
+        <v>49</v>
       </c>
       <c r="F19" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="G19" s="15"/>
-      <c r="H19" s="21">
+        <v>50</v>
+      </c>
+      <c r="G19" s="16"/>
+      <c r="H19" s="22">
         <v>6.0</v>
       </c>
-      <c r="J19" s="17"/>
-      <c r="K19" s="18"/>
-      <c r="L19" s="15"/>
-      <c r="M19" s="20"/>
-      <c r="N19" s="15"/>
-      <c r="O19" s="7"/>
-      <c r="P19" s="15"/>
-      <c r="Q19" s="20"/>
+      <c r="J19" s="25"/>
+      <c r="K19" s="2"/>
+      <c r="L19" s="26"/>
+      <c r="M19" s="27"/>
+      <c r="N19" s="26"/>
+      <c r="O19" s="28"/>
+      <c r="P19" s="26"/>
+      <c r="Q19" s="27"/>
     </row>
     <row r="20">
-      <c r="A20" s="17" t="s">
+      <c r="A20" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="B20" s="18">
+      <c r="B20" s="19">
         <v>3008.0</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="D20" s="22">
+        <v>56</v>
+      </c>
+      <c r="D20" s="23">
         <v>3009.0</v>
       </c>
-      <c r="E20" s="23" t="s">
-        <v>30</v>
-      </c>
-      <c r="F20" s="16" t="s">
-        <v>31</v>
+      <c r="E20" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="F20" s="17" t="s">
+        <v>35</v>
       </c>
       <c r="G20" s="13"/>
       <c r="H20" s="24">
         <v>2.0</v>
       </c>
-      <c r="J20" s="17"/>
-      <c r="K20" s="18"/>
-      <c r="L20" s="13"/>
-      <c r="M20" s="22"/>
-      <c r="N20" s="13"/>
-      <c r="O20" s="16"/>
-      <c r="P20" s="13"/>
-      <c r="Q20" s="22"/>
+      <c r="J20" s="25"/>
+      <c r="K20" s="2"/>
+      <c r="L20" s="29"/>
+      <c r="M20" s="30"/>
+      <c r="N20" s="31"/>
+      <c r="O20" s="32"/>
+      <c r="P20" s="31"/>
+      <c r="Q20" s="30"/>
     </row>
     <row r="21">
-      <c r="A21" s="17" t="s">
+      <c r="A21" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="B21" s="18">
+      <c r="B21" s="19">
         <v>3009.0</v>
       </c>
-      <c r="C21" s="15" t="s">
-        <v>53</v>
-      </c>
-      <c r="D21" s="20">
+      <c r="C21" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="D21" s="21">
         <v>3010.0</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="F21" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="G21" s="15"/>
-      <c r="H21" s="21">
+        <v>50</v>
+      </c>
+      <c r="G21" s="16"/>
+      <c r="H21" s="22">
         <v>6.0</v>
       </c>
-      <c r="J21" s="17"/>
-      <c r="K21" s="18"/>
-      <c r="L21" s="15"/>
-      <c r="M21" s="20"/>
-      <c r="N21" s="15"/>
-      <c r="O21" s="7"/>
-      <c r="P21" s="15"/>
-      <c r="Q21" s="20"/>
+      <c r="J21" s="25"/>
+      <c r="K21" s="2"/>
+      <c r="L21" s="31"/>
+      <c r="M21" s="30"/>
+      <c r="N21" s="31"/>
+      <c r="O21" s="33"/>
+      <c r="P21" s="31"/>
+      <c r="Q21" s="30"/>
     </row>
     <row r="22">
-      <c r="A22" s="17" t="s">
+      <c r="A22" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="B22" s="18">
+      <c r="B22" s="19">
         <v>3010.0</v>
       </c>
-      <c r="C22" s="19" t="s">
+      <c r="C22" s="20" t="s">
+        <v>58</v>
+      </c>
+      <c r="D22" s="23">
+        <v>3011.0</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="F22" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="G22" s="13"/>
+      <c r="H22" s="23">
+        <v>2.0</v>
+      </c>
+      <c r="J22" s="25"/>
+      <c r="K22" s="2"/>
+      <c r="L22" s="31"/>
+      <c r="M22" s="30"/>
+      <c r="N22" s="31"/>
+      <c r="O22" s="33"/>
+      <c r="P22" s="31"/>
+      <c r="Q22" s="30"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="18" t="s">
+        <v>9</v>
+      </c>
+      <c r="B23" s="19">
+        <v>3011.0</v>
+      </c>
+      <c r="C23" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="D22" s="22">
-        <v>3011.0</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>30</v>
-      </c>
-      <c r="F22" s="11" t="s">
-        <v>31</v>
-      </c>
-      <c r="G22" s="13"/>
-      <c r="H22" s="22">
-        <v>2.0</v>
-      </c>
-      <c r="J22" s="17"/>
-      <c r="K22" s="18"/>
-      <c r="L22" s="13"/>
-      <c r="M22" s="22"/>
-      <c r="N22" s="13"/>
-      <c r="O22" s="11"/>
-      <c r="P22" s="13"/>
-      <c r="Q22" s="22"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="17" t="s">
+      <c r="D23" s="21">
+        <v>3012.0</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="F23" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="G23" s="16"/>
+      <c r="H23" s="22">
+        <v>5.0</v>
+      </c>
+      <c r="J23" s="25"/>
+      <c r="K23" s="2"/>
+      <c r="L23" s="31"/>
+      <c r="M23" s="30"/>
+      <c r="N23" s="31"/>
+      <c r="O23" s="32"/>
+      <c r="P23" s="31"/>
+      <c r="Q23" s="30"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="B23" s="18">
-        <v>3011.0</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="D23" s="20">
+      <c r="B24" s="18">
         <v>3012.0</v>
       </c>
-      <c r="E23" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="F23" s="8" t="s">
-        <v>46</v>
-      </c>
-      <c r="G23" s="15"/>
-      <c r="H23" s="21">
-        <v>5.0</v>
-      </c>
-      <c r="J23" s="17"/>
-      <c r="K23" s="18"/>
-      <c r="L23" s="15"/>
-      <c r="M23" s="20"/>
-      <c r="N23" s="15"/>
-      <c r="O23" s="8"/>
-      <c r="P23" s="15"/>
-      <c r="Q23" s="20"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="B24" s="17">
-        <v>3012.0</v>
-      </c>
       <c r="C24" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="D24" s="22">
+        <v>59</v>
+      </c>
+      <c r="D24" s="23">
         <v>3013.0</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H24" s="4">
         <v>2.0</v>
       </c>
-      <c r="J24" s="17"/>
-      <c r="K24" s="18"/>
-      <c r="L24" s="13"/>
-      <c r="M24" s="22"/>
-      <c r="N24" s="13"/>
-      <c r="O24" s="11"/>
-      <c r="P24" s="13"/>
-      <c r="Q24" s="22"/>
+      <c r="J24" s="25"/>
+      <c r="K24" s="2"/>
+      <c r="L24" s="31"/>
+      <c r="M24" s="30"/>
+      <c r="N24" s="31"/>
+      <c r="O24" s="33"/>
+      <c r="P24" s="31"/>
+      <c r="Q24" s="30"/>
     </row>
     <row r="25">
-      <c r="A25" s="17" t="s">
+      <c r="A25" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="B25" s="18">
+      <c r="B25" s="19">
         <v>3013.0</v>
       </c>
       <c r="C25" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="D25" s="20">
+        <v>60</v>
+      </c>
+      <c r="D25" s="21">
         <v>3014.0</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>35</v>
+        <v>39</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="H25" s="4">
         <v>7.0</v>
       </c>
-      <c r="J25" s="17"/>
-      <c r="K25" s="18"/>
-      <c r="L25" s="15"/>
-      <c r="M25" s="14"/>
-      <c r="N25" s="15"/>
-      <c r="O25" s="7"/>
-      <c r="P25" s="15"/>
-      <c r="Q25" s="20"/>
+      <c r="J25" s="25"/>
+      <c r="K25" s="2"/>
+      <c r="L25" s="26"/>
+      <c r="M25" s="34"/>
+      <c r="N25" s="26"/>
+      <c r="O25" s="28"/>
+      <c r="P25" s="26"/>
+      <c r="Q25" s="27"/>
     </row>
     <row r="26">
-      <c r="A26" s="17" t="s">
+      <c r="A26" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="B26" s="17">
+      <c r="B26" s="18">
         <v>3014.0</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>57</v>
-      </c>
-      <c r="D26" s="22">
+        <v>61</v>
+      </c>
+      <c r="D26" s="23">
         <v>3015.0</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="H26" s="4">
         <v>2.0</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="17" t="s">
+      <c r="A27" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="B27" s="18">
+      <c r="B27" s="19">
         <v>3015.0</v>
       </c>
-      <c r="C27" s="23" t="s">
-        <v>58</v>
-      </c>
-      <c r="D27" s="20">
+      <c r="C27" s="14" t="s">
+        <v>62</v>
+      </c>
+      <c r="D27" s="21">
         <v>3016.0</v>
       </c>
       <c r="E27" s="13" t="s">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="F27" s="11" t="s">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="G27" s="13"/>
-      <c r="H27" s="22">
+      <c r="H27" s="23">
         <v>0.0</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="17" t="s">
+      <c r="A28" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="B28" s="17">
+      <c r="B28" s="18">
         <v>3016.0</v>
       </c>
-      <c r="C28" s="19" t="s">
-        <v>59</v>
-      </c>
-      <c r="D28" s="14">
+      <c r="C28" s="20" t="s">
+        <v>63</v>
+      </c>
+      <c r="D28" s="15">
         <v>-1.0</v>
       </c>
-      <c r="E28" s="15" t="s">
-        <v>30</v>
+      <c r="E28" s="16" t="s">
+        <v>34</v>
       </c>
       <c r="F28" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="G28" s="15" t="s">
-        <v>60</v>
-      </c>
-      <c r="H28" s="20">
+        <v>35</v>
+      </c>
+      <c r="G28" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="H28" s="21">
         <v>0.0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="B29" s="4">
+        <v>4001.0</v>
+      </c>
+      <c r="C29" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="D29" s="35">
+        <v>4002.0</v>
+      </c>
+      <c r="E29" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="F29" s="7"/>
+      <c r="G29" s="16"/>
+      <c r="H29" s="22">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="B30" s="4">
+        <v>4002.0</v>
+      </c>
+      <c r="C30" s="20" t="s">
+        <v>66</v>
+      </c>
+      <c r="D30" s="35">
+        <v>-1.0</v>
+      </c>
+      <c r="E30" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="F30" s="7"/>
+      <c r="G30" s="16"/>
+      <c r="H30" s="22">
+        <v>-1.0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="B31" s="4">
+        <v>5001.0</v>
+      </c>
+      <c r="C31" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="D31" s="4">
+        <v>5002.0</v>
+      </c>
+      <c r="E31" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="F31" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="G31" s="16"/>
+      <c r="H31" s="22">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="B32" s="4">
+        <v>5002.0</v>
+      </c>
+      <c r="C32" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="D32" s="4">
+        <v>5003.0</v>
+      </c>
+      <c r="E32" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="F32" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="G32" s="16"/>
+      <c r="H32" s="22">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="B33" s="4">
+        <v>5003.0</v>
+      </c>
+      <c r="C33" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="D33" s="4">
+        <v>5004.0</v>
+      </c>
+      <c r="E33" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="F33" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="G33" s="16"/>
+      <c r="H33" s="22">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="B34" s="4">
+        <v>5004.0</v>
+      </c>
+      <c r="C34" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="D34" s="4">
+        <v>5005.0</v>
+      </c>
+      <c r="E34" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="F34" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="G34" s="16"/>
+      <c r="H34" s="22">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="B35" s="4">
+        <v>5005.0</v>
+      </c>
+      <c r="C35" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="D35" s="4">
+        <v>5006.0</v>
+      </c>
+      <c r="E35" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="F35" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="G35" s="16"/>
+      <c r="H35" s="22">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="18" t="s">
+        <v>13</v>
+      </c>
+      <c r="B36" s="4">
+        <v>5006.0</v>
+      </c>
+      <c r="C36" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="D36" s="35">
+        <v>-1.0</v>
+      </c>
+      <c r="E36" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="F36" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="G36" s="16"/>
+      <c r="H36" s="22">
+        <v>3.0</v>
       </c>
     </row>
   </sheetData>
@@ -1581,27 +1878,27 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>61</v>
+        <v>72</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="25" t="s">
-        <v>60</v>
-      </c>
-      <c r="B2" s="17" t="s">
+      <c r="A2" s="36" t="s">
         <v>64</v>
       </c>
-      <c r="C2" s="17" t="s">
-        <v>65</v>
+      <c r="B2" s="18" t="s">
+        <v>75</v>
+      </c>
+      <c r="C2" s="18" t="s">
+        <v>76</v>
       </c>
       <c r="D2" s="1"/>
     </row>

--- a/Assets/02Script/Table/EventTable.xlsx
+++ b/Assets/02Script/Table/EventTable.xlsx
@@ -205,7 +205,7 @@
     <t>꺄아아악!!!!!!!!!!!!!!!!!!!!!!!!</t>
   </si>
   <si>
-    <t>&lt;i&gt;그러고 보니 엄마는 오래전에 돌아가셨어,,&lt;/i&gt;</t>
+    <t>&lt;i&gt;그러고 보니 엄마는 오래전에 돌아가셨어.&lt;/i&gt;</t>
   </si>
   <si>
     <t>&lt;i&gt;그럼 여기 있는 건 누구지?&lt;/i&gt;</t>
@@ -220,7 +220,7 @@
     <t>...........</t>
   </si>
   <si>
-    <t>꺄아아아아악!</t>
+    <t>....헉!</t>
   </si>
   <si>
     <t>뭐...뭐였지????</t>

--- a/Assets/02Script/Table/EventTable.xlsx
+++ b/Assets/02Script/Table/EventTable.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="81">
   <si>
     <t>EventID</t>
   </si>
@@ -114,6 +114,9 @@
     <t>ChoiceID</t>
   </si>
   <si>
+    <t>Textbox</t>
+  </si>
+  <si>
     <t>Emotion</t>
   </si>
   <si>
@@ -126,6 +129,9 @@
     <t>서린</t>
   </si>
   <si>
+    <t>Basic</t>
+  </si>
+  <si>
     <t>어렸을 때 엄마랑 자주 오던 공원이랑 똑같네..</t>
   </si>
   <si>
@@ -165,7 +171,7 @@
     <t>.................................</t>
   </si>
   <si>
-    <t>Extra</t>
+    <t>Mom</t>
   </si>
   <si>
     <t>엄마</t>
@@ -193,6 +199,9 @@
     <t>......ㄴㅏ....ㄹ....ㅏㅇ.....가....자....</t>
   </si>
   <si>
+    <t>Monster</t>
+  </si>
+  <si>
     <t>어디를 가자는 거예요?</t>
   </si>
   <si>
@@ -205,10 +214,13 @@
     <t>꺄아아악!!!!!!!!!!!!!!!!!!!!!!!!</t>
   </si>
   <si>
-    <t>&lt;i&gt;그러고 보니 엄마는 오래전에 돌아가셨어.&lt;/i&gt;</t>
-  </si>
-  <si>
-    <t>&lt;i&gt;그럼 여기 있는 건 누구지?&lt;/i&gt;</t>
+    <t>그러고 보니 엄마는 오래전에 돌아가셨어.</t>
+  </si>
+  <si>
+    <t>Monologue</t>
+  </si>
+  <si>
+    <t>그럼 여기 있는 건 누구지?</t>
   </si>
   <si>
     <t>C001</t>
@@ -232,7 +244,7 @@
     <t>다시 돌아온건가?</t>
   </si>
   <si>
-    <t>&lt;i&gt;아까 그 괴물이 다시 나타날지도 모르니 우선 움직여볼까&lt;/i&gt;</t>
+    <t>아까 그 괴물이 다시 나타날지도 모르니 우선 움직여볼까</t>
   </si>
   <si>
     <t>Choice0</t>
@@ -307,7 +319,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="41">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -353,6 +365,9 @@
     <xf borderId="0" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" vertical="bottom"/>
     </xf>
+    <xf borderId="0" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
     <xf borderId="0" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -377,8 +392,14 @@
     <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
     </xf>
+    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
+    </xf>
     <xf borderId="0" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
@@ -407,6 +428,9 @@
     </xf>
     <xf borderId="0" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" shrinkToFit="0" vertical="bottom" wrapText="0"/>
@@ -493,21 +517,23 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="C2:H36" displayName="Table_2" name="Table_2" id="2">
-  <tableColumns count="6">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="C2:J36" displayName="Table_2" name="Table_2" id="2">
+  <tableColumns count="8">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
     <tableColumn name="Column3" id="3"/>
     <tableColumn name="Column4" id="4"/>
     <tableColumn name="Column5" id="5"/>
     <tableColumn name="Column6" id="6"/>
+    <tableColumn name="Column7" id="7"/>
+    <tableColumn name="Column8" id="8"/>
   </tableColumns>
   <tableStyleInfo name="Dialog-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="L19:Q25" displayName="Table_3" name="Table_3" id="3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="M19:R25" displayName="Table_3" name="Table_3" id="3">
   <tableColumns count="6">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -934,8 +960,8 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col customWidth="1" min="3" max="3" width="30.13"/>
-    <col customWidth="1" min="12" max="12" width="36.75"/>
+    <col customWidth="1" min="3" max="3" width="36.25"/>
+    <col customWidth="1" min="13" max="13" width="36.75"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -960,8 +986,11 @@
       <c r="G1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="H1" s="3" t="s">
         <v>32</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="2">
@@ -972,21 +1001,25 @@
         <v>2001.0</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D2" s="12">
         <v>2002.0</v>
       </c>
       <c r="E2" s="11" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G2" s="13"/>
-      <c r="H2" s="14">
+      <c r="H2" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="I2" s="14">
         <v>-1.0</v>
       </c>
+      <c r="J2" s="15"/>
     </row>
     <row r="3">
       <c r="A3" s="9" t="s">
@@ -996,21 +1029,25 @@
         <v>2002.0</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>36</v>
-      </c>
-      <c r="D3" s="15">
+        <v>38</v>
+      </c>
+      <c r="D3" s="16">
         <v>2003.0</v>
       </c>
       <c r="E3" s="7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F3" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="G3" s="16"/>
-      <c r="H3" s="14">
+        <v>36</v>
+      </c>
+      <c r="G3" s="17"/>
+      <c r="H3" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="I3" s="14">
         <v>-1.0</v>
       </c>
+      <c r="J3" s="15"/>
     </row>
     <row r="4">
       <c r="A4" s="9" t="s">
@@ -1019,22 +1056,26 @@
       <c r="B4" s="10">
         <v>2003.0</v>
       </c>
-      <c r="C4" s="17" t="s">
-        <v>37</v>
+      <c r="C4" s="18" t="s">
+        <v>39</v>
       </c>
       <c r="D4" s="12">
         <v>2004.0</v>
       </c>
       <c r="E4" s="11" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G4" s="13"/>
-      <c r="H4" s="14">
+      <c r="H4" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="I4" s="14">
         <v>-1.0</v>
       </c>
+      <c r="J4" s="15"/>
     </row>
     <row r="5">
       <c r="A5" s="9" t="s">
@@ -1044,21 +1085,25 @@
         <v>2004.0</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="D5" s="15">
+        <v>40</v>
+      </c>
+      <c r="D5" s="16">
         <v>2005.0</v>
       </c>
       <c r="E5" s="7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="G5" s="16"/>
-      <c r="H5" s="14">
+        <v>42</v>
+      </c>
+      <c r="G5" s="17"/>
+      <c r="H5" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="I5" s="14">
         <v>-1.0</v>
       </c>
+      <c r="J5" s="15"/>
     </row>
     <row r="6">
       <c r="A6" s="9" t="s">
@@ -1068,21 +1113,25 @@
         <v>2005.0</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="D6" s="12">
         <v>2006.0</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G6" s="13"/>
-      <c r="H6" s="14">
+      <c r="H6" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="I6" s="14">
         <v>-1.0</v>
       </c>
+      <c r="J6" s="15"/>
     </row>
     <row r="7">
       <c r="A7" s="9" t="s">
@@ -1092,21 +1141,25 @@
         <v>2006.0</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="D7" s="15">
+        <v>40</v>
+      </c>
+      <c r="D7" s="16">
         <v>2007.0</v>
       </c>
       <c r="E7" s="7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="G7" s="16"/>
-      <c r="H7" s="14">
+        <v>42</v>
+      </c>
+      <c r="G7" s="17"/>
+      <c r="H7" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="I7" s="14">
         <v>-1.0</v>
       </c>
+      <c r="J7" s="15"/>
     </row>
     <row r="8">
       <c r="A8" s="9" t="s">
@@ -1116,21 +1169,25 @@
         <v>2007.0</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="D8" s="12">
         <v>2008.0</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G8" s="13"/>
-      <c r="H8" s="14">
+      <c r="H8" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="I8" s="14">
         <v>-1.0</v>
       </c>
+      <c r="J8" s="15"/>
     </row>
     <row r="9">
       <c r="A9" s="9" t="s">
@@ -1140,21 +1197,25 @@
         <v>2008.0</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>43</v>
-      </c>
-      <c r="D9" s="15">
+        <v>45</v>
+      </c>
+      <c r="D9" s="16">
         <v>2009.0</v>
       </c>
       <c r="E9" s="7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="G9" s="16"/>
-      <c r="H9" s="14">
+        <v>42</v>
+      </c>
+      <c r="G9" s="17"/>
+      <c r="H9" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="I9" s="14">
         <v>-1.0</v>
       </c>
+      <c r="J9" s="15"/>
     </row>
     <row r="10">
       <c r="A10" s="9" t="s">
@@ -1164,21 +1225,25 @@
         <v>2009.0</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D10" s="12">
         <v>2010.0</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G10" s="13"/>
-      <c r="H10" s="14">
+      <c r="H10" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="I10" s="14">
         <v>-1.0</v>
       </c>
+      <c r="J10" s="15"/>
     </row>
     <row r="11">
       <c r="A11" s="9" t="s">
@@ -1188,21 +1253,25 @@
         <v>2010.0</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="D11" s="15">
+        <v>47</v>
+      </c>
+      <c r="D11" s="16">
         <v>2011.0</v>
       </c>
       <c r="E11" s="7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="F11" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="G11" s="16"/>
-      <c r="H11" s="14">
+        <v>42</v>
+      </c>
+      <c r="G11" s="17"/>
+      <c r="H11" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="I11" s="14">
         <v>-1.0</v>
       </c>
+      <c r="J11" s="15"/>
     </row>
     <row r="12">
       <c r="A12" s="9" t="s">
@@ -1212,648 +1281,748 @@
         <v>2011.0</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="D12" s="12">
         <v>-1.0</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G12" s="13"/>
-      <c r="H12" s="14">
+      <c r="H12" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="I12" s="14">
         <v>-1.0</v>
       </c>
+      <c r="J12" s="15"/>
     </row>
     <row r="13">
-      <c r="A13" s="18" t="s">
+      <c r="A13" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="B13" s="19">
+      <c r="B13" s="20">
         <v>3001.0</v>
       </c>
-      <c r="C13" s="20" t="s">
-        <v>47</v>
-      </c>
-      <c r="D13" s="21">
+      <c r="C13" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="D13" s="22">
         <v>3002.0</v>
       </c>
-      <c r="E13" s="16" t="s">
-        <v>34</v>
+      <c r="E13" s="17" t="s">
+        <v>35</v>
       </c>
       <c r="F13" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="G13" s="16"/>
-      <c r="H13" s="22">
+        <v>36</v>
+      </c>
+      <c r="G13" s="17"/>
+      <c r="H13" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="I13" s="23">
         <v>4.0</v>
       </c>
+      <c r="J13" s="24"/>
     </row>
     <row r="14">
-      <c r="A14" s="18" t="s">
+      <c r="A14" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="B14" s="19">
+      <c r="B14" s="20">
         <v>3002.0</v>
       </c>
       <c r="C14" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="D14" s="23">
+        <v>50</v>
+      </c>
+      <c r="D14" s="25">
         <v>3003.0</v>
       </c>
-      <c r="E14" s="14" t="s">
-        <v>49</v>
-      </c>
-      <c r="F14" s="17" t="s">
-        <v>50</v>
+      <c r="E14" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="F14" s="18" t="s">
+        <v>52</v>
       </c>
       <c r="G14" s="13"/>
-      <c r="H14" s="24">
-        <v>5.0</v>
-      </c>
+      <c r="H14" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="I14" s="26">
+        <v>0.0</v>
+      </c>
+      <c r="J14" s="27"/>
     </row>
     <row r="15">
-      <c r="A15" s="18" t="s">
+      <c r="A15" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="B15" s="19">
+      <c r="B15" s="20">
         <v>3003.0</v>
       </c>
-      <c r="C15" s="20" t="s">
+      <c r="C15" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="D15" s="22">
+        <v>3004.0</v>
+      </c>
+      <c r="E15" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="G15" s="17"/>
+      <c r="H15" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="I15" s="23">
+        <v>2.0</v>
+      </c>
+      <c r="J15" s="24"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="B16" s="20">
+        <v>3004.0</v>
+      </c>
+      <c r="C16" s="14" t="s">
+        <v>54</v>
+      </c>
+      <c r="D16" s="25">
+        <v>3005.0</v>
+      </c>
+      <c r="E16" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="D15" s="21">
-        <v>3004.0</v>
-      </c>
-      <c r="E15" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="F15" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="G15" s="16"/>
-      <c r="H15" s="22">
+      <c r="F16" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="G16" s="13"/>
+      <c r="H16" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="I16" s="26">
+        <v>0.0</v>
+      </c>
+      <c r="J16" s="27"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="B17" s="20">
+        <v>3005.0</v>
+      </c>
+      <c r="C17" s="21" t="s">
+        <v>55</v>
+      </c>
+      <c r="D17" s="22">
+        <v>3006.0</v>
+      </c>
+      <c r="E17" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="G17" s="17"/>
+      <c r="H17" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="I17" s="22">
         <v>2.0</v>
       </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="18" t="s">
+      <c r="J17" s="22"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="B16" s="19">
-        <v>3004.0</v>
-      </c>
-      <c r="C16" s="14" t="s">
+      <c r="B18" s="20">
+        <v>3006.0</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D18" s="25">
+        <v>3007.0</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="F18" s="18" t="s">
         <v>52</v>
       </c>
-      <c r="D16" s="23">
-        <v>3005.0</v>
-      </c>
-      <c r="E16" s="14" t="s">
-        <v>49</v>
-      </c>
-      <c r="F16" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="G16" s="13"/>
-      <c r="H16" s="24">
-        <v>5.0</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="18" t="s">
+      <c r="G18" s="13"/>
+      <c r="H18" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="I18" s="26">
+        <v>1.0</v>
+      </c>
+      <c r="J18" s="27"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="B17" s="19">
-        <v>3005.0</v>
-      </c>
-      <c r="C17" s="20" t="s">
-        <v>53</v>
-      </c>
-      <c r="D17" s="21">
-        <v>3006.0</v>
-      </c>
-      <c r="E17" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="F17" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="G17" s="16"/>
-      <c r="H17" s="21">
+      <c r="B19" s="20">
+        <v>3007.0</v>
+      </c>
+      <c r="C19" s="13" t="s">
+        <v>57</v>
+      </c>
+      <c r="D19" s="22">
+        <v>3008.0</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="F19" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="G19" s="17"/>
+      <c r="H19" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="I19" s="23">
         <v>2.0</v>
       </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="18" t="s">
+      <c r="J19" s="24"/>
+      <c r="K19" s="28"/>
+      <c r="L19" s="2"/>
+      <c r="M19" s="29"/>
+      <c r="N19" s="30"/>
+      <c r="O19" s="29"/>
+      <c r="P19" s="31"/>
+      <c r="Q19" s="29"/>
+      <c r="R19" s="30"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="B18" s="19">
-        <v>3006.0</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="D18" s="23">
-        <v>3007.0</v>
-      </c>
-      <c r="E18" s="14" t="s">
-        <v>49</v>
-      </c>
-      <c r="F18" s="17" t="s">
-        <v>50</v>
-      </c>
-      <c r="G18" s="13"/>
-      <c r="H18" s="24">
-        <v>5.0</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="18" t="s">
+      <c r="B20" s="20">
+        <v>3008.0</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="D20" s="25">
+        <v>3009.0</v>
+      </c>
+      <c r="E20" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="F20" s="18" t="s">
+        <v>36</v>
+      </c>
+      <c r="G20" s="13"/>
+      <c r="H20" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="I20" s="26">
+        <v>2.0</v>
+      </c>
+      <c r="J20" s="27"/>
+      <c r="K20" s="28"/>
+      <c r="L20" s="2"/>
+      <c r="M20" s="32"/>
+      <c r="N20" s="33"/>
+      <c r="O20" s="34"/>
+      <c r="P20" s="35"/>
+      <c r="Q20" s="34"/>
+      <c r="R20" s="33"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="B19" s="19">
-        <v>3007.0</v>
-      </c>
-      <c r="C19" s="13" t="s">
-        <v>55</v>
-      </c>
-      <c r="D19" s="21">
-        <v>3008.0</v>
-      </c>
-      <c r="E19" s="20" t="s">
-        <v>49</v>
-      </c>
-      <c r="F19" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="G19" s="16"/>
-      <c r="H19" s="22">
-        <v>6.0</v>
-      </c>
-      <c r="J19" s="25"/>
-      <c r="K19" s="2"/>
-      <c r="L19" s="26"/>
-      <c r="M19" s="27"/>
-      <c r="N19" s="26"/>
-      <c r="O19" s="28"/>
-      <c r="P19" s="26"/>
-      <c r="Q19" s="27"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="18" t="s">
+      <c r="B21" s="20">
+        <v>3009.0</v>
+      </c>
+      <c r="C21" s="17" t="s">
+        <v>59</v>
+      </c>
+      <c r="D21" s="22">
+        <v>3010.0</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="F21" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="G21" s="17"/>
+      <c r="H21" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="I21" s="23">
+        <v>1.0</v>
+      </c>
+      <c r="J21" s="23"/>
+      <c r="K21" s="28"/>
+      <c r="L21" s="2"/>
+      <c r="M21" s="34"/>
+      <c r="N21" s="33"/>
+      <c r="O21" s="34"/>
+      <c r="P21" s="36"/>
+      <c r="Q21" s="34"/>
+      <c r="R21" s="33"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="B20" s="19">
-        <v>3008.0</v>
-      </c>
-      <c r="C20" s="4" t="s">
+      <c r="B22" s="20">
+        <v>3010.0</v>
+      </c>
+      <c r="C22" s="21" t="s">
+        <v>61</v>
+      </c>
+      <c r="D22" s="25">
+        <v>3011.0</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="F22" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="G22" s="13"/>
+      <c r="H22" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="I22" s="25">
+        <v>2.0</v>
+      </c>
+      <c r="J22" s="25"/>
+      <c r="K22" s="28"/>
+      <c r="L22" s="2"/>
+      <c r="M22" s="34"/>
+      <c r="N22" s="33"/>
+      <c r="O22" s="34"/>
+      <c r="P22" s="36"/>
+      <c r="Q22" s="34"/>
+      <c r="R22" s="33"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="B23" s="20">
+        <v>3011.0</v>
+      </c>
+      <c r="C23" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="D20" s="23">
-        <v>3009.0</v>
-      </c>
-      <c r="E20" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="F20" s="17" t="s">
-        <v>35</v>
-      </c>
-      <c r="G20" s="13"/>
-      <c r="H20" s="24">
+      <c r="D23" s="22">
+        <v>3012.0</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="F23" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="G23" s="17"/>
+      <c r="H23" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="I23" s="23">
+        <v>1.0</v>
+      </c>
+      <c r="J23" s="24"/>
+      <c r="K23" s="28"/>
+      <c r="L23" s="2"/>
+      <c r="M23" s="34"/>
+      <c r="N23" s="33"/>
+      <c r="O23" s="34"/>
+      <c r="P23" s="35"/>
+      <c r="Q23" s="34"/>
+      <c r="R23" s="33"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="B24" s="19">
+        <v>3012.0</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="D24" s="25">
+        <v>3013.0</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F24" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="H24" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="I24" s="4">
         <v>2.0</v>
       </c>
-      <c r="J20" s="25"/>
-      <c r="K20" s="2"/>
-      <c r="L20" s="29"/>
-      <c r="M20" s="30"/>
-      <c r="N20" s="31"/>
-      <c r="O20" s="32"/>
-      <c r="P20" s="31"/>
-      <c r="Q20" s="30"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="18" t="s">
+      <c r="J24" s="37"/>
+      <c r="K24" s="28"/>
+      <c r="L24" s="2"/>
+      <c r="M24" s="34"/>
+      <c r="N24" s="33"/>
+      <c r="O24" s="34"/>
+      <c r="P24" s="36"/>
+      <c r="Q24" s="34"/>
+      <c r="R24" s="33"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="B21" s="19">
-        <v>3009.0</v>
-      </c>
-      <c r="C21" s="16" t="s">
-        <v>57</v>
-      </c>
-      <c r="D21" s="21">
-        <v>3010.0</v>
-      </c>
-      <c r="E21" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="F21" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="G21" s="16"/>
-      <c r="H21" s="22">
-        <v>6.0</v>
-      </c>
-      <c r="J21" s="25"/>
-      <c r="K21" s="2"/>
-      <c r="L21" s="31"/>
-      <c r="M21" s="30"/>
-      <c r="N21" s="31"/>
-      <c r="O21" s="33"/>
-      <c r="P21" s="31"/>
-      <c r="Q21" s="30"/>
-    </row>
-    <row r="22">
-      <c r="A22" s="18" t="s">
+      <c r="B25" s="20">
+        <v>3013.0</v>
+      </c>
+      <c r="C25" s="13" t="s">
+        <v>63</v>
+      </c>
+      <c r="D25" s="22">
+        <v>3014.0</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="F25" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="H25" s="14" t="s">
+        <v>60</v>
+      </c>
+      <c r="I25" s="4">
+        <v>2.0</v>
+      </c>
+      <c r="J25" s="37"/>
+      <c r="K25" s="28"/>
+      <c r="L25" s="2"/>
+      <c r="M25" s="29"/>
+      <c r="N25" s="38"/>
+      <c r="O25" s="29"/>
+      <c r="P25" s="31"/>
+      <c r="Q25" s="29"/>
+      <c r="R25" s="30"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="B22" s="19">
-        <v>3010.0</v>
-      </c>
-      <c r="C22" s="20" t="s">
-        <v>58</v>
-      </c>
-      <c r="D22" s="23">
-        <v>3011.0</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="F22" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="G22" s="13"/>
-      <c r="H22" s="23">
+      <c r="B26" s="19">
+        <v>3014.0</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="D26" s="25">
+        <v>3015.0</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="H26" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="I26" s="4">
         <v>2.0</v>
       </c>
-      <c r="J22" s="25"/>
-      <c r="K22" s="2"/>
-      <c r="L22" s="31"/>
-      <c r="M22" s="30"/>
-      <c r="N22" s="31"/>
-      <c r="O22" s="33"/>
-      <c r="P22" s="31"/>
-      <c r="Q22" s="30"/>
-    </row>
-    <row r="23">
-      <c r="A23" s="18" t="s">
+      <c r="J26" s="37"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="B23" s="19">
-        <v>3011.0</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="D23" s="21">
-        <v>3012.0</v>
-      </c>
-      <c r="E23" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="F23" s="8" t="s">
-        <v>50</v>
-      </c>
-      <c r="G23" s="16"/>
-      <c r="H23" s="22">
-        <v>5.0</v>
-      </c>
-      <c r="J23" s="25"/>
-      <c r="K23" s="2"/>
-      <c r="L23" s="31"/>
-      <c r="M23" s="30"/>
-      <c r="N23" s="31"/>
-      <c r="O23" s="32"/>
-      <c r="P23" s="31"/>
-      <c r="Q23" s="30"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="18" t="s">
+      <c r="B27" s="20">
+        <v>3015.0</v>
+      </c>
+      <c r="C27" s="14" t="s">
+        <v>65</v>
+      </c>
+      <c r="D27" s="22">
+        <v>3016.0</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="F27" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="G27" s="13"/>
+      <c r="H27" s="23" t="s">
+        <v>66</v>
+      </c>
+      <c r="I27" s="25">
+        <v>0.0</v>
+      </c>
+      <c r="J27" s="25"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="19" t="s">
         <v>9</v>
       </c>
-      <c r="B24" s="18">
-        <v>3012.0</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="D24" s="23">
-        <v>3013.0</v>
-      </c>
-      <c r="E24" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="F24" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="H24" s="4">
-        <v>2.0</v>
-      </c>
-      <c r="J24" s="25"/>
-      <c r="K24" s="2"/>
-      <c r="L24" s="31"/>
-      <c r="M24" s="30"/>
-      <c r="N24" s="31"/>
-      <c r="O24" s="33"/>
-      <c r="P24" s="31"/>
-      <c r="Q24" s="30"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="18" t="s">
-        <v>9</v>
-      </c>
-      <c r="B25" s="19">
-        <v>3013.0</v>
-      </c>
-      <c r="C25" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="D25" s="21">
-        <v>3014.0</v>
-      </c>
-      <c r="E25" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="F25" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="H25" s="4">
-        <v>7.0</v>
-      </c>
-      <c r="J25" s="25"/>
-      <c r="K25" s="2"/>
-      <c r="L25" s="26"/>
-      <c r="M25" s="34"/>
-      <c r="N25" s="26"/>
-      <c r="O25" s="28"/>
-      <c r="P25" s="26"/>
-      <c r="Q25" s="27"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="18" t="s">
-        <v>9</v>
-      </c>
-      <c r="B26" s="18">
-        <v>3014.0</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="D26" s="23">
-        <v>3015.0</v>
-      </c>
-      <c r="E26" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="F26" s="4" t="s">
-        <v>35</v>
-      </c>
-      <c r="H26" s="4">
-        <v>2.0</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="18" t="s">
-        <v>9</v>
-      </c>
-      <c r="B27" s="19">
-        <v>3015.0</v>
-      </c>
-      <c r="C27" s="14" t="s">
-        <v>62</v>
-      </c>
-      <c r="D27" s="21">
+      <c r="B28" s="19">
         <v>3016.0</v>
       </c>
-      <c r="E27" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="F27" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="G27" s="13"/>
-      <c r="H27" s="23">
+      <c r="C28" s="21" t="s">
+        <v>67</v>
+      </c>
+      <c r="D28" s="16">
+        <v>-1.0</v>
+      </c>
+      <c r="E28" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="F28" s="7" t="s">
+        <v>36</v>
+      </c>
+      <c r="G28" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="H28" s="23" t="s">
+        <v>66</v>
+      </c>
+      <c r="I28" s="22">
         <v>0.0</v>
       </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="18" t="s">
-        <v>9</v>
-      </c>
-      <c r="B28" s="18">
-        <v>3016.0</v>
-      </c>
-      <c r="C28" s="20" t="s">
-        <v>63</v>
-      </c>
-      <c r="D28" s="15">
-        <v>-1.0</v>
-      </c>
-      <c r="E28" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="F28" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="G28" s="16" t="s">
-        <v>64</v>
-      </c>
-      <c r="H28" s="21">
-        <v>0.0</v>
-      </c>
+      <c r="J28" s="22"/>
     </row>
     <row r="29">
-      <c r="A29" s="18" t="s">
+      <c r="A29" s="19" t="s">
         <v>11</v>
       </c>
       <c r="B29" s="4">
         <v>4001.0</v>
       </c>
-      <c r="C29" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="D29" s="35">
+      <c r="C29" s="21" t="s">
+        <v>69</v>
+      </c>
+      <c r="D29" s="39">
         <v>4002.0</v>
       </c>
-      <c r="E29" s="16" t="s">
-        <v>34</v>
+      <c r="E29" s="17" t="s">
+        <v>35</v>
       </c>
       <c r="F29" s="7"/>
-      <c r="G29" s="16"/>
-      <c r="H29" s="22">
+      <c r="G29" s="17"/>
+      <c r="H29" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="I29" s="23">
         <v>-1.0</v>
       </c>
+      <c r="J29" s="24"/>
     </row>
     <row r="30">
-      <c r="A30" s="18" t="s">
+      <c r="A30" s="19" t="s">
         <v>11</v>
       </c>
       <c r="B30" s="4">
         <v>4002.0</v>
       </c>
-      <c r="C30" s="20" t="s">
-        <v>66</v>
-      </c>
-      <c r="D30" s="35">
+      <c r="C30" s="21" t="s">
+        <v>70</v>
+      </c>
+      <c r="D30" s="39">
         <v>-1.0</v>
       </c>
-      <c r="E30" s="16" t="s">
-        <v>34</v>
+      <c r="E30" s="17" t="s">
+        <v>35</v>
       </c>
       <c r="F30" s="7"/>
-      <c r="G30" s="16"/>
-      <c r="H30" s="22">
+      <c r="G30" s="17"/>
+      <c r="H30" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="I30" s="23">
         <v>-1.0</v>
       </c>
+      <c r="J30" s="24"/>
     </row>
     <row r="31">
-      <c r="A31" s="18" t="s">
+      <c r="A31" s="19" t="s">
         <v>13</v>
       </c>
       <c r="B31" s="4">
         <v>5001.0</v>
       </c>
-      <c r="C31" s="20" t="s">
-        <v>67</v>
+      <c r="C31" s="21" t="s">
+        <v>71</v>
       </c>
       <c r="D31" s="4">
         <v>5002.0</v>
       </c>
-      <c r="E31" s="16" t="s">
-        <v>34</v>
+      <c r="E31" s="17" t="s">
+        <v>35</v>
       </c>
       <c r="F31" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="G31" s="16"/>
-      <c r="H31" s="22">
+        <v>36</v>
+      </c>
+      <c r="G31" s="17"/>
+      <c r="H31" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="I31" s="23">
         <v>2.0</v>
       </c>
+      <c r="J31" s="24"/>
     </row>
     <row r="32">
-      <c r="A32" s="18" t="s">
+      <c r="A32" s="19" t="s">
         <v>13</v>
       </c>
       <c r="B32" s="4">
         <v>5002.0</v>
       </c>
-      <c r="C32" s="20" t="s">
-        <v>68</v>
+      <c r="C32" s="21" t="s">
+        <v>72</v>
       </c>
       <c r="D32" s="4">
         <v>5003.0</v>
       </c>
-      <c r="E32" s="16" t="s">
-        <v>34</v>
+      <c r="E32" s="17" t="s">
+        <v>35</v>
       </c>
       <c r="F32" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="G32" s="16"/>
-      <c r="H32" s="22">
+        <v>36</v>
+      </c>
+      <c r="G32" s="17"/>
+      <c r="H32" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="I32" s="23">
         <v>2.0</v>
       </c>
+      <c r="J32" s="24"/>
     </row>
     <row r="33">
-      <c r="A33" s="18" t="s">
+      <c r="A33" s="19" t="s">
         <v>13</v>
       </c>
       <c r="B33" s="4">
         <v>5003.0</v>
       </c>
-      <c r="C33" s="20" t="s">
-        <v>33</v>
+      <c r="C33" s="21" t="s">
+        <v>34</v>
       </c>
       <c r="D33" s="4">
         <v>5004.0</v>
       </c>
-      <c r="E33" s="16" t="s">
-        <v>34</v>
+      <c r="E33" s="17" t="s">
+        <v>35</v>
       </c>
       <c r="F33" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="G33" s="16"/>
-      <c r="H33" s="22">
+        <v>36</v>
+      </c>
+      <c r="G33" s="17"/>
+      <c r="H33" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="I33" s="23">
         <v>0.0</v>
       </c>
+      <c r="J33" s="24"/>
     </row>
     <row r="34">
-      <c r="A34" s="18" t="s">
+      <c r="A34" s="19" t="s">
         <v>13</v>
       </c>
       <c r="B34" s="4">
         <v>5004.0</v>
       </c>
-      <c r="C34" s="20" t="s">
-        <v>69</v>
+      <c r="C34" s="21" t="s">
+        <v>73</v>
       </c>
       <c r="D34" s="4">
         <v>5005.0</v>
       </c>
-      <c r="E34" s="16" t="s">
-        <v>34</v>
+      <c r="E34" s="17" t="s">
+        <v>35</v>
       </c>
       <c r="F34" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="G34" s="16"/>
-      <c r="H34" s="22">
+        <v>36</v>
+      </c>
+      <c r="G34" s="17"/>
+      <c r="H34" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="I34" s="23">
         <v>0.0</v>
       </c>
+      <c r="J34" s="24"/>
     </row>
     <row r="35">
-      <c r="A35" s="18" t="s">
+      <c r="A35" s="19" t="s">
         <v>13</v>
       </c>
       <c r="B35" s="4">
         <v>5005.0</v>
       </c>
-      <c r="C35" s="20" t="s">
-        <v>70</v>
+      <c r="C35" s="21" t="s">
+        <v>74</v>
       </c>
       <c r="D35" s="4">
         <v>5006.0</v>
       </c>
-      <c r="E35" s="16" t="s">
-        <v>34</v>
+      <c r="E35" s="17" t="s">
+        <v>35</v>
       </c>
       <c r="F35" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="G35" s="16"/>
-      <c r="H35" s="22">
+        <v>36</v>
+      </c>
+      <c r="G35" s="17"/>
+      <c r="H35" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="I35" s="23">
         <v>0.0</v>
       </c>
+      <c r="J35" s="24"/>
     </row>
     <row r="36">
-      <c r="A36" s="18" t="s">
+      <c r="A36" s="19" t="s">
         <v>13</v>
       </c>
       <c r="B36" s="4">
         <v>5006.0</v>
       </c>
-      <c r="C36" s="20" t="s">
-        <v>71</v>
-      </c>
-      <c r="D36" s="35">
+      <c r="C36" s="21" t="s">
+        <v>75</v>
+      </c>
+      <c r="D36" s="39">
         <v>-1.0</v>
       </c>
-      <c r="E36" s="16" t="s">
-        <v>34</v>
+      <c r="E36" s="17" t="s">
+        <v>35</v>
       </c>
       <c r="F36" s="7" t="s">
-        <v>35</v>
-      </c>
-      <c r="G36" s="16"/>
-      <c r="H36" s="22">
-        <v>3.0</v>
-      </c>
+        <v>36</v>
+      </c>
+      <c r="G36" s="17"/>
+      <c r="H36" s="23" t="s">
+        <v>66</v>
+      </c>
+      <c r="I36" s="23">
+        <v>0.0</v>
+      </c>
+      <c r="J36" s="24"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
@@ -1881,24 +2050,24 @@
         <v>31</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="36" t="s">
-        <v>64</v>
-      </c>
-      <c r="B2" s="18" t="s">
-        <v>75</v>
-      </c>
-      <c r="C2" s="18" t="s">
-        <v>76</v>
+      <c r="A2" s="40" t="s">
+        <v>68</v>
+      </c>
+      <c r="B2" s="19" t="s">
+        <v>79</v>
+      </c>
+      <c r="C2" s="19" t="s">
+        <v>80</v>
       </c>
       <c r="D2" s="1"/>
     </row>

--- a/Assets/02Script/Table/EventTable.xlsx
+++ b/Assets/02Script/Table/EventTable.xlsx
@@ -6975,8 +6975,8 @@
       <c r="E3" s="2">
         <v>0.0</v>
       </c>
-      <c r="F3" s="2">
-        <v>10.0</v>
+      <c r="F3" s="23">
+        <v>-10.0</v>
       </c>
       <c r="G3" s="1"/>
     </row>
@@ -6991,8 +6991,8 @@
         <v>172</v>
       </c>
       <c r="D4" s="1"/>
-      <c r="E4" s="2">
-        <v>10.0</v>
+      <c r="E4" s="23">
+        <v>-10.0</v>
       </c>
       <c r="F4" s="2">
         <v>0.0</v>

--- a/Assets/02Script/Table/EventTable.xlsx
+++ b/Assets/02Script/Table/EventTable.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="574" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="160">
   <si>
     <t>EventID</t>
   </si>
@@ -70,15 +70,15 @@
     <t>E007</t>
   </si>
   <si>
+    <t>First_Path_Pass</t>
+  </si>
+  <si>
+    <t>E008</t>
+  </si>
+  <si>
     <t>First_Path_Enter</t>
   </si>
   <si>
-    <t>E008</t>
-  </si>
-  <si>
-    <t>First_Path_Conversation</t>
-  </si>
-  <si>
     <t>E009</t>
   </si>
   <si>
@@ -88,31 +88,31 @@
     <t>E010</t>
   </si>
   <si>
+    <t>Try_Enter_FspMap</t>
+  </si>
+  <si>
+    <t>E011</t>
+  </si>
+  <si>
     <t>Second_Path_Discover</t>
   </si>
   <si>
-    <t>E011</t>
+    <t>E012</t>
+  </si>
+  <si>
+    <t>Second_Path_Pass</t>
+  </si>
+  <si>
+    <t>E013</t>
   </si>
   <si>
     <t>Second_Path_Enter</t>
   </si>
   <si>
-    <t>E012</t>
-  </si>
-  <si>
-    <t>Second_Path_Conversation</t>
-  </si>
-  <si>
-    <t>E013</t>
+    <t>E014</t>
   </si>
   <si>
     <t>Exit_Door_Discover</t>
-  </si>
-  <si>
-    <t>E014</t>
-  </si>
-  <si>
-    <t>Exit_Door_Conversation</t>
   </si>
   <si>
     <t>E015</t>
@@ -339,6 +339,9 @@
     <t>한번 확인해 봐야겠어.</t>
   </si>
   <si>
+    <t>지금은 저길 확인해 보는 게 우선이야..</t>
+  </si>
+  <si>
     <t>여긴.....</t>
   </si>
   <si>
@@ -354,51 +357,6 @@
     <t>시루 너야??</t>
   </si>
   <si>
-    <t>시루야!!!!</t>
-  </si>
-  <si>
-    <t>시루</t>
-  </si>
-  <si>
-    <t>보고 싶었어..시루야..</t>
-  </si>
-  <si>
-    <t>끼이잉..</t>
-  </si>
-  <si>
-    <t>내 말에 대답하는 거 같네, 알아듣는건가?</t>
-  </si>
-  <si>
-    <t>시루야 내가 하는 말 알아들을 수 있어?</t>
-  </si>
-  <si>
-    <t>왕왕왕!!!</t>
-  </si>
-  <si>
-    <t>진짜야 이거?</t>
-  </si>
-  <si>
-    <t>정말 보고 싶었어...</t>
-  </si>
-  <si>
-    <t>왕!!</t>
-  </si>
-  <si>
-    <t>오랜만에 봐서 너무 행복하지만,, 이제 가봐야 할 거 같아.</t>
-  </si>
-  <si>
-    <t>끼잉..끼이잉..</t>
-  </si>
-  <si>
-    <t>우리 다음에.. 또 볼 수 있겠지?</t>
-  </si>
-  <si>
-    <t>왕왕!</t>
-  </si>
-  <si>
-    <t>그래, 다음에 다시 만나자!</t>
-  </si>
-  <si>
     <t>시루를 다시 보게 될 줄이야..</t>
   </si>
   <si>
@@ -411,6 +369,9 @@
     <t>뭔가.. 이상한 곳 같아...</t>
   </si>
   <si>
+    <t>뭔가 지금은 가면 안 될 거 같아..</t>
+  </si>
+  <si>
     <t>꺄르르르르륵...</t>
   </si>
   <si>
@@ -435,6 +396,9 @@
     <t>한번....들어가 볼까?</t>
   </si>
   <si>
+    <t>아무래도 저길 먼저 확인해 봐야겠어...</t>
+  </si>
+  <si>
     <t>여긴... 어렸을 때 엄마랑 자주 놀러 오던 곳이잖아..</t>
   </si>
   <si>
@@ -444,10 +408,7 @@
     <t>저건... 엄마가 사줬던 풍선..?</t>
   </si>
   <si>
-    <t>어렸을 땐 엄마랑 풍선만 있어도 행복했는데..</t>
-  </si>
-  <si>
-    <t>근데 이 풍선... 왜 여기에 있는 걸까?</t>
+    <t xml:space="preserve"> E014</t>
   </si>
   <si>
     <t>저게 뭐지....?</t>
@@ -456,23 +417,13 @@
     <t>문..? 문이 왜 이런 곳에 있는 거지?</t>
   </si>
   <si>
-    <t>왜 이런 곳에 문이 있지?</t>
-  </si>
-  <si>
-    <t>열쇠가 필요한 거 같은데..
-여기 어딘가에 떨어져 있으려나?</t>
-  </si>
-  <si>
-    <t>일단 이 주변을 한번 둘러봐야겠다..</t>
-  </si>
-  <si>
     <t>저기에 저렇게 무성한 숲길이 있었나..?</t>
   </si>
   <si>
     <t>안쪽이 하나도 안 보이네..</t>
   </si>
   <si>
-    <t>뭔가..여기 안쪽에 열쇠가 있을 것 만 같아.</t>
+    <t>뭔가.. 안쪽에 열쇠가 있을 것 만 같아.</t>
   </si>
   <si>
     <t>무섭지만 들어가 봐야겠어.</t>
@@ -528,23 +479,30 @@
     <t>C002</t>
   </si>
   <si>
-    <t>왜 있는진 모르겠지만
-다시 보니까 그때 기억이 떠오르네</t>
-  </si>
-  <si>
-    <t>이상해.. 아무래도 현실이 아닌 것 같아.. 
-내가 꿈을 꾸고 있는 걸까?</t>
+    <t>오랜만에 보니까
+옛날 생각이 나네..</t>
+  </si>
+  <si>
+    <t>내가 꿈을 꾸는 게 아닐까?</t>
   </si>
   <si>
     <t>C003</t>
   </si>
   <si>
-    <t>이 꽃.. 아무리 봐도 소름 끼쳐..
-현실에 이런 꽃이 존재할 리가 없는데..</t>
-  </si>
-  <si>
-    <t>에이.. 그럴 리가 있겠어?
-내가 잘 못 본 거겠지?</t>
+    <t>현실에 이런 꽃이 
+존재할 리가 없어..</t>
+  </si>
+  <si>
+    <t>내가 잘못 본 거겠지?</t>
+  </si>
+  <si>
+    <t>C004</t>
+  </si>
+  <si>
+    <t>아무래도 꿈속이 맞나 봐..</t>
+  </si>
+  <si>
+    <t>비슷한 풍선이겠지?</t>
   </si>
 </sst>
 </file>
@@ -614,7 +572,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="44">
+  <cellXfs count="45">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -718,6 +676,9 @@
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" vertical="bottom"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" vertical="bottom"/>
+    </xf>
     <xf borderId="0" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0"/>
     </xf>
@@ -731,19 +692,19 @@
       <alignment vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
+      <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="bottom"/>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center"/>
+      <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" vertical="bottom"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -821,7 +782,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="C2:J92" displayName="Table_2" name="Table_2" id="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="C2:J73" displayName="Table_2" name="Table_2" id="2">
   <tableColumns count="8">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -1103,7 +1064,7 @@
       <c r="D4" s="2"/>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="1" t="s">
         <v>11</v>
       </c>
       <c r="B5" s="4" t="s">
@@ -1114,7 +1075,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B6" s="4" t="s">
@@ -1125,7 +1086,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B7" s="4" t="s">
@@ -1136,29 +1097,29 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="s">
+      <c r="A8" s="1" t="s">
         <v>17</v>
       </c>
       <c r="B8" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="1" t="s">
+      <c r="C8" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="1" t="s">
         <v>19</v>
       </c>
       <c r="B9" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="1" t="s">
         <v>21</v>
       </c>
       <c r="B10" s="4" t="s">
@@ -1169,7 +1130,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="1" t="s">
         <v>23</v>
       </c>
       <c r="B11" s="4" t="s">
@@ -1180,18 +1141,18 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="s">
+      <c r="A12" s="1" t="s">
         <v>25</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="C12" s="1" t="s">
+      <c r="C12" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="s">
+      <c r="A13" s="1" t="s">
         <v>27</v>
       </c>
       <c r="B13" s="4" t="s">
@@ -1202,7 +1163,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="s">
+      <c r="A14" s="1" t="s">
         <v>29</v>
       </c>
       <c r="B14" s="4" t="s">
@@ -1213,18 +1174,18 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="s">
+      <c r="A15" s="1" t="s">
         <v>31</v>
       </c>
       <c r="B15" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C15" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="s">
+      <c r="A16" s="3" t="s">
         <v>33</v>
       </c>
       <c r="B16" s="4" t="s">
@@ -1235,7 +1196,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="s">
+      <c r="A17" s="3" t="s">
         <v>35</v>
       </c>
       <c r="B17" s="4" t="s">
@@ -1246,7 +1207,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="s">
+      <c r="A18" s="3" t="s">
         <v>37</v>
       </c>
       <c r="B18" s="4" t="s">
@@ -2470,9 +2431,8 @@
       <c r="C37" s="14" t="s">
         <v>100</v>
       </c>
-      <c r="D37" s="18">
-        <f t="shared" ref="D37:D90" si="1">if(B38&gt; B37+900,-1,B38)</f>
-        <v>6002</v>
+      <c r="D37" s="19">
+        <v>6002.0</v>
       </c>
       <c r="E37" s="14" t="s">
         <v>101</v>
@@ -2499,9 +2459,8 @@
       <c r="C38" s="14" t="s">
         <v>102</v>
       </c>
-      <c r="D38" s="18">
-        <f t="shared" si="1"/>
-        <v>6003</v>
+      <c r="D38" s="19">
+        <v>6003.0</v>
       </c>
       <c r="E38" s="14" t="s">
         <v>59</v>
@@ -2528,9 +2487,8 @@
       <c r="C39" s="14" t="s">
         <v>103</v>
       </c>
-      <c r="D39" s="18">
-        <f t="shared" si="1"/>
-        <v>6004</v>
+      <c r="D39" s="19">
+        <v>6004.0</v>
       </c>
       <c r="E39" s="14" t="s">
         <v>101</v>
@@ -2557,9 +2515,8 @@
       <c r="C40" s="14" t="s">
         <v>104</v>
       </c>
-      <c r="D40" s="18">
-        <f t="shared" si="1"/>
-        <v>6005</v>
+      <c r="D40" s="19">
+        <v>6005.0</v>
       </c>
       <c r="E40" s="14" t="s">
         <v>59</v>
@@ -2586,9 +2543,8 @@
       <c r="C41" s="14" t="s">
         <v>105</v>
       </c>
-      <c r="D41" s="18">
-        <f t="shared" si="1"/>
-        <v>-1</v>
+      <c r="D41" s="19">
+        <v>-1.0</v>
       </c>
       <c r="E41" s="14" t="s">
         <v>59</v>
@@ -2606,47 +2562,45 @@
       <c r="J41" s="20"/>
     </row>
     <row r="42">
-      <c r="A42" s="33" t="s">
+      <c r="A42" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="B42" s="2">
+      <c r="B42" s="23">
         <v>7001.0</v>
       </c>
-      <c r="C42" s="14" t="s">
+      <c r="C42" s="15" t="s">
         <v>106</v>
       </c>
-      <c r="D42" s="18">
-        <f t="shared" si="1"/>
-        <v>7002</v>
-      </c>
-      <c r="E42" s="14" t="s">
+      <c r="D42" s="19">
+        <v>-1.0</v>
+      </c>
+      <c r="E42" s="15" t="s">
         <v>59</v>
       </c>
       <c r="F42" s="17" t="s">
         <v>60</v>
       </c>
       <c r="G42" s="14"/>
-      <c r="H42" s="14" t="s">
+      <c r="H42" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="I42" s="18">
-        <v>1.0</v>
+      <c r="I42" s="19">
+        <v>-1.0</v>
       </c>
       <c r="J42" s="20"/>
     </row>
     <row r="43">
-      <c r="A43" s="33" t="s">
-        <v>17</v>
-      </c>
-      <c r="B43" s="2">
-        <v>7002.0</v>
+      <c r="A43" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B43" s="23">
+        <v>8001.0</v>
       </c>
       <c r="C43" s="14" t="s">
         <v>107</v>
       </c>
-      <c r="D43" s="18">
-        <f t="shared" si="1"/>
-        <v>7003</v>
+      <c r="D43" s="19">
+        <v>8002.0</v>
       </c>
       <c r="E43" s="14" t="s">
         <v>59</v>
@@ -2664,18 +2618,17 @@
       <c r="J43" s="20"/>
     </row>
     <row r="44">
-      <c r="A44" s="33" t="s">
-        <v>17</v>
-      </c>
-      <c r="B44" s="2">
-        <v>7003.0</v>
+      <c r="A44" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B44" s="23">
+        <v>8002.0</v>
       </c>
       <c r="C44" s="14" t="s">
         <v>108</v>
       </c>
-      <c r="D44" s="18">
-        <f t="shared" si="1"/>
-        <v>7004</v>
+      <c r="D44" s="19">
+        <v>8003.0</v>
       </c>
       <c r="E44" s="14" t="s">
         <v>59</v>
@@ -2693,76 +2646,73 @@
       <c r="J44" s="20"/>
     </row>
     <row r="45">
-      <c r="A45" s="33" t="s">
-        <v>17</v>
-      </c>
-      <c r="B45" s="2">
-        <v>7004.0</v>
+      <c r="A45" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B45" s="23">
+        <v>8003.0</v>
       </c>
       <c r="C45" s="14" t="s">
         <v>109</v>
       </c>
-      <c r="D45" s="18">
-        <f t="shared" si="1"/>
-        <v>7005</v>
+      <c r="D45" s="19">
+        <v>8004.0</v>
       </c>
       <c r="E45" s="14" t="s">
-        <v>101</v>
-      </c>
-      <c r="F45" s="12" t="s">
-        <v>66</v>
+        <v>59</v>
+      </c>
+      <c r="F45" s="17" t="s">
+        <v>60</v>
       </c>
       <c r="G45" s="14"/>
-      <c r="H45" s="18" t="s">
-        <v>90</v>
+      <c r="H45" s="14" t="s">
+        <v>61</v>
       </c>
       <c r="I45" s="18">
-        <v>-1.0</v>
+        <v>1.0</v>
       </c>
       <c r="J45" s="20"/>
     </row>
     <row r="46">
-      <c r="A46" s="33" t="s">
-        <v>17</v>
-      </c>
-      <c r="B46" s="2">
-        <v>7005.0</v>
+      <c r="A46" s="9" t="s">
+        <v>19</v>
+      </c>
+      <c r="B46" s="23">
+        <v>8004.0</v>
       </c>
       <c r="C46" s="14" t="s">
         <v>110</v>
       </c>
-      <c r="D46" s="18">
-        <f t="shared" si="1"/>
-        <v>-1</v>
+      <c r="D46" s="19">
+        <v>8005.0</v>
       </c>
       <c r="E46" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="F46" s="17" t="s">
-        <v>60</v>
+        <v>101</v>
+      </c>
+      <c r="F46" s="12" t="s">
+        <v>66</v>
       </c>
       <c r="G46" s="14"/>
-      <c r="H46" s="14" t="s">
-        <v>61</v>
+      <c r="H46" s="18" t="s">
+        <v>90</v>
       </c>
       <c r="I46" s="18">
-        <v>2.0</v>
+        <v>-1.0</v>
       </c>
       <c r="J46" s="20"/>
     </row>
     <row r="47">
-      <c r="A47" s="33" t="s">
+      <c r="A47" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="B47" s="2">
-        <v>8001.0</v>
+      <c r="B47" s="23">
+        <v>8005.0</v>
       </c>
       <c r="C47" s="14" t="s">
         <v>111</v>
       </c>
-      <c r="D47" s="18">
-        <f t="shared" si="1"/>
-        <v>8002</v>
+      <c r="D47" s="19">
+        <v>-1.0</v>
       </c>
       <c r="E47" s="14" t="s">
         <v>59</v>
@@ -2775,52 +2725,50 @@
         <v>61</v>
       </c>
       <c r="I47" s="18">
+        <v>2.0</v>
+      </c>
+      <c r="J47" s="20"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B48" s="23">
+        <v>9001.0</v>
+      </c>
+      <c r="C48" s="14" t="s">
+        <v>112</v>
+      </c>
+      <c r="D48" s="19">
+        <v>9002.0</v>
+      </c>
+      <c r="E48" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="F48" s="17" t="s">
+        <v>60</v>
+      </c>
+      <c r="G48" s="14"/>
+      <c r="H48" s="34" t="s">
+        <v>61</v>
+      </c>
+      <c r="I48" s="18">
         <v>0.0</v>
       </c>
-      <c r="J47" s="20"/>
-    </row>
-    <row r="48">
-      <c r="A48" s="33" t="s">
-        <v>19</v>
-      </c>
-      <c r="B48" s="2">
-        <v>8002.0</v>
-      </c>
-      <c r="C48" s="14" t="s">
-        <v>109</v>
-      </c>
-      <c r="D48" s="18">
-        <f t="shared" si="1"/>
-        <v>8003</v>
-      </c>
-      <c r="E48" s="14" t="s">
-        <v>101</v>
-      </c>
-      <c r="F48" s="12" t="s">
-        <v>112</v>
-      </c>
-      <c r="G48" s="14"/>
-      <c r="H48" s="18" t="s">
-        <v>90</v>
-      </c>
-      <c r="I48" s="18">
-        <v>-1.0</v>
-      </c>
       <c r="J48" s="20"/>
     </row>
     <row r="49">
-      <c r="A49" s="33" t="s">
-        <v>19</v>
-      </c>
-      <c r="B49" s="2">
-        <v>8003.0</v>
+      <c r="A49" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B49" s="23">
+        <v>9002.0</v>
       </c>
       <c r="C49" s="14" t="s">
         <v>113</v>
       </c>
-      <c r="D49" s="18">
-        <f t="shared" si="1"/>
-        <v>8004</v>
+      <c r="D49" s="19">
+        <v>9003.0</v>
       </c>
       <c r="E49" s="14" t="s">
         <v>59</v>
@@ -2829,56 +2777,54 @@
         <v>60</v>
       </c>
       <c r="G49" s="14"/>
-      <c r="H49" s="14" t="s">
+      <c r="H49" s="34" t="s">
         <v>61</v>
       </c>
       <c r="I49" s="18">
-        <v>4.0</v>
+        <v>0.0</v>
       </c>
       <c r="J49" s="20"/>
     </row>
     <row r="50">
-      <c r="A50" s="33" t="s">
-        <v>19</v>
-      </c>
-      <c r="B50" s="2">
-        <v>8004.0</v>
+      <c r="A50" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B50" s="23">
+        <v>9003.0</v>
       </c>
       <c r="C50" s="14" t="s">
         <v>114</v>
       </c>
-      <c r="D50" s="18">
-        <f t="shared" si="1"/>
-        <v>8005</v>
+      <c r="D50" s="19">
+        <v>9004.0</v>
       </c>
       <c r="E50" s="14" t="s">
-        <v>101</v>
-      </c>
-      <c r="F50" s="12" t="s">
-        <v>112</v>
+        <v>59</v>
+      </c>
+      <c r="F50" s="17" t="s">
+        <v>60</v>
       </c>
       <c r="G50" s="14"/>
-      <c r="H50" s="18" t="s">
-        <v>90</v>
+      <c r="H50" s="34" t="s">
+        <v>61</v>
       </c>
       <c r="I50" s="18">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="J50" s="20"/>
     </row>
     <row r="51">
-      <c r="A51" s="33" t="s">
-        <v>19</v>
-      </c>
-      <c r="B51" s="2">
-        <v>8005.0</v>
+      <c r="A51" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B51" s="23">
+        <v>9004.0</v>
       </c>
       <c r="C51" s="14" t="s">
         <v>115</v>
       </c>
-      <c r="D51" s="18">
-        <f t="shared" si="1"/>
-        <v>8006</v>
+      <c r="D51" s="19">
+        <v>-1.0</v>
       </c>
       <c r="E51" s="14" t="s">
         <v>59</v>
@@ -2887,8 +2833,8 @@
         <v>60</v>
       </c>
       <c r="G51" s="14"/>
-      <c r="H51" s="18" t="s">
-        <v>90</v>
+      <c r="H51" s="34" t="s">
+        <v>61</v>
       </c>
       <c r="I51" s="18">
         <v>0.0</v>
@@ -2896,53 +2842,51 @@
       <c r="J51" s="20"/>
     </row>
     <row r="52">
-      <c r="A52" s="33" t="s">
-        <v>19</v>
-      </c>
-      <c r="B52" s="2">
-        <v>8006.0</v>
-      </c>
-      <c r="C52" s="14" t="s">
+      <c r="A52" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="B52" s="23">
+        <v>10001.0</v>
+      </c>
+      <c r="C52" s="15" t="s">
         <v>116</v>
       </c>
-      <c r="D52" s="18">
-        <f t="shared" si="1"/>
-        <v>8007</v>
-      </c>
-      <c r="E52" s="14" t="s">
+      <c r="D52" s="19">
+        <v>-1.0</v>
+      </c>
+      <c r="E52" s="15" t="s">
         <v>59</v>
       </c>
       <c r="F52" s="17" t="s">
         <v>60</v>
       </c>
       <c r="G52" s="14"/>
-      <c r="H52" s="14" t="s">
+      <c r="H52" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="I52" s="18">
-        <v>0.0</v>
+      <c r="I52" s="19">
+        <v>-1.0</v>
       </c>
       <c r="J52" s="20"/>
     </row>
     <row r="53">
-      <c r="A53" s="33" t="s">
-        <v>19</v>
-      </c>
-      <c r="B53" s="2">
-        <v>8007.0</v>
+      <c r="A53" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="B53" s="23">
+        <v>11001.0</v>
       </c>
       <c r="C53" s="14" t="s">
         <v>117</v>
       </c>
-      <c r="D53" s="18">
-        <f t="shared" si="1"/>
-        <v>8008</v>
+      <c r="D53" s="19">
+        <v>11002.0</v>
       </c>
       <c r="E53" s="14" t="s">
         <v>101</v>
       </c>
       <c r="F53" s="12" t="s">
-        <v>112</v>
+        <v>66</v>
       </c>
       <c r="G53" s="14"/>
       <c r="H53" s="18" t="s">
@@ -2954,18 +2898,17 @@
       <c r="J53" s="20"/>
     </row>
     <row r="54">
-      <c r="A54" s="33" t="s">
-        <v>19</v>
-      </c>
-      <c r="B54" s="2">
-        <v>8008.0</v>
+      <c r="A54" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="B54" s="23">
+        <v>11002.0</v>
       </c>
       <c r="C54" s="14" t="s">
         <v>118</v>
       </c>
-      <c r="D54" s="18">
-        <f t="shared" si="1"/>
-        <v>8009</v>
+      <c r="D54" s="19">
+        <v>11003.0</v>
       </c>
       <c r="E54" s="14" t="s">
         <v>59</v>
@@ -2974,7 +2917,7 @@
         <v>60</v>
       </c>
       <c r="G54" s="14"/>
-      <c r="H54" s="14" t="s">
+      <c r="H54" s="34" t="s">
         <v>61</v>
       </c>
       <c r="I54" s="18">
@@ -2983,24 +2926,23 @@
       <c r="J54" s="20"/>
     </row>
     <row r="55">
-      <c r="A55" s="33" t="s">
-        <v>19</v>
-      </c>
-      <c r="B55" s="2">
-        <v>8009.0</v>
+      <c r="A55" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="B55" s="23">
+        <v>11003.0</v>
       </c>
       <c r="C55" s="14" t="s">
-        <v>109</v>
-      </c>
-      <c r="D55" s="18">
-        <f t="shared" si="1"/>
-        <v>8010</v>
+        <v>119</v>
+      </c>
+      <c r="D55" s="19">
+        <v>11004.0</v>
       </c>
       <c r="E55" s="14" t="s">
         <v>101</v>
       </c>
       <c r="F55" s="12" t="s">
-        <v>112</v>
+        <v>66</v>
       </c>
       <c r="G55" s="14"/>
       <c r="H55" s="18" t="s">
@@ -3012,18 +2954,17 @@
       <c r="J55" s="20"/>
     </row>
     <row r="56">
-      <c r="A56" s="33" t="s">
-        <v>19</v>
-      </c>
-      <c r="B56" s="2">
-        <v>8010.0</v>
+      <c r="A56" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="B56" s="23">
+        <v>11004.0</v>
       </c>
       <c r="C56" s="14" t="s">
-        <v>119</v>
-      </c>
-      <c r="D56" s="18">
-        <f t="shared" si="1"/>
-        <v>8011</v>
+        <v>120</v>
+      </c>
+      <c r="D56" s="19">
+        <v>11005.0</v>
       </c>
       <c r="E56" s="14" t="s">
         <v>59</v>
@@ -3032,114 +2973,110 @@
         <v>60</v>
       </c>
       <c r="G56" s="14"/>
-      <c r="H56" s="14" t="s">
+      <c r="H56" s="34" t="s">
         <v>61</v>
       </c>
       <c r="I56" s="18">
-        <v>4.0</v>
+        <v>2.0</v>
       </c>
       <c r="J56" s="20"/>
     </row>
     <row r="57">
-      <c r="A57" s="33" t="s">
-        <v>19</v>
-      </c>
-      <c r="B57" s="2">
-        <v>8011.0</v>
+      <c r="A57" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="B57" s="23">
+        <v>11005.0</v>
       </c>
       <c r="C57" s="14" t="s">
-        <v>120</v>
-      </c>
-      <c r="D57" s="18">
-        <f t="shared" si="1"/>
-        <v>8012</v>
+        <v>121</v>
+      </c>
+      <c r="D57" s="19">
+        <v>11006.0</v>
       </c>
       <c r="E57" s="14" t="s">
+        <v>59</v>
+      </c>
+      <c r="F57" s="17" t="s">
+        <v>60</v>
+      </c>
+      <c r="G57" s="14"/>
+      <c r="H57" s="34" t="s">
+        <v>61</v>
+      </c>
+      <c r="I57" s="18">
+        <v>0.0</v>
+      </c>
+      <c r="J57" s="20"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="B58" s="23">
+        <v>11006.0</v>
+      </c>
+      <c r="C58" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="D58" s="19">
+        <v>11007.0</v>
+      </c>
+      <c r="E58" s="14" t="s">
         <v>101</v>
       </c>
-      <c r="F57" s="12" t="s">
-        <v>112</v>
-      </c>
-      <c r="G57" s="14"/>
-      <c r="H57" s="18" t="s">
+      <c r="F58" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="G58" s="14"/>
+      <c r="H58" s="18" t="s">
         <v>90</v>
       </c>
-      <c r="I57" s="18">
+      <c r="I58" s="18">
         <v>-1.0</v>
       </c>
-      <c r="J57" s="20"/>
-    </row>
-    <row r="58">
-      <c r="A58" s="33" t="s">
-        <v>19</v>
-      </c>
-      <c r="B58" s="2">
-        <v>8012.0</v>
-      </c>
-      <c r="C58" s="14" t="s">
-        <v>121</v>
-      </c>
-      <c r="D58" s="18">
-        <f t="shared" si="1"/>
-        <v>8013</v>
-      </c>
-      <c r="E58" s="14" t="s">
+      <c r="J58" s="20"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="B59" s="23">
+        <v>11007.0</v>
+      </c>
+      <c r="C59" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="D59" s="19">
+        <v>11008.0</v>
+      </c>
+      <c r="E59" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="F58" s="17" t="s">
+      <c r="F59" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="G58" s="14"/>
-      <c r="H58" s="14" t="s">
+      <c r="G59" s="14"/>
+      <c r="H59" s="34" t="s">
         <v>61</v>
       </c>
-      <c r="I58" s="18">
-        <v>4.0</v>
-      </c>
-      <c r="J58" s="20"/>
-    </row>
-    <row r="59">
-      <c r="A59" s="33" t="s">
-        <v>19</v>
-      </c>
-      <c r="B59" s="2">
-        <v>8013.0</v>
-      </c>
-      <c r="C59" s="14" t="s">
-        <v>122</v>
-      </c>
-      <c r="D59" s="18">
-        <f t="shared" si="1"/>
-        <v>8014</v>
-      </c>
-      <c r="E59" s="14" t="s">
-        <v>101</v>
-      </c>
-      <c r="F59" s="12" t="s">
-        <v>112</v>
-      </c>
-      <c r="G59" s="14"/>
-      <c r="H59" s="18" t="s">
-        <v>90</v>
-      </c>
       <c r="I59" s="18">
+        <v>0.0</v>
+      </c>
+      <c r="J59" s="20"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="9" t="s">
+        <v>25</v>
+      </c>
+      <c r="B60" s="23">
+        <v>11008.0</v>
+      </c>
+      <c r="C60" s="14" t="s">
+        <v>124</v>
+      </c>
+      <c r="D60" s="19">
         <v>-1.0</v>
-      </c>
-      <c r="J59" s="20"/>
-    </row>
-    <row r="60">
-      <c r="A60" s="33" t="s">
-        <v>19</v>
-      </c>
-      <c r="B60" s="2">
-        <v>8014.0</v>
-      </c>
-      <c r="C60" s="14" t="s">
-        <v>123</v>
-      </c>
-      <c r="D60" s="18">
-        <f t="shared" si="1"/>
-        <v>8015</v>
       </c>
       <c r="E60" s="14" t="s">
         <v>59</v>
@@ -3148,8 +3085,8 @@
         <v>60</v>
       </c>
       <c r="G60" s="14"/>
-      <c r="H60" s="14" t="s">
-        <v>61</v>
+      <c r="H60" s="18" t="s">
+        <v>90</v>
       </c>
       <c r="I60" s="18">
         <v>0.0</v>
@@ -3157,47 +3094,45 @@
       <c r="J60" s="20"/>
     </row>
     <row r="61">
-      <c r="A61" s="33" t="s">
-        <v>19</v>
-      </c>
-      <c r="B61" s="2">
-        <v>8015.0</v>
-      </c>
-      <c r="C61" s="14" t="s">
-        <v>124</v>
-      </c>
-      <c r="D61" s="18">
-        <f t="shared" si="1"/>
-        <v>8016</v>
-      </c>
-      <c r="E61" s="14" t="s">
-        <v>101</v>
-      </c>
-      <c r="F61" s="12" t="s">
-        <v>112</v>
+      <c r="A61" s="9" t="s">
+        <v>27</v>
+      </c>
+      <c r="B61" s="23">
+        <v>12001.0</v>
+      </c>
+      <c r="C61" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="D61" s="19">
+        <v>-1.0</v>
+      </c>
+      <c r="E61" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="F61" s="17" t="s">
+        <v>60</v>
       </c>
       <c r="G61" s="14"/>
-      <c r="H61" s="18" t="s">
-        <v>90</v>
-      </c>
-      <c r="I61" s="18">
+      <c r="H61" s="35" t="s">
+        <v>61</v>
+      </c>
+      <c r="I61" s="19">
         <v>-1.0</v>
       </c>
       <c r="J61" s="20"/>
     </row>
     <row r="62">
-      <c r="A62" s="33" t="s">
-        <v>19</v>
-      </c>
-      <c r="B62" s="2">
-        <v>8016.0</v>
+      <c r="A62" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="B62" s="23">
+        <v>13001.0</v>
       </c>
       <c r="C62" s="14" t="s">
-        <v>125</v>
-      </c>
-      <c r="D62" s="18">
-        <f t="shared" si="1"/>
-        <v>8017</v>
+        <v>126</v>
+      </c>
+      <c r="D62" s="19">
+        <v>13002.0</v>
       </c>
       <c r="E62" s="14" t="s">
         <v>59</v>
@@ -3206,7 +3141,7 @@
         <v>60</v>
       </c>
       <c r="G62" s="14"/>
-      <c r="H62" s="14" t="s">
+      <c r="H62" s="34" t="s">
         <v>61</v>
       </c>
       <c r="I62" s="18">
@@ -3215,47 +3150,45 @@
       <c r="J62" s="20"/>
     </row>
     <row r="63">
-      <c r="A63" s="33" t="s">
-        <v>19</v>
-      </c>
-      <c r="B63" s="2">
-        <v>8017.0</v>
+      <c r="A63" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="B63" s="23">
+        <v>13002.0</v>
       </c>
       <c r="C63" s="14" t="s">
-        <v>117</v>
-      </c>
-      <c r="D63" s="18">
-        <f t="shared" si="1"/>
-        <v>-1</v>
+        <v>127</v>
+      </c>
+      <c r="D63" s="19">
+        <v>13003.0</v>
       </c>
       <c r="E63" s="14" t="s">
-        <v>101</v>
-      </c>
-      <c r="F63" s="12" t="s">
-        <v>112</v>
+        <v>59</v>
+      </c>
+      <c r="F63" s="17" t="s">
+        <v>60</v>
       </c>
       <c r="G63" s="14"/>
-      <c r="H63" s="18" t="s">
-        <v>90</v>
+      <c r="H63" s="34" t="s">
+        <v>61</v>
       </c>
       <c r="I63" s="18">
+        <v>0.0</v>
+      </c>
+      <c r="J63" s="20"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="B64" s="23">
+        <v>13003.0</v>
+      </c>
+      <c r="C64" s="14" t="s">
+        <v>128</v>
+      </c>
+      <c r="D64" s="19">
         <v>-1.0</v>
-      </c>
-      <c r="J63" s="20"/>
-    </row>
-    <row r="64">
-      <c r="A64" s="33" t="s">
-        <v>21</v>
-      </c>
-      <c r="B64" s="2">
-        <v>9001.0</v>
-      </c>
-      <c r="C64" s="14" t="s">
-        <v>126</v>
-      </c>
-      <c r="D64" s="18">
-        <f t="shared" si="1"/>
-        <v>9002</v>
       </c>
       <c r="E64" s="14" t="s">
         <v>59</v>
@@ -3273,18 +3206,17 @@
       <c r="J64" s="20"/>
     </row>
     <row r="65">
-      <c r="A65" s="33" t="s">
-        <v>21</v>
-      </c>
-      <c r="B65" s="2">
-        <v>9002.0</v>
+      <c r="A65" s="9" t="s">
+        <v>129</v>
+      </c>
+      <c r="B65" s="23">
+        <v>14001.0</v>
       </c>
       <c r="C65" s="14" t="s">
-        <v>127</v>
-      </c>
-      <c r="D65" s="18">
-        <f t="shared" si="1"/>
-        <v>9003</v>
+        <v>130</v>
+      </c>
+      <c r="D65" s="19">
+        <v>14002.0</v>
       </c>
       <c r="E65" s="14" t="s">
         <v>59</v>
@@ -3302,18 +3234,17 @@
       <c r="J65" s="20"/>
     </row>
     <row r="66">
-      <c r="A66" s="33" t="s">
-        <v>21</v>
-      </c>
-      <c r="B66" s="2">
-        <v>9003.0</v>
+      <c r="A66" s="9" t="s">
+        <v>31</v>
+      </c>
+      <c r="B66" s="23">
+        <v>14002.0</v>
       </c>
       <c r="C66" s="14" t="s">
-        <v>128</v>
-      </c>
-      <c r="D66" s="18">
-        <f t="shared" si="1"/>
-        <v>9004</v>
+        <v>131</v>
+      </c>
+      <c r="D66" s="19">
+        <v>-1.0</v>
       </c>
       <c r="E66" s="14" t="s">
         <v>59</v>
@@ -3331,18 +3262,17 @@
       <c r="J66" s="20"/>
     </row>
     <row r="67">
-      <c r="A67" s="33" t="s">
-        <v>21</v>
-      </c>
-      <c r="B67" s="2">
-        <v>9004.0</v>
+      <c r="A67" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="B67" s="23">
+        <v>15001.0</v>
       </c>
       <c r="C67" s="14" t="s">
-        <v>129</v>
-      </c>
-      <c r="D67" s="18">
-        <f t="shared" si="1"/>
-        <v>-1</v>
+        <v>132</v>
+      </c>
+      <c r="D67" s="19">
+        <v>15002.0</v>
       </c>
       <c r="E67" s="14" t="s">
         <v>59</v>
@@ -3360,47 +3290,45 @@
       <c r="J67" s="20"/>
     </row>
     <row r="68">
-      <c r="A68" s="33" t="s">
-        <v>23</v>
-      </c>
-      <c r="B68" s="2">
-        <v>10001.0</v>
+      <c r="A68" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="B68" s="23">
+        <v>15002.0</v>
       </c>
       <c r="C68" s="14" t="s">
-        <v>130</v>
-      </c>
-      <c r="D68" s="18">
-        <f t="shared" si="1"/>
-        <v>10002</v>
+        <v>133</v>
+      </c>
+      <c r="D68" s="19">
+        <v>15003.0</v>
       </c>
       <c r="E68" s="14" t="s">
-        <v>101</v>
-      </c>
-      <c r="F68" s="12" t="s">
-        <v>66</v>
+        <v>59</v>
+      </c>
+      <c r="F68" s="17" t="s">
+        <v>60</v>
       </c>
       <c r="G68" s="14"/>
-      <c r="H68" s="18" t="s">
-        <v>90</v>
+      <c r="H68" s="34" t="s">
+        <v>61</v>
       </c>
       <c r="I68" s="18">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="J68" s="20"/>
     </row>
     <row r="69">
-      <c r="A69" s="33" t="s">
-        <v>23</v>
-      </c>
-      <c r="B69" s="2">
-        <v>10002.0</v>
-      </c>
-      <c r="C69" s="14" t="s">
-        <v>131</v>
-      </c>
-      <c r="D69" s="18">
-        <f t="shared" si="1"/>
-        <v>10003</v>
+      <c r="A69" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="B69" s="23">
+        <v>15003.0</v>
+      </c>
+      <c r="C69" s="15" t="s">
+        <v>134</v>
+      </c>
+      <c r="D69" s="19">
+        <v>15004.0</v>
       </c>
       <c r="E69" s="14" t="s">
         <v>59</v>
@@ -3413,52 +3341,50 @@
         <v>61</v>
       </c>
       <c r="I69" s="18">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="J69" s="20"/>
     </row>
     <row r="70">
-      <c r="A70" s="33" t="s">
-        <v>23</v>
-      </c>
-      <c r="B70" s="2">
-        <v>10003.0</v>
+      <c r="A70" s="9" t="s">
+        <v>33</v>
+      </c>
+      <c r="B70" s="23">
+        <v>15004.0</v>
       </c>
       <c r="C70" s="14" t="s">
-        <v>132</v>
-      </c>
-      <c r="D70" s="18">
-        <f t="shared" si="1"/>
-        <v>10004</v>
+        <v>135</v>
+      </c>
+      <c r="D70" s="19">
+        <v>-1.0</v>
       </c>
       <c r="E70" s="14" t="s">
-        <v>101</v>
-      </c>
-      <c r="F70" s="12" t="s">
-        <v>66</v>
+        <v>59</v>
+      </c>
+      <c r="F70" s="17" t="s">
+        <v>60</v>
       </c>
       <c r="G70" s="14"/>
-      <c r="H70" s="18" t="s">
-        <v>90</v>
+      <c r="H70" s="34" t="s">
+        <v>61</v>
       </c>
       <c r="I70" s="18">
-        <v>-1.0</v>
+        <v>0.0</v>
       </c>
       <c r="J70" s="20"/>
     </row>
     <row r="71">
-      <c r="A71" s="33" t="s">
-        <v>23</v>
-      </c>
-      <c r="B71" s="2">
-        <v>10004.0</v>
+      <c r="A71" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="B71" s="23">
+        <v>16001.0</v>
       </c>
       <c r="C71" s="14" t="s">
-        <v>133</v>
-      </c>
-      <c r="D71" s="18">
-        <f t="shared" si="1"/>
-        <v>10005</v>
+        <v>136</v>
+      </c>
+      <c r="D71" s="19">
+        <v>16002.0</v>
       </c>
       <c r="E71" s="14" t="s">
         <v>59</v>
@@ -3471,23 +3397,22 @@
         <v>61</v>
       </c>
       <c r="I71" s="18">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="J71" s="20"/>
     </row>
     <row r="72">
-      <c r="A72" s="33" t="s">
-        <v>23</v>
-      </c>
-      <c r="B72" s="2">
-        <v>10005.0</v>
+      <c r="A72" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="B72" s="23">
+        <v>16002.0</v>
       </c>
       <c r="C72" s="14" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="D72" s="18">
-        <f t="shared" si="1"/>
-        <v>10006</v>
+        <v>-1.0</v>
       </c>
       <c r="E72" s="14" t="s">
         <v>59</v>
@@ -3505,3398 +3430,2848 @@
       <c r="J72" s="20"/>
     </row>
     <row r="73">
-      <c r="A73" s="33" t="s">
-        <v>23</v>
-      </c>
-      <c r="B73" s="2">
-        <v>10006.0</v>
-      </c>
-      <c r="C73" s="14" t="s">
-        <v>135</v>
-      </c>
-      <c r="D73" s="18">
-        <f t="shared" si="1"/>
-        <v>10007</v>
-      </c>
-      <c r="E73" s="14" t="s">
-        <v>101</v>
-      </c>
-      <c r="F73" s="12" t="s">
-        <v>66</v>
+      <c r="A73" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="B73" s="4">
+        <v>17001.0</v>
+      </c>
+      <c r="C73" s="15" t="s">
+        <v>138</v>
+      </c>
+      <c r="D73" s="19">
+        <v>17002.0</v>
+      </c>
+      <c r="E73" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="F73" s="17" t="s">
+        <v>60</v>
       </c>
       <c r="G73" s="14"/>
-      <c r="H73" s="18" t="s">
-        <v>90</v>
-      </c>
-      <c r="I73" s="18">
-        <v>-1.0</v>
+      <c r="H73" s="34" t="s">
+        <v>61</v>
+      </c>
+      <c r="I73" s="19">
+        <v>2.0</v>
       </c>
       <c r="J73" s="20"/>
     </row>
     <row r="74">
-      <c r="A74" s="33" t="s">
-        <v>23</v>
-      </c>
-      <c r="B74" s="2">
-        <v>10007.0</v>
-      </c>
-      <c r="C74" s="14" t="s">
-        <v>136</v>
-      </c>
-      <c r="D74" s="18">
-        <f t="shared" si="1"/>
-        <v>10008</v>
-      </c>
-      <c r="E74" s="14" t="s">
+      <c r="A74" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="B74" s="4">
+        <v>17002.0</v>
+      </c>
+      <c r="C74" s="37" t="s">
+        <v>139</v>
+      </c>
+      <c r="D74" s="4">
+        <v>17003.0</v>
+      </c>
+      <c r="E74" s="15" t="s">
         <v>59</v>
       </c>
       <c r="F74" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="G74" s="14"/>
       <c r="H74" s="34" t="s">
         <v>61</v>
       </c>
-      <c r="I74" s="18">
-        <v>0.0</v>
-      </c>
-      <c r="J74" s="20"/>
+      <c r="I74" s="19">
+        <v>2.0</v>
+      </c>
     </row>
     <row r="75">
-      <c r="A75" s="33" t="s">
-        <v>23</v>
-      </c>
-      <c r="B75" s="2">
-        <v>10008.0</v>
-      </c>
-      <c r="C75" s="14" t="s">
-        <v>137</v>
-      </c>
-      <c r="D75" s="18">
-        <f t="shared" si="1"/>
-        <v>-1</v>
-      </c>
-      <c r="E75" s="14" t="s">
+      <c r="A75" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="B75" s="4">
+        <v>17003.0</v>
+      </c>
+      <c r="C75" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="D75" s="19">
+        <v>17004.0</v>
+      </c>
+      <c r="E75" s="15" t="s">
         <v>59</v>
       </c>
       <c r="F75" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="G75" s="14"/>
-      <c r="H75" s="18" t="s">
-        <v>90</v>
-      </c>
-      <c r="I75" s="18">
-        <v>0.0</v>
-      </c>
-      <c r="J75" s="20"/>
+      <c r="H75" s="34" t="s">
+        <v>61</v>
+      </c>
+      <c r="I75" s="19">
+        <v>2.0</v>
+      </c>
     </row>
     <row r="76">
-      <c r="A76" s="33" t="s">
-        <v>25</v>
-      </c>
-      <c r="B76" s="2">
-        <v>11001.0</v>
-      </c>
-      <c r="C76" s="14" t="s">
-        <v>138</v>
-      </c>
-      <c r="D76" s="18">
-        <f t="shared" si="1"/>
-        <v>11002</v>
-      </c>
-      <c r="E76" s="14" t="s">
+      <c r="A76" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="B76" s="4">
+        <v>17004.0</v>
+      </c>
+      <c r="C76" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="D76" s="4">
+        <v>17005.0</v>
+      </c>
+      <c r="E76" s="15" t="s">
         <v>59</v>
       </c>
       <c r="F76" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="G76" s="14"/>
       <c r="H76" s="34" t="s">
         <v>61</v>
       </c>
-      <c r="I76" s="18">
-        <v>0.0</v>
-      </c>
-      <c r="J76" s="20"/>
+      <c r="I76" s="19">
+        <v>2.0</v>
+      </c>
     </row>
     <row r="77">
-      <c r="A77" s="33" t="s">
-        <v>25</v>
-      </c>
-      <c r="B77" s="2">
-        <v>11002.0</v>
-      </c>
-      <c r="C77" s="14" t="s">
-        <v>139</v>
-      </c>
-      <c r="D77" s="18">
-        <f t="shared" si="1"/>
-        <v>11003</v>
-      </c>
-      <c r="E77" s="14" t="s">
+      <c r="A77" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="B77" s="4">
+        <v>17005.0</v>
+      </c>
+      <c r="C77" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="D77" s="4">
+        <v>-1.0</v>
+      </c>
+      <c r="E77" s="15" t="s">
         <v>59</v>
       </c>
       <c r="F77" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="G77" s="14"/>
       <c r="H77" s="34" t="s">
         <v>61</v>
       </c>
-      <c r="I77" s="18">
+      <c r="I77" s="4">
         <v>0.0</v>
       </c>
-      <c r="J77" s="20"/>
     </row>
     <row r="78">
-      <c r="A78" s="33" t="s">
-        <v>25</v>
-      </c>
-      <c r="B78" s="2">
-        <v>11003.0</v>
-      </c>
-      <c r="C78" s="14" t="s">
-        <v>140</v>
-      </c>
-      <c r="D78" s="18">
-        <f t="shared" si="1"/>
-        <v>-1</v>
-      </c>
-      <c r="E78" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="F78" s="17" t="s">
-        <v>60</v>
-      </c>
-      <c r="G78" s="14"/>
-      <c r="H78" s="34" t="s">
-        <v>61</v>
-      </c>
-      <c r="I78" s="18">
-        <v>0.0</v>
-      </c>
-      <c r="J78" s="20"/>
+      <c r="A78" s="38"/>
     </row>
     <row r="79">
-      <c r="A79" s="33" t="s">
-        <v>27</v>
-      </c>
-      <c r="B79" s="2">
-        <v>12001.0</v>
-      </c>
-      <c r="C79" s="14" t="s">
-        <v>141</v>
-      </c>
-      <c r="D79" s="18">
-        <f t="shared" si="1"/>
-        <v>12003</v>
-      </c>
-      <c r="E79" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="F79" s="17" t="s">
-        <v>60</v>
-      </c>
-      <c r="G79" s="14"/>
-      <c r="H79" s="34" t="s">
-        <v>61</v>
-      </c>
-      <c r="I79" s="18">
-        <v>4.0</v>
-      </c>
-      <c r="J79" s="20"/>
+      <c r="A79" s="38"/>
     </row>
     <row r="80">
-      <c r="A80" s="33" t="s">
-        <v>27</v>
-      </c>
-      <c r="B80" s="2">
-        <v>12003.0</v>
-      </c>
-      <c r="C80" s="14" t="s">
-        <v>142</v>
-      </c>
-      <c r="D80" s="18">
-        <f t="shared" si="1"/>
-        <v>-1</v>
-      </c>
-      <c r="E80" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="F80" s="17" t="s">
-        <v>60</v>
-      </c>
-      <c r="G80" s="14"/>
-      <c r="H80" s="34" t="s">
-        <v>61</v>
-      </c>
-      <c r="I80" s="18">
-        <v>0.0</v>
-      </c>
-      <c r="J80" s="20"/>
+      <c r="A80" s="38"/>
     </row>
     <row r="81">
-      <c r="A81" s="33" t="s">
-        <v>29</v>
-      </c>
-      <c r="B81" s="2">
-        <v>13001.0</v>
-      </c>
-      <c r="C81" s="14" t="s">
-        <v>143</v>
-      </c>
-      <c r="D81" s="18">
-        <f t="shared" si="1"/>
-        <v>13002</v>
-      </c>
-      <c r="E81" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="F81" s="17" t="s">
-        <v>60</v>
-      </c>
-      <c r="G81" s="14"/>
-      <c r="H81" s="34" t="s">
-        <v>61</v>
-      </c>
-      <c r="I81" s="18">
-        <v>0.0</v>
-      </c>
-      <c r="J81" s="20"/>
+      <c r="A81" s="38"/>
     </row>
     <row r="82">
-      <c r="A82" s="33" t="s">
-        <v>29</v>
-      </c>
-      <c r="B82" s="2">
-        <v>13002.0</v>
-      </c>
-      <c r="C82" s="14" t="s">
-        <v>144</v>
-      </c>
-      <c r="D82" s="18">
-        <f t="shared" si="1"/>
-        <v>-1</v>
-      </c>
-      <c r="E82" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="F82" s="17" t="s">
-        <v>60</v>
-      </c>
-      <c r="G82" s="14"/>
-      <c r="H82" s="34" t="s">
-        <v>61</v>
-      </c>
-      <c r="I82" s="18">
-        <v>0.0</v>
-      </c>
-      <c r="J82" s="20"/>
+      <c r="A82" s="38"/>
     </row>
     <row r="83">
-      <c r="A83" s="33" t="s">
-        <v>31</v>
-      </c>
-      <c r="B83" s="2">
-        <v>14001.0</v>
-      </c>
-      <c r="C83" s="14" t="s">
-        <v>145</v>
-      </c>
-      <c r="D83" s="18">
-        <f t="shared" si="1"/>
-        <v>14002</v>
-      </c>
-      <c r="E83" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="F83" s="17" t="s">
-        <v>60</v>
-      </c>
-      <c r="G83" s="14"/>
-      <c r="H83" s="34" t="s">
-        <v>61</v>
-      </c>
-      <c r="I83" s="18">
-        <v>0.0</v>
-      </c>
-      <c r="J83" s="20"/>
+      <c r="A83" s="38"/>
     </row>
     <row r="84">
-      <c r="A84" s="33" t="s">
-        <v>31</v>
-      </c>
-      <c r="B84" s="2">
-        <v>14002.0</v>
-      </c>
-      <c r="C84" s="14" t="s">
-        <v>146</v>
-      </c>
-      <c r="D84" s="18">
-        <f t="shared" si="1"/>
-        <v>14003</v>
-      </c>
-      <c r="E84" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="F84" s="17" t="s">
-        <v>60</v>
-      </c>
-      <c r="G84" s="14"/>
-      <c r="H84" s="34" t="s">
-        <v>61</v>
-      </c>
-      <c r="I84" s="18">
-        <v>0.0</v>
-      </c>
-      <c r="J84" s="20"/>
+      <c r="A84" s="38"/>
     </row>
     <row r="85">
-      <c r="A85" s="33" t="s">
-        <v>31</v>
-      </c>
-      <c r="B85" s="2">
-        <v>14003.0</v>
-      </c>
-      <c r="C85" s="14" t="s">
-        <v>147</v>
-      </c>
-      <c r="D85" s="18">
-        <f t="shared" si="1"/>
-        <v>-1</v>
-      </c>
-      <c r="E85" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="F85" s="17" t="s">
-        <v>60</v>
-      </c>
-      <c r="G85" s="14"/>
-      <c r="H85" s="34" t="s">
-        <v>61</v>
-      </c>
-      <c r="I85" s="18">
-        <v>0.0</v>
-      </c>
-      <c r="J85" s="20"/>
+      <c r="A85" s="38"/>
     </row>
     <row r="86">
-      <c r="A86" s="33" t="s">
-        <v>33</v>
-      </c>
-      <c r="B86" s="2">
-        <v>15001.0</v>
-      </c>
-      <c r="C86" s="14" t="s">
-        <v>148</v>
-      </c>
-      <c r="D86" s="18">
-        <f t="shared" si="1"/>
-        <v>15002</v>
-      </c>
-      <c r="E86" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="F86" s="17" t="s">
-        <v>60</v>
-      </c>
-      <c r="G86" s="14"/>
-      <c r="H86" s="34" t="s">
-        <v>61</v>
-      </c>
-      <c r="I86" s="18">
-        <v>0.0</v>
-      </c>
-      <c r="J86" s="20"/>
+      <c r="A86" s="38"/>
     </row>
     <row r="87">
-      <c r="A87" s="33" t="s">
-        <v>33</v>
-      </c>
-      <c r="B87" s="2">
-        <v>15002.0</v>
-      </c>
-      <c r="C87" s="14" t="s">
-        <v>149</v>
-      </c>
-      <c r="D87" s="18">
-        <f t="shared" si="1"/>
-        <v>15003</v>
-      </c>
-      <c r="E87" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="F87" s="17" t="s">
-        <v>60</v>
-      </c>
-      <c r="G87" s="14"/>
-      <c r="H87" s="34" t="s">
-        <v>61</v>
-      </c>
-      <c r="I87" s="18">
-        <v>0.0</v>
-      </c>
-      <c r="J87" s="20"/>
+      <c r="A87" s="38"/>
     </row>
     <row r="88">
-      <c r="A88" s="33" t="s">
-        <v>33</v>
-      </c>
-      <c r="B88" s="2">
-        <v>15003.0</v>
-      </c>
-      <c r="C88" s="14" t="s">
-        <v>150</v>
-      </c>
-      <c r="D88" s="18">
-        <f t="shared" si="1"/>
-        <v>15004</v>
-      </c>
-      <c r="E88" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="F88" s="17" t="s">
-        <v>60</v>
-      </c>
-      <c r="G88" s="14"/>
-      <c r="H88" s="34" t="s">
-        <v>61</v>
-      </c>
-      <c r="I88" s="18">
-        <v>0.0</v>
-      </c>
-      <c r="J88" s="20"/>
+      <c r="A88" s="38"/>
     </row>
     <row r="89">
-      <c r="A89" s="33" t="s">
-        <v>33</v>
-      </c>
-      <c r="B89" s="2">
-        <v>15004.0</v>
-      </c>
-      <c r="C89" s="14" t="s">
-        <v>151</v>
-      </c>
-      <c r="D89" s="18">
-        <f t="shared" si="1"/>
-        <v>-1</v>
-      </c>
-      <c r="E89" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="F89" s="17" t="s">
-        <v>60</v>
-      </c>
-      <c r="G89" s="14"/>
-      <c r="H89" s="34" t="s">
-        <v>61</v>
-      </c>
-      <c r="I89" s="18">
-        <v>0.0</v>
-      </c>
-      <c r="J89" s="20"/>
+      <c r="A89" s="38"/>
     </row>
     <row r="90">
-      <c r="A90" s="33" t="s">
-        <v>35</v>
-      </c>
-      <c r="B90" s="2">
-        <v>16001.0</v>
-      </c>
-      <c r="C90" s="14" t="s">
-        <v>152</v>
-      </c>
-      <c r="D90" s="18">
-        <f t="shared" si="1"/>
-        <v>16002</v>
-      </c>
-      <c r="E90" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="F90" s="17" t="s">
-        <v>60</v>
-      </c>
-      <c r="G90" s="14"/>
-      <c r="H90" s="34" t="s">
-        <v>61</v>
-      </c>
-      <c r="I90" s="18">
-        <v>0.0</v>
-      </c>
-      <c r="J90" s="20"/>
+      <c r="A90" s="38"/>
     </row>
     <row r="91">
-      <c r="A91" s="33" t="s">
-        <v>35</v>
-      </c>
-      <c r="B91" s="2">
-        <v>16002.0</v>
-      </c>
-      <c r="C91" s="14" t="s">
-        <v>153</v>
-      </c>
-      <c r="D91" s="18">
-        <v>-1.0</v>
-      </c>
-      <c r="E91" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="F91" s="17" t="s">
-        <v>60</v>
-      </c>
-      <c r="G91" s="14"/>
-      <c r="H91" s="34" t="s">
-        <v>61</v>
-      </c>
-      <c r="I91" s="18">
-        <v>0.0</v>
-      </c>
-      <c r="J91" s="20"/>
+      <c r="A91" s="38"/>
     </row>
     <row r="92">
-      <c r="A92" s="35" t="s">
-        <v>37</v>
-      </c>
-      <c r="B92" s="4">
-        <v>17001.0</v>
-      </c>
-      <c r="C92" s="15" t="s">
-        <v>154</v>
-      </c>
-      <c r="D92" s="19">
-        <v>17002.0</v>
-      </c>
-      <c r="E92" s="15" t="s">
-        <v>59</v>
-      </c>
-      <c r="F92" s="17" t="s">
-        <v>60</v>
-      </c>
-      <c r="G92" s="14"/>
-      <c r="H92" s="34" t="s">
-        <v>61</v>
-      </c>
-      <c r="I92" s="19">
-        <v>2.0</v>
-      </c>
-      <c r="J92" s="20"/>
+      <c r="A92" s="38"/>
     </row>
     <row r="93">
-      <c r="A93" s="35" t="s">
-        <v>37</v>
-      </c>
-      <c r="B93" s="4">
-        <v>17002.0</v>
-      </c>
-      <c r="C93" s="36" t="s">
-        <v>155</v>
-      </c>
-      <c r="D93" s="4">
-        <v>17003.0</v>
-      </c>
-      <c r="E93" s="15" t="s">
-        <v>59</v>
-      </c>
-      <c r="F93" s="17" t="s">
-        <v>60</v>
-      </c>
-      <c r="H93" s="34" t="s">
-        <v>61</v>
-      </c>
-      <c r="I93" s="19">
-        <v>2.0</v>
-      </c>
+      <c r="A93" s="38"/>
     </row>
     <row r="94">
-      <c r="A94" s="35" t="s">
-        <v>37</v>
-      </c>
-      <c r="B94" s="4">
-        <v>17003.0</v>
-      </c>
-      <c r="C94" s="4" t="s">
-        <v>156</v>
-      </c>
-      <c r="D94" s="19">
-        <v>17004.0</v>
-      </c>
-      <c r="E94" s="15" t="s">
-        <v>59</v>
-      </c>
-      <c r="F94" s="17" t="s">
-        <v>60</v>
-      </c>
-      <c r="H94" s="34" t="s">
-        <v>61</v>
-      </c>
-      <c r="I94" s="19">
-        <v>2.0</v>
-      </c>
+      <c r="A94" s="38"/>
     </row>
     <row r="95">
-      <c r="A95" s="35" t="s">
-        <v>37</v>
-      </c>
-      <c r="B95" s="4">
-        <v>17004.0</v>
-      </c>
-      <c r="C95" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="D95" s="4">
-        <v>17005.0</v>
-      </c>
-      <c r="E95" s="15" t="s">
-        <v>59</v>
-      </c>
-      <c r="F95" s="17" t="s">
-        <v>60</v>
-      </c>
-      <c r="H95" s="34" t="s">
-        <v>61</v>
-      </c>
-      <c r="I95" s="19">
-        <v>2.0</v>
-      </c>
+      <c r="A95" s="38"/>
     </row>
     <row r="96">
-      <c r="A96" s="35" t="s">
-        <v>37</v>
-      </c>
-      <c r="B96" s="4">
-        <v>17005.0</v>
-      </c>
-      <c r="C96" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="D96" s="4">
-        <v>-1.0</v>
-      </c>
-      <c r="E96" s="15" t="s">
-        <v>59</v>
-      </c>
-      <c r="F96" s="17" t="s">
-        <v>60</v>
-      </c>
-      <c r="H96" s="34" t="s">
-        <v>61</v>
-      </c>
-      <c r="I96" s="4">
-        <v>0.0</v>
-      </c>
+      <c r="A96" s="38"/>
     </row>
     <row r="97">
-      <c r="A97" s="37"/>
+      <c r="A97" s="38"/>
     </row>
     <row r="98">
-      <c r="A98" s="37"/>
+      <c r="A98" s="38"/>
     </row>
     <row r="99">
-      <c r="A99" s="37"/>
+      <c r="A99" s="38"/>
     </row>
     <row r="100">
-      <c r="A100" s="37"/>
+      <c r="A100" s="38"/>
     </row>
     <row r="101">
-      <c r="A101" s="37"/>
+      <c r="A101" s="38"/>
     </row>
     <row r="102">
-      <c r="A102" s="37"/>
+      <c r="A102" s="38"/>
     </row>
     <row r="103">
-      <c r="A103" s="37"/>
+      <c r="A103" s="38"/>
     </row>
     <row r="104">
-      <c r="A104" s="37"/>
+      <c r="A104" s="38"/>
     </row>
     <row r="105">
-      <c r="A105" s="37"/>
+      <c r="A105" s="38"/>
     </row>
     <row r="106">
-      <c r="A106" s="37"/>
+      <c r="A106" s="38"/>
     </row>
     <row r="107">
-      <c r="A107" s="37"/>
+      <c r="A107" s="38"/>
     </row>
     <row r="108">
-      <c r="A108" s="37"/>
+      <c r="A108" s="38"/>
     </row>
     <row r="109">
-      <c r="A109" s="37"/>
+      <c r="A109" s="38"/>
     </row>
     <row r="110">
-      <c r="A110" s="37"/>
+      <c r="A110" s="38"/>
     </row>
     <row r="111">
-      <c r="A111" s="37"/>
+      <c r="A111" s="38"/>
     </row>
     <row r="112">
-      <c r="A112" s="37"/>
+      <c r="A112" s="38"/>
     </row>
     <row r="113">
-      <c r="A113" s="37"/>
+      <c r="A113" s="38"/>
     </row>
     <row r="114">
-      <c r="A114" s="37"/>
+      <c r="A114" s="38"/>
     </row>
     <row r="115">
-      <c r="A115" s="37"/>
+      <c r="A115" s="38"/>
     </row>
     <row r="116">
-      <c r="A116" s="37"/>
+      <c r="A116" s="38"/>
     </row>
     <row r="117">
-      <c r="A117" s="37"/>
+      <c r="A117" s="38"/>
     </row>
     <row r="118">
-      <c r="A118" s="37"/>
+      <c r="A118" s="38"/>
     </row>
     <row r="119">
-      <c r="A119" s="37"/>
+      <c r="A119" s="38"/>
     </row>
     <row r="120">
-      <c r="A120" s="37"/>
+      <c r="A120" s="38"/>
     </row>
     <row r="121">
-      <c r="A121" s="37"/>
+      <c r="A121" s="38"/>
     </row>
     <row r="122">
-      <c r="A122" s="37"/>
+      <c r="A122" s="38"/>
     </row>
     <row r="123">
-      <c r="A123" s="37"/>
+      <c r="A123" s="38"/>
     </row>
     <row r="124">
-      <c r="A124" s="37"/>
+      <c r="A124" s="38"/>
     </row>
     <row r="125">
-      <c r="A125" s="37"/>
+      <c r="A125" s="38"/>
     </row>
     <row r="126">
-      <c r="A126" s="37"/>
+      <c r="A126" s="38"/>
     </row>
     <row r="127">
-      <c r="A127" s="37"/>
+      <c r="A127" s="38"/>
     </row>
     <row r="128">
-      <c r="A128" s="37"/>
+      <c r="A128" s="38"/>
     </row>
     <row r="129">
-      <c r="A129" s="37"/>
+      <c r="A129" s="38"/>
     </row>
     <row r="130">
-      <c r="A130" s="37"/>
+      <c r="A130" s="38"/>
     </row>
     <row r="131">
-      <c r="A131" s="37"/>
+      <c r="A131" s="38"/>
     </row>
     <row r="132">
-      <c r="A132" s="37"/>
+      <c r="A132" s="38"/>
     </row>
     <row r="133">
-      <c r="A133" s="37"/>
+      <c r="A133" s="38"/>
     </row>
     <row r="134">
-      <c r="A134" s="37"/>
+      <c r="A134" s="38"/>
     </row>
     <row r="135">
-      <c r="A135" s="37"/>
+      <c r="A135" s="38"/>
     </row>
     <row r="136">
-      <c r="A136" s="37"/>
+      <c r="A136" s="38"/>
     </row>
     <row r="137">
-      <c r="A137" s="37"/>
+      <c r="A137" s="38"/>
     </row>
     <row r="138">
-      <c r="A138" s="37"/>
+      <c r="A138" s="38"/>
     </row>
     <row r="139">
-      <c r="A139" s="37"/>
+      <c r="A139" s="38"/>
     </row>
     <row r="140">
-      <c r="A140" s="37"/>
+      <c r="A140" s="38"/>
     </row>
     <row r="141">
-      <c r="A141" s="37"/>
+      <c r="A141" s="38"/>
     </row>
     <row r="142">
-      <c r="A142" s="37"/>
+      <c r="A142" s="38"/>
     </row>
     <row r="143">
-      <c r="A143" s="37"/>
+      <c r="A143" s="38"/>
     </row>
     <row r="144">
-      <c r="A144" s="37"/>
+      <c r="A144" s="38"/>
     </row>
     <row r="145">
-      <c r="A145" s="37"/>
+      <c r="A145" s="38"/>
     </row>
     <row r="146">
-      <c r="A146" s="37"/>
+      <c r="A146" s="38"/>
     </row>
     <row r="147">
-      <c r="A147" s="37"/>
+      <c r="A147" s="38"/>
     </row>
     <row r="148">
-      <c r="A148" s="37"/>
+      <c r="A148" s="38"/>
     </row>
     <row r="149">
-      <c r="A149" s="37"/>
+      <c r="A149" s="38"/>
     </row>
     <row r="150">
-      <c r="A150" s="37"/>
+      <c r="A150" s="38"/>
     </row>
     <row r="151">
-      <c r="A151" s="37"/>
+      <c r="A151" s="38"/>
     </row>
     <row r="152">
-      <c r="A152" s="37"/>
+      <c r="A152" s="38"/>
     </row>
     <row r="153">
-      <c r="A153" s="37"/>
+      <c r="A153" s="38"/>
     </row>
     <row r="154">
-      <c r="A154" s="37"/>
+      <c r="A154" s="38"/>
     </row>
     <row r="155">
-      <c r="A155" s="37"/>
+      <c r="A155" s="38"/>
     </row>
     <row r="156">
-      <c r="A156" s="37"/>
+      <c r="A156" s="38"/>
     </row>
     <row r="157">
-      <c r="A157" s="37"/>
+      <c r="A157" s="38"/>
     </row>
     <row r="158">
-      <c r="A158" s="37"/>
+      <c r="A158" s="38"/>
     </row>
     <row r="159">
-      <c r="A159" s="37"/>
+      <c r="A159" s="38"/>
     </row>
     <row r="160">
-      <c r="A160" s="37"/>
+      <c r="A160" s="38"/>
     </row>
     <row r="161">
-      <c r="A161" s="37"/>
+      <c r="A161" s="38"/>
     </row>
     <row r="162">
-      <c r="A162" s="37"/>
+      <c r="A162" s="38"/>
     </row>
     <row r="163">
-      <c r="A163" s="37"/>
+      <c r="A163" s="38"/>
     </row>
     <row r="164">
-      <c r="A164" s="37"/>
+      <c r="A164" s="38"/>
     </row>
     <row r="165">
-      <c r="A165" s="37"/>
+      <c r="A165" s="38"/>
     </row>
     <row r="166">
-      <c r="A166" s="37"/>
+      <c r="A166" s="38"/>
     </row>
     <row r="167">
-      <c r="A167" s="37"/>
+      <c r="A167" s="38"/>
     </row>
     <row r="168">
-      <c r="A168" s="37"/>
+      <c r="A168" s="38"/>
     </row>
     <row r="169">
-      <c r="A169" s="37"/>
+      <c r="A169" s="38"/>
     </row>
     <row r="170">
-      <c r="A170" s="37"/>
+      <c r="A170" s="38"/>
     </row>
     <row r="171">
-      <c r="A171" s="37"/>
+      <c r="A171" s="38"/>
     </row>
     <row r="172">
-      <c r="A172" s="37"/>
+      <c r="A172" s="38"/>
     </row>
     <row r="173">
-      <c r="A173" s="37"/>
+      <c r="A173" s="38"/>
     </row>
     <row r="174">
-      <c r="A174" s="37"/>
+      <c r="A174" s="38"/>
     </row>
     <row r="175">
-      <c r="A175" s="37"/>
+      <c r="A175" s="38"/>
     </row>
     <row r="176">
-      <c r="A176" s="37"/>
+      <c r="A176" s="38"/>
     </row>
     <row r="177">
-      <c r="A177" s="37"/>
+      <c r="A177" s="38"/>
     </row>
     <row r="178">
-      <c r="A178" s="37"/>
+      <c r="A178" s="38"/>
     </row>
     <row r="179">
-      <c r="A179" s="37"/>
+      <c r="A179" s="38"/>
     </row>
     <row r="180">
-      <c r="A180" s="37"/>
+      <c r="A180" s="38"/>
     </row>
     <row r="181">
-      <c r="A181" s="37"/>
+      <c r="A181" s="38"/>
     </row>
     <row r="182">
-      <c r="A182" s="37"/>
+      <c r="A182" s="38"/>
     </row>
     <row r="183">
-      <c r="A183" s="37"/>
+      <c r="A183" s="38"/>
     </row>
     <row r="184">
-      <c r="A184" s="37"/>
+      <c r="A184" s="38"/>
     </row>
     <row r="185">
-      <c r="A185" s="37"/>
+      <c r="A185" s="38"/>
     </row>
     <row r="186">
-      <c r="A186" s="37"/>
+      <c r="A186" s="38"/>
     </row>
     <row r="187">
-      <c r="A187" s="37"/>
+      <c r="A187" s="38"/>
     </row>
     <row r="188">
-      <c r="A188" s="37"/>
+      <c r="A188" s="38"/>
     </row>
     <row r="189">
-      <c r="A189" s="37"/>
+      <c r="A189" s="38"/>
     </row>
     <row r="190">
-      <c r="A190" s="37"/>
+      <c r="A190" s="38"/>
     </row>
     <row r="191">
-      <c r="A191" s="37"/>
+      <c r="A191" s="38"/>
     </row>
     <row r="192">
-      <c r="A192" s="37"/>
+      <c r="A192" s="38"/>
     </row>
     <row r="193">
-      <c r="A193" s="37"/>
+      <c r="A193" s="38"/>
     </row>
     <row r="194">
-      <c r="A194" s="37"/>
+      <c r="A194" s="38"/>
     </row>
     <row r="195">
-      <c r="A195" s="37"/>
+      <c r="A195" s="38"/>
     </row>
     <row r="196">
-      <c r="A196" s="37"/>
+      <c r="A196" s="38"/>
     </row>
     <row r="197">
-      <c r="A197" s="37"/>
+      <c r="A197" s="38"/>
     </row>
     <row r="198">
-      <c r="A198" s="37"/>
+      <c r="A198" s="38"/>
     </row>
     <row r="199">
-      <c r="A199" s="37"/>
+      <c r="A199" s="38"/>
     </row>
     <row r="200">
-      <c r="A200" s="37"/>
+      <c r="A200" s="38"/>
     </row>
     <row r="201">
-      <c r="A201" s="37"/>
+      <c r="A201" s="38"/>
     </row>
     <row r="202">
-      <c r="A202" s="37"/>
+      <c r="A202" s="38"/>
     </row>
     <row r="203">
-      <c r="A203" s="37"/>
+      <c r="A203" s="38"/>
     </row>
     <row r="204">
-      <c r="A204" s="37"/>
+      <c r="A204" s="38"/>
     </row>
     <row r="205">
-      <c r="A205" s="37"/>
+      <c r="A205" s="38"/>
     </row>
     <row r="206">
-      <c r="A206" s="37"/>
+      <c r="A206" s="38"/>
     </row>
     <row r="207">
-      <c r="A207" s="37"/>
+      <c r="A207" s="38"/>
     </row>
     <row r="208">
-      <c r="A208" s="37"/>
+      <c r="A208" s="38"/>
     </row>
     <row r="209">
-      <c r="A209" s="37"/>
+      <c r="A209" s="38"/>
     </row>
     <row r="210">
-      <c r="A210" s="37"/>
+      <c r="A210" s="38"/>
     </row>
     <row r="211">
-      <c r="A211" s="37"/>
+      <c r="A211" s="38"/>
     </row>
     <row r="212">
-      <c r="A212" s="37"/>
+      <c r="A212" s="38"/>
     </row>
     <row r="213">
-      <c r="A213" s="37"/>
+      <c r="A213" s="38"/>
     </row>
     <row r="214">
-      <c r="A214" s="37"/>
+      <c r="A214" s="38"/>
     </row>
     <row r="215">
-      <c r="A215" s="37"/>
+      <c r="A215" s="38"/>
     </row>
     <row r="216">
-      <c r="A216" s="37"/>
+      <c r="A216" s="38"/>
     </row>
     <row r="217">
-      <c r="A217" s="37"/>
+      <c r="A217" s="38"/>
     </row>
     <row r="218">
-      <c r="A218" s="37"/>
+      <c r="A218" s="38"/>
     </row>
     <row r="219">
-      <c r="A219" s="37"/>
+      <c r="A219" s="38"/>
     </row>
     <row r="220">
-      <c r="A220" s="37"/>
+      <c r="A220" s="38"/>
     </row>
     <row r="221">
-      <c r="A221" s="37"/>
+      <c r="A221" s="38"/>
     </row>
     <row r="222">
-      <c r="A222" s="37"/>
+      <c r="A222" s="38"/>
     </row>
     <row r="223">
-      <c r="A223" s="37"/>
+      <c r="A223" s="38"/>
     </row>
     <row r="224">
-      <c r="A224" s="37"/>
+      <c r="A224" s="38"/>
     </row>
     <row r="225">
-      <c r="A225" s="37"/>
+      <c r="A225" s="38"/>
     </row>
     <row r="226">
-      <c r="A226" s="37"/>
+      <c r="A226" s="38"/>
     </row>
     <row r="227">
-      <c r="A227" s="37"/>
+      <c r="A227" s="38"/>
     </row>
     <row r="228">
-      <c r="A228" s="37"/>
+      <c r="A228" s="38"/>
     </row>
     <row r="229">
-      <c r="A229" s="37"/>
+      <c r="A229" s="38"/>
     </row>
     <row r="230">
-      <c r="A230" s="37"/>
+      <c r="A230" s="38"/>
     </row>
     <row r="231">
-      <c r="A231" s="37"/>
+      <c r="A231" s="38"/>
     </row>
     <row r="232">
-      <c r="A232" s="37"/>
+      <c r="A232" s="38"/>
     </row>
     <row r="233">
-      <c r="A233" s="37"/>
+      <c r="A233" s="38"/>
     </row>
     <row r="234">
-      <c r="A234" s="37"/>
+      <c r="A234" s="38"/>
     </row>
     <row r="235">
-      <c r="A235" s="37"/>
+      <c r="A235" s="38"/>
     </row>
     <row r="236">
-      <c r="A236" s="37"/>
+      <c r="A236" s="38"/>
     </row>
     <row r="237">
-      <c r="A237" s="37"/>
+      <c r="A237" s="38"/>
     </row>
     <row r="238">
-      <c r="A238" s="37"/>
+      <c r="A238" s="38"/>
     </row>
     <row r="239">
-      <c r="A239" s="37"/>
+      <c r="A239" s="38"/>
     </row>
     <row r="240">
-      <c r="A240" s="37"/>
+      <c r="A240" s="38"/>
     </row>
     <row r="241">
-      <c r="A241" s="37"/>
+      <c r="A241" s="38"/>
     </row>
     <row r="242">
-      <c r="A242" s="37"/>
+      <c r="A242" s="38"/>
     </row>
     <row r="243">
-      <c r="A243" s="37"/>
+      <c r="A243" s="38"/>
     </row>
     <row r="244">
-      <c r="A244" s="37"/>
+      <c r="A244" s="38"/>
     </row>
     <row r="245">
-      <c r="A245" s="37"/>
+      <c r="A245" s="38"/>
     </row>
     <row r="246">
-      <c r="A246" s="37"/>
+      <c r="A246" s="38"/>
     </row>
     <row r="247">
-      <c r="A247" s="37"/>
+      <c r="A247" s="38"/>
     </row>
     <row r="248">
-      <c r="A248" s="37"/>
+      <c r="A248" s="38"/>
     </row>
     <row r="249">
-      <c r="A249" s="37"/>
+      <c r="A249" s="38"/>
     </row>
     <row r="250">
-      <c r="A250" s="37"/>
+      <c r="A250" s="38"/>
     </row>
     <row r="251">
-      <c r="A251" s="37"/>
+      <c r="A251" s="38"/>
     </row>
     <row r="252">
-      <c r="A252" s="37"/>
+      <c r="A252" s="38"/>
     </row>
     <row r="253">
-      <c r="A253" s="37"/>
+      <c r="A253" s="38"/>
     </row>
     <row r="254">
-      <c r="A254" s="37"/>
+      <c r="A254" s="38"/>
     </row>
     <row r="255">
-      <c r="A255" s="37"/>
+      <c r="A255" s="38"/>
     </row>
     <row r="256">
-      <c r="A256" s="37"/>
+      <c r="A256" s="38"/>
     </row>
     <row r="257">
-      <c r="A257" s="37"/>
+      <c r="A257" s="38"/>
     </row>
     <row r="258">
-      <c r="A258" s="37"/>
+      <c r="A258" s="38"/>
     </row>
     <row r="259">
-      <c r="A259" s="37"/>
+      <c r="A259" s="38"/>
     </row>
     <row r="260">
-      <c r="A260" s="37"/>
+      <c r="A260" s="38"/>
     </row>
     <row r="261">
-      <c r="A261" s="37"/>
+      <c r="A261" s="38"/>
     </row>
     <row r="262">
-      <c r="A262" s="37"/>
+      <c r="A262" s="38"/>
     </row>
     <row r="263">
-      <c r="A263" s="37"/>
+      <c r="A263" s="38"/>
     </row>
     <row r="264">
-      <c r="A264" s="37"/>
+      <c r="A264" s="38"/>
     </row>
     <row r="265">
-      <c r="A265" s="37"/>
+      <c r="A265" s="38"/>
     </row>
     <row r="266">
-      <c r="A266" s="37"/>
+      <c r="A266" s="38"/>
     </row>
     <row r="267">
-      <c r="A267" s="37"/>
+      <c r="A267" s="38"/>
     </row>
     <row r="268">
-      <c r="A268" s="37"/>
+      <c r="A268" s="38"/>
     </row>
     <row r="269">
-      <c r="A269" s="37"/>
+      <c r="A269" s="38"/>
     </row>
     <row r="270">
-      <c r="A270" s="37"/>
+      <c r="A270" s="38"/>
     </row>
     <row r="271">
-      <c r="A271" s="37"/>
+      <c r="A271" s="38"/>
     </row>
     <row r="272">
-      <c r="A272" s="37"/>
+      <c r="A272" s="38"/>
     </row>
     <row r="273">
-      <c r="A273" s="37"/>
+      <c r="A273" s="38"/>
     </row>
     <row r="274">
-      <c r="A274" s="37"/>
+      <c r="A274" s="38"/>
     </row>
     <row r="275">
-      <c r="A275" s="37"/>
+      <c r="A275" s="38"/>
     </row>
     <row r="276">
-      <c r="A276" s="37"/>
+      <c r="A276" s="38"/>
     </row>
     <row r="277">
-      <c r="A277" s="37"/>
+      <c r="A277" s="38"/>
     </row>
     <row r="278">
-      <c r="A278" s="37"/>
+      <c r="A278" s="38"/>
     </row>
     <row r="279">
-      <c r="A279" s="37"/>
+      <c r="A279" s="38"/>
     </row>
     <row r="280">
-      <c r="A280" s="37"/>
+      <c r="A280" s="38"/>
     </row>
     <row r="281">
-      <c r="A281" s="37"/>
+      <c r="A281" s="38"/>
     </row>
     <row r="282">
-      <c r="A282" s="37"/>
+      <c r="A282" s="38"/>
     </row>
     <row r="283">
-      <c r="A283" s="37"/>
+      <c r="A283" s="38"/>
     </row>
     <row r="284">
-      <c r="A284" s="37"/>
+      <c r="A284" s="38"/>
     </row>
     <row r="285">
-      <c r="A285" s="37"/>
+      <c r="A285" s="38"/>
     </row>
     <row r="286">
-      <c r="A286" s="37"/>
+      <c r="A286" s="38"/>
     </row>
     <row r="287">
-      <c r="A287" s="37"/>
+      <c r="A287" s="38"/>
     </row>
     <row r="288">
-      <c r="A288" s="37"/>
+      <c r="A288" s="38"/>
     </row>
     <row r="289">
-      <c r="A289" s="37"/>
+      <c r="A289" s="38"/>
     </row>
     <row r="290">
-      <c r="A290" s="37"/>
+      <c r="A290" s="38"/>
     </row>
     <row r="291">
-      <c r="A291" s="37"/>
+      <c r="A291" s="38"/>
     </row>
     <row r="292">
-      <c r="A292" s="37"/>
+      <c r="A292" s="38"/>
     </row>
     <row r="293">
-      <c r="A293" s="37"/>
+      <c r="A293" s="38"/>
     </row>
     <row r="294">
-      <c r="A294" s="37"/>
+      <c r="A294" s="38"/>
     </row>
     <row r="295">
-      <c r="A295" s="37"/>
+      <c r="A295" s="38"/>
     </row>
     <row r="296">
-      <c r="A296" s="37"/>
+      <c r="A296" s="38"/>
     </row>
     <row r="297">
-      <c r="A297" s="37"/>
+      <c r="A297" s="38"/>
     </row>
     <row r="298">
-      <c r="A298" s="37"/>
+      <c r="A298" s="38"/>
     </row>
     <row r="299">
-      <c r="A299" s="37"/>
+      <c r="A299" s="38"/>
     </row>
     <row r="300">
-      <c r="A300" s="37"/>
+      <c r="A300" s="38"/>
     </row>
     <row r="301">
-      <c r="A301" s="37"/>
+      <c r="A301" s="38"/>
     </row>
     <row r="302">
-      <c r="A302" s="37"/>
+      <c r="A302" s="38"/>
     </row>
     <row r="303">
-      <c r="A303" s="37"/>
+      <c r="A303" s="38"/>
     </row>
     <row r="304">
-      <c r="A304" s="37"/>
+      <c r="A304" s="38"/>
     </row>
     <row r="305">
-      <c r="A305" s="37"/>
+      <c r="A305" s="38"/>
     </row>
     <row r="306">
-      <c r="A306" s="37"/>
+      <c r="A306" s="38"/>
     </row>
     <row r="307">
-      <c r="A307" s="37"/>
+      <c r="A307" s="38"/>
     </row>
     <row r="308">
-      <c r="A308" s="37"/>
+      <c r="A308" s="38"/>
     </row>
     <row r="309">
-      <c r="A309" s="37"/>
+      <c r="A309" s="38"/>
     </row>
     <row r="310">
-      <c r="A310" s="37"/>
+      <c r="A310" s="38"/>
     </row>
     <row r="311">
-      <c r="A311" s="37"/>
+      <c r="A311" s="38"/>
     </row>
     <row r="312">
-      <c r="A312" s="37"/>
+      <c r="A312" s="38"/>
     </row>
     <row r="313">
-      <c r="A313" s="37"/>
+      <c r="A313" s="38"/>
     </row>
     <row r="314">
-      <c r="A314" s="37"/>
+      <c r="A314" s="38"/>
     </row>
     <row r="315">
-      <c r="A315" s="37"/>
+      <c r="A315" s="38"/>
     </row>
     <row r="316">
-      <c r="A316" s="37"/>
+      <c r="A316" s="38"/>
     </row>
     <row r="317">
-      <c r="A317" s="37"/>
+      <c r="A317" s="38"/>
     </row>
     <row r="318">
-      <c r="A318" s="37"/>
+      <c r="A318" s="38"/>
     </row>
     <row r="319">
-      <c r="A319" s="37"/>
+      <c r="A319" s="38"/>
     </row>
     <row r="320">
-      <c r="A320" s="37"/>
+      <c r="A320" s="38"/>
     </row>
     <row r="321">
-      <c r="A321" s="37"/>
+      <c r="A321" s="38"/>
     </row>
     <row r="322">
-      <c r="A322" s="37"/>
+      <c r="A322" s="38"/>
     </row>
     <row r="323">
-      <c r="A323" s="37"/>
+      <c r="A323" s="38"/>
     </row>
     <row r="324">
-      <c r="A324" s="37"/>
+      <c r="A324" s="38"/>
     </row>
     <row r="325">
-      <c r="A325" s="37"/>
+      <c r="A325" s="38"/>
     </row>
     <row r="326">
-      <c r="A326" s="37"/>
+      <c r="A326" s="38"/>
     </row>
     <row r="327">
-      <c r="A327" s="37"/>
+      <c r="A327" s="38"/>
     </row>
     <row r="328">
-      <c r="A328" s="37"/>
+      <c r="A328" s="38"/>
     </row>
     <row r="329">
-      <c r="A329" s="37"/>
+      <c r="A329" s="38"/>
     </row>
     <row r="330">
-      <c r="A330" s="37"/>
+      <c r="A330" s="38"/>
     </row>
     <row r="331">
-      <c r="A331" s="37"/>
+      <c r="A331" s="38"/>
     </row>
     <row r="332">
-      <c r="A332" s="37"/>
+      <c r="A332" s="38"/>
     </row>
     <row r="333">
-      <c r="A333" s="37"/>
+      <c r="A333" s="38"/>
     </row>
     <row r="334">
-      <c r="A334" s="37"/>
+      <c r="A334" s="38"/>
     </row>
     <row r="335">
-      <c r="A335" s="37"/>
+      <c r="A335" s="38"/>
     </row>
     <row r="336">
-      <c r="A336" s="37"/>
+      <c r="A336" s="38"/>
     </row>
     <row r="337">
-      <c r="A337" s="37"/>
+      <c r="A337" s="38"/>
     </row>
     <row r="338">
-      <c r="A338" s="37"/>
+      <c r="A338" s="38"/>
     </row>
     <row r="339">
-      <c r="A339" s="37"/>
+      <c r="A339" s="38"/>
     </row>
     <row r="340">
-      <c r="A340" s="37"/>
+      <c r="A340" s="38"/>
     </row>
     <row r="341">
-      <c r="A341" s="37"/>
+      <c r="A341" s="38"/>
     </row>
     <row r="342">
-      <c r="A342" s="37"/>
+      <c r="A342" s="38"/>
     </row>
     <row r="343">
-      <c r="A343" s="37"/>
+      <c r="A343" s="38"/>
     </row>
     <row r="344">
-      <c r="A344" s="37"/>
+      <c r="A344" s="38"/>
     </row>
     <row r="345">
-      <c r="A345" s="37"/>
+      <c r="A345" s="38"/>
     </row>
     <row r="346">
-      <c r="A346" s="37"/>
+      <c r="A346" s="38"/>
     </row>
     <row r="347">
-      <c r="A347" s="37"/>
+      <c r="A347" s="38"/>
     </row>
     <row r="348">
-      <c r="A348" s="37"/>
+      <c r="A348" s="38"/>
     </row>
     <row r="349">
-      <c r="A349" s="37"/>
+      <c r="A349" s="38"/>
     </row>
     <row r="350">
-      <c r="A350" s="37"/>
+      <c r="A350" s="38"/>
     </row>
     <row r="351">
-      <c r="A351" s="37"/>
+      <c r="A351" s="38"/>
     </row>
     <row r="352">
-      <c r="A352" s="37"/>
+      <c r="A352" s="38"/>
     </row>
     <row r="353">
-      <c r="A353" s="37"/>
+      <c r="A353" s="38"/>
     </row>
     <row r="354">
-      <c r="A354" s="37"/>
+      <c r="A354" s="38"/>
     </row>
     <row r="355">
-      <c r="A355" s="37"/>
+      <c r="A355" s="38"/>
     </row>
     <row r="356">
-      <c r="A356" s="37"/>
+      <c r="A356" s="38"/>
     </row>
     <row r="357">
-      <c r="A357" s="37"/>
+      <c r="A357" s="38"/>
     </row>
     <row r="358">
-      <c r="A358" s="37"/>
+      <c r="A358" s="38"/>
     </row>
     <row r="359">
-      <c r="A359" s="37"/>
+      <c r="A359" s="38"/>
     </row>
     <row r="360">
-      <c r="A360" s="37"/>
+      <c r="A360" s="38"/>
     </row>
     <row r="361">
-      <c r="A361" s="37"/>
+      <c r="A361" s="38"/>
     </row>
     <row r="362">
-      <c r="A362" s="37"/>
+      <c r="A362" s="38"/>
     </row>
     <row r="363">
-      <c r="A363" s="37"/>
+      <c r="A363" s="38"/>
     </row>
     <row r="364">
-      <c r="A364" s="37"/>
+      <c r="A364" s="38"/>
     </row>
     <row r="365">
-      <c r="A365" s="37"/>
+      <c r="A365" s="38"/>
     </row>
     <row r="366">
-      <c r="A366" s="37"/>
+      <c r="A366" s="38"/>
     </row>
     <row r="367">
-      <c r="A367" s="37"/>
+      <c r="A367" s="38"/>
     </row>
     <row r="368">
-      <c r="A368" s="37"/>
+      <c r="A368" s="38"/>
     </row>
     <row r="369">
-      <c r="A369" s="37"/>
+      <c r="A369" s="38"/>
     </row>
     <row r="370">
-      <c r="A370" s="37"/>
+      <c r="A370" s="38"/>
     </row>
     <row r="371">
-      <c r="A371" s="37"/>
+      <c r="A371" s="38"/>
     </row>
     <row r="372">
-      <c r="A372" s="37"/>
+      <c r="A372" s="38"/>
     </row>
     <row r="373">
-      <c r="A373" s="37"/>
+      <c r="A373" s="38"/>
     </row>
     <row r="374">
-      <c r="A374" s="37"/>
+      <c r="A374" s="38"/>
     </row>
     <row r="375">
-      <c r="A375" s="37"/>
+      <c r="A375" s="38"/>
     </row>
     <row r="376">
-      <c r="A376" s="37"/>
+      <c r="A376" s="38"/>
     </row>
     <row r="377">
-      <c r="A377" s="37"/>
+      <c r="A377" s="38"/>
     </row>
     <row r="378">
-      <c r="A378" s="37"/>
+      <c r="A378" s="38"/>
     </row>
     <row r="379">
-      <c r="A379" s="37"/>
+      <c r="A379" s="38"/>
     </row>
     <row r="380">
-      <c r="A380" s="37"/>
+      <c r="A380" s="38"/>
     </row>
     <row r="381">
-      <c r="A381" s="37"/>
+      <c r="A381" s="38"/>
     </row>
     <row r="382">
-      <c r="A382" s="37"/>
+      <c r="A382" s="38"/>
     </row>
     <row r="383">
-      <c r="A383" s="37"/>
+      <c r="A383" s="38"/>
     </row>
     <row r="384">
-      <c r="A384" s="37"/>
+      <c r="A384" s="38"/>
     </row>
     <row r="385">
-      <c r="A385" s="37"/>
+      <c r="A385" s="38"/>
     </row>
     <row r="386">
-      <c r="A386" s="37"/>
+      <c r="A386" s="38"/>
     </row>
     <row r="387">
-      <c r="A387" s="37"/>
+      <c r="A387" s="38"/>
     </row>
     <row r="388">
-      <c r="A388" s="37"/>
+      <c r="A388" s="38"/>
     </row>
     <row r="389">
-      <c r="A389" s="37"/>
+      <c r="A389" s="38"/>
     </row>
     <row r="390">
-      <c r="A390" s="37"/>
+      <c r="A390" s="38"/>
     </row>
     <row r="391">
-      <c r="A391" s="37"/>
+      <c r="A391" s="38"/>
     </row>
     <row r="392">
-      <c r="A392" s="37"/>
+      <c r="A392" s="38"/>
     </row>
     <row r="393">
-      <c r="A393" s="37"/>
+      <c r="A393" s="38"/>
     </row>
     <row r="394">
-      <c r="A394" s="37"/>
+      <c r="A394" s="38"/>
     </row>
     <row r="395">
-      <c r="A395" s="37"/>
+      <c r="A395" s="38"/>
     </row>
     <row r="396">
-      <c r="A396" s="37"/>
+      <c r="A396" s="38"/>
     </row>
     <row r="397">
-      <c r="A397" s="37"/>
+      <c r="A397" s="38"/>
     </row>
     <row r="398">
-      <c r="A398" s="37"/>
+      <c r="A398" s="38"/>
     </row>
     <row r="399">
-      <c r="A399" s="37"/>
+      <c r="A399" s="38"/>
     </row>
     <row r="400">
-      <c r="A400" s="37"/>
+      <c r="A400" s="38"/>
     </row>
     <row r="401">
-      <c r="A401" s="37"/>
+      <c r="A401" s="38"/>
     </row>
     <row r="402">
-      <c r="A402" s="37"/>
+      <c r="A402" s="38"/>
     </row>
     <row r="403">
-      <c r="A403" s="37"/>
+      <c r="A403" s="38"/>
     </row>
     <row r="404">
-      <c r="A404" s="37"/>
+      <c r="A404" s="38"/>
     </row>
     <row r="405">
-      <c r="A405" s="37"/>
+      <c r="A405" s="38"/>
     </row>
     <row r="406">
-      <c r="A406" s="37"/>
+      <c r="A406" s="38"/>
     </row>
     <row r="407">
-      <c r="A407" s="37"/>
+      <c r="A407" s="38"/>
     </row>
     <row r="408">
-      <c r="A408" s="37"/>
+      <c r="A408" s="38"/>
     </row>
     <row r="409">
-      <c r="A409" s="37"/>
+      <c r="A409" s="38"/>
     </row>
     <row r="410">
-      <c r="A410" s="37"/>
+      <c r="A410" s="38"/>
     </row>
     <row r="411">
-      <c r="A411" s="37"/>
+      <c r="A411" s="38"/>
     </row>
     <row r="412">
-      <c r="A412" s="37"/>
+      <c r="A412" s="38"/>
     </row>
     <row r="413">
-      <c r="A413" s="37"/>
+      <c r="A413" s="38"/>
     </row>
     <row r="414">
-      <c r="A414" s="37"/>
+      <c r="A414" s="38"/>
     </row>
     <row r="415">
-      <c r="A415" s="37"/>
+      <c r="A415" s="38"/>
     </row>
     <row r="416">
-      <c r="A416" s="37"/>
+      <c r="A416" s="38"/>
     </row>
     <row r="417">
-      <c r="A417" s="37"/>
+      <c r="A417" s="38"/>
     </row>
     <row r="418">
-      <c r="A418" s="37"/>
+      <c r="A418" s="38"/>
     </row>
     <row r="419">
-      <c r="A419" s="37"/>
+      <c r="A419" s="38"/>
     </row>
     <row r="420">
-      <c r="A420" s="37"/>
+      <c r="A420" s="38"/>
     </row>
     <row r="421">
-      <c r="A421" s="37"/>
+      <c r="A421" s="38"/>
     </row>
     <row r="422">
-      <c r="A422" s="37"/>
+      <c r="A422" s="38"/>
     </row>
     <row r="423">
-      <c r="A423" s="37"/>
+      <c r="A423" s="38"/>
     </row>
     <row r="424">
-      <c r="A424" s="37"/>
+      <c r="A424" s="38"/>
     </row>
     <row r="425">
-      <c r="A425" s="37"/>
+      <c r="A425" s="38"/>
     </row>
     <row r="426">
-      <c r="A426" s="37"/>
+      <c r="A426" s="38"/>
     </row>
     <row r="427">
-      <c r="A427" s="37"/>
+      <c r="A427" s="38"/>
     </row>
     <row r="428">
-      <c r="A428" s="37"/>
+      <c r="A428" s="38"/>
     </row>
     <row r="429">
-      <c r="A429" s="37"/>
+      <c r="A429" s="38"/>
     </row>
     <row r="430">
-      <c r="A430" s="37"/>
+      <c r="A430" s="38"/>
     </row>
     <row r="431">
-      <c r="A431" s="37"/>
+      <c r="A431" s="38"/>
     </row>
     <row r="432">
-      <c r="A432" s="37"/>
+      <c r="A432" s="38"/>
     </row>
     <row r="433">
-      <c r="A433" s="37"/>
+      <c r="A433" s="38"/>
     </row>
     <row r="434">
-      <c r="A434" s="37"/>
+      <c r="A434" s="38"/>
     </row>
     <row r="435">
-      <c r="A435" s="37"/>
+      <c r="A435" s="38"/>
     </row>
     <row r="436">
-      <c r="A436" s="37"/>
+      <c r="A436" s="38"/>
     </row>
     <row r="437">
-      <c r="A437" s="37"/>
+      <c r="A437" s="38"/>
     </row>
     <row r="438">
-      <c r="A438" s="37"/>
+      <c r="A438" s="38"/>
     </row>
     <row r="439">
-      <c r="A439" s="37"/>
+      <c r="A439" s="38"/>
     </row>
     <row r="440">
-      <c r="A440" s="37"/>
+      <c r="A440" s="38"/>
     </row>
     <row r="441">
-      <c r="A441" s="37"/>
+      <c r="A441" s="38"/>
     </row>
     <row r="442">
-      <c r="A442" s="37"/>
+      <c r="A442" s="38"/>
     </row>
     <row r="443">
-      <c r="A443" s="37"/>
+      <c r="A443" s="38"/>
     </row>
     <row r="444">
-      <c r="A444" s="37"/>
+      <c r="A444" s="38"/>
     </row>
     <row r="445">
-      <c r="A445" s="37"/>
+      <c r="A445" s="38"/>
     </row>
     <row r="446">
-      <c r="A446" s="37"/>
+      <c r="A446" s="38"/>
     </row>
     <row r="447">
-      <c r="A447" s="37"/>
+      <c r="A447" s="38"/>
     </row>
     <row r="448">
-      <c r="A448" s="37"/>
+      <c r="A448" s="38"/>
     </row>
     <row r="449">
-      <c r="A449" s="37"/>
+      <c r="A449" s="38"/>
     </row>
     <row r="450">
-      <c r="A450" s="37"/>
+      <c r="A450" s="38"/>
     </row>
     <row r="451">
-      <c r="A451" s="37"/>
+      <c r="A451" s="38"/>
     </row>
     <row r="452">
-      <c r="A452" s="37"/>
+      <c r="A452" s="38"/>
     </row>
     <row r="453">
-      <c r="A453" s="37"/>
+      <c r="A453" s="38"/>
     </row>
     <row r="454">
-      <c r="A454" s="37"/>
+      <c r="A454" s="38"/>
     </row>
     <row r="455">
-      <c r="A455" s="37"/>
+      <c r="A455" s="38"/>
     </row>
     <row r="456">
-      <c r="A456" s="37"/>
+      <c r="A456" s="38"/>
     </row>
     <row r="457">
-      <c r="A457" s="37"/>
+      <c r="A457" s="38"/>
     </row>
     <row r="458">
-      <c r="A458" s="37"/>
+      <c r="A458" s="38"/>
     </row>
     <row r="459">
-      <c r="A459" s="37"/>
+      <c r="A459" s="38"/>
     </row>
     <row r="460">
-      <c r="A460" s="37"/>
+      <c r="A460" s="38"/>
     </row>
     <row r="461">
-      <c r="A461" s="37"/>
+      <c r="A461" s="38"/>
     </row>
     <row r="462">
-      <c r="A462" s="37"/>
+      <c r="A462" s="38"/>
     </row>
     <row r="463">
-      <c r="A463" s="37"/>
+      <c r="A463" s="38"/>
     </row>
     <row r="464">
-      <c r="A464" s="37"/>
+      <c r="A464" s="38"/>
     </row>
     <row r="465">
-      <c r="A465" s="37"/>
+      <c r="A465" s="38"/>
     </row>
     <row r="466">
-      <c r="A466" s="37"/>
+      <c r="A466" s="38"/>
     </row>
     <row r="467">
-      <c r="A467" s="37"/>
+      <c r="A467" s="38"/>
     </row>
     <row r="468">
-      <c r="A468" s="37"/>
+      <c r="A468" s="38"/>
     </row>
     <row r="469">
-      <c r="A469" s="37"/>
+      <c r="A469" s="38"/>
     </row>
     <row r="470">
-      <c r="A470" s="37"/>
+      <c r="A470" s="38"/>
     </row>
     <row r="471">
-      <c r="A471" s="37"/>
+      <c r="A471" s="38"/>
     </row>
     <row r="472">
-      <c r="A472" s="37"/>
+      <c r="A472" s="38"/>
     </row>
     <row r="473">
-      <c r="A473" s="37"/>
+      <c r="A473" s="38"/>
     </row>
     <row r="474">
-      <c r="A474" s="37"/>
+      <c r="A474" s="38"/>
     </row>
     <row r="475">
-      <c r="A475" s="37"/>
+      <c r="A475" s="38"/>
     </row>
     <row r="476">
-      <c r="A476" s="37"/>
+      <c r="A476" s="38"/>
     </row>
     <row r="477">
-      <c r="A477" s="37"/>
+      <c r="A477" s="38"/>
     </row>
     <row r="478">
-      <c r="A478" s="37"/>
+      <c r="A478" s="38"/>
     </row>
     <row r="479">
-      <c r="A479" s="37"/>
+      <c r="A479" s="38"/>
     </row>
     <row r="480">
-      <c r="A480" s="37"/>
+      <c r="A480" s="38"/>
     </row>
     <row r="481">
-      <c r="A481" s="37"/>
+      <c r="A481" s="38"/>
     </row>
     <row r="482">
-      <c r="A482" s="37"/>
+      <c r="A482" s="38"/>
     </row>
     <row r="483">
-      <c r="A483" s="37"/>
+      <c r="A483" s="38"/>
     </row>
     <row r="484">
-      <c r="A484" s="37"/>
+      <c r="A484" s="38"/>
     </row>
     <row r="485">
-      <c r="A485" s="37"/>
+      <c r="A485" s="38"/>
     </row>
     <row r="486">
-      <c r="A486" s="37"/>
+      <c r="A486" s="38"/>
     </row>
     <row r="487">
-      <c r="A487" s="37"/>
+      <c r="A487" s="38"/>
     </row>
     <row r="488">
-      <c r="A488" s="37"/>
+      <c r="A488" s="38"/>
     </row>
     <row r="489">
-      <c r="A489" s="37"/>
+      <c r="A489" s="38"/>
     </row>
     <row r="490">
-      <c r="A490" s="37"/>
+      <c r="A490" s="38"/>
     </row>
     <row r="491">
-      <c r="A491" s="37"/>
+      <c r="A491" s="38"/>
     </row>
     <row r="492">
-      <c r="A492" s="37"/>
+      <c r="A492" s="38"/>
     </row>
     <row r="493">
-      <c r="A493" s="37"/>
+      <c r="A493" s="38"/>
     </row>
     <row r="494">
-      <c r="A494" s="37"/>
+      <c r="A494" s="38"/>
     </row>
     <row r="495">
-      <c r="A495" s="37"/>
+      <c r="A495" s="38"/>
     </row>
     <row r="496">
-      <c r="A496" s="37"/>
+      <c r="A496" s="38"/>
     </row>
     <row r="497">
-      <c r="A497" s="37"/>
+      <c r="A497" s="38"/>
     </row>
     <row r="498">
-      <c r="A498" s="37"/>
+      <c r="A498" s="38"/>
     </row>
     <row r="499">
-      <c r="A499" s="37"/>
+      <c r="A499" s="38"/>
     </row>
     <row r="500">
-      <c r="A500" s="37"/>
+      <c r="A500" s="38"/>
     </row>
     <row r="501">
-      <c r="A501" s="37"/>
+      <c r="A501" s="38"/>
     </row>
     <row r="502">
-      <c r="A502" s="37"/>
+      <c r="A502" s="38"/>
     </row>
     <row r="503">
-      <c r="A503" s="37"/>
+      <c r="A503" s="38"/>
     </row>
     <row r="504">
-      <c r="A504" s="37"/>
+      <c r="A504" s="38"/>
     </row>
     <row r="505">
-      <c r="A505" s="37"/>
+      <c r="A505" s="38"/>
     </row>
     <row r="506">
-      <c r="A506" s="37"/>
+      <c r="A506" s="38"/>
     </row>
     <row r="507">
-      <c r="A507" s="37"/>
+      <c r="A507" s="38"/>
     </row>
     <row r="508">
-      <c r="A508" s="37"/>
+      <c r="A508" s="38"/>
     </row>
     <row r="509">
-      <c r="A509" s="37"/>
+      <c r="A509" s="38"/>
     </row>
     <row r="510">
-      <c r="A510" s="37"/>
+      <c r="A510" s="38"/>
     </row>
     <row r="511">
-      <c r="A511" s="37"/>
+      <c r="A511" s="38"/>
     </row>
     <row r="512">
-      <c r="A512" s="37"/>
+      <c r="A512" s="38"/>
     </row>
     <row r="513">
-      <c r="A513" s="37"/>
+      <c r="A513" s="38"/>
     </row>
     <row r="514">
-      <c r="A514" s="37"/>
+      <c r="A514" s="38"/>
     </row>
     <row r="515">
-      <c r="A515" s="37"/>
+      <c r="A515" s="38"/>
     </row>
     <row r="516">
-      <c r="A516" s="37"/>
+      <c r="A516" s="38"/>
     </row>
     <row r="517">
-      <c r="A517" s="37"/>
+      <c r="A517" s="38"/>
     </row>
     <row r="518">
-      <c r="A518" s="37"/>
+      <c r="A518" s="38"/>
     </row>
     <row r="519">
-      <c r="A519" s="37"/>
+      <c r="A519" s="38"/>
     </row>
     <row r="520">
-      <c r="A520" s="37"/>
+      <c r="A520" s="38"/>
     </row>
     <row r="521">
-      <c r="A521" s="37"/>
+      <c r="A521" s="38"/>
     </row>
     <row r="522">
-      <c r="A522" s="37"/>
+      <c r="A522" s="38"/>
     </row>
     <row r="523">
-      <c r="A523" s="37"/>
+      <c r="A523" s="38"/>
     </row>
     <row r="524">
-      <c r="A524" s="37"/>
+      <c r="A524" s="38"/>
     </row>
     <row r="525">
-      <c r="A525" s="37"/>
+      <c r="A525" s="38"/>
     </row>
     <row r="526">
-      <c r="A526" s="37"/>
+      <c r="A526" s="38"/>
     </row>
     <row r="527">
-      <c r="A527" s="37"/>
+      <c r="A527" s="38"/>
     </row>
     <row r="528">
-      <c r="A528" s="37"/>
+      <c r="A528" s="38"/>
     </row>
     <row r="529">
-      <c r="A529" s="37"/>
+      <c r="A529" s="38"/>
     </row>
     <row r="530">
-      <c r="A530" s="37"/>
+      <c r="A530" s="38"/>
     </row>
     <row r="531">
-      <c r="A531" s="37"/>
+      <c r="A531" s="38"/>
     </row>
     <row r="532">
-      <c r="A532" s="37"/>
+      <c r="A532" s="38"/>
     </row>
     <row r="533">
-      <c r="A533" s="37"/>
+      <c r="A533" s="38"/>
     </row>
     <row r="534">
-      <c r="A534" s="37"/>
+      <c r="A534" s="38"/>
     </row>
     <row r="535">
-      <c r="A535" s="37"/>
+      <c r="A535" s="38"/>
     </row>
     <row r="536">
-      <c r="A536" s="37"/>
+      <c r="A536" s="38"/>
     </row>
     <row r="537">
-      <c r="A537" s="37"/>
+      <c r="A537" s="38"/>
     </row>
     <row r="538">
-      <c r="A538" s="37"/>
+      <c r="A538" s="38"/>
     </row>
     <row r="539">
-      <c r="A539" s="37"/>
+      <c r="A539" s="38"/>
     </row>
     <row r="540">
-      <c r="A540" s="37"/>
+      <c r="A540" s="38"/>
     </row>
     <row r="541">
-      <c r="A541" s="37"/>
+      <c r="A541" s="38"/>
     </row>
     <row r="542">
-      <c r="A542" s="37"/>
+      <c r="A542" s="38"/>
     </row>
     <row r="543">
-      <c r="A543" s="37"/>
+      <c r="A543" s="38"/>
     </row>
     <row r="544">
-      <c r="A544" s="37"/>
+      <c r="A544" s="38"/>
     </row>
     <row r="545">
-      <c r="A545" s="37"/>
+      <c r="A545" s="38"/>
     </row>
     <row r="546">
-      <c r="A546" s="37"/>
+      <c r="A546" s="38"/>
     </row>
     <row r="547">
-      <c r="A547" s="37"/>
+      <c r="A547" s="38"/>
     </row>
     <row r="548">
-      <c r="A548" s="37"/>
+      <c r="A548" s="38"/>
     </row>
     <row r="549">
-      <c r="A549" s="37"/>
+      <c r="A549" s="38"/>
     </row>
     <row r="550">
-      <c r="A550" s="37"/>
+      <c r="A550" s="38"/>
     </row>
     <row r="551">
-      <c r="A551" s="37"/>
+      <c r="A551" s="38"/>
     </row>
     <row r="552">
-      <c r="A552" s="37"/>
+      <c r="A552" s="38"/>
     </row>
     <row r="553">
-      <c r="A553" s="37"/>
+      <c r="A553" s="38"/>
     </row>
     <row r="554">
-      <c r="A554" s="37"/>
+      <c r="A554" s="38"/>
     </row>
     <row r="555">
-      <c r="A555" s="37"/>
+      <c r="A555" s="38"/>
     </row>
     <row r="556">
-      <c r="A556" s="37"/>
+      <c r="A556" s="38"/>
     </row>
     <row r="557">
-      <c r="A557" s="37"/>
+      <c r="A557" s="38"/>
     </row>
     <row r="558">
-      <c r="A558" s="37"/>
+      <c r="A558" s="38"/>
     </row>
     <row r="559">
-      <c r="A559" s="37"/>
+      <c r="A559" s="38"/>
     </row>
     <row r="560">
-      <c r="A560" s="37"/>
+      <c r="A560" s="38"/>
     </row>
     <row r="561">
-      <c r="A561" s="37"/>
+      <c r="A561" s="38"/>
     </row>
     <row r="562">
-      <c r="A562" s="37"/>
+      <c r="A562" s="38"/>
     </row>
     <row r="563">
-      <c r="A563" s="37"/>
+      <c r="A563" s="38"/>
     </row>
     <row r="564">
-      <c r="A564" s="37"/>
+      <c r="A564" s="38"/>
     </row>
     <row r="565">
-      <c r="A565" s="37"/>
+      <c r="A565" s="38"/>
     </row>
     <row r="566">
-      <c r="A566" s="37"/>
+      <c r="A566" s="38"/>
     </row>
     <row r="567">
-      <c r="A567" s="37"/>
+      <c r="A567" s="38"/>
     </row>
     <row r="568">
-      <c r="A568" s="37"/>
+      <c r="A568" s="38"/>
     </row>
     <row r="569">
-      <c r="A569" s="37"/>
+      <c r="A569" s="38"/>
     </row>
     <row r="570">
-      <c r="A570" s="37"/>
+      <c r="A570" s="38"/>
     </row>
     <row r="571">
-      <c r="A571" s="37"/>
+      <c r="A571" s="38"/>
     </row>
     <row r="572">
-      <c r="A572" s="37"/>
+      <c r="A572" s="38"/>
     </row>
     <row r="573">
-      <c r="A573" s="37"/>
+      <c r="A573" s="38"/>
     </row>
     <row r="574">
-      <c r="A574" s="37"/>
+      <c r="A574" s="38"/>
     </row>
     <row r="575">
-      <c r="A575" s="37"/>
+      <c r="A575" s="38"/>
     </row>
     <row r="576">
-      <c r="A576" s="37"/>
+      <c r="A576" s="38"/>
     </row>
     <row r="577">
-      <c r="A577" s="37"/>
+      <c r="A577" s="38"/>
     </row>
     <row r="578">
-      <c r="A578" s="37"/>
+      <c r="A578" s="38"/>
     </row>
     <row r="579">
-      <c r="A579" s="37"/>
+      <c r="A579" s="38"/>
     </row>
     <row r="580">
-      <c r="A580" s="37"/>
+      <c r="A580" s="38"/>
     </row>
     <row r="581">
-      <c r="A581" s="37"/>
+      <c r="A581" s="38"/>
     </row>
     <row r="582">
-      <c r="A582" s="37"/>
+      <c r="A582" s="38"/>
     </row>
     <row r="583">
-      <c r="A583" s="37"/>
+      <c r="A583" s="38"/>
     </row>
     <row r="584">
-      <c r="A584" s="37"/>
+      <c r="A584" s="38"/>
     </row>
     <row r="585">
-      <c r="A585" s="37"/>
+      <c r="A585" s="38"/>
     </row>
     <row r="586">
-      <c r="A586" s="37"/>
+      <c r="A586" s="38"/>
     </row>
     <row r="587">
-      <c r="A587" s="37"/>
+      <c r="A587" s="38"/>
     </row>
     <row r="588">
-      <c r="A588" s="37"/>
+      <c r="A588" s="38"/>
     </row>
     <row r="589">
-      <c r="A589" s="37"/>
+      <c r="A589" s="38"/>
     </row>
     <row r="590">
-      <c r="A590" s="37"/>
+      <c r="A590" s="38"/>
     </row>
     <row r="591">
-      <c r="A591" s="37"/>
+      <c r="A591" s="38"/>
     </row>
     <row r="592">
-      <c r="A592" s="37"/>
+      <c r="A592" s="38"/>
     </row>
     <row r="593">
-      <c r="A593" s="37"/>
+      <c r="A593" s="38"/>
     </row>
     <row r="594">
-      <c r="A594" s="37"/>
+      <c r="A594" s="38"/>
     </row>
     <row r="595">
-      <c r="A595" s="37"/>
+      <c r="A595" s="38"/>
     </row>
     <row r="596">
-      <c r="A596" s="37"/>
+      <c r="A596" s="38"/>
     </row>
     <row r="597">
-      <c r="A597" s="37"/>
+      <c r="A597" s="38"/>
     </row>
     <row r="598">
-      <c r="A598" s="37"/>
+      <c r="A598" s="38"/>
     </row>
     <row r="599">
-      <c r="A599" s="37"/>
+      <c r="A599" s="38"/>
     </row>
     <row r="600">
-      <c r="A600" s="37"/>
+      <c r="A600" s="38"/>
     </row>
     <row r="601">
-      <c r="A601" s="37"/>
+      <c r="A601" s="38"/>
     </row>
     <row r="602">
-      <c r="A602" s="37"/>
+      <c r="A602" s="38"/>
     </row>
     <row r="603">
-      <c r="A603" s="37"/>
+      <c r="A603" s="38"/>
     </row>
     <row r="604">
-      <c r="A604" s="37"/>
+      <c r="A604" s="38"/>
     </row>
     <row r="605">
-      <c r="A605" s="37"/>
+      <c r="A605" s="38"/>
     </row>
     <row r="606">
-      <c r="A606" s="37"/>
+      <c r="A606" s="38"/>
     </row>
     <row r="607">
-      <c r="A607" s="37"/>
+      <c r="A607" s="38"/>
     </row>
     <row r="608">
-      <c r="A608" s="37"/>
+      <c r="A608" s="38"/>
     </row>
     <row r="609">
-      <c r="A609" s="37"/>
+      <c r="A609" s="38"/>
     </row>
     <row r="610">
-      <c r="A610" s="37"/>
+      <c r="A610" s="38"/>
     </row>
     <row r="611">
-      <c r="A611" s="37"/>
+      <c r="A611" s="38"/>
     </row>
     <row r="612">
-      <c r="A612" s="37"/>
+      <c r="A612" s="38"/>
     </row>
     <row r="613">
-      <c r="A613" s="37"/>
+      <c r="A613" s="38"/>
     </row>
     <row r="614">
-      <c r="A614" s="37"/>
+      <c r="A614" s="38"/>
     </row>
     <row r="615">
-      <c r="A615" s="37"/>
+      <c r="A615" s="38"/>
     </row>
     <row r="616">
-      <c r="A616" s="37"/>
+      <c r="A616" s="38"/>
     </row>
     <row r="617">
-      <c r="A617" s="37"/>
+      <c r="A617" s="38"/>
     </row>
     <row r="618">
-      <c r="A618" s="37"/>
+      <c r="A618" s="38"/>
     </row>
     <row r="619">
-      <c r="A619" s="37"/>
+      <c r="A619" s="38"/>
     </row>
     <row r="620">
-      <c r="A620" s="37"/>
+      <c r="A620" s="38"/>
     </row>
     <row r="621">
-      <c r="A621" s="37"/>
+      <c r="A621" s="38"/>
     </row>
     <row r="622">
-      <c r="A622" s="37"/>
+      <c r="A622" s="38"/>
     </row>
     <row r="623">
-      <c r="A623" s="37"/>
+      <c r="A623" s="38"/>
     </row>
     <row r="624">
-      <c r="A624" s="37"/>
+      <c r="A624" s="38"/>
     </row>
     <row r="625">
-      <c r="A625" s="37"/>
+      <c r="A625" s="38"/>
     </row>
     <row r="626">
-      <c r="A626" s="37"/>
+      <c r="A626" s="38"/>
     </row>
     <row r="627">
-      <c r="A627" s="37"/>
+      <c r="A627" s="38"/>
     </row>
     <row r="628">
-      <c r="A628" s="37"/>
+      <c r="A628" s="38"/>
     </row>
     <row r="629">
-      <c r="A629" s="37"/>
+      <c r="A629" s="38"/>
     </row>
     <row r="630">
-      <c r="A630" s="37"/>
+      <c r="A630" s="38"/>
     </row>
     <row r="631">
-      <c r="A631" s="37"/>
+      <c r="A631" s="38"/>
     </row>
     <row r="632">
-      <c r="A632" s="37"/>
+      <c r="A632" s="38"/>
     </row>
     <row r="633">
-      <c r="A633" s="37"/>
+      <c r="A633" s="38"/>
     </row>
     <row r="634">
-      <c r="A634" s="37"/>
+      <c r="A634" s="38"/>
     </row>
     <row r="635">
-      <c r="A635" s="37"/>
+      <c r="A635" s="38"/>
     </row>
     <row r="636">
-      <c r="A636" s="37"/>
+      <c r="A636" s="38"/>
     </row>
     <row r="637">
-      <c r="A637" s="37"/>
+      <c r="A637" s="38"/>
     </row>
     <row r="638">
-      <c r="A638" s="37"/>
+      <c r="A638" s="38"/>
     </row>
     <row r="639">
-      <c r="A639" s="37"/>
+      <c r="A639" s="38"/>
     </row>
     <row r="640">
-      <c r="A640" s="37"/>
+      <c r="A640" s="38"/>
     </row>
     <row r="641">
-      <c r="A641" s="37"/>
+      <c r="A641" s="38"/>
     </row>
     <row r="642">
-      <c r="A642" s="37"/>
+      <c r="A642" s="38"/>
     </row>
     <row r="643">
-      <c r="A643" s="37"/>
+      <c r="A643" s="38"/>
     </row>
     <row r="644">
-      <c r="A644" s="37"/>
+      <c r="A644" s="38"/>
     </row>
     <row r="645">
-      <c r="A645" s="37"/>
+      <c r="A645" s="38"/>
     </row>
     <row r="646">
-      <c r="A646" s="37"/>
+      <c r="A646" s="38"/>
     </row>
     <row r="647">
-      <c r="A647" s="37"/>
+      <c r="A647" s="38"/>
     </row>
     <row r="648">
-      <c r="A648" s="37"/>
+      <c r="A648" s="38"/>
     </row>
     <row r="649">
-      <c r="A649" s="37"/>
+      <c r="A649" s="38"/>
     </row>
     <row r="650">
-      <c r="A650" s="37"/>
+      <c r="A650" s="38"/>
     </row>
     <row r="651">
-      <c r="A651" s="37"/>
+      <c r="A651" s="38"/>
     </row>
     <row r="652">
-      <c r="A652" s="37"/>
+      <c r="A652" s="38"/>
     </row>
     <row r="653">
-      <c r="A653" s="37"/>
+      <c r="A653" s="38"/>
     </row>
     <row r="654">
-      <c r="A654" s="37"/>
+      <c r="A654" s="38"/>
     </row>
     <row r="655">
-      <c r="A655" s="37"/>
+      <c r="A655" s="38"/>
     </row>
     <row r="656">
-      <c r="A656" s="37"/>
+      <c r="A656" s="38"/>
     </row>
     <row r="657">
-      <c r="A657" s="37"/>
+      <c r="A657" s="38"/>
     </row>
     <row r="658">
-      <c r="A658" s="37"/>
+      <c r="A658" s="38"/>
     </row>
     <row r="659">
-      <c r="A659" s="37"/>
+      <c r="A659" s="38"/>
     </row>
     <row r="660">
-      <c r="A660" s="37"/>
+      <c r="A660" s="38"/>
     </row>
     <row r="661">
-      <c r="A661" s="37"/>
+      <c r="A661" s="38"/>
     </row>
     <row r="662">
-      <c r="A662" s="37"/>
+      <c r="A662" s="38"/>
     </row>
     <row r="663">
-      <c r="A663" s="37"/>
+      <c r="A663" s="38"/>
     </row>
     <row r="664">
-      <c r="A664" s="37"/>
+      <c r="A664" s="38"/>
     </row>
     <row r="665">
-      <c r="A665" s="37"/>
+      <c r="A665" s="38"/>
     </row>
     <row r="666">
-      <c r="A666" s="37"/>
+      <c r="A666" s="38"/>
     </row>
     <row r="667">
-      <c r="A667" s="37"/>
+      <c r="A667" s="38"/>
     </row>
     <row r="668">
-      <c r="A668" s="37"/>
+      <c r="A668" s="38"/>
     </row>
     <row r="669">
-      <c r="A669" s="37"/>
+      <c r="A669" s="38"/>
     </row>
     <row r="670">
-      <c r="A670" s="37"/>
+      <c r="A670" s="38"/>
     </row>
     <row r="671">
-      <c r="A671" s="37"/>
+      <c r="A671" s="38"/>
     </row>
     <row r="672">
-      <c r="A672" s="37"/>
+      <c r="A672" s="38"/>
     </row>
     <row r="673">
-      <c r="A673" s="37"/>
+      <c r="A673" s="38"/>
     </row>
     <row r="674">
-      <c r="A674" s="37"/>
+      <c r="A674" s="38"/>
     </row>
     <row r="675">
-      <c r="A675" s="37"/>
+      <c r="A675" s="38"/>
     </row>
     <row r="676">
-      <c r="A676" s="37"/>
+      <c r="A676" s="38"/>
     </row>
     <row r="677">
-      <c r="A677" s="37"/>
+      <c r="A677" s="38"/>
     </row>
     <row r="678">
-      <c r="A678" s="37"/>
+      <c r="A678" s="38"/>
     </row>
     <row r="679">
-      <c r="A679" s="37"/>
+      <c r="A679" s="38"/>
     </row>
     <row r="680">
-      <c r="A680" s="37"/>
+      <c r="A680" s="38"/>
     </row>
     <row r="681">
-      <c r="A681" s="37"/>
+      <c r="A681" s="38"/>
     </row>
     <row r="682">
-      <c r="A682" s="37"/>
+      <c r="A682" s="38"/>
     </row>
     <row r="683">
-      <c r="A683" s="37"/>
+      <c r="A683" s="38"/>
     </row>
     <row r="684">
-      <c r="A684" s="37"/>
+      <c r="A684" s="38"/>
     </row>
     <row r="685">
-      <c r="A685" s="37"/>
+      <c r="A685" s="38"/>
     </row>
     <row r="686">
-      <c r="A686" s="37"/>
+      <c r="A686" s="38"/>
     </row>
     <row r="687">
-      <c r="A687" s="37"/>
+      <c r="A687" s="38"/>
     </row>
     <row r="688">
-      <c r="A688" s="37"/>
+      <c r="A688" s="38"/>
     </row>
     <row r="689">
-      <c r="A689" s="37"/>
+      <c r="A689" s="38"/>
     </row>
     <row r="690">
-      <c r="A690" s="37"/>
+      <c r="A690" s="38"/>
     </row>
     <row r="691">
-      <c r="A691" s="37"/>
+      <c r="A691" s="38"/>
     </row>
     <row r="692">
-      <c r="A692" s="37"/>
+      <c r="A692" s="38"/>
     </row>
     <row r="693">
-      <c r="A693" s="37"/>
+      <c r="A693" s="38"/>
     </row>
     <row r="694">
-      <c r="A694" s="37"/>
+      <c r="A694" s="38"/>
     </row>
     <row r="695">
-      <c r="A695" s="37"/>
+      <c r="A695" s="38"/>
     </row>
     <row r="696">
-      <c r="A696" s="37"/>
+      <c r="A696" s="38"/>
     </row>
     <row r="697">
-      <c r="A697" s="37"/>
+      <c r="A697" s="38"/>
     </row>
     <row r="698">
-      <c r="A698" s="37"/>
+      <c r="A698" s="38"/>
     </row>
     <row r="699">
-      <c r="A699" s="37"/>
+      <c r="A699" s="38"/>
     </row>
     <row r="700">
-      <c r="A700" s="37"/>
+      <c r="A700" s="38"/>
     </row>
     <row r="701">
-      <c r="A701" s="37"/>
+      <c r="A701" s="38"/>
     </row>
     <row r="702">
-      <c r="A702" s="37"/>
+      <c r="A702" s="38"/>
     </row>
     <row r="703">
-      <c r="A703" s="37"/>
+      <c r="A703" s="38"/>
     </row>
     <row r="704">
-      <c r="A704" s="37"/>
+      <c r="A704" s="38"/>
     </row>
     <row r="705">
-      <c r="A705" s="37"/>
+      <c r="A705" s="38"/>
     </row>
     <row r="706">
-      <c r="A706" s="37"/>
+      <c r="A706" s="38"/>
     </row>
     <row r="707">
-      <c r="A707" s="37"/>
+      <c r="A707" s="38"/>
     </row>
     <row r="708">
-      <c r="A708" s="37"/>
+      <c r="A708" s="38"/>
     </row>
     <row r="709">
-      <c r="A709" s="37"/>
+      <c r="A709" s="38"/>
     </row>
     <row r="710">
-      <c r="A710" s="37"/>
+      <c r="A710" s="38"/>
     </row>
     <row r="711">
-      <c r="A711" s="37"/>
+      <c r="A711" s="38"/>
     </row>
     <row r="712">
-      <c r="A712" s="37"/>
+      <c r="A712" s="38"/>
     </row>
     <row r="713">
-      <c r="A713" s="37"/>
+      <c r="A713" s="38"/>
     </row>
     <row r="714">
-      <c r="A714" s="37"/>
+      <c r="A714" s="38"/>
     </row>
     <row r="715">
-      <c r="A715" s="37"/>
+      <c r="A715" s="38"/>
     </row>
     <row r="716">
-      <c r="A716" s="37"/>
+      <c r="A716" s="38"/>
     </row>
     <row r="717">
-      <c r="A717" s="37"/>
+      <c r="A717" s="38"/>
     </row>
     <row r="718">
-      <c r="A718" s="37"/>
+      <c r="A718" s="38"/>
     </row>
     <row r="719">
-      <c r="A719" s="37"/>
+      <c r="A719" s="38"/>
     </row>
     <row r="720">
-      <c r="A720" s="37"/>
+      <c r="A720" s="38"/>
     </row>
     <row r="721">
-      <c r="A721" s="37"/>
+      <c r="A721" s="38"/>
     </row>
     <row r="722">
-      <c r="A722" s="37"/>
+      <c r="A722" s="38"/>
     </row>
     <row r="723">
-      <c r="A723" s="37"/>
+      <c r="A723" s="38"/>
     </row>
     <row r="724">
-      <c r="A724" s="37"/>
+      <c r="A724" s="38"/>
     </row>
     <row r="725">
-      <c r="A725" s="37"/>
+      <c r="A725" s="38"/>
     </row>
     <row r="726">
-      <c r="A726" s="37"/>
+      <c r="A726" s="38"/>
     </row>
     <row r="727">
-      <c r="A727" s="37"/>
+      <c r="A727" s="38"/>
     </row>
     <row r="728">
-      <c r="A728" s="37"/>
+      <c r="A728" s="38"/>
     </row>
     <row r="729">
-      <c r="A729" s="37"/>
+      <c r="A729" s="38"/>
     </row>
     <row r="730">
-      <c r="A730" s="37"/>
+      <c r="A730" s="38"/>
     </row>
     <row r="731">
-      <c r="A731" s="37"/>
+      <c r="A731" s="38"/>
     </row>
     <row r="732">
-      <c r="A732" s="37"/>
+      <c r="A732" s="38"/>
     </row>
     <row r="733">
-      <c r="A733" s="37"/>
+      <c r="A733" s="38"/>
     </row>
     <row r="734">
-      <c r="A734" s="37"/>
+      <c r="A734" s="38"/>
     </row>
     <row r="735">
-      <c r="A735" s="37"/>
+      <c r="A735" s="38"/>
     </row>
     <row r="736">
-      <c r="A736" s="37"/>
+      <c r="A736" s="38"/>
     </row>
     <row r="737">
-      <c r="A737" s="37"/>
+      <c r="A737" s="38"/>
     </row>
     <row r="738">
-      <c r="A738" s="37"/>
+      <c r="A738" s="38"/>
     </row>
     <row r="739">
-      <c r="A739" s="37"/>
+      <c r="A739" s="38"/>
     </row>
     <row r="740">
-      <c r="A740" s="37"/>
+      <c r="A740" s="38"/>
     </row>
     <row r="741">
-      <c r="A741" s="37"/>
+      <c r="A741" s="38"/>
     </row>
     <row r="742">
-      <c r="A742" s="37"/>
+      <c r="A742" s="38"/>
     </row>
     <row r="743">
-      <c r="A743" s="37"/>
+      <c r="A743" s="38"/>
     </row>
     <row r="744">
-      <c r="A744" s="37"/>
+      <c r="A744" s="38"/>
     </row>
     <row r="745">
-      <c r="A745" s="37"/>
+      <c r="A745" s="38"/>
     </row>
     <row r="746">
-      <c r="A746" s="37"/>
+      <c r="A746" s="38"/>
     </row>
     <row r="747">
-      <c r="A747" s="37"/>
+      <c r="A747" s="38"/>
     </row>
     <row r="748">
-      <c r="A748" s="37"/>
+      <c r="A748" s="38"/>
     </row>
     <row r="749">
-      <c r="A749" s="37"/>
+      <c r="A749" s="38"/>
     </row>
     <row r="750">
-      <c r="A750" s="37"/>
+      <c r="A750" s="38"/>
     </row>
     <row r="751">
-      <c r="A751" s="37"/>
+      <c r="A751" s="38"/>
     </row>
     <row r="752">
-      <c r="A752" s="37"/>
+      <c r="A752" s="38"/>
     </row>
     <row r="753">
-      <c r="A753" s="37"/>
+      <c r="A753" s="38"/>
     </row>
     <row r="754">
-      <c r="A754" s="37"/>
+      <c r="A754" s="38"/>
     </row>
     <row r="755">
-      <c r="A755" s="37"/>
+      <c r="A755" s="38"/>
     </row>
     <row r="756">
-      <c r="A756" s="37"/>
+      <c r="A756" s="38"/>
     </row>
     <row r="757">
-      <c r="A757" s="37"/>
+      <c r="A757" s="38"/>
     </row>
     <row r="758">
-      <c r="A758" s="37"/>
+      <c r="A758" s="38"/>
     </row>
     <row r="759">
-      <c r="A759" s="37"/>
+      <c r="A759" s="38"/>
     </row>
     <row r="760">
-      <c r="A760" s="37"/>
+      <c r="A760" s="38"/>
     </row>
     <row r="761">
-      <c r="A761" s="37"/>
+      <c r="A761" s="38"/>
     </row>
     <row r="762">
-      <c r="A762" s="37"/>
+      <c r="A762" s="38"/>
     </row>
     <row r="763">
-      <c r="A763" s="37"/>
+      <c r="A763" s="38"/>
     </row>
     <row r="764">
-      <c r="A764" s="37"/>
+      <c r="A764" s="38"/>
     </row>
     <row r="765">
-      <c r="A765" s="37"/>
+      <c r="A765" s="38"/>
     </row>
     <row r="766">
-      <c r="A766" s="37"/>
+      <c r="A766" s="38"/>
     </row>
     <row r="767">
-      <c r="A767" s="37"/>
+      <c r="A767" s="38"/>
     </row>
     <row r="768">
-      <c r="A768" s="37"/>
+      <c r="A768" s="38"/>
     </row>
     <row r="769">
-      <c r="A769" s="37"/>
+      <c r="A769" s="38"/>
     </row>
     <row r="770">
-      <c r="A770" s="37"/>
+      <c r="A770" s="38"/>
     </row>
     <row r="771">
-      <c r="A771" s="37"/>
+      <c r="A771" s="38"/>
     </row>
     <row r="772">
-      <c r="A772" s="37"/>
+      <c r="A772" s="38"/>
     </row>
     <row r="773">
-      <c r="A773" s="37"/>
+      <c r="A773" s="38"/>
     </row>
     <row r="774">
-      <c r="A774" s="37"/>
+      <c r="A774" s="38"/>
     </row>
     <row r="775">
-      <c r="A775" s="37"/>
+      <c r="A775" s="38"/>
     </row>
     <row r="776">
-      <c r="A776" s="37"/>
+      <c r="A776" s="38"/>
     </row>
     <row r="777">
-      <c r="A777" s="37"/>
+      <c r="A777" s="38"/>
     </row>
     <row r="778">
-      <c r="A778" s="37"/>
+      <c r="A778" s="38"/>
     </row>
     <row r="779">
-      <c r="A779" s="37"/>
+      <c r="A779" s="38"/>
     </row>
     <row r="780">
-      <c r="A780" s="37"/>
+      <c r="A780" s="38"/>
     </row>
     <row r="781">
-      <c r="A781" s="37"/>
+      <c r="A781" s="38"/>
     </row>
     <row r="782">
-      <c r="A782" s="37"/>
+      <c r="A782" s="38"/>
     </row>
     <row r="783">
-      <c r="A783" s="37"/>
+      <c r="A783" s="38"/>
     </row>
     <row r="784">
-      <c r="A784" s="37"/>
+      <c r="A784" s="38"/>
     </row>
     <row r="785">
-      <c r="A785" s="37"/>
+      <c r="A785" s="38"/>
     </row>
     <row r="786">
-      <c r="A786" s="37"/>
+      <c r="A786" s="38"/>
     </row>
     <row r="787">
-      <c r="A787" s="37"/>
+      <c r="A787" s="38"/>
     </row>
     <row r="788">
-      <c r="A788" s="37"/>
+      <c r="A788" s="38"/>
     </row>
     <row r="789">
-      <c r="A789" s="37"/>
+      <c r="A789" s="38"/>
     </row>
     <row r="790">
-      <c r="A790" s="37"/>
+      <c r="A790" s="38"/>
     </row>
     <row r="791">
-      <c r="A791" s="37"/>
+      <c r="A791" s="38"/>
     </row>
     <row r="792">
-      <c r="A792" s="37"/>
+      <c r="A792" s="38"/>
     </row>
     <row r="793">
-      <c r="A793" s="37"/>
+      <c r="A793" s="38"/>
     </row>
     <row r="794">
-      <c r="A794" s="37"/>
+      <c r="A794" s="38"/>
     </row>
     <row r="795">
-      <c r="A795" s="37"/>
+      <c r="A795" s="38"/>
     </row>
     <row r="796">
-      <c r="A796" s="37"/>
+      <c r="A796" s="38"/>
     </row>
     <row r="797">
-      <c r="A797" s="37"/>
+      <c r="A797" s="38"/>
     </row>
     <row r="798">
-      <c r="A798" s="37"/>
+      <c r="A798" s="38"/>
     </row>
     <row r="799">
-      <c r="A799" s="37"/>
+      <c r="A799" s="38"/>
     </row>
     <row r="800">
-      <c r="A800" s="37"/>
+      <c r="A800" s="38"/>
     </row>
     <row r="801">
-      <c r="A801" s="37"/>
+      <c r="A801" s="38"/>
     </row>
     <row r="802">
-      <c r="A802" s="37"/>
+      <c r="A802" s="38"/>
     </row>
     <row r="803">
-      <c r="A803" s="37"/>
+      <c r="A803" s="38"/>
     </row>
     <row r="804">
-      <c r="A804" s="37"/>
+      <c r="A804" s="38"/>
     </row>
     <row r="805">
-      <c r="A805" s="37"/>
+      <c r="A805" s="38"/>
     </row>
     <row r="806">
-      <c r="A806" s="37"/>
+      <c r="A806" s="38"/>
     </row>
     <row r="807">
-      <c r="A807" s="37"/>
+      <c r="A807" s="38"/>
     </row>
     <row r="808">
-      <c r="A808" s="37"/>
+      <c r="A808" s="38"/>
     </row>
     <row r="809">
-      <c r="A809" s="37"/>
+      <c r="A809" s="38"/>
     </row>
     <row r="810">
-      <c r="A810" s="37"/>
+      <c r="A810" s="38"/>
     </row>
     <row r="811">
-      <c r="A811" s="37"/>
+      <c r="A811" s="38"/>
     </row>
     <row r="812">
-      <c r="A812" s="37"/>
+      <c r="A812" s="38"/>
     </row>
     <row r="813">
-      <c r="A813" s="37"/>
+      <c r="A813" s="38"/>
     </row>
     <row r="814">
-      <c r="A814" s="37"/>
+      <c r="A814" s="38"/>
     </row>
     <row r="815">
-      <c r="A815" s="37"/>
+      <c r="A815" s="38"/>
     </row>
     <row r="816">
-      <c r="A816" s="37"/>
+      <c r="A816" s="38"/>
     </row>
     <row r="817">
-      <c r="A817" s="37"/>
+      <c r="A817" s="38"/>
     </row>
     <row r="818">
-      <c r="A818" s="37"/>
+      <c r="A818" s="38"/>
     </row>
     <row r="819">
-      <c r="A819" s="37"/>
+      <c r="A819" s="38"/>
     </row>
     <row r="820">
-      <c r="A820" s="37"/>
+      <c r="A820" s="38"/>
     </row>
     <row r="821">
-      <c r="A821" s="37"/>
+      <c r="A821" s="38"/>
     </row>
     <row r="822">
-      <c r="A822" s="37"/>
+      <c r="A822" s="38"/>
     </row>
     <row r="823">
-      <c r="A823" s="37"/>
+      <c r="A823" s="38"/>
     </row>
     <row r="824">
-      <c r="A824" s="37"/>
+      <c r="A824" s="38"/>
     </row>
     <row r="825">
-      <c r="A825" s="37"/>
+      <c r="A825" s="38"/>
     </row>
     <row r="826">
-      <c r="A826" s="37"/>
+      <c r="A826" s="38"/>
     </row>
     <row r="827">
-      <c r="A827" s="37"/>
+      <c r="A827" s="38"/>
     </row>
     <row r="828">
-      <c r="A828" s="37"/>
+      <c r="A828" s="38"/>
     </row>
     <row r="829">
-      <c r="A829" s="37"/>
+      <c r="A829" s="38"/>
     </row>
     <row r="830">
-      <c r="A830" s="37"/>
+      <c r="A830" s="38"/>
     </row>
     <row r="831">
-      <c r="A831" s="37"/>
+      <c r="A831" s="38"/>
     </row>
     <row r="832">
-      <c r="A832" s="37"/>
+      <c r="A832" s="38"/>
     </row>
     <row r="833">
-      <c r="A833" s="37"/>
+      <c r="A833" s="38"/>
     </row>
     <row r="834">
-      <c r="A834" s="37"/>
+      <c r="A834" s="38"/>
     </row>
     <row r="835">
-      <c r="A835" s="37"/>
+      <c r="A835" s="38"/>
     </row>
     <row r="836">
-      <c r="A836" s="37"/>
+      <c r="A836" s="38"/>
     </row>
     <row r="837">
-      <c r="A837" s="37"/>
+      <c r="A837" s="38"/>
     </row>
     <row r="838">
-      <c r="A838" s="37"/>
+      <c r="A838" s="38"/>
     </row>
     <row r="839">
-      <c r="A839" s="37"/>
+      <c r="A839" s="38"/>
     </row>
     <row r="840">
-      <c r="A840" s="37"/>
+      <c r="A840" s="38"/>
     </row>
     <row r="841">
-      <c r="A841" s="37"/>
+      <c r="A841" s="38"/>
     </row>
     <row r="842">
-      <c r="A842" s="37"/>
+      <c r="A842" s="38"/>
     </row>
     <row r="843">
-      <c r="A843" s="37"/>
+      <c r="A843" s="38"/>
     </row>
     <row r="844">
-      <c r="A844" s="37"/>
+      <c r="A844" s="38"/>
     </row>
     <row r="845">
-      <c r="A845" s="37"/>
+      <c r="A845" s="38"/>
     </row>
     <row r="846">
-      <c r="A846" s="37"/>
+      <c r="A846" s="38"/>
     </row>
     <row r="847">
-      <c r="A847" s="37"/>
+      <c r="A847" s="38"/>
     </row>
     <row r="848">
-      <c r="A848" s="37"/>
+      <c r="A848" s="38"/>
     </row>
     <row r="849">
-      <c r="A849" s="37"/>
+      <c r="A849" s="38"/>
     </row>
     <row r="850">
-      <c r="A850" s="37"/>
+      <c r="A850" s="38"/>
     </row>
     <row r="851">
-      <c r="A851" s="37"/>
+      <c r="A851" s="38"/>
     </row>
     <row r="852">
-      <c r="A852" s="37"/>
+      <c r="A852" s="38"/>
     </row>
     <row r="853">
-      <c r="A853" s="37"/>
+      <c r="A853" s="38"/>
     </row>
     <row r="854">
-      <c r="A854" s="37"/>
+      <c r="A854" s="38"/>
     </row>
     <row r="855">
-      <c r="A855" s="37"/>
+      <c r="A855" s="38"/>
     </row>
     <row r="856">
-      <c r="A856" s="37"/>
+      <c r="A856" s="38"/>
     </row>
     <row r="857">
-      <c r="A857" s="37"/>
+      <c r="A857" s="38"/>
     </row>
     <row r="858">
-      <c r="A858" s="37"/>
+      <c r="A858" s="38"/>
     </row>
     <row r="859">
-      <c r="A859" s="37"/>
+      <c r="A859" s="38"/>
     </row>
     <row r="860">
-      <c r="A860" s="37"/>
+      <c r="A860" s="38"/>
     </row>
     <row r="861">
-      <c r="A861" s="37"/>
+      <c r="A861" s="38"/>
     </row>
     <row r="862">
-      <c r="A862" s="37"/>
+      <c r="A862" s="38"/>
     </row>
     <row r="863">
-      <c r="A863" s="37"/>
+      <c r="A863" s="38"/>
     </row>
     <row r="864">
-      <c r="A864" s="37"/>
+      <c r="A864" s="38"/>
     </row>
     <row r="865">
-      <c r="A865" s="37"/>
+      <c r="A865" s="38"/>
     </row>
     <row r="866">
-      <c r="A866" s="37"/>
+      <c r="A866" s="38"/>
     </row>
     <row r="867">
-      <c r="A867" s="37"/>
+      <c r="A867" s="38"/>
     </row>
     <row r="868">
-      <c r="A868" s="37"/>
+      <c r="A868" s="38"/>
     </row>
     <row r="869">
-      <c r="A869" s="37"/>
+      <c r="A869" s="38"/>
     </row>
     <row r="870">
-      <c r="A870" s="37"/>
+      <c r="A870" s="38"/>
     </row>
     <row r="871">
-      <c r="A871" s="37"/>
+      <c r="A871" s="38"/>
     </row>
     <row r="872">
-      <c r="A872" s="37"/>
+      <c r="A872" s="38"/>
     </row>
     <row r="873">
-      <c r="A873" s="37"/>
+      <c r="A873" s="38"/>
     </row>
     <row r="874">
-      <c r="A874" s="37"/>
+      <c r="A874" s="38"/>
     </row>
     <row r="875">
-      <c r="A875" s="37"/>
+      <c r="A875" s="38"/>
     </row>
     <row r="876">
-      <c r="A876" s="37"/>
+      <c r="A876" s="38"/>
     </row>
     <row r="877">
-      <c r="A877" s="37"/>
+      <c r="A877" s="38"/>
     </row>
     <row r="878">
-      <c r="A878" s="37"/>
+      <c r="A878" s="38"/>
     </row>
     <row r="879">
-      <c r="A879" s="37"/>
+      <c r="A879" s="38"/>
     </row>
     <row r="880">
-      <c r="A880" s="37"/>
+      <c r="A880" s="38"/>
     </row>
     <row r="881">
-      <c r="A881" s="37"/>
+      <c r="A881" s="38"/>
     </row>
     <row r="882">
-      <c r="A882" s="37"/>
+      <c r="A882" s="38"/>
     </row>
     <row r="883">
-      <c r="A883" s="37"/>
+      <c r="A883" s="38"/>
     </row>
     <row r="884">
-      <c r="A884" s="37"/>
+      <c r="A884" s="38"/>
     </row>
     <row r="885">
-      <c r="A885" s="37"/>
+      <c r="A885" s="38"/>
     </row>
     <row r="886">
-      <c r="A886" s="37"/>
+      <c r="A886" s="38"/>
     </row>
     <row r="887">
-      <c r="A887" s="37"/>
+      <c r="A887" s="38"/>
     </row>
     <row r="888">
-      <c r="A888" s="37"/>
+      <c r="A888" s="38"/>
     </row>
     <row r="889">
-      <c r="A889" s="37"/>
+      <c r="A889" s="38"/>
     </row>
     <row r="890">
-      <c r="A890" s="37"/>
+      <c r="A890" s="38"/>
     </row>
     <row r="891">
-      <c r="A891" s="37"/>
+      <c r="A891" s="38"/>
     </row>
     <row r="892">
-      <c r="A892" s="37"/>
+      <c r="A892" s="38"/>
     </row>
     <row r="893">
-      <c r="A893" s="37"/>
+      <c r="A893" s="38"/>
     </row>
     <row r="894">
-      <c r="A894" s="37"/>
+      <c r="A894" s="38"/>
     </row>
     <row r="895">
-      <c r="A895" s="37"/>
+      <c r="A895" s="38"/>
     </row>
     <row r="896">
-      <c r="A896" s="37"/>
+      <c r="A896" s="38"/>
     </row>
     <row r="897">
-      <c r="A897" s="37"/>
+      <c r="A897" s="38"/>
     </row>
     <row r="898">
-      <c r="A898" s="37"/>
+      <c r="A898" s="38"/>
     </row>
     <row r="899">
-      <c r="A899" s="37"/>
+      <c r="A899" s="38"/>
     </row>
     <row r="900">
-      <c r="A900" s="37"/>
+      <c r="A900" s="38"/>
     </row>
     <row r="901">
-      <c r="A901" s="37"/>
+      <c r="A901" s="38"/>
     </row>
     <row r="902">
-      <c r="A902" s="37"/>
+      <c r="A902" s="38"/>
     </row>
     <row r="903">
-      <c r="A903" s="37"/>
+      <c r="A903" s="38"/>
     </row>
     <row r="904">
-      <c r="A904" s="37"/>
+      <c r="A904" s="38"/>
     </row>
     <row r="905">
-      <c r="A905" s="37"/>
+      <c r="A905" s="38"/>
     </row>
     <row r="906">
-      <c r="A906" s="37"/>
+      <c r="A906" s="38"/>
     </row>
     <row r="907">
-      <c r="A907" s="37"/>
+      <c r="A907" s="38"/>
     </row>
     <row r="908">
-      <c r="A908" s="37"/>
+      <c r="A908" s="38"/>
     </row>
     <row r="909">
-      <c r="A909" s="37"/>
+      <c r="A909" s="38"/>
     </row>
     <row r="910">
-      <c r="A910" s="37"/>
+      <c r="A910" s="38"/>
     </row>
     <row r="911">
-      <c r="A911" s="37"/>
+      <c r="A911" s="38"/>
     </row>
     <row r="912">
-      <c r="A912" s="37"/>
+      <c r="A912" s="38"/>
     </row>
     <row r="913">
-      <c r="A913" s="37"/>
+      <c r="A913" s="38"/>
     </row>
     <row r="914">
-      <c r="A914" s="37"/>
+      <c r="A914" s="38"/>
     </row>
     <row r="915">
-      <c r="A915" s="37"/>
+      <c r="A915" s="38"/>
     </row>
     <row r="916">
-      <c r="A916" s="37"/>
+      <c r="A916" s="38"/>
     </row>
     <row r="917">
-      <c r="A917" s="37"/>
+      <c r="A917" s="38"/>
     </row>
     <row r="918">
-      <c r="A918" s="37"/>
+      <c r="A918" s="38"/>
     </row>
     <row r="919">
-      <c r="A919" s="37"/>
+      <c r="A919" s="38"/>
     </row>
     <row r="920">
-      <c r="A920" s="37"/>
+      <c r="A920" s="38"/>
     </row>
     <row r="921">
-      <c r="A921" s="37"/>
+      <c r="A921" s="38"/>
     </row>
     <row r="922">
-      <c r="A922" s="37"/>
+      <c r="A922" s="38"/>
     </row>
     <row r="923">
-      <c r="A923" s="37"/>
+      <c r="A923" s="38"/>
     </row>
     <row r="924">
-      <c r="A924" s="37"/>
+      <c r="A924" s="38"/>
     </row>
     <row r="925">
-      <c r="A925" s="37"/>
+      <c r="A925" s="38"/>
     </row>
     <row r="926">
-      <c r="A926" s="37"/>
+      <c r="A926" s="38"/>
     </row>
     <row r="927">
-      <c r="A927" s="37"/>
+      <c r="A927" s="38"/>
     </row>
     <row r="928">
-      <c r="A928" s="37"/>
+      <c r="A928" s="38"/>
     </row>
     <row r="929">
-      <c r="A929" s="37"/>
+      <c r="A929" s="38"/>
     </row>
     <row r="930">
-      <c r="A930" s="37"/>
+      <c r="A930" s="38"/>
     </row>
     <row r="931">
-      <c r="A931" s="37"/>
+      <c r="A931" s="38"/>
     </row>
     <row r="932">
-      <c r="A932" s="37"/>
+      <c r="A932" s="38"/>
     </row>
     <row r="933">
-      <c r="A933" s="37"/>
+      <c r="A933" s="38"/>
     </row>
     <row r="934">
-      <c r="A934" s="37"/>
+      <c r="A934" s="38"/>
     </row>
     <row r="935">
-      <c r="A935" s="37"/>
+      <c r="A935" s="38"/>
     </row>
     <row r="936">
-      <c r="A936" s="37"/>
+      <c r="A936" s="38"/>
     </row>
     <row r="937">
-      <c r="A937" s="37"/>
+      <c r="A937" s="38"/>
     </row>
     <row r="938">
-      <c r="A938" s="37"/>
+      <c r="A938" s="38"/>
     </row>
     <row r="939">
-      <c r="A939" s="37"/>
+      <c r="A939" s="38"/>
     </row>
     <row r="940">
-      <c r="A940" s="37"/>
+      <c r="A940" s="38"/>
     </row>
     <row r="941">
-      <c r="A941" s="37"/>
+      <c r="A941" s="38"/>
     </row>
     <row r="942">
-      <c r="A942" s="37"/>
+      <c r="A942" s="38"/>
     </row>
     <row r="943">
-      <c r="A943" s="37"/>
+      <c r="A943" s="38"/>
     </row>
     <row r="944">
-      <c r="A944" s="37"/>
+      <c r="A944" s="38"/>
     </row>
     <row r="945">
-      <c r="A945" s="37"/>
+      <c r="A945" s="38"/>
     </row>
     <row r="946">
-      <c r="A946" s="37"/>
+      <c r="A946" s="38"/>
     </row>
     <row r="947">
-      <c r="A947" s="37"/>
+      <c r="A947" s="38"/>
     </row>
     <row r="948">
-      <c r="A948" s="37"/>
+      <c r="A948" s="38"/>
     </row>
     <row r="949">
-      <c r="A949" s="37"/>
+      <c r="A949" s="38"/>
     </row>
     <row r="950">
-      <c r="A950" s="37"/>
+      <c r="A950" s="38"/>
     </row>
     <row r="951">
-      <c r="A951" s="37"/>
+      <c r="A951" s="38"/>
     </row>
     <row r="952">
-      <c r="A952" s="37"/>
+      <c r="A952" s="38"/>
     </row>
     <row r="953">
-      <c r="A953" s="37"/>
+      <c r="A953" s="38"/>
     </row>
     <row r="954">
-      <c r="A954" s="37"/>
+      <c r="A954" s="38"/>
     </row>
     <row r="955">
-      <c r="A955" s="37"/>
+      <c r="A955" s="38"/>
     </row>
     <row r="956">
-      <c r="A956" s="37"/>
+      <c r="A956" s="38"/>
     </row>
     <row r="957">
-      <c r="A957" s="37"/>
+      <c r="A957" s="38"/>
     </row>
     <row r="958">
-      <c r="A958" s="37"/>
+      <c r="A958" s="38"/>
     </row>
     <row r="959">
-      <c r="A959" s="37"/>
+      <c r="A959" s="38"/>
     </row>
     <row r="960">
-      <c r="A960" s="37"/>
+      <c r="A960" s="38"/>
     </row>
     <row r="961">
-      <c r="A961" s="37"/>
+      <c r="A961" s="38"/>
     </row>
     <row r="962">
-      <c r="A962" s="37"/>
+      <c r="A962" s="38"/>
     </row>
     <row r="963">
-      <c r="A963" s="37"/>
+      <c r="A963" s="38"/>
     </row>
     <row r="964">
-      <c r="A964" s="37"/>
+      <c r="A964" s="38"/>
     </row>
     <row r="965">
-      <c r="A965" s="37"/>
+      <c r="A965" s="38"/>
     </row>
     <row r="966">
-      <c r="A966" s="37"/>
+      <c r="A966" s="38"/>
     </row>
     <row r="967">
-      <c r="A967" s="37"/>
+      <c r="A967" s="38"/>
     </row>
     <row r="968">
-      <c r="A968" s="37"/>
+      <c r="A968" s="38"/>
     </row>
     <row r="969">
-      <c r="A969" s="37"/>
+      <c r="A969" s="38"/>
     </row>
     <row r="970">
-      <c r="A970" s="37"/>
+      <c r="A970" s="38"/>
     </row>
     <row r="971">
-      <c r="A971" s="37"/>
+      <c r="A971" s="38"/>
     </row>
     <row r="972">
-      <c r="A972" s="37"/>
+      <c r="A972" s="38"/>
     </row>
     <row r="973">
-      <c r="A973" s="37"/>
+      <c r="A973" s="38"/>
     </row>
     <row r="974">
-      <c r="A974" s="37"/>
+      <c r="A974" s="38"/>
     </row>
     <row r="975">
-      <c r="A975" s="37"/>
+      <c r="A975" s="38"/>
     </row>
     <row r="976">
-      <c r="A976" s="37"/>
+      <c r="A976" s="38"/>
     </row>
     <row r="977">
-      <c r="A977" s="37"/>
+      <c r="A977" s="38"/>
     </row>
     <row r="978">
-      <c r="A978" s="37"/>
+      <c r="A978" s="38"/>
     </row>
     <row r="979">
-      <c r="A979" s="37"/>
+      <c r="A979" s="38"/>
     </row>
     <row r="980">
-      <c r="A980" s="37"/>
+      <c r="A980" s="38"/>
     </row>
     <row r="981">
-      <c r="A981" s="37"/>
-    </row>
-    <row r="982">
-      <c r="A982" s="37"/>
-    </row>
-    <row r="983">
-      <c r="A983" s="37"/>
-    </row>
-    <row r="984">
-      <c r="A984" s="37"/>
-    </row>
-    <row r="985">
-      <c r="A985" s="37"/>
-    </row>
-    <row r="986">
-      <c r="A986" s="37"/>
-    </row>
-    <row r="987">
-      <c r="A987" s="37"/>
-    </row>
-    <row r="988">
-      <c r="A988" s="37"/>
-    </row>
-    <row r="989">
-      <c r="A989" s="37"/>
-    </row>
-    <row r="990">
-      <c r="A990" s="37"/>
-    </row>
-    <row r="991">
-      <c r="A991" s="37"/>
-    </row>
-    <row r="992">
-      <c r="A992" s="37"/>
-    </row>
-    <row r="993">
-      <c r="A993" s="37"/>
-    </row>
-    <row r="994">
-      <c r="A994" s="37"/>
-    </row>
-    <row r="995">
-      <c r="A995" s="37"/>
-    </row>
-    <row r="996">
-      <c r="A996" s="37"/>
-    </row>
-    <row r="997">
-      <c r="A997" s="37"/>
-    </row>
-    <row r="998">
-      <c r="A998" s="37"/>
-    </row>
-    <row r="999">
-      <c r="A999" s="37"/>
-    </row>
-    <row r="1000">
-      <c r="A1000" s="37"/>
+      <c r="A981" s="38"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
@@ -6925,33 +6300,33 @@
         <v>55</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>159</v>
+        <v>143</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>160</v>
+        <v>144</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>161</v>
+        <v>145</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>162</v>
+        <v>146</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>163</v>
+        <v>147</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>164</v>
+        <v>148</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="38" t="s">
+      <c r="A2" s="39" t="s">
         <v>92</v>
       </c>
-      <c r="B2" s="39" t="s">
-        <v>165</v>
-      </c>
-      <c r="C2" s="39" t="s">
-        <v>166</v>
+      <c r="B2" s="40" t="s">
+        <v>149</v>
+      </c>
+      <c r="C2" s="40" t="s">
+        <v>150</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="4">
@@ -6962,14 +6337,14 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="40" t="s">
-        <v>167</v>
-      </c>
-      <c r="B3" s="41" t="s">
-        <v>168</v>
+      <c r="A3" s="41" t="s">
+        <v>151</v>
+      </c>
+      <c r="B3" s="40" t="s">
+        <v>152</v>
       </c>
       <c r="C3" s="42" t="s">
-        <v>169</v>
+        <v>153</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="2">
@@ -6982,13 +6357,13 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>170</v>
+        <v>154</v>
       </c>
       <c r="B4" s="43" t="s">
-        <v>171</v>
+        <v>155</v>
       </c>
       <c r="C4" s="43" t="s">
-        <v>172</v>
+        <v>156</v>
       </c>
       <c r="D4" s="1"/>
       <c r="E4" s="23">
@@ -6998,6 +6373,23 @@
         <v>0.0</v>
       </c>
       <c r="G4" s="1"/>
+    </row>
+    <row r="5" ht="19.5" customHeight="1">
+      <c r="A5" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="B5" s="44" t="s">
+        <v>158</v>
+      </c>
+      <c r="C5" s="44" t="s">
+        <v>159</v>
+      </c>
+      <c r="E5" s="4">
+        <v>-10.0</v>
+      </c>
+      <c r="F5" s="4">
+        <v>0.0</v>
+      </c>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>

--- a/Assets/02Script/Table/EventTable.xlsx
+++ b/Assets/02Script/Table/EventTable.xlsx
@@ -499,7 +499,8 @@
     <t>C004</t>
   </si>
   <si>
-    <t>아무래도 꿈속이 맞나 봐..</t>
+    <t>아무래도 
+꿈속이 맞나 봐..</t>
   </si>
   <si>
     <t>비슷한 풍선이겠지?</t>
@@ -2612,8 +2613,8 @@
       <c r="H43" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="I43" s="18">
-        <v>1.0</v>
+      <c r="I43" s="19">
+        <v>-1.0</v>
       </c>
       <c r="J43" s="20"/>
     </row>
@@ -2640,8 +2641,8 @@
       <c r="H44" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="I44" s="18">
-        <v>1.0</v>
+      <c r="I44" s="19">
+        <v>-1.0</v>
       </c>
       <c r="J44" s="20"/>
     </row>
@@ -2668,8 +2669,8 @@
       <c r="H45" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="I45" s="18">
-        <v>1.0</v>
+      <c r="I45" s="19">
+        <v>-1.0</v>
       </c>
       <c r="J45" s="20"/>
     </row>
@@ -3144,8 +3145,8 @@
       <c r="H62" s="34" t="s">
         <v>61</v>
       </c>
-      <c r="I62" s="18">
-        <v>0.0</v>
+      <c r="I62" s="19">
+        <v>-1.0</v>
       </c>
       <c r="J62" s="20"/>
     </row>
@@ -3172,8 +3173,8 @@
       <c r="H63" s="34" t="s">
         <v>61</v>
       </c>
-      <c r="I63" s="18">
-        <v>0.0</v>
+      <c r="I63" s="19">
+        <v>-1.0</v>
       </c>
       <c r="J63" s="20"/>
     </row>
@@ -3200,8 +3201,8 @@
       <c r="H64" s="34" t="s">
         <v>61</v>
       </c>
-      <c r="I64" s="18">
-        <v>0.0</v>
+      <c r="I64" s="19">
+        <v>-1.0</v>
       </c>
       <c r="J64" s="20"/>
     </row>
@@ -6374,7 +6375,7 @@
       </c>
       <c r="G4" s="1"/>
     </row>
-    <row r="5" ht="19.5" customHeight="1">
+    <row r="5">
       <c r="A5" s="4" t="s">
         <v>157</v>
       </c>

--- a/Assets/02Script/Table/EventTable.xlsx
+++ b/Assets/02Script/Table/EventTable.xlsx
@@ -2725,8 +2725,8 @@
       <c r="H47" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="I47" s="18">
-        <v>2.0</v>
+      <c r="I47" s="19">
+        <v>-1.0</v>
       </c>
       <c r="J47" s="20"/>
     </row>

--- a/Assets/02Script/Table/EventTable.xlsx
+++ b/Assets/02Script/Table/EventTable.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="482" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="491" uniqueCount="169">
   <si>
     <t>EventID</t>
   </si>
@@ -504,6 +504,33 @@
   </si>
   <si>
     <t>비슷한 풍선이겠지?</t>
+  </si>
+  <si>
+    <t>C005</t>
+  </si>
+  <si>
+    <t>사람??</t>
+  </si>
+  <si>
+    <t>어.. 고양이?</t>
+  </si>
+  <si>
+    <t>C006</t>
+  </si>
+  <si>
+    <t>음...13인가?</t>
+  </si>
+  <si>
+    <t>정답은 8이야.</t>
+  </si>
+  <si>
+    <t>C007</t>
+  </si>
+  <si>
+    <t>0...?</t>
+  </si>
+  <si>
+    <t>403,002,187,492??</t>
   </si>
 </sst>
 </file>
@@ -6392,6 +6419,57 @@
         <v>0.0</v>
       </c>
     </row>
+    <row r="6">
+      <c r="A6" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="E6" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="F6" s="4">
+        <v>-10.0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="E7" s="4">
+        <v>-10.0</v>
+      </c>
+      <c r="F7" s="4">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="E8" s="4">
+        <v>0.0</v>
+      </c>
+      <c r="F8" s="4">
+        <v>-10.0</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/Assets/02Script/Table/EventTable.xlsx
+++ b/Assets/02Script/Table/EventTable.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="539" uniqueCount="202">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="543" uniqueCount="206">
   <si>
     <t>EventID</t>
   </si>
@@ -255,7 +255,7 @@
   </si>
   <si>
     <t>그러니… 이 글을 읽는 네가 혹시라도 
-그 존재를 마주하게 된다면,</t>
+그 존재를 마주하게 된다면.</t>
   </si>
   <si>
     <t>무슨 일이 있어도 삶을 포기하지 마렴.</t>
@@ -571,7 +571,13 @@
     <t>Score2</t>
   </si>
   <si>
-    <t>Continue</t>
+    <t>Continue0</t>
+  </si>
+  <si>
+    <t>Continue1</t>
+  </si>
+  <si>
+    <t>Continue2</t>
   </si>
   <si>
     <t xml:space="preserve"> 당신은 엄마가 아니야.
@@ -590,6 +596,12 @@
   </si>
   <si>
     <t>내가 꿈을 꾸는 게 아닐까?</t>
+  </si>
+  <si>
+    <t>N001_0</t>
+  </si>
+  <si>
+    <t>N001_1</t>
   </si>
   <si>
     <t>C003</t>
@@ -6593,8 +6605,10 @@
   <cols>
     <col customWidth="1" min="2" max="2" width="27.25"/>
     <col customWidth="1" min="3" max="3" width="28.13"/>
-    <col customWidth="1" min="4" max="4" width="25.5"/>
-    <col customWidth="1" min="5" max="5" width="14.75"/>
+    <col customWidth="1" min="4" max="4" width="26.13"/>
+    <col customWidth="1" min="5" max="5" width="8.0"/>
+    <col customWidth="1" min="6" max="6" width="7.75"/>
+    <col customWidth="1" min="7" max="7" width="7.0"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6622,16 +6636,22 @@
       <c r="H1" s="3" t="s">
         <v>181</v>
       </c>
+      <c r="I1" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="J1" s="3" t="s">
+        <v>183</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="35" t="s">
         <v>123</v>
       </c>
       <c r="B2" s="36" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C2" s="36" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="D2" s="4"/>
       <c r="E2" s="3">
@@ -6643,13 +6663,13 @@
     </row>
     <row r="3">
       <c r="A3" s="37" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="B3" s="36" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C3" s="38" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="D3" s="4"/>
       <c r="E3" s="5">
@@ -6659,16 +6679,22 @@
         <v>-10.0</v>
       </c>
       <c r="G3" s="4"/>
+      <c r="H3" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>190</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="B4" s="39" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="C4" s="39" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="D4" s="4"/>
       <c r="E4" s="2">
@@ -6681,13 +6707,13 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="B5" s="40" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="C5" s="40" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="E5" s="3">
         <v>-10.0</v>
@@ -6698,13 +6724,13 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="E6" s="3">
         <v>0.0</v>
@@ -6715,13 +6741,13 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="E7" s="3">
         <v>-10.0</v>
@@ -6732,13 +6758,13 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="E8" s="3">
         <v>0.0</v>

--- a/Assets/02Script/Table/EventTable.xlsx
+++ b/Assets/02Script/Table/EventTable.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="543" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="681" uniqueCount="225">
   <si>
     <t>EventID</t>
   </si>
@@ -268,6 +268,9 @@
 너를 꿈속에서 나갈 수 있게 해줄거야.</t>
   </si>
   <si>
+    <t>EventDetailID</t>
+  </si>
+  <si>
     <t>LogID</t>
   </si>
   <si>
@@ -553,6 +556,51 @@
     <t>우선.. 이 열쇠가 맞는지 확인해 봐야겠다.</t>
   </si>
   <si>
+    <t>E020</t>
+  </si>
+  <si>
+    <t>임시입니다!!!!!</t>
+  </si>
+  <si>
+    <t>개발자</t>
+  </si>
+  <si>
+    <t>이벤트용 선택지 테스트 중입니다</t>
+  </si>
+  <si>
+    <t>멍멍멍멍아르르르르??</t>
+  </si>
+  <si>
+    <t>C008</t>
+  </si>
+  <si>
+    <t>E020_0</t>
+  </si>
+  <si>
+    <t>정답은 멍멍이였습니다~~~</t>
+  </si>
+  <si>
+    <t>짝짝짝짝짝</t>
+  </si>
+  <si>
+    <t>E020_1</t>
+  </si>
+  <si>
+    <t>겠냐?</t>
+  </si>
+  <si>
+    <t>ㅉㅉ</t>
+  </si>
+  <si>
+    <t>E020_2</t>
+  </si>
+  <si>
+    <t>좀만 더 힘내자...</t>
+  </si>
+  <si>
+    <t>얼마...안남았을걸?</t>
+  </si>
+  <si>
     <t>Choice0</t>
   </si>
   <si>
@@ -649,6 +697,15 @@
   </si>
   <si>
     <t>403,002,187,492??</t>
+  </si>
+  <si>
+    <t>정답! 강아지!!</t>
+  </si>
+  <si>
+    <t>음.. 고양이?</t>
+  </si>
+  <si>
+    <t>하....죽같다</t>
   </si>
 </sst>
 </file>
@@ -916,7 +973,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="C2:J73" displayName="Table_2" name="Table_2" id="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="D2:K73" displayName="Table_2" name="Table_2" id="2">
   <tableColumns count="8">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -932,7 +989,7 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="M19:R25" displayName="Table_3" name="Table_3" id="3">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="N19:S25" displayName="Table_3" name="Table_3" id="3">
   <tableColumns count="6">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -1625,15 +1682,15 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
   <cols>
-    <col customWidth="1" min="3" max="3" width="36.25"/>
-    <col customWidth="1" min="13" max="13" width="12.0"/>
+    <col customWidth="1" min="4" max="4" width="36.25"/>
+    <col customWidth="1" min="14" max="14" width="12.0"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="8" t="s">
         <v>81</v>
       </c>
       <c r="C1" s="1" t="s">
@@ -1656,2098 +1713,2320 @@
       </c>
       <c r="I1" s="1" t="s">
         <v>88</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>89</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="10">
+      <c r="B2" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="10">
         <v>2001.0</v>
       </c>
-      <c r="C2" s="11" t="s">
-        <v>89</v>
-      </c>
-      <c r="D2" s="12">
+      <c r="D2" s="11" t="s">
+        <v>90</v>
+      </c>
+      <c r="E2" s="12">
         <v>2002.0</v>
-      </c>
-      <c r="E2" s="11" t="s">
-        <v>90</v>
       </c>
       <c r="F2" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="G2" s="13"/>
-      <c r="H2" s="14" t="s">
+      <c r="G2" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="I2" s="14">
+      <c r="H2" s="13"/>
+      <c r="I2" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="J2" s="14">
         <v>-1.0</v>
       </c>
-      <c r="J2" s="15"/>
+      <c r="K2" s="15"/>
     </row>
     <row r="3">
       <c r="A3" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="10">
+      <c r="B3" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="10">
         <v>2002.0</v>
       </c>
-      <c r="C3" s="11" t="s">
-        <v>93</v>
-      </c>
-      <c r="D3" s="12">
+      <c r="D3" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="E3" s="12">
         <v>2003.0</v>
-      </c>
-      <c r="E3" s="11" t="s">
-        <v>90</v>
       </c>
       <c r="F3" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="G3" s="13"/>
-      <c r="H3" s="14" t="s">
+      <c r="G3" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="I3" s="14">
+      <c r="H3" s="13"/>
+      <c r="I3" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="J3" s="14">
         <v>-1.0</v>
       </c>
-      <c r="J3" s="15"/>
+      <c r="K3" s="15"/>
     </row>
     <row r="4">
       <c r="A4" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="10">
+      <c r="B4" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" s="10">
         <v>2003.0</v>
       </c>
-      <c r="C4" s="11" t="s">
-        <v>94</v>
-      </c>
-      <c r="D4" s="12">
+      <c r="D4" s="11" t="s">
+        <v>95</v>
+      </c>
+      <c r="E4" s="12">
         <v>2004.0</v>
-      </c>
-      <c r="E4" s="11" t="s">
-        <v>90</v>
       </c>
       <c r="F4" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="G4" s="13"/>
-      <c r="H4" s="14" t="s">
+      <c r="G4" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="I4" s="14">
+      <c r="H4" s="13"/>
+      <c r="I4" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="J4" s="14">
         <v>-1.0</v>
       </c>
-      <c r="J4" s="15"/>
+      <c r="K4" s="15"/>
     </row>
     <row r="5">
       <c r="A5" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="10">
+      <c r="B5" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="10">
         <v>2004.0</v>
       </c>
-      <c r="C5" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="D5" s="12">
+      <c r="D5" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="E5" s="12">
         <v>2005.0</v>
-      </c>
-      <c r="E5" s="11" t="s">
-        <v>96</v>
       </c>
       <c r="F5" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="G5" s="13"/>
-      <c r="H5" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="I5" s="14">
+      <c r="G5" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="H5" s="13"/>
+      <c r="I5" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="J5" s="14">
         <v>-1.0</v>
       </c>
-      <c r="J5" s="15"/>
+      <c r="K5" s="15"/>
     </row>
     <row r="6">
       <c r="A6" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="10">
+      <c r="B6" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="10">
         <v>2005.0</v>
       </c>
-      <c r="C6" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="D6" s="12">
+      <c r="D6" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="E6" s="12">
         <v>2006.0</v>
-      </c>
-      <c r="E6" s="11" t="s">
-        <v>90</v>
       </c>
       <c r="F6" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="G6" s="13"/>
-      <c r="H6" s="14" t="s">
+      <c r="G6" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="I6" s="14">
+      <c r="H6" s="13"/>
+      <c r="I6" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="J6" s="14">
         <v>-1.0</v>
       </c>
-      <c r="J6" s="15"/>
+      <c r="K6" s="15"/>
     </row>
     <row r="7">
       <c r="A7" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="10">
+      <c r="B7" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="10">
         <v>2006.0</v>
       </c>
-      <c r="C7" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="D7" s="12">
+      <c r="D7" s="11" t="s">
+        <v>96</v>
+      </c>
+      <c r="E7" s="12">
         <v>2007.0</v>
-      </c>
-      <c r="E7" s="11" t="s">
-        <v>96</v>
       </c>
       <c r="F7" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="G7" s="13"/>
-      <c r="H7" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="I7" s="14">
+      <c r="G7" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="H7" s="13"/>
+      <c r="I7" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="J7" s="14">
         <v>-1.0</v>
       </c>
-      <c r="J7" s="15"/>
+      <c r="K7" s="15"/>
     </row>
     <row r="8">
       <c r="A8" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="B8" s="10">
+      <c r="B8" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="10">
         <v>2007.0</v>
       </c>
-      <c r="C8" s="11" t="s">
-        <v>99</v>
-      </c>
-      <c r="D8" s="12">
+      <c r="D8" s="11" t="s">
+        <v>100</v>
+      </c>
+      <c r="E8" s="12">
         <v>2008.0</v>
-      </c>
-      <c r="E8" s="11" t="s">
-        <v>90</v>
       </c>
       <c r="F8" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="G8" s="13"/>
-      <c r="H8" s="14" t="s">
+      <c r="G8" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="I8" s="14">
+      <c r="H8" s="13"/>
+      <c r="I8" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="J8" s="14">
         <v>-1.0</v>
       </c>
-      <c r="J8" s="15"/>
+      <c r="K8" s="15"/>
     </row>
     <row r="9">
       <c r="A9" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="10">
+      <c r="B9" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="10">
         <v>2008.0</v>
       </c>
-      <c r="C9" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="D9" s="12">
+      <c r="D9" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="E9" s="12">
         <v>2009.0</v>
-      </c>
-      <c r="E9" s="11" t="s">
-        <v>96</v>
       </c>
       <c r="F9" s="11" t="s">
         <v>97</v>
       </c>
-      <c r="G9" s="13"/>
-      <c r="H9" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="I9" s="14">
+      <c r="G9" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="H9" s="13"/>
+      <c r="I9" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="J9" s="14">
         <v>-1.0</v>
       </c>
-      <c r="J9" s="15"/>
+      <c r="K9" s="15"/>
     </row>
     <row r="10">
       <c r="A10" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="B10" s="10">
+      <c r="B10" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C10" s="10">
         <v>2009.0</v>
       </c>
-      <c r="C10" s="11" t="s">
-        <v>101</v>
-      </c>
-      <c r="D10" s="12">
+      <c r="D10" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="E10" s="12">
         <v>2010.0</v>
-      </c>
-      <c r="E10" s="11" t="s">
-        <v>90</v>
       </c>
       <c r="F10" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="G10" s="13"/>
-      <c r="H10" s="14" t="s">
+      <c r="G10" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="I10" s="14">
+      <c r="H10" s="13"/>
+      <c r="I10" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="J10" s="14">
         <v>-1.0</v>
       </c>
-      <c r="J10" s="15"/>
+      <c r="K10" s="15"/>
     </row>
     <row r="11">
       <c r="A11" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="B11" s="10">
+      <c r="B11" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="10">
         <v>2010.0</v>
       </c>
-      <c r="C11" s="11" t="s">
-        <v>102</v>
-      </c>
-      <c r="D11" s="12">
+      <c r="D11" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="E11" s="12">
         <v>2011.0</v>
       </c>
-      <c r="E11" s="11" t="s">
-        <v>96</v>
-      </c>
       <c r="F11" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="G11" s="13"/>
-      <c r="H11" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="I11" s="14">
+        <v>97</v>
+      </c>
+      <c r="G11" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="H11" s="13"/>
+      <c r="I11" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="J11" s="14">
         <v>-1.0</v>
       </c>
-      <c r="J11" s="15"/>
+      <c r="K11" s="15"/>
     </row>
     <row r="12">
       <c r="A12" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="B12" s="10">
+      <c r="B12" s="9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="10">
         <v>2011.0</v>
       </c>
-      <c r="C12" s="11" t="s">
-        <v>104</v>
-      </c>
-      <c r="D12" s="12">
+      <c r="D12" s="11" t="s">
+        <v>105</v>
+      </c>
+      <c r="E12" s="12">
         <v>-1.0</v>
-      </c>
-      <c r="E12" s="11" t="s">
-        <v>90</v>
       </c>
       <c r="F12" s="11" t="s">
         <v>91</v>
       </c>
-      <c r="G12" s="13"/>
-      <c r="H12" s="14" t="s">
+      <c r="G12" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="I12" s="14">
+      <c r="H12" s="13"/>
+      <c r="I12" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="J12" s="14">
         <v>-1.0</v>
       </c>
-      <c r="J12" s="15"/>
+      <c r="K12" s="15"/>
     </row>
     <row r="13">
       <c r="A13" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="2">
+      <c r="B13" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C13" s="2">
         <v>3001.0</v>
       </c>
-      <c r="C13" s="14" t="s">
-        <v>105</v>
-      </c>
-      <c r="D13" s="16">
+      <c r="D13" s="14" t="s">
+        <v>106</v>
+      </c>
+      <c r="E13" s="16">
         <v>3002.0</v>
       </c>
-      <c r="E13" s="14" t="s">
-        <v>90</v>
-      </c>
-      <c r="F13" s="11" t="s">
+      <c r="F13" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="G13" s="13"/>
-      <c r="H13" s="14" t="s">
+      <c r="G13" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="I13" s="16">
+      <c r="H13" s="13"/>
+      <c r="I13" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="J13" s="16">
         <v>4.0</v>
       </c>
-      <c r="J13" s="17"/>
+      <c r="K13" s="17"/>
     </row>
     <row r="14">
       <c r="A14" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B14" s="2">
+      <c r="B14" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C14" s="2">
         <v>3002.0</v>
       </c>
-      <c r="C14" s="14" t="s">
-        <v>106</v>
-      </c>
-      <c r="D14" s="16">
+      <c r="D14" s="14" t="s">
+        <v>107</v>
+      </c>
+      <c r="E14" s="16">
         <v>3003.0</v>
       </c>
-      <c r="E14" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="F14" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="G14" s="13"/>
-      <c r="H14" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="I14" s="16">
+      <c r="F14" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="G14" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="H14" s="13"/>
+      <c r="I14" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="J14" s="16">
         <v>0.0</v>
       </c>
-      <c r="J14" s="18"/>
+      <c r="K14" s="18"/>
     </row>
     <row r="15">
       <c r="A15" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B15" s="2">
+      <c r="B15" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C15" s="2">
         <v>3003.0</v>
       </c>
-      <c r="C15" s="14" t="s">
-        <v>108</v>
-      </c>
-      <c r="D15" s="16">
+      <c r="D15" s="14" t="s">
+        <v>109</v>
+      </c>
+      <c r="E15" s="16">
         <v>3004.0</v>
       </c>
-      <c r="E15" s="14" t="s">
-        <v>90</v>
-      </c>
-      <c r="F15" s="11" t="s">
+      <c r="F15" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="G15" s="13"/>
-      <c r="H15" s="14" t="s">
+      <c r="G15" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="I15" s="16">
+      <c r="H15" s="13"/>
+      <c r="I15" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="J15" s="16">
         <v>2.0</v>
       </c>
-      <c r="J15" s="17"/>
+      <c r="K15" s="17"/>
     </row>
     <row r="16">
       <c r="A16" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B16" s="2">
+      <c r="B16" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C16" s="2">
         <v>3004.0</v>
       </c>
-      <c r="C16" s="14" t="s">
-        <v>109</v>
-      </c>
-      <c r="D16" s="16">
+      <c r="D16" s="14" t="s">
+        <v>110</v>
+      </c>
+      <c r="E16" s="16">
         <v>3005.0</v>
       </c>
-      <c r="E16" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="F16" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="G16" s="13"/>
-      <c r="H16" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="I16" s="16">
+      <c r="F16" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="G16" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="H16" s="13"/>
+      <c r="I16" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="J16" s="16">
         <v>0.0</v>
       </c>
-      <c r="J16" s="18"/>
+      <c r="K16" s="18"/>
     </row>
     <row r="17">
       <c r="A17" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B17" s="2">
+      <c r="B17" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C17" s="2">
         <v>3005.0</v>
       </c>
-      <c r="C17" s="14" t="s">
-        <v>110</v>
-      </c>
-      <c r="D17" s="16">
+      <c r="D17" s="14" t="s">
+        <v>111</v>
+      </c>
+      <c r="E17" s="16">
         <v>3006.0</v>
       </c>
-      <c r="E17" s="14" t="s">
-        <v>90</v>
-      </c>
-      <c r="F17" s="11" t="s">
+      <c r="F17" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="G17" s="13"/>
-      <c r="H17" s="14" t="s">
+      <c r="G17" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="I17" s="16">
+      <c r="H17" s="13"/>
+      <c r="I17" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="J17" s="16">
         <v>2.0</v>
       </c>
-      <c r="J17" s="19"/>
+      <c r="K17" s="19"/>
     </row>
     <row r="18">
       <c r="A18" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B18" s="2">
+      <c r="B18" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C18" s="2">
         <v>3006.0</v>
       </c>
-      <c r="C18" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="D18" s="16">
+      <c r="D18" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="E18" s="16">
         <v>3007.0</v>
       </c>
-      <c r="E18" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="F18" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="G18" s="13"/>
-      <c r="H18" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="I18" s="16">
+      <c r="F18" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="G18" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="H18" s="13"/>
+      <c r="I18" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="J18" s="16">
         <v>0.0</v>
       </c>
-      <c r="J18" s="18"/>
+      <c r="K18" s="18"/>
     </row>
     <row r="19">
       <c r="A19" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B19" s="2">
+      <c r="B19" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C19" s="2">
         <v>3007.0</v>
       </c>
-      <c r="C19" s="14" t="s">
-        <v>112</v>
-      </c>
-      <c r="D19" s="16">
+      <c r="D19" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="E19" s="16">
         <v>3008.0</v>
       </c>
-      <c r="E19" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="F19" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="G19" s="13"/>
-      <c r="H19" s="14" t="s">
-        <v>92</v>
-      </c>
-      <c r="I19" s="16">
+      <c r="F19" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="G19" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="H19" s="13"/>
+      <c r="I19" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="J19" s="16">
         <v>1.0</v>
       </c>
-      <c r="J19" s="17"/>
-      <c r="K19" s="2"/>
-      <c r="L19" s="5"/>
-      <c r="M19" s="13"/>
-      <c r="N19" s="20"/>
-      <c r="O19" s="13"/>
-      <c r="P19" s="21"/>
-      <c r="Q19" s="13"/>
-      <c r="R19" s="20"/>
+      <c r="K19" s="17"/>
+      <c r="L19" s="2"/>
+      <c r="M19" s="5"/>
+      <c r="N19" s="13"/>
+      <c r="O19" s="20"/>
+      <c r="P19" s="13"/>
+      <c r="Q19" s="21"/>
+      <c r="R19" s="13"/>
+      <c r="S19" s="20"/>
     </row>
     <row r="20">
       <c r="A20" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B20" s="2">
+      <c r="B20" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C20" s="2">
         <v>3008.0</v>
       </c>
-      <c r="C20" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="D20" s="16">
+      <c r="D20" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="E20" s="16">
         <v>3009.0</v>
       </c>
-      <c r="E20" s="14" t="s">
-        <v>90</v>
-      </c>
-      <c r="F20" s="11" t="s">
+      <c r="F20" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="G20" s="13"/>
-      <c r="H20" s="14" t="s">
+      <c r="G20" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="I20" s="16">
+      <c r="H20" s="13"/>
+      <c r="I20" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="J20" s="16">
         <v>2.0</v>
       </c>
-      <c r="J20" s="18"/>
-      <c r="K20" s="2"/>
-      <c r="L20" s="5"/>
-      <c r="M20" s="22"/>
-      <c r="N20" s="23"/>
-      <c r="O20" s="24"/>
-      <c r="P20" s="25"/>
-      <c r="Q20" s="24"/>
-      <c r="R20" s="23"/>
+      <c r="K20" s="18"/>
+      <c r="L20" s="2"/>
+      <c r="M20" s="5"/>
+      <c r="N20" s="22"/>
+      <c r="O20" s="23"/>
+      <c r="P20" s="24"/>
+      <c r="Q20" s="25"/>
+      <c r="R20" s="24"/>
+      <c r="S20" s="23"/>
     </row>
     <row r="21">
       <c r="A21" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B21" s="2">
+      <c r="B21" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C21" s="2">
         <v>3009.0</v>
       </c>
-      <c r="C21" s="14" t="s">
-        <v>114</v>
-      </c>
-      <c r="D21" s="16">
+      <c r="D21" s="14" t="s">
+        <v>115</v>
+      </c>
+      <c r="E21" s="16">
         <v>3010.0</v>
       </c>
-      <c r="E21" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="F21" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="G21" s="13"/>
-      <c r="H21" s="14" t="s">
-        <v>115</v>
-      </c>
-      <c r="I21" s="16">
+      <c r="F21" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="G21" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="H21" s="13"/>
+      <c r="I21" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="J21" s="16">
         <v>1.0</v>
       </c>
-      <c r="J21" s="26"/>
-      <c r="K21" s="2"/>
-      <c r="L21" s="5"/>
-      <c r="M21" s="24"/>
-      <c r="N21" s="23"/>
-      <c r="O21" s="24"/>
-      <c r="P21" s="27"/>
-      <c r="Q21" s="24"/>
-      <c r="R21" s="23"/>
+      <c r="K21" s="26"/>
+      <c r="L21" s="2"/>
+      <c r="M21" s="5"/>
+      <c r="N21" s="24"/>
+      <c r="O21" s="23"/>
+      <c r="P21" s="24"/>
+      <c r="Q21" s="27"/>
+      <c r="R21" s="24"/>
+      <c r="S21" s="23"/>
     </row>
     <row r="22">
       <c r="A22" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B22" s="2">
+      <c r="B22" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C22" s="2">
         <v>3010.0</v>
       </c>
-      <c r="C22" s="14" t="s">
-        <v>116</v>
-      </c>
-      <c r="D22" s="16">
+      <c r="D22" s="14" t="s">
+        <v>117</v>
+      </c>
+      <c r="E22" s="16">
         <v>3011.0</v>
       </c>
-      <c r="E22" s="14" t="s">
-        <v>90</v>
-      </c>
-      <c r="F22" s="11" t="s">
+      <c r="F22" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="G22" s="13"/>
-      <c r="H22" s="14" t="s">
+      <c r="G22" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="I22" s="16">
+      <c r="H22" s="13"/>
+      <c r="I22" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="J22" s="16">
         <v>2.0</v>
       </c>
-      <c r="J22" s="28"/>
-      <c r="K22" s="2"/>
-      <c r="L22" s="5"/>
-      <c r="M22" s="24"/>
-      <c r="N22" s="23"/>
-      <c r="O22" s="24"/>
-      <c r="P22" s="27"/>
-      <c r="Q22" s="24"/>
-      <c r="R22" s="23"/>
+      <c r="K22" s="28"/>
+      <c r="L22" s="2"/>
+      <c r="M22" s="5"/>
+      <c r="N22" s="24"/>
+      <c r="O22" s="23"/>
+      <c r="P22" s="24"/>
+      <c r="Q22" s="27"/>
+      <c r="R22" s="24"/>
+      <c r="S22" s="23"/>
     </row>
     <row r="23">
       <c r="A23" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B23" s="2">
+      <c r="B23" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C23" s="2">
         <v>3011.0</v>
       </c>
-      <c r="C23" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="D23" s="16">
+      <c r="D23" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="E23" s="16">
         <v>3012.0</v>
       </c>
-      <c r="E23" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="F23" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="G23" s="13"/>
-      <c r="H23" s="14" t="s">
-        <v>115</v>
-      </c>
-      <c r="I23" s="16">
+      <c r="F23" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="G23" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="H23" s="13"/>
+      <c r="I23" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="J23" s="16">
         <v>1.0</v>
       </c>
-      <c r="J23" s="17"/>
-      <c r="K23" s="2"/>
-      <c r="L23" s="5"/>
-      <c r="M23" s="24"/>
-      <c r="N23" s="23"/>
-      <c r="O23" s="24"/>
-      <c r="P23" s="25"/>
-      <c r="Q23" s="24"/>
-      <c r="R23" s="23"/>
+      <c r="K23" s="17"/>
+      <c r="L23" s="2"/>
+      <c r="M23" s="5"/>
+      <c r="N23" s="24"/>
+      <c r="O23" s="23"/>
+      <c r="P23" s="24"/>
+      <c r="Q23" s="25"/>
+      <c r="R23" s="24"/>
+      <c r="S23" s="23"/>
     </row>
     <row r="24">
       <c r="A24" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B24" s="2">
+      <c r="B24" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C24" s="2">
         <v>3012.0</v>
       </c>
-      <c r="C24" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="D24" s="16">
+      <c r="D24" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="E24" s="16">
         <v>3013.0</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>90</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="H24" s="14" t="s">
+      <c r="G24" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="I24" s="3">
+      <c r="I24" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="J24" s="3">
         <v>2.0</v>
       </c>
-      <c r="J24" s="29"/>
-      <c r="K24" s="2"/>
-      <c r="L24" s="5"/>
-      <c r="M24" s="24"/>
-      <c r="N24" s="23"/>
-      <c r="O24" s="24"/>
-      <c r="P24" s="27"/>
-      <c r="Q24" s="24"/>
-      <c r="R24" s="23"/>
+      <c r="K24" s="29"/>
+      <c r="L24" s="2"/>
+      <c r="M24" s="5"/>
+      <c r="N24" s="24"/>
+      <c r="O24" s="23"/>
+      <c r="P24" s="24"/>
+      <c r="Q24" s="27"/>
+      <c r="R24" s="24"/>
+      <c r="S24" s="23"/>
     </row>
     <row r="25">
       <c r="A25" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B25" s="2">
+      <c r="B25" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C25" s="2">
         <v>3013.0</v>
       </c>
-      <c r="C25" s="14" t="s">
-        <v>118</v>
-      </c>
-      <c r="D25" s="16">
+      <c r="D25" s="14" t="s">
+        <v>119</v>
+      </c>
+      <c r="E25" s="16">
         <v>3014.0</v>
       </c>
-      <c r="E25" s="3" t="s">
-        <v>107</v>
-      </c>
       <c r="F25" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="H25" s="14" t="s">
-        <v>115</v>
-      </c>
-      <c r="I25" s="3">
+        <v>108</v>
+      </c>
+      <c r="G25" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="I25" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="J25" s="3">
         <v>2.0</v>
       </c>
-      <c r="J25" s="29"/>
-      <c r="K25" s="2"/>
-      <c r="L25" s="5"/>
-      <c r="M25" s="13"/>
-      <c r="N25" s="30"/>
-      <c r="O25" s="13"/>
-      <c r="P25" s="21"/>
-      <c r="Q25" s="13"/>
-      <c r="R25" s="20"/>
+      <c r="K25" s="29"/>
+      <c r="L25" s="2"/>
+      <c r="M25" s="5"/>
+      <c r="N25" s="13"/>
+      <c r="O25" s="30"/>
+      <c r="P25" s="13"/>
+      <c r="Q25" s="21"/>
+      <c r="R25" s="13"/>
+      <c r="S25" s="20"/>
     </row>
     <row r="26">
       <c r="A26" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B26" s="2">
+      <c r="B26" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C26" s="2">
         <v>3014.0</v>
       </c>
-      <c r="C26" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="D26" s="16">
+      <c r="D26" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="E26" s="16">
         <v>3015.0</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>90</v>
       </c>
       <c r="F26" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="H26" s="14" t="s">
+      <c r="G26" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="I26" s="3">
+      <c r="I26" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="J26" s="3">
         <v>2.0</v>
       </c>
-      <c r="J26" s="29"/>
+      <c r="K26" s="29"/>
     </row>
     <row r="27">
       <c r="A27" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B27" s="2">
+      <c r="B27" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C27" s="2">
         <v>3015.0</v>
       </c>
-      <c r="C27" s="14" t="s">
-        <v>120</v>
-      </c>
-      <c r="D27" s="16">
+      <c r="D27" s="14" t="s">
+        <v>121</v>
+      </c>
+      <c r="E27" s="16">
         <v>3016.0</v>
       </c>
-      <c r="E27" s="14" t="s">
-        <v>90</v>
-      </c>
-      <c r="F27" s="11" t="s">
+      <c r="F27" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="G27" s="13"/>
-      <c r="H27" s="16" t="s">
-        <v>121</v>
-      </c>
-      <c r="I27" s="16">
+      <c r="G27" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="H27" s="13"/>
+      <c r="I27" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="J27" s="16">
         <v>0.0</v>
       </c>
-      <c r="J27" s="28"/>
+      <c r="K27" s="28"/>
     </row>
     <row r="28">
       <c r="A28" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="B28" s="2">
+      <c r="B28" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C28" s="2">
         <v>3016.0</v>
       </c>
-      <c r="C28" s="14" t="s">
+      <c r="D28" s="14" t="s">
+        <v>123</v>
+      </c>
+      <c r="E28" s="12">
+        <v>-1.0</v>
+      </c>
+      <c r="F28" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="G28" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="H28" s="14" t="s">
+        <v>124</v>
+      </c>
+      <c r="I28" s="16" t="s">
         <v>122</v>
       </c>
-      <c r="D28" s="12">
-        <v>-1.0</v>
-      </c>
-      <c r="E28" s="14" t="s">
-        <v>90</v>
-      </c>
-      <c r="F28" s="11" t="s">
-        <v>91</v>
-      </c>
-      <c r="G28" s="14" t="s">
-        <v>123</v>
-      </c>
-      <c r="H28" s="16" t="s">
-        <v>121</v>
-      </c>
-      <c r="I28" s="16">
+      <c r="J28" s="16">
         <v>0.0</v>
       </c>
-      <c r="J28" s="19"/>
+      <c r="K28" s="19"/>
     </row>
     <row r="29">
       <c r="A29" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="B29" s="3">
+      <c r="B29" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C29" s="3">
         <v>4001.0</v>
       </c>
-      <c r="C29" s="14" t="s">
-        <v>124</v>
-      </c>
-      <c r="D29" s="12">
+      <c r="D29" s="14" t="s">
+        <v>125</v>
+      </c>
+      <c r="E29" s="12">
         <v>4002.0</v>
       </c>
-      <c r="E29" s="14" t="s">
-        <v>90</v>
-      </c>
-      <c r="F29" s="21"/>
-      <c r="G29" s="13"/>
-      <c r="H29" s="16" t="s">
-        <v>121</v>
-      </c>
-      <c r="I29" s="16">
+      <c r="F29" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="G29" s="21"/>
+      <c r="H29" s="13"/>
+      <c r="I29" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="J29" s="16">
         <v>-1.0</v>
       </c>
-      <c r="J29" s="17"/>
+      <c r="K29" s="17"/>
     </row>
     <row r="30">
       <c r="A30" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="B30" s="3">
+      <c r="B30" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C30" s="3">
         <v>4002.0</v>
       </c>
-      <c r="C30" s="14" t="s">
-        <v>125</v>
-      </c>
-      <c r="D30" s="12">
+      <c r="D30" s="14" t="s">
+        <v>126</v>
+      </c>
+      <c r="E30" s="12">
         <v>-1.0</v>
       </c>
-      <c r="E30" s="14" t="s">
-        <v>90</v>
-      </c>
-      <c r="F30" s="21"/>
-      <c r="G30" s="13"/>
-      <c r="H30" s="16" t="s">
-        <v>121</v>
-      </c>
-      <c r="I30" s="16">
+      <c r="F30" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="G30" s="21"/>
+      <c r="H30" s="13"/>
+      <c r="I30" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="J30" s="16">
         <v>-1.0</v>
       </c>
-      <c r="J30" s="17"/>
+      <c r="K30" s="17"/>
     </row>
     <row r="31">
       <c r="A31" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="B31" s="3">
+      <c r="B31" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C31" s="3">
         <v>5001.0</v>
       </c>
-      <c r="C31" s="14" t="s">
-        <v>126</v>
-      </c>
-      <c r="D31" s="3">
+      <c r="D31" s="14" t="s">
+        <v>127</v>
+      </c>
+      <c r="E31" s="3">
         <v>5002.0</v>
       </c>
-      <c r="E31" s="14" t="s">
-        <v>90</v>
-      </c>
-      <c r="F31" s="11" t="s">
+      <c r="F31" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="G31" s="13"/>
-      <c r="H31" s="14" t="s">
+      <c r="G31" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="I31" s="16">
+      <c r="H31" s="13"/>
+      <c r="I31" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="J31" s="16">
         <v>2.0</v>
       </c>
-      <c r="J31" s="17"/>
+      <c r="K31" s="17"/>
     </row>
     <row r="32">
       <c r="A32" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="B32" s="3">
+      <c r="B32" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C32" s="3">
         <v>5002.0</v>
       </c>
-      <c r="C32" s="14" t="s">
-        <v>127</v>
-      </c>
-      <c r="D32" s="3">
+      <c r="D32" s="14" t="s">
+        <v>128</v>
+      </c>
+      <c r="E32" s="3">
         <v>5003.0</v>
       </c>
-      <c r="E32" s="14" t="s">
-        <v>90</v>
-      </c>
-      <c r="F32" s="11" t="s">
+      <c r="F32" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="G32" s="13"/>
-      <c r="H32" s="14" t="s">
+      <c r="G32" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="I32" s="16">
+      <c r="H32" s="13"/>
+      <c r="I32" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="J32" s="16">
         <v>2.0</v>
       </c>
-      <c r="J32" s="17"/>
+      <c r="K32" s="17"/>
     </row>
     <row r="33">
       <c r="A33" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="B33" s="3">
+      <c r="B33" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C33" s="3">
         <v>5003.0</v>
       </c>
-      <c r="C33" s="14" t="s">
-        <v>89</v>
-      </c>
-      <c r="D33" s="3">
+      <c r="D33" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="E33" s="3">
         <v>5004.0</v>
       </c>
-      <c r="E33" s="14" t="s">
-        <v>90</v>
-      </c>
-      <c r="F33" s="11" t="s">
+      <c r="F33" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="G33" s="13"/>
-      <c r="H33" s="14" t="s">
+      <c r="G33" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="I33" s="16">
+      <c r="H33" s="13"/>
+      <c r="I33" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="J33" s="16">
         <v>0.0</v>
       </c>
-      <c r="J33" s="17"/>
+      <c r="K33" s="17"/>
     </row>
     <row r="34">
       <c r="A34" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="B34" s="3">
+      <c r="B34" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C34" s="3">
         <v>5004.0</v>
       </c>
-      <c r="C34" s="14" t="s">
-        <v>128</v>
-      </c>
-      <c r="D34" s="3">
+      <c r="D34" s="14" t="s">
+        <v>129</v>
+      </c>
+      <c r="E34" s="3">
         <v>5005.0</v>
       </c>
-      <c r="E34" s="14" t="s">
-        <v>90</v>
-      </c>
-      <c r="F34" s="11" t="s">
+      <c r="F34" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="G34" s="13"/>
-      <c r="H34" s="14" t="s">
+      <c r="G34" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="I34" s="16">
+      <c r="H34" s="13"/>
+      <c r="I34" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="J34" s="16">
         <v>0.0</v>
       </c>
-      <c r="J34" s="17"/>
+      <c r="K34" s="17"/>
     </row>
     <row r="35">
       <c r="A35" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="B35" s="3">
+      <c r="B35" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C35" s="3">
         <v>5005.0</v>
       </c>
-      <c r="C35" s="14" t="s">
-        <v>129</v>
-      </c>
-      <c r="D35" s="3">
+      <c r="D35" s="14" t="s">
+        <v>130</v>
+      </c>
+      <c r="E35" s="3">
         <v>5006.0</v>
       </c>
-      <c r="E35" s="14" t="s">
-        <v>90</v>
-      </c>
-      <c r="F35" s="11" t="s">
+      <c r="F35" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="G35" s="13"/>
-      <c r="H35" s="14" t="s">
+      <c r="G35" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="I35" s="16">
+      <c r="H35" s="13"/>
+      <c r="I35" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="J35" s="16">
         <v>0.0</v>
       </c>
-      <c r="J35" s="17"/>
+      <c r="K35" s="17"/>
     </row>
     <row r="36">
       <c r="A36" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="B36" s="3">
+      <c r="B36" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="C36" s="3">
         <v>5006.0</v>
       </c>
-      <c r="C36" s="14" t="s">
-        <v>130</v>
-      </c>
-      <c r="D36" s="12">
+      <c r="D36" s="14" t="s">
+        <v>131</v>
+      </c>
+      <c r="E36" s="12">
         <v>-1.0</v>
       </c>
-      <c r="E36" s="14" t="s">
-        <v>90</v>
-      </c>
-      <c r="F36" s="11" t="s">
+      <c r="F36" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="G36" s="13"/>
-      <c r="H36" s="16" t="s">
-        <v>121</v>
-      </c>
-      <c r="I36" s="16">
+      <c r="G36" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="H36" s="13"/>
+      <c r="I36" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="J36" s="16">
         <v>0.0</v>
       </c>
-      <c r="J36" s="17"/>
+      <c r="K36" s="17"/>
     </row>
     <row r="37">
       <c r="A37" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="B37" s="2">
+      <c r="B37" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C37" s="2">
         <v>6001.0</v>
       </c>
-      <c r="C37" s="14" t="s">
-        <v>131</v>
-      </c>
-      <c r="D37" s="16">
+      <c r="D37" s="14" t="s">
+        <v>132</v>
+      </c>
+      <c r="E37" s="16">
         <v>6002.0</v>
       </c>
-      <c r="E37" s="14" t="s">
-        <v>132</v>
-      </c>
-      <c r="F37" s="11" t="s">
-        <v>97</v>
-      </c>
-      <c r="G37" s="13"/>
-      <c r="H37" s="16" t="s">
-        <v>121</v>
-      </c>
-      <c r="I37" s="16">
+      <c r="F37" s="14" t="s">
+        <v>133</v>
+      </c>
+      <c r="G37" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="H37" s="13"/>
+      <c r="I37" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="J37" s="16">
         <v>-1.0</v>
       </c>
-      <c r="J37" s="17"/>
+      <c r="K37" s="17"/>
     </row>
     <row r="38">
       <c r="A38" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="B38" s="2">
+      <c r="B38" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C38" s="2">
         <v>6002.0</v>
       </c>
-      <c r="C38" s="14" t="s">
-        <v>133</v>
-      </c>
-      <c r="D38" s="16">
+      <c r="D38" s="14" t="s">
+        <v>134</v>
+      </c>
+      <c r="E38" s="16">
         <v>6003.0</v>
       </c>
-      <c r="E38" s="14" t="s">
-        <v>90</v>
-      </c>
-      <c r="F38" s="11" t="s">
+      <c r="F38" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="G38" s="13"/>
-      <c r="H38" s="14" t="s">
+      <c r="G38" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="I38" s="16">
+      <c r="H38" s="13"/>
+      <c r="I38" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="J38" s="16">
         <v>0.0</v>
       </c>
-      <c r="J38" s="17"/>
+      <c r="K38" s="17"/>
     </row>
     <row r="39">
       <c r="A39" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="B39" s="2">
+      <c r="B39" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C39" s="2">
         <v>6003.0</v>
       </c>
-      <c r="C39" s="14" t="s">
-        <v>134</v>
-      </c>
-      <c r="D39" s="16">
+      <c r="D39" s="14" t="s">
+        <v>135</v>
+      </c>
+      <c r="E39" s="16">
         <v>6004.0</v>
       </c>
-      <c r="E39" s="14" t="s">
-        <v>132</v>
-      </c>
-      <c r="F39" s="11" t="s">
-        <v>97</v>
-      </c>
-      <c r="G39" s="13"/>
-      <c r="H39" s="16" t="s">
-        <v>121</v>
-      </c>
-      <c r="I39" s="16">
+      <c r="F39" s="14" t="s">
+        <v>133</v>
+      </c>
+      <c r="G39" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="H39" s="13"/>
+      <c r="I39" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="J39" s="16">
         <v>-1.0</v>
       </c>
-      <c r="J39" s="17"/>
+      <c r="K39" s="17"/>
     </row>
     <row r="40">
       <c r="A40" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="B40" s="2">
+      <c r="B40" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C40" s="2">
         <v>6004.0</v>
       </c>
-      <c r="C40" s="14" t="s">
-        <v>135</v>
-      </c>
-      <c r="D40" s="16">
+      <c r="D40" s="14" t="s">
+        <v>136</v>
+      </c>
+      <c r="E40" s="16">
         <v>6005.0</v>
       </c>
-      <c r="E40" s="14" t="s">
-        <v>90</v>
-      </c>
-      <c r="F40" s="11" t="s">
+      <c r="F40" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="G40" s="13"/>
-      <c r="H40" s="14" t="s">
+      <c r="G40" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="I40" s="16">
+      <c r="H40" s="13"/>
+      <c r="I40" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="J40" s="16">
         <v>0.0</v>
       </c>
-      <c r="J40" s="17"/>
+      <c r="K40" s="17"/>
     </row>
     <row r="41">
       <c r="A41" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="B41" s="2">
+      <c r="B41" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="C41" s="2">
         <v>6005.0</v>
       </c>
-      <c r="C41" s="14" t="s">
-        <v>136</v>
-      </c>
-      <c r="D41" s="16">
+      <c r="D41" s="14" t="s">
+        <v>137</v>
+      </c>
+      <c r="E41" s="16">
         <v>-1.0</v>
       </c>
-      <c r="E41" s="14" t="s">
-        <v>90</v>
-      </c>
-      <c r="F41" s="11" t="s">
+      <c r="F41" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="G41" s="13"/>
-      <c r="H41" s="14" t="s">
+      <c r="G41" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="I41" s="16">
+      <c r="H41" s="13"/>
+      <c r="I41" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="J41" s="16">
         <v>0.0</v>
       </c>
-      <c r="J41" s="17"/>
+      <c r="K41" s="17"/>
     </row>
     <row r="42">
       <c r="A42" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="B42" s="2">
+      <c r="B42" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="C42" s="2">
         <v>7001.0</v>
       </c>
-      <c r="C42" s="14" t="s">
-        <v>137</v>
-      </c>
-      <c r="D42" s="16">
+      <c r="D42" s="14" t="s">
+        <v>138</v>
+      </c>
+      <c r="E42" s="16">
         <v>-1.0</v>
       </c>
-      <c r="E42" s="14" t="s">
-        <v>90</v>
-      </c>
-      <c r="F42" s="11" t="s">
+      <c r="F42" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="G42" s="13"/>
-      <c r="H42" s="14" t="s">
+      <c r="G42" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="I42" s="16">
+      <c r="H42" s="13"/>
+      <c r="I42" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="J42" s="16">
         <v>-1.0</v>
       </c>
-      <c r="J42" s="17"/>
+      <c r="K42" s="17"/>
     </row>
     <row r="43">
       <c r="A43" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="B43" s="2">
+      <c r="B43" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="C43" s="2">
         <v>8001.0</v>
       </c>
-      <c r="C43" s="14" t="s">
-        <v>138</v>
-      </c>
-      <c r="D43" s="16">
+      <c r="D43" s="14" t="s">
+        <v>139</v>
+      </c>
+      <c r="E43" s="16">
         <v>8002.0</v>
       </c>
-      <c r="E43" s="14" t="s">
-        <v>90</v>
-      </c>
-      <c r="F43" s="11" t="s">
+      <c r="F43" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="G43" s="13"/>
-      <c r="H43" s="14" t="s">
+      <c r="G43" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="I43" s="16">
+      <c r="H43" s="13"/>
+      <c r="I43" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="J43" s="16">
         <v>-1.0</v>
       </c>
-      <c r="J43" s="17"/>
+      <c r="K43" s="17"/>
     </row>
     <row r="44">
       <c r="A44" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="B44" s="2">
+      <c r="B44" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="C44" s="2">
         <v>8002.0</v>
       </c>
-      <c r="C44" s="14" t="s">
-        <v>139</v>
-      </c>
-      <c r="D44" s="16">
+      <c r="D44" s="14" t="s">
+        <v>140</v>
+      </c>
+      <c r="E44" s="16">
         <v>8003.0</v>
       </c>
-      <c r="E44" s="14" t="s">
-        <v>90</v>
-      </c>
-      <c r="F44" s="11" t="s">
+      <c r="F44" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="G44" s="13"/>
-      <c r="H44" s="14" t="s">
+      <c r="G44" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="I44" s="16">
+      <c r="H44" s="13"/>
+      <c r="I44" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="J44" s="16">
         <v>-1.0</v>
       </c>
-      <c r="J44" s="17"/>
+      <c r="K44" s="17"/>
     </row>
     <row r="45">
       <c r="A45" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="B45" s="2">
+      <c r="B45" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="C45" s="2">
         <v>8003.0</v>
       </c>
-      <c r="C45" s="14" t="s">
-        <v>140</v>
-      </c>
-      <c r="D45" s="16">
+      <c r="D45" s="14" t="s">
+        <v>141</v>
+      </c>
+      <c r="E45" s="16">
         <v>8004.0</v>
       </c>
-      <c r="E45" s="14" t="s">
-        <v>90</v>
-      </c>
-      <c r="F45" s="11" t="s">
+      <c r="F45" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="G45" s="13"/>
-      <c r="H45" s="14" t="s">
+      <c r="G45" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="I45" s="16">
+      <c r="H45" s="13"/>
+      <c r="I45" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="J45" s="16">
         <v>-1.0</v>
       </c>
-      <c r="J45" s="17"/>
+      <c r="K45" s="17"/>
     </row>
     <row r="46">
       <c r="A46" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="B46" s="2">
+      <c r="B46" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="C46" s="2">
         <v>8004.0</v>
       </c>
-      <c r="C46" s="14" t="s">
-        <v>141</v>
-      </c>
-      <c r="D46" s="16">
+      <c r="D46" s="14" t="s">
+        <v>142</v>
+      </c>
+      <c r="E46" s="16">
         <v>8005.0</v>
       </c>
-      <c r="E46" s="14" t="s">
-        <v>132</v>
-      </c>
-      <c r="F46" s="11" t="s">
-        <v>97</v>
-      </c>
-      <c r="G46" s="13"/>
-      <c r="H46" s="16" t="s">
-        <v>121</v>
-      </c>
-      <c r="I46" s="16">
+      <c r="F46" s="14" t="s">
+        <v>133</v>
+      </c>
+      <c r="G46" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="H46" s="13"/>
+      <c r="I46" s="16" t="s">
+        <v>122</v>
+      </c>
+      <c r="J46" s="16">
         <v>-1.0</v>
       </c>
-      <c r="J46" s="17"/>
+      <c r="K46" s="17"/>
     </row>
     <row r="47">
       <c r="A47" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="B47" s="2">
+      <c r="B47" s="8" t="s">
+        <v>30</v>
+      </c>
+      <c r="C47" s="2">
         <v>8005.0</v>
       </c>
-      <c r="C47" s="14" t="s">
-        <v>142</v>
-      </c>
-      <c r="D47" s="16">
+      <c r="D47" s="14" t="s">
+        <v>143</v>
+      </c>
+      <c r="E47" s="16">
         <v>-1.0</v>
       </c>
-      <c r="E47" s="14" t="s">
-        <v>90</v>
-      </c>
-      <c r="F47" s="11" t="s">
+      <c r="F47" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="G47" s="13"/>
-      <c r="H47" s="14" t="s">
+      <c r="G47" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="I47" s="16">
+      <c r="H47" s="13"/>
+      <c r="I47" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="J47" s="16">
         <v>-1.0</v>
       </c>
-      <c r="J47" s="17"/>
+      <c r="K47" s="17"/>
     </row>
     <row r="48">
       <c r="A48" s="8" t="s">
         <v>33</v>
       </c>
-      <c r="B48" s="2">
+      <c r="B48" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="C48" s="2">
         <v>9001.0</v>
       </c>
-      <c r="C48" s="14" t="s">
-        <v>143</v>
-      </c>
-      <c r="D48" s="16">
+      <c r="D48" s="14" t="s">
+        <v>144</v>
+      </c>
+      <c r="E48" s="16">
         <v>-1.0</v>
       </c>
-      <c r="E48" s="14" t="s">
-        <v>90</v>
-      </c>
-      <c r="F48" s="11" t="s">
+      <c r="F48" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="G48" s="13"/>
-      <c r="H48" s="31" t="s">
+      <c r="G48" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="I48" s="16">
+      <c r="H48" s="13"/>
+      <c r="I48" s="31" t="s">
+        <v>93</v>
+      </c>
+      <c r="J48" s="16">
         <v>-1.0</v>
       </c>
-      <c r="J48" s="17"/>
+      <c r="K48" s="17"/>
     </row>
     <row r="49">
       <c r="A49" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="B49" s="2">
+      <c r="B49" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="C49" s="2">
         <v>10001.0</v>
       </c>
-      <c r="C49" s="14" t="s">
-        <v>144</v>
-      </c>
-      <c r="D49" s="16">
+      <c r="D49" s="14" t="s">
+        <v>145</v>
+      </c>
+      <c r="E49" s="16">
         <v>10002.0</v>
       </c>
-      <c r="E49" s="14" t="s">
-        <v>90</v>
-      </c>
-      <c r="F49" s="11" t="s">
+      <c r="F49" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="G49" s="13"/>
-      <c r="H49" s="31" t="s">
+      <c r="G49" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="I49" s="16">
+      <c r="H49" s="13"/>
+      <c r="I49" s="31" t="s">
+        <v>93</v>
+      </c>
+      <c r="J49" s="16">
         <v>0.0</v>
       </c>
-      <c r="J49" s="17"/>
+      <c r="K49" s="17"/>
     </row>
     <row r="50">
       <c r="A50" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="B50" s="2">
+      <c r="B50" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="C50" s="2">
         <v>10002.0</v>
       </c>
-      <c r="C50" s="14" t="s">
-        <v>145</v>
-      </c>
-      <c r="D50" s="16">
+      <c r="D50" s="14" t="s">
+        <v>146</v>
+      </c>
+      <c r="E50" s="16">
         <v>10003.0</v>
       </c>
-      <c r="E50" s="14" t="s">
-        <v>90</v>
-      </c>
-      <c r="F50" s="11" t="s">
+      <c r="F50" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="G50" s="13"/>
-      <c r="H50" s="31" t="s">
+      <c r="G50" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="I50" s="16">
+      <c r="H50" s="13"/>
+      <c r="I50" s="31" t="s">
+        <v>93</v>
+      </c>
+      <c r="J50" s="16">
         <v>0.0</v>
       </c>
-      <c r="J50" s="17"/>
+      <c r="K50" s="17"/>
     </row>
     <row r="51">
       <c r="A51" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="B51" s="2">
+      <c r="B51" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="C51" s="2">
         <v>10003.0</v>
       </c>
-      <c r="C51" s="14" t="s">
-        <v>146</v>
-      </c>
-      <c r="D51" s="16">
+      <c r="D51" s="14" t="s">
+        <v>147</v>
+      </c>
+      <c r="E51" s="16">
         <v>10004.0</v>
       </c>
-      <c r="E51" s="14" t="s">
-        <v>90</v>
-      </c>
-      <c r="F51" s="11" t="s">
+      <c r="F51" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="G51" s="13"/>
-      <c r="H51" s="31" t="s">
+      <c r="G51" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="I51" s="16">
+      <c r="H51" s="13"/>
+      <c r="I51" s="31" t="s">
+        <v>93</v>
+      </c>
+      <c r="J51" s="16">
         <v>0.0</v>
       </c>
-      <c r="J51" s="17"/>
+      <c r="K51" s="17"/>
     </row>
     <row r="52">
       <c r="A52" s="8" t="s">
         <v>36</v>
       </c>
-      <c r="B52" s="2">
+      <c r="B52" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="C52" s="2">
         <v>10004.0</v>
       </c>
-      <c r="C52" s="14" t="s">
-        <v>147</v>
-      </c>
-      <c r="D52" s="16">
+      <c r="D52" s="14" t="s">
+        <v>148</v>
+      </c>
+      <c r="E52" s="16">
         <v>-1.0</v>
       </c>
-      <c r="E52" s="14" t="s">
-        <v>90</v>
-      </c>
-      <c r="F52" s="11" t="s">
+      <c r="F52" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="G52" s="13"/>
-      <c r="H52" s="16" t="s">
+      <c r="G52" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="I52" s="16">
+      <c r="H52" s="13"/>
+      <c r="I52" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="J52" s="16">
         <v>0.0</v>
       </c>
-      <c r="J52" s="17"/>
+      <c r="K52" s="17"/>
     </row>
     <row r="53">
       <c r="A53" s="8" t="s">
         <v>39</v>
       </c>
-      <c r="B53" s="2">
+      <c r="B53" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="C53" s="2">
         <v>11001.0</v>
       </c>
-      <c r="C53" s="14" t="s">
-        <v>148</v>
-      </c>
-      <c r="D53" s="16">
+      <c r="D53" s="14" t="s">
+        <v>149</v>
+      </c>
+      <c r="E53" s="16">
         <v>-1.0</v>
       </c>
-      <c r="E53" s="14" t="s">
-        <v>90</v>
-      </c>
-      <c r="F53" s="11" t="s">
+      <c r="F53" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="G53" s="13"/>
-      <c r="H53" s="16" t="s">
+      <c r="G53" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="I53" s="16">
+      <c r="H53" s="13"/>
+      <c r="I53" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="J53" s="16">
         <v>-1.0</v>
       </c>
-      <c r="J53" s="17"/>
+      <c r="K53" s="17"/>
     </row>
     <row r="54">
       <c r="A54" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="B54" s="2">
+      <c r="B54" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="C54" s="2">
         <v>12001.0</v>
       </c>
-      <c r="C54" s="14" t="s">
-        <v>149</v>
-      </c>
-      <c r="D54" s="16">
+      <c r="D54" s="14" t="s">
+        <v>150</v>
+      </c>
+      <c r="E54" s="16">
         <v>12002.0</v>
       </c>
-      <c r="E54" s="14" t="s">
-        <v>132</v>
-      </c>
-      <c r="F54" s="11" t="s">
-        <v>97</v>
-      </c>
-      <c r="G54" s="13"/>
-      <c r="H54" s="31" t="s">
-        <v>121</v>
-      </c>
-      <c r="I54" s="16">
+      <c r="F54" s="14" t="s">
+        <v>133</v>
+      </c>
+      <c r="G54" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="H54" s="13"/>
+      <c r="I54" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="J54" s="16">
         <v>-1.0</v>
       </c>
-      <c r="J54" s="17"/>
+      <c r="K54" s="17"/>
     </row>
     <row r="55">
       <c r="A55" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="B55" s="2">
+      <c r="B55" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="C55" s="2">
         <v>12002.0</v>
       </c>
-      <c r="C55" s="14" t="s">
-        <v>150</v>
-      </c>
-      <c r="D55" s="16">
+      <c r="D55" s="14" t="s">
+        <v>151</v>
+      </c>
+      <c r="E55" s="16">
         <v>12003.0</v>
       </c>
-      <c r="E55" s="14" t="s">
-        <v>90</v>
-      </c>
-      <c r="F55" s="11" t="s">
+      <c r="F55" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="G55" s="13"/>
-      <c r="H55" s="16" t="s">
+      <c r="G55" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="I55" s="16">
+      <c r="H55" s="13"/>
+      <c r="I55" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="J55" s="16">
         <v>2.0</v>
       </c>
-      <c r="J55" s="17"/>
+      <c r="K55" s="17"/>
     </row>
     <row r="56">
       <c r="A56" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="B56" s="2">
+      <c r="B56" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="C56" s="2">
         <v>12003.0</v>
       </c>
-      <c r="C56" s="14" t="s">
-        <v>151</v>
-      </c>
-      <c r="D56" s="16">
+      <c r="D56" s="14" t="s">
+        <v>152</v>
+      </c>
+      <c r="E56" s="16">
         <v>12004.0</v>
       </c>
-      <c r="E56" s="14" t="s">
-        <v>132</v>
-      </c>
-      <c r="F56" s="11" t="s">
-        <v>97</v>
-      </c>
-      <c r="G56" s="13"/>
-      <c r="H56" s="31" t="s">
-        <v>121</v>
-      </c>
-      <c r="I56" s="16">
+      <c r="F56" s="14" t="s">
+        <v>133</v>
+      </c>
+      <c r="G56" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="H56" s="13"/>
+      <c r="I56" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="J56" s="16">
         <v>-1.0</v>
       </c>
-      <c r="J56" s="17"/>
+      <c r="K56" s="17"/>
     </row>
     <row r="57">
       <c r="A57" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="B57" s="2">
+      <c r="B57" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="C57" s="2">
         <v>12004.0</v>
       </c>
-      <c r="C57" s="14" t="s">
-        <v>152</v>
-      </c>
-      <c r="D57" s="16">
+      <c r="D57" s="14" t="s">
+        <v>153</v>
+      </c>
+      <c r="E57" s="16">
         <v>12005.0</v>
       </c>
-      <c r="E57" s="14" t="s">
-        <v>90</v>
-      </c>
-      <c r="F57" s="11" t="s">
+      <c r="F57" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="G57" s="13"/>
-      <c r="H57" s="31" t="s">
+      <c r="G57" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="I57" s="16">
+      <c r="H57" s="13"/>
+      <c r="I57" s="31" t="s">
+        <v>93</v>
+      </c>
+      <c r="J57" s="16">
         <v>2.0</v>
       </c>
-      <c r="J57" s="17"/>
+      <c r="K57" s="17"/>
     </row>
     <row r="58">
       <c r="A58" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="B58" s="2">
+      <c r="B58" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="C58" s="2">
         <v>12005.0</v>
       </c>
-      <c r="C58" s="14" t="s">
-        <v>153</v>
-      </c>
-      <c r="D58" s="16">
+      <c r="D58" s="14" t="s">
+        <v>154</v>
+      </c>
+      <c r="E58" s="16">
         <v>12006.0</v>
       </c>
-      <c r="E58" s="14" t="s">
-        <v>90</v>
-      </c>
-      <c r="F58" s="11" t="s">
+      <c r="F58" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="G58" s="13"/>
-      <c r="H58" s="16" t="s">
+      <c r="G58" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="I58" s="16">
+      <c r="H58" s="13"/>
+      <c r="I58" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="J58" s="16">
         <v>0.0</v>
       </c>
-      <c r="J58" s="17"/>
+      <c r="K58" s="17"/>
     </row>
     <row r="59">
       <c r="A59" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="B59" s="2">
+      <c r="B59" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="C59" s="2">
         <v>12006.0</v>
       </c>
-      <c r="C59" s="14" t="s">
-        <v>154</v>
-      </c>
-      <c r="D59" s="16">
+      <c r="D59" s="14" t="s">
+        <v>155</v>
+      </c>
+      <c r="E59" s="16">
         <v>12007.0</v>
       </c>
-      <c r="E59" s="14" t="s">
-        <v>132</v>
-      </c>
-      <c r="F59" s="11" t="s">
-        <v>97</v>
-      </c>
-      <c r="G59" s="13"/>
-      <c r="H59" s="31" t="s">
-        <v>121</v>
-      </c>
-      <c r="I59" s="16">
+      <c r="F59" s="14" t="s">
+        <v>133</v>
+      </c>
+      <c r="G59" s="11" t="s">
+        <v>98</v>
+      </c>
+      <c r="H59" s="13"/>
+      <c r="I59" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="J59" s="16">
         <v>-1.0</v>
       </c>
-      <c r="J59" s="17"/>
+      <c r="K59" s="17"/>
     </row>
     <row r="60">
       <c r="A60" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="B60" s="2">
+      <c r="B60" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="C60" s="2">
         <v>12007.0</v>
       </c>
-      <c r="C60" s="14" t="s">
-        <v>155</v>
-      </c>
-      <c r="D60" s="16">
+      <c r="D60" s="14" t="s">
+        <v>156</v>
+      </c>
+      <c r="E60" s="16">
         <v>12008.0</v>
       </c>
-      <c r="E60" s="14" t="s">
-        <v>90</v>
-      </c>
-      <c r="F60" s="11" t="s">
+      <c r="F60" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="G60" s="13"/>
-      <c r="H60" s="16" t="s">
+      <c r="G60" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="I60" s="16">
+      <c r="H60" s="13"/>
+      <c r="I60" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="J60" s="16">
         <v>0.0</v>
       </c>
-      <c r="J60" s="17"/>
+      <c r="K60" s="17"/>
     </row>
     <row r="61">
       <c r="A61" s="8" t="s">
         <v>42</v>
       </c>
-      <c r="B61" s="2">
+      <c r="B61" s="8" t="s">
+        <v>42</v>
+      </c>
+      <c r="C61" s="2">
         <v>12008.0</v>
       </c>
-      <c r="C61" s="14" t="s">
-        <v>156</v>
-      </c>
-      <c r="D61" s="16">
+      <c r="D61" s="14" t="s">
+        <v>157</v>
+      </c>
+      <c r="E61" s="16">
         <v>-1.0</v>
       </c>
-      <c r="E61" s="14" t="s">
-        <v>90</v>
-      </c>
-      <c r="F61" s="11" t="s">
+      <c r="F61" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="G61" s="13"/>
-      <c r="H61" s="31" t="s">
-        <v>121</v>
-      </c>
-      <c r="I61" s="16">
+      <c r="G61" s="11" t="s">
+        <v>92</v>
+      </c>
+      <c r="H61" s="13"/>
+      <c r="I61" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="J61" s="16">
         <v>0.0</v>
       </c>
-      <c r="J61" s="17"/>
+      <c r="K61" s="17"/>
     </row>
     <row r="62">
       <c r="A62" s="8" t="s">
         <v>45</v>
       </c>
-      <c r="B62" s="2">
+      <c r="B62" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="C62" s="2">
         <v>13001.0</v>
       </c>
-      <c r="C62" s="14" t="s">
-        <v>157</v>
-      </c>
-      <c r="D62" s="16">
+      <c r="D62" s="14" t="s">
+        <v>158</v>
+      </c>
+      <c r="E62" s="16">
         <v>-1.0</v>
       </c>
-      <c r="E62" s="14" t="s">
-        <v>90</v>
-      </c>
-      <c r="F62" s="11" t="s">
+      <c r="F62" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="G62" s="13"/>
-      <c r="H62" s="31" t="s">
+      <c r="G62" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="I62" s="16">
+      <c r="H62" s="13"/>
+      <c r="I62" s="31" t="s">
+        <v>93</v>
+      </c>
+      <c r="J62" s="16">
         <v>-1.0</v>
       </c>
-      <c r="J62" s="17"/>
+      <c r="K62" s="17"/>
     </row>
     <row r="63">
       <c r="A63" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="B63" s="2">
+      <c r="B63" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="C63" s="2">
         <v>14001.0</v>
       </c>
-      <c r="C63" s="14" t="s">
-        <v>158</v>
-      </c>
-      <c r="D63" s="16">
+      <c r="D63" s="14" t="s">
+        <v>159</v>
+      </c>
+      <c r="E63" s="16">
         <v>14002.0</v>
       </c>
-      <c r="E63" s="14" t="s">
-        <v>90</v>
-      </c>
-      <c r="F63" s="11" t="s">
+      <c r="F63" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="G63" s="13"/>
-      <c r="H63" s="31" t="s">
+      <c r="G63" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="I63" s="16">
+      <c r="H63" s="13"/>
+      <c r="I63" s="31" t="s">
+        <v>93</v>
+      </c>
+      <c r="J63" s="16">
         <v>-1.0</v>
       </c>
-      <c r="J63" s="17"/>
+      <c r="K63" s="17"/>
     </row>
     <row r="64">
       <c r="A64" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="B64" s="2">
+      <c r="B64" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="C64" s="2">
         <v>14002.0</v>
       </c>
-      <c r="C64" s="14" t="s">
-        <v>159</v>
-      </c>
-      <c r="D64" s="16">
+      <c r="D64" s="14" t="s">
+        <v>160</v>
+      </c>
+      <c r="E64" s="16">
         <v>14003.0</v>
       </c>
-      <c r="E64" s="14" t="s">
-        <v>90</v>
-      </c>
-      <c r="F64" s="11" t="s">
+      <c r="F64" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="G64" s="13"/>
-      <c r="H64" s="31" t="s">
+      <c r="G64" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="I64" s="16">
+      <c r="H64" s="13"/>
+      <c r="I64" s="31" t="s">
+        <v>93</v>
+      </c>
+      <c r="J64" s="16">
         <v>-1.0</v>
       </c>
-      <c r="J64" s="17"/>
+      <c r="K64" s="17"/>
     </row>
     <row r="65">
       <c r="A65" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="B65" s="2">
+      <c r="B65" s="8" t="s">
+        <v>48</v>
+      </c>
+      <c r="C65" s="2">
         <v>14003.0</v>
       </c>
-      <c r="C65" s="14" t="s">
-        <v>160</v>
-      </c>
-      <c r="D65" s="16">
+      <c r="D65" s="14" t="s">
+        <v>161</v>
+      </c>
+      <c r="E65" s="16">
         <v>-1.0</v>
       </c>
-      <c r="E65" s="14" t="s">
-        <v>90</v>
-      </c>
-      <c r="F65" s="11" t="s">
+      <c r="F65" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="G65" s="13"/>
-      <c r="H65" s="31" t="s">
+      <c r="G65" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="I65" s="16">
+      <c r="H65" s="13"/>
+      <c r="I65" s="31" t="s">
+        <v>93</v>
+      </c>
+      <c r="J65" s="16">
         <v>-1.0</v>
       </c>
-      <c r="J65" s="17"/>
+      <c r="K65" s="17"/>
     </row>
     <row r="66">
       <c r="A66" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="B66" s="2">
+      <c r="B66" s="8" t="s">
+        <v>51</v>
+      </c>
+      <c r="C66" s="2">
         <v>15001.0</v>
       </c>
-      <c r="C66" s="14" t="s">
-        <v>161</v>
-      </c>
-      <c r="D66" s="16">
+      <c r="D66" s="14" t="s">
+        <v>162</v>
+      </c>
+      <c r="E66" s="16">
         <v>-1.0</v>
       </c>
-      <c r="E66" s="14" t="s">
-        <v>90</v>
-      </c>
-      <c r="F66" s="11" t="s">
+      <c r="F66" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="G66" s="13"/>
-      <c r="H66" s="31" t="s">
+      <c r="G66" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="I66" s="16">
+      <c r="H66" s="13"/>
+      <c r="I66" s="31" t="s">
+        <v>93</v>
+      </c>
+      <c r="J66" s="16">
         <v>-1.0</v>
       </c>
-      <c r="J66" s="17"/>
+      <c r="K66" s="17"/>
     </row>
     <row r="67">
       <c r="A67" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="B67" s="2">
+      <c r="B67" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="C67" s="2">
         <v>16001.0</v>
       </c>
-      <c r="C67" s="14" t="s">
-        <v>162</v>
-      </c>
-      <c r="D67" s="16">
+      <c r="D67" s="14" t="s">
+        <v>163</v>
+      </c>
+      <c r="E67" s="16">
         <v>16002.0</v>
       </c>
-      <c r="E67" s="14" t="s">
-        <v>90</v>
-      </c>
-      <c r="F67" s="11" t="s">
+      <c r="F67" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="G67" s="13"/>
-      <c r="H67" s="31" t="s">
+      <c r="G67" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="I67" s="16">
+      <c r="H67" s="13"/>
+      <c r="I67" s="31" t="s">
+        <v>93</v>
+      </c>
+      <c r="J67" s="16">
         <v>0.0</v>
       </c>
-      <c r="J67" s="17"/>
+      <c r="K67" s="17"/>
     </row>
     <row r="68">
       <c r="A68" s="8" t="s">
         <v>54</v>
       </c>
-      <c r="B68" s="2">
+      <c r="B68" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="C68" s="2">
         <v>16002.0</v>
       </c>
-      <c r="C68" s="14" t="s">
-        <v>163</v>
-      </c>
-      <c r="D68" s="16">
+      <c r="D68" s="14" t="s">
+        <v>164</v>
+      </c>
+      <c r="E68" s="16">
         <v>-1.0</v>
       </c>
-      <c r="E68" s="14" t="s">
-        <v>90</v>
-      </c>
-      <c r="F68" s="11" t="s">
+      <c r="F68" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="G68" s="13"/>
-      <c r="H68" s="31" t="s">
+      <c r="G68" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="I68" s="16">
+      <c r="H68" s="13"/>
+      <c r="I68" s="31" t="s">
+        <v>93</v>
+      </c>
+      <c r="J68" s="16">
         <v>0.0</v>
       </c>
-      <c r="J68" s="17"/>
+      <c r="K68" s="17"/>
     </row>
     <row r="69">
       <c r="A69" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="B69" s="2">
+      <c r="B69" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="C69" s="2">
         <v>17001.0</v>
       </c>
-      <c r="C69" s="14" t="s">
-        <v>164</v>
-      </c>
-      <c r="D69" s="16">
+      <c r="D69" s="14" t="s">
+        <v>165</v>
+      </c>
+      <c r="E69" s="16">
         <v>17002.0</v>
       </c>
-      <c r="E69" s="14" t="s">
-        <v>90</v>
-      </c>
-      <c r="F69" s="11" t="s">
+      <c r="F69" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="G69" s="13"/>
-      <c r="H69" s="31" t="s">
+      <c r="G69" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="I69" s="16">
+      <c r="H69" s="13"/>
+      <c r="I69" s="31" t="s">
+        <v>93</v>
+      </c>
+      <c r="J69" s="16">
         <v>0.0</v>
       </c>
-      <c r="J69" s="17"/>
+      <c r="K69" s="17"/>
     </row>
     <row r="70">
       <c r="A70" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="B70" s="2">
+      <c r="B70" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="C70" s="2">
         <v>17002.0</v>
       </c>
-      <c r="C70" s="14" t="s">
-        <v>165</v>
-      </c>
-      <c r="D70" s="16">
+      <c r="D70" s="14" t="s">
+        <v>166</v>
+      </c>
+      <c r="E70" s="16">
         <v>17003.0</v>
       </c>
-      <c r="E70" s="14" t="s">
-        <v>90</v>
-      </c>
-      <c r="F70" s="11" t="s">
+      <c r="F70" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="G70" s="13"/>
-      <c r="H70" s="31" t="s">
+      <c r="G70" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="I70" s="16">
+      <c r="H70" s="13"/>
+      <c r="I70" s="31" t="s">
+        <v>93</v>
+      </c>
+      <c r="J70" s="16">
         <v>0.0</v>
       </c>
-      <c r="J70" s="17"/>
+      <c r="K70" s="17"/>
     </row>
     <row r="71">
       <c r="A71" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="B71" s="2">
+      <c r="B71" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="C71" s="2">
         <v>17003.0</v>
       </c>
-      <c r="C71" s="14" t="s">
-        <v>166</v>
-      </c>
-      <c r="D71" s="16">
+      <c r="D71" s="14" t="s">
+        <v>167</v>
+      </c>
+      <c r="E71" s="16">
         <v>17004.0</v>
       </c>
-      <c r="E71" s="14" t="s">
-        <v>90</v>
-      </c>
-      <c r="F71" s="11" t="s">
+      <c r="F71" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="G71" s="13"/>
-      <c r="H71" s="31" t="s">
+      <c r="G71" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="I71" s="16">
+      <c r="H71" s="13"/>
+      <c r="I71" s="31" t="s">
+        <v>93</v>
+      </c>
+      <c r="J71" s="16">
         <v>0.0</v>
       </c>
-      <c r="J71" s="17"/>
+      <c r="K71" s="17"/>
     </row>
     <row r="72">
       <c r="A72" s="8" t="s">
         <v>57</v>
       </c>
-      <c r="B72" s="2">
+      <c r="B72" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="C72" s="2">
         <v>17004.0</v>
       </c>
-      <c r="C72" s="14" t="s">
-        <v>167</v>
-      </c>
-      <c r="D72" s="16">
+      <c r="D72" s="14" t="s">
+        <v>168</v>
+      </c>
+      <c r="E72" s="16">
         <v>-1.0</v>
       </c>
-      <c r="E72" s="14" t="s">
-        <v>90</v>
-      </c>
-      <c r="F72" s="11" t="s">
+      <c r="F72" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="G72" s="13"/>
-      <c r="H72" s="31" t="s">
+      <c r="G72" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="I72" s="16">
+      <c r="H72" s="13"/>
+      <c r="I72" s="31" t="s">
+        <v>93</v>
+      </c>
+      <c r="J72" s="16">
         <v>0.0</v>
       </c>
-      <c r="J72" s="17"/>
+      <c r="K72" s="17"/>
     </row>
     <row r="73">
       <c r="A73" s="32" t="s">
         <v>60</v>
       </c>
-      <c r="B73" s="3">
+      <c r="B73" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="C73" s="3">
         <v>18001.0</v>
       </c>
-      <c r="C73" s="14" t="s">
-        <v>168</v>
-      </c>
-      <c r="D73" s="16">
+      <c r="D73" s="14" t="s">
+        <v>169</v>
+      </c>
+      <c r="E73" s="16">
         <v>18002.0</v>
       </c>
-      <c r="E73" s="14" t="s">
-        <v>90</v>
-      </c>
-      <c r="F73" s="11" t="s">
+      <c r="F73" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="G73" s="13"/>
-      <c r="H73" s="31" t="s">
+      <c r="G73" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="I73" s="16">
+      <c r="H73" s="13"/>
+      <c r="I73" s="31" t="s">
+        <v>93</v>
+      </c>
+      <c r="J73" s="16">
         <v>0.0</v>
       </c>
-      <c r="J73" s="17"/>
+      <c r="K73" s="17"/>
     </row>
     <row r="74">
       <c r="A74" s="32" t="s">
         <v>60</v>
       </c>
-      <c r="B74" s="3">
+      <c r="B74" s="32" t="s">
+        <v>60</v>
+      </c>
+      <c r="C74" s="3">
         <v>18002.0</v>
       </c>
-      <c r="C74" s="33" t="s">
-        <v>169</v>
-      </c>
-      <c r="D74" s="3">
+      <c r="D74" s="33" t="s">
+        <v>170</v>
+      </c>
+      <c r="E74" s="3">
         <v>-1.0</v>
       </c>
-      <c r="E74" s="14" t="s">
-        <v>90</v>
-      </c>
-      <c r="F74" s="11" t="s">
+      <c r="F74" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="H74" s="31" t="s">
+      <c r="G74" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="I74" s="16">
+      <c r="I74" s="31" t="s">
+        <v>93</v>
+      </c>
+      <c r="J74" s="16">
         <v>0.0</v>
       </c>
     </row>
@@ -3755,25 +4034,28 @@
       <c r="A75" s="32" t="s">
         <v>63</v>
       </c>
-      <c r="B75" s="3">
+      <c r="B75" s="32" t="s">
+        <v>63</v>
+      </c>
+      <c r="C75" s="3">
         <v>19001.0</v>
       </c>
-      <c r="C75" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="D75" s="16">
+      <c r="D75" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="E75" s="16">
         <v>19002.0</v>
       </c>
-      <c r="E75" s="14" t="s">
-        <v>90</v>
-      </c>
-      <c r="F75" s="11" t="s">
+      <c r="F75" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="H75" s="31" t="s">
+      <c r="G75" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="I75" s="16">
+      <c r="I75" s="31" t="s">
+        <v>93</v>
+      </c>
+      <c r="J75" s="16">
         <v>2.0</v>
       </c>
     </row>
@@ -3781,25 +4063,28 @@
       <c r="A76" s="32" t="s">
         <v>63</v>
       </c>
-      <c r="B76" s="3">
+      <c r="B76" s="32" t="s">
+        <v>63</v>
+      </c>
+      <c r="C76" s="3">
         <v>19002.0</v>
       </c>
-      <c r="C76" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="D76" s="3">
+      <c r="D76" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="E76" s="3">
         <v>19003.0</v>
       </c>
-      <c r="E76" s="14" t="s">
-        <v>90</v>
-      </c>
-      <c r="F76" s="11" t="s">
+      <c r="F76" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="H76" s="31" t="s">
+      <c r="G76" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="I76" s="16">
+      <c r="I76" s="31" t="s">
+        <v>93</v>
+      </c>
+      <c r="J76" s="16">
         <v>2.0</v>
       </c>
     </row>
@@ -3807,25 +4092,28 @@
       <c r="A77" s="32" t="s">
         <v>63</v>
       </c>
-      <c r="B77" s="3">
+      <c r="B77" s="32" t="s">
+        <v>63</v>
+      </c>
+      <c r="C77" s="3">
         <v>19003.0</v>
       </c>
-      <c r="C77" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="D77" s="3">
+      <c r="D77" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="E77" s="3">
         <v>19004.0</v>
       </c>
-      <c r="E77" s="14" t="s">
-        <v>90</v>
-      </c>
-      <c r="F77" s="11" t="s">
+      <c r="F77" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="H77" s="31" t="s">
+      <c r="G77" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="I77" s="3">
+      <c r="I77" s="31" t="s">
+        <v>93</v>
+      </c>
+      <c r="J77" s="3">
         <v>2.0</v>
       </c>
     </row>
@@ -3833,25 +4121,28 @@
       <c r="A78" s="32" t="s">
         <v>63</v>
       </c>
-      <c r="B78" s="3">
+      <c r="B78" s="32" t="s">
+        <v>63</v>
+      </c>
+      <c r="C78" s="3">
         <v>19004.0</v>
       </c>
-      <c r="C78" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="D78" s="3">
+      <c r="D78" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="E78" s="3">
         <v>19005.0</v>
-      </c>
-      <c r="E78" s="3" t="s">
-        <v>90</v>
       </c>
       <c r="F78" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="H78" s="3" t="s">
+      <c r="G78" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="I78" s="3">
+      <c r="I78" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="J78" s="3">
         <v>2.0</v>
       </c>
     </row>
@@ -3859,2733 +4150,3866 @@
       <c r="A79" s="32" t="s">
         <v>63</v>
       </c>
-      <c r="B79" s="3">
+      <c r="B79" s="32" t="s">
+        <v>63</v>
+      </c>
+      <c r="C79" s="3">
         <v>19005.0</v>
       </c>
-      <c r="C79" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="D79" s="3">
+      <c r="D79" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="E79" s="3">
         <v>-1.0</v>
-      </c>
-      <c r="E79" s="3" t="s">
-        <v>90</v>
       </c>
       <c r="F79" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="H79" s="3" t="s">
+      <c r="G79" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="I79" s="3">
+      <c r="I79" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="J79" s="3">
         <v>0.0</v>
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="34"/>
+      <c r="A80" s="32" t="s">
+        <v>176</v>
+      </c>
+      <c r="B80" s="32" t="s">
+        <v>176</v>
+      </c>
+      <c r="C80" s="3">
+        <v>20001.0</v>
+      </c>
+      <c r="D80" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="E80" s="3">
+        <v>20002.0</v>
+      </c>
+      <c r="F80" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="G80" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="I80" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="J80" s="3">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="81">
-      <c r="A81" s="34"/>
+      <c r="A81" s="32" t="s">
+        <v>176</v>
+      </c>
+      <c r="B81" s="32" t="s">
+        <v>176</v>
+      </c>
+      <c r="C81" s="3">
+        <v>20002.0</v>
+      </c>
+      <c r="D81" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="E81" s="3">
+        <v>20003.0</v>
+      </c>
+      <c r="F81" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="G81" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="I81" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="J81" s="3">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="82">
-      <c r="A82" s="34"/>
+      <c r="A82" s="32" t="s">
+        <v>176</v>
+      </c>
+      <c r="B82" s="32" t="s">
+        <v>176</v>
+      </c>
+      <c r="C82" s="3">
+        <v>20003.0</v>
+      </c>
+      <c r="D82" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="E82" s="3">
+        <v>-1.0</v>
+      </c>
+      <c r="F82" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="G82" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="H82" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="I82" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="J82" s="3">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="83">
-      <c r="A83" s="34"/>
+      <c r="A83" s="32" t="s">
+        <v>176</v>
+      </c>
+      <c r="B83" s="32" t="s">
+        <v>182</v>
+      </c>
+      <c r="C83" s="3">
+        <v>20004.0</v>
+      </c>
+      <c r="D83" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="E83" s="3">
+        <v>20005.0</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="G83" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="I83" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="J83" s="3">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="84">
-      <c r="A84" s="34"/>
+      <c r="A84" s="32" t="s">
+        <v>176</v>
+      </c>
+      <c r="B84" s="32" t="s">
+        <v>182</v>
+      </c>
+      <c r="C84" s="3">
+        <v>20005.0</v>
+      </c>
+      <c r="D84" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="E84" s="3">
+        <v>-1.0</v>
+      </c>
+      <c r="F84" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="G84" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="I84" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="J84" s="3">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="85">
-      <c r="A85" s="34"/>
+      <c r="A85" s="32" t="s">
+        <v>176</v>
+      </c>
+      <c r="B85" s="32" t="s">
+        <v>185</v>
+      </c>
+      <c r="C85" s="3">
+        <v>20006.0</v>
+      </c>
+      <c r="D85" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="E85" s="3">
+        <v>20007.0</v>
+      </c>
+      <c r="F85" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="G85" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="I85" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="J85" s="3">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="86">
-      <c r="A86" s="34"/>
+      <c r="A86" s="32" t="s">
+        <v>176</v>
+      </c>
+      <c r="B86" s="32" t="s">
+        <v>185</v>
+      </c>
+      <c r="C86" s="3">
+        <v>20007.0</v>
+      </c>
+      <c r="D86" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="E86" s="3">
+        <v>-1.0</v>
+      </c>
+      <c r="F86" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="G86" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="I86" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="J86" s="3">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="87">
-      <c r="A87" s="34"/>
+      <c r="A87" s="32" t="s">
+        <v>176</v>
+      </c>
+      <c r="B87" s="32" t="s">
+        <v>188</v>
+      </c>
+      <c r="C87" s="3">
+        <v>20008.0</v>
+      </c>
+      <c r="D87" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="E87" s="3">
+        <v>20009.0</v>
+      </c>
+      <c r="F87" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="G87" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="I87" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="J87" s="3">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="88">
-      <c r="A88" s="34"/>
+      <c r="A88" s="32" t="s">
+        <v>176</v>
+      </c>
+      <c r="B88" s="32" t="s">
+        <v>188</v>
+      </c>
+      <c r="C88" s="3">
+        <v>20009.0</v>
+      </c>
+      <c r="D88" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="E88" s="3">
+        <v>-1.0</v>
+      </c>
+      <c r="F88" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="G88" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="I88" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="J88" s="3">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="34"/>
+      <c r="B89" s="34"/>
     </row>
     <row r="90">
       <c r="A90" s="34"/>
+      <c r="B90" s="34"/>
     </row>
     <row r="91">
       <c r="A91" s="34"/>
+      <c r="B91" s="34"/>
     </row>
     <row r="92">
       <c r="A92" s="34"/>
+      <c r="B92" s="34"/>
     </row>
     <row r="93">
       <c r="A93" s="34"/>
+      <c r="B93" s="34"/>
     </row>
     <row r="94">
       <c r="A94" s="34"/>
+      <c r="B94" s="34"/>
     </row>
     <row r="95">
       <c r="A95" s="34"/>
+      <c r="B95" s="34"/>
     </row>
     <row r="96">
       <c r="A96" s="34"/>
+      <c r="B96" s="34"/>
     </row>
     <row r="97">
       <c r="A97" s="34"/>
+      <c r="B97" s="34"/>
     </row>
     <row r="98">
       <c r="A98" s="34"/>
+      <c r="B98" s="34"/>
     </row>
     <row r="99">
       <c r="A99" s="34"/>
+      <c r="B99" s="34"/>
     </row>
     <row r="100">
       <c r="A100" s="34"/>
+      <c r="B100" s="34"/>
     </row>
     <row r="101">
       <c r="A101" s="34"/>
+      <c r="B101" s="34"/>
     </row>
     <row r="102">
       <c r="A102" s="34"/>
+      <c r="B102" s="34"/>
     </row>
     <row r="103">
       <c r="A103" s="34"/>
+      <c r="B103" s="34"/>
     </row>
     <row r="104">
       <c r="A104" s="34"/>
+      <c r="B104" s="34"/>
     </row>
     <row r="105">
       <c r="A105" s="34"/>
+      <c r="B105" s="34"/>
     </row>
     <row r="106">
       <c r="A106" s="34"/>
+      <c r="B106" s="34"/>
     </row>
     <row r="107">
       <c r="A107" s="34"/>
+      <c r="B107" s="34"/>
     </row>
     <row r="108">
       <c r="A108" s="34"/>
+      <c r="B108" s="34"/>
     </row>
     <row r="109">
       <c r="A109" s="34"/>
+      <c r="B109" s="34"/>
     </row>
     <row r="110">
       <c r="A110" s="34"/>
+      <c r="B110" s="34"/>
     </row>
     <row r="111">
       <c r="A111" s="34"/>
+      <c r="B111" s="34"/>
     </row>
     <row r="112">
       <c r="A112" s="34"/>
+      <c r="B112" s="34"/>
     </row>
     <row r="113">
       <c r="A113" s="34"/>
+      <c r="B113" s="34"/>
     </row>
     <row r="114">
       <c r="A114" s="34"/>
+      <c r="B114" s="34"/>
     </row>
     <row r="115">
       <c r="A115" s="34"/>
+      <c r="B115" s="34"/>
     </row>
     <row r="116">
       <c r="A116" s="34"/>
+      <c r="B116" s="34"/>
     </row>
     <row r="117">
       <c r="A117" s="34"/>
+      <c r="B117" s="34"/>
     </row>
     <row r="118">
       <c r="A118" s="34"/>
+      <c r="B118" s="34"/>
     </row>
     <row r="119">
       <c r="A119" s="34"/>
+      <c r="B119" s="34"/>
     </row>
     <row r="120">
       <c r="A120" s="34"/>
+      <c r="B120" s="34"/>
     </row>
     <row r="121">
       <c r="A121" s="34"/>
+      <c r="B121" s="34"/>
     </row>
     <row r="122">
       <c r="A122" s="34"/>
+      <c r="B122" s="34"/>
     </row>
     <row r="123">
       <c r="A123" s="34"/>
+      <c r="B123" s="34"/>
     </row>
     <row r="124">
       <c r="A124" s="34"/>
+      <c r="B124" s="34"/>
     </row>
     <row r="125">
       <c r="A125" s="34"/>
+      <c r="B125" s="34"/>
     </row>
     <row r="126">
       <c r="A126" s="34"/>
+      <c r="B126" s="34"/>
     </row>
     <row r="127">
       <c r="A127" s="34"/>
+      <c r="B127" s="34"/>
     </row>
     <row r="128">
       <c r="A128" s="34"/>
+      <c r="B128" s="34"/>
     </row>
     <row r="129">
       <c r="A129" s="34"/>
+      <c r="B129" s="34"/>
     </row>
     <row r="130">
       <c r="A130" s="34"/>
+      <c r="B130" s="34"/>
     </row>
     <row r="131">
       <c r="A131" s="34"/>
+      <c r="B131" s="34"/>
     </row>
     <row r="132">
       <c r="A132" s="34"/>
+      <c r="B132" s="34"/>
     </row>
     <row r="133">
       <c r="A133" s="34"/>
+      <c r="B133" s="34"/>
     </row>
     <row r="134">
       <c r="A134" s="34"/>
+      <c r="B134" s="34"/>
     </row>
     <row r="135">
       <c r="A135" s="34"/>
+      <c r="B135" s="34"/>
     </row>
     <row r="136">
       <c r="A136" s="34"/>
+      <c r="B136" s="34"/>
     </row>
     <row r="137">
       <c r="A137" s="34"/>
+      <c r="B137" s="34"/>
     </row>
     <row r="138">
       <c r="A138" s="34"/>
+      <c r="B138" s="34"/>
     </row>
     <row r="139">
       <c r="A139" s="34"/>
+      <c r="B139" s="34"/>
     </row>
     <row r="140">
       <c r="A140" s="34"/>
+      <c r="B140" s="34"/>
     </row>
     <row r="141">
       <c r="A141" s="34"/>
+      <c r="B141" s="34"/>
     </row>
     <row r="142">
       <c r="A142" s="34"/>
+      <c r="B142" s="34"/>
     </row>
     <row r="143">
       <c r="A143" s="34"/>
+      <c r="B143" s="34"/>
     </row>
     <row r="144">
       <c r="A144" s="34"/>
+      <c r="B144" s="34"/>
     </row>
     <row r="145">
       <c r="A145" s="34"/>
+      <c r="B145" s="34"/>
     </row>
     <row r="146">
       <c r="A146" s="34"/>
+      <c r="B146" s="34"/>
     </row>
     <row r="147">
       <c r="A147" s="34"/>
+      <c r="B147" s="34"/>
     </row>
     <row r="148">
       <c r="A148" s="34"/>
+      <c r="B148" s="34"/>
     </row>
     <row r="149">
       <c r="A149" s="34"/>
+      <c r="B149" s="34"/>
     </row>
     <row r="150">
       <c r="A150" s="34"/>
+      <c r="B150" s="34"/>
     </row>
     <row r="151">
       <c r="A151" s="34"/>
+      <c r="B151" s="34"/>
     </row>
     <row r="152">
       <c r="A152" s="34"/>
+      <c r="B152" s="34"/>
     </row>
     <row r="153">
       <c r="A153" s="34"/>
+      <c r="B153" s="34"/>
     </row>
     <row r="154">
       <c r="A154" s="34"/>
+      <c r="B154" s="34"/>
     </row>
     <row r="155">
       <c r="A155" s="34"/>
+      <c r="B155" s="34"/>
     </row>
     <row r="156">
       <c r="A156" s="34"/>
+      <c r="B156" s="34"/>
     </row>
     <row r="157">
       <c r="A157" s="34"/>
+      <c r="B157" s="34"/>
     </row>
     <row r="158">
       <c r="A158" s="34"/>
+      <c r="B158" s="34"/>
     </row>
     <row r="159">
       <c r="A159" s="34"/>
+      <c r="B159" s="34"/>
     </row>
     <row r="160">
       <c r="A160" s="34"/>
+      <c r="B160" s="34"/>
     </row>
     <row r="161">
       <c r="A161" s="34"/>
+      <c r="B161" s="34"/>
     </row>
     <row r="162">
       <c r="A162" s="34"/>
+      <c r="B162" s="34"/>
     </row>
     <row r="163">
       <c r="A163" s="34"/>
+      <c r="B163" s="34"/>
     </row>
     <row r="164">
       <c r="A164" s="34"/>
+      <c r="B164" s="34"/>
     </row>
     <row r="165">
       <c r="A165" s="34"/>
+      <c r="B165" s="34"/>
     </row>
     <row r="166">
       <c r="A166" s="34"/>
+      <c r="B166" s="34"/>
     </row>
     <row r="167">
       <c r="A167" s="34"/>
+      <c r="B167" s="34"/>
     </row>
     <row r="168">
       <c r="A168" s="34"/>
+      <c r="B168" s="34"/>
     </row>
     <row r="169">
       <c r="A169" s="34"/>
+      <c r="B169" s="34"/>
     </row>
     <row r="170">
       <c r="A170" s="34"/>
+      <c r="B170" s="34"/>
     </row>
     <row r="171">
       <c r="A171" s="34"/>
+      <c r="B171" s="34"/>
     </row>
     <row r="172">
       <c r="A172" s="34"/>
+      <c r="B172" s="34"/>
     </row>
     <row r="173">
       <c r="A173" s="34"/>
+      <c r="B173" s="34"/>
     </row>
     <row r="174">
       <c r="A174" s="34"/>
+      <c r="B174" s="34"/>
     </row>
     <row r="175">
       <c r="A175" s="34"/>
+      <c r="B175" s="34"/>
     </row>
     <row r="176">
       <c r="A176" s="34"/>
+      <c r="B176" s="34"/>
     </row>
     <row r="177">
       <c r="A177" s="34"/>
+      <c r="B177" s="34"/>
     </row>
     <row r="178">
       <c r="A178" s="34"/>
+      <c r="B178" s="34"/>
     </row>
     <row r="179">
       <c r="A179" s="34"/>
+      <c r="B179" s="34"/>
     </row>
     <row r="180">
       <c r="A180" s="34"/>
+      <c r="B180" s="34"/>
     </row>
     <row r="181">
       <c r="A181" s="34"/>
+      <c r="B181" s="34"/>
     </row>
     <row r="182">
       <c r="A182" s="34"/>
+      <c r="B182" s="34"/>
     </row>
     <row r="183">
       <c r="A183" s="34"/>
+      <c r="B183" s="34"/>
     </row>
     <row r="184">
       <c r="A184" s="34"/>
+      <c r="B184" s="34"/>
     </row>
     <row r="185">
       <c r="A185" s="34"/>
+      <c r="B185" s="34"/>
     </row>
     <row r="186">
       <c r="A186" s="34"/>
+      <c r="B186" s="34"/>
     </row>
     <row r="187">
       <c r="A187" s="34"/>
+      <c r="B187" s="34"/>
     </row>
     <row r="188">
       <c r="A188" s="34"/>
+      <c r="B188" s="34"/>
     </row>
     <row r="189">
       <c r="A189" s="34"/>
+      <c r="B189" s="34"/>
     </row>
     <row r="190">
       <c r="A190" s="34"/>
+      <c r="B190" s="34"/>
     </row>
     <row r="191">
       <c r="A191" s="34"/>
+      <c r="B191" s="34"/>
     </row>
     <row r="192">
       <c r="A192" s="34"/>
+      <c r="B192" s="34"/>
     </row>
     <row r="193">
       <c r="A193" s="34"/>
+      <c r="B193" s="34"/>
     </row>
     <row r="194">
       <c r="A194" s="34"/>
+      <c r="B194" s="34"/>
     </row>
     <row r="195">
       <c r="A195" s="34"/>
+      <c r="B195" s="34"/>
     </row>
     <row r="196">
       <c r="A196" s="34"/>
+      <c r="B196" s="34"/>
     </row>
     <row r="197">
       <c r="A197" s="34"/>
+      <c r="B197" s="34"/>
     </row>
     <row r="198">
       <c r="A198" s="34"/>
+      <c r="B198" s="34"/>
     </row>
     <row r="199">
       <c r="A199" s="34"/>
+      <c r="B199" s="34"/>
     </row>
     <row r="200">
       <c r="A200" s="34"/>
+      <c r="B200" s="34"/>
     </row>
     <row r="201">
       <c r="A201" s="34"/>
+      <c r="B201" s="34"/>
     </row>
     <row r="202">
       <c r="A202" s="34"/>
+      <c r="B202" s="34"/>
     </row>
     <row r="203">
       <c r="A203" s="34"/>
+      <c r="B203" s="34"/>
     </row>
     <row r="204">
       <c r="A204" s="34"/>
+      <c r="B204" s="34"/>
     </row>
     <row r="205">
       <c r="A205" s="34"/>
+      <c r="B205" s="34"/>
     </row>
     <row r="206">
       <c r="A206" s="34"/>
+      <c r="B206" s="34"/>
     </row>
     <row r="207">
       <c r="A207" s="34"/>
+      <c r="B207" s="34"/>
     </row>
     <row r="208">
       <c r="A208" s="34"/>
+      <c r="B208" s="34"/>
     </row>
     <row r="209">
       <c r="A209" s="34"/>
+      <c r="B209" s="34"/>
     </row>
     <row r="210">
       <c r="A210" s="34"/>
+      <c r="B210" s="34"/>
     </row>
     <row r="211">
       <c r="A211" s="34"/>
+      <c r="B211" s="34"/>
     </row>
     <row r="212">
       <c r="A212" s="34"/>
+      <c r="B212" s="34"/>
     </row>
     <row r="213">
       <c r="A213" s="34"/>
+      <c r="B213" s="34"/>
     </row>
     <row r="214">
       <c r="A214" s="34"/>
+      <c r="B214" s="34"/>
     </row>
     <row r="215">
       <c r="A215" s="34"/>
+      <c r="B215" s="34"/>
     </row>
     <row r="216">
       <c r="A216" s="34"/>
+      <c r="B216" s="34"/>
     </row>
     <row r="217">
       <c r="A217" s="34"/>
+      <c r="B217" s="34"/>
     </row>
     <row r="218">
       <c r="A218" s="34"/>
+      <c r="B218" s="34"/>
     </row>
     <row r="219">
       <c r="A219" s="34"/>
+      <c r="B219" s="34"/>
     </row>
     <row r="220">
       <c r="A220" s="34"/>
+      <c r="B220" s="34"/>
     </row>
     <row r="221">
       <c r="A221" s="34"/>
+      <c r="B221" s="34"/>
     </row>
     <row r="222">
       <c r="A222" s="34"/>
+      <c r="B222" s="34"/>
     </row>
     <row r="223">
       <c r="A223" s="34"/>
+      <c r="B223" s="34"/>
     </row>
     <row r="224">
       <c r="A224" s="34"/>
+      <c r="B224" s="34"/>
     </row>
     <row r="225">
       <c r="A225" s="34"/>
+      <c r="B225" s="34"/>
     </row>
     <row r="226">
       <c r="A226" s="34"/>
+      <c r="B226" s="34"/>
     </row>
     <row r="227">
       <c r="A227" s="34"/>
+      <c r="B227" s="34"/>
     </row>
     <row r="228">
       <c r="A228" s="34"/>
+      <c r="B228" s="34"/>
     </row>
     <row r="229">
       <c r="A229" s="34"/>
+      <c r="B229" s="34"/>
     </row>
     <row r="230">
       <c r="A230" s="34"/>
+      <c r="B230" s="34"/>
     </row>
     <row r="231">
       <c r="A231" s="34"/>
+      <c r="B231" s="34"/>
     </row>
     <row r="232">
       <c r="A232" s="34"/>
+      <c r="B232" s="34"/>
     </row>
     <row r="233">
       <c r="A233" s="34"/>
+      <c r="B233" s="34"/>
     </row>
     <row r="234">
       <c r="A234" s="34"/>
+      <c r="B234" s="34"/>
     </row>
     <row r="235">
       <c r="A235" s="34"/>
+      <c r="B235" s="34"/>
     </row>
     <row r="236">
       <c r="A236" s="34"/>
+      <c r="B236" s="34"/>
     </row>
     <row r="237">
       <c r="A237" s="34"/>
+      <c r="B237" s="34"/>
     </row>
     <row r="238">
       <c r="A238" s="34"/>
+      <c r="B238" s="34"/>
     </row>
     <row r="239">
       <c r="A239" s="34"/>
+      <c r="B239" s="34"/>
     </row>
     <row r="240">
       <c r="A240" s="34"/>
+      <c r="B240" s="34"/>
     </row>
     <row r="241">
       <c r="A241" s="34"/>
+      <c r="B241" s="34"/>
     </row>
     <row r="242">
       <c r="A242" s="34"/>
+      <c r="B242" s="34"/>
     </row>
     <row r="243">
       <c r="A243" s="34"/>
+      <c r="B243" s="34"/>
     </row>
     <row r="244">
       <c r="A244" s="34"/>
+      <c r="B244" s="34"/>
     </row>
     <row r="245">
       <c r="A245" s="34"/>
+      <c r="B245" s="34"/>
     </row>
     <row r="246">
       <c r="A246" s="34"/>
+      <c r="B246" s="34"/>
     </row>
     <row r="247">
       <c r="A247" s="34"/>
+      <c r="B247" s="34"/>
     </row>
     <row r="248">
       <c r="A248" s="34"/>
+      <c r="B248" s="34"/>
     </row>
     <row r="249">
       <c r="A249" s="34"/>
+      <c r="B249" s="34"/>
     </row>
     <row r="250">
       <c r="A250" s="34"/>
+      <c r="B250" s="34"/>
     </row>
     <row r="251">
       <c r="A251" s="34"/>
+      <c r="B251" s="34"/>
     </row>
     <row r="252">
       <c r="A252" s="34"/>
+      <c r="B252" s="34"/>
     </row>
     <row r="253">
       <c r="A253" s="34"/>
+      <c r="B253" s="34"/>
     </row>
     <row r="254">
       <c r="A254" s="34"/>
+      <c r="B254" s="34"/>
     </row>
     <row r="255">
       <c r="A255" s="34"/>
+      <c r="B255" s="34"/>
     </row>
     <row r="256">
       <c r="A256" s="34"/>
+      <c r="B256" s="34"/>
     </row>
     <row r="257">
       <c r="A257" s="34"/>
+      <c r="B257" s="34"/>
     </row>
     <row r="258">
       <c r="A258" s="34"/>
+      <c r="B258" s="34"/>
     </row>
     <row r="259">
       <c r="A259" s="34"/>
+      <c r="B259" s="34"/>
     </row>
     <row r="260">
       <c r="A260" s="34"/>
+      <c r="B260" s="34"/>
     </row>
     <row r="261">
       <c r="A261" s="34"/>
+      <c r="B261" s="34"/>
     </row>
     <row r="262">
       <c r="A262" s="34"/>
+      <c r="B262" s="34"/>
     </row>
     <row r="263">
       <c r="A263" s="34"/>
+      <c r="B263" s="34"/>
     </row>
     <row r="264">
       <c r="A264" s="34"/>
+      <c r="B264" s="34"/>
     </row>
     <row r="265">
       <c r="A265" s="34"/>
+      <c r="B265" s="34"/>
     </row>
     <row r="266">
       <c r="A266" s="34"/>
+      <c r="B266" s="34"/>
     </row>
     <row r="267">
       <c r="A267" s="34"/>
+      <c r="B267" s="34"/>
     </row>
     <row r="268">
       <c r="A268" s="34"/>
+      <c r="B268" s="34"/>
     </row>
     <row r="269">
       <c r="A269" s="34"/>
+      <c r="B269" s="34"/>
     </row>
     <row r="270">
       <c r="A270" s="34"/>
+      <c r="B270" s="34"/>
     </row>
     <row r="271">
       <c r="A271" s="34"/>
+      <c r="B271" s="34"/>
     </row>
     <row r="272">
       <c r="A272" s="34"/>
+      <c r="B272" s="34"/>
     </row>
     <row r="273">
       <c r="A273" s="34"/>
+      <c r="B273" s="34"/>
     </row>
     <row r="274">
       <c r="A274" s="34"/>
+      <c r="B274" s="34"/>
     </row>
     <row r="275">
       <c r="A275" s="34"/>
+      <c r="B275" s="34"/>
     </row>
     <row r="276">
       <c r="A276" s="34"/>
+      <c r="B276" s="34"/>
     </row>
     <row r="277">
       <c r="A277" s="34"/>
+      <c r="B277" s="34"/>
     </row>
     <row r="278">
       <c r="A278" s="34"/>
+      <c r="B278" s="34"/>
     </row>
     <row r="279">
       <c r="A279" s="34"/>
+      <c r="B279" s="34"/>
     </row>
     <row r="280">
       <c r="A280" s="34"/>
+      <c r="B280" s="34"/>
     </row>
     <row r="281">
       <c r="A281" s="34"/>
+      <c r="B281" s="34"/>
     </row>
     <row r="282">
       <c r="A282" s="34"/>
+      <c r="B282" s="34"/>
     </row>
     <row r="283">
       <c r="A283" s="34"/>
+      <c r="B283" s="34"/>
     </row>
     <row r="284">
       <c r="A284" s="34"/>
+      <c r="B284" s="34"/>
     </row>
     <row r="285">
       <c r="A285" s="34"/>
+      <c r="B285" s="34"/>
     </row>
     <row r="286">
       <c r="A286" s="34"/>
+      <c r="B286" s="34"/>
     </row>
     <row r="287">
       <c r="A287" s="34"/>
+      <c r="B287" s="34"/>
     </row>
     <row r="288">
       <c r="A288" s="34"/>
+      <c r="B288" s="34"/>
     </row>
     <row r="289">
       <c r="A289" s="34"/>
+      <c r="B289" s="34"/>
     </row>
     <row r="290">
       <c r="A290" s="34"/>
+      <c r="B290" s="34"/>
     </row>
     <row r="291">
       <c r="A291" s="34"/>
+      <c r="B291" s="34"/>
     </row>
     <row r="292">
       <c r="A292" s="34"/>
+      <c r="B292" s="34"/>
     </row>
     <row r="293">
       <c r="A293" s="34"/>
+      <c r="B293" s="34"/>
     </row>
     <row r="294">
       <c r="A294" s="34"/>
+      <c r="B294" s="34"/>
     </row>
     <row r="295">
       <c r="A295" s="34"/>
+      <c r="B295" s="34"/>
     </row>
     <row r="296">
       <c r="A296" s="34"/>
+      <c r="B296" s="34"/>
     </row>
     <row r="297">
       <c r="A297" s="34"/>
+      <c r="B297" s="34"/>
     </row>
     <row r="298">
       <c r="A298" s="34"/>
+      <c r="B298" s="34"/>
     </row>
     <row r="299">
       <c r="A299" s="34"/>
+      <c r="B299" s="34"/>
     </row>
     <row r="300">
       <c r="A300" s="34"/>
+      <c r="B300" s="34"/>
     </row>
     <row r="301">
       <c r="A301" s="34"/>
+      <c r="B301" s="34"/>
     </row>
     <row r="302">
       <c r="A302" s="34"/>
+      <c r="B302" s="34"/>
     </row>
     <row r="303">
       <c r="A303" s="34"/>
+      <c r="B303" s="34"/>
     </row>
     <row r="304">
       <c r="A304" s="34"/>
+      <c r="B304" s="34"/>
     </row>
     <row r="305">
       <c r="A305" s="34"/>
+      <c r="B305" s="34"/>
     </row>
     <row r="306">
       <c r="A306" s="34"/>
+      <c r="B306" s="34"/>
     </row>
     <row r="307">
       <c r="A307" s="34"/>
+      <c r="B307" s="34"/>
     </row>
     <row r="308">
       <c r="A308" s="34"/>
+      <c r="B308" s="34"/>
     </row>
     <row r="309">
       <c r="A309" s="34"/>
+      <c r="B309" s="34"/>
     </row>
     <row r="310">
       <c r="A310" s="34"/>
+      <c r="B310" s="34"/>
     </row>
     <row r="311">
       <c r="A311" s="34"/>
+      <c r="B311" s="34"/>
     </row>
     <row r="312">
       <c r="A312" s="34"/>
+      <c r="B312" s="34"/>
     </row>
     <row r="313">
       <c r="A313" s="34"/>
+      <c r="B313" s="34"/>
     </row>
     <row r="314">
       <c r="A314" s="34"/>
+      <c r="B314" s="34"/>
     </row>
     <row r="315">
       <c r="A315" s="34"/>
+      <c r="B315" s="34"/>
     </row>
     <row r="316">
       <c r="A316" s="34"/>
+      <c r="B316" s="34"/>
     </row>
     <row r="317">
       <c r="A317" s="34"/>
+      <c r="B317" s="34"/>
     </row>
     <row r="318">
       <c r="A318" s="34"/>
+      <c r="B318" s="34"/>
     </row>
     <row r="319">
       <c r="A319" s="34"/>
+      <c r="B319" s="34"/>
     </row>
     <row r="320">
       <c r="A320" s="34"/>
+      <c r="B320" s="34"/>
     </row>
     <row r="321">
       <c r="A321" s="34"/>
+      <c r="B321" s="34"/>
     </row>
     <row r="322">
       <c r="A322" s="34"/>
+      <c r="B322" s="34"/>
     </row>
     <row r="323">
       <c r="A323" s="34"/>
+      <c r="B323" s="34"/>
     </row>
     <row r="324">
       <c r="A324" s="34"/>
+      <c r="B324" s="34"/>
     </row>
     <row r="325">
       <c r="A325" s="34"/>
+      <c r="B325" s="34"/>
     </row>
     <row r="326">
       <c r="A326" s="34"/>
+      <c r="B326" s="34"/>
     </row>
     <row r="327">
       <c r="A327" s="34"/>
+      <c r="B327" s="34"/>
     </row>
     <row r="328">
       <c r="A328" s="34"/>
+      <c r="B328" s="34"/>
     </row>
     <row r="329">
       <c r="A329" s="34"/>
+      <c r="B329" s="34"/>
     </row>
     <row r="330">
       <c r="A330" s="34"/>
+      <c r="B330" s="34"/>
     </row>
     <row r="331">
       <c r="A331" s="34"/>
+      <c r="B331" s="34"/>
     </row>
     <row r="332">
       <c r="A332" s="34"/>
+      <c r="B332" s="34"/>
     </row>
     <row r="333">
       <c r="A333" s="34"/>
+      <c r="B333" s="34"/>
     </row>
     <row r="334">
       <c r="A334" s="34"/>
+      <c r="B334" s="34"/>
     </row>
     <row r="335">
       <c r="A335" s="34"/>
+      <c r="B335" s="34"/>
     </row>
     <row r="336">
       <c r="A336" s="34"/>
+      <c r="B336" s="34"/>
     </row>
     <row r="337">
       <c r="A337" s="34"/>
+      <c r="B337" s="34"/>
     </row>
     <row r="338">
       <c r="A338" s="34"/>
+      <c r="B338" s="34"/>
     </row>
     <row r="339">
       <c r="A339" s="34"/>
+      <c r="B339" s="34"/>
     </row>
     <row r="340">
       <c r="A340" s="34"/>
+      <c r="B340" s="34"/>
     </row>
     <row r="341">
       <c r="A341" s="34"/>
+      <c r="B341" s="34"/>
     </row>
     <row r="342">
       <c r="A342" s="34"/>
+      <c r="B342" s="34"/>
     </row>
     <row r="343">
       <c r="A343" s="34"/>
+      <c r="B343" s="34"/>
     </row>
     <row r="344">
       <c r="A344" s="34"/>
+      <c r="B344" s="34"/>
     </row>
     <row r="345">
       <c r="A345" s="34"/>
+      <c r="B345" s="34"/>
     </row>
     <row r="346">
       <c r="A346" s="34"/>
+      <c r="B346" s="34"/>
     </row>
     <row r="347">
       <c r="A347" s="34"/>
+      <c r="B347" s="34"/>
     </row>
     <row r="348">
       <c r="A348" s="34"/>
+      <c r="B348" s="34"/>
     </row>
     <row r="349">
       <c r="A349" s="34"/>
+      <c r="B349" s="34"/>
     </row>
     <row r="350">
       <c r="A350" s="34"/>
+      <c r="B350" s="34"/>
     </row>
     <row r="351">
       <c r="A351" s="34"/>
+      <c r="B351" s="34"/>
     </row>
     <row r="352">
       <c r="A352" s="34"/>
+      <c r="B352" s="34"/>
     </row>
     <row r="353">
       <c r="A353" s="34"/>
+      <c r="B353" s="34"/>
     </row>
     <row r="354">
       <c r="A354" s="34"/>
+      <c r="B354" s="34"/>
     </row>
     <row r="355">
       <c r="A355" s="34"/>
+      <c r="B355" s="34"/>
     </row>
     <row r="356">
       <c r="A356" s="34"/>
+      <c r="B356" s="34"/>
     </row>
     <row r="357">
       <c r="A357" s="34"/>
+      <c r="B357" s="34"/>
     </row>
     <row r="358">
       <c r="A358" s="34"/>
+      <c r="B358" s="34"/>
     </row>
     <row r="359">
       <c r="A359" s="34"/>
+      <c r="B359" s="34"/>
     </row>
     <row r="360">
       <c r="A360" s="34"/>
+      <c r="B360" s="34"/>
     </row>
     <row r="361">
       <c r="A361" s="34"/>
+      <c r="B361" s="34"/>
     </row>
     <row r="362">
       <c r="A362" s="34"/>
+      <c r="B362" s="34"/>
     </row>
     <row r="363">
       <c r="A363" s="34"/>
+      <c r="B363" s="34"/>
     </row>
     <row r="364">
       <c r="A364" s="34"/>
+      <c r="B364" s="34"/>
     </row>
     <row r="365">
       <c r="A365" s="34"/>
+      <c r="B365" s="34"/>
     </row>
     <row r="366">
       <c r="A366" s="34"/>
+      <c r="B366" s="34"/>
     </row>
     <row r="367">
       <c r="A367" s="34"/>
+      <c r="B367" s="34"/>
     </row>
     <row r="368">
       <c r="A368" s="34"/>
+      <c r="B368" s="34"/>
     </row>
     <row r="369">
       <c r="A369" s="34"/>
+      <c r="B369" s="34"/>
     </row>
     <row r="370">
       <c r="A370" s="34"/>
+      <c r="B370" s="34"/>
     </row>
     <row r="371">
       <c r="A371" s="34"/>
+      <c r="B371" s="34"/>
     </row>
     <row r="372">
       <c r="A372" s="34"/>
+      <c r="B372" s="34"/>
     </row>
     <row r="373">
       <c r="A373" s="34"/>
+      <c r="B373" s="34"/>
     </row>
     <row r="374">
       <c r="A374" s="34"/>
+      <c r="B374" s="34"/>
     </row>
     <row r="375">
       <c r="A375" s="34"/>
+      <c r="B375" s="34"/>
     </row>
     <row r="376">
       <c r="A376" s="34"/>
+      <c r="B376" s="34"/>
     </row>
     <row r="377">
       <c r="A377" s="34"/>
+      <c r="B377" s="34"/>
     </row>
     <row r="378">
       <c r="A378" s="34"/>
+      <c r="B378" s="34"/>
     </row>
     <row r="379">
       <c r="A379" s="34"/>
+      <c r="B379" s="34"/>
     </row>
     <row r="380">
       <c r="A380" s="34"/>
+      <c r="B380" s="34"/>
     </row>
     <row r="381">
       <c r="A381" s="34"/>
+      <c r="B381" s="34"/>
     </row>
     <row r="382">
       <c r="A382" s="34"/>
+      <c r="B382" s="34"/>
     </row>
     <row r="383">
       <c r="A383" s="34"/>
+      <c r="B383" s="34"/>
     </row>
     <row r="384">
       <c r="A384" s="34"/>
+      <c r="B384" s="34"/>
     </row>
     <row r="385">
       <c r="A385" s="34"/>
+      <c r="B385" s="34"/>
     </row>
     <row r="386">
       <c r="A386" s="34"/>
+      <c r="B386" s="34"/>
     </row>
     <row r="387">
       <c r="A387" s="34"/>
+      <c r="B387" s="34"/>
     </row>
     <row r="388">
       <c r="A388" s="34"/>
+      <c r="B388" s="34"/>
     </row>
     <row r="389">
       <c r="A389" s="34"/>
+      <c r="B389" s="34"/>
     </row>
     <row r="390">
       <c r="A390" s="34"/>
+      <c r="B390" s="34"/>
     </row>
     <row r="391">
       <c r="A391" s="34"/>
+      <c r="B391" s="34"/>
     </row>
     <row r="392">
       <c r="A392" s="34"/>
+      <c r="B392" s="34"/>
     </row>
     <row r="393">
       <c r="A393" s="34"/>
+      <c r="B393" s="34"/>
     </row>
     <row r="394">
       <c r="A394" s="34"/>
+      <c r="B394" s="34"/>
     </row>
     <row r="395">
       <c r="A395" s="34"/>
+      <c r="B395" s="34"/>
     </row>
     <row r="396">
       <c r="A396" s="34"/>
+      <c r="B396" s="34"/>
     </row>
     <row r="397">
       <c r="A397" s="34"/>
+      <c r="B397" s="34"/>
     </row>
     <row r="398">
       <c r="A398" s="34"/>
+      <c r="B398" s="34"/>
     </row>
     <row r="399">
       <c r="A399" s="34"/>
+      <c r="B399" s="34"/>
     </row>
     <row r="400">
       <c r="A400" s="34"/>
+      <c r="B400" s="34"/>
     </row>
     <row r="401">
       <c r="A401" s="34"/>
+      <c r="B401" s="34"/>
     </row>
     <row r="402">
       <c r="A402" s="34"/>
+      <c r="B402" s="34"/>
     </row>
     <row r="403">
       <c r="A403" s="34"/>
+      <c r="B403" s="34"/>
     </row>
     <row r="404">
       <c r="A404" s="34"/>
+      <c r="B404" s="34"/>
     </row>
     <row r="405">
       <c r="A405" s="34"/>
+      <c r="B405" s="34"/>
     </row>
     <row r="406">
       <c r="A406" s="34"/>
+      <c r="B406" s="34"/>
     </row>
     <row r="407">
       <c r="A407" s="34"/>
+      <c r="B407" s="34"/>
     </row>
     <row r="408">
       <c r="A408" s="34"/>
+      <c r="B408" s="34"/>
     </row>
     <row r="409">
       <c r="A409" s="34"/>
+      <c r="B409" s="34"/>
     </row>
     <row r="410">
       <c r="A410" s="34"/>
+      <c r="B410" s="34"/>
     </row>
     <row r="411">
       <c r="A411" s="34"/>
+      <c r="B411" s="34"/>
     </row>
     <row r="412">
       <c r="A412" s="34"/>
+      <c r="B412" s="34"/>
     </row>
     <row r="413">
       <c r="A413" s="34"/>
+      <c r="B413" s="34"/>
     </row>
     <row r="414">
       <c r="A414" s="34"/>
+      <c r="B414" s="34"/>
     </row>
     <row r="415">
       <c r="A415" s="34"/>
+      <c r="B415" s="34"/>
     </row>
     <row r="416">
       <c r="A416" s="34"/>
+      <c r="B416" s="34"/>
     </row>
     <row r="417">
       <c r="A417" s="34"/>
+      <c r="B417" s="34"/>
     </row>
     <row r="418">
       <c r="A418" s="34"/>
+      <c r="B418" s="34"/>
     </row>
     <row r="419">
       <c r="A419" s="34"/>
+      <c r="B419" s="34"/>
     </row>
     <row r="420">
       <c r="A420" s="34"/>
+      <c r="B420" s="34"/>
     </row>
     <row r="421">
       <c r="A421" s="34"/>
+      <c r="B421" s="34"/>
     </row>
     <row r="422">
       <c r="A422" s="34"/>
+      <c r="B422" s="34"/>
     </row>
     <row r="423">
       <c r="A423" s="34"/>
+      <c r="B423" s="34"/>
     </row>
     <row r="424">
       <c r="A424" s="34"/>
+      <c r="B424" s="34"/>
     </row>
     <row r="425">
       <c r="A425" s="34"/>
+      <c r="B425" s="34"/>
     </row>
     <row r="426">
       <c r="A426" s="34"/>
+      <c r="B426" s="34"/>
     </row>
     <row r="427">
       <c r="A427" s="34"/>
+      <c r="B427" s="34"/>
     </row>
     <row r="428">
       <c r="A428" s="34"/>
+      <c r="B428" s="34"/>
     </row>
     <row r="429">
       <c r="A429" s="34"/>
+      <c r="B429" s="34"/>
     </row>
     <row r="430">
       <c r="A430" s="34"/>
+      <c r="B430" s="34"/>
     </row>
     <row r="431">
       <c r="A431" s="34"/>
+      <c r="B431" s="34"/>
     </row>
     <row r="432">
       <c r="A432" s="34"/>
+      <c r="B432" s="34"/>
     </row>
     <row r="433">
       <c r="A433" s="34"/>
+      <c r="B433" s="34"/>
     </row>
     <row r="434">
       <c r="A434" s="34"/>
+      <c r="B434" s="34"/>
     </row>
     <row r="435">
       <c r="A435" s="34"/>
+      <c r="B435" s="34"/>
     </row>
     <row r="436">
       <c r="A436" s="34"/>
+      <c r="B436" s="34"/>
     </row>
     <row r="437">
       <c r="A437" s="34"/>
+      <c r="B437" s="34"/>
     </row>
     <row r="438">
       <c r="A438" s="34"/>
+      <c r="B438" s="34"/>
     </row>
     <row r="439">
       <c r="A439" s="34"/>
+      <c r="B439" s="34"/>
     </row>
     <row r="440">
       <c r="A440" s="34"/>
+      <c r="B440" s="34"/>
     </row>
     <row r="441">
       <c r="A441" s="34"/>
+      <c r="B441" s="34"/>
     </row>
     <row r="442">
       <c r="A442" s="34"/>
+      <c r="B442" s="34"/>
     </row>
     <row r="443">
       <c r="A443" s="34"/>
+      <c r="B443" s="34"/>
     </row>
     <row r="444">
       <c r="A444" s="34"/>
+      <c r="B444" s="34"/>
     </row>
     <row r="445">
       <c r="A445" s="34"/>
+      <c r="B445" s="34"/>
     </row>
     <row r="446">
       <c r="A446" s="34"/>
+      <c r="B446" s="34"/>
     </row>
     <row r="447">
       <c r="A447" s="34"/>
+      <c r="B447" s="34"/>
     </row>
     <row r="448">
       <c r="A448" s="34"/>
+      <c r="B448" s="34"/>
     </row>
     <row r="449">
       <c r="A449" s="34"/>
+      <c r="B449" s="34"/>
     </row>
     <row r="450">
       <c r="A450" s="34"/>
+      <c r="B450" s="34"/>
     </row>
     <row r="451">
       <c r="A451" s="34"/>
+      <c r="B451" s="34"/>
     </row>
     <row r="452">
       <c r="A452" s="34"/>
+      <c r="B452" s="34"/>
     </row>
     <row r="453">
       <c r="A453" s="34"/>
+      <c r="B453" s="34"/>
     </row>
     <row r="454">
       <c r="A454" s="34"/>
+      <c r="B454" s="34"/>
     </row>
     <row r="455">
       <c r="A455" s="34"/>
+      <c r="B455" s="34"/>
     </row>
     <row r="456">
       <c r="A456" s="34"/>
+      <c r="B456" s="34"/>
     </row>
     <row r="457">
       <c r="A457" s="34"/>
+      <c r="B457" s="34"/>
     </row>
     <row r="458">
       <c r="A458" s="34"/>
+      <c r="B458" s="34"/>
     </row>
     <row r="459">
       <c r="A459" s="34"/>
+      <c r="B459" s="34"/>
     </row>
     <row r="460">
       <c r="A460" s="34"/>
+      <c r="B460" s="34"/>
     </row>
     <row r="461">
       <c r="A461" s="34"/>
+      <c r="B461" s="34"/>
     </row>
     <row r="462">
       <c r="A462" s="34"/>
+      <c r="B462" s="34"/>
     </row>
     <row r="463">
       <c r="A463" s="34"/>
+      <c r="B463" s="34"/>
     </row>
     <row r="464">
       <c r="A464" s="34"/>
+      <c r="B464" s="34"/>
     </row>
     <row r="465">
       <c r="A465" s="34"/>
+      <c r="B465" s="34"/>
     </row>
     <row r="466">
       <c r="A466" s="34"/>
+      <c r="B466" s="34"/>
     </row>
     <row r="467">
       <c r="A467" s="34"/>
+      <c r="B467" s="34"/>
     </row>
     <row r="468">
       <c r="A468" s="34"/>
+      <c r="B468" s="34"/>
     </row>
     <row r="469">
       <c r="A469" s="34"/>
+      <c r="B469" s="34"/>
     </row>
     <row r="470">
       <c r="A470" s="34"/>
+      <c r="B470" s="34"/>
     </row>
     <row r="471">
       <c r="A471" s="34"/>
+      <c r="B471" s="34"/>
     </row>
     <row r="472">
       <c r="A472" s="34"/>
+      <c r="B472" s="34"/>
     </row>
     <row r="473">
       <c r="A473" s="34"/>
+      <c r="B473" s="34"/>
     </row>
     <row r="474">
       <c r="A474" s="34"/>
+      <c r="B474" s="34"/>
     </row>
     <row r="475">
       <c r="A475" s="34"/>
+      <c r="B475" s="34"/>
     </row>
     <row r="476">
       <c r="A476" s="34"/>
+      <c r="B476" s="34"/>
     </row>
     <row r="477">
       <c r="A477" s="34"/>
+      <c r="B477" s="34"/>
     </row>
     <row r="478">
       <c r="A478" s="34"/>
+      <c r="B478" s="34"/>
     </row>
     <row r="479">
       <c r="A479" s="34"/>
+      <c r="B479" s="34"/>
     </row>
     <row r="480">
       <c r="A480" s="34"/>
+      <c r="B480" s="34"/>
     </row>
     <row r="481">
       <c r="A481" s="34"/>
+      <c r="B481" s="34"/>
     </row>
     <row r="482">
       <c r="A482" s="34"/>
+      <c r="B482" s="34"/>
     </row>
     <row r="483">
       <c r="A483" s="34"/>
+      <c r="B483" s="34"/>
     </row>
     <row r="484">
       <c r="A484" s="34"/>
+      <c r="B484" s="34"/>
     </row>
     <row r="485">
       <c r="A485" s="34"/>
+      <c r="B485" s="34"/>
     </row>
     <row r="486">
       <c r="A486" s="34"/>
+      <c r="B486" s="34"/>
     </row>
     <row r="487">
       <c r="A487" s="34"/>
+      <c r="B487" s="34"/>
     </row>
     <row r="488">
       <c r="A488" s="34"/>
+      <c r="B488" s="34"/>
     </row>
     <row r="489">
       <c r="A489" s="34"/>
+      <c r="B489" s="34"/>
     </row>
     <row r="490">
       <c r="A490" s="34"/>
+      <c r="B490" s="34"/>
     </row>
     <row r="491">
       <c r="A491" s="34"/>
+      <c r="B491" s="34"/>
     </row>
     <row r="492">
       <c r="A492" s="34"/>
+      <c r="B492" s="34"/>
     </row>
     <row r="493">
       <c r="A493" s="34"/>
+      <c r="B493" s="34"/>
     </row>
     <row r="494">
       <c r="A494" s="34"/>
+      <c r="B494" s="34"/>
     </row>
     <row r="495">
       <c r="A495" s="34"/>
+      <c r="B495" s="34"/>
     </row>
     <row r="496">
       <c r="A496" s="34"/>
+      <c r="B496" s="34"/>
     </row>
     <row r="497">
       <c r="A497" s="34"/>
+      <c r="B497" s="34"/>
     </row>
     <row r="498">
       <c r="A498" s="34"/>
+      <c r="B498" s="34"/>
     </row>
     <row r="499">
       <c r="A499" s="34"/>
+      <c r="B499" s="34"/>
     </row>
     <row r="500">
       <c r="A500" s="34"/>
+      <c r="B500" s="34"/>
     </row>
     <row r="501">
       <c r="A501" s="34"/>
+      <c r="B501" s="34"/>
     </row>
     <row r="502">
       <c r="A502" s="34"/>
+      <c r="B502" s="34"/>
     </row>
     <row r="503">
       <c r="A503" s="34"/>
+      <c r="B503" s="34"/>
     </row>
     <row r="504">
       <c r="A504" s="34"/>
+      <c r="B504" s="34"/>
     </row>
     <row r="505">
       <c r="A505" s="34"/>
+      <c r="B505" s="34"/>
     </row>
     <row r="506">
       <c r="A506" s="34"/>
+      <c r="B506" s="34"/>
     </row>
     <row r="507">
       <c r="A507" s="34"/>
+      <c r="B507" s="34"/>
     </row>
     <row r="508">
       <c r="A508" s="34"/>
+      <c r="B508" s="34"/>
     </row>
     <row r="509">
       <c r="A509" s="34"/>
+      <c r="B509" s="34"/>
     </row>
     <row r="510">
       <c r="A510" s="34"/>
+      <c r="B510" s="34"/>
     </row>
     <row r="511">
       <c r="A511" s="34"/>
+      <c r="B511" s="34"/>
     </row>
     <row r="512">
       <c r="A512" s="34"/>
+      <c r="B512" s="34"/>
     </row>
     <row r="513">
       <c r="A513" s="34"/>
+      <c r="B513" s="34"/>
     </row>
     <row r="514">
       <c r="A514" s="34"/>
+      <c r="B514" s="34"/>
     </row>
     <row r="515">
       <c r="A515" s="34"/>
+      <c r="B515" s="34"/>
     </row>
     <row r="516">
       <c r="A516" s="34"/>
+      <c r="B516" s="34"/>
     </row>
     <row r="517">
       <c r="A517" s="34"/>
+      <c r="B517" s="34"/>
     </row>
     <row r="518">
       <c r="A518" s="34"/>
+      <c r="B518" s="34"/>
     </row>
     <row r="519">
       <c r="A519" s="34"/>
+      <c r="B519" s="34"/>
     </row>
     <row r="520">
       <c r="A520" s="34"/>
+      <c r="B520" s="34"/>
     </row>
     <row r="521">
       <c r="A521" s="34"/>
+      <c r="B521" s="34"/>
     </row>
     <row r="522">
       <c r="A522" s="34"/>
+      <c r="B522" s="34"/>
     </row>
     <row r="523">
       <c r="A523" s="34"/>
+      <c r="B523" s="34"/>
     </row>
     <row r="524">
       <c r="A524" s="34"/>
+      <c r="B524" s="34"/>
     </row>
     <row r="525">
       <c r="A525" s="34"/>
+      <c r="B525" s="34"/>
     </row>
     <row r="526">
       <c r="A526" s="34"/>
+      <c r="B526" s="34"/>
     </row>
     <row r="527">
       <c r="A527" s="34"/>
+      <c r="B527" s="34"/>
     </row>
     <row r="528">
       <c r="A528" s="34"/>
+      <c r="B528" s="34"/>
     </row>
     <row r="529">
       <c r="A529" s="34"/>
+      <c r="B529" s="34"/>
     </row>
     <row r="530">
       <c r="A530" s="34"/>
+      <c r="B530" s="34"/>
     </row>
     <row r="531">
       <c r="A531" s="34"/>
+      <c r="B531" s="34"/>
     </row>
     <row r="532">
       <c r="A532" s="34"/>
+      <c r="B532" s="34"/>
     </row>
     <row r="533">
       <c r="A533" s="34"/>
+      <c r="B533" s="34"/>
     </row>
     <row r="534">
       <c r="A534" s="34"/>
+      <c r="B534" s="34"/>
     </row>
     <row r="535">
       <c r="A535" s="34"/>
+      <c r="B535" s="34"/>
     </row>
     <row r="536">
       <c r="A536" s="34"/>
+      <c r="B536" s="34"/>
     </row>
     <row r="537">
       <c r="A537" s="34"/>
+      <c r="B537" s="34"/>
     </row>
     <row r="538">
       <c r="A538" s="34"/>
+      <c r="B538" s="34"/>
     </row>
     <row r="539">
       <c r="A539" s="34"/>
+      <c r="B539" s="34"/>
     </row>
     <row r="540">
       <c r="A540" s="34"/>
+      <c r="B540" s="34"/>
     </row>
     <row r="541">
       <c r="A541" s="34"/>
+      <c r="B541" s="34"/>
     </row>
     <row r="542">
       <c r="A542" s="34"/>
+      <c r="B542" s="34"/>
     </row>
     <row r="543">
       <c r="A543" s="34"/>
+      <c r="B543" s="34"/>
     </row>
     <row r="544">
       <c r="A544" s="34"/>
+      <c r="B544" s="34"/>
     </row>
     <row r="545">
       <c r="A545" s="34"/>
+      <c r="B545" s="34"/>
     </row>
     <row r="546">
       <c r="A546" s="34"/>
+      <c r="B546" s="34"/>
     </row>
     <row r="547">
       <c r="A547" s="34"/>
+      <c r="B547" s="34"/>
     </row>
     <row r="548">
       <c r="A548" s="34"/>
+      <c r="B548" s="34"/>
     </row>
     <row r="549">
       <c r="A549" s="34"/>
+      <c r="B549" s="34"/>
     </row>
     <row r="550">
       <c r="A550" s="34"/>
+      <c r="B550" s="34"/>
     </row>
     <row r="551">
       <c r="A551" s="34"/>
+      <c r="B551" s="34"/>
     </row>
     <row r="552">
       <c r="A552" s="34"/>
+      <c r="B552" s="34"/>
     </row>
     <row r="553">
       <c r="A553" s="34"/>
+      <c r="B553" s="34"/>
     </row>
     <row r="554">
       <c r="A554" s="34"/>
+      <c r="B554" s="34"/>
     </row>
     <row r="555">
       <c r="A555" s="34"/>
+      <c r="B555" s="34"/>
     </row>
     <row r="556">
       <c r="A556" s="34"/>
+      <c r="B556" s="34"/>
     </row>
     <row r="557">
       <c r="A557" s="34"/>
+      <c r="B557" s="34"/>
     </row>
     <row r="558">
       <c r="A558" s="34"/>
+      <c r="B558" s="34"/>
     </row>
     <row r="559">
       <c r="A559" s="34"/>
+      <c r="B559" s="34"/>
     </row>
     <row r="560">
       <c r="A560" s="34"/>
+      <c r="B560" s="34"/>
     </row>
     <row r="561">
       <c r="A561" s="34"/>
+      <c r="B561" s="34"/>
     </row>
     <row r="562">
       <c r="A562" s="34"/>
+      <c r="B562" s="34"/>
     </row>
     <row r="563">
       <c r="A563" s="34"/>
+      <c r="B563" s="34"/>
     </row>
     <row r="564">
       <c r="A564" s="34"/>
+      <c r="B564" s="34"/>
     </row>
     <row r="565">
       <c r="A565" s="34"/>
+      <c r="B565" s="34"/>
     </row>
     <row r="566">
       <c r="A566" s="34"/>
+      <c r="B566" s="34"/>
     </row>
     <row r="567">
       <c r="A567" s="34"/>
+      <c r="B567" s="34"/>
     </row>
     <row r="568">
       <c r="A568" s="34"/>
+      <c r="B568" s="34"/>
     </row>
     <row r="569">
       <c r="A569" s="34"/>
+      <c r="B569" s="34"/>
     </row>
     <row r="570">
       <c r="A570" s="34"/>
+      <c r="B570" s="34"/>
     </row>
     <row r="571">
       <c r="A571" s="34"/>
+      <c r="B571" s="34"/>
     </row>
     <row r="572">
       <c r="A572" s="34"/>
+      <c r="B572" s="34"/>
     </row>
     <row r="573">
       <c r="A573" s="34"/>
+      <c r="B573" s="34"/>
     </row>
     <row r="574">
       <c r="A574" s="34"/>
+      <c r="B574" s="34"/>
     </row>
     <row r="575">
       <c r="A575" s="34"/>
+      <c r="B575" s="34"/>
     </row>
     <row r="576">
       <c r="A576" s="34"/>
+      <c r="B576" s="34"/>
     </row>
     <row r="577">
       <c r="A577" s="34"/>
+      <c r="B577" s="34"/>
     </row>
     <row r="578">
       <c r="A578" s="34"/>
+      <c r="B578" s="34"/>
     </row>
     <row r="579">
       <c r="A579" s="34"/>
+      <c r="B579" s="34"/>
     </row>
     <row r="580">
       <c r="A580" s="34"/>
+      <c r="B580" s="34"/>
     </row>
     <row r="581">
       <c r="A581" s="34"/>
+      <c r="B581" s="34"/>
     </row>
     <row r="582">
       <c r="A582" s="34"/>
+      <c r="B582" s="34"/>
     </row>
     <row r="583">
       <c r="A583" s="34"/>
+      <c r="B583" s="34"/>
     </row>
     <row r="584">
       <c r="A584" s="34"/>
+      <c r="B584" s="34"/>
     </row>
     <row r="585">
       <c r="A585" s="34"/>
+      <c r="B585" s="34"/>
     </row>
     <row r="586">
       <c r="A586" s="34"/>
+      <c r="B586" s="34"/>
     </row>
     <row r="587">
       <c r="A587" s="34"/>
+      <c r="B587" s="34"/>
     </row>
     <row r="588">
       <c r="A588" s="34"/>
+      <c r="B588" s="34"/>
     </row>
     <row r="589">
       <c r="A589" s="34"/>
+      <c r="B589" s="34"/>
     </row>
     <row r="590">
       <c r="A590" s="34"/>
+      <c r="B590" s="34"/>
     </row>
     <row r="591">
       <c r="A591" s="34"/>
+      <c r="B591" s="34"/>
     </row>
     <row r="592">
       <c r="A592" s="34"/>
+      <c r="B592" s="34"/>
     </row>
     <row r="593">
       <c r="A593" s="34"/>
+      <c r="B593" s="34"/>
     </row>
     <row r="594">
       <c r="A594" s="34"/>
+      <c r="B594" s="34"/>
     </row>
     <row r="595">
       <c r="A595" s="34"/>
+      <c r="B595" s="34"/>
     </row>
     <row r="596">
       <c r="A596" s="34"/>
+      <c r="B596" s="34"/>
     </row>
     <row r="597">
       <c r="A597" s="34"/>
+      <c r="B597" s="34"/>
     </row>
     <row r="598">
       <c r="A598" s="34"/>
+      <c r="B598" s="34"/>
     </row>
     <row r="599">
       <c r="A599" s="34"/>
+      <c r="B599" s="34"/>
     </row>
     <row r="600">
       <c r="A600" s="34"/>
+      <c r="B600" s="34"/>
     </row>
     <row r="601">
       <c r="A601" s="34"/>
+      <c r="B601" s="34"/>
     </row>
     <row r="602">
       <c r="A602" s="34"/>
+      <c r="B602" s="34"/>
     </row>
     <row r="603">
       <c r="A603" s="34"/>
+      <c r="B603" s="34"/>
     </row>
     <row r="604">
       <c r="A604" s="34"/>
+      <c r="B604" s="34"/>
     </row>
     <row r="605">
       <c r="A605" s="34"/>
+      <c r="B605" s="34"/>
     </row>
     <row r="606">
       <c r="A606" s="34"/>
+      <c r="B606" s="34"/>
     </row>
     <row r="607">
       <c r="A607" s="34"/>
+      <c r="B607" s="34"/>
     </row>
     <row r="608">
       <c r="A608" s="34"/>
+      <c r="B608" s="34"/>
     </row>
     <row r="609">
       <c r="A609" s="34"/>
+      <c r="B609" s="34"/>
     </row>
     <row r="610">
       <c r="A610" s="34"/>
+      <c r="B610" s="34"/>
     </row>
     <row r="611">
       <c r="A611" s="34"/>
+      <c r="B611" s="34"/>
     </row>
     <row r="612">
       <c r="A612" s="34"/>
+      <c r="B612" s="34"/>
     </row>
     <row r="613">
       <c r="A613" s="34"/>
+      <c r="B613" s="34"/>
     </row>
     <row r="614">
       <c r="A614" s="34"/>
+      <c r="B614" s="34"/>
     </row>
     <row r="615">
       <c r="A615" s="34"/>
+      <c r="B615" s="34"/>
     </row>
     <row r="616">
       <c r="A616" s="34"/>
+      <c r="B616" s="34"/>
     </row>
     <row r="617">
       <c r="A617" s="34"/>
+      <c r="B617" s="34"/>
     </row>
     <row r="618">
       <c r="A618" s="34"/>
+      <c r="B618" s="34"/>
     </row>
     <row r="619">
       <c r="A619" s="34"/>
+      <c r="B619" s="34"/>
     </row>
     <row r="620">
       <c r="A620" s="34"/>
+      <c r="B620" s="34"/>
     </row>
     <row r="621">
       <c r="A621" s="34"/>
+      <c r="B621" s="34"/>
     </row>
     <row r="622">
       <c r="A622" s="34"/>
+      <c r="B622" s="34"/>
     </row>
     <row r="623">
       <c r="A623" s="34"/>
+      <c r="B623" s="34"/>
     </row>
     <row r="624">
       <c r="A624" s="34"/>
+      <c r="B624" s="34"/>
     </row>
     <row r="625">
       <c r="A625" s="34"/>
+      <c r="B625" s="34"/>
     </row>
     <row r="626">
       <c r="A626" s="34"/>
+      <c r="B626" s="34"/>
     </row>
     <row r="627">
       <c r="A627" s="34"/>
+      <c r="B627" s="34"/>
     </row>
     <row r="628">
       <c r="A628" s="34"/>
+      <c r="B628" s="34"/>
     </row>
     <row r="629">
       <c r="A629" s="34"/>
+      <c r="B629" s="34"/>
     </row>
     <row r="630">
       <c r="A630" s="34"/>
+      <c r="B630" s="34"/>
     </row>
     <row r="631">
       <c r="A631" s="34"/>
+      <c r="B631" s="34"/>
     </row>
     <row r="632">
       <c r="A632" s="34"/>
+      <c r="B632" s="34"/>
     </row>
     <row r="633">
       <c r="A633" s="34"/>
+      <c r="B633" s="34"/>
     </row>
     <row r="634">
       <c r="A634" s="34"/>
+      <c r="B634" s="34"/>
     </row>
     <row r="635">
       <c r="A635" s="34"/>
+      <c r="B635" s="34"/>
     </row>
     <row r="636">
       <c r="A636" s="34"/>
+      <c r="B636" s="34"/>
     </row>
     <row r="637">
       <c r="A637" s="34"/>
+      <c r="B637" s="34"/>
     </row>
     <row r="638">
       <c r="A638" s="34"/>
+      <c r="B638" s="34"/>
     </row>
     <row r="639">
       <c r="A639" s="34"/>
+      <c r="B639" s="34"/>
     </row>
     <row r="640">
       <c r="A640" s="34"/>
+      <c r="B640" s="34"/>
     </row>
     <row r="641">
       <c r="A641" s="34"/>
+      <c r="B641" s="34"/>
     </row>
     <row r="642">
       <c r="A642" s="34"/>
+      <c r="B642" s="34"/>
     </row>
     <row r="643">
       <c r="A643" s="34"/>
+      <c r="B643" s="34"/>
     </row>
     <row r="644">
       <c r="A644" s="34"/>
+      <c r="B644" s="34"/>
     </row>
     <row r="645">
       <c r="A645" s="34"/>
+      <c r="B645" s="34"/>
     </row>
     <row r="646">
       <c r="A646" s="34"/>
+      <c r="B646" s="34"/>
     </row>
     <row r="647">
       <c r="A647" s="34"/>
+      <c r="B647" s="34"/>
     </row>
     <row r="648">
       <c r="A648" s="34"/>
+      <c r="B648" s="34"/>
     </row>
     <row r="649">
       <c r="A649" s="34"/>
+      <c r="B649" s="34"/>
     </row>
     <row r="650">
       <c r="A650" s="34"/>
+      <c r="B650" s="34"/>
     </row>
     <row r="651">
       <c r="A651" s="34"/>
+      <c r="B651" s="34"/>
     </row>
     <row r="652">
       <c r="A652" s="34"/>
+      <c r="B652" s="34"/>
     </row>
     <row r="653">
       <c r="A653" s="34"/>
+      <c r="B653" s="34"/>
     </row>
     <row r="654">
       <c r="A654" s="34"/>
+      <c r="B654" s="34"/>
     </row>
     <row r="655">
       <c r="A655" s="34"/>
+      <c r="B655" s="34"/>
     </row>
     <row r="656">
       <c r="A656" s="34"/>
+      <c r="B656" s="34"/>
     </row>
     <row r="657">
       <c r="A657" s="34"/>
+      <c r="B657" s="34"/>
     </row>
     <row r="658">
       <c r="A658" s="34"/>
+      <c r="B658" s="34"/>
     </row>
     <row r="659">
       <c r="A659" s="34"/>
+      <c r="B659" s="34"/>
     </row>
     <row r="660">
       <c r="A660" s="34"/>
+      <c r="B660" s="34"/>
     </row>
     <row r="661">
       <c r="A661" s="34"/>
+      <c r="B661" s="34"/>
     </row>
     <row r="662">
       <c r="A662" s="34"/>
+      <c r="B662" s="34"/>
     </row>
     <row r="663">
       <c r="A663" s="34"/>
+      <c r="B663" s="34"/>
     </row>
     <row r="664">
       <c r="A664" s="34"/>
+      <c r="B664" s="34"/>
     </row>
     <row r="665">
       <c r="A665" s="34"/>
+      <c r="B665" s="34"/>
     </row>
     <row r="666">
       <c r="A666" s="34"/>
+      <c r="B666" s="34"/>
     </row>
     <row r="667">
       <c r="A667" s="34"/>
+      <c r="B667" s="34"/>
     </row>
     <row r="668">
       <c r="A668" s="34"/>
+      <c r="B668" s="34"/>
     </row>
     <row r="669">
       <c r="A669" s="34"/>
+      <c r="B669" s="34"/>
     </row>
     <row r="670">
       <c r="A670" s="34"/>
+      <c r="B670" s="34"/>
     </row>
     <row r="671">
       <c r="A671" s="34"/>
+      <c r="B671" s="34"/>
     </row>
     <row r="672">
       <c r="A672" s="34"/>
+      <c r="B672" s="34"/>
     </row>
     <row r="673">
       <c r="A673" s="34"/>
+      <c r="B673" s="34"/>
     </row>
     <row r="674">
       <c r="A674" s="34"/>
+      <c r="B674" s="34"/>
     </row>
     <row r="675">
       <c r="A675" s="34"/>
+      <c r="B675" s="34"/>
     </row>
     <row r="676">
       <c r="A676" s="34"/>
+      <c r="B676" s="34"/>
     </row>
     <row r="677">
       <c r="A677" s="34"/>
+      <c r="B677" s="34"/>
     </row>
     <row r="678">
       <c r="A678" s="34"/>
+      <c r="B678" s="34"/>
     </row>
     <row r="679">
       <c r="A679" s="34"/>
+      <c r="B679" s="34"/>
     </row>
     <row r="680">
       <c r="A680" s="34"/>
+      <c r="B680" s="34"/>
     </row>
     <row r="681">
       <c r="A681" s="34"/>
+      <c r="B681" s="34"/>
     </row>
     <row r="682">
       <c r="A682" s="34"/>
+      <c r="B682" s="34"/>
     </row>
     <row r="683">
       <c r="A683" s="34"/>
+      <c r="B683" s="34"/>
     </row>
     <row r="684">
       <c r="A684" s="34"/>
+      <c r="B684" s="34"/>
     </row>
     <row r="685">
       <c r="A685" s="34"/>
+      <c r="B685" s="34"/>
     </row>
     <row r="686">
       <c r="A686" s="34"/>
+      <c r="B686" s="34"/>
     </row>
     <row r="687">
       <c r="A687" s="34"/>
+      <c r="B687" s="34"/>
     </row>
     <row r="688">
       <c r="A688" s="34"/>
+      <c r="B688" s="34"/>
     </row>
     <row r="689">
       <c r="A689" s="34"/>
+      <c r="B689" s="34"/>
     </row>
     <row r="690">
       <c r="A690" s="34"/>
+      <c r="B690" s="34"/>
     </row>
     <row r="691">
       <c r="A691" s="34"/>
+      <c r="B691" s="34"/>
     </row>
     <row r="692">
       <c r="A692" s="34"/>
+      <c r="B692" s="34"/>
     </row>
     <row r="693">
       <c r="A693" s="34"/>
+      <c r="B693" s="34"/>
     </row>
     <row r="694">
       <c r="A694" s="34"/>
+      <c r="B694" s="34"/>
     </row>
     <row r="695">
       <c r="A695" s="34"/>
+      <c r="B695" s="34"/>
     </row>
     <row r="696">
       <c r="A696" s="34"/>
+      <c r="B696" s="34"/>
     </row>
     <row r="697">
       <c r="A697" s="34"/>
+      <c r="B697" s="34"/>
     </row>
     <row r="698">
       <c r="A698" s="34"/>
+      <c r="B698" s="34"/>
     </row>
     <row r="699">
       <c r="A699" s="34"/>
+      <c r="B699" s="34"/>
     </row>
     <row r="700">
       <c r="A700" s="34"/>
+      <c r="B700" s="34"/>
     </row>
     <row r="701">
       <c r="A701" s="34"/>
+      <c r="B701" s="34"/>
     </row>
     <row r="702">
       <c r="A702" s="34"/>
+      <c r="B702" s="34"/>
     </row>
     <row r="703">
       <c r="A703" s="34"/>
+      <c r="B703" s="34"/>
     </row>
     <row r="704">
       <c r="A704" s="34"/>
+      <c r="B704" s="34"/>
     </row>
     <row r="705">
       <c r="A705" s="34"/>
+      <c r="B705" s="34"/>
     </row>
     <row r="706">
       <c r="A706" s="34"/>
+      <c r="B706" s="34"/>
     </row>
     <row r="707">
       <c r="A707" s="34"/>
+      <c r="B707" s="34"/>
     </row>
     <row r="708">
       <c r="A708" s="34"/>
+      <c r="B708" s="34"/>
     </row>
     <row r="709">
       <c r="A709" s="34"/>
+      <c r="B709" s="34"/>
     </row>
     <row r="710">
       <c r="A710" s="34"/>
+      <c r="B710" s="34"/>
     </row>
     <row r="711">
       <c r="A711" s="34"/>
+      <c r="B711" s="34"/>
     </row>
     <row r="712">
       <c r="A712" s="34"/>
+      <c r="B712" s="34"/>
     </row>
     <row r="713">
       <c r="A713" s="34"/>
+      <c r="B713" s="34"/>
     </row>
     <row r="714">
       <c r="A714" s="34"/>
+      <c r="B714" s="34"/>
     </row>
     <row r="715">
       <c r="A715" s="34"/>
+      <c r="B715" s="34"/>
     </row>
     <row r="716">
       <c r="A716" s="34"/>
+      <c r="B716" s="34"/>
     </row>
     <row r="717">
       <c r="A717" s="34"/>
+      <c r="B717" s="34"/>
     </row>
     <row r="718">
       <c r="A718" s="34"/>
+      <c r="B718" s="34"/>
     </row>
     <row r="719">
       <c r="A719" s="34"/>
+      <c r="B719" s="34"/>
     </row>
     <row r="720">
       <c r="A720" s="34"/>
+      <c r="B720" s="34"/>
     </row>
     <row r="721">
       <c r="A721" s="34"/>
+      <c r="B721" s="34"/>
     </row>
     <row r="722">
       <c r="A722" s="34"/>
+      <c r="B722" s="34"/>
     </row>
     <row r="723">
       <c r="A723" s="34"/>
+      <c r="B723" s="34"/>
     </row>
     <row r="724">
       <c r="A724" s="34"/>
+      <c r="B724" s="34"/>
     </row>
     <row r="725">
       <c r="A725" s="34"/>
+      <c r="B725" s="34"/>
     </row>
     <row r="726">
       <c r="A726" s="34"/>
+      <c r="B726" s="34"/>
     </row>
     <row r="727">
       <c r="A727" s="34"/>
+      <c r="B727" s="34"/>
     </row>
     <row r="728">
       <c r="A728" s="34"/>
+      <c r="B728" s="34"/>
     </row>
     <row r="729">
       <c r="A729" s="34"/>
+      <c r="B729" s="34"/>
     </row>
     <row r="730">
       <c r="A730" s="34"/>
+      <c r="B730" s="34"/>
     </row>
     <row r="731">
       <c r="A731" s="34"/>
+      <c r="B731" s="34"/>
     </row>
     <row r="732">
       <c r="A732" s="34"/>
+      <c r="B732" s="34"/>
     </row>
     <row r="733">
       <c r="A733" s="34"/>
+      <c r="B733" s="34"/>
     </row>
     <row r="734">
       <c r="A734" s="34"/>
+      <c r="B734" s="34"/>
     </row>
     <row r="735">
       <c r="A735" s="34"/>
+      <c r="B735" s="34"/>
     </row>
     <row r="736">
       <c r="A736" s="34"/>
+      <c r="B736" s="34"/>
     </row>
     <row r="737">
       <c r="A737" s="34"/>
+      <c r="B737" s="34"/>
     </row>
     <row r="738">
       <c r="A738" s="34"/>
+      <c r="B738" s="34"/>
     </row>
     <row r="739">
       <c r="A739" s="34"/>
+      <c r="B739" s="34"/>
     </row>
     <row r="740">
       <c r="A740" s="34"/>
+      <c r="B740" s="34"/>
     </row>
     <row r="741">
       <c r="A741" s="34"/>
+      <c r="B741" s="34"/>
     </row>
     <row r="742">
       <c r="A742" s="34"/>
+      <c r="B742" s="34"/>
     </row>
     <row r="743">
       <c r="A743" s="34"/>
+      <c r="B743" s="34"/>
     </row>
     <row r="744">
       <c r="A744" s="34"/>
+      <c r="B744" s="34"/>
     </row>
     <row r="745">
       <c r="A745" s="34"/>
+      <c r="B745" s="34"/>
     </row>
     <row r="746">
       <c r="A746" s="34"/>
+      <c r="B746" s="34"/>
     </row>
     <row r="747">
       <c r="A747" s="34"/>
+      <c r="B747" s="34"/>
     </row>
     <row r="748">
       <c r="A748" s="34"/>
+      <c r="B748" s="34"/>
     </row>
     <row r="749">
       <c r="A749" s="34"/>
+      <c r="B749" s="34"/>
     </row>
     <row r="750">
       <c r="A750" s="34"/>
+      <c r="B750" s="34"/>
     </row>
     <row r="751">
       <c r="A751" s="34"/>
+      <c r="B751" s="34"/>
     </row>
     <row r="752">
       <c r="A752" s="34"/>
+      <c r="B752" s="34"/>
     </row>
     <row r="753">
       <c r="A753" s="34"/>
+      <c r="B753" s="34"/>
     </row>
     <row r="754">
       <c r="A754" s="34"/>
+      <c r="B754" s="34"/>
     </row>
     <row r="755">
       <c r="A755" s="34"/>
+      <c r="B755" s="34"/>
     </row>
     <row r="756">
       <c r="A756" s="34"/>
+      <c r="B756" s="34"/>
     </row>
     <row r="757">
       <c r="A757" s="34"/>
+      <c r="B757" s="34"/>
     </row>
     <row r="758">
       <c r="A758" s="34"/>
+      <c r="B758" s="34"/>
     </row>
     <row r="759">
       <c r="A759" s="34"/>
+      <c r="B759" s="34"/>
     </row>
     <row r="760">
       <c r="A760" s="34"/>
+      <c r="B760" s="34"/>
     </row>
     <row r="761">
       <c r="A761" s="34"/>
+      <c r="B761" s="34"/>
     </row>
     <row r="762">
       <c r="A762" s="34"/>
+      <c r="B762" s="34"/>
     </row>
     <row r="763">
       <c r="A763" s="34"/>
+      <c r="B763" s="34"/>
     </row>
     <row r="764">
       <c r="A764" s="34"/>
+      <c r="B764" s="34"/>
     </row>
     <row r="765">
       <c r="A765" s="34"/>
+      <c r="B765" s="34"/>
     </row>
     <row r="766">
       <c r="A766" s="34"/>
+      <c r="B766" s="34"/>
     </row>
     <row r="767">
       <c r="A767" s="34"/>
+      <c r="B767" s="34"/>
     </row>
     <row r="768">
       <c r="A768" s="34"/>
+      <c r="B768" s="34"/>
     </row>
     <row r="769">
       <c r="A769" s="34"/>
+      <c r="B769" s="34"/>
     </row>
     <row r="770">
       <c r="A770" s="34"/>
+      <c r="B770" s="34"/>
     </row>
     <row r="771">
       <c r="A771" s="34"/>
+      <c r="B771" s="34"/>
     </row>
     <row r="772">
       <c r="A772" s="34"/>
+      <c r="B772" s="34"/>
     </row>
     <row r="773">
       <c r="A773" s="34"/>
+      <c r="B773" s="34"/>
     </row>
     <row r="774">
       <c r="A774" s="34"/>
+      <c r="B774" s="34"/>
     </row>
     <row r="775">
       <c r="A775" s="34"/>
+      <c r="B775" s="34"/>
     </row>
     <row r="776">
       <c r="A776" s="34"/>
+      <c r="B776" s="34"/>
     </row>
     <row r="777">
       <c r="A777" s="34"/>
+      <c r="B777" s="34"/>
     </row>
     <row r="778">
       <c r="A778" s="34"/>
+      <c r="B778" s="34"/>
     </row>
     <row r="779">
       <c r="A779" s="34"/>
+      <c r="B779" s="34"/>
     </row>
     <row r="780">
       <c r="A780" s="34"/>
+      <c r="B780" s="34"/>
     </row>
     <row r="781">
       <c r="A781" s="34"/>
+      <c r="B781" s="34"/>
     </row>
     <row r="782">
       <c r="A782" s="34"/>
+      <c r="B782" s="34"/>
     </row>
     <row r="783">
       <c r="A783" s="34"/>
+      <c r="B783" s="34"/>
     </row>
     <row r="784">
       <c r="A784" s="34"/>
+      <c r="B784" s="34"/>
     </row>
     <row r="785">
       <c r="A785" s="34"/>
+      <c r="B785" s="34"/>
     </row>
     <row r="786">
       <c r="A786" s="34"/>
+      <c r="B786" s="34"/>
     </row>
     <row r="787">
       <c r="A787" s="34"/>
+      <c r="B787" s="34"/>
     </row>
     <row r="788">
       <c r="A788" s="34"/>
+      <c r="B788" s="34"/>
     </row>
     <row r="789">
       <c r="A789" s="34"/>
+      <c r="B789" s="34"/>
     </row>
     <row r="790">
       <c r="A790" s="34"/>
+      <c r="B790" s="34"/>
     </row>
     <row r="791">
       <c r="A791" s="34"/>
+      <c r="B791" s="34"/>
     </row>
     <row r="792">
       <c r="A792" s="34"/>
+      <c r="B792" s="34"/>
     </row>
     <row r="793">
       <c r="A793" s="34"/>
+      <c r="B793" s="34"/>
     </row>
     <row r="794">
       <c r="A794" s="34"/>
+      <c r="B794" s="34"/>
     </row>
     <row r="795">
       <c r="A795" s="34"/>
+      <c r="B795" s="34"/>
     </row>
     <row r="796">
       <c r="A796" s="34"/>
+      <c r="B796" s="34"/>
     </row>
     <row r="797">
       <c r="A797" s="34"/>
+      <c r="B797" s="34"/>
     </row>
     <row r="798">
       <c r="A798" s="34"/>
+      <c r="B798" s="34"/>
     </row>
     <row r="799">
       <c r="A799" s="34"/>
+      <c r="B799" s="34"/>
     </row>
     <row r="800">
       <c r="A800" s="34"/>
+      <c r="B800" s="34"/>
     </row>
     <row r="801">
       <c r="A801" s="34"/>
+      <c r="B801" s="34"/>
     </row>
     <row r="802">
       <c r="A802" s="34"/>
+      <c r="B802" s="34"/>
     </row>
     <row r="803">
       <c r="A803" s="34"/>
+      <c r="B803" s="34"/>
     </row>
     <row r="804">
       <c r="A804" s="34"/>
+      <c r="B804" s="34"/>
     </row>
     <row r="805">
       <c r="A805" s="34"/>
+      <c r="B805" s="34"/>
     </row>
     <row r="806">
       <c r="A806" s="34"/>
+      <c r="B806" s="34"/>
     </row>
     <row r="807">
       <c r="A807" s="34"/>
+      <c r="B807" s="34"/>
     </row>
     <row r="808">
       <c r="A808" s="34"/>
+      <c r="B808" s="34"/>
     </row>
     <row r="809">
       <c r="A809" s="34"/>
+      <c r="B809" s="34"/>
     </row>
     <row r="810">
       <c r="A810" s="34"/>
+      <c r="B810" s="34"/>
     </row>
     <row r="811">
       <c r="A811" s="34"/>
+      <c r="B811" s="34"/>
     </row>
     <row r="812">
       <c r="A812" s="34"/>
+      <c r="B812" s="34"/>
     </row>
     <row r="813">
       <c r="A813" s="34"/>
+      <c r="B813" s="34"/>
     </row>
     <row r="814">
       <c r="A814" s="34"/>
+      <c r="B814" s="34"/>
     </row>
     <row r="815">
       <c r="A815" s="34"/>
+      <c r="B815" s="34"/>
     </row>
     <row r="816">
       <c r="A816" s="34"/>
+      <c r="B816" s="34"/>
     </row>
     <row r="817">
       <c r="A817" s="34"/>
+      <c r="B817" s="34"/>
     </row>
     <row r="818">
       <c r="A818" s="34"/>
+      <c r="B818" s="34"/>
     </row>
     <row r="819">
       <c r="A819" s="34"/>
+      <c r="B819" s="34"/>
     </row>
     <row r="820">
       <c r="A820" s="34"/>
+      <c r="B820" s="34"/>
     </row>
     <row r="821">
       <c r="A821" s="34"/>
+      <c r="B821" s="34"/>
     </row>
     <row r="822">
       <c r="A822" s="34"/>
+      <c r="B822" s="34"/>
     </row>
     <row r="823">
       <c r="A823" s="34"/>
+      <c r="B823" s="34"/>
     </row>
     <row r="824">
       <c r="A824" s="34"/>
+      <c r="B824" s="34"/>
     </row>
     <row r="825">
       <c r="A825" s="34"/>
+      <c r="B825" s="34"/>
     </row>
     <row r="826">
       <c r="A826" s="34"/>
+      <c r="B826" s="34"/>
     </row>
     <row r="827">
       <c r="A827" s="34"/>
+      <c r="B827" s="34"/>
     </row>
     <row r="828">
       <c r="A828" s="34"/>
+      <c r="B828" s="34"/>
     </row>
     <row r="829">
       <c r="A829" s="34"/>
+      <c r="B829" s="34"/>
     </row>
     <row r="830">
       <c r="A830" s="34"/>
+      <c r="B830" s="34"/>
     </row>
     <row r="831">
       <c r="A831" s="34"/>
+      <c r="B831" s="34"/>
     </row>
     <row r="832">
       <c r="A832" s="34"/>
+      <c r="B832" s="34"/>
     </row>
     <row r="833">
       <c r="A833" s="34"/>
+      <c r="B833" s="34"/>
     </row>
     <row r="834">
       <c r="A834" s="34"/>
+      <c r="B834" s="34"/>
     </row>
     <row r="835">
       <c r="A835" s="34"/>
+      <c r="B835" s="34"/>
     </row>
     <row r="836">
       <c r="A836" s="34"/>
+      <c r="B836" s="34"/>
     </row>
     <row r="837">
       <c r="A837" s="34"/>
+      <c r="B837" s="34"/>
     </row>
     <row r="838">
       <c r="A838" s="34"/>
+      <c r="B838" s="34"/>
     </row>
     <row r="839">
       <c r="A839" s="34"/>
+      <c r="B839" s="34"/>
     </row>
     <row r="840">
       <c r="A840" s="34"/>
+      <c r="B840" s="34"/>
     </row>
     <row r="841">
       <c r="A841" s="34"/>
+      <c r="B841" s="34"/>
     </row>
     <row r="842">
       <c r="A842" s="34"/>
+      <c r="B842" s="34"/>
     </row>
     <row r="843">
       <c r="A843" s="34"/>
+      <c r="B843" s="34"/>
     </row>
     <row r="844">
       <c r="A844" s="34"/>
+      <c r="B844" s="34"/>
     </row>
     <row r="845">
       <c r="A845" s="34"/>
+      <c r="B845" s="34"/>
     </row>
     <row r="846">
       <c r="A846" s="34"/>
+      <c r="B846" s="34"/>
     </row>
     <row r="847">
       <c r="A847" s="34"/>
+      <c r="B847" s="34"/>
     </row>
     <row r="848">
       <c r="A848" s="34"/>
+      <c r="B848" s="34"/>
     </row>
     <row r="849">
       <c r="A849" s="34"/>
+      <c r="B849" s="34"/>
     </row>
     <row r="850">
       <c r="A850" s="34"/>
+      <c r="B850" s="34"/>
     </row>
     <row r="851">
       <c r="A851" s="34"/>
+      <c r="B851" s="34"/>
     </row>
     <row r="852">
       <c r="A852" s="34"/>
+      <c r="B852" s="34"/>
     </row>
     <row r="853">
       <c r="A853" s="34"/>
+      <c r="B853" s="34"/>
     </row>
     <row r="854">
       <c r="A854" s="34"/>
+      <c r="B854" s="34"/>
     </row>
     <row r="855">
       <c r="A855" s="34"/>
+      <c r="B855" s="34"/>
     </row>
     <row r="856">
       <c r="A856" s="34"/>
+      <c r="B856" s="34"/>
     </row>
     <row r="857">
       <c r="A857" s="34"/>
+      <c r="B857" s="34"/>
     </row>
     <row r="858">
       <c r="A858" s="34"/>
+      <c r="B858" s="34"/>
     </row>
     <row r="859">
       <c r="A859" s="34"/>
+      <c r="B859" s="34"/>
     </row>
     <row r="860">
       <c r="A860" s="34"/>
+      <c r="B860" s="34"/>
     </row>
     <row r="861">
       <c r="A861" s="34"/>
+      <c r="B861" s="34"/>
     </row>
     <row r="862">
       <c r="A862" s="34"/>
+      <c r="B862" s="34"/>
     </row>
     <row r="863">
       <c r="A863" s="34"/>
+      <c r="B863" s="34"/>
     </row>
     <row r="864">
       <c r="A864" s="34"/>
+      <c r="B864" s="34"/>
     </row>
     <row r="865">
       <c r="A865" s="34"/>
+      <c r="B865" s="34"/>
     </row>
     <row r="866">
       <c r="A866" s="34"/>
+      <c r="B866" s="34"/>
     </row>
     <row r="867">
       <c r="A867" s="34"/>
+      <c r="B867" s="34"/>
     </row>
     <row r="868">
       <c r="A868" s="34"/>
+      <c r="B868" s="34"/>
     </row>
     <row r="869">
       <c r="A869" s="34"/>
+      <c r="B869" s="34"/>
     </row>
     <row r="870">
       <c r="A870" s="34"/>
+      <c r="B870" s="34"/>
     </row>
     <row r="871">
       <c r="A871" s="34"/>
+      <c r="B871" s="34"/>
     </row>
     <row r="872">
       <c r="A872" s="34"/>
+      <c r="B872" s="34"/>
     </row>
     <row r="873">
       <c r="A873" s="34"/>
+      <c r="B873" s="34"/>
     </row>
     <row r="874">
       <c r="A874" s="34"/>
+      <c r="B874" s="34"/>
     </row>
     <row r="875">
       <c r="A875" s="34"/>
+      <c r="B875" s="34"/>
     </row>
     <row r="876">
       <c r="A876" s="34"/>
+      <c r="B876" s="34"/>
     </row>
     <row r="877">
       <c r="A877" s="34"/>
+      <c r="B877" s="34"/>
     </row>
     <row r="878">
       <c r="A878" s="34"/>
+      <c r="B878" s="34"/>
     </row>
     <row r="879">
       <c r="A879" s="34"/>
+      <c r="B879" s="34"/>
     </row>
     <row r="880">
       <c r="A880" s="34"/>
+      <c r="B880" s="34"/>
     </row>
     <row r="881">
       <c r="A881" s="34"/>
+      <c r="B881" s="34"/>
     </row>
     <row r="882">
       <c r="A882" s="34"/>
+      <c r="B882" s="34"/>
     </row>
     <row r="883">
       <c r="A883" s="34"/>
+      <c r="B883" s="34"/>
     </row>
     <row r="884">
       <c r="A884" s="34"/>
+      <c r="B884" s="34"/>
     </row>
     <row r="885">
       <c r="A885" s="34"/>
+      <c r="B885" s="34"/>
     </row>
     <row r="886">
       <c r="A886" s="34"/>
+      <c r="B886" s="34"/>
     </row>
     <row r="887">
       <c r="A887" s="34"/>
+      <c r="B887" s="34"/>
     </row>
     <row r="888">
       <c r="A888" s="34"/>
+      <c r="B888" s="34"/>
     </row>
     <row r="889">
       <c r="A889" s="34"/>
+      <c r="B889" s="34"/>
     </row>
     <row r="890">
       <c r="A890" s="34"/>
+      <c r="B890" s="34"/>
     </row>
     <row r="891">
       <c r="A891" s="34"/>
+      <c r="B891" s="34"/>
     </row>
     <row r="892">
       <c r="A892" s="34"/>
+      <c r="B892" s="34"/>
     </row>
     <row r="893">
       <c r="A893" s="34"/>
+      <c r="B893" s="34"/>
     </row>
     <row r="894">
       <c r="A894" s="34"/>
+      <c r="B894" s="34"/>
     </row>
     <row r="895">
       <c r="A895" s="34"/>
+      <c r="B895" s="34"/>
     </row>
     <row r="896">
       <c r="A896" s="34"/>
+      <c r="B896" s="34"/>
     </row>
     <row r="897">
       <c r="A897" s="34"/>
+      <c r="B897" s="34"/>
     </row>
     <row r="898">
       <c r="A898" s="34"/>
+      <c r="B898" s="34"/>
     </row>
     <row r="899">
       <c r="A899" s="34"/>
+      <c r="B899" s="34"/>
     </row>
     <row r="900">
       <c r="A900" s="34"/>
+      <c r="B900" s="34"/>
     </row>
     <row r="901">
       <c r="A901" s="34"/>
+      <c r="B901" s="34"/>
     </row>
     <row r="902">
       <c r="A902" s="34"/>
+      <c r="B902" s="34"/>
     </row>
     <row r="903">
       <c r="A903" s="34"/>
+      <c r="B903" s="34"/>
     </row>
     <row r="904">
       <c r="A904" s="34"/>
+      <c r="B904" s="34"/>
     </row>
     <row r="905">
       <c r="A905" s="34"/>
+      <c r="B905" s="34"/>
     </row>
     <row r="906">
       <c r="A906" s="34"/>
+      <c r="B906" s="34"/>
     </row>
     <row r="907">
       <c r="A907" s="34"/>
+      <c r="B907" s="34"/>
     </row>
     <row r="908">
       <c r="A908" s="34"/>
+      <c r="B908" s="34"/>
     </row>
     <row r="909">
       <c r="A909" s="34"/>
+      <c r="B909" s="34"/>
     </row>
     <row r="910">
       <c r="A910" s="34"/>
+      <c r="B910" s="34"/>
     </row>
     <row r="911">
       <c r="A911" s="34"/>
+      <c r="B911" s="34"/>
     </row>
     <row r="912">
       <c r="A912" s="34"/>
+      <c r="B912" s="34"/>
     </row>
     <row r="913">
       <c r="A913" s="34"/>
+      <c r="B913" s="34"/>
     </row>
     <row r="914">
       <c r="A914" s="34"/>
+      <c r="B914" s="34"/>
     </row>
     <row r="915">
       <c r="A915" s="34"/>
+      <c r="B915" s="34"/>
     </row>
     <row r="916">
       <c r="A916" s="34"/>
+      <c r="B916" s="34"/>
     </row>
     <row r="917">
       <c r="A917" s="34"/>
+      <c r="B917" s="34"/>
     </row>
     <row r="918">
       <c r="A918" s="34"/>
+      <c r="B918" s="34"/>
     </row>
     <row r="919">
       <c r="A919" s="34"/>
+      <c r="B919" s="34"/>
     </row>
     <row r="920">
       <c r="A920" s="34"/>
+      <c r="B920" s="34"/>
     </row>
     <row r="921">
       <c r="A921" s="34"/>
+      <c r="B921" s="34"/>
     </row>
     <row r="922">
       <c r="A922" s="34"/>
+      <c r="B922" s="34"/>
     </row>
     <row r="923">
       <c r="A923" s="34"/>
+      <c r="B923" s="34"/>
     </row>
     <row r="924">
       <c r="A924" s="34"/>
+      <c r="B924" s="34"/>
     </row>
     <row r="925">
       <c r="A925" s="34"/>
+      <c r="B925" s="34"/>
     </row>
     <row r="926">
       <c r="A926" s="34"/>
+      <c r="B926" s="34"/>
     </row>
     <row r="927">
       <c r="A927" s="34"/>
+      <c r="B927" s="34"/>
     </row>
     <row r="928">
       <c r="A928" s="34"/>
+      <c r="B928" s="34"/>
     </row>
     <row r="929">
       <c r="A929" s="34"/>
+      <c r="B929" s="34"/>
     </row>
     <row r="930">
       <c r="A930" s="34"/>
+      <c r="B930" s="34"/>
     </row>
     <row r="931">
       <c r="A931" s="34"/>
+      <c r="B931" s="34"/>
     </row>
     <row r="932">
       <c r="A932" s="34"/>
+      <c r="B932" s="34"/>
     </row>
     <row r="933">
       <c r="A933" s="34"/>
+      <c r="B933" s="34"/>
     </row>
     <row r="934">
       <c r="A934" s="34"/>
+      <c r="B934" s="34"/>
     </row>
     <row r="935">
       <c r="A935" s="34"/>
+      <c r="B935" s="34"/>
     </row>
     <row r="936">
       <c r="A936" s="34"/>
+      <c r="B936" s="34"/>
     </row>
     <row r="937">
       <c r="A937" s="34"/>
+      <c r="B937" s="34"/>
     </row>
     <row r="938">
       <c r="A938" s="34"/>
+      <c r="B938" s="34"/>
     </row>
     <row r="939">
       <c r="A939" s="34"/>
+      <c r="B939" s="34"/>
     </row>
     <row r="940">
       <c r="A940" s="34"/>
+      <c r="B940" s="34"/>
     </row>
     <row r="941">
       <c r="A941" s="34"/>
+      <c r="B941" s="34"/>
     </row>
     <row r="942">
       <c r="A942" s="34"/>
+      <c r="B942" s="34"/>
     </row>
     <row r="943">
       <c r="A943" s="34"/>
+      <c r="B943" s="34"/>
     </row>
     <row r="944">
       <c r="A944" s="34"/>
+      <c r="B944" s="34"/>
     </row>
     <row r="945">
       <c r="A945" s="34"/>
+      <c r="B945" s="34"/>
     </row>
     <row r="946">
       <c r="A946" s="34"/>
+      <c r="B946" s="34"/>
     </row>
     <row r="947">
       <c r="A947" s="34"/>
+      <c r="B947" s="34"/>
     </row>
     <row r="948">
       <c r="A948" s="34"/>
+      <c r="B948" s="34"/>
     </row>
     <row r="949">
       <c r="A949" s="34"/>
+      <c r="B949" s="34"/>
     </row>
     <row r="950">
       <c r="A950" s="34"/>
+      <c r="B950" s="34"/>
     </row>
     <row r="951">
       <c r="A951" s="34"/>
+      <c r="B951" s="34"/>
     </row>
     <row r="952">
       <c r="A952" s="34"/>
+      <c r="B952" s="34"/>
     </row>
     <row r="953">
       <c r="A953" s="34"/>
+      <c r="B953" s="34"/>
     </row>
     <row r="954">
       <c r="A954" s="34"/>
+      <c r="B954" s="34"/>
     </row>
     <row r="955">
       <c r="A955" s="34"/>
+      <c r="B955" s="34"/>
     </row>
     <row r="956">
       <c r="A956" s="34"/>
+      <c r="B956" s="34"/>
     </row>
     <row r="957">
       <c r="A957" s="34"/>
+      <c r="B957" s="34"/>
     </row>
     <row r="958">
       <c r="A958" s="34"/>
+      <c r="B958" s="34"/>
     </row>
     <row r="959">
       <c r="A959" s="34"/>
+      <c r="B959" s="34"/>
     </row>
     <row r="960">
       <c r="A960" s="34"/>
+      <c r="B960" s="34"/>
     </row>
     <row r="961">
       <c r="A961" s="34"/>
+      <c r="B961" s="34"/>
     </row>
     <row r="962">
       <c r="A962" s="34"/>
+      <c r="B962" s="34"/>
     </row>
     <row r="963">
       <c r="A963" s="34"/>
+      <c r="B963" s="34"/>
     </row>
     <row r="964">
       <c r="A964" s="34"/>
+      <c r="B964" s="34"/>
     </row>
     <row r="965">
       <c r="A965" s="34"/>
+      <c r="B965" s="34"/>
     </row>
     <row r="966">
       <c r="A966" s="34"/>
+      <c r="B966" s="34"/>
     </row>
     <row r="967">
       <c r="A967" s="34"/>
+      <c r="B967" s="34"/>
     </row>
     <row r="968">
       <c r="A968" s="34"/>
+      <c r="B968" s="34"/>
     </row>
     <row r="969">
       <c r="A969" s="34"/>
+      <c r="B969" s="34"/>
     </row>
     <row r="970">
       <c r="A970" s="34"/>
+      <c r="B970" s="34"/>
     </row>
     <row r="971">
       <c r="A971" s="34"/>
+      <c r="B971" s="34"/>
     </row>
     <row r="972">
       <c r="A972" s="34"/>
+      <c r="B972" s="34"/>
     </row>
     <row r="973">
       <c r="A973" s="34"/>
+      <c r="B973" s="34"/>
     </row>
     <row r="974">
       <c r="A974" s="34"/>
+      <c r="B974" s="34"/>
     </row>
     <row r="975">
       <c r="A975" s="34"/>
+      <c r="B975" s="34"/>
     </row>
     <row r="976">
       <c r="A976" s="34"/>
+      <c r="B976" s="34"/>
     </row>
     <row r="977">
       <c r="A977" s="34"/>
+      <c r="B977" s="34"/>
     </row>
     <row r="978">
       <c r="A978" s="34"/>
+      <c r="B978" s="34"/>
     </row>
     <row r="979">
       <c r="A979" s="34"/>
+      <c r="B979" s="34"/>
     </row>
     <row r="980">
       <c r="A980" s="34"/>
+      <c r="B980" s="34"/>
     </row>
     <row r="981">
       <c r="A981" s="34"/>
+      <c r="B981" s="34"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
@@ -6613,45 +8037,45 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="4" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>175</v>
+        <v>191</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>176</v>
+        <v>192</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>177</v>
+        <v>193</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>178</v>
+        <v>194</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>179</v>
+        <v>195</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>180</v>
+        <v>196</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>181</v>
+        <v>197</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>182</v>
+        <v>198</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>183</v>
+        <v>199</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="35" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="B2" s="36" t="s">
-        <v>184</v>
+        <v>200</v>
       </c>
       <c r="C2" s="36" t="s">
-        <v>185</v>
+        <v>201</v>
       </c>
       <c r="D2" s="4"/>
       <c r="E2" s="3">
@@ -6663,13 +8087,13 @@
     </row>
     <row r="3">
       <c r="A3" s="37" t="s">
-        <v>186</v>
+        <v>202</v>
       </c>
       <c r="B3" s="36" t="s">
-        <v>187</v>
+        <v>203</v>
       </c>
       <c r="C3" s="38" t="s">
-        <v>188</v>
+        <v>204</v>
       </c>
       <c r="D3" s="4"/>
       <c r="E3" s="5">
@@ -6680,21 +8104,21 @@
       </c>
       <c r="G3" s="4"/>
       <c r="H3" s="3" t="s">
-        <v>189</v>
+        <v>205</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>190</v>
+        <v>206</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>191</v>
+        <v>207</v>
       </c>
       <c r="B4" s="39" t="s">
-        <v>192</v>
+        <v>208</v>
       </c>
       <c r="C4" s="39" t="s">
-        <v>193</v>
+        <v>209</v>
       </c>
       <c r="D4" s="4"/>
       <c r="E4" s="2">
@@ -6707,13 +8131,13 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>194</v>
+        <v>210</v>
       </c>
       <c r="B5" s="40" t="s">
-        <v>195</v>
+        <v>211</v>
       </c>
       <c r="C5" s="40" t="s">
-        <v>196</v>
+        <v>212</v>
       </c>
       <c r="E5" s="3">
         <v>-10.0</v>
@@ -6724,13 +8148,13 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>197</v>
+        <v>213</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>198</v>
+        <v>214</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>199</v>
+        <v>215</v>
       </c>
       <c r="E6" s="3">
         <v>0.0</v>
@@ -6741,13 +8165,13 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>200</v>
+        <v>216</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>201</v>
+        <v>217</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>202</v>
+        <v>218</v>
       </c>
       <c r="E7" s="3">
         <v>-10.0</v>
@@ -6758,18 +8182,41 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>203</v>
+        <v>219</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>204</v>
+        <v>220</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>205</v>
+        <v>221</v>
       </c>
       <c r="E8" s="3">
         <v>0.0</v>
       </c>
       <c r="F8" s="3">
+        <v>-10.0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="E9" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="F9" s="3">
+        <v>-10.0</v>
+      </c>
+      <c r="G9" s="3">
         <v>-10.0</v>
       </c>
     </row>

--- a/Assets/02Script/Table/EventTable.xlsx
+++ b/Assets/02Script/Table/EventTable.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="681" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="684" uniqueCount="225">
   <si>
     <t>EventID</t>
   </si>
@@ -8219,6 +8219,15 @@
       <c r="G9" s="3">
         <v>-10.0</v>
       </c>
+      <c r="H9" s="32" t="s">
+        <v>182</v>
+      </c>
+      <c r="I9" s="32" t="s">
+        <v>185</v>
+      </c>
+      <c r="J9" s="32" t="s">
+        <v>188</v>
+      </c>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>

--- a/Assets/02Script/Table/EventTable.xlsx
+++ b/Assets/02Script/Table/EventTable.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="684" uniqueCount="225">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="628" uniqueCount="213">
   <si>
     <t>EventID</t>
   </si>
@@ -556,51 +556,6 @@
     <t>우선.. 이 열쇠가 맞는지 확인해 봐야겠다.</t>
   </si>
   <si>
-    <t>E020</t>
-  </si>
-  <si>
-    <t>임시입니다!!!!!</t>
-  </si>
-  <si>
-    <t>개발자</t>
-  </si>
-  <si>
-    <t>이벤트용 선택지 테스트 중입니다</t>
-  </si>
-  <si>
-    <t>멍멍멍멍아르르르르??</t>
-  </si>
-  <si>
-    <t>C008</t>
-  </si>
-  <si>
-    <t>E020_0</t>
-  </si>
-  <si>
-    <t>정답은 멍멍이였습니다~~~</t>
-  </si>
-  <si>
-    <t>짝짝짝짝짝</t>
-  </si>
-  <si>
-    <t>E020_1</t>
-  </si>
-  <si>
-    <t>겠냐?</t>
-  </si>
-  <si>
-    <t>ㅉㅉ</t>
-  </si>
-  <si>
-    <t>E020_2</t>
-  </si>
-  <si>
-    <t>좀만 더 힘내자...</t>
-  </si>
-  <si>
-    <t>얼마...안남았을걸?</t>
-  </si>
-  <si>
     <t>Choice0</t>
   </si>
   <si>
@@ -681,6 +636,12 @@
     <t>어.. 고양이?</t>
   </si>
   <si>
+    <t>N006_0</t>
+  </si>
+  <si>
+    <t>N006_1</t>
+  </si>
+  <si>
     <t>C006</t>
   </si>
   <si>
@@ -690,6 +651,12 @@
     <t>정답은 8이야.</t>
   </si>
   <si>
+    <t>N007_0</t>
+  </si>
+  <si>
+    <t>N007_1</t>
+  </si>
+  <si>
     <t>C007</t>
   </si>
   <si>
@@ -699,13 +666,10 @@
     <t>403,002,187,492??</t>
   </si>
   <si>
-    <t>정답! 강아지!!</t>
-  </si>
-  <si>
-    <t>음.. 고양이?</t>
-  </si>
-  <si>
-    <t>하....죽같다</t>
+    <t>N008_0</t>
+  </si>
+  <si>
+    <t>N008_1</t>
   </si>
 </sst>
 </file>
@@ -4176,268 +4140,40 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="32" t="s">
-        <v>176</v>
-      </c>
-      <c r="B80" s="32" t="s">
-        <v>176</v>
-      </c>
-      <c r="C80" s="3">
-        <v>20001.0</v>
-      </c>
-      <c r="D80" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="E80" s="3">
-        <v>20002.0</v>
-      </c>
-      <c r="F80" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="G80" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="I80" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="J80" s="3">
-        <v>0.0</v>
-      </c>
+      <c r="A80" s="32"/>
+      <c r="B80" s="32"/>
     </row>
     <row r="81">
-      <c r="A81" s="32" t="s">
-        <v>176</v>
-      </c>
-      <c r="B81" s="32" t="s">
-        <v>176</v>
-      </c>
-      <c r="C81" s="3">
-        <v>20002.0</v>
-      </c>
-      <c r="D81" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="E81" s="3">
-        <v>20003.0</v>
-      </c>
-      <c r="F81" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="G81" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="I81" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="J81" s="3">
-        <v>0.0</v>
-      </c>
+      <c r="A81" s="32"/>
+      <c r="B81" s="32"/>
     </row>
     <row r="82">
-      <c r="A82" s="32" t="s">
-        <v>176</v>
-      </c>
-      <c r="B82" s="32" t="s">
-        <v>176</v>
-      </c>
-      <c r="C82" s="3">
-        <v>20003.0</v>
-      </c>
-      <c r="D82" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="E82" s="3">
-        <v>-1.0</v>
-      </c>
-      <c r="F82" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="G82" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H82" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="I82" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="J82" s="3">
-        <v>0.0</v>
-      </c>
+      <c r="A82" s="32"/>
+      <c r="B82" s="32"/>
     </row>
     <row r="83">
-      <c r="A83" s="32" t="s">
-        <v>176</v>
-      </c>
-      <c r="B83" s="32" t="s">
-        <v>182</v>
-      </c>
-      <c r="C83" s="3">
-        <v>20004.0</v>
-      </c>
-      <c r="D83" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="E83" s="3">
-        <v>20005.0</v>
-      </c>
-      <c r="F83" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="G83" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="I83" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="J83" s="3">
-        <v>0.0</v>
-      </c>
+      <c r="A83" s="32"/>
+      <c r="B83" s="32"/>
     </row>
     <row r="84">
-      <c r="A84" s="32" t="s">
-        <v>176</v>
-      </c>
-      <c r="B84" s="32" t="s">
-        <v>182</v>
-      </c>
-      <c r="C84" s="3">
-        <v>20005.0</v>
-      </c>
-      <c r="D84" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="E84" s="3">
-        <v>-1.0</v>
-      </c>
-      <c r="F84" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="G84" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="I84" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="J84" s="3">
-        <v>0.0</v>
-      </c>
+      <c r="A84" s="32"/>
+      <c r="B84" s="32"/>
     </row>
     <row r="85">
-      <c r="A85" s="32" t="s">
-        <v>176</v>
-      </c>
-      <c r="B85" s="32" t="s">
-        <v>185</v>
-      </c>
-      <c r="C85" s="3">
-        <v>20006.0</v>
-      </c>
-      <c r="D85" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="E85" s="3">
-        <v>20007.0</v>
-      </c>
-      <c r="F85" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="G85" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="I85" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="J85" s="3">
-        <v>0.0</v>
-      </c>
+      <c r="A85" s="32"/>
+      <c r="B85" s="32"/>
     </row>
     <row r="86">
-      <c r="A86" s="32" t="s">
-        <v>176</v>
-      </c>
-      <c r="B86" s="32" t="s">
-        <v>185</v>
-      </c>
-      <c r="C86" s="3">
-        <v>20007.0</v>
-      </c>
-      <c r="D86" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="E86" s="3">
-        <v>-1.0</v>
-      </c>
-      <c r="F86" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="G86" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="I86" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="J86" s="3">
-        <v>0.0</v>
-      </c>
+      <c r="A86" s="32"/>
+      <c r="B86" s="32"/>
     </row>
     <row r="87">
-      <c r="A87" s="32" t="s">
-        <v>176</v>
-      </c>
-      <c r="B87" s="32" t="s">
-        <v>188</v>
-      </c>
-      <c r="C87" s="3">
-        <v>20008.0</v>
-      </c>
-      <c r="D87" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="E87" s="3">
-        <v>20009.0</v>
-      </c>
-      <c r="F87" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="G87" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="I87" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="J87" s="3">
-        <v>0.0</v>
-      </c>
+      <c r="A87" s="32"/>
+      <c r="B87" s="32"/>
     </row>
     <row r="88">
-      <c r="A88" s="32" t="s">
-        <v>176</v>
-      </c>
-      <c r="B88" s="32" t="s">
-        <v>188</v>
-      </c>
-      <c r="C88" s="3">
-        <v>20009.0</v>
-      </c>
-      <c r="D88" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="E88" s="3">
-        <v>-1.0</v>
-      </c>
-      <c r="F88" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="G88" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="I88" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="J88" s="3">
-        <v>0.0</v>
-      </c>
+      <c r="A88" s="32"/>
+      <c r="B88" s="32"/>
     </row>
     <row r="89">
       <c r="A89" s="34"/>
@@ -8040,31 +7776,31 @@
         <v>87</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>191</v>
+        <v>176</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>192</v>
+        <v>177</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>193</v>
+        <v>178</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>194</v>
+        <v>179</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>195</v>
+        <v>180</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>196</v>
+        <v>181</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>197</v>
+        <v>182</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>198</v>
+        <v>183</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>199</v>
+        <v>184</v>
       </c>
     </row>
     <row r="2">
@@ -8072,10 +7808,10 @@
         <v>124</v>
       </c>
       <c r="B2" s="36" t="s">
-        <v>200</v>
+        <v>185</v>
       </c>
       <c r="C2" s="36" t="s">
-        <v>201</v>
+        <v>186</v>
       </c>
       <c r="D2" s="4"/>
       <c r="E2" s="3">
@@ -8087,13 +7823,13 @@
     </row>
     <row r="3">
       <c r="A3" s="37" t="s">
-        <v>202</v>
+        <v>187</v>
       </c>
       <c r="B3" s="36" t="s">
-        <v>203</v>
+        <v>188</v>
       </c>
       <c r="C3" s="38" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="D3" s="4"/>
       <c r="E3" s="5">
@@ -8104,21 +7840,21 @@
       </c>
       <c r="G3" s="4"/>
       <c r="H3" s="3" t="s">
-        <v>205</v>
+        <v>190</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>206</v>
+        <v>191</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>207</v>
+        <v>192</v>
       </c>
       <c r="B4" s="39" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="C4" s="39" t="s">
-        <v>209</v>
+        <v>194</v>
       </c>
       <c r="D4" s="4"/>
       <c r="E4" s="2">
@@ -8131,13 +7867,13 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>210</v>
+        <v>195</v>
       </c>
       <c r="B5" s="40" t="s">
-        <v>211</v>
+        <v>196</v>
       </c>
       <c r="C5" s="40" t="s">
-        <v>212</v>
+        <v>197</v>
       </c>
       <c r="E5" s="3">
         <v>-10.0</v>
@@ -8148,13 +7884,13 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>214</v>
+        <v>199</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>215</v>
+        <v>200</v>
       </c>
       <c r="E6" s="3">
         <v>0.0</v>
@@ -8162,16 +7898,22 @@
       <c r="F6" s="3">
         <v>-10.0</v>
       </c>
+      <c r="H6" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>202</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>216</v>
+        <v>203</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>217</v>
+        <v>204</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>218</v>
+        <v>205</v>
       </c>
       <c r="E7" s="3">
         <v>-10.0</v>
@@ -8179,16 +7921,22 @@
       <c r="F7" s="3">
         <v>0.0</v>
       </c>
+      <c r="H7" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>207</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>219</v>
+        <v>208</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>220</v>
+        <v>209</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="E8" s="3">
         <v>0.0</v>
@@ -8196,38 +7944,17 @@
       <c r="F8" s="3">
         <v>-10.0</v>
       </c>
+      <c r="H8" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>212</v>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="E9" s="3">
-        <v>0.0</v>
-      </c>
-      <c r="F9" s="3">
-        <v>-10.0</v>
-      </c>
-      <c r="G9" s="3">
-        <v>-10.0</v>
-      </c>
-      <c r="H9" s="32" t="s">
-        <v>182</v>
-      </c>
-      <c r="I9" s="32" t="s">
-        <v>185</v>
-      </c>
-      <c r="J9" s="32" t="s">
-        <v>188</v>
-      </c>
+      <c r="H9" s="32"/>
+      <c r="I9" s="32"/>
+      <c r="J9" s="32"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>

--- a/Assets/02Script/Table/EventTable.xlsx
+++ b/Assets/02Script/Table/EventTable.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1118" uniqueCount="350">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1139" uniqueCount="355">
   <si>
     <t>EventID</t>
   </si>
@@ -332,6 +332,12 @@
   </si>
   <si>
     <t>2스테이지 2번 골목 안들어 가려고 할 때</t>
+  </si>
+  <si>
+    <t>E040</t>
+  </si>
+  <si>
+    <t>1스테이지 1인칭 맵 귀신 나타났을 때</t>
   </si>
   <si>
     <t>Order</t>
@@ -889,6 +895,15 @@
   </si>
   <si>
     <t>확인하는 게 마음이 편하겠어..</t>
+  </si>
+  <si>
+    <t>뭐...뭐야. 이소리는.</t>
+  </si>
+  <si>
+    <t>설마.... 아까 봤던 그 괴물의 소리...?</t>
+  </si>
+  <si>
+    <t>도망쳐야해...!</t>
   </si>
   <si>
     <t>Choice0</t>
@@ -1167,7 +1182,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="51">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1291,6 +1306,9 @@
     </xf>
     <xf borderId="0" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right"/>
@@ -1426,7 +1444,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="D80:J146" displayName="Table_4" name="Table_4" id="4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="D80:J149" displayName="Table_4" name="Table_4" id="4">
   <tableColumns count="7">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -2156,6 +2174,17 @@
         <v>105</v>
       </c>
     </row>
+    <row r="42">
+      <c r="A42" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -2176,10 +2205,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="2">
@@ -2190,7 +2219,7 @@
         <v>1.0</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
     </row>
     <row r="3">
@@ -2201,7 +2230,7 @@
         <v>2.0</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="4">
@@ -2212,7 +2241,7 @@
         <v>3.0</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="5">
@@ -2223,7 +2252,7 @@
         <v>4.0</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
     </row>
     <row r="6">
@@ -2234,7 +2263,7 @@
         <v>5.0</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
     </row>
     <row r="7">
@@ -2245,7 +2274,7 @@
         <v>6.0</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
     </row>
     <row r="8">
@@ -2256,7 +2285,7 @@
         <v>7.0</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="9">
@@ -2267,7 +2296,7 @@
         <v>8.0</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="10">
@@ -2278,7 +2307,7 @@
         <v>9.0</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
     </row>
     <row r="11">
@@ -2289,7 +2318,7 @@
         <v>10.0</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
     </row>
     <row r="12">
@@ -2300,7 +2329,7 @@
         <v>11.0</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="13">
@@ -2311,7 +2340,7 @@
         <v>12.0</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
     </row>
     <row r="14">
@@ -2322,7 +2351,7 @@
         <v>13.0</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
     </row>
   </sheetData>
@@ -2349,31 +2378,31 @@
         <v>0</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
     </row>
     <row r="2">
@@ -2387,20 +2416,20 @@
         <v>2001.0</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E2" s="12">
         <v>2002.0</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G2" s="11" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H2" s="13"/>
       <c r="I2" s="14" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J2" s="14">
         <v>-1.0</v>
@@ -2418,20 +2447,20 @@
         <v>2002.0</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E3" s="12">
         <v>2003.0</v>
       </c>
       <c r="F3" s="11" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G3" s="11" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H3" s="13"/>
       <c r="I3" s="14" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J3" s="14">
         <v>-1.0</v>
@@ -2449,20 +2478,20 @@
         <v>2003.0</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E4" s="12">
         <v>2004.0</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H4" s="13"/>
       <c r="I4" s="14" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J4" s="14">
         <v>-1.0</v>
@@ -2480,20 +2509,20 @@
         <v>2004.0</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E5" s="12">
         <v>2005.0</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="G5" s="11" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H5" s="13"/>
       <c r="I5" s="14" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J5" s="14">
         <v>-1.0</v>
@@ -2511,20 +2540,20 @@
         <v>2005.0</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E6" s="12">
         <v>2006.0</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G6" s="11" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H6" s="13"/>
       <c r="I6" s="14" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J6" s="14">
         <v>-1.0</v>
@@ -2542,20 +2571,20 @@
         <v>2006.0</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E7" s="12">
         <v>2007.0</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="G7" s="11" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H7" s="13"/>
       <c r="I7" s="14" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J7" s="14">
         <v>-1.0</v>
@@ -2573,20 +2602,20 @@
         <v>2007.0</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="E8" s="12">
         <v>2008.0</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H8" s="13"/>
       <c r="I8" s="14" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J8" s="14">
         <v>-1.0</v>
@@ -2604,20 +2633,20 @@
         <v>2008.0</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E9" s="12">
         <v>2009.0</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="G9" s="11" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H9" s="13"/>
       <c r="I9" s="14" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J9" s="14">
         <v>-1.0</v>
@@ -2635,20 +2664,20 @@
         <v>2009.0</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E10" s="12">
         <v>2010.0</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G10" s="11" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H10" s="13"/>
       <c r="I10" s="14" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J10" s="14">
         <v>-1.0</v>
@@ -2666,20 +2695,20 @@
         <v>2010.0</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E11" s="12">
         <v>2011.0</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="G11" s="11" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="H11" s="13"/>
       <c r="I11" s="14" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J11" s="14">
         <v>-1.0</v>
@@ -2697,20 +2726,20 @@
         <v>2011.0</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E12" s="12">
         <v>-1.0</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H12" s="13"/>
       <c r="I12" s="14" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J12" s="14">
         <v>-1.0</v>
@@ -2728,20 +2757,20 @@
         <v>3001.0</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E13" s="16">
         <v>3002.0</v>
       </c>
       <c r="F13" s="14" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G13" s="11" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H13" s="13"/>
       <c r="I13" s="14" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J13" s="16">
         <v>4.0</v>
@@ -2759,20 +2788,20 @@
         <v>3002.0</v>
       </c>
       <c r="D14" s="14" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="E14" s="16">
         <v>3003.0</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="G14" s="11" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="H14" s="13"/>
       <c r="I14" s="14" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J14" s="16">
         <v>0.0</v>
@@ -2790,20 +2819,20 @@
         <v>3003.0</v>
       </c>
       <c r="D15" s="14" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="E15" s="16">
         <v>3004.0</v>
       </c>
       <c r="F15" s="14" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G15" s="11" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H15" s="13"/>
       <c r="I15" s="14" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J15" s="16">
         <v>2.0</v>
@@ -2821,20 +2850,20 @@
         <v>3004.0</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E16" s="16">
         <v>3005.0</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="G16" s="11" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="H16" s="13"/>
       <c r="I16" s="14" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J16" s="16">
         <v>0.0</v>
@@ -2852,20 +2881,20 @@
         <v>3005.0</v>
       </c>
       <c r="D17" s="14" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="E17" s="16">
         <v>3006.0</v>
       </c>
       <c r="F17" s="14" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G17" s="11" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H17" s="13"/>
       <c r="I17" s="14" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J17" s="16">
         <v>2.0</v>
@@ -2883,20 +2912,20 @@
         <v>3006.0</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E18" s="16">
         <v>3007.0</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="G18" s="11" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="H18" s="13"/>
       <c r="I18" s="14" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J18" s="16">
         <v>0.0</v>
@@ -2914,20 +2943,20 @@
         <v>3007.0</v>
       </c>
       <c r="D19" s="14" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E19" s="16">
         <v>3008.0</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="G19" s="11" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="H19" s="13"/>
       <c r="I19" s="14" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J19" s="16">
         <v>1.0</v>
@@ -2953,20 +2982,20 @@
         <v>3008.0</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E20" s="16">
         <v>3009.0</v>
       </c>
       <c r="F20" s="14" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G20" s="11" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H20" s="13"/>
       <c r="I20" s="14" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J20" s="16">
         <v>2.0</v>
@@ -2992,20 +3021,20 @@
         <v>3009.0</v>
       </c>
       <c r="D21" s="14" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E21" s="16">
         <v>3010.0</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="G21" s="11" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="H21" s="13"/>
       <c r="I21" s="14" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="J21" s="16">
         <v>1.0</v>
@@ -3031,20 +3060,20 @@
         <v>3010.0</v>
       </c>
       <c r="D22" s="14" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E22" s="16">
         <v>3011.0</v>
       </c>
       <c r="F22" s="14" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G22" s="11" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H22" s="13"/>
       <c r="I22" s="14" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J22" s="16">
         <v>2.0</v>
@@ -3070,20 +3099,20 @@
         <v>3011.0</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E23" s="16">
         <v>3012.0</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="G23" s="11" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="H23" s="13"/>
       <c r="I23" s="14" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="J23" s="16">
         <v>1.0</v>
@@ -3109,19 +3138,19 @@
         <v>3012.0</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="E24" s="16">
         <v>3013.0</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="I24" s="14" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J24" s="3">
         <v>2.0</v>
@@ -3147,19 +3176,19 @@
         <v>3013.0</v>
       </c>
       <c r="D25" s="14" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="E25" s="16">
         <v>3014.0</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="I25" s="14" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="J25" s="3">
         <v>2.0</v>
@@ -3185,19 +3214,19 @@
         <v>3014.0</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="E26" s="16">
         <v>3015.0</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="I26" s="14" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J26" s="3">
         <v>2.0</v>
@@ -3215,20 +3244,20 @@
         <v>3015.0</v>
       </c>
       <c r="D27" s="14" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E27" s="16">
         <v>3016.0</v>
       </c>
       <c r="F27" s="14" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G27" s="11" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H27" s="13"/>
       <c r="I27" s="16" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="J27" s="16">
         <v>0.0</v>
@@ -3246,22 +3275,22 @@
         <v>3016.0</v>
       </c>
       <c r="D28" s="14" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E28" s="12">
         <v>-1.0</v>
       </c>
       <c r="F28" s="14" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G28" s="11" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H28" s="14" t="s">
+        <v>166</v>
+      </c>
+      <c r="I28" s="16" t="s">
         <v>164</v>
-      </c>
-      <c r="I28" s="16" t="s">
-        <v>162</v>
       </c>
       <c r="J28" s="16">
         <v>0.0</v>
@@ -3279,18 +3308,18 @@
         <v>4001.0</v>
       </c>
       <c r="D29" s="14" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="E29" s="12">
         <v>4002.0</v>
       </c>
       <c r="F29" s="14" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G29" s="21"/>
       <c r="H29" s="13"/>
       <c r="I29" s="16" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="J29" s="16">
         <v>-1.0</v>
@@ -3308,18 +3337,18 @@
         <v>4002.0</v>
       </c>
       <c r="D30" s="14" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E30" s="12">
         <v>-1.0</v>
       </c>
       <c r="F30" s="14" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G30" s="21"/>
       <c r="H30" s="13"/>
       <c r="I30" s="16" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="J30" s="16">
         <v>-1.0</v>
@@ -3337,20 +3366,20 @@
         <v>5001.0</v>
       </c>
       <c r="D31" s="14" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="E31" s="3">
         <v>5002.0</v>
       </c>
       <c r="F31" s="14" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G31" s="11" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H31" s="13"/>
       <c r="I31" s="14" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J31" s="16">
         <v>2.0</v>
@@ -3368,20 +3397,20 @@
         <v>5002.0</v>
       </c>
       <c r="D32" s="14" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E32" s="3">
         <v>5003.0</v>
       </c>
       <c r="F32" s="14" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G32" s="11" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H32" s="13"/>
       <c r="I32" s="14" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J32" s="16">
         <v>2.0</v>
@@ -3399,20 +3428,20 @@
         <v>5003.0</v>
       </c>
       <c r="D33" s="14" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E33" s="3">
         <v>5004.0</v>
       </c>
       <c r="F33" s="14" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G33" s="11" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H33" s="13"/>
       <c r="I33" s="14" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J33" s="16">
         <v>0.0</v>
@@ -3430,20 +3459,20 @@
         <v>5004.0</v>
       </c>
       <c r="D34" s="14" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E34" s="3">
         <v>5005.0</v>
       </c>
       <c r="F34" s="14" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G34" s="11" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H34" s="13"/>
       <c r="I34" s="14" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J34" s="16">
         <v>0.0</v>
@@ -3461,20 +3490,20 @@
         <v>5005.0</v>
       </c>
       <c r="D35" s="14" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="E35" s="3">
         <v>5006.0</v>
       </c>
       <c r="F35" s="14" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G35" s="11" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H35" s="13"/>
       <c r="I35" s="14" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J35" s="16">
         <v>0.0</v>
@@ -3492,20 +3521,20 @@
         <v>5006.0</v>
       </c>
       <c r="D36" s="14" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E36" s="12">
         <v>-1.0</v>
       </c>
       <c r="F36" s="14" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G36" s="11" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H36" s="13"/>
       <c r="I36" s="16" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="J36" s="16">
         <v>0.0</v>
@@ -3523,20 +3552,20 @@
         <v>6001.0</v>
       </c>
       <c r="D37" s="14" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E37" s="16">
         <v>6002.0</v>
       </c>
       <c r="F37" s="14" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="G37" s="11" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H37" s="13"/>
       <c r="I37" s="16" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="J37" s="16">
         <v>-1.0</v>
@@ -3554,20 +3583,20 @@
         <v>6002.0</v>
       </c>
       <c r="D38" s="14" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E38" s="16">
         <v>6003.0</v>
       </c>
       <c r="F38" s="14" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G38" s="11" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H38" s="13"/>
       <c r="I38" s="14" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J38" s="16">
         <v>0.0</v>
@@ -3585,20 +3614,20 @@
         <v>6003.0</v>
       </c>
       <c r="D39" s="14" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E39" s="16">
         <v>6004.0</v>
       </c>
       <c r="F39" s="14" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="G39" s="11" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H39" s="13"/>
       <c r="I39" s="16" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="J39" s="16">
         <v>-1.0</v>
@@ -3616,20 +3645,20 @@
         <v>6004.0</v>
       </c>
       <c r="D40" s="14" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="E40" s="16">
         <v>6005.0</v>
       </c>
       <c r="F40" s="14" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G40" s="11" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H40" s="13"/>
       <c r="I40" s="14" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J40" s="16">
         <v>0.0</v>
@@ -3647,20 +3676,20 @@
         <v>6005.0</v>
       </c>
       <c r="D41" s="14" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="E41" s="16">
         <v>-1.0</v>
       </c>
       <c r="F41" s="14" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G41" s="11" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H41" s="13"/>
       <c r="I41" s="14" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J41" s="16">
         <v>0.0</v>
@@ -3678,20 +3707,20 @@
         <v>7001.0</v>
       </c>
       <c r="D42" s="14" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E42" s="16">
         <v>-1.0</v>
       </c>
       <c r="F42" s="14" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G42" s="11" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H42" s="13"/>
       <c r="I42" s="14" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J42" s="16">
         <v>-1.0</v>
@@ -3709,20 +3738,20 @@
         <v>8001.0</v>
       </c>
       <c r="D43" s="14" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="E43" s="16">
         <v>8002.0</v>
       </c>
       <c r="F43" s="14" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G43" s="11" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H43" s="13"/>
       <c r="I43" s="14" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J43" s="16">
         <v>-1.0</v>
@@ -3740,20 +3769,20 @@
         <v>8002.0</v>
       </c>
       <c r="D44" s="14" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="E44" s="16">
         <v>8003.0</v>
       </c>
       <c r="F44" s="14" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G44" s="11" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H44" s="13"/>
       <c r="I44" s="14" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J44" s="16">
         <v>-1.0</v>
@@ -3771,20 +3800,20 @@
         <v>8003.0</v>
       </c>
       <c r="D45" s="14" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="E45" s="16">
         <v>8004.0</v>
       </c>
       <c r="F45" s="14" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G45" s="11" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H45" s="13"/>
       <c r="I45" s="14" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J45" s="16">
         <v>-1.0</v>
@@ -3802,20 +3831,20 @@
         <v>8004.0</v>
       </c>
       <c r="D46" s="14" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="E46" s="16">
         <v>8005.0</v>
       </c>
       <c r="F46" s="14" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="G46" s="11" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H46" s="13"/>
       <c r="I46" s="16" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="J46" s="16">
         <v>-1.0</v>
@@ -3833,20 +3862,20 @@
         <v>8005.0</v>
       </c>
       <c r="D47" s="14" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="E47" s="16">
         <v>-1.0</v>
       </c>
       <c r="F47" s="14" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G47" s="11" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H47" s="13"/>
       <c r="I47" s="14" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J47" s="16">
         <v>-1.0</v>
@@ -3864,20 +3893,20 @@
         <v>9001.0</v>
       </c>
       <c r="D48" s="14" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="E48" s="16">
         <v>-1.0</v>
       </c>
       <c r="F48" s="14" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G48" s="11" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H48" s="13"/>
       <c r="I48" s="31" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J48" s="16">
         <v>-1.0</v>
@@ -3895,20 +3924,20 @@
         <v>10001.0</v>
       </c>
       <c r="D49" s="14" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="E49" s="16">
         <v>10002.0</v>
       </c>
       <c r="F49" s="14" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G49" s="11" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H49" s="13"/>
       <c r="I49" s="31" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J49" s="16">
         <v>0.0</v>
@@ -3926,20 +3955,20 @@
         <v>10002.0</v>
       </c>
       <c r="D50" s="14" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E50" s="16">
         <v>10003.0</v>
       </c>
       <c r="F50" s="14" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G50" s="11" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H50" s="13"/>
       <c r="I50" s="31" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J50" s="16">
         <v>0.0</v>
@@ -3957,20 +3986,20 @@
         <v>10003.0</v>
       </c>
       <c r="D51" s="14" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="E51" s="16">
         <v>10004.0</v>
       </c>
       <c r="F51" s="14" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G51" s="11" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H51" s="13"/>
       <c r="I51" s="31" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J51" s="16">
         <v>0.0</v>
@@ -3988,20 +4017,20 @@
         <v>10004.0</v>
       </c>
       <c r="D52" s="14" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E52" s="16">
         <v>-1.0</v>
       </c>
       <c r="F52" s="14" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G52" s="11" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H52" s="13"/>
       <c r="I52" s="16" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J52" s="16">
         <v>0.0</v>
@@ -4019,20 +4048,20 @@
         <v>11001.0</v>
       </c>
       <c r="D53" s="14" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="E53" s="16">
         <v>-1.0</v>
       </c>
       <c r="F53" s="14" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G53" s="11" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H53" s="13"/>
       <c r="I53" s="16" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J53" s="16">
         <v>-1.0</v>
@@ -4050,20 +4079,20 @@
         <v>12001.0</v>
       </c>
       <c r="D54" s="14" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="E54" s="16">
         <v>12002.0</v>
       </c>
       <c r="F54" s="14" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="G54" s="11" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H54" s="13"/>
       <c r="I54" s="31" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="J54" s="16">
         <v>-1.0</v>
@@ -4081,20 +4110,20 @@
         <v>12002.0</v>
       </c>
       <c r="D55" s="14" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="E55" s="16">
         <v>12003.0</v>
       </c>
       <c r="F55" s="14" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G55" s="11" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H55" s="13"/>
       <c r="I55" s="16" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J55" s="16">
         <v>2.0</v>
@@ -4112,20 +4141,20 @@
         <v>12003.0</v>
       </c>
       <c r="D56" s="14" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="E56" s="16">
         <v>12004.0</v>
       </c>
       <c r="F56" s="14" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="G56" s="11" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H56" s="13"/>
       <c r="I56" s="31" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="J56" s="16">
         <v>-1.0</v>
@@ -4143,20 +4172,20 @@
         <v>12004.0</v>
       </c>
       <c r="D57" s="14" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="E57" s="16">
         <v>12005.0</v>
       </c>
       <c r="F57" s="14" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G57" s="11" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H57" s="13"/>
       <c r="I57" s="31" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J57" s="16">
         <v>2.0</v>
@@ -4174,20 +4203,20 @@
         <v>12005.0</v>
       </c>
       <c r="D58" s="14" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="E58" s="16">
         <v>12006.0</v>
       </c>
       <c r="F58" s="14" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G58" s="11" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H58" s="13"/>
       <c r="I58" s="16" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J58" s="16">
         <v>0.0</v>
@@ -4205,20 +4234,20 @@
         <v>12006.0</v>
       </c>
       <c r="D59" s="14" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="E59" s="16">
         <v>12007.0</v>
       </c>
       <c r="F59" s="14" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="G59" s="11" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H59" s="13"/>
       <c r="I59" s="31" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="J59" s="16">
         <v>-1.0</v>
@@ -4236,20 +4265,20 @@
         <v>12007.0</v>
       </c>
       <c r="D60" s="14" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="E60" s="16">
         <v>12008.0</v>
       </c>
       <c r="F60" s="14" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G60" s="11" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H60" s="13"/>
       <c r="I60" s="16" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J60" s="16">
         <v>0.0</v>
@@ -4267,20 +4296,20 @@
         <v>12008.0</v>
       </c>
       <c r="D61" s="14" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="E61" s="16">
         <v>-1.0</v>
       </c>
       <c r="F61" s="14" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G61" s="11" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H61" s="13"/>
       <c r="I61" s="31" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="J61" s="16">
         <v>0.0</v>
@@ -4298,20 +4327,20 @@
         <v>13001.0</v>
       </c>
       <c r="D62" s="14" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="E62" s="16">
         <v>-1.0</v>
       </c>
       <c r="F62" s="14" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G62" s="11" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H62" s="13"/>
       <c r="I62" s="31" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J62" s="16">
         <v>-1.0</v>
@@ -4329,20 +4358,20 @@
         <v>14001.0</v>
       </c>
       <c r="D63" s="14" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="E63" s="16">
         <v>14002.0</v>
       </c>
       <c r="F63" s="14" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G63" s="11" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H63" s="13"/>
       <c r="I63" s="31" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J63" s="16">
         <v>-1.0</v>
@@ -4360,20 +4389,20 @@
         <v>14002.0</v>
       </c>
       <c r="D64" s="14" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="E64" s="16">
         <v>14003.0</v>
       </c>
       <c r="F64" s="14" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G64" s="11" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H64" s="13"/>
       <c r="I64" s="31" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J64" s="16">
         <v>-1.0</v>
@@ -4391,20 +4420,20 @@
         <v>14003.0</v>
       </c>
       <c r="D65" s="14" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="E65" s="16">
         <v>-1.0</v>
       </c>
       <c r="F65" s="14" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G65" s="11" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H65" s="13"/>
       <c r="I65" s="31" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J65" s="16">
         <v>-1.0</v>
@@ -4422,20 +4451,20 @@
         <v>15001.0</v>
       </c>
       <c r="D66" s="14" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="E66" s="16">
         <v>-1.0</v>
       </c>
       <c r="F66" s="14" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G66" s="11" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H66" s="13"/>
       <c r="I66" s="31" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J66" s="16">
         <v>-1.0</v>
@@ -4453,20 +4482,20 @@
         <v>16001.0</v>
       </c>
       <c r="D67" s="14" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="E67" s="16">
         <v>16002.0</v>
       </c>
       <c r="F67" s="14" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G67" s="11" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H67" s="13"/>
       <c r="I67" s="31" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J67" s="16">
         <v>0.0</v>
@@ -4484,20 +4513,20 @@
         <v>16002.0</v>
       </c>
       <c r="D68" s="14" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="E68" s="16">
         <v>-1.0</v>
       </c>
       <c r="F68" s="14" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G68" s="11" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H68" s="13"/>
       <c r="I68" s="31" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J68" s="16">
         <v>0.0</v>
@@ -4515,20 +4544,20 @@
         <v>17001.0</v>
       </c>
       <c r="D69" s="14" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="E69" s="16">
         <v>17002.0</v>
       </c>
       <c r="F69" s="14" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G69" s="11" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H69" s="13"/>
       <c r="I69" s="31" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J69" s="16">
         <v>0.0</v>
@@ -4546,20 +4575,20 @@
         <v>17002.0</v>
       </c>
       <c r="D70" s="14" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="E70" s="16">
         <v>17003.0</v>
       </c>
       <c r="F70" s="14" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G70" s="11" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H70" s="13"/>
       <c r="I70" s="31" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J70" s="16">
         <v>0.0</v>
@@ -4577,20 +4606,20 @@
         <v>17003.0</v>
       </c>
       <c r="D71" s="14" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="E71" s="16">
         <v>17004.0</v>
       </c>
       <c r="F71" s="14" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G71" s="11" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H71" s="13"/>
       <c r="I71" s="31" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J71" s="16">
         <v>0.0</v>
@@ -4608,20 +4637,20 @@
         <v>17004.0</v>
       </c>
       <c r="D72" s="14" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="E72" s="16">
         <v>-1.0</v>
       </c>
       <c r="F72" s="14" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G72" s="11" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H72" s="13"/>
       <c r="I72" s="31" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J72" s="16">
         <v>0.0</v>
@@ -4639,20 +4668,20 @@
         <v>18001.0</v>
       </c>
       <c r="D73" s="14" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="E73" s="16">
         <v>18002.0</v>
       </c>
       <c r="F73" s="14" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G73" s="11" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H73" s="13"/>
       <c r="I73" s="31" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J73" s="16">
         <v>0.0</v>
@@ -4670,19 +4699,19 @@
         <v>18002.0</v>
       </c>
       <c r="D74" s="33" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="E74" s="3">
         <v>-1.0</v>
       </c>
       <c r="F74" s="14" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G74" s="11" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="I74" s="31" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J74" s="16">
         <v>0.0</v>
@@ -4699,19 +4728,19 @@
         <v>19001.0</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="E75" s="16">
         <v>19002.0</v>
       </c>
       <c r="F75" s="14" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G75" s="11" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="I75" s="31" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J75" s="16">
         <v>2.0</v>
@@ -4728,19 +4757,19 @@
         <v>19002.0</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="E76" s="3">
         <v>19003.0</v>
       </c>
       <c r="F76" s="14" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G76" s="11" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="I76" s="31" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J76" s="16">
         <v>2.0</v>
@@ -4757,19 +4786,19 @@
         <v>19003.0</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="E77" s="3">
         <v>19004.0</v>
       </c>
       <c r="F77" s="14" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G77" s="11" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="I77" s="31" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J77" s="3">
         <v>2.0</v>
@@ -4786,19 +4815,19 @@
         <v>19004.0</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="E78" s="3">
         <v>19005.0</v>
       </c>
       <c r="F78" s="3" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G78" s="3" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J78" s="3">
         <v>2.0</v>
@@ -4815,19 +4844,19 @@
         <v>19005.0</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="E79" s="3">
         <v>-1.0</v>
       </c>
       <c r="F79" s="3" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G79" s="3" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J79" s="3">
         <v>0.0</v>
@@ -4844,20 +4873,20 @@
         <v>20001.0</v>
       </c>
       <c r="D80" s="36" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="E80" s="28">
         <v>20002.0</v>
       </c>
       <c r="F80" s="36" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G80" s="37" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H80" s="36"/>
       <c r="I80" s="38" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J80" s="28">
         <v>0.0</v>
@@ -4874,20 +4903,20 @@
         <v>20002.0</v>
       </c>
       <c r="D81" s="39" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="E81" s="19">
         <v>20003.0</v>
       </c>
       <c r="F81" s="39" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G81" s="37" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H81" s="39"/>
       <c r="I81" s="38" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J81" s="19">
         <v>0.0</v>
@@ -4904,20 +4933,20 @@
         <v>20003.0</v>
       </c>
       <c r="D82" s="36" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="E82" s="28">
         <v>20004.0</v>
       </c>
       <c r="F82" s="36" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G82" s="37" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H82" s="36"/>
       <c r="I82" s="38" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J82" s="28">
         <v>0.0</v>
@@ -4934,20 +4963,20 @@
         <v>20004.0</v>
       </c>
       <c r="D83" s="39" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E83" s="19">
         <v>20005.0</v>
       </c>
       <c r="F83" s="39" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G83" s="37" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H83" s="39"/>
       <c r="I83" s="38" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J83" s="19">
         <v>0.0</v>
@@ -4964,20 +4993,20 @@
         <v>20005.0</v>
       </c>
       <c r="D84" s="36" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="E84" s="28">
         <v>20006.0</v>
       </c>
       <c r="F84" s="36" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G84" s="37" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H84" s="36"/>
       <c r="I84" s="38" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J84" s="28">
         <v>0.0</v>
@@ -4994,20 +5023,20 @@
         <v>20006.0</v>
       </c>
       <c r="D85" s="39" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="E85" s="19">
         <v>-1.0</v>
       </c>
       <c r="F85" s="39" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G85" s="37" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H85" s="39"/>
       <c r="I85" s="38" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J85" s="19">
         <v>0.0</v>
@@ -5024,20 +5053,20 @@
         <v>21001.0</v>
       </c>
       <c r="D86" s="36" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="E86" s="28">
         <v>-1.0</v>
       </c>
       <c r="F86" s="36" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G86" s="37" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H86" s="36"/>
       <c r="I86" s="38" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J86" s="28">
         <v>0.0</v>
@@ -5054,20 +5083,20 @@
         <v>22001.0</v>
       </c>
       <c r="D87" s="39" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="E87" s="19">
         <v>22002.0</v>
       </c>
       <c r="F87" s="39" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G87" s="37" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H87" s="39"/>
       <c r="I87" s="38" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J87" s="19">
         <v>0.0</v>
@@ -5084,20 +5113,20 @@
         <v>22002.0</v>
       </c>
       <c r="D88" s="36" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="E88" s="28">
         <v>22003.0</v>
       </c>
       <c r="F88" s="36" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G88" s="37" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H88" s="36"/>
       <c r="I88" s="38" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J88" s="28">
         <v>0.0</v>
@@ -5114,20 +5143,20 @@
         <v>22003.0</v>
       </c>
       <c r="D89" s="39" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="E89" s="19">
         <v>22004.0</v>
       </c>
       <c r="F89" s="39" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G89" s="37" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H89" s="39"/>
       <c r="I89" s="38" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J89" s="19">
         <v>0.0</v>
@@ -5144,20 +5173,20 @@
         <v>22004.0</v>
       </c>
       <c r="D90" s="36" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="E90" s="28">
         <v>22005.0</v>
       </c>
       <c r="F90" s="36" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G90" s="37" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H90" s="36"/>
       <c r="I90" s="38" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J90" s="28">
         <v>0.0</v>
@@ -5174,20 +5203,20 @@
         <v>22005.0</v>
       </c>
       <c r="D91" s="39" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="E91" s="19">
         <v>22006.0</v>
       </c>
       <c r="F91" s="39" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G91" s="37" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H91" s="39"/>
       <c r="I91" s="38" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J91" s="19">
         <v>0.0</v>
@@ -5204,20 +5233,20 @@
         <v>23001.0</v>
       </c>
       <c r="D92" s="36" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="E92" s="28">
         <v>22007.0</v>
       </c>
       <c r="F92" s="36" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G92" s="37" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H92" s="36"/>
       <c r="I92" s="38" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J92" s="28">
         <v>0.0</v>
@@ -5234,20 +5263,20 @@
         <v>23002.0</v>
       </c>
       <c r="D93" s="39" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E93" s="19">
         <v>22008.0</v>
       </c>
       <c r="F93" s="39" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G93" s="37" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H93" s="39"/>
       <c r="I93" s="38" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J93" s="19">
         <v>0.0</v>
@@ -5264,20 +5293,20 @@
         <v>23003.0</v>
       </c>
       <c r="D94" s="36" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="E94" s="28">
         <v>22009.0</v>
       </c>
       <c r="F94" s="36" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G94" s="37" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H94" s="36"/>
       <c r="I94" s="38" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J94" s="28">
         <v>0.0</v>
@@ -5294,20 +5323,20 @@
         <v>23004.0</v>
       </c>
       <c r="D95" s="39" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="E95" s="19">
         <v>-1.0</v>
       </c>
       <c r="F95" s="39" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G95" s="37" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H95" s="39"/>
       <c r="I95" s="38" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J95" s="19">
         <v>0.0</v>
@@ -5324,20 +5353,20 @@
         <v>24001.0</v>
       </c>
       <c r="D96" s="36" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="E96" s="28">
         <v>24002.0</v>
       </c>
       <c r="F96" s="36" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G96" s="37" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H96" s="36"/>
       <c r="I96" s="38" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J96" s="28">
         <v>0.0</v>
@@ -5354,20 +5383,20 @@
         <v>24002.0</v>
       </c>
       <c r="D97" s="39" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="E97" s="19">
         <v>24003.0</v>
       </c>
       <c r="F97" s="39" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G97" s="37" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H97" s="39"/>
       <c r="I97" s="38" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J97" s="19">
         <v>0.0</v>
@@ -5384,20 +5413,20 @@
         <v>24003.0</v>
       </c>
       <c r="D98" s="36" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="E98" s="28">
         <v>24004.0</v>
       </c>
       <c r="F98" s="36" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G98" s="37" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H98" s="36"/>
       <c r="I98" s="38" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J98" s="28">
         <v>0.0</v>
@@ -5414,20 +5443,20 @@
         <v>24004.0</v>
       </c>
       <c r="D99" s="39" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="E99" s="19">
         <v>24005.0</v>
       </c>
       <c r="F99" s="39" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G99" s="37" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H99" s="39"/>
       <c r="I99" s="38" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J99" s="19">
         <v>0.0</v>
@@ -5444,20 +5473,20 @@
         <v>24005.0</v>
       </c>
       <c r="D100" s="36" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="E100" s="28">
         <v>24006.0</v>
       </c>
       <c r="F100" s="36" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G100" s="37" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H100" s="36"/>
       <c r="I100" s="38" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J100" s="28">
         <v>0.0</v>
@@ -5474,20 +5503,20 @@
         <v>24006.0</v>
       </c>
       <c r="D101" s="39" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="E101" s="19">
         <v>24007.0</v>
       </c>
       <c r="F101" s="39" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G101" s="37" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H101" s="39"/>
       <c r="I101" s="38" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J101" s="19">
         <v>0.0</v>
@@ -5504,20 +5533,20 @@
         <v>24007.0</v>
       </c>
       <c r="D102" s="36" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="E102" s="28">
         <v>24008.0</v>
       </c>
       <c r="F102" s="36" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G102" s="37" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H102" s="36"/>
       <c r="I102" s="38" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J102" s="28">
         <v>0.0</v>
@@ -5534,20 +5563,20 @@
         <v>24008.0</v>
       </c>
       <c r="D103" s="39" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="E103" s="19">
         <v>-1.0</v>
       </c>
       <c r="F103" s="39" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G103" s="37" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H103" s="39"/>
       <c r="I103" s="38" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J103" s="19">
         <v>0.0</v>
@@ -5564,20 +5593,20 @@
         <v>25001.0</v>
       </c>
       <c r="D104" s="36" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="E104" s="28">
         <v>25002.0</v>
       </c>
       <c r="F104" s="36" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="G104" s="36" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H104" s="36"/>
       <c r="I104" s="36" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="J104" s="28">
         <v>0.0</v>
@@ -5594,20 +5623,20 @@
         <v>25002.0</v>
       </c>
       <c r="D105" s="39" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="E105" s="19">
         <v>25003.0</v>
       </c>
       <c r="F105" s="39" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G105" s="39" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H105" s="39"/>
       <c r="I105" s="38" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J105" s="19">
         <v>0.0</v>
@@ -5624,20 +5653,20 @@
         <v>25003.0</v>
       </c>
       <c r="D106" s="36" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="E106" s="28">
         <v>25004.0</v>
       </c>
       <c r="F106" s="36" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="G106" s="36" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H106" s="36"/>
       <c r="I106" s="36" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="J106" s="28">
         <v>0.0</v>
@@ -5654,20 +5683,20 @@
         <v>25004.0</v>
       </c>
       <c r="D107" s="39" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="E107" s="19">
         <v>25005.0</v>
       </c>
       <c r="F107" s="39" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G107" s="39" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H107" s="39"/>
       <c r="I107" s="38" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J107" s="19">
         <v>0.0</v>
@@ -5684,20 +5713,20 @@
         <v>25005.0</v>
       </c>
       <c r="D108" s="36" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="E108" s="28">
         <v>25006.0</v>
       </c>
       <c r="F108" s="36" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G108" s="36" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H108" s="36"/>
       <c r="I108" s="38" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J108" s="28">
         <v>0.0</v>
@@ -5714,20 +5743,20 @@
         <v>25006.0</v>
       </c>
       <c r="D109" s="39" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="E109" s="19">
         <v>-1.0</v>
       </c>
       <c r="F109" s="39" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G109" s="39" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H109" s="39"/>
       <c r="I109" s="38" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J109" s="19">
         <v>0.0</v>
@@ -5744,20 +5773,20 @@
         <v>26001.0</v>
       </c>
       <c r="D110" s="36" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="E110" s="28">
         <v>-1.0</v>
       </c>
       <c r="F110" s="36" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G110" s="36" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H110" s="36"/>
       <c r="I110" s="36" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="J110" s="28">
         <v>0.0</v>
@@ -5774,20 +5803,20 @@
         <v>27001.0</v>
       </c>
       <c r="D111" s="39" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="E111" s="19">
         <v>27002.0</v>
       </c>
       <c r="F111" s="39" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G111" s="39" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H111" s="39"/>
       <c r="I111" s="38" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J111" s="19">
         <v>0.0</v>
@@ -5804,20 +5833,20 @@
         <v>27002.0</v>
       </c>
       <c r="D112" s="36" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="E112" s="28">
         <v>27003.0</v>
       </c>
       <c r="F112" s="36" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G112" s="36" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H112" s="36"/>
       <c r="I112" s="38" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J112" s="28">
         <v>0.0</v>
@@ -5834,20 +5863,20 @@
         <v>27003.0</v>
       </c>
       <c r="D113" s="39" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="E113" s="19">
         <v>-1.0</v>
       </c>
       <c r="F113" s="39" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G113" s="39" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H113" s="39"/>
       <c r="I113" s="38" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J113" s="19">
         <v>0.0</v>
@@ -5864,20 +5893,20 @@
         <v>28001.0</v>
       </c>
       <c r="D114" s="36" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="E114" s="28">
         <v>28002.0</v>
       </c>
       <c r="F114" s="36" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="G114" s="36" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="H114" s="36"/>
       <c r="I114" s="36" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="J114" s="28">
         <v>0.0</v>
@@ -5894,20 +5923,20 @@
         <v>28002.0</v>
       </c>
       <c r="D115" s="39" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="E115" s="19">
         <v>28003.0</v>
       </c>
       <c r="F115" s="39" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="G115" s="39" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="H115" s="39"/>
       <c r="I115" s="39" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="J115" s="19">
         <v>0.0</v>
@@ -5924,20 +5953,20 @@
         <v>28003.0</v>
       </c>
       <c r="D116" s="36" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="E116" s="28">
         <v>-1.0</v>
       </c>
       <c r="F116" s="36" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G116" s="36" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H116" s="36"/>
       <c r="I116" s="38" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J116" s="28">
         <v>0.0</v>
@@ -5954,20 +5983,20 @@
         <v>29001.0</v>
       </c>
       <c r="D117" s="39" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="E117" s="19">
         <v>-1.0</v>
       </c>
       <c r="F117" s="39" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G117" s="39" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H117" s="39"/>
       <c r="I117" s="38" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J117" s="19">
         <v>0.0</v>
@@ -5984,20 +6013,20 @@
         <v>30001.0</v>
       </c>
       <c r="D118" s="36" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="E118" s="28">
         <v>30002.0</v>
       </c>
       <c r="F118" s="36" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G118" s="36" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H118" s="36"/>
       <c r="I118" s="38" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J118" s="28">
         <v>0.0</v>
@@ -6014,20 +6043,20 @@
         <v>30002.0</v>
       </c>
       <c r="D119" s="39" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="E119" s="19">
         <v>30003.0</v>
       </c>
       <c r="F119" s="39" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G119" s="39" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H119" s="39"/>
       <c r="I119" s="38" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J119" s="19">
         <v>0.0</v>
@@ -6044,20 +6073,20 @@
         <v>30003.0</v>
       </c>
       <c r="D120" s="36" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="E120" s="28">
         <v>-1.0</v>
       </c>
       <c r="F120" s="36" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G120" s="36" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H120" s="36"/>
       <c r="I120" s="38" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J120" s="28">
         <v>0.0</v>
@@ -6074,20 +6103,20 @@
         <v>31001.0</v>
       </c>
       <c r="D121" s="39" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="E121" s="19">
         <v>31002.0</v>
       </c>
       <c r="F121" s="39" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G121" s="39" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H121" s="39"/>
       <c r="I121" s="38" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J121" s="19">
         <v>0.0</v>
@@ -6104,20 +6133,20 @@
         <v>31002.0</v>
       </c>
       <c r="D122" s="36" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="E122" s="28">
         <v>-1.0</v>
       </c>
       <c r="F122" s="36" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G122" s="36" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H122" s="36"/>
       <c r="I122" s="38" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J122" s="28">
         <v>0.0</v>
@@ -6134,20 +6163,20 @@
         <v>32001.0</v>
       </c>
       <c r="D123" s="39" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="E123" s="19">
         <v>32002.0</v>
       </c>
       <c r="F123" s="39" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="G123" s="39" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H123" s="39"/>
       <c r="I123" s="39" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="J123" s="19">
         <v>0.0</v>
@@ -6164,20 +6193,20 @@
         <v>32002.0</v>
       </c>
       <c r="D124" s="36" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="E124" s="28">
         <v>32003.0</v>
       </c>
       <c r="F124" s="36" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="G124" s="36" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H124" s="36"/>
       <c r="I124" s="36" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="J124" s="28">
         <v>0.0</v>
@@ -6194,20 +6223,20 @@
         <v>32003.0</v>
       </c>
       <c r="D125" s="39" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="E125" s="19">
         <v>32004.0</v>
       </c>
       <c r="F125" s="39" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="G125" s="39" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="H125" s="39"/>
       <c r="I125" s="39" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="J125" s="19">
         <v>0.0</v>
@@ -6224,20 +6253,20 @@
         <v>32004.0</v>
       </c>
       <c r="D126" s="36" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="E126" s="28">
         <v>32005.0</v>
       </c>
       <c r="F126" s="36" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G126" s="36" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H126" s="36"/>
       <c r="I126" s="38" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J126" s="28">
         <v>0.0</v>
@@ -6254,20 +6283,20 @@
         <v>32005.0</v>
       </c>
       <c r="D127" s="39" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="E127" s="19">
         <v>32006.0</v>
       </c>
       <c r="F127" s="39" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G127" s="39" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H127" s="39"/>
       <c r="I127" s="38" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J127" s="19">
         <v>0.0</v>
@@ -6284,20 +6313,20 @@
         <v>32006.0</v>
       </c>
       <c r="D128" s="36" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="E128" s="28">
         <v>-1.0</v>
       </c>
       <c r="F128" s="36" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G128" s="36" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H128" s="36"/>
       <c r="I128" s="38" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J128" s="28">
         <v>0.0</v>
@@ -6314,20 +6343,20 @@
         <v>33001.0</v>
       </c>
       <c r="D129" s="39" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="E129" s="19">
         <v>33002.0</v>
       </c>
       <c r="F129" s="39" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G129" s="39" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H129" s="39"/>
       <c r="I129" s="38" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J129" s="19">
         <v>0.0</v>
@@ -6344,20 +6373,20 @@
         <v>33002.0</v>
       </c>
       <c r="D130" s="36" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="E130" s="28">
         <v>-1.0</v>
       </c>
       <c r="F130" s="36" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G130" s="36" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H130" s="36"/>
       <c r="I130" s="38" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J130" s="28">
         <v>0.0</v>
@@ -6374,20 +6403,20 @@
         <v>34001.0</v>
       </c>
       <c r="D131" s="39" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="E131" s="19">
         <v>34002.0</v>
       </c>
       <c r="F131" s="39" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="G131" s="39" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="H131" s="39"/>
       <c r="I131" s="39" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="J131" s="19">
         <v>0.0</v>
@@ -6404,20 +6433,20 @@
         <v>34002.0</v>
       </c>
       <c r="D132" s="36" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="E132" s="28">
         <v>34003.0</v>
       </c>
       <c r="F132" s="36" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="G132" s="36" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="H132" s="36"/>
       <c r="I132" s="36" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="J132" s="28">
         <v>0.0</v>
@@ -6434,20 +6463,20 @@
         <v>34003.0</v>
       </c>
       <c r="D133" s="39" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="E133" s="19">
         <v>-1.0</v>
       </c>
       <c r="F133" s="39" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G133" s="39" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H133" s="39"/>
       <c r="I133" s="38" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J133" s="19">
         <v>0.0</v>
@@ -6464,20 +6493,20 @@
         <v>35001.0</v>
       </c>
       <c r="D134" s="36" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="E134" s="28">
         <v>-1.0</v>
       </c>
       <c r="F134" s="36" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G134" s="36" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H134" s="36"/>
       <c r="I134" s="38" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J134" s="28">
         <v>0.0</v>
@@ -6494,20 +6523,20 @@
         <v>36001.0</v>
       </c>
       <c r="D135" s="39" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="E135" s="19">
         <v>36002.0</v>
       </c>
       <c r="F135" s="39" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G135" s="39" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H135" s="39"/>
       <c r="I135" s="38" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J135" s="19">
         <v>0.0</v>
@@ -6524,20 +6553,20 @@
         <v>36002.0</v>
       </c>
       <c r="D136" s="36" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="E136" s="28">
         <v>36003.0</v>
       </c>
       <c r="F136" s="36" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G136" s="36" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H136" s="36"/>
       <c r="I136" s="38" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J136" s="28">
         <v>0.0</v>
@@ -6554,20 +6583,20 @@
         <v>36003.0</v>
       </c>
       <c r="D137" s="39" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="E137" s="19">
         <v>36004.0</v>
       </c>
       <c r="F137" s="39" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G137" s="39" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H137" s="39"/>
       <c r="I137" s="38" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J137" s="19">
         <v>0.0</v>
@@ -6584,20 +6613,20 @@
         <v>36004.0</v>
       </c>
       <c r="D138" s="36" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E138" s="28">
         <v>-1.0</v>
       </c>
       <c r="F138" s="36" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G138" s="36" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H138" s="36"/>
       <c r="I138" s="38" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J138" s="28">
         <v>0.0</v>
@@ -6614,20 +6643,20 @@
         <v>37001.0</v>
       </c>
       <c r="D139" s="39" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="E139" s="19">
         <v>37002.0</v>
       </c>
       <c r="F139" s="39" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G139" s="39" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H139" s="39"/>
       <c r="I139" s="38" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J139" s="19">
         <v>0.0</v>
@@ -6644,20 +6673,20 @@
         <v>37002.0</v>
       </c>
       <c r="D140" s="36" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E140" s="28">
         <v>37003.0</v>
       </c>
       <c r="F140" s="36" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G140" s="36" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H140" s="36"/>
       <c r="I140" s="38" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J140" s="28">
         <v>0.0</v>
@@ -6674,20 +6703,20 @@
         <v>37003.0</v>
       </c>
       <c r="D141" s="39" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="E141" s="19">
         <v>-1.0</v>
       </c>
       <c r="F141" s="39" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G141" s="39" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H141" s="39"/>
       <c r="I141" s="38" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J141" s="19">
         <v>0.0</v>
@@ -6704,20 +6733,20 @@
         <v>38001.0</v>
       </c>
       <c r="D142" s="36" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E142" s="28">
         <v>38002.0</v>
       </c>
       <c r="F142" s="36" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G142" s="36" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H142" s="36"/>
       <c r="I142" s="38" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J142" s="28">
         <v>0.0</v>
@@ -6734,20 +6763,20 @@
         <v>38002.0</v>
       </c>
       <c r="D143" s="39" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="E143" s="19">
         <v>38003.0</v>
       </c>
       <c r="F143" s="39" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G143" s="39" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H143" s="39"/>
       <c r="I143" s="38" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J143" s="19">
         <v>0.0</v>
@@ -6764,20 +6793,20 @@
         <v>38003.0</v>
       </c>
       <c r="D144" s="36" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="E144" s="28">
         <v>38004.0</v>
       </c>
       <c r="F144" s="36" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G144" s="36" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H144" s="36"/>
       <c r="I144" s="38" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J144" s="28">
         <v>0.0</v>
@@ -6794,20 +6823,20 @@
         <v>38004.0</v>
       </c>
       <c r="D145" s="39" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="E145" s="19">
         <v>-1.0</v>
       </c>
       <c r="F145" s="39" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G145" s="39" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H145" s="39"/>
       <c r="I145" s="38" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J145" s="19">
         <v>0.0</v>
@@ -6824,3364 +6853,3442 @@
         <v>39001.0</v>
       </c>
       <c r="D146" s="41" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="E146" s="28">
         <v>-1.0</v>
       </c>
       <c r="F146" s="36" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="G146" s="36" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="H146" s="36"/>
       <c r="I146" s="38" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="J146" s="28">
         <v>0.0</v>
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="42"/>
-      <c r="B147" s="42"/>
+      <c r="A147" s="32" t="s">
+        <v>106</v>
+      </c>
+      <c r="B147" s="32" t="s">
+        <v>106</v>
+      </c>
+      <c r="C147" s="3">
+        <v>40000.0</v>
+      </c>
+      <c r="D147" s="41" t="s">
+        <v>288</v>
+      </c>
+      <c r="E147" s="3">
+        <v>40001.0</v>
+      </c>
+      <c r="F147" s="36" t="s">
+        <v>133</v>
+      </c>
+      <c r="G147" s="36" t="s">
+        <v>134</v>
+      </c>
+      <c r="H147" s="36"/>
+      <c r="I147" s="38" t="s">
+        <v>135</v>
+      </c>
+      <c r="J147" s="28">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="148">
-      <c r="A148" s="42"/>
-      <c r="B148" s="42"/>
+      <c r="A148" s="32" t="s">
+        <v>106</v>
+      </c>
+      <c r="B148" s="32" t="s">
+        <v>106</v>
+      </c>
+      <c r="C148" s="3">
+        <v>40001.0</v>
+      </c>
+      <c r="D148" s="41" t="s">
+        <v>289</v>
+      </c>
+      <c r="E148" s="3">
+        <v>40002.0</v>
+      </c>
+      <c r="F148" s="36" t="s">
+        <v>133</v>
+      </c>
+      <c r="G148" s="36" t="s">
+        <v>134</v>
+      </c>
+      <c r="H148" s="36"/>
+      <c r="I148" s="38" t="s">
+        <v>135</v>
+      </c>
+      <c r="J148" s="28">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="149">
-      <c r="A149" s="42"/>
-      <c r="B149" s="42"/>
+      <c r="A149" s="32" t="s">
+        <v>106</v>
+      </c>
+      <c r="B149" s="32" t="s">
+        <v>106</v>
+      </c>
+      <c r="C149" s="3">
+        <v>40002.0</v>
+      </c>
+      <c r="D149" s="41" t="s">
+        <v>290</v>
+      </c>
+      <c r="E149" s="42">
+        <v>-1.0</v>
+      </c>
+      <c r="F149" s="36" t="s">
+        <v>133</v>
+      </c>
+      <c r="G149" s="36" t="s">
+        <v>134</v>
+      </c>
+      <c r="H149" s="36"/>
+      <c r="I149" s="38" t="s">
+        <v>135</v>
+      </c>
+      <c r="J149" s="28">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="150">
-      <c r="A150" s="42"/>
-      <c r="B150" s="42"/>
+      <c r="A150" s="43"/>
+      <c r="B150" s="43"/>
     </row>
     <row r="151">
-      <c r="A151" s="42"/>
-      <c r="B151" s="42"/>
+      <c r="A151" s="43"/>
+      <c r="B151" s="43"/>
     </row>
     <row r="152">
-      <c r="A152" s="42"/>
-      <c r="B152" s="42"/>
+      <c r="A152" s="43"/>
+      <c r="B152" s="43"/>
     </row>
     <row r="153">
-      <c r="A153" s="42"/>
-      <c r="B153" s="42"/>
+      <c r="A153" s="43"/>
+      <c r="B153" s="43"/>
     </row>
     <row r="154">
-      <c r="A154" s="42"/>
-      <c r="B154" s="42"/>
+      <c r="A154" s="43"/>
+      <c r="B154" s="43"/>
     </row>
     <row r="155">
-      <c r="A155" s="42"/>
-      <c r="B155" s="42"/>
+      <c r="A155" s="43"/>
+      <c r="B155" s="43"/>
     </row>
     <row r="156">
-      <c r="A156" s="42"/>
-      <c r="B156" s="42"/>
+      <c r="A156" s="43"/>
+      <c r="B156" s="43"/>
     </row>
     <row r="157">
-      <c r="A157" s="42"/>
-      <c r="B157" s="42"/>
+      <c r="A157" s="43"/>
+      <c r="B157" s="43"/>
     </row>
     <row r="158">
-      <c r="A158" s="42"/>
-      <c r="B158" s="42"/>
+      <c r="A158" s="43"/>
+      <c r="B158" s="43"/>
     </row>
     <row r="159">
-      <c r="A159" s="42"/>
-      <c r="B159" s="42"/>
+      <c r="A159" s="43"/>
+      <c r="B159" s="43"/>
     </row>
     <row r="160">
-      <c r="A160" s="42"/>
-      <c r="B160" s="42"/>
+      <c r="A160" s="43"/>
+      <c r="B160" s="43"/>
     </row>
     <row r="161">
-      <c r="A161" s="42"/>
-      <c r="B161" s="42"/>
+      <c r="A161" s="43"/>
+      <c r="B161" s="43"/>
     </row>
     <row r="162">
-      <c r="A162" s="42"/>
-      <c r="B162" s="42"/>
+      <c r="A162" s="43"/>
+      <c r="B162" s="43"/>
     </row>
     <row r="163">
-      <c r="A163" s="42"/>
-      <c r="B163" s="42"/>
+      <c r="A163" s="43"/>
+      <c r="B163" s="43"/>
     </row>
     <row r="164">
-      <c r="A164" s="42"/>
-      <c r="B164" s="42"/>
+      <c r="A164" s="43"/>
+      <c r="B164" s="43"/>
     </row>
     <row r="165">
-      <c r="A165" s="42"/>
-      <c r="B165" s="42"/>
+      <c r="A165" s="43"/>
+      <c r="B165" s="43"/>
     </row>
     <row r="166">
-      <c r="A166" s="42"/>
-      <c r="B166" s="42"/>
+      <c r="A166" s="43"/>
+      <c r="B166" s="43"/>
     </row>
     <row r="167">
-      <c r="A167" s="42"/>
-      <c r="B167" s="42"/>
+      <c r="A167" s="43"/>
+      <c r="B167" s="43"/>
     </row>
     <row r="168">
-      <c r="A168" s="42"/>
-      <c r="B168" s="42"/>
+      <c r="A168" s="43"/>
+      <c r="B168" s="43"/>
     </row>
     <row r="169">
-      <c r="A169" s="42"/>
-      <c r="B169" s="42"/>
+      <c r="A169" s="43"/>
+      <c r="B169" s="43"/>
     </row>
     <row r="170">
-      <c r="A170" s="42"/>
-      <c r="B170" s="42"/>
+      <c r="A170" s="43"/>
+      <c r="B170" s="43"/>
     </row>
     <row r="171">
-      <c r="A171" s="42"/>
-      <c r="B171" s="42"/>
+      <c r="A171" s="43"/>
+      <c r="B171" s="43"/>
     </row>
     <row r="172">
-      <c r="A172" s="42"/>
-      <c r="B172" s="42"/>
+      <c r="A172" s="43"/>
+      <c r="B172" s="43"/>
     </row>
     <row r="173">
-      <c r="A173" s="42"/>
-      <c r="B173" s="42"/>
+      <c r="A173" s="43"/>
+      <c r="B173" s="43"/>
     </row>
     <row r="174">
-      <c r="A174" s="42"/>
-      <c r="B174" s="42"/>
+      <c r="A174" s="43"/>
+      <c r="B174" s="43"/>
     </row>
     <row r="175">
-      <c r="A175" s="42"/>
-      <c r="B175" s="42"/>
+      <c r="A175" s="43"/>
+      <c r="B175" s="43"/>
     </row>
     <row r="176">
-      <c r="A176" s="42"/>
-      <c r="B176" s="42"/>
+      <c r="A176" s="43"/>
+      <c r="B176" s="43"/>
     </row>
     <row r="177">
-      <c r="A177" s="42"/>
-      <c r="B177" s="42"/>
+      <c r="A177" s="43"/>
+      <c r="B177" s="43"/>
     </row>
     <row r="178">
-      <c r="A178" s="42"/>
-      <c r="B178" s="42"/>
+      <c r="A178" s="43"/>
+      <c r="B178" s="43"/>
     </row>
     <row r="179">
-      <c r="A179" s="42"/>
-      <c r="B179" s="42"/>
+      <c r="A179" s="43"/>
+      <c r="B179" s="43"/>
     </row>
     <row r="180">
-      <c r="A180" s="42"/>
-      <c r="B180" s="42"/>
+      <c r="A180" s="43"/>
+      <c r="B180" s="43"/>
     </row>
     <row r="181">
-      <c r="A181" s="42"/>
-      <c r="B181" s="42"/>
+      <c r="A181" s="43"/>
+      <c r="B181" s="43"/>
     </row>
     <row r="182">
-      <c r="A182" s="42"/>
-      <c r="B182" s="42"/>
+      <c r="A182" s="43"/>
+      <c r="B182" s="43"/>
     </row>
     <row r="183">
-      <c r="A183" s="42"/>
-      <c r="B183" s="42"/>
+      <c r="A183" s="43"/>
+      <c r="B183" s="43"/>
     </row>
     <row r="184">
-      <c r="A184" s="42"/>
-      <c r="B184" s="42"/>
+      <c r="A184" s="43"/>
+      <c r="B184" s="43"/>
     </row>
     <row r="185">
-      <c r="A185" s="42"/>
-      <c r="B185" s="42"/>
+      <c r="A185" s="43"/>
+      <c r="B185" s="43"/>
     </row>
     <row r="186">
-      <c r="A186" s="42"/>
-      <c r="B186" s="42"/>
+      <c r="A186" s="43"/>
+      <c r="B186" s="43"/>
     </row>
     <row r="187">
-      <c r="A187" s="42"/>
-      <c r="B187" s="42"/>
+      <c r="A187" s="43"/>
+      <c r="B187" s="43"/>
     </row>
     <row r="188">
-      <c r="A188" s="42"/>
-      <c r="B188" s="42"/>
+      <c r="A188" s="43"/>
+      <c r="B188" s="43"/>
     </row>
     <row r="189">
-      <c r="A189" s="42"/>
-      <c r="B189" s="42"/>
+      <c r="A189" s="43"/>
+      <c r="B189" s="43"/>
     </row>
     <row r="190">
-      <c r="A190" s="42"/>
-      <c r="B190" s="42"/>
+      <c r="A190" s="43"/>
+      <c r="B190" s="43"/>
     </row>
     <row r="191">
-      <c r="A191" s="42"/>
-      <c r="B191" s="42"/>
+      <c r="A191" s="43"/>
+      <c r="B191" s="43"/>
     </row>
     <row r="192">
-      <c r="A192" s="42"/>
-      <c r="B192" s="42"/>
+      <c r="A192" s="43"/>
+      <c r="B192" s="43"/>
     </row>
     <row r="193">
-      <c r="A193" s="42"/>
-      <c r="B193" s="42"/>
+      <c r="A193" s="43"/>
+      <c r="B193" s="43"/>
     </row>
     <row r="194">
-      <c r="A194" s="42"/>
-      <c r="B194" s="42"/>
+      <c r="A194" s="43"/>
+      <c r="B194" s="43"/>
     </row>
     <row r="195">
-      <c r="A195" s="42"/>
-      <c r="B195" s="42"/>
+      <c r="A195" s="43"/>
+      <c r="B195" s="43"/>
     </row>
     <row r="196">
-      <c r="A196" s="42"/>
-      <c r="B196" s="42"/>
+      <c r="A196" s="43"/>
+      <c r="B196" s="43"/>
     </row>
     <row r="197">
-      <c r="A197" s="42"/>
-      <c r="B197" s="42"/>
+      <c r="A197" s="43"/>
+      <c r="B197" s="43"/>
     </row>
     <row r="198">
-      <c r="A198" s="42"/>
-      <c r="B198" s="42"/>
+      <c r="A198" s="43"/>
+      <c r="B198" s="43"/>
     </row>
     <row r="199">
-      <c r="A199" s="42"/>
-      <c r="B199" s="42"/>
+      <c r="A199" s="43"/>
+      <c r="B199" s="43"/>
     </row>
     <row r="200">
-      <c r="A200" s="42"/>
-      <c r="B200" s="42"/>
+      <c r="A200" s="43"/>
+      <c r="B200" s="43"/>
     </row>
     <row r="201">
-      <c r="A201" s="42"/>
-      <c r="B201" s="42"/>
+      <c r="A201" s="43"/>
+      <c r="B201" s="43"/>
     </row>
     <row r="202">
-      <c r="A202" s="42"/>
-      <c r="B202" s="42"/>
+      <c r="A202" s="43"/>
+      <c r="B202" s="43"/>
     </row>
     <row r="203">
-      <c r="A203" s="42"/>
-      <c r="B203" s="42"/>
+      <c r="A203" s="43"/>
+      <c r="B203" s="43"/>
     </row>
     <row r="204">
-      <c r="A204" s="42"/>
-      <c r="B204" s="42"/>
+      <c r="A204" s="43"/>
+      <c r="B204" s="43"/>
     </row>
     <row r="205">
-      <c r="A205" s="42"/>
-      <c r="B205" s="42"/>
+      <c r="A205" s="43"/>
+      <c r="B205" s="43"/>
     </row>
     <row r="206">
-      <c r="A206" s="42"/>
-      <c r="B206" s="42"/>
+      <c r="A206" s="43"/>
+      <c r="B206" s="43"/>
     </row>
     <row r="207">
-      <c r="A207" s="42"/>
-      <c r="B207" s="42"/>
+      <c r="A207" s="43"/>
+      <c r="B207" s="43"/>
     </row>
     <row r="208">
-      <c r="A208" s="42"/>
-      <c r="B208" s="42"/>
+      <c r="A208" s="43"/>
+      <c r="B208" s="43"/>
     </row>
     <row r="209">
-      <c r="A209" s="42"/>
-      <c r="B209" s="42"/>
+      <c r="A209" s="43"/>
+      <c r="B209" s="43"/>
     </row>
     <row r="210">
-      <c r="A210" s="42"/>
-      <c r="B210" s="42"/>
+      <c r="A210" s="43"/>
+      <c r="B210" s="43"/>
     </row>
     <row r="211">
-      <c r="A211" s="42"/>
-      <c r="B211" s="42"/>
+      <c r="A211" s="43"/>
+      <c r="B211" s="43"/>
     </row>
     <row r="212">
-      <c r="A212" s="42"/>
-      <c r="B212" s="42"/>
+      <c r="A212" s="43"/>
+      <c r="B212" s="43"/>
     </row>
     <row r="213">
-      <c r="A213" s="42"/>
-      <c r="B213" s="42"/>
+      <c r="A213" s="43"/>
+      <c r="B213" s="43"/>
     </row>
     <row r="214">
-      <c r="A214" s="42"/>
-      <c r="B214" s="42"/>
+      <c r="A214" s="43"/>
+      <c r="B214" s="43"/>
     </row>
     <row r="215">
-      <c r="A215" s="42"/>
-      <c r="B215" s="42"/>
+      <c r="A215" s="43"/>
+      <c r="B215" s="43"/>
     </row>
     <row r="216">
-      <c r="A216" s="42"/>
-      <c r="B216" s="42"/>
+      <c r="A216" s="43"/>
+      <c r="B216" s="43"/>
     </row>
     <row r="217">
-      <c r="A217" s="42"/>
-      <c r="B217" s="42"/>
+      <c r="A217" s="43"/>
+      <c r="B217" s="43"/>
     </row>
     <row r="218">
-      <c r="A218" s="42"/>
-      <c r="B218" s="42"/>
+      <c r="A218" s="43"/>
+      <c r="B218" s="43"/>
     </row>
     <row r="219">
-      <c r="A219" s="42"/>
-      <c r="B219" s="42"/>
+      <c r="A219" s="43"/>
+      <c r="B219" s="43"/>
     </row>
     <row r="220">
-      <c r="A220" s="42"/>
-      <c r="B220" s="42"/>
+      <c r="A220" s="43"/>
+      <c r="B220" s="43"/>
     </row>
     <row r="221">
-      <c r="A221" s="42"/>
-      <c r="B221" s="42"/>
+      <c r="A221" s="43"/>
+      <c r="B221" s="43"/>
     </row>
     <row r="222">
-      <c r="A222" s="42"/>
-      <c r="B222" s="42"/>
+      <c r="A222" s="43"/>
+      <c r="B222" s="43"/>
     </row>
     <row r="223">
-      <c r="A223" s="42"/>
-      <c r="B223" s="42"/>
+      <c r="A223" s="43"/>
+      <c r="B223" s="43"/>
     </row>
     <row r="224">
-      <c r="A224" s="42"/>
-      <c r="B224" s="42"/>
+      <c r="A224" s="43"/>
+      <c r="B224" s="43"/>
     </row>
     <row r="225">
-      <c r="A225" s="42"/>
-      <c r="B225" s="42"/>
+      <c r="A225" s="43"/>
+      <c r="B225" s="43"/>
     </row>
     <row r="226">
-      <c r="A226" s="42"/>
-      <c r="B226" s="42"/>
+      <c r="A226" s="43"/>
+      <c r="B226" s="43"/>
     </row>
     <row r="227">
-      <c r="A227" s="42"/>
-      <c r="B227" s="42"/>
+      <c r="A227" s="43"/>
+      <c r="B227" s="43"/>
     </row>
     <row r="228">
-      <c r="A228" s="42"/>
-      <c r="B228" s="42"/>
+      <c r="A228" s="43"/>
+      <c r="B228" s="43"/>
     </row>
     <row r="229">
-      <c r="A229" s="42"/>
-      <c r="B229" s="42"/>
+      <c r="A229" s="43"/>
+      <c r="B229" s="43"/>
     </row>
     <row r="230">
-      <c r="A230" s="42"/>
-      <c r="B230" s="42"/>
+      <c r="A230" s="43"/>
+      <c r="B230" s="43"/>
     </row>
     <row r="231">
-      <c r="A231" s="42"/>
-      <c r="B231" s="42"/>
+      <c r="A231" s="43"/>
+      <c r="B231" s="43"/>
     </row>
     <row r="232">
-      <c r="A232" s="42"/>
-      <c r="B232" s="42"/>
+      <c r="A232" s="43"/>
+      <c r="B232" s="43"/>
     </row>
     <row r="233">
-      <c r="A233" s="42"/>
-      <c r="B233" s="42"/>
+      <c r="A233" s="43"/>
+      <c r="B233" s="43"/>
     </row>
     <row r="234">
-      <c r="A234" s="42"/>
-      <c r="B234" s="42"/>
+      <c r="A234" s="43"/>
+      <c r="B234" s="43"/>
     </row>
     <row r="235">
-      <c r="A235" s="42"/>
-      <c r="B235" s="42"/>
+      <c r="A235" s="43"/>
+      <c r="B235" s="43"/>
     </row>
     <row r="236">
-      <c r="A236" s="42"/>
-      <c r="B236" s="42"/>
+      <c r="A236" s="43"/>
+      <c r="B236" s="43"/>
     </row>
     <row r="237">
-      <c r="A237" s="42"/>
-      <c r="B237" s="42"/>
+      <c r="A237" s="43"/>
+      <c r="B237" s="43"/>
     </row>
     <row r="238">
-      <c r="A238" s="42"/>
-      <c r="B238" s="42"/>
+      <c r="A238" s="43"/>
+      <c r="B238" s="43"/>
     </row>
     <row r="239">
-      <c r="A239" s="42"/>
-      <c r="B239" s="42"/>
+      <c r="A239" s="43"/>
+      <c r="B239" s="43"/>
     </row>
     <row r="240">
-      <c r="A240" s="42"/>
-      <c r="B240" s="42"/>
+      <c r="A240" s="43"/>
+      <c r="B240" s="43"/>
     </row>
     <row r="241">
-      <c r="A241" s="42"/>
-      <c r="B241" s="42"/>
+      <c r="A241" s="43"/>
+      <c r="B241" s="43"/>
     </row>
     <row r="242">
-      <c r="A242" s="42"/>
-      <c r="B242" s="42"/>
+      <c r="A242" s="43"/>
+      <c r="B242" s="43"/>
     </row>
     <row r="243">
-      <c r="A243" s="42"/>
-      <c r="B243" s="42"/>
+      <c r="A243" s="43"/>
+      <c r="B243" s="43"/>
     </row>
     <row r="244">
-      <c r="A244" s="42"/>
-      <c r="B244" s="42"/>
+      <c r="A244" s="43"/>
+      <c r="B244" s="43"/>
     </row>
     <row r="245">
-      <c r="A245" s="42"/>
-      <c r="B245" s="42"/>
+      <c r="A245" s="43"/>
+      <c r="B245" s="43"/>
     </row>
     <row r="246">
-      <c r="A246" s="42"/>
-      <c r="B246" s="42"/>
+      <c r="A246" s="43"/>
+      <c r="B246" s="43"/>
     </row>
     <row r="247">
-      <c r="A247" s="42"/>
-      <c r="B247" s="42"/>
+      <c r="A247" s="43"/>
+      <c r="B247" s="43"/>
     </row>
     <row r="248">
-      <c r="A248" s="42"/>
-      <c r="B248" s="42"/>
+      <c r="A248" s="43"/>
+      <c r="B248" s="43"/>
     </row>
     <row r="249">
-      <c r="A249" s="42"/>
-      <c r="B249" s="42"/>
+      <c r="A249" s="43"/>
+      <c r="B249" s="43"/>
     </row>
     <row r="250">
-      <c r="A250" s="42"/>
-      <c r="B250" s="42"/>
+      <c r="A250" s="43"/>
+      <c r="B250" s="43"/>
     </row>
     <row r="251">
-      <c r="A251" s="42"/>
-      <c r="B251" s="42"/>
+      <c r="A251" s="43"/>
+      <c r="B251" s="43"/>
     </row>
     <row r="252">
-      <c r="A252" s="42"/>
-      <c r="B252" s="42"/>
+      <c r="A252" s="43"/>
+      <c r="B252" s="43"/>
     </row>
     <row r="253">
-      <c r="A253" s="42"/>
-      <c r="B253" s="42"/>
+      <c r="A253" s="43"/>
+      <c r="B253" s="43"/>
     </row>
     <row r="254">
-      <c r="A254" s="42"/>
-      <c r="B254" s="42"/>
+      <c r="A254" s="43"/>
+      <c r="B254" s="43"/>
     </row>
     <row r="255">
-      <c r="A255" s="42"/>
-      <c r="B255" s="42"/>
+      <c r="A255" s="43"/>
+      <c r="B255" s="43"/>
     </row>
     <row r="256">
-      <c r="A256" s="42"/>
-      <c r="B256" s="42"/>
+      <c r="A256" s="43"/>
+      <c r="B256" s="43"/>
     </row>
     <row r="257">
-      <c r="A257" s="42"/>
-      <c r="B257" s="42"/>
+      <c r="A257" s="43"/>
+      <c r="B257" s="43"/>
     </row>
     <row r="258">
-      <c r="A258" s="42"/>
-      <c r="B258" s="42"/>
+      <c r="A258" s="43"/>
+      <c r="B258" s="43"/>
     </row>
     <row r="259">
-      <c r="A259" s="42"/>
-      <c r="B259" s="42"/>
+      <c r="A259" s="43"/>
+      <c r="B259" s="43"/>
     </row>
     <row r="260">
-      <c r="A260" s="42"/>
-      <c r="B260" s="42"/>
+      <c r="A260" s="43"/>
+      <c r="B260" s="43"/>
     </row>
     <row r="261">
-      <c r="A261" s="42"/>
-      <c r="B261" s="42"/>
+      <c r="A261" s="43"/>
+      <c r="B261" s="43"/>
     </row>
     <row r="262">
-      <c r="A262" s="42"/>
-      <c r="B262" s="42"/>
+      <c r="A262" s="43"/>
+      <c r="B262" s="43"/>
     </row>
     <row r="263">
-      <c r="A263" s="42"/>
-      <c r="B263" s="42"/>
+      <c r="A263" s="43"/>
+      <c r="B263" s="43"/>
     </row>
     <row r="264">
-      <c r="A264" s="42"/>
-      <c r="B264" s="42"/>
+      <c r="A264" s="43"/>
+      <c r="B264" s="43"/>
     </row>
     <row r="265">
-      <c r="A265" s="42"/>
-      <c r="B265" s="42"/>
+      <c r="A265" s="43"/>
+      <c r="B265" s="43"/>
     </row>
     <row r="266">
-      <c r="A266" s="42"/>
-      <c r="B266" s="42"/>
+      <c r="A266" s="43"/>
+      <c r="B266" s="43"/>
     </row>
     <row r="267">
-      <c r="A267" s="42"/>
-      <c r="B267" s="42"/>
+      <c r="A267" s="43"/>
+      <c r="B267" s="43"/>
     </row>
     <row r="268">
-      <c r="A268" s="42"/>
-      <c r="B268" s="42"/>
+      <c r="A268" s="43"/>
+      <c r="B268" s="43"/>
     </row>
     <row r="269">
-      <c r="A269" s="42"/>
-      <c r="B269" s="42"/>
+      <c r="A269" s="43"/>
+      <c r="B269" s="43"/>
     </row>
     <row r="270">
-      <c r="A270" s="42"/>
-      <c r="B270" s="42"/>
+      <c r="A270" s="43"/>
+      <c r="B270" s="43"/>
     </row>
     <row r="271">
-      <c r="A271" s="42"/>
-      <c r="B271" s="42"/>
+      <c r="A271" s="43"/>
+      <c r="B271" s="43"/>
     </row>
     <row r="272">
-      <c r="A272" s="42"/>
-      <c r="B272" s="42"/>
+      <c r="A272" s="43"/>
+      <c r="B272" s="43"/>
     </row>
     <row r="273">
-      <c r="A273" s="42"/>
-      <c r="B273" s="42"/>
+      <c r="A273" s="43"/>
+      <c r="B273" s="43"/>
     </row>
     <row r="274">
-      <c r="A274" s="42"/>
-      <c r="B274" s="42"/>
+      <c r="A274" s="43"/>
+      <c r="B274" s="43"/>
     </row>
     <row r="275">
-      <c r="A275" s="42"/>
-      <c r="B275" s="42"/>
+      <c r="A275" s="43"/>
+      <c r="B275" s="43"/>
     </row>
     <row r="276">
-      <c r="A276" s="42"/>
-      <c r="B276" s="42"/>
+      <c r="A276" s="43"/>
+      <c r="B276" s="43"/>
     </row>
     <row r="277">
-      <c r="A277" s="42"/>
-      <c r="B277" s="42"/>
+      <c r="A277" s="43"/>
+      <c r="B277" s="43"/>
     </row>
     <row r="278">
-      <c r="A278" s="42"/>
-      <c r="B278" s="42"/>
+      <c r="A278" s="43"/>
+      <c r="B278" s="43"/>
     </row>
     <row r="279">
-      <c r="A279" s="42"/>
-      <c r="B279" s="42"/>
+      <c r="A279" s="43"/>
+      <c r="B279" s="43"/>
     </row>
     <row r="280">
-      <c r="A280" s="42"/>
-      <c r="B280" s="42"/>
+      <c r="A280" s="43"/>
+      <c r="B280" s="43"/>
     </row>
     <row r="281">
-      <c r="A281" s="42"/>
-      <c r="B281" s="42"/>
+      <c r="A281" s="43"/>
+      <c r="B281" s="43"/>
     </row>
     <row r="282">
-      <c r="A282" s="42"/>
-      <c r="B282" s="42"/>
+      <c r="A282" s="43"/>
+      <c r="B282" s="43"/>
     </row>
     <row r="283">
-      <c r="A283" s="42"/>
-      <c r="B283" s="42"/>
+      <c r="A283" s="43"/>
+      <c r="B283" s="43"/>
     </row>
     <row r="284">
-      <c r="A284" s="42"/>
-      <c r="B284" s="42"/>
+      <c r="A284" s="43"/>
+      <c r="B284" s="43"/>
     </row>
     <row r="285">
-      <c r="A285" s="42"/>
-      <c r="B285" s="42"/>
+      <c r="A285" s="43"/>
+      <c r="B285" s="43"/>
     </row>
     <row r="286">
-      <c r="A286" s="42"/>
-      <c r="B286" s="42"/>
+      <c r="A286" s="43"/>
+      <c r="B286" s="43"/>
     </row>
     <row r="287">
-      <c r="A287" s="42"/>
-      <c r="B287" s="42"/>
+      <c r="A287" s="43"/>
+      <c r="B287" s="43"/>
     </row>
     <row r="288">
-      <c r="A288" s="42"/>
-      <c r="B288" s="42"/>
+      <c r="A288" s="43"/>
+      <c r="B288" s="43"/>
     </row>
     <row r="289">
-      <c r="A289" s="42"/>
-      <c r="B289" s="42"/>
+      <c r="A289" s="43"/>
+      <c r="B289" s="43"/>
     </row>
     <row r="290">
-      <c r="A290" s="42"/>
-      <c r="B290" s="42"/>
+      <c r="A290" s="43"/>
+      <c r="B290" s="43"/>
     </row>
     <row r="291">
-      <c r="A291" s="42"/>
-      <c r="B291" s="42"/>
+      <c r="A291" s="43"/>
+      <c r="B291" s="43"/>
     </row>
     <row r="292">
-      <c r="A292" s="42"/>
-      <c r="B292" s="42"/>
+      <c r="A292" s="43"/>
+      <c r="B292" s="43"/>
     </row>
     <row r="293">
-      <c r="A293" s="42"/>
-      <c r="B293" s="42"/>
+      <c r="A293" s="43"/>
+      <c r="B293" s="43"/>
     </row>
     <row r="294">
-      <c r="A294" s="42"/>
-      <c r="B294" s="42"/>
+      <c r="A294" s="43"/>
+      <c r="B294" s="43"/>
     </row>
     <row r="295">
-      <c r="A295" s="42"/>
-      <c r="B295" s="42"/>
+      <c r="A295" s="43"/>
+      <c r="B295" s="43"/>
     </row>
     <row r="296">
-      <c r="A296" s="42"/>
-      <c r="B296" s="42"/>
+      <c r="A296" s="43"/>
+      <c r="B296" s="43"/>
     </row>
     <row r="297">
-      <c r="A297" s="42"/>
-      <c r="B297" s="42"/>
+      <c r="A297" s="43"/>
+      <c r="B297" s="43"/>
     </row>
     <row r="298">
-      <c r="A298" s="42"/>
-      <c r="B298" s="42"/>
+      <c r="A298" s="43"/>
+      <c r="B298" s="43"/>
     </row>
     <row r="299">
-      <c r="A299" s="42"/>
-      <c r="B299" s="42"/>
+      <c r="A299" s="43"/>
+      <c r="B299" s="43"/>
     </row>
     <row r="300">
-      <c r="A300" s="42"/>
-      <c r="B300" s="42"/>
+      <c r="A300" s="43"/>
+      <c r="B300" s="43"/>
     </row>
     <row r="301">
-      <c r="A301" s="42"/>
-      <c r="B301" s="42"/>
+      <c r="A301" s="43"/>
+      <c r="B301" s="43"/>
     </row>
     <row r="302">
-      <c r="A302" s="42"/>
-      <c r="B302" s="42"/>
+      <c r="A302" s="43"/>
+      <c r="B302" s="43"/>
     </row>
     <row r="303">
-      <c r="A303" s="42"/>
-      <c r="B303" s="42"/>
+      <c r="A303" s="43"/>
+      <c r="B303" s="43"/>
     </row>
     <row r="304">
-      <c r="A304" s="42"/>
-      <c r="B304" s="42"/>
+      <c r="A304" s="43"/>
+      <c r="B304" s="43"/>
     </row>
     <row r="305">
-      <c r="A305" s="42"/>
-      <c r="B305" s="42"/>
+      <c r="A305" s="43"/>
+      <c r="B305" s="43"/>
     </row>
     <row r="306">
-      <c r="A306" s="42"/>
-      <c r="B306" s="42"/>
+      <c r="A306" s="43"/>
+      <c r="B306" s="43"/>
     </row>
     <row r="307">
-      <c r="A307" s="42"/>
-      <c r="B307" s="42"/>
+      <c r="A307" s="43"/>
+      <c r="B307" s="43"/>
     </row>
     <row r="308">
-      <c r="A308" s="42"/>
-      <c r="B308" s="42"/>
+      <c r="A308" s="43"/>
+      <c r="B308" s="43"/>
     </row>
     <row r="309">
-      <c r="A309" s="42"/>
-      <c r="B309" s="42"/>
+      <c r="A309" s="43"/>
+      <c r="B309" s="43"/>
     </row>
     <row r="310">
-      <c r="A310" s="42"/>
-      <c r="B310" s="42"/>
+      <c r="A310" s="43"/>
+      <c r="B310" s="43"/>
     </row>
     <row r="311">
-      <c r="A311" s="42"/>
-      <c r="B311" s="42"/>
+      <c r="A311" s="43"/>
+      <c r="B311" s="43"/>
     </row>
     <row r="312">
-      <c r="A312" s="42"/>
-      <c r="B312" s="42"/>
+      <c r="A312" s="43"/>
+      <c r="B312" s="43"/>
     </row>
     <row r="313">
-      <c r="A313" s="42"/>
-      <c r="B313" s="42"/>
+      <c r="A313" s="43"/>
+      <c r="B313" s="43"/>
     </row>
     <row r="314">
-      <c r="A314" s="42"/>
-      <c r="B314" s="42"/>
+      <c r="A314" s="43"/>
+      <c r="B314" s="43"/>
     </row>
     <row r="315">
-      <c r="A315" s="42"/>
-      <c r="B315" s="42"/>
+      <c r="A315" s="43"/>
+      <c r="B315" s="43"/>
     </row>
     <row r="316">
-      <c r="A316" s="42"/>
-      <c r="B316" s="42"/>
+      <c r="A316" s="43"/>
+      <c r="B316" s="43"/>
     </row>
     <row r="317">
-      <c r="A317" s="42"/>
-      <c r="B317" s="42"/>
+      <c r="A317" s="43"/>
+      <c r="B317" s="43"/>
     </row>
     <row r="318">
-      <c r="A318" s="42"/>
-      <c r="B318" s="42"/>
+      <c r="A318" s="43"/>
+      <c r="B318" s="43"/>
     </row>
     <row r="319">
-      <c r="A319" s="42"/>
-      <c r="B319" s="42"/>
+      <c r="A319" s="43"/>
+      <c r="B319" s="43"/>
     </row>
     <row r="320">
-      <c r="A320" s="42"/>
-      <c r="B320" s="42"/>
+      <c r="A320" s="43"/>
+      <c r="B320" s="43"/>
     </row>
     <row r="321">
-      <c r="A321" s="42"/>
-      <c r="B321" s="42"/>
+      <c r="A321" s="43"/>
+      <c r="B321" s="43"/>
     </row>
     <row r="322">
-      <c r="A322" s="42"/>
-      <c r="B322" s="42"/>
+      <c r="A322" s="43"/>
+      <c r="B322" s="43"/>
     </row>
     <row r="323">
-      <c r="A323" s="42"/>
-      <c r="B323" s="42"/>
+      <c r="A323" s="43"/>
+      <c r="B323" s="43"/>
     </row>
     <row r="324">
-      <c r="A324" s="42"/>
-      <c r="B324" s="42"/>
+      <c r="A324" s="43"/>
+      <c r="B324" s="43"/>
     </row>
     <row r="325">
-      <c r="A325" s="42"/>
-      <c r="B325" s="42"/>
+      <c r="A325" s="43"/>
+      <c r="B325" s="43"/>
     </row>
     <row r="326">
-      <c r="A326" s="42"/>
-      <c r="B326" s="42"/>
+      <c r="A326" s="43"/>
+      <c r="B326" s="43"/>
     </row>
     <row r="327">
-      <c r="A327" s="42"/>
-      <c r="B327" s="42"/>
+      <c r="A327" s="43"/>
+      <c r="B327" s="43"/>
     </row>
     <row r="328">
-      <c r="A328" s="42"/>
-      <c r="B328" s="42"/>
+      <c r="A328" s="43"/>
+      <c r="B328" s="43"/>
     </row>
     <row r="329">
-      <c r="A329" s="42"/>
-      <c r="B329" s="42"/>
+      <c r="A329" s="43"/>
+      <c r="B329" s="43"/>
     </row>
     <row r="330">
-      <c r="A330" s="42"/>
-      <c r="B330" s="42"/>
+      <c r="A330" s="43"/>
+      <c r="B330" s="43"/>
     </row>
     <row r="331">
-      <c r="A331" s="42"/>
-      <c r="B331" s="42"/>
+      <c r="A331" s="43"/>
+      <c r="B331" s="43"/>
     </row>
     <row r="332">
-      <c r="A332" s="42"/>
-      <c r="B332" s="42"/>
+      <c r="A332" s="43"/>
+      <c r="B332" s="43"/>
     </row>
     <row r="333">
-      <c r="A333" s="42"/>
-      <c r="B333" s="42"/>
+      <c r="A333" s="43"/>
+      <c r="B333" s="43"/>
     </row>
     <row r="334">
-      <c r="A334" s="42"/>
-      <c r="B334" s="42"/>
+      <c r="A334" s="43"/>
+      <c r="B334" s="43"/>
     </row>
     <row r="335">
-      <c r="A335" s="42"/>
-      <c r="B335" s="42"/>
+      <c r="A335" s="43"/>
+      <c r="B335" s="43"/>
     </row>
     <row r="336">
-      <c r="A336" s="42"/>
-      <c r="B336" s="42"/>
+      <c r="A336" s="43"/>
+      <c r="B336" s="43"/>
     </row>
     <row r="337">
-      <c r="A337" s="42"/>
-      <c r="B337" s="42"/>
+      <c r="A337" s="43"/>
+      <c r="B337" s="43"/>
     </row>
     <row r="338">
-      <c r="A338" s="42"/>
-      <c r="B338" s="42"/>
+      <c r="A338" s="43"/>
+      <c r="B338" s="43"/>
     </row>
     <row r="339">
-      <c r="A339" s="42"/>
-      <c r="B339" s="42"/>
+      <c r="A339" s="43"/>
+      <c r="B339" s="43"/>
     </row>
     <row r="340">
-      <c r="A340" s="42"/>
-      <c r="B340" s="42"/>
+      <c r="A340" s="43"/>
+      <c r="B340" s="43"/>
     </row>
     <row r="341">
-      <c r="A341" s="42"/>
-      <c r="B341" s="42"/>
+      <c r="A341" s="43"/>
+      <c r="B341" s="43"/>
     </row>
     <row r="342">
-      <c r="A342" s="42"/>
-      <c r="B342" s="42"/>
+      <c r="A342" s="43"/>
+      <c r="B342" s="43"/>
     </row>
     <row r="343">
-      <c r="A343" s="42"/>
-      <c r="B343" s="42"/>
+      <c r="A343" s="43"/>
+      <c r="B343" s="43"/>
     </row>
     <row r="344">
-      <c r="A344" s="42"/>
-      <c r="B344" s="42"/>
+      <c r="A344" s="43"/>
+      <c r="B344" s="43"/>
     </row>
     <row r="345">
-      <c r="A345" s="42"/>
-      <c r="B345" s="42"/>
+      <c r="A345" s="43"/>
+      <c r="B345" s="43"/>
     </row>
     <row r="346">
-      <c r="A346" s="42"/>
-      <c r="B346" s="42"/>
+      <c r="A346" s="43"/>
+      <c r="B346" s="43"/>
     </row>
     <row r="347">
-      <c r="A347" s="42"/>
-      <c r="B347" s="42"/>
+      <c r="A347" s="43"/>
+      <c r="B347" s="43"/>
     </row>
     <row r="348">
-      <c r="A348" s="42"/>
-      <c r="B348" s="42"/>
+      <c r="A348" s="43"/>
+      <c r="B348" s="43"/>
     </row>
     <row r="349">
-      <c r="A349" s="42"/>
-      <c r="B349" s="42"/>
+      <c r="A349" s="43"/>
+      <c r="B349" s="43"/>
     </row>
     <row r="350">
-      <c r="A350" s="42"/>
-      <c r="B350" s="42"/>
+      <c r="A350" s="43"/>
+      <c r="B350" s="43"/>
     </row>
     <row r="351">
-      <c r="A351" s="42"/>
-      <c r="B351" s="42"/>
+      <c r="A351" s="43"/>
+      <c r="B351" s="43"/>
     </row>
     <row r="352">
-      <c r="A352" s="42"/>
-      <c r="B352" s="42"/>
+      <c r="A352" s="43"/>
+      <c r="B352" s="43"/>
     </row>
     <row r="353">
-      <c r="A353" s="42"/>
-      <c r="B353" s="42"/>
+      <c r="A353" s="43"/>
+      <c r="B353" s="43"/>
     </row>
     <row r="354">
-      <c r="A354" s="42"/>
-      <c r="B354" s="42"/>
+      <c r="A354" s="43"/>
+      <c r="B354" s="43"/>
     </row>
     <row r="355">
-      <c r="A355" s="42"/>
-      <c r="B355" s="42"/>
+      <c r="A355" s="43"/>
+      <c r="B355" s="43"/>
     </row>
     <row r="356">
-      <c r="A356" s="42"/>
-      <c r="B356" s="42"/>
+      <c r="A356" s="43"/>
+      <c r="B356" s="43"/>
     </row>
     <row r="357">
-      <c r="A357" s="42"/>
-      <c r="B357" s="42"/>
+      <c r="A357" s="43"/>
+      <c r="B357" s="43"/>
     </row>
     <row r="358">
-      <c r="A358" s="42"/>
-      <c r="B358" s="42"/>
+      <c r="A358" s="43"/>
+      <c r="B358" s="43"/>
     </row>
     <row r="359">
-      <c r="A359" s="42"/>
-      <c r="B359" s="42"/>
+      <c r="A359" s="43"/>
+      <c r="B359" s="43"/>
     </row>
     <row r="360">
-      <c r="A360" s="42"/>
-      <c r="B360" s="42"/>
+      <c r="A360" s="43"/>
+      <c r="B360" s="43"/>
     </row>
     <row r="361">
-      <c r="A361" s="42"/>
-      <c r="B361" s="42"/>
+      <c r="A361" s="43"/>
+      <c r="B361" s="43"/>
     </row>
     <row r="362">
-      <c r="A362" s="42"/>
-      <c r="B362" s="42"/>
+      <c r="A362" s="43"/>
+      <c r="B362" s="43"/>
     </row>
     <row r="363">
-      <c r="A363" s="42"/>
-      <c r="B363" s="42"/>
+      <c r="A363" s="43"/>
+      <c r="B363" s="43"/>
     </row>
     <row r="364">
-      <c r="A364" s="42"/>
-      <c r="B364" s="42"/>
+      <c r="A364" s="43"/>
+      <c r="B364" s="43"/>
     </row>
     <row r="365">
-      <c r="A365" s="42"/>
-      <c r="B365" s="42"/>
+      <c r="A365" s="43"/>
+      <c r="B365" s="43"/>
     </row>
     <row r="366">
-      <c r="A366" s="42"/>
-      <c r="B366" s="42"/>
+      <c r="A366" s="43"/>
+      <c r="B366" s="43"/>
     </row>
     <row r="367">
-      <c r="A367" s="42"/>
-      <c r="B367" s="42"/>
+      <c r="A367" s="43"/>
+      <c r="B367" s="43"/>
     </row>
     <row r="368">
-      <c r="A368" s="42"/>
-      <c r="B368" s="42"/>
+      <c r="A368" s="43"/>
+      <c r="B368" s="43"/>
     </row>
     <row r="369">
-      <c r="A369" s="42"/>
-      <c r="B369" s="42"/>
+      <c r="A369" s="43"/>
+      <c r="B369" s="43"/>
     </row>
     <row r="370">
-      <c r="A370" s="42"/>
-      <c r="B370" s="42"/>
+      <c r="A370" s="43"/>
+      <c r="B370" s="43"/>
     </row>
     <row r="371">
-      <c r="A371" s="42"/>
-      <c r="B371" s="42"/>
+      <c r="A371" s="43"/>
+      <c r="B371" s="43"/>
     </row>
     <row r="372">
-      <c r="A372" s="42"/>
-      <c r="B372" s="42"/>
+      <c r="A372" s="43"/>
+      <c r="B372" s="43"/>
     </row>
     <row r="373">
-      <c r="A373" s="42"/>
-      <c r="B373" s="42"/>
+      <c r="A373" s="43"/>
+      <c r="B373" s="43"/>
     </row>
     <row r="374">
-      <c r="A374" s="42"/>
-      <c r="B374" s="42"/>
+      <c r="A374" s="43"/>
+      <c r="B374" s="43"/>
     </row>
     <row r="375">
-      <c r="A375" s="42"/>
-      <c r="B375" s="42"/>
+      <c r="A375" s="43"/>
+      <c r="B375" s="43"/>
     </row>
     <row r="376">
-      <c r="A376" s="42"/>
-      <c r="B376" s="42"/>
+      <c r="A376" s="43"/>
+      <c r="B376" s="43"/>
     </row>
     <row r="377">
-      <c r="A377" s="42"/>
-      <c r="B377" s="42"/>
+      <c r="A377" s="43"/>
+      <c r="B377" s="43"/>
     </row>
     <row r="378">
-      <c r="A378" s="42"/>
-      <c r="B378" s="42"/>
+      <c r="A378" s="43"/>
+      <c r="B378" s="43"/>
     </row>
     <row r="379">
-      <c r="A379" s="42"/>
-      <c r="B379" s="42"/>
+      <c r="A379" s="43"/>
+      <c r="B379" s="43"/>
     </row>
     <row r="380">
-      <c r="A380" s="42"/>
-      <c r="B380" s="42"/>
+      <c r="A380" s="43"/>
+      <c r="B380" s="43"/>
     </row>
     <row r="381">
-      <c r="A381" s="42"/>
-      <c r="B381" s="42"/>
+      <c r="A381" s="43"/>
+      <c r="B381" s="43"/>
     </row>
     <row r="382">
-      <c r="A382" s="42"/>
-      <c r="B382" s="42"/>
+      <c r="A382" s="43"/>
+      <c r="B382" s="43"/>
     </row>
     <row r="383">
-      <c r="A383" s="42"/>
-      <c r="B383" s="42"/>
+      <c r="A383" s="43"/>
+      <c r="B383" s="43"/>
     </row>
     <row r="384">
-      <c r="A384" s="42"/>
-      <c r="B384" s="42"/>
+      <c r="A384" s="43"/>
+      <c r="B384" s="43"/>
     </row>
     <row r="385">
-      <c r="A385" s="42"/>
-      <c r="B385" s="42"/>
+      <c r="A385" s="43"/>
+      <c r="B385" s="43"/>
     </row>
     <row r="386">
-      <c r="A386" s="42"/>
-      <c r="B386" s="42"/>
+      <c r="A386" s="43"/>
+      <c r="B386" s="43"/>
     </row>
     <row r="387">
-      <c r="A387" s="42"/>
-      <c r="B387" s="42"/>
+      <c r="A387" s="43"/>
+      <c r="B387" s="43"/>
     </row>
     <row r="388">
-      <c r="A388" s="42"/>
-      <c r="B388" s="42"/>
+      <c r="A388" s="43"/>
+      <c r="B388" s="43"/>
     </row>
     <row r="389">
-      <c r="A389" s="42"/>
-      <c r="B389" s="42"/>
+      <c r="A389" s="43"/>
+      <c r="B389" s="43"/>
     </row>
     <row r="390">
-      <c r="A390" s="42"/>
-      <c r="B390" s="42"/>
+      <c r="A390" s="43"/>
+      <c r="B390" s="43"/>
     </row>
     <row r="391">
-      <c r="A391" s="42"/>
-      <c r="B391" s="42"/>
+      <c r="A391" s="43"/>
+      <c r="B391" s="43"/>
     </row>
     <row r="392">
-      <c r="A392" s="42"/>
-      <c r="B392" s="42"/>
+      <c r="A392" s="43"/>
+      <c r="B392" s="43"/>
     </row>
     <row r="393">
-      <c r="A393" s="42"/>
-      <c r="B393" s="42"/>
+      <c r="A393" s="43"/>
+      <c r="B393" s="43"/>
     </row>
     <row r="394">
-      <c r="A394" s="42"/>
-      <c r="B394" s="42"/>
+      <c r="A394" s="43"/>
+      <c r="B394" s="43"/>
     </row>
     <row r="395">
-      <c r="A395" s="42"/>
-      <c r="B395" s="42"/>
+      <c r="A395" s="43"/>
+      <c r="B395" s="43"/>
     </row>
     <row r="396">
-      <c r="A396" s="42"/>
-      <c r="B396" s="42"/>
+      <c r="A396" s="43"/>
+      <c r="B396" s="43"/>
     </row>
     <row r="397">
-      <c r="A397" s="42"/>
-      <c r="B397" s="42"/>
+      <c r="A397" s="43"/>
+      <c r="B397" s="43"/>
     </row>
     <row r="398">
-      <c r="A398" s="42"/>
-      <c r="B398" s="42"/>
+      <c r="A398" s="43"/>
+      <c r="B398" s="43"/>
     </row>
     <row r="399">
-      <c r="A399" s="42"/>
-      <c r="B399" s="42"/>
+      <c r="A399" s="43"/>
+      <c r="B399" s="43"/>
     </row>
     <row r="400">
-      <c r="A400" s="42"/>
-      <c r="B400" s="42"/>
+      <c r="A400" s="43"/>
+      <c r="B400" s="43"/>
     </row>
     <row r="401">
-      <c r="A401" s="42"/>
-      <c r="B401" s="42"/>
+      <c r="A401" s="43"/>
+      <c r="B401" s="43"/>
     </row>
     <row r="402">
-      <c r="A402" s="42"/>
-      <c r="B402" s="42"/>
+      <c r="A402" s="43"/>
+      <c r="B402" s="43"/>
     </row>
     <row r="403">
-      <c r="A403" s="42"/>
-      <c r="B403" s="42"/>
+      <c r="A403" s="43"/>
+      <c r="B403" s="43"/>
     </row>
     <row r="404">
-      <c r="A404" s="42"/>
-      <c r="B404" s="42"/>
+      <c r="A404" s="43"/>
+      <c r="B404" s="43"/>
     </row>
     <row r="405">
-      <c r="A405" s="42"/>
-      <c r="B405" s="42"/>
+      <c r="A405" s="43"/>
+      <c r="B405" s="43"/>
     </row>
     <row r="406">
-      <c r="A406" s="42"/>
-      <c r="B406" s="42"/>
+      <c r="A406" s="43"/>
+      <c r="B406" s="43"/>
     </row>
     <row r="407">
-      <c r="A407" s="42"/>
-      <c r="B407" s="42"/>
+      <c r="A407" s="43"/>
+      <c r="B407" s="43"/>
     </row>
     <row r="408">
-      <c r="A408" s="42"/>
-      <c r="B408" s="42"/>
+      <c r="A408" s="43"/>
+      <c r="B408" s="43"/>
     </row>
     <row r="409">
-      <c r="A409" s="42"/>
-      <c r="B409" s="42"/>
+      <c r="A409" s="43"/>
+      <c r="B409" s="43"/>
     </row>
     <row r="410">
-      <c r="A410" s="42"/>
-      <c r="B410" s="42"/>
+      <c r="A410" s="43"/>
+      <c r="B410" s="43"/>
     </row>
     <row r="411">
-      <c r="A411" s="42"/>
-      <c r="B411" s="42"/>
+      <c r="A411" s="43"/>
+      <c r="B411" s="43"/>
     </row>
     <row r="412">
-      <c r="A412" s="42"/>
-      <c r="B412" s="42"/>
+      <c r="A412" s="43"/>
+      <c r="B412" s="43"/>
     </row>
     <row r="413">
-      <c r="A413" s="42"/>
-      <c r="B413" s="42"/>
+      <c r="A413" s="43"/>
+      <c r="B413" s="43"/>
     </row>
     <row r="414">
-      <c r="A414" s="42"/>
-      <c r="B414" s="42"/>
+      <c r="A414" s="43"/>
+      <c r="B414" s="43"/>
     </row>
     <row r="415">
-      <c r="A415" s="42"/>
-      <c r="B415" s="42"/>
+      <c r="A415" s="43"/>
+      <c r="B415" s="43"/>
     </row>
     <row r="416">
-      <c r="A416" s="42"/>
-      <c r="B416" s="42"/>
+      <c r="A416" s="43"/>
+      <c r="B416" s="43"/>
     </row>
     <row r="417">
-      <c r="A417" s="42"/>
-      <c r="B417" s="42"/>
+      <c r="A417" s="43"/>
+      <c r="B417" s="43"/>
     </row>
     <row r="418">
-      <c r="A418" s="42"/>
-      <c r="B418" s="42"/>
+      <c r="A418" s="43"/>
+      <c r="B418" s="43"/>
     </row>
     <row r="419">
-      <c r="A419" s="42"/>
-      <c r="B419" s="42"/>
+      <c r="A419" s="43"/>
+      <c r="B419" s="43"/>
     </row>
     <row r="420">
-      <c r="A420" s="42"/>
-      <c r="B420" s="42"/>
+      <c r="A420" s="43"/>
+      <c r="B420" s="43"/>
     </row>
     <row r="421">
-      <c r="A421" s="42"/>
-      <c r="B421" s="42"/>
+      <c r="A421" s="43"/>
+      <c r="B421" s="43"/>
     </row>
     <row r="422">
-      <c r="A422" s="42"/>
-      <c r="B422" s="42"/>
+      <c r="A422" s="43"/>
+      <c r="B422" s="43"/>
     </row>
     <row r="423">
-      <c r="A423" s="42"/>
-      <c r="B423" s="42"/>
+      <c r="A423" s="43"/>
+      <c r="B423" s="43"/>
     </row>
     <row r="424">
-      <c r="A424" s="42"/>
-      <c r="B424" s="42"/>
+      <c r="A424" s="43"/>
+      <c r="B424" s="43"/>
     </row>
     <row r="425">
-      <c r="A425" s="42"/>
-      <c r="B425" s="42"/>
+      <c r="A425" s="43"/>
+      <c r="B425" s="43"/>
     </row>
     <row r="426">
-      <c r="A426" s="42"/>
-      <c r="B426" s="42"/>
+      <c r="A426" s="43"/>
+      <c r="B426" s="43"/>
     </row>
     <row r="427">
-      <c r="A427" s="42"/>
-      <c r="B427" s="42"/>
+      <c r="A427" s="43"/>
+      <c r="B427" s="43"/>
     </row>
     <row r="428">
-      <c r="A428" s="42"/>
-      <c r="B428" s="42"/>
+      <c r="A428" s="43"/>
+      <c r="B428" s="43"/>
     </row>
     <row r="429">
-      <c r="A429" s="42"/>
-      <c r="B429" s="42"/>
+      <c r="A429" s="43"/>
+      <c r="B429" s="43"/>
     </row>
     <row r="430">
-      <c r="A430" s="42"/>
-      <c r="B430" s="42"/>
+      <c r="A430" s="43"/>
+      <c r="B430" s="43"/>
     </row>
     <row r="431">
-      <c r="A431" s="42"/>
-      <c r="B431" s="42"/>
+      <c r="A431" s="43"/>
+      <c r="B431" s="43"/>
     </row>
     <row r="432">
-      <c r="A432" s="42"/>
-      <c r="B432" s="42"/>
+      <c r="A432" s="43"/>
+      <c r="B432" s="43"/>
     </row>
     <row r="433">
-      <c r="A433" s="42"/>
-      <c r="B433" s="42"/>
+      <c r="A433" s="43"/>
+      <c r="B433" s="43"/>
     </row>
     <row r="434">
-      <c r="A434" s="42"/>
-      <c r="B434" s="42"/>
+      <c r="A434" s="43"/>
+      <c r="B434" s="43"/>
     </row>
     <row r="435">
-      <c r="A435" s="42"/>
-      <c r="B435" s="42"/>
+      <c r="A435" s="43"/>
+      <c r="B435" s="43"/>
     </row>
     <row r="436">
-      <c r="A436" s="42"/>
-      <c r="B436" s="42"/>
+      <c r="A436" s="43"/>
+      <c r="B436" s="43"/>
     </row>
     <row r="437">
-      <c r="A437" s="42"/>
-      <c r="B437" s="42"/>
+      <c r="A437" s="43"/>
+      <c r="B437" s="43"/>
     </row>
     <row r="438">
-      <c r="A438" s="42"/>
-      <c r="B438" s="42"/>
+      <c r="A438" s="43"/>
+      <c r="B438" s="43"/>
     </row>
     <row r="439">
-      <c r="A439" s="42"/>
-      <c r="B439" s="42"/>
+      <c r="A439" s="43"/>
+      <c r="B439" s="43"/>
     </row>
     <row r="440">
-      <c r="A440" s="42"/>
-      <c r="B440" s="42"/>
+      <c r="A440" s="43"/>
+      <c r="B440" s="43"/>
     </row>
     <row r="441">
-      <c r="A441" s="42"/>
-      <c r="B441" s="42"/>
+      <c r="A441" s="43"/>
+      <c r="B441" s="43"/>
     </row>
     <row r="442">
-      <c r="A442" s="42"/>
-      <c r="B442" s="42"/>
+      <c r="A442" s="43"/>
+      <c r="B442" s="43"/>
     </row>
     <row r="443">
-      <c r="A443" s="42"/>
-      <c r="B443" s="42"/>
+      <c r="A443" s="43"/>
+      <c r="B443" s="43"/>
     </row>
     <row r="444">
-      <c r="A444" s="42"/>
-      <c r="B444" s="42"/>
+      <c r="A444" s="43"/>
+      <c r="B444" s="43"/>
     </row>
     <row r="445">
-      <c r="A445" s="42"/>
-      <c r="B445" s="42"/>
+      <c r="A445" s="43"/>
+      <c r="B445" s="43"/>
     </row>
     <row r="446">
-      <c r="A446" s="42"/>
-      <c r="B446" s="42"/>
+      <c r="A446" s="43"/>
+      <c r="B446" s="43"/>
     </row>
     <row r="447">
-      <c r="A447" s="42"/>
-      <c r="B447" s="42"/>
+      <c r="A447" s="43"/>
+      <c r="B447" s="43"/>
     </row>
     <row r="448">
-      <c r="A448" s="42"/>
-      <c r="B448" s="42"/>
+      <c r="A448" s="43"/>
+      <c r="B448" s="43"/>
     </row>
     <row r="449">
-      <c r="A449" s="42"/>
-      <c r="B449" s="42"/>
+      <c r="A449" s="43"/>
+      <c r="B449" s="43"/>
     </row>
     <row r="450">
-      <c r="A450" s="42"/>
-      <c r="B450" s="42"/>
+      <c r="A450" s="43"/>
+      <c r="B450" s="43"/>
     </row>
     <row r="451">
-      <c r="A451" s="42"/>
-      <c r="B451" s="42"/>
+      <c r="A451" s="43"/>
+      <c r="B451" s="43"/>
     </row>
     <row r="452">
-      <c r="A452" s="42"/>
-      <c r="B452" s="42"/>
+      <c r="A452" s="43"/>
+      <c r="B452" s="43"/>
     </row>
     <row r="453">
-      <c r="A453" s="42"/>
-      <c r="B453" s="42"/>
+      <c r="A453" s="43"/>
+      <c r="B453" s="43"/>
     </row>
     <row r="454">
-      <c r="A454" s="42"/>
-      <c r="B454" s="42"/>
+      <c r="A454" s="43"/>
+      <c r="B454" s="43"/>
     </row>
     <row r="455">
-      <c r="A455" s="42"/>
-      <c r="B455" s="42"/>
+      <c r="A455" s="43"/>
+      <c r="B455" s="43"/>
     </row>
     <row r="456">
-      <c r="A456" s="42"/>
-      <c r="B456" s="42"/>
+      <c r="A456" s="43"/>
+      <c r="B456" s="43"/>
     </row>
     <row r="457">
-      <c r="A457" s="42"/>
-      <c r="B457" s="42"/>
+      <c r="A457" s="43"/>
+      <c r="B457" s="43"/>
     </row>
     <row r="458">
-      <c r="A458" s="42"/>
-      <c r="B458" s="42"/>
+      <c r="A458" s="43"/>
+      <c r="B458" s="43"/>
     </row>
     <row r="459">
-      <c r="A459" s="42"/>
-      <c r="B459" s="42"/>
+      <c r="A459" s="43"/>
+      <c r="B459" s="43"/>
     </row>
     <row r="460">
-      <c r="A460" s="42"/>
-      <c r="B460" s="42"/>
+      <c r="A460" s="43"/>
+      <c r="B460" s="43"/>
     </row>
     <row r="461">
-      <c r="A461" s="42"/>
-      <c r="B461" s="42"/>
+      <c r="A461" s="43"/>
+      <c r="B461" s="43"/>
     </row>
     <row r="462">
-      <c r="A462" s="42"/>
-      <c r="B462" s="42"/>
+      <c r="A462" s="43"/>
+      <c r="B462" s="43"/>
     </row>
     <row r="463">
-      <c r="A463" s="42"/>
-      <c r="B463" s="42"/>
+      <c r="A463" s="43"/>
+      <c r="B463" s="43"/>
     </row>
     <row r="464">
-      <c r="A464" s="42"/>
-      <c r="B464" s="42"/>
+      <c r="A464" s="43"/>
+      <c r="B464" s="43"/>
     </row>
     <row r="465">
-      <c r="A465" s="42"/>
-      <c r="B465" s="42"/>
+      <c r="A465" s="43"/>
+      <c r="B465" s="43"/>
     </row>
     <row r="466">
-      <c r="A466" s="42"/>
-      <c r="B466" s="42"/>
+      <c r="A466" s="43"/>
+      <c r="B466" s="43"/>
     </row>
     <row r="467">
-      <c r="A467" s="42"/>
-      <c r="B467" s="42"/>
+      <c r="A467" s="43"/>
+      <c r="B467" s="43"/>
     </row>
     <row r="468">
-      <c r="A468" s="42"/>
-      <c r="B468" s="42"/>
+      <c r="A468" s="43"/>
+      <c r="B468" s="43"/>
     </row>
     <row r="469">
-      <c r="A469" s="42"/>
-      <c r="B469" s="42"/>
+      <c r="A469" s="43"/>
+      <c r="B469" s="43"/>
     </row>
     <row r="470">
-      <c r="A470" s="42"/>
-      <c r="B470" s="42"/>
+      <c r="A470" s="43"/>
+      <c r="B470" s="43"/>
     </row>
     <row r="471">
-      <c r="A471" s="42"/>
-      <c r="B471" s="42"/>
+      <c r="A471" s="43"/>
+      <c r="B471" s="43"/>
     </row>
     <row r="472">
-      <c r="A472" s="42"/>
-      <c r="B472" s="42"/>
+      <c r="A472" s="43"/>
+      <c r="B472" s="43"/>
     </row>
     <row r="473">
-      <c r="A473" s="42"/>
-      <c r="B473" s="42"/>
+      <c r="A473" s="43"/>
+      <c r="B473" s="43"/>
     </row>
     <row r="474">
-      <c r="A474" s="42"/>
-      <c r="B474" s="42"/>
+      <c r="A474" s="43"/>
+      <c r="B474" s="43"/>
     </row>
     <row r="475">
-      <c r="A475" s="42"/>
-      <c r="B475" s="42"/>
+      <c r="A475" s="43"/>
+      <c r="B475" s="43"/>
     </row>
     <row r="476">
-      <c r="A476" s="42"/>
-      <c r="B476" s="42"/>
+      <c r="A476" s="43"/>
+      <c r="B476" s="43"/>
     </row>
     <row r="477">
-      <c r="A477" s="42"/>
-      <c r="B477" s="42"/>
+      <c r="A477" s="43"/>
+      <c r="B477" s="43"/>
     </row>
     <row r="478">
-      <c r="A478" s="42"/>
-      <c r="B478" s="42"/>
+      <c r="A478" s="43"/>
+      <c r="B478" s="43"/>
     </row>
     <row r="479">
-      <c r="A479" s="42"/>
-      <c r="B479" s="42"/>
+      <c r="A479" s="43"/>
+      <c r="B479" s="43"/>
     </row>
     <row r="480">
-      <c r="A480" s="42"/>
-      <c r="B480" s="42"/>
+      <c r="A480" s="43"/>
+      <c r="B480" s="43"/>
     </row>
     <row r="481">
-      <c r="A481" s="42"/>
-      <c r="B481" s="42"/>
+      <c r="A481" s="43"/>
+      <c r="B481" s="43"/>
     </row>
     <row r="482">
-      <c r="A482" s="42"/>
-      <c r="B482" s="42"/>
+      <c r="A482" s="43"/>
+      <c r="B482" s="43"/>
     </row>
     <row r="483">
-      <c r="A483" s="42"/>
-      <c r="B483" s="42"/>
+      <c r="A483" s="43"/>
+      <c r="B483" s="43"/>
     </row>
     <row r="484">
-      <c r="A484" s="42"/>
-      <c r="B484" s="42"/>
+      <c r="A484" s="43"/>
+      <c r="B484" s="43"/>
     </row>
     <row r="485">
-      <c r="A485" s="42"/>
-      <c r="B485" s="42"/>
+      <c r="A485" s="43"/>
+      <c r="B485" s="43"/>
     </row>
     <row r="486">
-      <c r="A486" s="42"/>
-      <c r="B486" s="42"/>
+      <c r="A486" s="43"/>
+      <c r="B486" s="43"/>
     </row>
     <row r="487">
-      <c r="A487" s="42"/>
-      <c r="B487" s="42"/>
+      <c r="A487" s="43"/>
+      <c r="B487" s="43"/>
     </row>
     <row r="488">
-      <c r="A488" s="42"/>
-      <c r="B488" s="42"/>
+      <c r="A488" s="43"/>
+      <c r="B488" s="43"/>
     </row>
     <row r="489">
-      <c r="A489" s="42"/>
-      <c r="B489" s="42"/>
+      <c r="A489" s="43"/>
+      <c r="B489" s="43"/>
     </row>
     <row r="490">
-      <c r="A490" s="42"/>
-      <c r="B490" s="42"/>
+      <c r="A490" s="43"/>
+      <c r="B490" s="43"/>
     </row>
     <row r="491">
-      <c r="A491" s="42"/>
-      <c r="B491" s="42"/>
+      <c r="A491" s="43"/>
+      <c r="B491" s="43"/>
     </row>
     <row r="492">
-      <c r="A492" s="42"/>
-      <c r="B492" s="42"/>
+      <c r="A492" s="43"/>
+      <c r="B492" s="43"/>
     </row>
     <row r="493">
-      <c r="A493" s="42"/>
-      <c r="B493" s="42"/>
+      <c r="A493" s="43"/>
+      <c r="B493" s="43"/>
     </row>
     <row r="494">
-      <c r="A494" s="42"/>
-      <c r="B494" s="42"/>
+      <c r="A494" s="43"/>
+      <c r="B494" s="43"/>
     </row>
     <row r="495">
-      <c r="A495" s="42"/>
-      <c r="B495" s="42"/>
+      <c r="A495" s="43"/>
+      <c r="B495" s="43"/>
     </row>
     <row r="496">
-      <c r="A496" s="42"/>
-      <c r="B496" s="42"/>
+      <c r="A496" s="43"/>
+      <c r="B496" s="43"/>
     </row>
     <row r="497">
-      <c r="A497" s="42"/>
-      <c r="B497" s="42"/>
+      <c r="A497" s="43"/>
+      <c r="B497" s="43"/>
     </row>
     <row r="498">
-      <c r="A498" s="42"/>
-      <c r="B498" s="42"/>
+      <c r="A498" s="43"/>
+      <c r="B498" s="43"/>
     </row>
     <row r="499">
-      <c r="A499" s="42"/>
-      <c r="B499" s="42"/>
+      <c r="A499" s="43"/>
+      <c r="B499" s="43"/>
     </row>
     <row r="500">
-      <c r="A500" s="42"/>
-      <c r="B500" s="42"/>
+      <c r="A500" s="43"/>
+      <c r="B500" s="43"/>
     </row>
     <row r="501">
-      <c r="A501" s="42"/>
-      <c r="B501" s="42"/>
+      <c r="A501" s="43"/>
+      <c r="B501" s="43"/>
     </row>
     <row r="502">
-      <c r="A502" s="42"/>
-      <c r="B502" s="42"/>
+      <c r="A502" s="43"/>
+      <c r="B502" s="43"/>
     </row>
     <row r="503">
-      <c r="A503" s="42"/>
-      <c r="B503" s="42"/>
+      <c r="A503" s="43"/>
+      <c r="B503" s="43"/>
     </row>
     <row r="504">
-      <c r="A504" s="42"/>
-      <c r="B504" s="42"/>
+      <c r="A504" s="43"/>
+      <c r="B504" s="43"/>
     </row>
     <row r="505">
-      <c r="A505" s="42"/>
-      <c r="B505" s="42"/>
+      <c r="A505" s="43"/>
+      <c r="B505" s="43"/>
     </row>
     <row r="506">
-      <c r="A506" s="42"/>
-      <c r="B506" s="42"/>
+      <c r="A506" s="43"/>
+      <c r="B506" s="43"/>
     </row>
     <row r="507">
-      <c r="A507" s="42"/>
-      <c r="B507" s="42"/>
+      <c r="A507" s="43"/>
+      <c r="B507" s="43"/>
     </row>
     <row r="508">
-      <c r="A508" s="42"/>
-      <c r="B508" s="42"/>
+      <c r="A508" s="43"/>
+      <c r="B508" s="43"/>
     </row>
     <row r="509">
-      <c r="A509" s="42"/>
-      <c r="B509" s="42"/>
+      <c r="A509" s="43"/>
+      <c r="B509" s="43"/>
     </row>
     <row r="510">
-      <c r="A510" s="42"/>
-      <c r="B510" s="42"/>
+      <c r="A510" s="43"/>
+      <c r="B510" s="43"/>
     </row>
     <row r="511">
-      <c r="A511" s="42"/>
-      <c r="B511" s="42"/>
+      <c r="A511" s="43"/>
+      <c r="B511" s="43"/>
     </row>
     <row r="512">
-      <c r="A512" s="42"/>
-      <c r="B512" s="42"/>
+      <c r="A512" s="43"/>
+      <c r="B512" s="43"/>
     </row>
     <row r="513">
-      <c r="A513" s="42"/>
-      <c r="B513" s="42"/>
+      <c r="A513" s="43"/>
+      <c r="B513" s="43"/>
     </row>
     <row r="514">
-      <c r="A514" s="42"/>
-      <c r="B514" s="42"/>
+      <c r="A514" s="43"/>
+      <c r="B514" s="43"/>
     </row>
     <row r="515">
-      <c r="A515" s="42"/>
-      <c r="B515" s="42"/>
+      <c r="A515" s="43"/>
+      <c r="B515" s="43"/>
     </row>
     <row r="516">
-      <c r="A516" s="42"/>
-      <c r="B516" s="42"/>
+      <c r="A516" s="43"/>
+      <c r="B516" s="43"/>
     </row>
     <row r="517">
-      <c r="A517" s="42"/>
-      <c r="B517" s="42"/>
+      <c r="A517" s="43"/>
+      <c r="B517" s="43"/>
     </row>
     <row r="518">
-      <c r="A518" s="42"/>
-      <c r="B518" s="42"/>
+      <c r="A518" s="43"/>
+      <c r="B518" s="43"/>
     </row>
     <row r="519">
-      <c r="A519" s="42"/>
-      <c r="B519" s="42"/>
+      <c r="A519" s="43"/>
+      <c r="B519" s="43"/>
     </row>
     <row r="520">
-      <c r="A520" s="42"/>
-      <c r="B520" s="42"/>
+      <c r="A520" s="43"/>
+      <c r="B520" s="43"/>
     </row>
     <row r="521">
-      <c r="A521" s="42"/>
-      <c r="B521" s="42"/>
+      <c r="A521" s="43"/>
+      <c r="B521" s="43"/>
     </row>
     <row r="522">
-      <c r="A522" s="42"/>
-      <c r="B522" s="42"/>
+      <c r="A522" s="43"/>
+      <c r="B522" s="43"/>
     </row>
     <row r="523">
-      <c r="A523" s="42"/>
-      <c r="B523" s="42"/>
+      <c r="A523" s="43"/>
+      <c r="B523" s="43"/>
     </row>
     <row r="524">
-      <c r="A524" s="42"/>
-      <c r="B524" s="42"/>
+      <c r="A524" s="43"/>
+      <c r="B524" s="43"/>
     </row>
     <row r="525">
-      <c r="A525" s="42"/>
-      <c r="B525" s="42"/>
+      <c r="A525" s="43"/>
+      <c r="B525" s="43"/>
     </row>
     <row r="526">
-      <c r="A526" s="42"/>
-      <c r="B526" s="42"/>
+      <c r="A526" s="43"/>
+      <c r="B526" s="43"/>
     </row>
     <row r="527">
-      <c r="A527" s="42"/>
-      <c r="B527" s="42"/>
+      <c r="A527" s="43"/>
+      <c r="B527" s="43"/>
     </row>
     <row r="528">
-      <c r="A528" s="42"/>
-      <c r="B528" s="42"/>
+      <c r="A528" s="43"/>
+      <c r="B528" s="43"/>
     </row>
     <row r="529">
-      <c r="A529" s="42"/>
-      <c r="B529" s="42"/>
+      <c r="A529" s="43"/>
+      <c r="B529" s="43"/>
     </row>
     <row r="530">
-      <c r="A530" s="42"/>
-      <c r="B530" s="42"/>
+      <c r="A530" s="43"/>
+      <c r="B530" s="43"/>
     </row>
     <row r="531">
-      <c r="A531" s="42"/>
-      <c r="B531" s="42"/>
+      <c r="A531" s="43"/>
+      <c r="B531" s="43"/>
     </row>
     <row r="532">
-      <c r="A532" s="42"/>
-      <c r="B532" s="42"/>
+      <c r="A532" s="43"/>
+      <c r="B532" s="43"/>
     </row>
     <row r="533">
-      <c r="A533" s="42"/>
-      <c r="B533" s="42"/>
+      <c r="A533" s="43"/>
+      <c r="B533" s="43"/>
     </row>
     <row r="534">
-      <c r="A534" s="42"/>
-      <c r="B534" s="42"/>
+      <c r="A534" s="43"/>
+      <c r="B534" s="43"/>
     </row>
     <row r="535">
-      <c r="A535" s="42"/>
-      <c r="B535" s="42"/>
+      <c r="A535" s="43"/>
+      <c r="B535" s="43"/>
     </row>
     <row r="536">
-      <c r="A536" s="42"/>
-      <c r="B536" s="42"/>
+      <c r="A536" s="43"/>
+      <c r="B536" s="43"/>
     </row>
     <row r="537">
-      <c r="A537" s="42"/>
-      <c r="B537" s="42"/>
+      <c r="A537" s="43"/>
+      <c r="B537" s="43"/>
     </row>
     <row r="538">
-      <c r="A538" s="42"/>
-      <c r="B538" s="42"/>
+      <c r="A538" s="43"/>
+      <c r="B538" s="43"/>
     </row>
     <row r="539">
-      <c r="A539" s="42"/>
-      <c r="B539" s="42"/>
+      <c r="A539" s="43"/>
+      <c r="B539" s="43"/>
     </row>
     <row r="540">
-      <c r="A540" s="42"/>
-      <c r="B540" s="42"/>
+      <c r="A540" s="43"/>
+      <c r="B540" s="43"/>
     </row>
     <row r="541">
-      <c r="A541" s="42"/>
-      <c r="B541" s="42"/>
+      <c r="A541" s="43"/>
+      <c r="B541" s="43"/>
     </row>
     <row r="542">
-      <c r="A542" s="42"/>
-      <c r="B542" s="42"/>
+      <c r="A542" s="43"/>
+      <c r="B542" s="43"/>
     </row>
     <row r="543">
-      <c r="A543" s="42"/>
-      <c r="B543" s="42"/>
+      <c r="A543" s="43"/>
+      <c r="B543" s="43"/>
     </row>
     <row r="544">
-      <c r="A544" s="42"/>
-      <c r="B544" s="42"/>
+      <c r="A544" s="43"/>
+      <c r="B544" s="43"/>
     </row>
     <row r="545">
-      <c r="A545" s="42"/>
-      <c r="B545" s="42"/>
+      <c r="A545" s="43"/>
+      <c r="B545" s="43"/>
     </row>
     <row r="546">
-      <c r="A546" s="42"/>
-      <c r="B546" s="42"/>
+      <c r="A546" s="43"/>
+      <c r="B546" s="43"/>
     </row>
     <row r="547">
-      <c r="A547" s="42"/>
-      <c r="B547" s="42"/>
+      <c r="A547" s="43"/>
+      <c r="B547" s="43"/>
     </row>
     <row r="548">
-      <c r="A548" s="42"/>
-      <c r="B548" s="42"/>
+      <c r="A548" s="43"/>
+      <c r="B548" s="43"/>
     </row>
     <row r="549">
-      <c r="A549" s="42"/>
-      <c r="B549" s="42"/>
+      <c r="A549" s="43"/>
+      <c r="B549" s="43"/>
     </row>
     <row r="550">
-      <c r="A550" s="42"/>
-      <c r="B550" s="42"/>
+      <c r="A550" s="43"/>
+      <c r="B550" s="43"/>
     </row>
     <row r="551">
-      <c r="A551" s="42"/>
-      <c r="B551" s="42"/>
+      <c r="A551" s="43"/>
+      <c r="B551" s="43"/>
     </row>
     <row r="552">
-      <c r="A552" s="42"/>
-      <c r="B552" s="42"/>
+      <c r="A552" s="43"/>
+      <c r="B552" s="43"/>
     </row>
     <row r="553">
-      <c r="A553" s="42"/>
-      <c r="B553" s="42"/>
+      <c r="A553" s="43"/>
+      <c r="B553" s="43"/>
     </row>
     <row r="554">
-      <c r="A554" s="42"/>
-      <c r="B554" s="42"/>
+      <c r="A554" s="43"/>
+      <c r="B554" s="43"/>
     </row>
     <row r="555">
-      <c r="A555" s="42"/>
-      <c r="B555" s="42"/>
+      <c r="A555" s="43"/>
+      <c r="B555" s="43"/>
     </row>
     <row r="556">
-      <c r="A556" s="42"/>
-      <c r="B556" s="42"/>
+      <c r="A556" s="43"/>
+      <c r="B556" s="43"/>
     </row>
     <row r="557">
-      <c r="A557" s="42"/>
-      <c r="B557" s="42"/>
+      <c r="A557" s="43"/>
+      <c r="B557" s="43"/>
     </row>
     <row r="558">
-      <c r="A558" s="42"/>
-      <c r="B558" s="42"/>
+      <c r="A558" s="43"/>
+      <c r="B558" s="43"/>
     </row>
     <row r="559">
-      <c r="A559" s="42"/>
-      <c r="B559" s="42"/>
+      <c r="A559" s="43"/>
+      <c r="B559" s="43"/>
     </row>
     <row r="560">
-      <c r="A560" s="42"/>
-      <c r="B560" s="42"/>
+      <c r="A560" s="43"/>
+      <c r="B560" s="43"/>
     </row>
     <row r="561">
-      <c r="A561" s="42"/>
-      <c r="B561" s="42"/>
+      <c r="A561" s="43"/>
+      <c r="B561" s="43"/>
     </row>
     <row r="562">
-      <c r="A562" s="42"/>
-      <c r="B562" s="42"/>
+      <c r="A562" s="43"/>
+      <c r="B562" s="43"/>
     </row>
     <row r="563">
-      <c r="A563" s="42"/>
-      <c r="B563" s="42"/>
+      <c r="A563" s="43"/>
+      <c r="B563" s="43"/>
     </row>
     <row r="564">
-      <c r="A564" s="42"/>
-      <c r="B564" s="42"/>
+      <c r="A564" s="43"/>
+      <c r="B564" s="43"/>
     </row>
     <row r="565">
-      <c r="A565" s="42"/>
-      <c r="B565" s="42"/>
+      <c r="A565" s="43"/>
+      <c r="B565" s="43"/>
     </row>
     <row r="566">
-      <c r="A566" s="42"/>
-      <c r="B566" s="42"/>
+      <c r="A566" s="43"/>
+      <c r="B566" s="43"/>
     </row>
     <row r="567">
-      <c r="A567" s="42"/>
-      <c r="B567" s="42"/>
+      <c r="A567" s="43"/>
+      <c r="B567" s="43"/>
     </row>
     <row r="568">
-      <c r="A568" s="42"/>
-      <c r="B568" s="42"/>
+      <c r="A568" s="43"/>
+      <c r="B568" s="43"/>
     </row>
     <row r="569">
-      <c r="A569" s="42"/>
-      <c r="B569" s="42"/>
+      <c r="A569" s="43"/>
+      <c r="B569" s="43"/>
     </row>
     <row r="570">
-      <c r="A570" s="42"/>
-      <c r="B570" s="42"/>
+      <c r="A570" s="43"/>
+      <c r="B570" s="43"/>
     </row>
     <row r="571">
-      <c r="A571" s="42"/>
-      <c r="B571" s="42"/>
+      <c r="A571" s="43"/>
+      <c r="B571" s="43"/>
     </row>
     <row r="572">
-      <c r="A572" s="42"/>
-      <c r="B572" s="42"/>
+      <c r="A572" s="43"/>
+      <c r="B572" s="43"/>
     </row>
     <row r="573">
-      <c r="A573" s="42"/>
-      <c r="B573" s="42"/>
+      <c r="A573" s="43"/>
+      <c r="B573" s="43"/>
     </row>
     <row r="574">
-      <c r="A574" s="42"/>
-      <c r="B574" s="42"/>
+      <c r="A574" s="43"/>
+      <c r="B574" s="43"/>
     </row>
     <row r="575">
-      <c r="A575" s="42"/>
-      <c r="B575" s="42"/>
+      <c r="A575" s="43"/>
+      <c r="B575" s="43"/>
     </row>
     <row r="576">
-      <c r="A576" s="42"/>
-      <c r="B576" s="42"/>
+      <c r="A576" s="43"/>
+      <c r="B576" s="43"/>
     </row>
     <row r="577">
-      <c r="A577" s="42"/>
-      <c r="B577" s="42"/>
+      <c r="A577" s="43"/>
+      <c r="B577" s="43"/>
     </row>
     <row r="578">
-      <c r="A578" s="42"/>
-      <c r="B578" s="42"/>
+      <c r="A578" s="43"/>
+      <c r="B578" s="43"/>
     </row>
     <row r="579">
-      <c r="A579" s="42"/>
-      <c r="B579" s="42"/>
+      <c r="A579" s="43"/>
+      <c r="B579" s="43"/>
     </row>
     <row r="580">
-      <c r="A580" s="42"/>
-      <c r="B580" s="42"/>
+      <c r="A580" s="43"/>
+      <c r="B580" s="43"/>
     </row>
     <row r="581">
-      <c r="A581" s="42"/>
-      <c r="B581" s="42"/>
+      <c r="A581" s="43"/>
+      <c r="B581" s="43"/>
     </row>
     <row r="582">
-      <c r="A582" s="42"/>
-      <c r="B582" s="42"/>
+      <c r="A582" s="43"/>
+      <c r="B582" s="43"/>
     </row>
     <row r="583">
-      <c r="A583" s="42"/>
-      <c r="B583" s="42"/>
+      <c r="A583" s="43"/>
+      <c r="B583" s="43"/>
     </row>
     <row r="584">
-      <c r="A584" s="42"/>
-      <c r="B584" s="42"/>
+      <c r="A584" s="43"/>
+      <c r="B584" s="43"/>
     </row>
     <row r="585">
-      <c r="A585" s="42"/>
-      <c r="B585" s="42"/>
+      <c r="A585" s="43"/>
+      <c r="B585" s="43"/>
     </row>
     <row r="586">
-      <c r="A586" s="42"/>
-      <c r="B586" s="42"/>
+      <c r="A586" s="43"/>
+      <c r="B586" s="43"/>
     </row>
     <row r="587">
-      <c r="A587" s="42"/>
-      <c r="B587" s="42"/>
+      <c r="A587" s="43"/>
+      <c r="B587" s="43"/>
     </row>
     <row r="588">
-      <c r="A588" s="42"/>
-      <c r="B588" s="42"/>
+      <c r="A588" s="43"/>
+      <c r="B588" s="43"/>
     </row>
     <row r="589">
-      <c r="A589" s="42"/>
-      <c r="B589" s="42"/>
+      <c r="A589" s="43"/>
+      <c r="B589" s="43"/>
     </row>
     <row r="590">
-      <c r="A590" s="42"/>
-      <c r="B590" s="42"/>
+      <c r="A590" s="43"/>
+      <c r="B590" s="43"/>
     </row>
     <row r="591">
-      <c r="A591" s="42"/>
-      <c r="B591" s="42"/>
+      <c r="A591" s="43"/>
+      <c r="B591" s="43"/>
     </row>
     <row r="592">
-      <c r="A592" s="42"/>
-      <c r="B592" s="42"/>
+      <c r="A592" s="43"/>
+      <c r="B592" s="43"/>
     </row>
     <row r="593">
-      <c r="A593" s="42"/>
-      <c r="B593" s="42"/>
+      <c r="A593" s="43"/>
+      <c r="B593" s="43"/>
     </row>
     <row r="594">
-      <c r="A594" s="42"/>
-      <c r="B594" s="42"/>
+      <c r="A594" s="43"/>
+      <c r="B594" s="43"/>
     </row>
     <row r="595">
-      <c r="A595" s="42"/>
-      <c r="B595" s="42"/>
+      <c r="A595" s="43"/>
+      <c r="B595" s="43"/>
     </row>
     <row r="596">
-      <c r="A596" s="42"/>
-      <c r="B596" s="42"/>
+      <c r="A596" s="43"/>
+      <c r="B596" s="43"/>
     </row>
     <row r="597">
-      <c r="A597" s="42"/>
-      <c r="B597" s="42"/>
+      <c r="A597" s="43"/>
+      <c r="B597" s="43"/>
     </row>
     <row r="598">
-      <c r="A598" s="42"/>
-      <c r="B598" s="42"/>
+      <c r="A598" s="43"/>
+      <c r="B598" s="43"/>
     </row>
     <row r="599">
-      <c r="A599" s="42"/>
-      <c r="B599" s="42"/>
+      <c r="A599" s="43"/>
+      <c r="B599" s="43"/>
     </row>
     <row r="600">
-      <c r="A600" s="42"/>
-      <c r="B600" s="42"/>
+      <c r="A600" s="43"/>
+      <c r="B600" s="43"/>
     </row>
     <row r="601">
-      <c r="A601" s="42"/>
-      <c r="B601" s="42"/>
+      <c r="A601" s="43"/>
+      <c r="B601" s="43"/>
     </row>
     <row r="602">
-      <c r="A602" s="42"/>
-      <c r="B602" s="42"/>
+      <c r="A602" s="43"/>
+      <c r="B602" s="43"/>
     </row>
     <row r="603">
-      <c r="A603" s="42"/>
-      <c r="B603" s="42"/>
+      <c r="A603" s="43"/>
+      <c r="B603" s="43"/>
     </row>
     <row r="604">
-      <c r="A604" s="42"/>
-      <c r="B604" s="42"/>
+      <c r="A604" s="43"/>
+      <c r="B604" s="43"/>
     </row>
     <row r="605">
-      <c r="A605" s="42"/>
-      <c r="B605" s="42"/>
+      <c r="A605" s="43"/>
+      <c r="B605" s="43"/>
     </row>
     <row r="606">
-      <c r="A606" s="42"/>
-      <c r="B606" s="42"/>
+      <c r="A606" s="43"/>
+      <c r="B606" s="43"/>
     </row>
     <row r="607">
-      <c r="A607" s="42"/>
-      <c r="B607" s="42"/>
+      <c r="A607" s="43"/>
+      <c r="B607" s="43"/>
     </row>
     <row r="608">
-      <c r="A608" s="42"/>
-      <c r="B608" s="42"/>
+      <c r="A608" s="43"/>
+      <c r="B608" s="43"/>
     </row>
     <row r="609">
-      <c r="A609" s="42"/>
-      <c r="B609" s="42"/>
+      <c r="A609" s="43"/>
+      <c r="B609" s="43"/>
     </row>
     <row r="610">
-      <c r="A610" s="42"/>
-      <c r="B610" s="42"/>
+      <c r="A610" s="43"/>
+      <c r="B610" s="43"/>
     </row>
     <row r="611">
-      <c r="A611" s="42"/>
-      <c r="B611" s="42"/>
+      <c r="A611" s="43"/>
+      <c r="B611" s="43"/>
     </row>
     <row r="612">
-      <c r="A612" s="42"/>
-      <c r="B612" s="42"/>
+      <c r="A612" s="43"/>
+      <c r="B612" s="43"/>
     </row>
     <row r="613">
-      <c r="A613" s="42"/>
-      <c r="B613" s="42"/>
+      <c r="A613" s="43"/>
+      <c r="B613" s="43"/>
     </row>
     <row r="614">
-      <c r="A614" s="42"/>
-      <c r="B614" s="42"/>
+      <c r="A614" s="43"/>
+      <c r="B614" s="43"/>
     </row>
     <row r="615">
-      <c r="A615" s="42"/>
-      <c r="B615" s="42"/>
+      <c r="A615" s="43"/>
+      <c r="B615" s="43"/>
     </row>
     <row r="616">
-      <c r="A616" s="42"/>
-      <c r="B616" s="42"/>
+      <c r="A616" s="43"/>
+      <c r="B616" s="43"/>
     </row>
     <row r="617">
-      <c r="A617" s="42"/>
-      <c r="B617" s="42"/>
+      <c r="A617" s="43"/>
+      <c r="B617" s="43"/>
     </row>
     <row r="618">
-      <c r="A618" s="42"/>
-      <c r="B618" s="42"/>
+      <c r="A618" s="43"/>
+      <c r="B618" s="43"/>
     </row>
     <row r="619">
-      <c r="A619" s="42"/>
-      <c r="B619" s="42"/>
+      <c r="A619" s="43"/>
+      <c r="B619" s="43"/>
     </row>
     <row r="620">
-      <c r="A620" s="42"/>
-      <c r="B620" s="42"/>
+      <c r="A620" s="43"/>
+      <c r="B620" s="43"/>
     </row>
     <row r="621">
-      <c r="A621" s="42"/>
-      <c r="B621" s="42"/>
+      <c r="A621" s="43"/>
+      <c r="B621" s="43"/>
     </row>
     <row r="622">
-      <c r="A622" s="42"/>
-      <c r="B622" s="42"/>
+      <c r="A622" s="43"/>
+      <c r="B622" s="43"/>
     </row>
     <row r="623">
-      <c r="A623" s="42"/>
-      <c r="B623" s="42"/>
+      <c r="A623" s="43"/>
+      <c r="B623" s="43"/>
     </row>
     <row r="624">
-      <c r="A624" s="42"/>
-      <c r="B624" s="42"/>
+      <c r="A624" s="43"/>
+      <c r="B624" s="43"/>
     </row>
     <row r="625">
-      <c r="A625" s="42"/>
-      <c r="B625" s="42"/>
+      <c r="A625" s="43"/>
+      <c r="B625" s="43"/>
     </row>
     <row r="626">
-      <c r="A626" s="42"/>
-      <c r="B626" s="42"/>
+      <c r="A626" s="43"/>
+      <c r="B626" s="43"/>
     </row>
     <row r="627">
-      <c r="A627" s="42"/>
-      <c r="B627" s="42"/>
+      <c r="A627" s="43"/>
+      <c r="B627" s="43"/>
     </row>
     <row r="628">
-      <c r="A628" s="42"/>
-      <c r="B628" s="42"/>
+      <c r="A628" s="43"/>
+      <c r="B628" s="43"/>
     </row>
     <row r="629">
-      <c r="A629" s="42"/>
-      <c r="B629" s="42"/>
+      <c r="A629" s="43"/>
+      <c r="B629" s="43"/>
     </row>
     <row r="630">
-      <c r="A630" s="42"/>
-      <c r="B630" s="42"/>
+      <c r="A630" s="43"/>
+      <c r="B630" s="43"/>
     </row>
     <row r="631">
-      <c r="A631" s="42"/>
-      <c r="B631" s="42"/>
+      <c r="A631" s="43"/>
+      <c r="B631" s="43"/>
     </row>
     <row r="632">
-      <c r="A632" s="42"/>
-      <c r="B632" s="42"/>
+      <c r="A632" s="43"/>
+      <c r="B632" s="43"/>
     </row>
     <row r="633">
-      <c r="A633" s="42"/>
-      <c r="B633" s="42"/>
+      <c r="A633" s="43"/>
+      <c r="B633" s="43"/>
     </row>
     <row r="634">
-      <c r="A634" s="42"/>
-      <c r="B634" s="42"/>
+      <c r="A634" s="43"/>
+      <c r="B634" s="43"/>
     </row>
     <row r="635">
-      <c r="A635" s="42"/>
-      <c r="B635" s="42"/>
+      <c r="A635" s="43"/>
+      <c r="B635" s="43"/>
     </row>
     <row r="636">
-      <c r="A636" s="42"/>
-      <c r="B636" s="42"/>
+      <c r="A636" s="43"/>
+      <c r="B636" s="43"/>
     </row>
     <row r="637">
-      <c r="A637" s="42"/>
-      <c r="B637" s="42"/>
+      <c r="A637" s="43"/>
+      <c r="B637" s="43"/>
     </row>
     <row r="638">
-      <c r="A638" s="42"/>
-      <c r="B638" s="42"/>
+      <c r="A638" s="43"/>
+      <c r="B638" s="43"/>
     </row>
     <row r="639">
-      <c r="A639" s="42"/>
-      <c r="B639" s="42"/>
+      <c r="A639" s="43"/>
+      <c r="B639" s="43"/>
     </row>
     <row r="640">
-      <c r="A640" s="42"/>
-      <c r="B640" s="42"/>
+      <c r="A640" s="43"/>
+      <c r="B640" s="43"/>
     </row>
     <row r="641">
-      <c r="A641" s="42"/>
-      <c r="B641" s="42"/>
+      <c r="A641" s="43"/>
+      <c r="B641" s="43"/>
     </row>
     <row r="642">
-      <c r="A642" s="42"/>
-      <c r="B642" s="42"/>
+      <c r="A642" s="43"/>
+      <c r="B642" s="43"/>
     </row>
     <row r="643">
-      <c r="A643" s="42"/>
-      <c r="B643" s="42"/>
+      <c r="A643" s="43"/>
+      <c r="B643" s="43"/>
     </row>
     <row r="644">
-      <c r="A644" s="42"/>
-      <c r="B644" s="42"/>
+      <c r="A644" s="43"/>
+      <c r="B644" s="43"/>
     </row>
     <row r="645">
-      <c r="A645" s="42"/>
-      <c r="B645" s="42"/>
+      <c r="A645" s="43"/>
+      <c r="B645" s="43"/>
     </row>
     <row r="646">
-      <c r="A646" s="42"/>
-      <c r="B646" s="42"/>
+      <c r="A646" s="43"/>
+      <c r="B646" s="43"/>
     </row>
     <row r="647">
-      <c r="A647" s="42"/>
-      <c r="B647" s="42"/>
+      <c r="A647" s="43"/>
+      <c r="B647" s="43"/>
     </row>
     <row r="648">
-      <c r="A648" s="42"/>
-      <c r="B648" s="42"/>
+      <c r="A648" s="43"/>
+      <c r="B648" s="43"/>
     </row>
     <row r="649">
-      <c r="A649" s="42"/>
-      <c r="B649" s="42"/>
+      <c r="A649" s="43"/>
+      <c r="B649" s="43"/>
     </row>
     <row r="650">
-      <c r="A650" s="42"/>
-      <c r="B650" s="42"/>
+      <c r="A650" s="43"/>
+      <c r="B650" s="43"/>
     </row>
     <row r="651">
-      <c r="A651" s="42"/>
-      <c r="B651" s="42"/>
+      <c r="A651" s="43"/>
+      <c r="B651" s="43"/>
     </row>
     <row r="652">
-      <c r="A652" s="42"/>
-      <c r="B652" s="42"/>
+      <c r="A652" s="43"/>
+      <c r="B652" s="43"/>
     </row>
     <row r="653">
-      <c r="A653" s="42"/>
-      <c r="B653" s="42"/>
+      <c r="A653" s="43"/>
+      <c r="B653" s="43"/>
     </row>
     <row r="654">
-      <c r="A654" s="42"/>
-      <c r="B654" s="42"/>
+      <c r="A654" s="43"/>
+      <c r="B654" s="43"/>
     </row>
     <row r="655">
-      <c r="A655" s="42"/>
-      <c r="B655" s="42"/>
+      <c r="A655" s="43"/>
+      <c r="B655" s="43"/>
     </row>
     <row r="656">
-      <c r="A656" s="42"/>
-      <c r="B656" s="42"/>
+      <c r="A656" s="43"/>
+      <c r="B656" s="43"/>
     </row>
     <row r="657">
-      <c r="A657" s="42"/>
-      <c r="B657" s="42"/>
+      <c r="A657" s="43"/>
+      <c r="B657" s="43"/>
     </row>
     <row r="658">
-      <c r="A658" s="42"/>
-      <c r="B658" s="42"/>
+      <c r="A658" s="43"/>
+      <c r="B658" s="43"/>
     </row>
     <row r="659">
-      <c r="A659" s="42"/>
-      <c r="B659" s="42"/>
+      <c r="A659" s="43"/>
+      <c r="B659" s="43"/>
     </row>
     <row r="660">
-      <c r="A660" s="42"/>
-      <c r="B660" s="42"/>
+      <c r="A660" s="43"/>
+      <c r="B660" s="43"/>
     </row>
     <row r="661">
-      <c r="A661" s="42"/>
-      <c r="B661" s="42"/>
+      <c r="A661" s="43"/>
+      <c r="B661" s="43"/>
     </row>
     <row r="662">
-      <c r="A662" s="42"/>
-      <c r="B662" s="42"/>
+      <c r="A662" s="43"/>
+      <c r="B662" s="43"/>
     </row>
     <row r="663">
-      <c r="A663" s="42"/>
-      <c r="B663" s="42"/>
+      <c r="A663" s="43"/>
+      <c r="B663" s="43"/>
     </row>
     <row r="664">
-      <c r="A664" s="42"/>
-      <c r="B664" s="42"/>
+      <c r="A664" s="43"/>
+      <c r="B664" s="43"/>
     </row>
     <row r="665">
-      <c r="A665" s="42"/>
-      <c r="B665" s="42"/>
+      <c r="A665" s="43"/>
+      <c r="B665" s="43"/>
     </row>
     <row r="666">
-      <c r="A666" s="42"/>
-      <c r="B666" s="42"/>
+      <c r="A666" s="43"/>
+      <c r="B666" s="43"/>
     </row>
     <row r="667">
-      <c r="A667" s="42"/>
-      <c r="B667" s="42"/>
+      <c r="A667" s="43"/>
+      <c r="B667" s="43"/>
     </row>
     <row r="668">
-      <c r="A668" s="42"/>
-      <c r="B668" s="42"/>
+      <c r="A668" s="43"/>
+      <c r="B668" s="43"/>
     </row>
     <row r="669">
-      <c r="A669" s="42"/>
-      <c r="B669" s="42"/>
+      <c r="A669" s="43"/>
+      <c r="B669" s="43"/>
     </row>
     <row r="670">
-      <c r="A670" s="42"/>
-      <c r="B670" s="42"/>
+      <c r="A670" s="43"/>
+      <c r="B670" s="43"/>
     </row>
     <row r="671">
-      <c r="A671" s="42"/>
-      <c r="B671" s="42"/>
+      <c r="A671" s="43"/>
+      <c r="B671" s="43"/>
     </row>
     <row r="672">
-      <c r="A672" s="42"/>
-      <c r="B672" s="42"/>
+      <c r="A672" s="43"/>
+      <c r="B672" s="43"/>
     </row>
     <row r="673">
-      <c r="A673" s="42"/>
-      <c r="B673" s="42"/>
+      <c r="A673" s="43"/>
+      <c r="B673" s="43"/>
     </row>
     <row r="674">
-      <c r="A674" s="42"/>
-      <c r="B674" s="42"/>
+      <c r="A674" s="43"/>
+      <c r="B674" s="43"/>
     </row>
     <row r="675">
-      <c r="A675" s="42"/>
-      <c r="B675" s="42"/>
+      <c r="A675" s="43"/>
+      <c r="B675" s="43"/>
     </row>
     <row r="676">
-      <c r="A676" s="42"/>
-      <c r="B676" s="42"/>
+      <c r="A676" s="43"/>
+      <c r="B676" s="43"/>
     </row>
     <row r="677">
-      <c r="A677" s="42"/>
-      <c r="B677" s="42"/>
+      <c r="A677" s="43"/>
+      <c r="B677" s="43"/>
     </row>
     <row r="678">
-      <c r="A678" s="42"/>
-      <c r="B678" s="42"/>
+      <c r="A678" s="43"/>
+      <c r="B678" s="43"/>
     </row>
     <row r="679">
-      <c r="A679" s="42"/>
-      <c r="B679" s="42"/>
+      <c r="A679" s="43"/>
+      <c r="B679" s="43"/>
     </row>
     <row r="680">
-      <c r="A680" s="42"/>
-      <c r="B680" s="42"/>
+      <c r="A680" s="43"/>
+      <c r="B680" s="43"/>
     </row>
     <row r="681">
-      <c r="A681" s="42"/>
-      <c r="B681" s="42"/>
+      <c r="A681" s="43"/>
+      <c r="B681" s="43"/>
     </row>
     <row r="682">
-      <c r="A682" s="42"/>
-      <c r="B682" s="42"/>
+      <c r="A682" s="43"/>
+      <c r="B682" s="43"/>
     </row>
     <row r="683">
-      <c r="A683" s="42"/>
-      <c r="B683" s="42"/>
+      <c r="A683" s="43"/>
+      <c r="B683" s="43"/>
     </row>
     <row r="684">
-      <c r="A684" s="42"/>
-      <c r="B684" s="42"/>
+      <c r="A684" s="43"/>
+      <c r="B684" s="43"/>
     </row>
     <row r="685">
-      <c r="A685" s="42"/>
-      <c r="B685" s="42"/>
+      <c r="A685" s="43"/>
+      <c r="B685" s="43"/>
     </row>
     <row r="686">
-      <c r="A686" s="42"/>
-      <c r="B686" s="42"/>
+      <c r="A686" s="43"/>
+      <c r="B686" s="43"/>
     </row>
     <row r="687">
-      <c r="A687" s="42"/>
-      <c r="B687" s="42"/>
+      <c r="A687" s="43"/>
+      <c r="B687" s="43"/>
     </row>
     <row r="688">
-      <c r="A688" s="42"/>
-      <c r="B688" s="42"/>
+      <c r="A688" s="43"/>
+      <c r="B688" s="43"/>
     </row>
     <row r="689">
-      <c r="A689" s="42"/>
-      <c r="B689" s="42"/>
+      <c r="A689" s="43"/>
+      <c r="B689" s="43"/>
     </row>
     <row r="690">
-      <c r="A690" s="42"/>
-      <c r="B690" s="42"/>
+      <c r="A690" s="43"/>
+      <c r="B690" s="43"/>
     </row>
     <row r="691">
-      <c r="A691" s="42"/>
-      <c r="B691" s="42"/>
+      <c r="A691" s="43"/>
+      <c r="B691" s="43"/>
     </row>
     <row r="692">
-      <c r="A692" s="42"/>
-      <c r="B692" s="42"/>
+      <c r="A692" s="43"/>
+      <c r="B692" s="43"/>
     </row>
     <row r="693">
-      <c r="A693" s="42"/>
-      <c r="B693" s="42"/>
+      <c r="A693" s="43"/>
+      <c r="B693" s="43"/>
     </row>
     <row r="694">
-      <c r="A694" s="42"/>
-      <c r="B694" s="42"/>
+      <c r="A694" s="43"/>
+      <c r="B694" s="43"/>
     </row>
     <row r="695">
-      <c r="A695" s="42"/>
-      <c r="B695" s="42"/>
+      <c r="A695" s="43"/>
+      <c r="B695" s="43"/>
     </row>
     <row r="696">
-      <c r="A696" s="42"/>
-      <c r="B696" s="42"/>
+      <c r="A696" s="43"/>
+      <c r="B696" s="43"/>
     </row>
     <row r="697">
-      <c r="A697" s="42"/>
-      <c r="B697" s="42"/>
+      <c r="A697" s="43"/>
+      <c r="B697" s="43"/>
     </row>
     <row r="698">
-      <c r="A698" s="42"/>
-      <c r="B698" s="42"/>
+      <c r="A698" s="43"/>
+      <c r="B698" s="43"/>
     </row>
     <row r="699">
-      <c r="A699" s="42"/>
-      <c r="B699" s="42"/>
+      <c r="A699" s="43"/>
+      <c r="B699" s="43"/>
     </row>
     <row r="700">
-      <c r="A700" s="42"/>
-      <c r="B700" s="42"/>
+      <c r="A700" s="43"/>
+      <c r="B700" s="43"/>
     </row>
     <row r="701">
-      <c r="A701" s="42"/>
-      <c r="B701" s="42"/>
+      <c r="A701" s="43"/>
+      <c r="B701" s="43"/>
     </row>
     <row r="702">
-      <c r="A702" s="42"/>
-      <c r="B702" s="42"/>
+      <c r="A702" s="43"/>
+      <c r="B702" s="43"/>
     </row>
     <row r="703">
-      <c r="A703" s="42"/>
-      <c r="B703" s="42"/>
+      <c r="A703" s="43"/>
+      <c r="B703" s="43"/>
     </row>
     <row r="704">
-      <c r="A704" s="42"/>
-      <c r="B704" s="42"/>
+      <c r="A704" s="43"/>
+      <c r="B704" s="43"/>
     </row>
     <row r="705">
-      <c r="A705" s="42"/>
-      <c r="B705" s="42"/>
+      <c r="A705" s="43"/>
+      <c r="B705" s="43"/>
     </row>
     <row r="706">
-      <c r="A706" s="42"/>
-      <c r="B706" s="42"/>
+      <c r="A706" s="43"/>
+      <c r="B706" s="43"/>
     </row>
     <row r="707">
-      <c r="A707" s="42"/>
-      <c r="B707" s="42"/>
+      <c r="A707" s="43"/>
+      <c r="B707" s="43"/>
     </row>
     <row r="708">
-      <c r="A708" s="42"/>
-      <c r="B708" s="42"/>
+      <c r="A708" s="43"/>
+      <c r="B708" s="43"/>
     </row>
     <row r="709">
-      <c r="A709" s="42"/>
-      <c r="B709" s="42"/>
+      <c r="A709" s="43"/>
+      <c r="B709" s="43"/>
     </row>
     <row r="710">
-      <c r="A710" s="42"/>
-      <c r="B710" s="42"/>
+      <c r="A710" s="43"/>
+      <c r="B710" s="43"/>
     </row>
     <row r="711">
-      <c r="A711" s="42"/>
-      <c r="B711" s="42"/>
+      <c r="A711" s="43"/>
+      <c r="B711" s="43"/>
     </row>
     <row r="712">
-      <c r="A712" s="42"/>
-      <c r="B712" s="42"/>
+      <c r="A712" s="43"/>
+      <c r="B712" s="43"/>
     </row>
     <row r="713">
-      <c r="A713" s="42"/>
-      <c r="B713" s="42"/>
+      <c r="A713" s="43"/>
+      <c r="B713" s="43"/>
     </row>
     <row r="714">
-      <c r="A714" s="42"/>
-      <c r="B714" s="42"/>
+      <c r="A714" s="43"/>
+      <c r="B714" s="43"/>
     </row>
     <row r="715">
-      <c r="A715" s="42"/>
-      <c r="B715" s="42"/>
+      <c r="A715" s="43"/>
+      <c r="B715" s="43"/>
     </row>
     <row r="716">
-      <c r="A716" s="42"/>
-      <c r="B716" s="42"/>
+      <c r="A716" s="43"/>
+      <c r="B716" s="43"/>
     </row>
     <row r="717">
-      <c r="A717" s="42"/>
-      <c r="B717" s="42"/>
+      <c r="A717" s="43"/>
+      <c r="B717" s="43"/>
     </row>
     <row r="718">
-      <c r="A718" s="42"/>
-      <c r="B718" s="42"/>
+      <c r="A718" s="43"/>
+      <c r="B718" s="43"/>
     </row>
     <row r="719">
-      <c r="A719" s="42"/>
-      <c r="B719" s="42"/>
+      <c r="A719" s="43"/>
+      <c r="B719" s="43"/>
     </row>
     <row r="720">
-      <c r="A720" s="42"/>
-      <c r="B720" s="42"/>
+      <c r="A720" s="43"/>
+      <c r="B720" s="43"/>
     </row>
     <row r="721">
-      <c r="A721" s="42"/>
-      <c r="B721" s="42"/>
+      <c r="A721" s="43"/>
+      <c r="B721" s="43"/>
     </row>
     <row r="722">
-      <c r="A722" s="42"/>
-      <c r="B722" s="42"/>
+      <c r="A722" s="43"/>
+      <c r="B722" s="43"/>
     </row>
     <row r="723">
-      <c r="A723" s="42"/>
-      <c r="B723" s="42"/>
+      <c r="A723" s="43"/>
+      <c r="B723" s="43"/>
     </row>
     <row r="724">
-      <c r="A724" s="42"/>
-      <c r="B724" s="42"/>
+      <c r="A724" s="43"/>
+      <c r="B724" s="43"/>
     </row>
     <row r="725">
-      <c r="A725" s="42"/>
-      <c r="B725" s="42"/>
+      <c r="A725" s="43"/>
+      <c r="B725" s="43"/>
     </row>
     <row r="726">
-      <c r="A726" s="42"/>
-      <c r="B726" s="42"/>
+      <c r="A726" s="43"/>
+      <c r="B726" s="43"/>
     </row>
     <row r="727">
-      <c r="A727" s="42"/>
-      <c r="B727" s="42"/>
+      <c r="A727" s="43"/>
+      <c r="B727" s="43"/>
     </row>
     <row r="728">
-      <c r="A728" s="42"/>
-      <c r="B728" s="42"/>
+      <c r="A728" s="43"/>
+      <c r="B728" s="43"/>
     </row>
     <row r="729">
-      <c r="A729" s="42"/>
-      <c r="B729" s="42"/>
+      <c r="A729" s="43"/>
+      <c r="B729" s="43"/>
     </row>
     <row r="730">
-      <c r="A730" s="42"/>
-      <c r="B730" s="42"/>
+      <c r="A730" s="43"/>
+      <c r="B730" s="43"/>
     </row>
     <row r="731">
-      <c r="A731" s="42"/>
-      <c r="B731" s="42"/>
+      <c r="A731" s="43"/>
+      <c r="B731" s="43"/>
     </row>
     <row r="732">
-      <c r="A732" s="42"/>
-      <c r="B732" s="42"/>
+      <c r="A732" s="43"/>
+      <c r="B732" s="43"/>
     </row>
     <row r="733">
-      <c r="A733" s="42"/>
-      <c r="B733" s="42"/>
+      <c r="A733" s="43"/>
+      <c r="B733" s="43"/>
     </row>
     <row r="734">
-      <c r="A734" s="42"/>
-      <c r="B734" s="42"/>
+      <c r="A734" s="43"/>
+      <c r="B734" s="43"/>
     </row>
     <row r="735">
-      <c r="A735" s="42"/>
-      <c r="B735" s="42"/>
+      <c r="A735" s="43"/>
+      <c r="B735" s="43"/>
     </row>
     <row r="736">
-      <c r="A736" s="42"/>
-      <c r="B736" s="42"/>
+      <c r="A736" s="43"/>
+      <c r="B736" s="43"/>
     </row>
     <row r="737">
-      <c r="A737" s="42"/>
-      <c r="B737" s="42"/>
+      <c r="A737" s="43"/>
+      <c r="B737" s="43"/>
     </row>
     <row r="738">
-      <c r="A738" s="42"/>
-      <c r="B738" s="42"/>
+      <c r="A738" s="43"/>
+      <c r="B738" s="43"/>
     </row>
     <row r="739">
-      <c r="A739" s="42"/>
-      <c r="B739" s="42"/>
+      <c r="A739" s="43"/>
+      <c r="B739" s="43"/>
     </row>
     <row r="740">
-      <c r="A740" s="42"/>
-      <c r="B740" s="42"/>
+      <c r="A740" s="43"/>
+      <c r="B740" s="43"/>
     </row>
     <row r="741">
-      <c r="A741" s="42"/>
-      <c r="B741" s="42"/>
+      <c r="A741" s="43"/>
+      <c r="B741" s="43"/>
     </row>
     <row r="742">
-      <c r="A742" s="42"/>
-      <c r="B742" s="42"/>
+      <c r="A742" s="43"/>
+      <c r="B742" s="43"/>
     </row>
     <row r="743">
-      <c r="A743" s="42"/>
-      <c r="B743" s="42"/>
+      <c r="A743" s="43"/>
+      <c r="B743" s="43"/>
     </row>
     <row r="744">
-      <c r="A744" s="42"/>
-      <c r="B744" s="42"/>
+      <c r="A744" s="43"/>
+      <c r="B744" s="43"/>
     </row>
     <row r="745">
-      <c r="A745" s="42"/>
-      <c r="B745" s="42"/>
+      <c r="A745" s="43"/>
+      <c r="B745" s="43"/>
     </row>
     <row r="746">
-      <c r="A746" s="42"/>
-      <c r="B746" s="42"/>
+      <c r="A746" s="43"/>
+      <c r="B746" s="43"/>
     </row>
     <row r="747">
-      <c r="A747" s="42"/>
-      <c r="B747" s="42"/>
+      <c r="A747" s="43"/>
+      <c r="B747" s="43"/>
     </row>
     <row r="748">
-      <c r="A748" s="42"/>
-      <c r="B748" s="42"/>
+      <c r="A748" s="43"/>
+      <c r="B748" s="43"/>
     </row>
     <row r="749">
-      <c r="A749" s="42"/>
-      <c r="B749" s="42"/>
+      <c r="A749" s="43"/>
+      <c r="B749" s="43"/>
     </row>
     <row r="750">
-      <c r="A750" s="42"/>
-      <c r="B750" s="42"/>
+      <c r="A750" s="43"/>
+      <c r="B750" s="43"/>
     </row>
     <row r="751">
-      <c r="A751" s="42"/>
-      <c r="B751" s="42"/>
+      <c r="A751" s="43"/>
+      <c r="B751" s="43"/>
     </row>
     <row r="752">
-      <c r="A752" s="42"/>
-      <c r="B752" s="42"/>
+      <c r="A752" s="43"/>
+      <c r="B752" s="43"/>
     </row>
     <row r="753">
-      <c r="A753" s="42"/>
-      <c r="B753" s="42"/>
+      <c r="A753" s="43"/>
+      <c r="B753" s="43"/>
     </row>
     <row r="754">
-      <c r="A754" s="42"/>
-      <c r="B754" s="42"/>
+      <c r="A754" s="43"/>
+      <c r="B754" s="43"/>
     </row>
     <row r="755">
-      <c r="A755" s="42"/>
-      <c r="B755" s="42"/>
+      <c r="A755" s="43"/>
+      <c r="B755" s="43"/>
     </row>
     <row r="756">
-      <c r="A756" s="42"/>
-      <c r="B756" s="42"/>
+      <c r="A756" s="43"/>
+      <c r="B756" s="43"/>
     </row>
     <row r="757">
-      <c r="A757" s="42"/>
-      <c r="B757" s="42"/>
+      <c r="A757" s="43"/>
+      <c r="B757" s="43"/>
     </row>
     <row r="758">
-      <c r="A758" s="42"/>
-      <c r="B758" s="42"/>
+      <c r="A758" s="43"/>
+      <c r="B758" s="43"/>
     </row>
     <row r="759">
-      <c r="A759" s="42"/>
-      <c r="B759" s="42"/>
+      <c r="A759" s="43"/>
+      <c r="B759" s="43"/>
     </row>
     <row r="760">
-      <c r="A760" s="42"/>
-      <c r="B760" s="42"/>
+      <c r="A760" s="43"/>
+      <c r="B760" s="43"/>
     </row>
     <row r="761">
-      <c r="A761" s="42"/>
-      <c r="B761" s="42"/>
+      <c r="A761" s="43"/>
+      <c r="B761" s="43"/>
     </row>
     <row r="762">
-      <c r="A762" s="42"/>
-      <c r="B762" s="42"/>
+      <c r="A762" s="43"/>
+      <c r="B762" s="43"/>
     </row>
     <row r="763">
-      <c r="A763" s="42"/>
-      <c r="B763" s="42"/>
+      <c r="A763" s="43"/>
+      <c r="B763" s="43"/>
     </row>
     <row r="764">
-      <c r="A764" s="42"/>
-      <c r="B764" s="42"/>
+      <c r="A764" s="43"/>
+      <c r="B764" s="43"/>
     </row>
     <row r="765">
-      <c r="A765" s="42"/>
-      <c r="B765" s="42"/>
+      <c r="A765" s="43"/>
+      <c r="B765" s="43"/>
     </row>
     <row r="766">
-      <c r="A766" s="42"/>
-      <c r="B766" s="42"/>
+      <c r="A766" s="43"/>
+      <c r="B766" s="43"/>
     </row>
     <row r="767">
-      <c r="A767" s="42"/>
-      <c r="B767" s="42"/>
+      <c r="A767" s="43"/>
+      <c r="B767" s="43"/>
     </row>
     <row r="768">
-      <c r="A768" s="42"/>
-      <c r="B768" s="42"/>
+      <c r="A768" s="43"/>
+      <c r="B768" s="43"/>
     </row>
     <row r="769">
-      <c r="A769" s="42"/>
-      <c r="B769" s="42"/>
+      <c r="A769" s="43"/>
+      <c r="B769" s="43"/>
     </row>
     <row r="770">
-      <c r="A770" s="42"/>
-      <c r="B770" s="42"/>
+      <c r="A770" s="43"/>
+      <c r="B770" s="43"/>
     </row>
     <row r="771">
-      <c r="A771" s="42"/>
-      <c r="B771" s="42"/>
+      <c r="A771" s="43"/>
+      <c r="B771" s="43"/>
     </row>
     <row r="772">
-      <c r="A772" s="42"/>
-      <c r="B772" s="42"/>
+      <c r="A772" s="43"/>
+      <c r="B772" s="43"/>
     </row>
     <row r="773">
-      <c r="A773" s="42"/>
-      <c r="B773" s="42"/>
+      <c r="A773" s="43"/>
+      <c r="B773" s="43"/>
     </row>
     <row r="774">
-      <c r="A774" s="42"/>
-      <c r="B774" s="42"/>
+      <c r="A774" s="43"/>
+      <c r="B774" s="43"/>
     </row>
     <row r="775">
-      <c r="A775" s="42"/>
-      <c r="B775" s="42"/>
+      <c r="A775" s="43"/>
+      <c r="B775" s="43"/>
     </row>
     <row r="776">
-      <c r="A776" s="42"/>
-      <c r="B776" s="42"/>
+      <c r="A776" s="43"/>
+      <c r="B776" s="43"/>
     </row>
     <row r="777">
-      <c r="A777" s="42"/>
-      <c r="B777" s="42"/>
+      <c r="A777" s="43"/>
+      <c r="B777" s="43"/>
     </row>
     <row r="778">
-      <c r="A778" s="42"/>
-      <c r="B778" s="42"/>
+      <c r="A778" s="43"/>
+      <c r="B778" s="43"/>
     </row>
     <row r="779">
-      <c r="A779" s="42"/>
-      <c r="B779" s="42"/>
+      <c r="A779" s="43"/>
+      <c r="B779" s="43"/>
     </row>
     <row r="780">
-      <c r="A780" s="42"/>
-      <c r="B780" s="42"/>
+      <c r="A780" s="43"/>
+      <c r="B780" s="43"/>
     </row>
     <row r="781">
-      <c r="A781" s="42"/>
-      <c r="B781" s="42"/>
+      <c r="A781" s="43"/>
+      <c r="B781" s="43"/>
     </row>
     <row r="782">
-      <c r="A782" s="42"/>
-      <c r="B782" s="42"/>
+      <c r="A782" s="43"/>
+      <c r="B782" s="43"/>
     </row>
     <row r="783">
-      <c r="A783" s="42"/>
-      <c r="B783" s="42"/>
+      <c r="A783" s="43"/>
+      <c r="B783" s="43"/>
     </row>
     <row r="784">
-      <c r="A784" s="42"/>
-      <c r="B784" s="42"/>
+      <c r="A784" s="43"/>
+      <c r="B784" s="43"/>
     </row>
     <row r="785">
-      <c r="A785" s="42"/>
-      <c r="B785" s="42"/>
+      <c r="A785" s="43"/>
+      <c r="B785" s="43"/>
     </row>
     <row r="786">
-      <c r="A786" s="42"/>
-      <c r="B786" s="42"/>
+      <c r="A786" s="43"/>
+      <c r="B786" s="43"/>
     </row>
     <row r="787">
-      <c r="A787" s="42"/>
-      <c r="B787" s="42"/>
+      <c r="A787" s="43"/>
+      <c r="B787" s="43"/>
     </row>
     <row r="788">
-      <c r="A788" s="42"/>
-      <c r="B788" s="42"/>
+      <c r="A788" s="43"/>
+      <c r="B788" s="43"/>
     </row>
     <row r="789">
-      <c r="A789" s="42"/>
-      <c r="B789" s="42"/>
+      <c r="A789" s="43"/>
+      <c r="B789" s="43"/>
     </row>
     <row r="790">
-      <c r="A790" s="42"/>
-      <c r="B790" s="42"/>
+      <c r="A790" s="43"/>
+      <c r="B790" s="43"/>
     </row>
     <row r="791">
-      <c r="A791" s="42"/>
-      <c r="B791" s="42"/>
+      <c r="A791" s="43"/>
+      <c r="B791" s="43"/>
     </row>
     <row r="792">
-      <c r="A792" s="42"/>
-      <c r="B792" s="42"/>
+      <c r="A792" s="43"/>
+      <c r="B792" s="43"/>
     </row>
     <row r="793">
-      <c r="A793" s="42"/>
-      <c r="B793" s="42"/>
+      <c r="A793" s="43"/>
+      <c r="B793" s="43"/>
     </row>
     <row r="794">
-      <c r="A794" s="42"/>
-      <c r="B794" s="42"/>
+      <c r="A794" s="43"/>
+      <c r="B794" s="43"/>
     </row>
     <row r="795">
-      <c r="A795" s="42"/>
-      <c r="B795" s="42"/>
+      <c r="A795" s="43"/>
+      <c r="B795" s="43"/>
     </row>
     <row r="796">
-      <c r="A796" s="42"/>
-      <c r="B796" s="42"/>
+      <c r="A796" s="43"/>
+      <c r="B796" s="43"/>
     </row>
     <row r="797">
-      <c r="A797" s="42"/>
-      <c r="B797" s="42"/>
+      <c r="A797" s="43"/>
+      <c r="B797" s="43"/>
     </row>
     <row r="798">
-      <c r="A798" s="42"/>
-      <c r="B798" s="42"/>
+      <c r="A798" s="43"/>
+      <c r="B798" s="43"/>
     </row>
     <row r="799">
-      <c r="A799" s="42"/>
-      <c r="B799" s="42"/>
+      <c r="A799" s="43"/>
+      <c r="B799" s="43"/>
     </row>
     <row r="800">
-      <c r="A800" s="42"/>
-      <c r="B800" s="42"/>
+      <c r="A800" s="43"/>
+      <c r="B800" s="43"/>
     </row>
     <row r="801">
-      <c r="A801" s="42"/>
-      <c r="B801" s="42"/>
+      <c r="A801" s="43"/>
+      <c r="B801" s="43"/>
     </row>
     <row r="802">
-      <c r="A802" s="42"/>
-      <c r="B802" s="42"/>
+      <c r="A802" s="43"/>
+      <c r="B802" s="43"/>
     </row>
     <row r="803">
-      <c r="A803" s="42"/>
-      <c r="B803" s="42"/>
+      <c r="A803" s="43"/>
+      <c r="B803" s="43"/>
     </row>
     <row r="804">
-      <c r="A804" s="42"/>
-      <c r="B804" s="42"/>
+      <c r="A804" s="43"/>
+      <c r="B804" s="43"/>
     </row>
     <row r="805">
-      <c r="A805" s="42"/>
-      <c r="B805" s="42"/>
+      <c r="A805" s="43"/>
+      <c r="B805" s="43"/>
     </row>
     <row r="806">
-      <c r="A806" s="42"/>
-      <c r="B806" s="42"/>
+      <c r="A806" s="43"/>
+      <c r="B806" s="43"/>
     </row>
     <row r="807">
-      <c r="A807" s="42"/>
-      <c r="B807" s="42"/>
+      <c r="A807" s="43"/>
+      <c r="B807" s="43"/>
     </row>
     <row r="808">
-      <c r="A808" s="42"/>
-      <c r="B808" s="42"/>
+      <c r="A808" s="43"/>
+      <c r="B808" s="43"/>
     </row>
     <row r="809">
-      <c r="A809" s="42"/>
-      <c r="B809" s="42"/>
+      <c r="A809" s="43"/>
+      <c r="B809" s="43"/>
     </row>
     <row r="810">
-      <c r="A810" s="42"/>
-      <c r="B810" s="42"/>
+      <c r="A810" s="43"/>
+      <c r="B810" s="43"/>
     </row>
     <row r="811">
-      <c r="A811" s="42"/>
-      <c r="B811" s="42"/>
+      <c r="A811" s="43"/>
+      <c r="B811" s="43"/>
     </row>
     <row r="812">
-      <c r="A812" s="42"/>
-      <c r="B812" s="42"/>
+      <c r="A812" s="43"/>
+      <c r="B812" s="43"/>
     </row>
     <row r="813">
-      <c r="A813" s="42"/>
-      <c r="B813" s="42"/>
+      <c r="A813" s="43"/>
+      <c r="B813" s="43"/>
     </row>
     <row r="814">
-      <c r="A814" s="42"/>
-      <c r="B814" s="42"/>
+      <c r="A814" s="43"/>
+      <c r="B814" s="43"/>
     </row>
     <row r="815">
-      <c r="A815" s="42"/>
-      <c r="B815" s="42"/>
+      <c r="A815" s="43"/>
+      <c r="B815" s="43"/>
     </row>
     <row r="816">
-      <c r="A816" s="42"/>
-      <c r="B816" s="42"/>
+      <c r="A816" s="43"/>
+      <c r="B816" s="43"/>
     </row>
     <row r="817">
-      <c r="A817" s="42"/>
-      <c r="B817" s="42"/>
+      <c r="A817" s="43"/>
+      <c r="B817" s="43"/>
     </row>
     <row r="818">
-      <c r="A818" s="42"/>
-      <c r="B818" s="42"/>
+      <c r="A818" s="43"/>
+      <c r="B818" s="43"/>
     </row>
     <row r="819">
-      <c r="A819" s="42"/>
-      <c r="B819" s="42"/>
+      <c r="A819" s="43"/>
+      <c r="B819" s="43"/>
     </row>
     <row r="820">
-      <c r="A820" s="42"/>
-      <c r="B820" s="42"/>
+      <c r="A820" s="43"/>
+      <c r="B820" s="43"/>
     </row>
     <row r="821">
-      <c r="A821" s="42"/>
-      <c r="B821" s="42"/>
+      <c r="A821" s="43"/>
+      <c r="B821" s="43"/>
     </row>
     <row r="822">
-      <c r="A822" s="42"/>
-      <c r="B822" s="42"/>
+      <c r="A822" s="43"/>
+      <c r="B822" s="43"/>
     </row>
     <row r="823">
-      <c r="A823" s="42"/>
-      <c r="B823" s="42"/>
+      <c r="A823" s="43"/>
+      <c r="B823" s="43"/>
     </row>
     <row r="824">
-      <c r="A824" s="42"/>
-      <c r="B824" s="42"/>
+      <c r="A824" s="43"/>
+      <c r="B824" s="43"/>
     </row>
     <row r="825">
-      <c r="A825" s="42"/>
-      <c r="B825" s="42"/>
+      <c r="A825" s="43"/>
+      <c r="B825" s="43"/>
     </row>
     <row r="826">
-      <c r="A826" s="42"/>
-      <c r="B826" s="42"/>
+      <c r="A826" s="43"/>
+      <c r="B826" s="43"/>
     </row>
     <row r="827">
-      <c r="A827" s="42"/>
-      <c r="B827" s="42"/>
+      <c r="A827" s="43"/>
+      <c r="B827" s="43"/>
     </row>
     <row r="828">
-      <c r="A828" s="42"/>
-      <c r="B828" s="42"/>
+      <c r="A828" s="43"/>
+      <c r="B828" s="43"/>
     </row>
     <row r="829">
-      <c r="A829" s="42"/>
-      <c r="B829" s="42"/>
+      <c r="A829" s="43"/>
+      <c r="B829" s="43"/>
     </row>
     <row r="830">
-      <c r="A830" s="42"/>
-      <c r="B830" s="42"/>
+      <c r="A830" s="43"/>
+      <c r="B830" s="43"/>
     </row>
     <row r="831">
-      <c r="A831" s="42"/>
-      <c r="B831" s="42"/>
+      <c r="A831" s="43"/>
+      <c r="B831" s="43"/>
     </row>
     <row r="832">
-      <c r="A832" s="42"/>
-      <c r="B832" s="42"/>
+      <c r="A832" s="43"/>
+      <c r="B832" s="43"/>
     </row>
     <row r="833">
-      <c r="A833" s="42"/>
-      <c r="B833" s="42"/>
+      <c r="A833" s="43"/>
+      <c r="B833" s="43"/>
     </row>
     <row r="834">
-      <c r="A834" s="42"/>
-      <c r="B834" s="42"/>
+      <c r="A834" s="43"/>
+      <c r="B834" s="43"/>
     </row>
     <row r="835">
-      <c r="A835" s="42"/>
-      <c r="B835" s="42"/>
+      <c r="A835" s="43"/>
+      <c r="B835" s="43"/>
     </row>
     <row r="836">
-      <c r="A836" s="42"/>
-      <c r="B836" s="42"/>
+      <c r="A836" s="43"/>
+      <c r="B836" s="43"/>
     </row>
     <row r="837">
-      <c r="A837" s="42"/>
-      <c r="B837" s="42"/>
+      <c r="A837" s="43"/>
+      <c r="B837" s="43"/>
     </row>
     <row r="838">
-      <c r="A838" s="42"/>
-      <c r="B838" s="42"/>
+      <c r="A838" s="43"/>
+      <c r="B838" s="43"/>
     </row>
     <row r="839">
-      <c r="A839" s="42"/>
-      <c r="B839" s="42"/>
+      <c r="A839" s="43"/>
+      <c r="B839" s="43"/>
     </row>
     <row r="840">
-      <c r="A840" s="42"/>
-      <c r="B840" s="42"/>
+      <c r="A840" s="43"/>
+      <c r="B840" s="43"/>
     </row>
     <row r="841">
-      <c r="A841" s="42"/>
-      <c r="B841" s="42"/>
+      <c r="A841" s="43"/>
+      <c r="B841" s="43"/>
     </row>
     <row r="842">
-      <c r="A842" s="42"/>
-      <c r="B842" s="42"/>
+      <c r="A842" s="43"/>
+      <c r="B842" s="43"/>
     </row>
     <row r="843">
-      <c r="A843" s="42"/>
-      <c r="B843" s="42"/>
+      <c r="A843" s="43"/>
+      <c r="B843" s="43"/>
     </row>
     <row r="844">
-      <c r="A844" s="42"/>
-      <c r="B844" s="42"/>
+      <c r="A844" s="43"/>
+      <c r="B844" s="43"/>
     </row>
     <row r="845">
-      <c r="A845" s="42"/>
-      <c r="B845" s="42"/>
+      <c r="A845" s="43"/>
+      <c r="B845" s="43"/>
     </row>
     <row r="846">
-      <c r="A846" s="42"/>
-      <c r="B846" s="42"/>
+      <c r="A846" s="43"/>
+      <c r="B846" s="43"/>
     </row>
     <row r="847">
-      <c r="A847" s="42"/>
-      <c r="B847" s="42"/>
+      <c r="A847" s="43"/>
+      <c r="B847" s="43"/>
     </row>
     <row r="848">
-      <c r="A848" s="42"/>
-      <c r="B848" s="42"/>
+      <c r="A848" s="43"/>
+      <c r="B848" s="43"/>
     </row>
     <row r="849">
-      <c r="A849" s="42"/>
-      <c r="B849" s="42"/>
+      <c r="A849" s="43"/>
+      <c r="B849" s="43"/>
     </row>
     <row r="850">
-      <c r="A850" s="42"/>
-      <c r="B850" s="42"/>
+      <c r="A850" s="43"/>
+      <c r="B850" s="43"/>
     </row>
     <row r="851">
-      <c r="A851" s="42"/>
-      <c r="B851" s="42"/>
+      <c r="A851" s="43"/>
+      <c r="B851" s="43"/>
     </row>
     <row r="852">
-      <c r="A852" s="42"/>
-      <c r="B852" s="42"/>
+      <c r="A852" s="43"/>
+      <c r="B852" s="43"/>
     </row>
     <row r="853">
-      <c r="A853" s="42"/>
-      <c r="B853" s="42"/>
+      <c r="A853" s="43"/>
+      <c r="B853" s="43"/>
     </row>
     <row r="854">
-      <c r="A854" s="42"/>
-      <c r="B854" s="42"/>
+      <c r="A854" s="43"/>
+      <c r="B854" s="43"/>
     </row>
     <row r="855">
-      <c r="A855" s="42"/>
-      <c r="B855" s="42"/>
+      <c r="A855" s="43"/>
+      <c r="B855" s="43"/>
     </row>
     <row r="856">
-      <c r="A856" s="42"/>
-      <c r="B856" s="42"/>
+      <c r="A856" s="43"/>
+      <c r="B856" s="43"/>
     </row>
     <row r="857">
-      <c r="A857" s="42"/>
-      <c r="B857" s="42"/>
+      <c r="A857" s="43"/>
+      <c r="B857" s="43"/>
     </row>
     <row r="858">
-      <c r="A858" s="42"/>
-      <c r="B858" s="42"/>
+      <c r="A858" s="43"/>
+      <c r="B858" s="43"/>
     </row>
     <row r="859">
-      <c r="A859" s="42"/>
-      <c r="B859" s="42"/>
+      <c r="A859" s="43"/>
+      <c r="B859" s="43"/>
     </row>
     <row r="860">
-      <c r="A860" s="42"/>
-      <c r="B860" s="42"/>
+      <c r="A860" s="43"/>
+      <c r="B860" s="43"/>
     </row>
     <row r="861">
-      <c r="A861" s="42"/>
-      <c r="B861" s="42"/>
+      <c r="A861" s="43"/>
+      <c r="B861" s="43"/>
     </row>
     <row r="862">
-      <c r="A862" s="42"/>
-      <c r="B862" s="42"/>
+      <c r="A862" s="43"/>
+      <c r="B862" s="43"/>
     </row>
     <row r="863">
-      <c r="A863" s="42"/>
-      <c r="B863" s="42"/>
+      <c r="A863" s="43"/>
+      <c r="B863" s="43"/>
     </row>
     <row r="864">
-      <c r="A864" s="42"/>
-      <c r="B864" s="42"/>
+      <c r="A864" s="43"/>
+      <c r="B864" s="43"/>
     </row>
     <row r="865">
-      <c r="A865" s="42"/>
-      <c r="B865" s="42"/>
+      <c r="A865" s="43"/>
+      <c r="B865" s="43"/>
     </row>
     <row r="866">
-      <c r="A866" s="42"/>
-      <c r="B866" s="42"/>
+      <c r="A866" s="43"/>
+      <c r="B866" s="43"/>
     </row>
     <row r="867">
-      <c r="A867" s="42"/>
-      <c r="B867" s="42"/>
+      <c r="A867" s="43"/>
+      <c r="B867" s="43"/>
     </row>
     <row r="868">
-      <c r="A868" s="42"/>
-      <c r="B868" s="42"/>
+      <c r="A868" s="43"/>
+      <c r="B868" s="43"/>
     </row>
     <row r="869">
-      <c r="A869" s="42"/>
-      <c r="B869" s="42"/>
+      <c r="A869" s="43"/>
+      <c r="B869" s="43"/>
     </row>
     <row r="870">
-      <c r="A870" s="42"/>
-      <c r="B870" s="42"/>
+      <c r="A870" s="43"/>
+      <c r="B870" s="43"/>
     </row>
     <row r="871">
-      <c r="A871" s="42"/>
-      <c r="B871" s="42"/>
+      <c r="A871" s="43"/>
+      <c r="B871" s="43"/>
     </row>
     <row r="872">
-      <c r="A872" s="42"/>
-      <c r="B872" s="42"/>
+      <c r="A872" s="43"/>
+      <c r="B872" s="43"/>
     </row>
     <row r="873">
-      <c r="A873" s="42"/>
-      <c r="B873" s="42"/>
+      <c r="A873" s="43"/>
+      <c r="B873" s="43"/>
     </row>
     <row r="874">
-      <c r="A874" s="42"/>
-      <c r="B874" s="42"/>
+      <c r="A874" s="43"/>
+      <c r="B874" s="43"/>
     </row>
     <row r="875">
-      <c r="A875" s="42"/>
-      <c r="B875" s="42"/>
+      <c r="A875" s="43"/>
+      <c r="B875" s="43"/>
     </row>
     <row r="876">
-      <c r="A876" s="42"/>
-      <c r="B876" s="42"/>
+      <c r="A876" s="43"/>
+      <c r="B876" s="43"/>
     </row>
     <row r="877">
-      <c r="A877" s="42"/>
-      <c r="B877" s="42"/>
+      <c r="A877" s="43"/>
+      <c r="B877" s="43"/>
     </row>
     <row r="878">
-      <c r="A878" s="42"/>
-      <c r="B878" s="42"/>
+      <c r="A878" s="43"/>
+      <c r="B878" s="43"/>
     </row>
     <row r="879">
-      <c r="A879" s="42"/>
-      <c r="B879" s="42"/>
+      <c r="A879" s="43"/>
+      <c r="B879" s="43"/>
     </row>
     <row r="880">
-      <c r="A880" s="42"/>
-      <c r="B880" s="42"/>
+      <c r="A880" s="43"/>
+      <c r="B880" s="43"/>
     </row>
     <row r="881">
-      <c r="A881" s="42"/>
-      <c r="B881" s="42"/>
+      <c r="A881" s="43"/>
+      <c r="B881" s="43"/>
     </row>
     <row r="882">
-      <c r="A882" s="42"/>
-      <c r="B882" s="42"/>
+      <c r="A882" s="43"/>
+      <c r="B882" s="43"/>
     </row>
     <row r="883">
-      <c r="A883" s="42"/>
-      <c r="B883" s="42"/>
+      <c r="A883" s="43"/>
+      <c r="B883" s="43"/>
     </row>
     <row r="884">
-      <c r="A884" s="42"/>
-      <c r="B884" s="42"/>
+      <c r="A884" s="43"/>
+      <c r="B884" s="43"/>
     </row>
     <row r="885">
-      <c r="A885" s="42"/>
-      <c r="B885" s="42"/>
+      <c r="A885" s="43"/>
+      <c r="B885" s="43"/>
     </row>
     <row r="886">
-      <c r="A886" s="42"/>
-      <c r="B886" s="42"/>
+      <c r="A886" s="43"/>
+      <c r="B886" s="43"/>
     </row>
     <row r="887">
-      <c r="A887" s="42"/>
-      <c r="B887" s="42"/>
+      <c r="A887" s="43"/>
+      <c r="B887" s="43"/>
     </row>
     <row r="888">
-      <c r="A888" s="42"/>
-      <c r="B888" s="42"/>
+      <c r="A888" s="43"/>
+      <c r="B888" s="43"/>
     </row>
     <row r="889">
-      <c r="A889" s="42"/>
-      <c r="B889" s="42"/>
+      <c r="A889" s="43"/>
+      <c r="B889" s="43"/>
     </row>
     <row r="890">
-      <c r="A890" s="42"/>
-      <c r="B890" s="42"/>
+      <c r="A890" s="43"/>
+      <c r="B890" s="43"/>
     </row>
     <row r="891">
-      <c r="A891" s="42"/>
-      <c r="B891" s="42"/>
+      <c r="A891" s="43"/>
+      <c r="B891" s="43"/>
     </row>
     <row r="892">
-      <c r="A892" s="42"/>
-      <c r="B892" s="42"/>
+      <c r="A892" s="43"/>
+      <c r="B892" s="43"/>
     </row>
     <row r="893">
-      <c r="A893" s="42"/>
-      <c r="B893" s="42"/>
+      <c r="A893" s="43"/>
+      <c r="B893" s="43"/>
     </row>
     <row r="894">
-      <c r="A894" s="42"/>
-      <c r="B894" s="42"/>
+      <c r="A894" s="43"/>
+      <c r="B894" s="43"/>
     </row>
     <row r="895">
-      <c r="A895" s="42"/>
-      <c r="B895" s="42"/>
+      <c r="A895" s="43"/>
+      <c r="B895" s="43"/>
     </row>
     <row r="896">
-      <c r="A896" s="42"/>
-      <c r="B896" s="42"/>
+      <c r="A896" s="43"/>
+      <c r="B896" s="43"/>
     </row>
     <row r="897">
-      <c r="A897" s="42"/>
-      <c r="B897" s="42"/>
+      <c r="A897" s="43"/>
+      <c r="B897" s="43"/>
     </row>
     <row r="898">
-      <c r="A898" s="42"/>
-      <c r="B898" s="42"/>
+      <c r="A898" s="43"/>
+      <c r="B898" s="43"/>
     </row>
     <row r="899">
-      <c r="A899" s="42"/>
-      <c r="B899" s="42"/>
+      <c r="A899" s="43"/>
+      <c r="B899" s="43"/>
     </row>
     <row r="900">
-      <c r="A900" s="42"/>
-      <c r="B900" s="42"/>
+      <c r="A900" s="43"/>
+      <c r="B900" s="43"/>
     </row>
     <row r="901">
-      <c r="A901" s="42"/>
-      <c r="B901" s="42"/>
+      <c r="A901" s="43"/>
+      <c r="B901" s="43"/>
     </row>
     <row r="902">
-      <c r="A902" s="42"/>
-      <c r="B902" s="42"/>
+      <c r="A902" s="43"/>
+      <c r="B902" s="43"/>
     </row>
     <row r="903">
-      <c r="A903" s="42"/>
-      <c r="B903" s="42"/>
+      <c r="A903" s="43"/>
+      <c r="B903" s="43"/>
     </row>
     <row r="904">
-      <c r="A904" s="42"/>
-      <c r="B904" s="42"/>
+      <c r="A904" s="43"/>
+      <c r="B904" s="43"/>
     </row>
     <row r="905">
-      <c r="A905" s="42"/>
-      <c r="B905" s="42"/>
+      <c r="A905" s="43"/>
+      <c r="B905" s="43"/>
     </row>
     <row r="906">
-      <c r="A906" s="42"/>
-      <c r="B906" s="42"/>
+      <c r="A906" s="43"/>
+      <c r="B906" s="43"/>
     </row>
     <row r="907">
-      <c r="A907" s="42"/>
-      <c r="B907" s="42"/>
+      <c r="A907" s="43"/>
+      <c r="B907" s="43"/>
     </row>
     <row r="908">
-      <c r="A908" s="42"/>
-      <c r="B908" s="42"/>
+      <c r="A908" s="43"/>
+      <c r="B908" s="43"/>
     </row>
     <row r="909">
-      <c r="A909" s="42"/>
-      <c r="B909" s="42"/>
+      <c r="A909" s="43"/>
+      <c r="B909" s="43"/>
     </row>
     <row r="910">
-      <c r="A910" s="42"/>
-      <c r="B910" s="42"/>
+      <c r="A910" s="43"/>
+      <c r="B910" s="43"/>
     </row>
     <row r="911">
-      <c r="A911" s="42"/>
-      <c r="B911" s="42"/>
+      <c r="A911" s="43"/>
+      <c r="B911" s="43"/>
     </row>
     <row r="912">
-      <c r="A912" s="42"/>
-      <c r="B912" s="42"/>
+      <c r="A912" s="43"/>
+      <c r="B912" s="43"/>
     </row>
     <row r="913">
-      <c r="A913" s="42"/>
-      <c r="B913" s="42"/>
+      <c r="A913" s="43"/>
+      <c r="B913" s="43"/>
     </row>
     <row r="914">
-      <c r="A914" s="42"/>
-      <c r="B914" s="42"/>
+      <c r="A914" s="43"/>
+      <c r="B914" s="43"/>
     </row>
     <row r="915">
-      <c r="A915" s="42"/>
-      <c r="B915" s="42"/>
+      <c r="A915" s="43"/>
+      <c r="B915" s="43"/>
     </row>
     <row r="916">
-      <c r="A916" s="42"/>
-      <c r="B916" s="42"/>
+      <c r="A916" s="43"/>
+      <c r="B916" s="43"/>
     </row>
     <row r="917">
-      <c r="A917" s="42"/>
-      <c r="B917" s="42"/>
+      <c r="A917" s="43"/>
+      <c r="B917" s="43"/>
     </row>
     <row r="918">
-      <c r="A918" s="42"/>
-      <c r="B918" s="42"/>
+      <c r="A918" s="43"/>
+      <c r="B918" s="43"/>
     </row>
     <row r="919">
-      <c r="A919" s="42"/>
-      <c r="B919" s="42"/>
+      <c r="A919" s="43"/>
+      <c r="B919" s="43"/>
     </row>
     <row r="920">
-      <c r="A920" s="42"/>
-      <c r="B920" s="42"/>
+      <c r="A920" s="43"/>
+      <c r="B920" s="43"/>
     </row>
     <row r="921">
-      <c r="A921" s="42"/>
-      <c r="B921" s="42"/>
+      <c r="A921" s="43"/>
+      <c r="B921" s="43"/>
     </row>
     <row r="922">
-      <c r="A922" s="42"/>
-      <c r="B922" s="42"/>
+      <c r="A922" s="43"/>
+      <c r="B922" s="43"/>
     </row>
     <row r="923">
-      <c r="A923" s="42"/>
-      <c r="B923" s="42"/>
+      <c r="A923" s="43"/>
+      <c r="B923" s="43"/>
     </row>
     <row r="924">
-      <c r="A924" s="42"/>
-      <c r="B924" s="42"/>
+      <c r="A924" s="43"/>
+      <c r="B924" s="43"/>
     </row>
     <row r="925">
-      <c r="A925" s="42"/>
-      <c r="B925" s="42"/>
+      <c r="A925" s="43"/>
+      <c r="B925" s="43"/>
     </row>
     <row r="926">
-      <c r="A926" s="42"/>
-      <c r="B926" s="42"/>
+      <c r="A926" s="43"/>
+      <c r="B926" s="43"/>
     </row>
     <row r="927">
-      <c r="A927" s="42"/>
-      <c r="B927" s="42"/>
+      <c r="A927" s="43"/>
+      <c r="B927" s="43"/>
     </row>
     <row r="928">
-      <c r="A928" s="42"/>
-      <c r="B928" s="42"/>
+      <c r="A928" s="43"/>
+      <c r="B928" s="43"/>
     </row>
     <row r="929">
-      <c r="A929" s="42"/>
-      <c r="B929" s="42"/>
+      <c r="A929" s="43"/>
+      <c r="B929" s="43"/>
     </row>
     <row r="930">
-      <c r="A930" s="42"/>
-      <c r="B930" s="42"/>
+      <c r="A930" s="43"/>
+      <c r="B930" s="43"/>
     </row>
     <row r="931">
-      <c r="A931" s="42"/>
-      <c r="B931" s="42"/>
+      <c r="A931" s="43"/>
+      <c r="B931" s="43"/>
     </row>
     <row r="932">
-      <c r="A932" s="42"/>
-      <c r="B932" s="42"/>
+      <c r="A932" s="43"/>
+      <c r="B932" s="43"/>
     </row>
     <row r="933">
-      <c r="A933" s="42"/>
-      <c r="B933" s="42"/>
+      <c r="A933" s="43"/>
+      <c r="B933" s="43"/>
     </row>
     <row r="934">
-      <c r="A934" s="42"/>
-      <c r="B934" s="42"/>
+      <c r="A934" s="43"/>
+      <c r="B934" s="43"/>
     </row>
     <row r="935">
-      <c r="A935" s="42"/>
-      <c r="B935" s="42"/>
+      <c r="A935" s="43"/>
+      <c r="B935" s="43"/>
     </row>
     <row r="936">
-      <c r="A936" s="42"/>
-      <c r="B936" s="42"/>
+      <c r="A936" s="43"/>
+      <c r="B936" s="43"/>
     </row>
     <row r="937">
-      <c r="A937" s="42"/>
-      <c r="B937" s="42"/>
+      <c r="A937" s="43"/>
+      <c r="B937" s="43"/>
     </row>
     <row r="938">
-      <c r="A938" s="42"/>
-      <c r="B938" s="42"/>
+      <c r="A938" s="43"/>
+      <c r="B938" s="43"/>
     </row>
     <row r="939">
-      <c r="A939" s="42"/>
-      <c r="B939" s="42"/>
+      <c r="A939" s="43"/>
+      <c r="B939" s="43"/>
     </row>
     <row r="940">
-      <c r="A940" s="42"/>
-      <c r="B940" s="42"/>
+      <c r="A940" s="43"/>
+      <c r="B940" s="43"/>
     </row>
     <row r="941">
-      <c r="A941" s="42"/>
-      <c r="B941" s="42"/>
+      <c r="A941" s="43"/>
+      <c r="B941" s="43"/>
     </row>
     <row r="942">
-      <c r="A942" s="42"/>
-      <c r="B942" s="42"/>
+      <c r="A942" s="43"/>
+      <c r="B942" s="43"/>
     </row>
     <row r="943">
-      <c r="A943" s="42"/>
-      <c r="B943" s="42"/>
+      <c r="A943" s="43"/>
+      <c r="B943" s="43"/>
     </row>
     <row r="944">
-      <c r="A944" s="42"/>
-      <c r="B944" s="42"/>
+      <c r="A944" s="43"/>
+      <c r="B944" s="43"/>
     </row>
     <row r="945">
-      <c r="A945" s="42"/>
-      <c r="B945" s="42"/>
+      <c r="A945" s="43"/>
+      <c r="B945" s="43"/>
     </row>
     <row r="946">
-      <c r="A946" s="42"/>
-      <c r="B946" s="42"/>
+      <c r="A946" s="43"/>
+      <c r="B946" s="43"/>
     </row>
     <row r="947">
-      <c r="A947" s="42"/>
-      <c r="B947" s="42"/>
+      <c r="A947" s="43"/>
+      <c r="B947" s="43"/>
     </row>
     <row r="948">
-      <c r="A948" s="42"/>
-      <c r="B948" s="42"/>
+      <c r="A948" s="43"/>
+      <c r="B948" s="43"/>
     </row>
     <row r="949">
-      <c r="A949" s="42"/>
-      <c r="B949" s="42"/>
+      <c r="A949" s="43"/>
+      <c r="B949" s="43"/>
     </row>
     <row r="950">
-      <c r="A950" s="42"/>
-      <c r="B950" s="42"/>
+      <c r="A950" s="43"/>
+      <c r="B950" s="43"/>
     </row>
     <row r="951">
-      <c r="A951" s="42"/>
-      <c r="B951" s="42"/>
+      <c r="A951" s="43"/>
+      <c r="B951" s="43"/>
     </row>
     <row r="952">
-      <c r="A952" s="42"/>
-      <c r="B952" s="42"/>
+      <c r="A952" s="43"/>
+      <c r="B952" s="43"/>
     </row>
     <row r="953">
-      <c r="A953" s="42"/>
-      <c r="B953" s="42"/>
+      <c r="A953" s="43"/>
+      <c r="B953" s="43"/>
     </row>
     <row r="954">
-      <c r="A954" s="42"/>
-      <c r="B954" s="42"/>
+      <c r="A954" s="43"/>
+      <c r="B954" s="43"/>
     </row>
     <row r="955">
-      <c r="A955" s="42"/>
-      <c r="B955" s="42"/>
+      <c r="A955" s="43"/>
+      <c r="B955" s="43"/>
     </row>
     <row r="956">
-      <c r="A956" s="42"/>
-      <c r="B956" s="42"/>
+      <c r="A956" s="43"/>
+      <c r="B956" s="43"/>
     </row>
     <row r="957">
-      <c r="A957" s="42"/>
-      <c r="B957" s="42"/>
+      <c r="A957" s="43"/>
+      <c r="B957" s="43"/>
     </row>
     <row r="958">
-      <c r="A958" s="42"/>
-      <c r="B958" s="42"/>
+      <c r="A958" s="43"/>
+      <c r="B958" s="43"/>
     </row>
     <row r="959">
-      <c r="A959" s="42"/>
-      <c r="B959" s="42"/>
+      <c r="A959" s="43"/>
+      <c r="B959" s="43"/>
     </row>
     <row r="960">
-      <c r="A960" s="42"/>
-      <c r="B960" s="42"/>
+      <c r="A960" s="43"/>
+      <c r="B960" s="43"/>
     </row>
     <row r="961">
-      <c r="A961" s="42"/>
-      <c r="B961" s="42"/>
+      <c r="A961" s="43"/>
+      <c r="B961" s="43"/>
     </row>
     <row r="962">
-      <c r="A962" s="42"/>
-      <c r="B962" s="42"/>
+      <c r="A962" s="43"/>
+      <c r="B962" s="43"/>
     </row>
     <row r="963">
-      <c r="A963" s="42"/>
-      <c r="B963" s="42"/>
+      <c r="A963" s="43"/>
+      <c r="B963" s="43"/>
     </row>
     <row r="964">
-      <c r="A964" s="42"/>
-      <c r="B964" s="42"/>
+      <c r="A964" s="43"/>
+      <c r="B964" s="43"/>
     </row>
     <row r="965">
-      <c r="A965" s="42"/>
-      <c r="B965" s="42"/>
+      <c r="A965" s="43"/>
+      <c r="B965" s="43"/>
     </row>
     <row r="966">
-      <c r="A966" s="42"/>
-      <c r="B966" s="42"/>
+      <c r="A966" s="43"/>
+      <c r="B966" s="43"/>
     </row>
     <row r="967">
-      <c r="A967" s="42"/>
-      <c r="B967" s="42"/>
+      <c r="A967" s="43"/>
+      <c r="B967" s="43"/>
     </row>
     <row r="968">
-      <c r="A968" s="42"/>
-      <c r="B968" s="42"/>
+      <c r="A968" s="43"/>
+      <c r="B968" s="43"/>
     </row>
     <row r="969">
-      <c r="A969" s="42"/>
-      <c r="B969" s="42"/>
+      <c r="A969" s="43"/>
+      <c r="B969" s="43"/>
     </row>
     <row r="970">
-      <c r="A970" s="42"/>
-      <c r="B970" s="42"/>
+      <c r="A970" s="43"/>
+      <c r="B970" s="43"/>
     </row>
     <row r="971">
-      <c r="A971" s="42"/>
-      <c r="B971" s="42"/>
+      <c r="A971" s="43"/>
+      <c r="B971" s="43"/>
     </row>
     <row r="972">
-      <c r="A972" s="42"/>
-      <c r="B972" s="42"/>
+      <c r="A972" s="43"/>
+      <c r="B972" s="43"/>
     </row>
     <row r="973">
-      <c r="A973" s="42"/>
-      <c r="B973" s="42"/>
+      <c r="A973" s="43"/>
+      <c r="B973" s="43"/>
     </row>
     <row r="974">
-      <c r="A974" s="42"/>
-      <c r="B974" s="42"/>
+      <c r="A974" s="43"/>
+      <c r="B974" s="43"/>
     </row>
     <row r="975">
-      <c r="A975" s="42"/>
-      <c r="B975" s="42"/>
+      <c r="A975" s="43"/>
+      <c r="B975" s="43"/>
     </row>
     <row r="976">
-      <c r="A976" s="42"/>
-      <c r="B976" s="42"/>
+      <c r="A976" s="43"/>
+      <c r="B976" s="43"/>
     </row>
     <row r="977">
-      <c r="A977" s="42"/>
-      <c r="B977" s="42"/>
+      <c r="A977" s="43"/>
+      <c r="B977" s="43"/>
     </row>
     <row r="978">
-      <c r="A978" s="42"/>
-      <c r="B978" s="42"/>
+      <c r="A978" s="43"/>
+      <c r="B978" s="43"/>
     </row>
     <row r="979">
-      <c r="A979" s="42"/>
-      <c r="B979" s="42"/>
+      <c r="A979" s="43"/>
+      <c r="B979" s="43"/>
     </row>
     <row r="980">
-      <c r="A980" s="42"/>
-      <c r="B980" s="42"/>
+      <c r="A980" s="43"/>
+      <c r="B980" s="43"/>
     </row>
     <row r="981">
-      <c r="A981" s="42"/>
-      <c r="B981" s="42"/>
+      <c r="A981" s="43"/>
+      <c r="B981" s="43"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
@@ -10210,48 +10317,48 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="4" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="43" t="s">
-        <v>164</v>
-      </c>
-      <c r="B2" s="44" t="s">
-        <v>296</v>
-      </c>
-      <c r="C2" s="44" t="s">
-        <v>297</v>
+      <c r="A2" s="44" t="s">
+        <v>166</v>
+      </c>
+      <c r="B2" s="45" t="s">
+        <v>301</v>
+      </c>
+      <c r="C2" s="45" t="s">
+        <v>302</v>
       </c>
       <c r="D2" s="4"/>
       <c r="E2" s="3">
@@ -10265,14 +10372,14 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="45" t="s">
-        <v>298</v>
-      </c>
-      <c r="B3" s="44" t="s">
-        <v>299</v>
-      </c>
-      <c r="C3" s="46" t="s">
-        <v>300</v>
+      <c r="A3" s="46" t="s">
+        <v>303</v>
+      </c>
+      <c r="B3" s="45" t="s">
+        <v>304</v>
+      </c>
+      <c r="C3" s="47" t="s">
+        <v>305</v>
       </c>
       <c r="D3" s="4"/>
       <c r="E3" s="5">
@@ -10283,24 +10390,24 @@
       </c>
       <c r="G3" s="4"/>
       <c r="H3" s="3" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>304</v>
-      </c>
-      <c r="B4" s="47" t="s">
-        <v>305</v>
-      </c>
-      <c r="C4" s="47" t="s">
-        <v>306</v>
+        <v>309</v>
+      </c>
+      <c r="B4" s="48" t="s">
+        <v>310</v>
+      </c>
+      <c r="C4" s="48" t="s">
+        <v>311</v>
       </c>
       <c r="D4" s="4"/>
       <c r="E4" s="2">
@@ -10311,24 +10418,24 @@
       </c>
       <c r="G4" s="4"/>
       <c r="H4" s="3" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>310</v>
-      </c>
-      <c r="B5" s="48" t="s">
-        <v>311</v>
-      </c>
-      <c r="C5" s="48" t="s">
-        <v>312</v>
+        <v>315</v>
+      </c>
+      <c r="B5" s="49" t="s">
+        <v>316</v>
+      </c>
+      <c r="C5" s="49" t="s">
+        <v>317</v>
       </c>
       <c r="E5" s="3">
         <v>-10.0</v>
@@ -10337,18 +10444,18 @@
         <v>0.0</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="E6" s="3">
         <v>0.0</v>
@@ -10357,24 +10464,24 @@
         <v>-10.0</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="E7" s="3">
         <v>-10.0</v>
@@ -10383,24 +10490,24 @@
         <v>0.0</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="E8" s="3">
         <v>0.0</v>
@@ -10409,24 +10516,24 @@
         <v>-10.0</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="E9" s="3">
         <v>0.0</v>
@@ -10435,25 +10542,25 @@
         <v>0.0</v>
       </c>
       <c r="H9" s="32" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="I9" s="32" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="J9" s="32"/>
       <c r="K9" s="3" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="E10" s="3">
         <v>-10.0</v>
@@ -10462,24 +10569,24 @@
         <v>-10.0</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>342</v>
-      </c>
-      <c r="K10" s="49" t="s">
-        <v>343</v>
+        <v>347</v>
+      </c>
+      <c r="K10" s="50" t="s">
+        <v>348</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="E11" s="3">
         <v>-10.0</v>
@@ -10488,13 +10595,13 @@
         <v>-10.0</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/02Script/Table/EventTable.xlsx
+++ b/Assets/02Script/Table/EventTable.xlsx
@@ -1305,10 +1305,10 @@
       <alignment horizontal="right" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" vertical="bottom"/>
+      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
+      <alignment readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right"/>
@@ -5205,8 +5205,8 @@
       <c r="D91" s="39" t="s">
         <v>229</v>
       </c>
-      <c r="E91" s="19">
-        <v>22006.0</v>
+      <c r="E91" s="26">
+        <v>-1.0</v>
       </c>
       <c r="F91" s="39" t="s">
         <v>133</v>
@@ -5235,8 +5235,8 @@
       <c r="D92" s="36" t="s">
         <v>230</v>
       </c>
-      <c r="E92" s="28">
-        <v>22007.0</v>
+      <c r="E92" s="5">
+        <v>23002.0</v>
       </c>
       <c r="F92" s="36" t="s">
         <v>133</v>
@@ -5265,8 +5265,8 @@
       <c r="D93" s="39" t="s">
         <v>231</v>
       </c>
-      <c r="E93" s="19">
-        <v>22008.0</v>
+      <c r="E93" s="5">
+        <v>23003.0</v>
       </c>
       <c r="F93" s="39" t="s">
         <v>133</v>
@@ -5295,8 +5295,8 @@
       <c r="D94" s="36" t="s">
         <v>232</v>
       </c>
-      <c r="E94" s="28">
-        <v>22009.0</v>
+      <c r="E94" s="5">
+        <v>23004.0</v>
       </c>
       <c r="F94" s="36" t="s">
         <v>133</v>
@@ -5608,8 +5608,8 @@
       <c r="I104" s="36" t="s">
         <v>164</v>
       </c>
-      <c r="J104" s="28">
-        <v>0.0</v>
+      <c r="J104" s="41">
+        <v>-1.0</v>
       </c>
     </row>
     <row r="105">
@@ -5668,8 +5668,8 @@
       <c r="I106" s="36" t="s">
         <v>164</v>
       </c>
-      <c r="J106" s="28">
-        <v>0.0</v>
+      <c r="J106" s="41">
+        <v>-1.0</v>
       </c>
     </row>
     <row r="107">
@@ -5908,8 +5908,8 @@
       <c r="I114" s="36" t="s">
         <v>164</v>
       </c>
-      <c r="J114" s="28">
-        <v>0.0</v>
+      <c r="J114" s="41">
+        <v>-1.0</v>
       </c>
     </row>
     <row r="115">
@@ -5938,8 +5938,8 @@
       <c r="I115" s="39" t="s">
         <v>164</v>
       </c>
-      <c r="J115" s="19">
-        <v>0.0</v>
+      <c r="J115" s="41">
+        <v>-1.0</v>
       </c>
     </row>
     <row r="116">
@@ -6178,8 +6178,8 @@
       <c r="I123" s="39" t="s">
         <v>164</v>
       </c>
-      <c r="J123" s="19">
-        <v>0.0</v>
+      <c r="J123" s="41">
+        <v>-1.0</v>
       </c>
     </row>
     <row r="124">
@@ -6208,8 +6208,8 @@
       <c r="I124" s="36" t="s">
         <v>164</v>
       </c>
-      <c r="J124" s="28">
-        <v>0.0</v>
+      <c r="J124" s="41">
+        <v>-1.0</v>
       </c>
     </row>
     <row r="125">
@@ -6238,8 +6238,8 @@
       <c r="I125" s="39" t="s">
         <v>164</v>
       </c>
-      <c r="J125" s="19">
-        <v>0.0</v>
+      <c r="J125" s="41">
+        <v>-1.0</v>
       </c>
     </row>
     <row r="126">
@@ -6418,8 +6418,8 @@
       <c r="I131" s="39" t="s">
         <v>164</v>
       </c>
-      <c r="J131" s="19">
-        <v>0.0</v>
+      <c r="J131" s="41">
+        <v>-1.0</v>
       </c>
     </row>
     <row r="132">
@@ -6448,8 +6448,8 @@
       <c r="I132" s="36" t="s">
         <v>164</v>
       </c>
-      <c r="J132" s="28">
-        <v>0.0</v>
+      <c r="J132" s="41">
+        <v>-1.0</v>
       </c>
     </row>
     <row r="133">
@@ -6852,7 +6852,7 @@
       <c r="C146" s="5">
         <v>39001.0</v>
       </c>
-      <c r="D146" s="41" t="s">
+      <c r="D146" s="42" t="s">
         <v>287</v>
       </c>
       <c r="E146" s="28">
@@ -6882,7 +6882,7 @@
       <c r="C147" s="3">
         <v>40000.0</v>
       </c>
-      <c r="D147" s="41" t="s">
+      <c r="D147" s="42" t="s">
         <v>288</v>
       </c>
       <c r="E147" s="3">
@@ -6912,7 +6912,7 @@
       <c r="C148" s="3">
         <v>40001.0</v>
       </c>
-      <c r="D148" s="41" t="s">
+      <c r="D148" s="42" t="s">
         <v>289</v>
       </c>
       <c r="E148" s="3">
@@ -6942,10 +6942,10 @@
       <c r="C149" s="3">
         <v>40002.0</v>
       </c>
-      <c r="D149" s="41" t="s">
+      <c r="D149" s="42" t="s">
         <v>290</v>
       </c>
-      <c r="E149" s="42">
+      <c r="E149" s="41">
         <v>-1.0</v>
       </c>
       <c r="F149" s="36" t="s">

--- a/Assets/02Script/Table/EventTable.xlsx
+++ b/Assets/02Script/Table/EventTable.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1139" uniqueCount="355">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1147" uniqueCount="359">
   <si>
     <t>EventID</t>
   </si>
@@ -906,6 +906,13 @@
     <t>도망쳐야해...!</t>
   </si>
   <si>
+    <t>E041</t>
+  </si>
+  <si>
+    <t>밖에 나가기엔 늦은 시간이야..
+내일을 위해서 어서 자야 해.</t>
+  </si>
+  <si>
     <t>Choice0</t>
   </si>
   <si>
@@ -991,6 +998,12 @@
   </si>
   <si>
     <t>비슷한 풍선이겠지?</t>
+  </si>
+  <si>
+    <t>N004_0</t>
+  </si>
+  <si>
+    <t>N004_1</t>
   </si>
   <si>
     <t>N004</t>
@@ -1182,7 +1195,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="52">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1308,6 +1321,9 @@
       <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" vertical="bottom"/>
+    </xf>
+    <xf borderId="0" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="3" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -1444,7 +1460,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="D80:J149" displayName="Table_4" name="Table_4" id="4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="D80:J150" displayName="Table_4" name="Table_4" id="4">
   <tableColumns count="7">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -6963,3332 +6979,3358 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="43"/>
-      <c r="B150" s="43"/>
+      <c r="A150" s="32" t="s">
+        <v>291</v>
+      </c>
+      <c r="B150" s="32" t="s">
+        <v>291</v>
+      </c>
+      <c r="C150" s="3">
+        <v>41001.0</v>
+      </c>
+      <c r="D150" s="42" t="s">
+        <v>292</v>
+      </c>
+      <c r="E150" s="41">
+        <v>-1.0</v>
+      </c>
+      <c r="F150" s="42" t="s">
+        <v>133</v>
+      </c>
+      <c r="G150" s="42" t="s">
+        <v>134</v>
+      </c>
+      <c r="H150" s="36"/>
+      <c r="I150" s="43" t="s">
+        <v>164</v>
+      </c>
+      <c r="J150" s="41">
+        <v>-1.0</v>
+      </c>
     </row>
     <row r="151">
-      <c r="A151" s="43"/>
-      <c r="B151" s="43"/>
+      <c r="A151" s="44"/>
+      <c r="B151" s="44"/>
     </row>
     <row r="152">
-      <c r="A152" s="43"/>
-      <c r="B152" s="43"/>
+      <c r="A152" s="44"/>
+      <c r="B152" s="44"/>
     </row>
     <row r="153">
-      <c r="A153" s="43"/>
-      <c r="B153" s="43"/>
+      <c r="A153" s="44"/>
+      <c r="B153" s="44"/>
     </row>
     <row r="154">
-      <c r="A154" s="43"/>
-      <c r="B154" s="43"/>
+      <c r="A154" s="44"/>
+      <c r="B154" s="44"/>
     </row>
     <row r="155">
-      <c r="A155" s="43"/>
-      <c r="B155" s="43"/>
+      <c r="A155" s="44"/>
+      <c r="B155" s="44"/>
     </row>
     <row r="156">
-      <c r="A156" s="43"/>
-      <c r="B156" s="43"/>
+      <c r="A156" s="44"/>
+      <c r="B156" s="44"/>
     </row>
     <row r="157">
-      <c r="A157" s="43"/>
-      <c r="B157" s="43"/>
+      <c r="A157" s="44"/>
+      <c r="B157" s="44"/>
     </row>
     <row r="158">
-      <c r="A158" s="43"/>
-      <c r="B158" s="43"/>
+      <c r="A158" s="44"/>
+      <c r="B158" s="44"/>
     </row>
     <row r="159">
-      <c r="A159" s="43"/>
-      <c r="B159" s="43"/>
+      <c r="A159" s="44"/>
+      <c r="B159" s="44"/>
     </row>
     <row r="160">
-      <c r="A160" s="43"/>
-      <c r="B160" s="43"/>
+      <c r="A160" s="44"/>
+      <c r="B160" s="44"/>
     </row>
     <row r="161">
-      <c r="A161" s="43"/>
-      <c r="B161" s="43"/>
+      <c r="A161" s="44"/>
+      <c r="B161" s="44"/>
     </row>
     <row r="162">
-      <c r="A162" s="43"/>
-      <c r="B162" s="43"/>
+      <c r="A162" s="44"/>
+      <c r="B162" s="44"/>
     </row>
     <row r="163">
-      <c r="A163" s="43"/>
-      <c r="B163" s="43"/>
+      <c r="A163" s="44"/>
+      <c r="B163" s="44"/>
     </row>
     <row r="164">
-      <c r="A164" s="43"/>
-      <c r="B164" s="43"/>
+      <c r="A164" s="44"/>
+      <c r="B164" s="44"/>
     </row>
     <row r="165">
-      <c r="A165" s="43"/>
-      <c r="B165" s="43"/>
+      <c r="A165" s="44"/>
+      <c r="B165" s="44"/>
     </row>
     <row r="166">
-      <c r="A166" s="43"/>
-      <c r="B166" s="43"/>
+      <c r="A166" s="44"/>
+      <c r="B166" s="44"/>
     </row>
     <row r="167">
-      <c r="A167" s="43"/>
-      <c r="B167" s="43"/>
+      <c r="A167" s="44"/>
+      <c r="B167" s="44"/>
     </row>
     <row r="168">
-      <c r="A168" s="43"/>
-      <c r="B168" s="43"/>
+      <c r="A168" s="44"/>
+      <c r="B168" s="44"/>
     </row>
     <row r="169">
-      <c r="A169" s="43"/>
-      <c r="B169" s="43"/>
+      <c r="A169" s="44"/>
+      <c r="B169" s="44"/>
     </row>
     <row r="170">
-      <c r="A170" s="43"/>
-      <c r="B170" s="43"/>
+      <c r="A170" s="44"/>
+      <c r="B170" s="44"/>
     </row>
     <row r="171">
-      <c r="A171" s="43"/>
-      <c r="B171" s="43"/>
+      <c r="A171" s="44"/>
+      <c r="B171" s="44"/>
     </row>
     <row r="172">
-      <c r="A172" s="43"/>
-      <c r="B172" s="43"/>
+      <c r="A172" s="44"/>
+      <c r="B172" s="44"/>
     </row>
     <row r="173">
-      <c r="A173" s="43"/>
-      <c r="B173" s="43"/>
+      <c r="A173" s="44"/>
+      <c r="B173" s="44"/>
     </row>
     <row r="174">
-      <c r="A174" s="43"/>
-      <c r="B174" s="43"/>
+      <c r="A174" s="44"/>
+      <c r="B174" s="44"/>
     </row>
     <row r="175">
-      <c r="A175" s="43"/>
-      <c r="B175" s="43"/>
+      <c r="A175" s="44"/>
+      <c r="B175" s="44"/>
     </row>
     <row r="176">
-      <c r="A176" s="43"/>
-      <c r="B176" s="43"/>
+      <c r="A176" s="44"/>
+      <c r="B176" s="44"/>
     </row>
     <row r="177">
-      <c r="A177" s="43"/>
-      <c r="B177" s="43"/>
+      <c r="A177" s="44"/>
+      <c r="B177" s="44"/>
     </row>
     <row r="178">
-      <c r="A178" s="43"/>
-      <c r="B178" s="43"/>
+      <c r="A178" s="44"/>
+      <c r="B178" s="44"/>
     </row>
     <row r="179">
-      <c r="A179" s="43"/>
-      <c r="B179" s="43"/>
+      <c r="A179" s="44"/>
+      <c r="B179" s="44"/>
     </row>
     <row r="180">
-      <c r="A180" s="43"/>
-      <c r="B180" s="43"/>
+      <c r="A180" s="44"/>
+      <c r="B180" s="44"/>
     </row>
     <row r="181">
-      <c r="A181" s="43"/>
-      <c r="B181" s="43"/>
+      <c r="A181" s="44"/>
+      <c r="B181" s="44"/>
     </row>
     <row r="182">
-      <c r="A182" s="43"/>
-      <c r="B182" s="43"/>
+      <c r="A182" s="44"/>
+      <c r="B182" s="44"/>
     </row>
     <row r="183">
-      <c r="A183" s="43"/>
-      <c r="B183" s="43"/>
+      <c r="A183" s="44"/>
+      <c r="B183" s="44"/>
     </row>
     <row r="184">
-      <c r="A184" s="43"/>
-      <c r="B184" s="43"/>
+      <c r="A184" s="44"/>
+      <c r="B184" s="44"/>
     </row>
     <row r="185">
-      <c r="A185" s="43"/>
-      <c r="B185" s="43"/>
+      <c r="A185" s="44"/>
+      <c r="B185" s="44"/>
     </row>
     <row r="186">
-      <c r="A186" s="43"/>
-      <c r="B186" s="43"/>
+      <c r="A186" s="44"/>
+      <c r="B186" s="44"/>
     </row>
     <row r="187">
-      <c r="A187" s="43"/>
-      <c r="B187" s="43"/>
+      <c r="A187" s="44"/>
+      <c r="B187" s="44"/>
     </row>
     <row r="188">
-      <c r="A188" s="43"/>
-      <c r="B188" s="43"/>
+      <c r="A188" s="44"/>
+      <c r="B188" s="44"/>
     </row>
     <row r="189">
-      <c r="A189" s="43"/>
-      <c r="B189" s="43"/>
+      <c r="A189" s="44"/>
+      <c r="B189" s="44"/>
     </row>
     <row r="190">
-      <c r="A190" s="43"/>
-      <c r="B190" s="43"/>
+      <c r="A190" s="44"/>
+      <c r="B190" s="44"/>
     </row>
     <row r="191">
-      <c r="A191" s="43"/>
-      <c r="B191" s="43"/>
+      <c r="A191" s="44"/>
+      <c r="B191" s="44"/>
     </row>
     <row r="192">
-      <c r="A192" s="43"/>
-      <c r="B192" s="43"/>
+      <c r="A192" s="44"/>
+      <c r="B192" s="44"/>
     </row>
     <row r="193">
-      <c r="A193" s="43"/>
-      <c r="B193" s="43"/>
+      <c r="A193" s="44"/>
+      <c r="B193" s="44"/>
     </row>
     <row r="194">
-      <c r="A194" s="43"/>
-      <c r="B194" s="43"/>
+      <c r="A194" s="44"/>
+      <c r="B194" s="44"/>
     </row>
     <row r="195">
-      <c r="A195" s="43"/>
-      <c r="B195" s="43"/>
+      <c r="A195" s="44"/>
+      <c r="B195" s="44"/>
     </row>
     <row r="196">
-      <c r="A196" s="43"/>
-      <c r="B196" s="43"/>
+      <c r="A196" s="44"/>
+      <c r="B196" s="44"/>
     </row>
     <row r="197">
-      <c r="A197" s="43"/>
-      <c r="B197" s="43"/>
+      <c r="A197" s="44"/>
+      <c r="B197" s="44"/>
     </row>
     <row r="198">
-      <c r="A198" s="43"/>
-      <c r="B198" s="43"/>
+      <c r="A198" s="44"/>
+      <c r="B198" s="44"/>
     </row>
     <row r="199">
-      <c r="A199" s="43"/>
-      <c r="B199" s="43"/>
+      <c r="A199" s="44"/>
+      <c r="B199" s="44"/>
     </row>
     <row r="200">
-      <c r="A200" s="43"/>
-      <c r="B200" s="43"/>
+      <c r="A200" s="44"/>
+      <c r="B200" s="44"/>
     </row>
     <row r="201">
-      <c r="A201" s="43"/>
-      <c r="B201" s="43"/>
+      <c r="A201" s="44"/>
+      <c r="B201" s="44"/>
     </row>
     <row r="202">
-      <c r="A202" s="43"/>
-      <c r="B202" s="43"/>
+      <c r="A202" s="44"/>
+      <c r="B202" s="44"/>
     </row>
     <row r="203">
-      <c r="A203" s="43"/>
-      <c r="B203" s="43"/>
+      <c r="A203" s="44"/>
+      <c r="B203" s="44"/>
     </row>
     <row r="204">
-      <c r="A204" s="43"/>
-      <c r="B204" s="43"/>
+      <c r="A204" s="44"/>
+      <c r="B204" s="44"/>
     </row>
     <row r="205">
-      <c r="A205" s="43"/>
-      <c r="B205" s="43"/>
+      <c r="A205" s="44"/>
+      <c r="B205" s="44"/>
     </row>
     <row r="206">
-      <c r="A206" s="43"/>
-      <c r="B206" s="43"/>
+      <c r="A206" s="44"/>
+      <c r="B206" s="44"/>
     </row>
     <row r="207">
-      <c r="A207" s="43"/>
-      <c r="B207" s="43"/>
+      <c r="A207" s="44"/>
+      <c r="B207" s="44"/>
     </row>
     <row r="208">
-      <c r="A208" s="43"/>
-      <c r="B208" s="43"/>
+      <c r="A208" s="44"/>
+      <c r="B208" s="44"/>
     </row>
     <row r="209">
-      <c r="A209" s="43"/>
-      <c r="B209" s="43"/>
+      <c r="A209" s="44"/>
+      <c r="B209" s="44"/>
     </row>
     <row r="210">
-      <c r="A210" s="43"/>
-      <c r="B210" s="43"/>
+      <c r="A210" s="44"/>
+      <c r="B210" s="44"/>
     </row>
     <row r="211">
-      <c r="A211" s="43"/>
-      <c r="B211" s="43"/>
+      <c r="A211" s="44"/>
+      <c r="B211" s="44"/>
     </row>
     <row r="212">
-      <c r="A212" s="43"/>
-      <c r="B212" s="43"/>
+      <c r="A212" s="44"/>
+      <c r="B212" s="44"/>
     </row>
     <row r="213">
-      <c r="A213" s="43"/>
-      <c r="B213" s="43"/>
+      <c r="A213" s="44"/>
+      <c r="B213" s="44"/>
     </row>
     <row r="214">
-      <c r="A214" s="43"/>
-      <c r="B214" s="43"/>
+      <c r="A214" s="44"/>
+      <c r="B214" s="44"/>
     </row>
     <row r="215">
-      <c r="A215" s="43"/>
-      <c r="B215" s="43"/>
+      <c r="A215" s="44"/>
+      <c r="B215" s="44"/>
     </row>
     <row r="216">
-      <c r="A216" s="43"/>
-      <c r="B216" s="43"/>
+      <c r="A216" s="44"/>
+      <c r="B216" s="44"/>
     </row>
     <row r="217">
-      <c r="A217" s="43"/>
-      <c r="B217" s="43"/>
+      <c r="A217" s="44"/>
+      <c r="B217" s="44"/>
     </row>
     <row r="218">
-      <c r="A218" s="43"/>
-      <c r="B218" s="43"/>
+      <c r="A218" s="44"/>
+      <c r="B218" s="44"/>
     </row>
     <row r="219">
-      <c r="A219" s="43"/>
-      <c r="B219" s="43"/>
+      <c r="A219" s="44"/>
+      <c r="B219" s="44"/>
     </row>
     <row r="220">
-      <c r="A220" s="43"/>
-      <c r="B220" s="43"/>
+      <c r="A220" s="44"/>
+      <c r="B220" s="44"/>
     </row>
     <row r="221">
-      <c r="A221" s="43"/>
-      <c r="B221" s="43"/>
+      <c r="A221" s="44"/>
+      <c r="B221" s="44"/>
     </row>
     <row r="222">
-      <c r="A222" s="43"/>
-      <c r="B222" s="43"/>
+      <c r="A222" s="44"/>
+      <c r="B222" s="44"/>
     </row>
     <row r="223">
-      <c r="A223" s="43"/>
-      <c r="B223" s="43"/>
+      <c r="A223" s="44"/>
+      <c r="B223" s="44"/>
     </row>
     <row r="224">
-      <c r="A224" s="43"/>
-      <c r="B224" s="43"/>
+      <c r="A224" s="44"/>
+      <c r="B224" s="44"/>
     </row>
     <row r="225">
-      <c r="A225" s="43"/>
-      <c r="B225" s="43"/>
+      <c r="A225" s="44"/>
+      <c r="B225" s="44"/>
     </row>
     <row r="226">
-      <c r="A226" s="43"/>
-      <c r="B226" s="43"/>
+      <c r="A226" s="44"/>
+      <c r="B226" s="44"/>
     </row>
     <row r="227">
-      <c r="A227" s="43"/>
-      <c r="B227" s="43"/>
+      <c r="A227" s="44"/>
+      <c r="B227" s="44"/>
     </row>
     <row r="228">
-      <c r="A228" s="43"/>
-      <c r="B228" s="43"/>
+      <c r="A228" s="44"/>
+      <c r="B228" s="44"/>
     </row>
     <row r="229">
-      <c r="A229" s="43"/>
-      <c r="B229" s="43"/>
+      <c r="A229" s="44"/>
+      <c r="B229" s="44"/>
     </row>
     <row r="230">
-      <c r="A230" s="43"/>
-      <c r="B230" s="43"/>
+      <c r="A230" s="44"/>
+      <c r="B230" s="44"/>
     </row>
     <row r="231">
-      <c r="A231" s="43"/>
-      <c r="B231" s="43"/>
+      <c r="A231" s="44"/>
+      <c r="B231" s="44"/>
     </row>
     <row r="232">
-      <c r="A232" s="43"/>
-      <c r="B232" s="43"/>
+      <c r="A232" s="44"/>
+      <c r="B232" s="44"/>
     </row>
     <row r="233">
-      <c r="A233" s="43"/>
-      <c r="B233" s="43"/>
+      <c r="A233" s="44"/>
+      <c r="B233" s="44"/>
     </row>
     <row r="234">
-      <c r="A234" s="43"/>
-      <c r="B234" s="43"/>
+      <c r="A234" s="44"/>
+      <c r="B234" s="44"/>
     </row>
     <row r="235">
-      <c r="A235" s="43"/>
-      <c r="B235" s="43"/>
+      <c r="A235" s="44"/>
+      <c r="B235" s="44"/>
     </row>
     <row r="236">
-      <c r="A236" s="43"/>
-      <c r="B236" s="43"/>
+      <c r="A236" s="44"/>
+      <c r="B236" s="44"/>
     </row>
     <row r="237">
-      <c r="A237" s="43"/>
-      <c r="B237" s="43"/>
+      <c r="A237" s="44"/>
+      <c r="B237" s="44"/>
     </row>
     <row r="238">
-      <c r="A238" s="43"/>
-      <c r="B238" s="43"/>
+      <c r="A238" s="44"/>
+      <c r="B238" s="44"/>
     </row>
     <row r="239">
-      <c r="A239" s="43"/>
-      <c r="B239" s="43"/>
+      <c r="A239" s="44"/>
+      <c r="B239" s="44"/>
     </row>
     <row r="240">
-      <c r="A240" s="43"/>
-      <c r="B240" s="43"/>
+      <c r="A240" s="44"/>
+      <c r="B240" s="44"/>
     </row>
     <row r="241">
-      <c r="A241" s="43"/>
-      <c r="B241" s="43"/>
+      <c r="A241" s="44"/>
+      <c r="B241" s="44"/>
     </row>
     <row r="242">
-      <c r="A242" s="43"/>
-      <c r="B242" s="43"/>
+      <c r="A242" s="44"/>
+      <c r="B242" s="44"/>
     </row>
     <row r="243">
-      <c r="A243" s="43"/>
-      <c r="B243" s="43"/>
+      <c r="A243" s="44"/>
+      <c r="B243" s="44"/>
     </row>
     <row r="244">
-      <c r="A244" s="43"/>
-      <c r="B244" s="43"/>
+      <c r="A244" s="44"/>
+      <c r="B244" s="44"/>
     </row>
     <row r="245">
-      <c r="A245" s="43"/>
-      <c r="B245" s="43"/>
+      <c r="A245" s="44"/>
+      <c r="B245" s="44"/>
     </row>
     <row r="246">
-      <c r="A246" s="43"/>
-      <c r="B246" s="43"/>
+      <c r="A246" s="44"/>
+      <c r="B246" s="44"/>
     </row>
     <row r="247">
-      <c r="A247" s="43"/>
-      <c r="B247" s="43"/>
+      <c r="A247" s="44"/>
+      <c r="B247" s="44"/>
     </row>
     <row r="248">
-      <c r="A248" s="43"/>
-      <c r="B248" s="43"/>
+      <c r="A248" s="44"/>
+      <c r="B248" s="44"/>
     </row>
     <row r="249">
-      <c r="A249" s="43"/>
-      <c r="B249" s="43"/>
+      <c r="A249" s="44"/>
+      <c r="B249" s="44"/>
     </row>
     <row r="250">
-      <c r="A250" s="43"/>
-      <c r="B250" s="43"/>
+      <c r="A250" s="44"/>
+      <c r="B250" s="44"/>
     </row>
     <row r="251">
-      <c r="A251" s="43"/>
-      <c r="B251" s="43"/>
+      <c r="A251" s="44"/>
+      <c r="B251" s="44"/>
     </row>
     <row r="252">
-      <c r="A252" s="43"/>
-      <c r="B252" s="43"/>
+      <c r="A252" s="44"/>
+      <c r="B252" s="44"/>
     </row>
     <row r="253">
-      <c r="A253" s="43"/>
-      <c r="B253" s="43"/>
+      <c r="A253" s="44"/>
+      <c r="B253" s="44"/>
     </row>
     <row r="254">
-      <c r="A254" s="43"/>
-      <c r="B254" s="43"/>
+      <c r="A254" s="44"/>
+      <c r="B254" s="44"/>
     </row>
     <row r="255">
-      <c r="A255" s="43"/>
-      <c r="B255" s="43"/>
+      <c r="A255" s="44"/>
+      <c r="B255" s="44"/>
     </row>
     <row r="256">
-      <c r="A256" s="43"/>
-      <c r="B256" s="43"/>
+      <c r="A256" s="44"/>
+      <c r="B256" s="44"/>
     </row>
     <row r="257">
-      <c r="A257" s="43"/>
-      <c r="B257" s="43"/>
+      <c r="A257" s="44"/>
+      <c r="B257" s="44"/>
     </row>
     <row r="258">
-      <c r="A258" s="43"/>
-      <c r="B258" s="43"/>
+      <c r="A258" s="44"/>
+      <c r="B258" s="44"/>
     </row>
     <row r="259">
-      <c r="A259" s="43"/>
-      <c r="B259" s="43"/>
+      <c r="A259" s="44"/>
+      <c r="B259" s="44"/>
     </row>
     <row r="260">
-      <c r="A260" s="43"/>
-      <c r="B260" s="43"/>
+      <c r="A260" s="44"/>
+      <c r="B260" s="44"/>
     </row>
     <row r="261">
-      <c r="A261" s="43"/>
-      <c r="B261" s="43"/>
+      <c r="A261" s="44"/>
+      <c r="B261" s="44"/>
     </row>
     <row r="262">
-      <c r="A262" s="43"/>
-      <c r="B262" s="43"/>
+      <c r="A262" s="44"/>
+      <c r="B262" s="44"/>
     </row>
     <row r="263">
-      <c r="A263" s="43"/>
-      <c r="B263" s="43"/>
+      <c r="A263" s="44"/>
+      <c r="B263" s="44"/>
     </row>
     <row r="264">
-      <c r="A264" s="43"/>
-      <c r="B264" s="43"/>
+      <c r="A264" s="44"/>
+      <c r="B264" s="44"/>
     </row>
     <row r="265">
-      <c r="A265" s="43"/>
-      <c r="B265" s="43"/>
+      <c r="A265" s="44"/>
+      <c r="B265" s="44"/>
     </row>
     <row r="266">
-      <c r="A266" s="43"/>
-      <c r="B266" s="43"/>
+      <c r="A266" s="44"/>
+      <c r="B266" s="44"/>
     </row>
     <row r="267">
-      <c r="A267" s="43"/>
-      <c r="B267" s="43"/>
+      <c r="A267" s="44"/>
+      <c r="B267" s="44"/>
     </row>
     <row r="268">
-      <c r="A268" s="43"/>
-      <c r="B268" s="43"/>
+      <c r="A268" s="44"/>
+      <c r="B268" s="44"/>
     </row>
     <row r="269">
-      <c r="A269" s="43"/>
-      <c r="B269" s="43"/>
+      <c r="A269" s="44"/>
+      <c r="B269" s="44"/>
     </row>
     <row r="270">
-      <c r="A270" s="43"/>
-      <c r="B270" s="43"/>
+      <c r="A270" s="44"/>
+      <c r="B270" s="44"/>
     </row>
     <row r="271">
-      <c r="A271" s="43"/>
-      <c r="B271" s="43"/>
+      <c r="A271" s="44"/>
+      <c r="B271" s="44"/>
     </row>
     <row r="272">
-      <c r="A272" s="43"/>
-      <c r="B272" s="43"/>
+      <c r="A272" s="44"/>
+      <c r="B272" s="44"/>
     </row>
     <row r="273">
-      <c r="A273" s="43"/>
-      <c r="B273" s="43"/>
+      <c r="A273" s="44"/>
+      <c r="B273" s="44"/>
     </row>
     <row r="274">
-      <c r="A274" s="43"/>
-      <c r="B274" s="43"/>
+      <c r="A274" s="44"/>
+      <c r="B274" s="44"/>
     </row>
     <row r="275">
-      <c r="A275" s="43"/>
-      <c r="B275" s="43"/>
+      <c r="A275" s="44"/>
+      <c r="B275" s="44"/>
     </row>
     <row r="276">
-      <c r="A276" s="43"/>
-      <c r="B276" s="43"/>
+      <c r="A276" s="44"/>
+      <c r="B276" s="44"/>
     </row>
     <row r="277">
-      <c r="A277" s="43"/>
-      <c r="B277" s="43"/>
+      <c r="A277" s="44"/>
+      <c r="B277" s="44"/>
     </row>
     <row r="278">
-      <c r="A278" s="43"/>
-      <c r="B278" s="43"/>
+      <c r="A278" s="44"/>
+      <c r="B278" s="44"/>
     </row>
     <row r="279">
-      <c r="A279" s="43"/>
-      <c r="B279" s="43"/>
+      <c r="A279" s="44"/>
+      <c r="B279" s="44"/>
     </row>
     <row r="280">
-      <c r="A280" s="43"/>
-      <c r="B280" s="43"/>
+      <c r="A280" s="44"/>
+      <c r="B280" s="44"/>
     </row>
     <row r="281">
-      <c r="A281" s="43"/>
-      <c r="B281" s="43"/>
+      <c r="A281" s="44"/>
+      <c r="B281" s="44"/>
     </row>
     <row r="282">
-      <c r="A282" s="43"/>
-      <c r="B282" s="43"/>
+      <c r="A282" s="44"/>
+      <c r="B282" s="44"/>
     </row>
     <row r="283">
-      <c r="A283" s="43"/>
-      <c r="B283" s="43"/>
+      <c r="A283" s="44"/>
+      <c r="B283" s="44"/>
     </row>
     <row r="284">
-      <c r="A284" s="43"/>
-      <c r="B284" s="43"/>
+      <c r="A284" s="44"/>
+      <c r="B284" s="44"/>
     </row>
     <row r="285">
-      <c r="A285" s="43"/>
-      <c r="B285" s="43"/>
+      <c r="A285" s="44"/>
+      <c r="B285" s="44"/>
     </row>
     <row r="286">
-      <c r="A286" s="43"/>
-      <c r="B286" s="43"/>
+      <c r="A286" s="44"/>
+      <c r="B286" s="44"/>
     </row>
     <row r="287">
-      <c r="A287" s="43"/>
-      <c r="B287" s="43"/>
+      <c r="A287" s="44"/>
+      <c r="B287" s="44"/>
     </row>
     <row r="288">
-      <c r="A288" s="43"/>
-      <c r="B288" s="43"/>
+      <c r="A288" s="44"/>
+      <c r="B288" s="44"/>
     </row>
     <row r="289">
-      <c r="A289" s="43"/>
-      <c r="B289" s="43"/>
+      <c r="A289" s="44"/>
+      <c r="B289" s="44"/>
     </row>
     <row r="290">
-      <c r="A290" s="43"/>
-      <c r="B290" s="43"/>
+      <c r="A290" s="44"/>
+      <c r="B290" s="44"/>
     </row>
     <row r="291">
-      <c r="A291" s="43"/>
-      <c r="B291" s="43"/>
+      <c r="A291" s="44"/>
+      <c r="B291" s="44"/>
     </row>
     <row r="292">
-      <c r="A292" s="43"/>
-      <c r="B292" s="43"/>
+      <c r="A292" s="44"/>
+      <c r="B292" s="44"/>
     </row>
     <row r="293">
-      <c r="A293" s="43"/>
-      <c r="B293" s="43"/>
+      <c r="A293" s="44"/>
+      <c r="B293" s="44"/>
     </row>
     <row r="294">
-      <c r="A294" s="43"/>
-      <c r="B294" s="43"/>
+      <c r="A294" s="44"/>
+      <c r="B294" s="44"/>
     </row>
     <row r="295">
-      <c r="A295" s="43"/>
-      <c r="B295" s="43"/>
+      <c r="A295" s="44"/>
+      <c r="B295" s="44"/>
     </row>
     <row r="296">
-      <c r="A296" s="43"/>
-      <c r="B296" s="43"/>
+      <c r="A296" s="44"/>
+      <c r="B296" s="44"/>
     </row>
     <row r="297">
-      <c r="A297" s="43"/>
-      <c r="B297" s="43"/>
+      <c r="A297" s="44"/>
+      <c r="B297" s="44"/>
     </row>
     <row r="298">
-      <c r="A298" s="43"/>
-      <c r="B298" s="43"/>
+      <c r="A298" s="44"/>
+      <c r="B298" s="44"/>
     </row>
     <row r="299">
-      <c r="A299" s="43"/>
-      <c r="B299" s="43"/>
+      <c r="A299" s="44"/>
+      <c r="B299" s="44"/>
     </row>
     <row r="300">
-      <c r="A300" s="43"/>
-      <c r="B300" s="43"/>
+      <c r="A300" s="44"/>
+      <c r="B300" s="44"/>
     </row>
     <row r="301">
-      <c r="A301" s="43"/>
-      <c r="B301" s="43"/>
+      <c r="A301" s="44"/>
+      <c r="B301" s="44"/>
     </row>
     <row r="302">
-      <c r="A302" s="43"/>
-      <c r="B302" s="43"/>
+      <c r="A302" s="44"/>
+      <c r="B302" s="44"/>
     </row>
     <row r="303">
-      <c r="A303" s="43"/>
-      <c r="B303" s="43"/>
+      <c r="A303" s="44"/>
+      <c r="B303" s="44"/>
     </row>
     <row r="304">
-      <c r="A304" s="43"/>
-      <c r="B304" s="43"/>
+      <c r="A304" s="44"/>
+      <c r="B304" s="44"/>
     </row>
     <row r="305">
-      <c r="A305" s="43"/>
-      <c r="B305" s="43"/>
+      <c r="A305" s="44"/>
+      <c r="B305" s="44"/>
     </row>
     <row r="306">
-      <c r="A306" s="43"/>
-      <c r="B306" s="43"/>
+      <c r="A306" s="44"/>
+      <c r="B306" s="44"/>
     </row>
     <row r="307">
-      <c r="A307" s="43"/>
-      <c r="B307" s="43"/>
+      <c r="A307" s="44"/>
+      <c r="B307" s="44"/>
     </row>
     <row r="308">
-      <c r="A308" s="43"/>
-      <c r="B308" s="43"/>
+      <c r="A308" s="44"/>
+      <c r="B308" s="44"/>
     </row>
     <row r="309">
-      <c r="A309" s="43"/>
-      <c r="B309" s="43"/>
+      <c r="A309" s="44"/>
+      <c r="B309" s="44"/>
     </row>
     <row r="310">
-      <c r="A310" s="43"/>
-      <c r="B310" s="43"/>
+      <c r="A310" s="44"/>
+      <c r="B310" s="44"/>
     </row>
     <row r="311">
-      <c r="A311" s="43"/>
-      <c r="B311" s="43"/>
+      <c r="A311" s="44"/>
+      <c r="B311" s="44"/>
     </row>
     <row r="312">
-      <c r="A312" s="43"/>
-      <c r="B312" s="43"/>
+      <c r="A312" s="44"/>
+      <c r="B312" s="44"/>
     </row>
     <row r="313">
-      <c r="A313" s="43"/>
-      <c r="B313" s="43"/>
+      <c r="A313" s="44"/>
+      <c r="B313" s="44"/>
     </row>
     <row r="314">
-      <c r="A314" s="43"/>
-      <c r="B314" s="43"/>
+      <c r="A314" s="44"/>
+      <c r="B314" s="44"/>
     </row>
     <row r="315">
-      <c r="A315" s="43"/>
-      <c r="B315" s="43"/>
+      <c r="A315" s="44"/>
+      <c r="B315" s="44"/>
     </row>
     <row r="316">
-      <c r="A316" s="43"/>
-      <c r="B316" s="43"/>
+      <c r="A316" s="44"/>
+      <c r="B316" s="44"/>
     </row>
     <row r="317">
-      <c r="A317" s="43"/>
-      <c r="B317" s="43"/>
+      <c r="A317" s="44"/>
+      <c r="B317" s="44"/>
     </row>
     <row r="318">
-      <c r="A318" s="43"/>
-      <c r="B318" s="43"/>
+      <c r="A318" s="44"/>
+      <c r="B318" s="44"/>
     </row>
     <row r="319">
-      <c r="A319" s="43"/>
-      <c r="B319" s="43"/>
+      <c r="A319" s="44"/>
+      <c r="B319" s="44"/>
     </row>
     <row r="320">
-      <c r="A320" s="43"/>
-      <c r="B320" s="43"/>
+      <c r="A320" s="44"/>
+      <c r="B320" s="44"/>
     </row>
     <row r="321">
-      <c r="A321" s="43"/>
-      <c r="B321" s="43"/>
+      <c r="A321" s="44"/>
+      <c r="B321" s="44"/>
     </row>
     <row r="322">
-      <c r="A322" s="43"/>
-      <c r="B322" s="43"/>
+      <c r="A322" s="44"/>
+      <c r="B322" s="44"/>
     </row>
     <row r="323">
-      <c r="A323" s="43"/>
-      <c r="B323" s="43"/>
+      <c r="A323" s="44"/>
+      <c r="B323" s="44"/>
     </row>
     <row r="324">
-      <c r="A324" s="43"/>
-      <c r="B324" s="43"/>
+      <c r="A324" s="44"/>
+      <c r="B324" s="44"/>
     </row>
     <row r="325">
-      <c r="A325" s="43"/>
-      <c r="B325" s="43"/>
+      <c r="A325" s="44"/>
+      <c r="B325" s="44"/>
     </row>
     <row r="326">
-      <c r="A326" s="43"/>
-      <c r="B326" s="43"/>
+      <c r="A326" s="44"/>
+      <c r="B326" s="44"/>
     </row>
     <row r="327">
-      <c r="A327" s="43"/>
-      <c r="B327" s="43"/>
+      <c r="A327" s="44"/>
+      <c r="B327" s="44"/>
     </row>
     <row r="328">
-      <c r="A328" s="43"/>
-      <c r="B328" s="43"/>
+      <c r="A328" s="44"/>
+      <c r="B328" s="44"/>
     </row>
     <row r="329">
-      <c r="A329" s="43"/>
-      <c r="B329" s="43"/>
+      <c r="A329" s="44"/>
+      <c r="B329" s="44"/>
     </row>
     <row r="330">
-      <c r="A330" s="43"/>
-      <c r="B330" s="43"/>
+      <c r="A330" s="44"/>
+      <c r="B330" s="44"/>
     </row>
     <row r="331">
-      <c r="A331" s="43"/>
-      <c r="B331" s="43"/>
+      <c r="A331" s="44"/>
+      <c r="B331" s="44"/>
     </row>
     <row r="332">
-      <c r="A332" s="43"/>
-      <c r="B332" s="43"/>
+      <c r="A332" s="44"/>
+      <c r="B332" s="44"/>
     </row>
     <row r="333">
-      <c r="A333" s="43"/>
-      <c r="B333" s="43"/>
+      <c r="A333" s="44"/>
+      <c r="B333" s="44"/>
     </row>
     <row r="334">
-      <c r="A334" s="43"/>
-      <c r="B334" s="43"/>
+      <c r="A334" s="44"/>
+      <c r="B334" s="44"/>
     </row>
     <row r="335">
-      <c r="A335" s="43"/>
-      <c r="B335" s="43"/>
+      <c r="A335" s="44"/>
+      <c r="B335" s="44"/>
     </row>
     <row r="336">
-      <c r="A336" s="43"/>
-      <c r="B336" s="43"/>
+      <c r="A336" s="44"/>
+      <c r="B336" s="44"/>
     </row>
     <row r="337">
-      <c r="A337" s="43"/>
-      <c r="B337" s="43"/>
+      <c r="A337" s="44"/>
+      <c r="B337" s="44"/>
     </row>
     <row r="338">
-      <c r="A338" s="43"/>
-      <c r="B338" s="43"/>
+      <c r="A338" s="44"/>
+      <c r="B338" s="44"/>
     </row>
     <row r="339">
-      <c r="A339" s="43"/>
-      <c r="B339" s="43"/>
+      <c r="A339" s="44"/>
+      <c r="B339" s="44"/>
     </row>
     <row r="340">
-      <c r="A340" s="43"/>
-      <c r="B340" s="43"/>
+      <c r="A340" s="44"/>
+      <c r="B340" s="44"/>
     </row>
     <row r="341">
-      <c r="A341" s="43"/>
-      <c r="B341" s="43"/>
+      <c r="A341" s="44"/>
+      <c r="B341" s="44"/>
     </row>
     <row r="342">
-      <c r="A342" s="43"/>
-      <c r="B342" s="43"/>
+      <c r="A342" s="44"/>
+      <c r="B342" s="44"/>
     </row>
     <row r="343">
-      <c r="A343" s="43"/>
-      <c r="B343" s="43"/>
+      <c r="A343" s="44"/>
+      <c r="B343" s="44"/>
     </row>
     <row r="344">
-      <c r="A344" s="43"/>
-      <c r="B344" s="43"/>
+      <c r="A344" s="44"/>
+      <c r="B344" s="44"/>
     </row>
     <row r="345">
-      <c r="A345" s="43"/>
-      <c r="B345" s="43"/>
+      <c r="A345" s="44"/>
+      <c r="B345" s="44"/>
     </row>
     <row r="346">
-      <c r="A346" s="43"/>
-      <c r="B346" s="43"/>
+      <c r="A346" s="44"/>
+      <c r="B346" s="44"/>
     </row>
     <row r="347">
-      <c r="A347" s="43"/>
-      <c r="B347" s="43"/>
+      <c r="A347" s="44"/>
+      <c r="B347" s="44"/>
     </row>
     <row r="348">
-      <c r="A348" s="43"/>
-      <c r="B348" s="43"/>
+      <c r="A348" s="44"/>
+      <c r="B348" s="44"/>
     </row>
     <row r="349">
-      <c r="A349" s="43"/>
-      <c r="B349" s="43"/>
+      <c r="A349" s="44"/>
+      <c r="B349" s="44"/>
     </row>
     <row r="350">
-      <c r="A350" s="43"/>
-      <c r="B350" s="43"/>
+      <c r="A350" s="44"/>
+      <c r="B350" s="44"/>
     </row>
     <row r="351">
-      <c r="A351" s="43"/>
-      <c r="B351" s="43"/>
+      <c r="A351" s="44"/>
+      <c r="B351" s="44"/>
     </row>
     <row r="352">
-      <c r="A352" s="43"/>
-      <c r="B352" s="43"/>
+      <c r="A352" s="44"/>
+      <c r="B352" s="44"/>
     </row>
     <row r="353">
-      <c r="A353" s="43"/>
-      <c r="B353" s="43"/>
+      <c r="A353" s="44"/>
+      <c r="B353" s="44"/>
     </row>
     <row r="354">
-      <c r="A354" s="43"/>
-      <c r="B354" s="43"/>
+      <c r="A354" s="44"/>
+      <c r="B354" s="44"/>
     </row>
     <row r="355">
-      <c r="A355" s="43"/>
-      <c r="B355" s="43"/>
+      <c r="A355" s="44"/>
+      <c r="B355" s="44"/>
     </row>
     <row r="356">
-      <c r="A356" s="43"/>
-      <c r="B356" s="43"/>
+      <c r="A356" s="44"/>
+      <c r="B356" s="44"/>
     </row>
     <row r="357">
-      <c r="A357" s="43"/>
-      <c r="B357" s="43"/>
+      <c r="A357" s="44"/>
+      <c r="B357" s="44"/>
     </row>
     <row r="358">
-      <c r="A358" s="43"/>
-      <c r="B358" s="43"/>
+      <c r="A358" s="44"/>
+      <c r="B358" s="44"/>
     </row>
     <row r="359">
-      <c r="A359" s="43"/>
-      <c r="B359" s="43"/>
+      <c r="A359" s="44"/>
+      <c r="B359" s="44"/>
     </row>
     <row r="360">
-      <c r="A360" s="43"/>
-      <c r="B360" s="43"/>
+      <c r="A360" s="44"/>
+      <c r="B360" s="44"/>
     </row>
     <row r="361">
-      <c r="A361" s="43"/>
-      <c r="B361" s="43"/>
+      <c r="A361" s="44"/>
+      <c r="B361" s="44"/>
     </row>
     <row r="362">
-      <c r="A362" s="43"/>
-      <c r="B362" s="43"/>
+      <c r="A362" s="44"/>
+      <c r="B362" s="44"/>
     </row>
     <row r="363">
-      <c r="A363" s="43"/>
-      <c r="B363" s="43"/>
+      <c r="A363" s="44"/>
+      <c r="B363" s="44"/>
     </row>
     <row r="364">
-      <c r="A364" s="43"/>
-      <c r="B364" s="43"/>
+      <c r="A364" s="44"/>
+      <c r="B364" s="44"/>
     </row>
     <row r="365">
-      <c r="A365" s="43"/>
-      <c r="B365" s="43"/>
+      <c r="A365" s="44"/>
+      <c r="B365" s="44"/>
     </row>
     <row r="366">
-      <c r="A366" s="43"/>
-      <c r="B366" s="43"/>
+      <c r="A366" s="44"/>
+      <c r="B366" s="44"/>
     </row>
     <row r="367">
-      <c r="A367" s="43"/>
-      <c r="B367" s="43"/>
+      <c r="A367" s="44"/>
+      <c r="B367" s="44"/>
     </row>
     <row r="368">
-      <c r="A368" s="43"/>
-      <c r="B368" s="43"/>
+      <c r="A368" s="44"/>
+      <c r="B368" s="44"/>
     </row>
     <row r="369">
-      <c r="A369" s="43"/>
-      <c r="B369" s="43"/>
+      <c r="A369" s="44"/>
+      <c r="B369" s="44"/>
     </row>
     <row r="370">
-      <c r="A370" s="43"/>
-      <c r="B370" s="43"/>
+      <c r="A370" s="44"/>
+      <c r="B370" s="44"/>
     </row>
     <row r="371">
-      <c r="A371" s="43"/>
-      <c r="B371" s="43"/>
+      <c r="A371" s="44"/>
+      <c r="B371" s="44"/>
     </row>
     <row r="372">
-      <c r="A372" s="43"/>
-      <c r="B372" s="43"/>
+      <c r="A372" s="44"/>
+      <c r="B372" s="44"/>
     </row>
     <row r="373">
-      <c r="A373" s="43"/>
-      <c r="B373" s="43"/>
+      <c r="A373" s="44"/>
+      <c r="B373" s="44"/>
     </row>
     <row r="374">
-      <c r="A374" s="43"/>
-      <c r="B374" s="43"/>
+      <c r="A374" s="44"/>
+      <c r="B374" s="44"/>
     </row>
     <row r="375">
-      <c r="A375" s="43"/>
-      <c r="B375" s="43"/>
+      <c r="A375" s="44"/>
+      <c r="B375" s="44"/>
     </row>
     <row r="376">
-      <c r="A376" s="43"/>
-      <c r="B376" s="43"/>
+      <c r="A376" s="44"/>
+      <c r="B376" s="44"/>
     </row>
     <row r="377">
-      <c r="A377" s="43"/>
-      <c r="B377" s="43"/>
+      <c r="A377" s="44"/>
+      <c r="B377" s="44"/>
     </row>
     <row r="378">
-      <c r="A378" s="43"/>
-      <c r="B378" s="43"/>
+      <c r="A378" s="44"/>
+      <c r="B378" s="44"/>
     </row>
     <row r="379">
-      <c r="A379" s="43"/>
-      <c r="B379" s="43"/>
+      <c r="A379" s="44"/>
+      <c r="B379" s="44"/>
     </row>
     <row r="380">
-      <c r="A380" s="43"/>
-      <c r="B380" s="43"/>
+      <c r="A380" s="44"/>
+      <c r="B380" s="44"/>
     </row>
     <row r="381">
-      <c r="A381" s="43"/>
-      <c r="B381" s="43"/>
+      <c r="A381" s="44"/>
+      <c r="B381" s="44"/>
     </row>
     <row r="382">
-      <c r="A382" s="43"/>
-      <c r="B382" s="43"/>
+      <c r="A382" s="44"/>
+      <c r="B382" s="44"/>
     </row>
     <row r="383">
-      <c r="A383" s="43"/>
-      <c r="B383" s="43"/>
+      <c r="A383" s="44"/>
+      <c r="B383" s="44"/>
     </row>
     <row r="384">
-      <c r="A384" s="43"/>
-      <c r="B384" s="43"/>
+      <c r="A384" s="44"/>
+      <c r="B384" s="44"/>
     </row>
     <row r="385">
-      <c r="A385" s="43"/>
-      <c r="B385" s="43"/>
+      <c r="A385" s="44"/>
+      <c r="B385" s="44"/>
     </row>
     <row r="386">
-      <c r="A386" s="43"/>
-      <c r="B386" s="43"/>
+      <c r="A386" s="44"/>
+      <c r="B386" s="44"/>
     </row>
     <row r="387">
-      <c r="A387" s="43"/>
-      <c r="B387" s="43"/>
+      <c r="A387" s="44"/>
+      <c r="B387" s="44"/>
     </row>
     <row r="388">
-      <c r="A388" s="43"/>
-      <c r="B388" s="43"/>
+      <c r="A388" s="44"/>
+      <c r="B388" s="44"/>
     </row>
     <row r="389">
-      <c r="A389" s="43"/>
-      <c r="B389" s="43"/>
+      <c r="A389" s="44"/>
+      <c r="B389" s="44"/>
     </row>
     <row r="390">
-      <c r="A390" s="43"/>
-      <c r="B390" s="43"/>
+      <c r="A390" s="44"/>
+      <c r="B390" s="44"/>
     </row>
     <row r="391">
-      <c r="A391" s="43"/>
-      <c r="B391" s="43"/>
+      <c r="A391" s="44"/>
+      <c r="B391" s="44"/>
     </row>
     <row r="392">
-      <c r="A392" s="43"/>
-      <c r="B392" s="43"/>
+      <c r="A392" s="44"/>
+      <c r="B392" s="44"/>
     </row>
     <row r="393">
-      <c r="A393" s="43"/>
-      <c r="B393" s="43"/>
+      <c r="A393" s="44"/>
+      <c r="B393" s="44"/>
     </row>
     <row r="394">
-      <c r="A394" s="43"/>
-      <c r="B394" s="43"/>
+      <c r="A394" s="44"/>
+      <c r="B394" s="44"/>
     </row>
     <row r="395">
-      <c r="A395" s="43"/>
-      <c r="B395" s="43"/>
+      <c r="A395" s="44"/>
+      <c r="B395" s="44"/>
     </row>
     <row r="396">
-      <c r="A396" s="43"/>
-      <c r="B396" s="43"/>
+      <c r="A396" s="44"/>
+      <c r="B396" s="44"/>
     </row>
     <row r="397">
-      <c r="A397" s="43"/>
-      <c r="B397" s="43"/>
+      <c r="A397" s="44"/>
+      <c r="B397" s="44"/>
     </row>
     <row r="398">
-      <c r="A398" s="43"/>
-      <c r="B398" s="43"/>
+      <c r="A398" s="44"/>
+      <c r="B398" s="44"/>
     </row>
     <row r="399">
-      <c r="A399" s="43"/>
-      <c r="B399" s="43"/>
+      <c r="A399" s="44"/>
+      <c r="B399" s="44"/>
     </row>
     <row r="400">
-      <c r="A400" s="43"/>
-      <c r="B400" s="43"/>
+      <c r="A400" s="44"/>
+      <c r="B400" s="44"/>
     </row>
     <row r="401">
-      <c r="A401" s="43"/>
-      <c r="B401" s="43"/>
+      <c r="A401" s="44"/>
+      <c r="B401" s="44"/>
     </row>
     <row r="402">
-      <c r="A402" s="43"/>
-      <c r="B402" s="43"/>
+      <c r="A402" s="44"/>
+      <c r="B402" s="44"/>
     </row>
     <row r="403">
-      <c r="A403" s="43"/>
-      <c r="B403" s="43"/>
+      <c r="A403" s="44"/>
+      <c r="B403" s="44"/>
     </row>
     <row r="404">
-      <c r="A404" s="43"/>
-      <c r="B404" s="43"/>
+      <c r="A404" s="44"/>
+      <c r="B404" s="44"/>
     </row>
     <row r="405">
-      <c r="A405" s="43"/>
-      <c r="B405" s="43"/>
+      <c r="A405" s="44"/>
+      <c r="B405" s="44"/>
     </row>
     <row r="406">
-      <c r="A406" s="43"/>
-      <c r="B406" s="43"/>
+      <c r="A406" s="44"/>
+      <c r="B406" s="44"/>
     </row>
     <row r="407">
-      <c r="A407" s="43"/>
-      <c r="B407" s="43"/>
+      <c r="A407" s="44"/>
+      <c r="B407" s="44"/>
     </row>
     <row r="408">
-      <c r="A408" s="43"/>
-      <c r="B408" s="43"/>
+      <c r="A408" s="44"/>
+      <c r="B408" s="44"/>
     </row>
     <row r="409">
-      <c r="A409" s="43"/>
-      <c r="B409" s="43"/>
+      <c r="A409" s="44"/>
+      <c r="B409" s="44"/>
     </row>
     <row r="410">
-      <c r="A410" s="43"/>
-      <c r="B410" s="43"/>
+      <c r="A410" s="44"/>
+      <c r="B410" s="44"/>
     </row>
     <row r="411">
-      <c r="A411" s="43"/>
-      <c r="B411" s="43"/>
+      <c r="A411" s="44"/>
+      <c r="B411" s="44"/>
     </row>
     <row r="412">
-      <c r="A412" s="43"/>
-      <c r="B412" s="43"/>
+      <c r="A412" s="44"/>
+      <c r="B412" s="44"/>
     </row>
     <row r="413">
-      <c r="A413" s="43"/>
-      <c r="B413" s="43"/>
+      <c r="A413" s="44"/>
+      <c r="B413" s="44"/>
     </row>
     <row r="414">
-      <c r="A414" s="43"/>
-      <c r="B414" s="43"/>
+      <c r="A414" s="44"/>
+      <c r="B414" s="44"/>
     </row>
     <row r="415">
-      <c r="A415" s="43"/>
-      <c r="B415" s="43"/>
+      <c r="A415" s="44"/>
+      <c r="B415" s="44"/>
     </row>
     <row r="416">
-      <c r="A416" s="43"/>
-      <c r="B416" s="43"/>
+      <c r="A416" s="44"/>
+      <c r="B416" s="44"/>
     </row>
     <row r="417">
-      <c r="A417" s="43"/>
-      <c r="B417" s="43"/>
+      <c r="A417" s="44"/>
+      <c r="B417" s="44"/>
     </row>
     <row r="418">
-      <c r="A418" s="43"/>
-      <c r="B418" s="43"/>
+      <c r="A418" s="44"/>
+      <c r="B418" s="44"/>
     </row>
     <row r="419">
-      <c r="A419" s="43"/>
-      <c r="B419" s="43"/>
+      <c r="A419" s="44"/>
+      <c r="B419" s="44"/>
     </row>
     <row r="420">
-      <c r="A420" s="43"/>
-      <c r="B420" s="43"/>
+      <c r="A420" s="44"/>
+      <c r="B420" s="44"/>
     </row>
     <row r="421">
-      <c r="A421" s="43"/>
-      <c r="B421" s="43"/>
+      <c r="A421" s="44"/>
+      <c r="B421" s="44"/>
     </row>
     <row r="422">
-      <c r="A422" s="43"/>
-      <c r="B422" s="43"/>
+      <c r="A422" s="44"/>
+      <c r="B422" s="44"/>
     </row>
     <row r="423">
-      <c r="A423" s="43"/>
-      <c r="B423" s="43"/>
+      <c r="A423" s="44"/>
+      <c r="B423" s="44"/>
     </row>
     <row r="424">
-      <c r="A424" s="43"/>
-      <c r="B424" s="43"/>
+      <c r="A424" s="44"/>
+      <c r="B424" s="44"/>
     </row>
     <row r="425">
-      <c r="A425" s="43"/>
-      <c r="B425" s="43"/>
+      <c r="A425" s="44"/>
+      <c r="B425" s="44"/>
     </row>
     <row r="426">
-      <c r="A426" s="43"/>
-      <c r="B426" s="43"/>
+      <c r="A426" s="44"/>
+      <c r="B426" s="44"/>
     </row>
     <row r="427">
-      <c r="A427" s="43"/>
-      <c r="B427" s="43"/>
+      <c r="A427" s="44"/>
+      <c r="B427" s="44"/>
     </row>
     <row r="428">
-      <c r="A428" s="43"/>
-      <c r="B428" s="43"/>
+      <c r="A428" s="44"/>
+      <c r="B428" s="44"/>
     </row>
     <row r="429">
-      <c r="A429" s="43"/>
-      <c r="B429" s="43"/>
+      <c r="A429" s="44"/>
+      <c r="B429" s="44"/>
     </row>
     <row r="430">
-      <c r="A430" s="43"/>
-      <c r="B430" s="43"/>
+      <c r="A430" s="44"/>
+      <c r="B430" s="44"/>
     </row>
     <row r="431">
-      <c r="A431" s="43"/>
-      <c r="B431" s="43"/>
+      <c r="A431" s="44"/>
+      <c r="B431" s="44"/>
     </row>
     <row r="432">
-      <c r="A432" s="43"/>
-      <c r="B432" s="43"/>
+      <c r="A432" s="44"/>
+      <c r="B432" s="44"/>
     </row>
     <row r="433">
-      <c r="A433" s="43"/>
-      <c r="B433" s="43"/>
+      <c r="A433" s="44"/>
+      <c r="B433" s="44"/>
     </row>
     <row r="434">
-      <c r="A434" s="43"/>
-      <c r="B434" s="43"/>
+      <c r="A434" s="44"/>
+      <c r="B434" s="44"/>
     </row>
     <row r="435">
-      <c r="A435" s="43"/>
-      <c r="B435" s="43"/>
+      <c r="A435" s="44"/>
+      <c r="B435" s="44"/>
     </row>
     <row r="436">
-      <c r="A436" s="43"/>
-      <c r="B436" s="43"/>
+      <c r="A436" s="44"/>
+      <c r="B436" s="44"/>
     </row>
     <row r="437">
-      <c r="A437" s="43"/>
-      <c r="B437" s="43"/>
+      <c r="A437" s="44"/>
+      <c r="B437" s="44"/>
     </row>
     <row r="438">
-      <c r="A438" s="43"/>
-      <c r="B438" s="43"/>
+      <c r="A438" s="44"/>
+      <c r="B438" s="44"/>
     </row>
     <row r="439">
-      <c r="A439" s="43"/>
-      <c r="B439" s="43"/>
+      <c r="A439" s="44"/>
+      <c r="B439" s="44"/>
     </row>
     <row r="440">
-      <c r="A440" s="43"/>
-      <c r="B440" s="43"/>
+      <c r="A440" s="44"/>
+      <c r="B440" s="44"/>
     </row>
     <row r="441">
-      <c r="A441" s="43"/>
-      <c r="B441" s="43"/>
+      <c r="A441" s="44"/>
+      <c r="B441" s="44"/>
     </row>
     <row r="442">
-      <c r="A442" s="43"/>
-      <c r="B442" s="43"/>
+      <c r="A442" s="44"/>
+      <c r="B442" s="44"/>
     </row>
     <row r="443">
-      <c r="A443" s="43"/>
-      <c r="B443" s="43"/>
+      <c r="A443" s="44"/>
+      <c r="B443" s="44"/>
     </row>
     <row r="444">
-      <c r="A444" s="43"/>
-      <c r="B444" s="43"/>
+      <c r="A444" s="44"/>
+      <c r="B444" s="44"/>
     </row>
     <row r="445">
-      <c r="A445" s="43"/>
-      <c r="B445" s="43"/>
+      <c r="A445" s="44"/>
+      <c r="B445" s="44"/>
     </row>
     <row r="446">
-      <c r="A446" s="43"/>
-      <c r="B446" s="43"/>
+      <c r="A446" s="44"/>
+      <c r="B446" s="44"/>
     </row>
     <row r="447">
-      <c r="A447" s="43"/>
-      <c r="B447" s="43"/>
+      <c r="A447" s="44"/>
+      <c r="B447" s="44"/>
     </row>
     <row r="448">
-      <c r="A448" s="43"/>
-      <c r="B448" s="43"/>
+      <c r="A448" s="44"/>
+      <c r="B448" s="44"/>
     </row>
     <row r="449">
-      <c r="A449" s="43"/>
-      <c r="B449" s="43"/>
+      <c r="A449" s="44"/>
+      <c r="B449" s="44"/>
     </row>
     <row r="450">
-      <c r="A450" s="43"/>
-      <c r="B450" s="43"/>
+      <c r="A450" s="44"/>
+      <c r="B450" s="44"/>
     </row>
     <row r="451">
-      <c r="A451" s="43"/>
-      <c r="B451" s="43"/>
+      <c r="A451" s="44"/>
+      <c r="B451" s="44"/>
     </row>
     <row r="452">
-      <c r="A452" s="43"/>
-      <c r="B452" s="43"/>
+      <c r="A452" s="44"/>
+      <c r="B452" s="44"/>
     </row>
     <row r="453">
-      <c r="A453" s="43"/>
-      <c r="B453" s="43"/>
+      <c r="A453" s="44"/>
+      <c r="B453" s="44"/>
     </row>
     <row r="454">
-      <c r="A454" s="43"/>
-      <c r="B454" s="43"/>
+      <c r="A454" s="44"/>
+      <c r="B454" s="44"/>
     </row>
     <row r="455">
-      <c r="A455" s="43"/>
-      <c r="B455" s="43"/>
+      <c r="A455" s="44"/>
+      <c r="B455" s="44"/>
     </row>
     <row r="456">
-      <c r="A456" s="43"/>
-      <c r="B456" s="43"/>
+      <c r="A456" s="44"/>
+      <c r="B456" s="44"/>
     </row>
     <row r="457">
-      <c r="A457" s="43"/>
-      <c r="B457" s="43"/>
+      <c r="A457" s="44"/>
+      <c r="B457" s="44"/>
     </row>
     <row r="458">
-      <c r="A458" s="43"/>
-      <c r="B458" s="43"/>
+      <c r="A458" s="44"/>
+      <c r="B458" s="44"/>
     </row>
     <row r="459">
-      <c r="A459" s="43"/>
-      <c r="B459" s="43"/>
+      <c r="A459" s="44"/>
+      <c r="B459" s="44"/>
     </row>
     <row r="460">
-      <c r="A460" s="43"/>
-      <c r="B460" s="43"/>
+      <c r="A460" s="44"/>
+      <c r="B460" s="44"/>
     </row>
     <row r="461">
-      <c r="A461" s="43"/>
-      <c r="B461" s="43"/>
+      <c r="A461" s="44"/>
+      <c r="B461" s="44"/>
     </row>
     <row r="462">
-      <c r="A462" s="43"/>
-      <c r="B462" s="43"/>
+      <c r="A462" s="44"/>
+      <c r="B462" s="44"/>
     </row>
     <row r="463">
-      <c r="A463" s="43"/>
-      <c r="B463" s="43"/>
+      <c r="A463" s="44"/>
+      <c r="B463" s="44"/>
     </row>
     <row r="464">
-      <c r="A464" s="43"/>
-      <c r="B464" s="43"/>
+      <c r="A464" s="44"/>
+      <c r="B464" s="44"/>
     </row>
     <row r="465">
-      <c r="A465" s="43"/>
-      <c r="B465" s="43"/>
+      <c r="A465" s="44"/>
+      <c r="B465" s="44"/>
     </row>
     <row r="466">
-      <c r="A466" s="43"/>
-      <c r="B466" s="43"/>
+      <c r="A466" s="44"/>
+      <c r="B466" s="44"/>
     </row>
     <row r="467">
-      <c r="A467" s="43"/>
-      <c r="B467" s="43"/>
+      <c r="A467" s="44"/>
+      <c r="B467" s="44"/>
     </row>
     <row r="468">
-      <c r="A468" s="43"/>
-      <c r="B468" s="43"/>
+      <c r="A468" s="44"/>
+      <c r="B468" s="44"/>
     </row>
     <row r="469">
-      <c r="A469" s="43"/>
-      <c r="B469" s="43"/>
+      <c r="A469" s="44"/>
+      <c r="B469" s="44"/>
     </row>
     <row r="470">
-      <c r="A470" s="43"/>
-      <c r="B470" s="43"/>
+      <c r="A470" s="44"/>
+      <c r="B470" s="44"/>
     </row>
     <row r="471">
-      <c r="A471" s="43"/>
-      <c r="B471" s="43"/>
+      <c r="A471" s="44"/>
+      <c r="B471" s="44"/>
     </row>
     <row r="472">
-      <c r="A472" s="43"/>
-      <c r="B472" s="43"/>
+      <c r="A472" s="44"/>
+      <c r="B472" s="44"/>
     </row>
     <row r="473">
-      <c r="A473" s="43"/>
-      <c r="B473" s="43"/>
+      <c r="A473" s="44"/>
+      <c r="B473" s="44"/>
     </row>
     <row r="474">
-      <c r="A474" s="43"/>
-      <c r="B474" s="43"/>
+      <c r="A474" s="44"/>
+      <c r="B474" s="44"/>
     </row>
     <row r="475">
-      <c r="A475" s="43"/>
-      <c r="B475" s="43"/>
+      <c r="A475" s="44"/>
+      <c r="B475" s="44"/>
     </row>
     <row r="476">
-      <c r="A476" s="43"/>
-      <c r="B476" s="43"/>
+      <c r="A476" s="44"/>
+      <c r="B476" s="44"/>
     </row>
     <row r="477">
-      <c r="A477" s="43"/>
-      <c r="B477" s="43"/>
+      <c r="A477" s="44"/>
+      <c r="B477" s="44"/>
     </row>
     <row r="478">
-      <c r="A478" s="43"/>
-      <c r="B478" s="43"/>
+      <c r="A478" s="44"/>
+      <c r="B478" s="44"/>
     </row>
     <row r="479">
-      <c r="A479" s="43"/>
-      <c r="B479" s="43"/>
+      <c r="A479" s="44"/>
+      <c r="B479" s="44"/>
     </row>
     <row r="480">
-      <c r="A480" s="43"/>
-      <c r="B480" s="43"/>
+      <c r="A480" s="44"/>
+      <c r="B480" s="44"/>
     </row>
     <row r="481">
-      <c r="A481" s="43"/>
-      <c r="B481" s="43"/>
+      <c r="A481" s="44"/>
+      <c r="B481" s="44"/>
     </row>
     <row r="482">
-      <c r="A482" s="43"/>
-      <c r="B482" s="43"/>
+      <c r="A482" s="44"/>
+      <c r="B482" s="44"/>
     </row>
     <row r="483">
-      <c r="A483" s="43"/>
-      <c r="B483" s="43"/>
+      <c r="A483" s="44"/>
+      <c r="B483" s="44"/>
     </row>
     <row r="484">
-      <c r="A484" s="43"/>
-      <c r="B484" s="43"/>
+      <c r="A484" s="44"/>
+      <c r="B484" s="44"/>
     </row>
     <row r="485">
-      <c r="A485" s="43"/>
-      <c r="B485" s="43"/>
+      <c r="A485" s="44"/>
+      <c r="B485" s="44"/>
     </row>
     <row r="486">
-      <c r="A486" s="43"/>
-      <c r="B486" s="43"/>
+      <c r="A486" s="44"/>
+      <c r="B486" s="44"/>
     </row>
     <row r="487">
-      <c r="A487" s="43"/>
-      <c r="B487" s="43"/>
+      <c r="A487" s="44"/>
+      <c r="B487" s="44"/>
     </row>
     <row r="488">
-      <c r="A488" s="43"/>
-      <c r="B488" s="43"/>
+      <c r="A488" s="44"/>
+      <c r="B488" s="44"/>
     </row>
     <row r="489">
-      <c r="A489" s="43"/>
-      <c r="B489" s="43"/>
+      <c r="A489" s="44"/>
+      <c r="B489" s="44"/>
     </row>
     <row r="490">
-      <c r="A490" s="43"/>
-      <c r="B490" s="43"/>
+      <c r="A490" s="44"/>
+      <c r="B490" s="44"/>
     </row>
     <row r="491">
-      <c r="A491" s="43"/>
-      <c r="B491" s="43"/>
+      <c r="A491" s="44"/>
+      <c r="B491" s="44"/>
     </row>
     <row r="492">
-      <c r="A492" s="43"/>
-      <c r="B492" s="43"/>
+      <c r="A492" s="44"/>
+      <c r="B492" s="44"/>
     </row>
     <row r="493">
-      <c r="A493" s="43"/>
-      <c r="B493" s="43"/>
+      <c r="A493" s="44"/>
+      <c r="B493" s="44"/>
     </row>
     <row r="494">
-      <c r="A494" s="43"/>
-      <c r="B494" s="43"/>
+      <c r="A494" s="44"/>
+      <c r="B494" s="44"/>
     </row>
     <row r="495">
-      <c r="A495" s="43"/>
-      <c r="B495" s="43"/>
+      <c r="A495" s="44"/>
+      <c r="B495" s="44"/>
     </row>
     <row r="496">
-      <c r="A496" s="43"/>
-      <c r="B496" s="43"/>
+      <c r="A496" s="44"/>
+      <c r="B496" s="44"/>
     </row>
     <row r="497">
-      <c r="A497" s="43"/>
-      <c r="B497" s="43"/>
+      <c r="A497" s="44"/>
+      <c r="B497" s="44"/>
     </row>
     <row r="498">
-      <c r="A498" s="43"/>
-      <c r="B498" s="43"/>
+      <c r="A498" s="44"/>
+      <c r="B498" s="44"/>
     </row>
     <row r="499">
-      <c r="A499" s="43"/>
-      <c r="B499" s="43"/>
+      <c r="A499" s="44"/>
+      <c r="B499" s="44"/>
     </row>
     <row r="500">
-      <c r="A500" s="43"/>
-      <c r="B500" s="43"/>
+      <c r="A500" s="44"/>
+      <c r="B500" s="44"/>
     </row>
     <row r="501">
-      <c r="A501" s="43"/>
-      <c r="B501" s="43"/>
+      <c r="A501" s="44"/>
+      <c r="B501" s="44"/>
     </row>
     <row r="502">
-      <c r="A502" s="43"/>
-      <c r="B502" s="43"/>
+      <c r="A502" s="44"/>
+      <c r="B502" s="44"/>
     </row>
     <row r="503">
-      <c r="A503" s="43"/>
-      <c r="B503" s="43"/>
+      <c r="A503" s="44"/>
+      <c r="B503" s="44"/>
     </row>
     <row r="504">
-      <c r="A504" s="43"/>
-      <c r="B504" s="43"/>
+      <c r="A504" s="44"/>
+      <c r="B504" s="44"/>
     </row>
     <row r="505">
-      <c r="A505" s="43"/>
-      <c r="B505" s="43"/>
+      <c r="A505" s="44"/>
+      <c r="B505" s="44"/>
     </row>
     <row r="506">
-      <c r="A506" s="43"/>
-      <c r="B506" s="43"/>
+      <c r="A506" s="44"/>
+      <c r="B506" s="44"/>
     </row>
     <row r="507">
-      <c r="A507" s="43"/>
-      <c r="B507" s="43"/>
+      <c r="A507" s="44"/>
+      <c r="B507" s="44"/>
     </row>
     <row r="508">
-      <c r="A508" s="43"/>
-      <c r="B508" s="43"/>
+      <c r="A508" s="44"/>
+      <c r="B508" s="44"/>
     </row>
     <row r="509">
-      <c r="A509" s="43"/>
-      <c r="B509" s="43"/>
+      <c r="A509" s="44"/>
+      <c r="B509" s="44"/>
     </row>
     <row r="510">
-      <c r="A510" s="43"/>
-      <c r="B510" s="43"/>
+      <c r="A510" s="44"/>
+      <c r="B510" s="44"/>
     </row>
     <row r="511">
-      <c r="A511" s="43"/>
-      <c r="B511" s="43"/>
+      <c r="A511" s="44"/>
+      <c r="B511" s="44"/>
     </row>
     <row r="512">
-      <c r="A512" s="43"/>
-      <c r="B512" s="43"/>
+      <c r="A512" s="44"/>
+      <c r="B512" s="44"/>
     </row>
     <row r="513">
-      <c r="A513" s="43"/>
-      <c r="B513" s="43"/>
+      <c r="A513" s="44"/>
+      <c r="B513" s="44"/>
     </row>
     <row r="514">
-      <c r="A514" s="43"/>
-      <c r="B514" s="43"/>
+      <c r="A514" s="44"/>
+      <c r="B514" s="44"/>
     </row>
     <row r="515">
-      <c r="A515" s="43"/>
-      <c r="B515" s="43"/>
+      <c r="A515" s="44"/>
+      <c r="B515" s="44"/>
     </row>
     <row r="516">
-      <c r="A516" s="43"/>
-      <c r="B516" s="43"/>
+      <c r="A516" s="44"/>
+      <c r="B516" s="44"/>
     </row>
     <row r="517">
-      <c r="A517" s="43"/>
-      <c r="B517" s="43"/>
+      <c r="A517" s="44"/>
+      <c r="B517" s="44"/>
     </row>
     <row r="518">
-      <c r="A518" s="43"/>
-      <c r="B518" s="43"/>
+      <c r="A518" s="44"/>
+      <c r="B518" s="44"/>
     </row>
     <row r="519">
-      <c r="A519" s="43"/>
-      <c r="B519" s="43"/>
+      <c r="A519" s="44"/>
+      <c r="B519" s="44"/>
     </row>
     <row r="520">
-      <c r="A520" s="43"/>
-      <c r="B520" s="43"/>
+      <c r="A520" s="44"/>
+      <c r="B520" s="44"/>
     </row>
     <row r="521">
-      <c r="A521" s="43"/>
-      <c r="B521" s="43"/>
+      <c r="A521" s="44"/>
+      <c r="B521" s="44"/>
     </row>
     <row r="522">
-      <c r="A522" s="43"/>
-      <c r="B522" s="43"/>
+      <c r="A522" s="44"/>
+      <c r="B522" s="44"/>
     </row>
     <row r="523">
-      <c r="A523" s="43"/>
-      <c r="B523" s="43"/>
+      <c r="A523" s="44"/>
+      <c r="B523" s="44"/>
     </row>
     <row r="524">
-      <c r="A524" s="43"/>
-      <c r="B524" s="43"/>
+      <c r="A524" s="44"/>
+      <c r="B524" s="44"/>
     </row>
     <row r="525">
-      <c r="A525" s="43"/>
-      <c r="B525" s="43"/>
+      <c r="A525" s="44"/>
+      <c r="B525" s="44"/>
     </row>
     <row r="526">
-      <c r="A526" s="43"/>
-      <c r="B526" s="43"/>
+      <c r="A526" s="44"/>
+      <c r="B526" s="44"/>
     </row>
     <row r="527">
-      <c r="A527" s="43"/>
-      <c r="B527" s="43"/>
+      <c r="A527" s="44"/>
+      <c r="B527" s="44"/>
     </row>
     <row r="528">
-      <c r="A528" s="43"/>
-      <c r="B528" s="43"/>
+      <c r="A528" s="44"/>
+      <c r="B528" s="44"/>
     </row>
     <row r="529">
-      <c r="A529" s="43"/>
-      <c r="B529" s="43"/>
+      <c r="A529" s="44"/>
+      <c r="B529" s="44"/>
     </row>
     <row r="530">
-      <c r="A530" s="43"/>
-      <c r="B530" s="43"/>
+      <c r="A530" s="44"/>
+      <c r="B530" s="44"/>
     </row>
     <row r="531">
-      <c r="A531" s="43"/>
-      <c r="B531" s="43"/>
+      <c r="A531" s="44"/>
+      <c r="B531" s="44"/>
     </row>
     <row r="532">
-      <c r="A532" s="43"/>
-      <c r="B532" s="43"/>
+      <c r="A532" s="44"/>
+      <c r="B532" s="44"/>
     </row>
     <row r="533">
-      <c r="A533" s="43"/>
-      <c r="B533" s="43"/>
+      <c r="A533" s="44"/>
+      <c r="B533" s="44"/>
     </row>
     <row r="534">
-      <c r="A534" s="43"/>
-      <c r="B534" s="43"/>
+      <c r="A534" s="44"/>
+      <c r="B534" s="44"/>
     </row>
     <row r="535">
-      <c r="A535" s="43"/>
-      <c r="B535" s="43"/>
+      <c r="A535" s="44"/>
+      <c r="B535" s="44"/>
     </row>
     <row r="536">
-      <c r="A536" s="43"/>
-      <c r="B536" s="43"/>
+      <c r="A536" s="44"/>
+      <c r="B536" s="44"/>
     </row>
     <row r="537">
-      <c r="A537" s="43"/>
-      <c r="B537" s="43"/>
+      <c r="A537" s="44"/>
+      <c r="B537" s="44"/>
     </row>
     <row r="538">
-      <c r="A538" s="43"/>
-      <c r="B538" s="43"/>
+      <c r="A538" s="44"/>
+      <c r="B538" s="44"/>
     </row>
     <row r="539">
-      <c r="A539" s="43"/>
-      <c r="B539" s="43"/>
+      <c r="A539" s="44"/>
+      <c r="B539" s="44"/>
     </row>
     <row r="540">
-      <c r="A540" s="43"/>
-      <c r="B540" s="43"/>
+      <c r="A540" s="44"/>
+      <c r="B540" s="44"/>
     </row>
     <row r="541">
-      <c r="A541" s="43"/>
-      <c r="B541" s="43"/>
+      <c r="A541" s="44"/>
+      <c r="B541" s="44"/>
     </row>
     <row r="542">
-      <c r="A542" s="43"/>
-      <c r="B542" s="43"/>
+      <c r="A542" s="44"/>
+      <c r="B542" s="44"/>
     </row>
     <row r="543">
-      <c r="A543" s="43"/>
-      <c r="B543" s="43"/>
+      <c r="A543" s="44"/>
+      <c r="B543" s="44"/>
     </row>
     <row r="544">
-      <c r="A544" s="43"/>
-      <c r="B544" s="43"/>
+      <c r="A544" s="44"/>
+      <c r="B544" s="44"/>
     </row>
     <row r="545">
-      <c r="A545" s="43"/>
-      <c r="B545" s="43"/>
+      <c r="A545" s="44"/>
+      <c r="B545" s="44"/>
     </row>
     <row r="546">
-      <c r="A546" s="43"/>
-      <c r="B546" s="43"/>
+      <c r="A546" s="44"/>
+      <c r="B546" s="44"/>
     </row>
     <row r="547">
-      <c r="A547" s="43"/>
-      <c r="B547" s="43"/>
+      <c r="A547" s="44"/>
+      <c r="B547" s="44"/>
     </row>
     <row r="548">
-      <c r="A548" s="43"/>
-      <c r="B548" s="43"/>
+      <c r="A548" s="44"/>
+      <c r="B548" s="44"/>
     </row>
     <row r="549">
-      <c r="A549" s="43"/>
-      <c r="B549" s="43"/>
+      <c r="A549" s="44"/>
+      <c r="B549" s="44"/>
     </row>
     <row r="550">
-      <c r="A550" s="43"/>
-      <c r="B550" s="43"/>
+      <c r="A550" s="44"/>
+      <c r="B550" s="44"/>
     </row>
     <row r="551">
-      <c r="A551" s="43"/>
-      <c r="B551" s="43"/>
+      <c r="A551" s="44"/>
+      <c r="B551" s="44"/>
     </row>
     <row r="552">
-      <c r="A552" s="43"/>
-      <c r="B552" s="43"/>
+      <c r="A552" s="44"/>
+      <c r="B552" s="44"/>
     </row>
     <row r="553">
-      <c r="A553" s="43"/>
-      <c r="B553" s="43"/>
+      <c r="A553" s="44"/>
+      <c r="B553" s="44"/>
     </row>
     <row r="554">
-      <c r="A554" s="43"/>
-      <c r="B554" s="43"/>
+      <c r="A554" s="44"/>
+      <c r="B554" s="44"/>
     </row>
     <row r="555">
-      <c r="A555" s="43"/>
-      <c r="B555" s="43"/>
+      <c r="A555" s="44"/>
+      <c r="B555" s="44"/>
     </row>
     <row r="556">
-      <c r="A556" s="43"/>
-      <c r="B556" s="43"/>
+      <c r="A556" s="44"/>
+      <c r="B556" s="44"/>
     </row>
     <row r="557">
-      <c r="A557" s="43"/>
-      <c r="B557" s="43"/>
+      <c r="A557" s="44"/>
+      <c r="B557" s="44"/>
     </row>
     <row r="558">
-      <c r="A558" s="43"/>
-      <c r="B558" s="43"/>
+      <c r="A558" s="44"/>
+      <c r="B558" s="44"/>
     </row>
     <row r="559">
-      <c r="A559" s="43"/>
-      <c r="B559" s="43"/>
+      <c r="A559" s="44"/>
+      <c r="B559" s="44"/>
     </row>
     <row r="560">
-      <c r="A560" s="43"/>
-      <c r="B560" s="43"/>
+      <c r="A560" s="44"/>
+      <c r="B560" s="44"/>
     </row>
     <row r="561">
-      <c r="A561" s="43"/>
-      <c r="B561" s="43"/>
+      <c r="A561" s="44"/>
+      <c r="B561" s="44"/>
     </row>
     <row r="562">
-      <c r="A562" s="43"/>
-      <c r="B562" s="43"/>
+      <c r="A562" s="44"/>
+      <c r="B562" s="44"/>
     </row>
     <row r="563">
-      <c r="A563" s="43"/>
-      <c r="B563" s="43"/>
+      <c r="A563" s="44"/>
+      <c r="B563" s="44"/>
     </row>
     <row r="564">
-      <c r="A564" s="43"/>
-      <c r="B564" s="43"/>
+      <c r="A564" s="44"/>
+      <c r="B564" s="44"/>
     </row>
     <row r="565">
-      <c r="A565" s="43"/>
-      <c r="B565" s="43"/>
+      <c r="A565" s="44"/>
+      <c r="B565" s="44"/>
     </row>
     <row r="566">
-      <c r="A566" s="43"/>
-      <c r="B566" s="43"/>
+      <c r="A566" s="44"/>
+      <c r="B566" s="44"/>
     </row>
     <row r="567">
-      <c r="A567" s="43"/>
-      <c r="B567" s="43"/>
+      <c r="A567" s="44"/>
+      <c r="B567" s="44"/>
     </row>
     <row r="568">
-      <c r="A568" s="43"/>
-      <c r="B568" s="43"/>
+      <c r="A568" s="44"/>
+      <c r="B568" s="44"/>
     </row>
     <row r="569">
-      <c r="A569" s="43"/>
-      <c r="B569" s="43"/>
+      <c r="A569" s="44"/>
+      <c r="B569" s="44"/>
     </row>
     <row r="570">
-      <c r="A570" s="43"/>
-      <c r="B570" s="43"/>
+      <c r="A570" s="44"/>
+      <c r="B570" s="44"/>
     </row>
     <row r="571">
-      <c r="A571" s="43"/>
-      <c r="B571" s="43"/>
+      <c r="A571" s="44"/>
+      <c r="B571" s="44"/>
     </row>
     <row r="572">
-      <c r="A572" s="43"/>
-      <c r="B572" s="43"/>
+      <c r="A572" s="44"/>
+      <c r="B572" s="44"/>
     </row>
     <row r="573">
-      <c r="A573" s="43"/>
-      <c r="B573" s="43"/>
+      <c r="A573" s="44"/>
+      <c r="B573" s="44"/>
     </row>
     <row r="574">
-      <c r="A574" s="43"/>
-      <c r="B574" s="43"/>
+      <c r="A574" s="44"/>
+      <c r="B574" s="44"/>
     </row>
     <row r="575">
-      <c r="A575" s="43"/>
-      <c r="B575" s="43"/>
+      <c r="A575" s="44"/>
+      <c r="B575" s="44"/>
     </row>
     <row r="576">
-      <c r="A576" s="43"/>
-      <c r="B576" s="43"/>
+      <c r="A576" s="44"/>
+      <c r="B576" s="44"/>
     </row>
     <row r="577">
-      <c r="A577" s="43"/>
-      <c r="B577" s="43"/>
+      <c r="A577" s="44"/>
+      <c r="B577" s="44"/>
     </row>
     <row r="578">
-      <c r="A578" s="43"/>
-      <c r="B578" s="43"/>
+      <c r="A578" s="44"/>
+      <c r="B578" s="44"/>
     </row>
     <row r="579">
-      <c r="A579" s="43"/>
-      <c r="B579" s="43"/>
+      <c r="A579" s="44"/>
+      <c r="B579" s="44"/>
     </row>
     <row r="580">
-      <c r="A580" s="43"/>
-      <c r="B580" s="43"/>
+      <c r="A580" s="44"/>
+      <c r="B580" s="44"/>
     </row>
     <row r="581">
-      <c r="A581" s="43"/>
-      <c r="B581" s="43"/>
+      <c r="A581" s="44"/>
+      <c r="B581" s="44"/>
     </row>
     <row r="582">
-      <c r="A582" s="43"/>
-      <c r="B582" s="43"/>
+      <c r="A582" s="44"/>
+      <c r="B582" s="44"/>
     </row>
     <row r="583">
-      <c r="A583" s="43"/>
-      <c r="B583" s="43"/>
+      <c r="A583" s="44"/>
+      <c r="B583" s="44"/>
     </row>
     <row r="584">
-      <c r="A584" s="43"/>
-      <c r="B584" s="43"/>
+      <c r="A584" s="44"/>
+      <c r="B584" s="44"/>
     </row>
     <row r="585">
-      <c r="A585" s="43"/>
-      <c r="B585" s="43"/>
+      <c r="A585" s="44"/>
+      <c r="B585" s="44"/>
     </row>
     <row r="586">
-      <c r="A586" s="43"/>
-      <c r="B586" s="43"/>
+      <c r="A586" s="44"/>
+      <c r="B586" s="44"/>
     </row>
     <row r="587">
-      <c r="A587" s="43"/>
-      <c r="B587" s="43"/>
+      <c r="A587" s="44"/>
+      <c r="B587" s="44"/>
     </row>
     <row r="588">
-      <c r="A588" s="43"/>
-      <c r="B588" s="43"/>
+      <c r="A588" s="44"/>
+      <c r="B588" s="44"/>
     </row>
     <row r="589">
-      <c r="A589" s="43"/>
-      <c r="B589" s="43"/>
+      <c r="A589" s="44"/>
+      <c r="B589" s="44"/>
     </row>
     <row r="590">
-      <c r="A590" s="43"/>
-      <c r="B590" s="43"/>
+      <c r="A590" s="44"/>
+      <c r="B590" s="44"/>
     </row>
     <row r="591">
-      <c r="A591" s="43"/>
-      <c r="B591" s="43"/>
+      <c r="A591" s="44"/>
+      <c r="B591" s="44"/>
     </row>
     <row r="592">
-      <c r="A592" s="43"/>
-      <c r="B592" s="43"/>
+      <c r="A592" s="44"/>
+      <c r="B592" s="44"/>
     </row>
     <row r="593">
-      <c r="A593" s="43"/>
-      <c r="B593" s="43"/>
+      <c r="A593" s="44"/>
+      <c r="B593" s="44"/>
     </row>
     <row r="594">
-      <c r="A594" s="43"/>
-      <c r="B594" s="43"/>
+      <c r="A594" s="44"/>
+      <c r="B594" s="44"/>
     </row>
     <row r="595">
-      <c r="A595" s="43"/>
-      <c r="B595" s="43"/>
+      <c r="A595" s="44"/>
+      <c r="B595" s="44"/>
     </row>
     <row r="596">
-      <c r="A596" s="43"/>
-      <c r="B596" s="43"/>
+      <c r="A596" s="44"/>
+      <c r="B596" s="44"/>
     </row>
     <row r="597">
-      <c r="A597" s="43"/>
-      <c r="B597" s="43"/>
+      <c r="A597" s="44"/>
+      <c r="B597" s="44"/>
     </row>
     <row r="598">
-      <c r="A598" s="43"/>
-      <c r="B598" s="43"/>
+      <c r="A598" s="44"/>
+      <c r="B598" s="44"/>
     </row>
     <row r="599">
-      <c r="A599" s="43"/>
-      <c r="B599" s="43"/>
+      <c r="A599" s="44"/>
+      <c r="B599" s="44"/>
     </row>
     <row r="600">
-      <c r="A600" s="43"/>
-      <c r="B600" s="43"/>
+      <c r="A600" s="44"/>
+      <c r="B600" s="44"/>
     </row>
     <row r="601">
-      <c r="A601" s="43"/>
-      <c r="B601" s="43"/>
+      <c r="A601" s="44"/>
+      <c r="B601" s="44"/>
     </row>
     <row r="602">
-      <c r="A602" s="43"/>
-      <c r="B602" s="43"/>
+      <c r="A602" s="44"/>
+      <c r="B602" s="44"/>
     </row>
     <row r="603">
-      <c r="A603" s="43"/>
-      <c r="B603" s="43"/>
+      <c r="A603" s="44"/>
+      <c r="B603" s="44"/>
     </row>
     <row r="604">
-      <c r="A604" s="43"/>
-      <c r="B604" s="43"/>
+      <c r="A604" s="44"/>
+      <c r="B604" s="44"/>
     </row>
     <row r="605">
-      <c r="A605" s="43"/>
-      <c r="B605" s="43"/>
+      <c r="A605" s="44"/>
+      <c r="B605" s="44"/>
     </row>
     <row r="606">
-      <c r="A606" s="43"/>
-      <c r="B606" s="43"/>
+      <c r="A606" s="44"/>
+      <c r="B606" s="44"/>
     </row>
     <row r="607">
-      <c r="A607" s="43"/>
-      <c r="B607" s="43"/>
+      <c r="A607" s="44"/>
+      <c r="B607" s="44"/>
     </row>
     <row r="608">
-      <c r="A608" s="43"/>
-      <c r="B608" s="43"/>
+      <c r="A608" s="44"/>
+      <c r="B608" s="44"/>
     </row>
     <row r="609">
-      <c r="A609" s="43"/>
-      <c r="B609" s="43"/>
+      <c r="A609" s="44"/>
+      <c r="B609" s="44"/>
     </row>
     <row r="610">
-      <c r="A610" s="43"/>
-      <c r="B610" s="43"/>
+      <c r="A610" s="44"/>
+      <c r="B610" s="44"/>
     </row>
     <row r="611">
-      <c r="A611" s="43"/>
-      <c r="B611" s="43"/>
+      <c r="A611" s="44"/>
+      <c r="B611" s="44"/>
     </row>
     <row r="612">
-      <c r="A612" s="43"/>
-      <c r="B612" s="43"/>
+      <c r="A612" s="44"/>
+      <c r="B612" s="44"/>
     </row>
     <row r="613">
-      <c r="A613" s="43"/>
-      <c r="B613" s="43"/>
+      <c r="A613" s="44"/>
+      <c r="B613" s="44"/>
     </row>
     <row r="614">
-      <c r="A614" s="43"/>
-      <c r="B614" s="43"/>
+      <c r="A614" s="44"/>
+      <c r="B614" s="44"/>
     </row>
     <row r="615">
-      <c r="A615" s="43"/>
-      <c r="B615" s="43"/>
+      <c r="A615" s="44"/>
+      <c r="B615" s="44"/>
     </row>
     <row r="616">
-      <c r="A616" s="43"/>
-      <c r="B616" s="43"/>
+      <c r="A616" s="44"/>
+      <c r="B616" s="44"/>
     </row>
     <row r="617">
-      <c r="A617" s="43"/>
-      <c r="B617" s="43"/>
+      <c r="A617" s="44"/>
+      <c r="B617" s="44"/>
     </row>
     <row r="618">
-      <c r="A618" s="43"/>
-      <c r="B618" s="43"/>
+      <c r="A618" s="44"/>
+      <c r="B618" s="44"/>
     </row>
     <row r="619">
-      <c r="A619" s="43"/>
-      <c r="B619" s="43"/>
+      <c r="A619" s="44"/>
+      <c r="B619" s="44"/>
     </row>
     <row r="620">
-      <c r="A620" s="43"/>
-      <c r="B620" s="43"/>
+      <c r="A620" s="44"/>
+      <c r="B620" s="44"/>
     </row>
     <row r="621">
-      <c r="A621" s="43"/>
-      <c r="B621" s="43"/>
+      <c r="A621" s="44"/>
+      <c r="B621" s="44"/>
     </row>
     <row r="622">
-      <c r="A622" s="43"/>
-      <c r="B622" s="43"/>
+      <c r="A622" s="44"/>
+      <c r="B622" s="44"/>
     </row>
     <row r="623">
-      <c r="A623" s="43"/>
-      <c r="B623" s="43"/>
+      <c r="A623" s="44"/>
+      <c r="B623" s="44"/>
     </row>
     <row r="624">
-      <c r="A624" s="43"/>
-      <c r="B624" s="43"/>
+      <c r="A624" s="44"/>
+      <c r="B624" s="44"/>
     </row>
     <row r="625">
-      <c r="A625" s="43"/>
-      <c r="B625" s="43"/>
+      <c r="A625" s="44"/>
+      <c r="B625" s="44"/>
     </row>
     <row r="626">
-      <c r="A626" s="43"/>
-      <c r="B626" s="43"/>
+      <c r="A626" s="44"/>
+      <c r="B626" s="44"/>
     </row>
     <row r="627">
-      <c r="A627" s="43"/>
-      <c r="B627" s="43"/>
+      <c r="A627" s="44"/>
+      <c r="B627" s="44"/>
     </row>
     <row r="628">
-      <c r="A628" s="43"/>
-      <c r="B628" s="43"/>
+      <c r="A628" s="44"/>
+      <c r="B628" s="44"/>
     </row>
     <row r="629">
-      <c r="A629" s="43"/>
-      <c r="B629" s="43"/>
+      <c r="A629" s="44"/>
+      <c r="B629" s="44"/>
     </row>
     <row r="630">
-      <c r="A630" s="43"/>
-      <c r="B630" s="43"/>
+      <c r="A630" s="44"/>
+      <c r="B630" s="44"/>
     </row>
     <row r="631">
-      <c r="A631" s="43"/>
-      <c r="B631" s="43"/>
+      <c r="A631" s="44"/>
+      <c r="B631" s="44"/>
     </row>
     <row r="632">
-      <c r="A632" s="43"/>
-      <c r="B632" s="43"/>
+      <c r="A632" s="44"/>
+      <c r="B632" s="44"/>
     </row>
     <row r="633">
-      <c r="A633" s="43"/>
-      <c r="B633" s="43"/>
+      <c r="A633" s="44"/>
+      <c r="B633" s="44"/>
     </row>
     <row r="634">
-      <c r="A634" s="43"/>
-      <c r="B634" s="43"/>
+      <c r="A634" s="44"/>
+      <c r="B634" s="44"/>
     </row>
     <row r="635">
-      <c r="A635" s="43"/>
-      <c r="B635" s="43"/>
+      <c r="A635" s="44"/>
+      <c r="B635" s="44"/>
     </row>
     <row r="636">
-      <c r="A636" s="43"/>
-      <c r="B636" s="43"/>
+      <c r="A636" s="44"/>
+      <c r="B636" s="44"/>
     </row>
     <row r="637">
-      <c r="A637" s="43"/>
-      <c r="B637" s="43"/>
+      <c r="A637" s="44"/>
+      <c r="B637" s="44"/>
     </row>
     <row r="638">
-      <c r="A638" s="43"/>
-      <c r="B638" s="43"/>
+      <c r="A638" s="44"/>
+      <c r="B638" s="44"/>
     </row>
     <row r="639">
-      <c r="A639" s="43"/>
-      <c r="B639" s="43"/>
+      <c r="A639" s="44"/>
+      <c r="B639" s="44"/>
     </row>
     <row r="640">
-      <c r="A640" s="43"/>
-      <c r="B640" s="43"/>
+      <c r="A640" s="44"/>
+      <c r="B640" s="44"/>
     </row>
     <row r="641">
-      <c r="A641" s="43"/>
-      <c r="B641" s="43"/>
+      <c r="A641" s="44"/>
+      <c r="B641" s="44"/>
     </row>
     <row r="642">
-      <c r="A642" s="43"/>
-      <c r="B642" s="43"/>
+      <c r="A642" s="44"/>
+      <c r="B642" s="44"/>
     </row>
     <row r="643">
-      <c r="A643" s="43"/>
-      <c r="B643" s="43"/>
+      <c r="A643" s="44"/>
+      <c r="B643" s="44"/>
     </row>
     <row r="644">
-      <c r="A644" s="43"/>
-      <c r="B644" s="43"/>
+      <c r="A644" s="44"/>
+      <c r="B644" s="44"/>
     </row>
     <row r="645">
-      <c r="A645" s="43"/>
-      <c r="B645" s="43"/>
+      <c r="A645" s="44"/>
+      <c r="B645" s="44"/>
     </row>
     <row r="646">
-      <c r="A646" s="43"/>
-      <c r="B646" s="43"/>
+      <c r="A646" s="44"/>
+      <c r="B646" s="44"/>
     </row>
     <row r="647">
-      <c r="A647" s="43"/>
-      <c r="B647" s="43"/>
+      <c r="A647" s="44"/>
+      <c r="B647" s="44"/>
     </row>
     <row r="648">
-      <c r="A648" s="43"/>
-      <c r="B648" s="43"/>
+      <c r="A648" s="44"/>
+      <c r="B648" s="44"/>
     </row>
     <row r="649">
-      <c r="A649" s="43"/>
-      <c r="B649" s="43"/>
+      <c r="A649" s="44"/>
+      <c r="B649" s="44"/>
     </row>
     <row r="650">
-      <c r="A650" s="43"/>
-      <c r="B650" s="43"/>
+      <c r="A650" s="44"/>
+      <c r="B650" s="44"/>
     </row>
     <row r="651">
-      <c r="A651" s="43"/>
-      <c r="B651" s="43"/>
+      <c r="A651" s="44"/>
+      <c r="B651" s="44"/>
     </row>
     <row r="652">
-      <c r="A652" s="43"/>
-      <c r="B652" s="43"/>
+      <c r="A652" s="44"/>
+      <c r="B652" s="44"/>
     </row>
     <row r="653">
-      <c r="A653" s="43"/>
-      <c r="B653" s="43"/>
+      <c r="A653" s="44"/>
+      <c r="B653" s="44"/>
     </row>
     <row r="654">
-      <c r="A654" s="43"/>
-      <c r="B654" s="43"/>
+      <c r="A654" s="44"/>
+      <c r="B654" s="44"/>
     </row>
     <row r="655">
-      <c r="A655" s="43"/>
-      <c r="B655" s="43"/>
+      <c r="A655" s="44"/>
+      <c r="B655" s="44"/>
     </row>
     <row r="656">
-      <c r="A656" s="43"/>
-      <c r="B656" s="43"/>
+      <c r="A656" s="44"/>
+      <c r="B656" s="44"/>
     </row>
     <row r="657">
-      <c r="A657" s="43"/>
-      <c r="B657" s="43"/>
+      <c r="A657" s="44"/>
+      <c r="B657" s="44"/>
     </row>
     <row r="658">
-      <c r="A658" s="43"/>
-      <c r="B658" s="43"/>
+      <c r="A658" s="44"/>
+      <c r="B658" s="44"/>
     </row>
     <row r="659">
-      <c r="A659" s="43"/>
-      <c r="B659" s="43"/>
+      <c r="A659" s="44"/>
+      <c r="B659" s="44"/>
     </row>
     <row r="660">
-      <c r="A660" s="43"/>
-      <c r="B660" s="43"/>
+      <c r="A660" s="44"/>
+      <c r="B660" s="44"/>
     </row>
     <row r="661">
-      <c r="A661" s="43"/>
-      <c r="B661" s="43"/>
+      <c r="A661" s="44"/>
+      <c r="B661" s="44"/>
     </row>
     <row r="662">
-      <c r="A662" s="43"/>
-      <c r="B662" s="43"/>
+      <c r="A662" s="44"/>
+      <c r="B662" s="44"/>
     </row>
     <row r="663">
-      <c r="A663" s="43"/>
-      <c r="B663" s="43"/>
+      <c r="A663" s="44"/>
+      <c r="B663" s="44"/>
     </row>
     <row r="664">
-      <c r="A664" s="43"/>
-      <c r="B664" s="43"/>
+      <c r="A664" s="44"/>
+      <c r="B664" s="44"/>
     </row>
     <row r="665">
-      <c r="A665" s="43"/>
-      <c r="B665" s="43"/>
+      <c r="A665" s="44"/>
+      <c r="B665" s="44"/>
     </row>
     <row r="666">
-      <c r="A666" s="43"/>
-      <c r="B666" s="43"/>
+      <c r="A666" s="44"/>
+      <c r="B666" s="44"/>
     </row>
     <row r="667">
-      <c r="A667" s="43"/>
-      <c r="B667" s="43"/>
+      <c r="A667" s="44"/>
+      <c r="B667" s="44"/>
     </row>
     <row r="668">
-      <c r="A668" s="43"/>
-      <c r="B668" s="43"/>
+      <c r="A668" s="44"/>
+      <c r="B668" s="44"/>
     </row>
     <row r="669">
-      <c r="A669" s="43"/>
-      <c r="B669" s="43"/>
+      <c r="A669" s="44"/>
+      <c r="B669" s="44"/>
     </row>
     <row r="670">
-      <c r="A670" s="43"/>
-      <c r="B670" s="43"/>
+      <c r="A670" s="44"/>
+      <c r="B670" s="44"/>
     </row>
     <row r="671">
-      <c r="A671" s="43"/>
-      <c r="B671" s="43"/>
+      <c r="A671" s="44"/>
+      <c r="B671" s="44"/>
     </row>
     <row r="672">
-      <c r="A672" s="43"/>
-      <c r="B672" s="43"/>
+      <c r="A672" s="44"/>
+      <c r="B672" s="44"/>
     </row>
     <row r="673">
-      <c r="A673" s="43"/>
-      <c r="B673" s="43"/>
+      <c r="A673" s="44"/>
+      <c r="B673" s="44"/>
     </row>
     <row r="674">
-      <c r="A674" s="43"/>
-      <c r="B674" s="43"/>
+      <c r="A674" s="44"/>
+      <c r="B674" s="44"/>
     </row>
     <row r="675">
-      <c r="A675" s="43"/>
-      <c r="B675" s="43"/>
+      <c r="A675" s="44"/>
+      <c r="B675" s="44"/>
     </row>
     <row r="676">
-      <c r="A676" s="43"/>
-      <c r="B676" s="43"/>
+      <c r="A676" s="44"/>
+      <c r="B676" s="44"/>
     </row>
     <row r="677">
-      <c r="A677" s="43"/>
-      <c r="B677" s="43"/>
+      <c r="A677" s="44"/>
+      <c r="B677" s="44"/>
     </row>
     <row r="678">
-      <c r="A678" s="43"/>
-      <c r="B678" s="43"/>
+      <c r="A678" s="44"/>
+      <c r="B678" s="44"/>
     </row>
     <row r="679">
-      <c r="A679" s="43"/>
-      <c r="B679" s="43"/>
+      <c r="A679" s="44"/>
+      <c r="B679" s="44"/>
     </row>
     <row r="680">
-      <c r="A680" s="43"/>
-      <c r="B680" s="43"/>
+      <c r="A680" s="44"/>
+      <c r="B680" s="44"/>
     </row>
     <row r="681">
-      <c r="A681" s="43"/>
-      <c r="B681" s="43"/>
+      <c r="A681" s="44"/>
+      <c r="B681" s="44"/>
     </row>
     <row r="682">
-      <c r="A682" s="43"/>
-      <c r="B682" s="43"/>
+      <c r="A682" s="44"/>
+      <c r="B682" s="44"/>
     </row>
     <row r="683">
-      <c r="A683" s="43"/>
-      <c r="B683" s="43"/>
+      <c r="A683" s="44"/>
+      <c r="B683" s="44"/>
     </row>
     <row r="684">
-      <c r="A684" s="43"/>
-      <c r="B684" s="43"/>
+      <c r="A684" s="44"/>
+      <c r="B684" s="44"/>
     </row>
     <row r="685">
-      <c r="A685" s="43"/>
-      <c r="B685" s="43"/>
+      <c r="A685" s="44"/>
+      <c r="B685" s="44"/>
     </row>
     <row r="686">
-      <c r="A686" s="43"/>
-      <c r="B686" s="43"/>
+      <c r="A686" s="44"/>
+      <c r="B686" s="44"/>
     </row>
     <row r="687">
-      <c r="A687" s="43"/>
-      <c r="B687" s="43"/>
+      <c r="A687" s="44"/>
+      <c r="B687" s="44"/>
     </row>
     <row r="688">
-      <c r="A688" s="43"/>
-      <c r="B688" s="43"/>
+      <c r="A688" s="44"/>
+      <c r="B688" s="44"/>
     </row>
     <row r="689">
-      <c r="A689" s="43"/>
-      <c r="B689" s="43"/>
+      <c r="A689" s="44"/>
+      <c r="B689" s="44"/>
     </row>
     <row r="690">
-      <c r="A690" s="43"/>
-      <c r="B690" s="43"/>
+      <c r="A690" s="44"/>
+      <c r="B690" s="44"/>
     </row>
     <row r="691">
-      <c r="A691" s="43"/>
-      <c r="B691" s="43"/>
+      <c r="A691" s="44"/>
+      <c r="B691" s="44"/>
     </row>
     <row r="692">
-      <c r="A692" s="43"/>
-      <c r="B692" s="43"/>
+      <c r="A692" s="44"/>
+      <c r="B692" s="44"/>
     </row>
     <row r="693">
-      <c r="A693" s="43"/>
-      <c r="B693" s="43"/>
+      <c r="A693" s="44"/>
+      <c r="B693" s="44"/>
     </row>
     <row r="694">
-      <c r="A694" s="43"/>
-      <c r="B694" s="43"/>
+      <c r="A694" s="44"/>
+      <c r="B694" s="44"/>
     </row>
     <row r="695">
-      <c r="A695" s="43"/>
-      <c r="B695" s="43"/>
+      <c r="A695" s="44"/>
+      <c r="B695" s="44"/>
     </row>
     <row r="696">
-      <c r="A696" s="43"/>
-      <c r="B696" s="43"/>
+      <c r="A696" s="44"/>
+      <c r="B696" s="44"/>
     </row>
     <row r="697">
-      <c r="A697" s="43"/>
-      <c r="B697" s="43"/>
+      <c r="A697" s="44"/>
+      <c r="B697" s="44"/>
     </row>
     <row r="698">
-      <c r="A698" s="43"/>
-      <c r="B698" s="43"/>
+      <c r="A698" s="44"/>
+      <c r="B698" s="44"/>
     </row>
     <row r="699">
-      <c r="A699" s="43"/>
-      <c r="B699" s="43"/>
+      <c r="A699" s="44"/>
+      <c r="B699" s="44"/>
     </row>
     <row r="700">
-      <c r="A700" s="43"/>
-      <c r="B700" s="43"/>
+      <c r="A700" s="44"/>
+      <c r="B700" s="44"/>
     </row>
     <row r="701">
-      <c r="A701" s="43"/>
-      <c r="B701" s="43"/>
+      <c r="A701" s="44"/>
+      <c r="B701" s="44"/>
     </row>
     <row r="702">
-      <c r="A702" s="43"/>
-      <c r="B702" s="43"/>
+      <c r="A702" s="44"/>
+      <c r="B702" s="44"/>
     </row>
     <row r="703">
-      <c r="A703" s="43"/>
-      <c r="B703" s="43"/>
+      <c r="A703" s="44"/>
+      <c r="B703" s="44"/>
     </row>
     <row r="704">
-      <c r="A704" s="43"/>
-      <c r="B704" s="43"/>
+      <c r="A704" s="44"/>
+      <c r="B704" s="44"/>
     </row>
     <row r="705">
-      <c r="A705" s="43"/>
-      <c r="B705" s="43"/>
+      <c r="A705" s="44"/>
+      <c r="B705" s="44"/>
     </row>
     <row r="706">
-      <c r="A706" s="43"/>
-      <c r="B706" s="43"/>
+      <c r="A706" s="44"/>
+      <c r="B706" s="44"/>
     </row>
     <row r="707">
-      <c r="A707" s="43"/>
-      <c r="B707" s="43"/>
+      <c r="A707" s="44"/>
+      <c r="B707" s="44"/>
     </row>
     <row r="708">
-      <c r="A708" s="43"/>
-      <c r="B708" s="43"/>
+      <c r="A708" s="44"/>
+      <c r="B708" s="44"/>
     </row>
     <row r="709">
-      <c r="A709" s="43"/>
-      <c r="B709" s="43"/>
+      <c r="A709" s="44"/>
+      <c r="B709" s="44"/>
     </row>
     <row r="710">
-      <c r="A710" s="43"/>
-      <c r="B710" s="43"/>
+      <c r="A710" s="44"/>
+      <c r="B710" s="44"/>
     </row>
     <row r="711">
-      <c r="A711" s="43"/>
-      <c r="B711" s="43"/>
+      <c r="A711" s="44"/>
+      <c r="B711" s="44"/>
     </row>
     <row r="712">
-      <c r="A712" s="43"/>
-      <c r="B712" s="43"/>
+      <c r="A712" s="44"/>
+      <c r="B712" s="44"/>
     </row>
     <row r="713">
-      <c r="A713" s="43"/>
-      <c r="B713" s="43"/>
+      <c r="A713" s="44"/>
+      <c r="B713" s="44"/>
     </row>
     <row r="714">
-      <c r="A714" s="43"/>
-      <c r="B714" s="43"/>
+      <c r="A714" s="44"/>
+      <c r="B714" s="44"/>
     </row>
     <row r="715">
-      <c r="A715" s="43"/>
-      <c r="B715" s="43"/>
+      <c r="A715" s="44"/>
+      <c r="B715" s="44"/>
     </row>
     <row r="716">
-      <c r="A716" s="43"/>
-      <c r="B716" s="43"/>
+      <c r="A716" s="44"/>
+      <c r="B716" s="44"/>
     </row>
     <row r="717">
-      <c r="A717" s="43"/>
-      <c r="B717" s="43"/>
+      <c r="A717" s="44"/>
+      <c r="B717" s="44"/>
     </row>
     <row r="718">
-      <c r="A718" s="43"/>
-      <c r="B718" s="43"/>
+      <c r="A718" s="44"/>
+      <c r="B718" s="44"/>
     </row>
     <row r="719">
-      <c r="A719" s="43"/>
-      <c r="B719" s="43"/>
+      <c r="A719" s="44"/>
+      <c r="B719" s="44"/>
     </row>
     <row r="720">
-      <c r="A720" s="43"/>
-      <c r="B720" s="43"/>
+      <c r="A720" s="44"/>
+      <c r="B720" s="44"/>
     </row>
     <row r="721">
-      <c r="A721" s="43"/>
-      <c r="B721" s="43"/>
+      <c r="A721" s="44"/>
+      <c r="B721" s="44"/>
     </row>
     <row r="722">
-      <c r="A722" s="43"/>
-      <c r="B722" s="43"/>
+      <c r="A722" s="44"/>
+      <c r="B722" s="44"/>
     </row>
     <row r="723">
-      <c r="A723" s="43"/>
-      <c r="B723" s="43"/>
+      <c r="A723" s="44"/>
+      <c r="B723" s="44"/>
     </row>
     <row r="724">
-      <c r="A724" s="43"/>
-      <c r="B724" s="43"/>
+      <c r="A724" s="44"/>
+      <c r="B724" s="44"/>
     </row>
     <row r="725">
-      <c r="A725" s="43"/>
-      <c r="B725" s="43"/>
+      <c r="A725" s="44"/>
+      <c r="B725" s="44"/>
     </row>
     <row r="726">
-      <c r="A726" s="43"/>
-      <c r="B726" s="43"/>
+      <c r="A726" s="44"/>
+      <c r="B726" s="44"/>
     </row>
     <row r="727">
-      <c r="A727" s="43"/>
-      <c r="B727" s="43"/>
+      <c r="A727" s="44"/>
+      <c r="B727" s="44"/>
     </row>
     <row r="728">
-      <c r="A728" s="43"/>
-      <c r="B728" s="43"/>
+      <c r="A728" s="44"/>
+      <c r="B728" s="44"/>
     </row>
     <row r="729">
-      <c r="A729" s="43"/>
-      <c r="B729" s="43"/>
+      <c r="A729" s="44"/>
+      <c r="B729" s="44"/>
     </row>
     <row r="730">
-      <c r="A730" s="43"/>
-      <c r="B730" s="43"/>
+      <c r="A730" s="44"/>
+      <c r="B730" s="44"/>
     </row>
     <row r="731">
-      <c r="A731" s="43"/>
-      <c r="B731" s="43"/>
+      <c r="A731" s="44"/>
+      <c r="B731" s="44"/>
     </row>
     <row r="732">
-      <c r="A732" s="43"/>
-      <c r="B732" s="43"/>
+      <c r="A732" s="44"/>
+      <c r="B732" s="44"/>
     </row>
     <row r="733">
-      <c r="A733" s="43"/>
-      <c r="B733" s="43"/>
+      <c r="A733" s="44"/>
+      <c r="B733" s="44"/>
     </row>
     <row r="734">
-      <c r="A734" s="43"/>
-      <c r="B734" s="43"/>
+      <c r="A734" s="44"/>
+      <c r="B734" s="44"/>
     </row>
     <row r="735">
-      <c r="A735" s="43"/>
-      <c r="B735" s="43"/>
+      <c r="A735" s="44"/>
+      <c r="B735" s="44"/>
     </row>
     <row r="736">
-      <c r="A736" s="43"/>
-      <c r="B736" s="43"/>
+      <c r="A736" s="44"/>
+      <c r="B736" s="44"/>
     </row>
     <row r="737">
-      <c r="A737" s="43"/>
-      <c r="B737" s="43"/>
+      <c r="A737" s="44"/>
+      <c r="B737" s="44"/>
     </row>
     <row r="738">
-      <c r="A738" s="43"/>
-      <c r="B738" s="43"/>
+      <c r="A738" s="44"/>
+      <c r="B738" s="44"/>
     </row>
     <row r="739">
-      <c r="A739" s="43"/>
-      <c r="B739" s="43"/>
+      <c r="A739" s="44"/>
+      <c r="B739" s="44"/>
     </row>
     <row r="740">
-      <c r="A740" s="43"/>
-      <c r="B740" s="43"/>
+      <c r="A740" s="44"/>
+      <c r="B740" s="44"/>
     </row>
     <row r="741">
-      <c r="A741" s="43"/>
-      <c r="B741" s="43"/>
+      <c r="A741" s="44"/>
+      <c r="B741" s="44"/>
     </row>
     <row r="742">
-      <c r="A742" s="43"/>
-      <c r="B742" s="43"/>
+      <c r="A742" s="44"/>
+      <c r="B742" s="44"/>
     </row>
     <row r="743">
-      <c r="A743" s="43"/>
-      <c r="B743" s="43"/>
+      <c r="A743" s="44"/>
+      <c r="B743" s="44"/>
     </row>
     <row r="744">
-      <c r="A744" s="43"/>
-      <c r="B744" s="43"/>
+      <c r="A744" s="44"/>
+      <c r="B744" s="44"/>
     </row>
     <row r="745">
-      <c r="A745" s="43"/>
-      <c r="B745" s="43"/>
+      <c r="A745" s="44"/>
+      <c r="B745" s="44"/>
     </row>
     <row r="746">
-      <c r="A746" s="43"/>
-      <c r="B746" s="43"/>
+      <c r="A746" s="44"/>
+      <c r="B746" s="44"/>
     </row>
     <row r="747">
-      <c r="A747" s="43"/>
-      <c r="B747" s="43"/>
+      <c r="A747" s="44"/>
+      <c r="B747" s="44"/>
     </row>
     <row r="748">
-      <c r="A748" s="43"/>
-      <c r="B748" s="43"/>
+      <c r="A748" s="44"/>
+      <c r="B748" s="44"/>
     </row>
     <row r="749">
-      <c r="A749" s="43"/>
-      <c r="B749" s="43"/>
+      <c r="A749" s="44"/>
+      <c r="B749" s="44"/>
     </row>
     <row r="750">
-      <c r="A750" s="43"/>
-      <c r="B750" s="43"/>
+      <c r="A750" s="44"/>
+      <c r="B750" s="44"/>
     </row>
     <row r="751">
-      <c r="A751" s="43"/>
-      <c r="B751" s="43"/>
+      <c r="A751" s="44"/>
+      <c r="B751" s="44"/>
     </row>
     <row r="752">
-      <c r="A752" s="43"/>
-      <c r="B752" s="43"/>
+      <c r="A752" s="44"/>
+      <c r="B752" s="44"/>
     </row>
     <row r="753">
-      <c r="A753" s="43"/>
-      <c r="B753" s="43"/>
+      <c r="A753" s="44"/>
+      <c r="B753" s="44"/>
     </row>
     <row r="754">
-      <c r="A754" s="43"/>
-      <c r="B754" s="43"/>
+      <c r="A754" s="44"/>
+      <c r="B754" s="44"/>
     </row>
     <row r="755">
-      <c r="A755" s="43"/>
-      <c r="B755" s="43"/>
+      <c r="A755" s="44"/>
+      <c r="B755" s="44"/>
     </row>
     <row r="756">
-      <c r="A756" s="43"/>
-      <c r="B756" s="43"/>
+      <c r="A756" s="44"/>
+      <c r="B756" s="44"/>
     </row>
     <row r="757">
-      <c r="A757" s="43"/>
-      <c r="B757" s="43"/>
+      <c r="A757" s="44"/>
+      <c r="B757" s="44"/>
     </row>
     <row r="758">
-      <c r="A758" s="43"/>
-      <c r="B758" s="43"/>
+      <c r="A758" s="44"/>
+      <c r="B758" s="44"/>
     </row>
     <row r="759">
-      <c r="A759" s="43"/>
-      <c r="B759" s="43"/>
+      <c r="A759" s="44"/>
+      <c r="B759" s="44"/>
     </row>
     <row r="760">
-      <c r="A760" s="43"/>
-      <c r="B760" s="43"/>
+      <c r="A760" s="44"/>
+      <c r="B760" s="44"/>
     </row>
     <row r="761">
-      <c r="A761" s="43"/>
-      <c r="B761" s="43"/>
+      <c r="A761" s="44"/>
+      <c r="B761" s="44"/>
     </row>
     <row r="762">
-      <c r="A762" s="43"/>
-      <c r="B762" s="43"/>
+      <c r="A762" s="44"/>
+      <c r="B762" s="44"/>
     </row>
     <row r="763">
-      <c r="A763" s="43"/>
-      <c r="B763" s="43"/>
+      <c r="A763" s="44"/>
+      <c r="B763" s="44"/>
     </row>
     <row r="764">
-      <c r="A764" s="43"/>
-      <c r="B764" s="43"/>
+      <c r="A764" s="44"/>
+      <c r="B764" s="44"/>
     </row>
     <row r="765">
-      <c r="A765" s="43"/>
-      <c r="B765" s="43"/>
+      <c r="A765" s="44"/>
+      <c r="B765" s="44"/>
     </row>
     <row r="766">
-      <c r="A766" s="43"/>
-      <c r="B766" s="43"/>
+      <c r="A766" s="44"/>
+      <c r="B766" s="44"/>
     </row>
     <row r="767">
-      <c r="A767" s="43"/>
-      <c r="B767" s="43"/>
+      <c r="A767" s="44"/>
+      <c r="B767" s="44"/>
     </row>
     <row r="768">
-      <c r="A768" s="43"/>
-      <c r="B768" s="43"/>
+      <c r="A768" s="44"/>
+      <c r="B768" s="44"/>
     </row>
     <row r="769">
-      <c r="A769" s="43"/>
-      <c r="B769" s="43"/>
+      <c r="A769" s="44"/>
+      <c r="B769" s="44"/>
     </row>
     <row r="770">
-      <c r="A770" s="43"/>
-      <c r="B770" s="43"/>
+      <c r="A770" s="44"/>
+      <c r="B770" s="44"/>
     </row>
     <row r="771">
-      <c r="A771" s="43"/>
-      <c r="B771" s="43"/>
+      <c r="A771" s="44"/>
+      <c r="B771" s="44"/>
     </row>
     <row r="772">
-      <c r="A772" s="43"/>
-      <c r="B772" s="43"/>
+      <c r="A772" s="44"/>
+      <c r="B772" s="44"/>
     </row>
     <row r="773">
-      <c r="A773" s="43"/>
-      <c r="B773" s="43"/>
+      <c r="A773" s="44"/>
+      <c r="B773" s="44"/>
     </row>
     <row r="774">
-      <c r="A774" s="43"/>
-      <c r="B774" s="43"/>
+      <c r="A774" s="44"/>
+      <c r="B774" s="44"/>
     </row>
     <row r="775">
-      <c r="A775" s="43"/>
-      <c r="B775" s="43"/>
+      <c r="A775" s="44"/>
+      <c r="B775" s="44"/>
     </row>
     <row r="776">
-      <c r="A776" s="43"/>
-      <c r="B776" s="43"/>
+      <c r="A776" s="44"/>
+      <c r="B776" s="44"/>
     </row>
     <row r="777">
-      <c r="A777" s="43"/>
-      <c r="B777" s="43"/>
+      <c r="A777" s="44"/>
+      <c r="B777" s="44"/>
     </row>
     <row r="778">
-      <c r="A778" s="43"/>
-      <c r="B778" s="43"/>
+      <c r="A778" s="44"/>
+      <c r="B778" s="44"/>
     </row>
     <row r="779">
-      <c r="A779" s="43"/>
-      <c r="B779" s="43"/>
+      <c r="A779" s="44"/>
+      <c r="B779" s="44"/>
     </row>
     <row r="780">
-      <c r="A780" s="43"/>
-      <c r="B780" s="43"/>
+      <c r="A780" s="44"/>
+      <c r="B780" s="44"/>
     </row>
     <row r="781">
-      <c r="A781" s="43"/>
-      <c r="B781" s="43"/>
+      <c r="A781" s="44"/>
+      <c r="B781" s="44"/>
     </row>
     <row r="782">
-      <c r="A782" s="43"/>
-      <c r="B782" s="43"/>
+      <c r="A782" s="44"/>
+      <c r="B782" s="44"/>
     </row>
     <row r="783">
-      <c r="A783" s="43"/>
-      <c r="B783" s="43"/>
+      <c r="A783" s="44"/>
+      <c r="B783" s="44"/>
     </row>
     <row r="784">
-      <c r="A784" s="43"/>
-      <c r="B784" s="43"/>
+      <c r="A784" s="44"/>
+      <c r="B784" s="44"/>
     </row>
     <row r="785">
-      <c r="A785" s="43"/>
-      <c r="B785" s="43"/>
+      <c r="A785" s="44"/>
+      <c r="B785" s="44"/>
     </row>
     <row r="786">
-      <c r="A786" s="43"/>
-      <c r="B786" s="43"/>
+      <c r="A786" s="44"/>
+      <c r="B786" s="44"/>
     </row>
     <row r="787">
-      <c r="A787" s="43"/>
-      <c r="B787" s="43"/>
+      <c r="A787" s="44"/>
+      <c r="B787" s="44"/>
     </row>
     <row r="788">
-      <c r="A788" s="43"/>
-      <c r="B788" s="43"/>
+      <c r="A788" s="44"/>
+      <c r="B788" s="44"/>
     </row>
     <row r="789">
-      <c r="A789" s="43"/>
-      <c r="B789" s="43"/>
+      <c r="A789" s="44"/>
+      <c r="B789" s="44"/>
     </row>
     <row r="790">
-      <c r="A790" s="43"/>
-      <c r="B790" s="43"/>
+      <c r="A790" s="44"/>
+      <c r="B790" s="44"/>
     </row>
     <row r="791">
-      <c r="A791" s="43"/>
-      <c r="B791" s="43"/>
+      <c r="A791" s="44"/>
+      <c r="B791" s="44"/>
     </row>
     <row r="792">
-      <c r="A792" s="43"/>
-      <c r="B792" s="43"/>
+      <c r="A792" s="44"/>
+      <c r="B792" s="44"/>
     </row>
     <row r="793">
-      <c r="A793" s="43"/>
-      <c r="B793" s="43"/>
+      <c r="A793" s="44"/>
+      <c r="B793" s="44"/>
     </row>
     <row r="794">
-      <c r="A794" s="43"/>
-      <c r="B794" s="43"/>
+      <c r="A794" s="44"/>
+      <c r="B794" s="44"/>
     </row>
     <row r="795">
-      <c r="A795" s="43"/>
-      <c r="B795" s="43"/>
+      <c r="A795" s="44"/>
+      <c r="B795" s="44"/>
     </row>
     <row r="796">
-      <c r="A796" s="43"/>
-      <c r="B796" s="43"/>
+      <c r="A796" s="44"/>
+      <c r="B796" s="44"/>
     </row>
     <row r="797">
-      <c r="A797" s="43"/>
-      <c r="B797" s="43"/>
+      <c r="A797" s="44"/>
+      <c r="B797" s="44"/>
     </row>
     <row r="798">
-      <c r="A798" s="43"/>
-      <c r="B798" s="43"/>
+      <c r="A798" s="44"/>
+      <c r="B798" s="44"/>
     </row>
     <row r="799">
-      <c r="A799" s="43"/>
-      <c r="B799" s="43"/>
+      <c r="A799" s="44"/>
+      <c r="B799" s="44"/>
     </row>
     <row r="800">
-      <c r="A800" s="43"/>
-      <c r="B800" s="43"/>
+      <c r="A800" s="44"/>
+      <c r="B800" s="44"/>
     </row>
     <row r="801">
-      <c r="A801" s="43"/>
-      <c r="B801" s="43"/>
+      <c r="A801" s="44"/>
+      <c r="B801" s="44"/>
     </row>
     <row r="802">
-      <c r="A802" s="43"/>
-      <c r="B802" s="43"/>
+      <c r="A802" s="44"/>
+      <c r="B802" s="44"/>
     </row>
     <row r="803">
-      <c r="A803" s="43"/>
-      <c r="B803" s="43"/>
+      <c r="A803" s="44"/>
+      <c r="B803" s="44"/>
     </row>
     <row r="804">
-      <c r="A804" s="43"/>
-      <c r="B804" s="43"/>
+      <c r="A804" s="44"/>
+      <c r="B804" s="44"/>
     </row>
     <row r="805">
-      <c r="A805" s="43"/>
-      <c r="B805" s="43"/>
+      <c r="A805" s="44"/>
+      <c r="B805" s="44"/>
     </row>
     <row r="806">
-      <c r="A806" s="43"/>
-      <c r="B806" s="43"/>
+      <c r="A806" s="44"/>
+      <c r="B806" s="44"/>
     </row>
     <row r="807">
-      <c r="A807" s="43"/>
-      <c r="B807" s="43"/>
+      <c r="A807" s="44"/>
+      <c r="B807" s="44"/>
     </row>
     <row r="808">
-      <c r="A808" s="43"/>
-      <c r="B808" s="43"/>
+      <c r="A808" s="44"/>
+      <c r="B808" s="44"/>
     </row>
     <row r="809">
-      <c r="A809" s="43"/>
-      <c r="B809" s="43"/>
+      <c r="A809" s="44"/>
+      <c r="B809" s="44"/>
     </row>
     <row r="810">
-      <c r="A810" s="43"/>
-      <c r="B810" s="43"/>
+      <c r="A810" s="44"/>
+      <c r="B810" s="44"/>
     </row>
     <row r="811">
-      <c r="A811" s="43"/>
-      <c r="B811" s="43"/>
+      <c r="A811" s="44"/>
+      <c r="B811" s="44"/>
     </row>
     <row r="812">
-      <c r="A812" s="43"/>
-      <c r="B812" s="43"/>
+      <c r="A812" s="44"/>
+      <c r="B812" s="44"/>
     </row>
     <row r="813">
-      <c r="A813" s="43"/>
-      <c r="B813" s="43"/>
+      <c r="A813" s="44"/>
+      <c r="B813" s="44"/>
     </row>
     <row r="814">
-      <c r="A814" s="43"/>
-      <c r="B814" s="43"/>
+      <c r="A814" s="44"/>
+      <c r="B814" s="44"/>
     </row>
     <row r="815">
-      <c r="A815" s="43"/>
-      <c r="B815" s="43"/>
+      <c r="A815" s="44"/>
+      <c r="B815" s="44"/>
     </row>
     <row r="816">
-      <c r="A816" s="43"/>
-      <c r="B816" s="43"/>
+      <c r="A816" s="44"/>
+      <c r="B816" s="44"/>
     </row>
     <row r="817">
-      <c r="A817" s="43"/>
-      <c r="B817" s="43"/>
+      <c r="A817" s="44"/>
+      <c r="B817" s="44"/>
     </row>
     <row r="818">
-      <c r="A818" s="43"/>
-      <c r="B818" s="43"/>
+      <c r="A818" s="44"/>
+      <c r="B818" s="44"/>
     </row>
     <row r="819">
-      <c r="A819" s="43"/>
-      <c r="B819" s="43"/>
+      <c r="A819" s="44"/>
+      <c r="B819" s="44"/>
     </row>
     <row r="820">
-      <c r="A820" s="43"/>
-      <c r="B820" s="43"/>
+      <c r="A820" s="44"/>
+      <c r="B820" s="44"/>
     </row>
     <row r="821">
-      <c r="A821" s="43"/>
-      <c r="B821" s="43"/>
+      <c r="A821" s="44"/>
+      <c r="B821" s="44"/>
     </row>
     <row r="822">
-      <c r="A822" s="43"/>
-      <c r="B822" s="43"/>
+      <c r="A822" s="44"/>
+      <c r="B822" s="44"/>
     </row>
     <row r="823">
-      <c r="A823" s="43"/>
-      <c r="B823" s="43"/>
+      <c r="A823" s="44"/>
+      <c r="B823" s="44"/>
     </row>
     <row r="824">
-      <c r="A824" s="43"/>
-      <c r="B824" s="43"/>
+      <c r="A824" s="44"/>
+      <c r="B824" s="44"/>
     </row>
     <row r="825">
-      <c r="A825" s="43"/>
-      <c r="B825" s="43"/>
+      <c r="A825" s="44"/>
+      <c r="B825" s="44"/>
     </row>
     <row r="826">
-      <c r="A826" s="43"/>
-      <c r="B826" s="43"/>
+      <c r="A826" s="44"/>
+      <c r="B826" s="44"/>
     </row>
     <row r="827">
-      <c r="A827" s="43"/>
-      <c r="B827" s="43"/>
+      <c r="A827" s="44"/>
+      <c r="B827" s="44"/>
     </row>
     <row r="828">
-      <c r="A828" s="43"/>
-      <c r="B828" s="43"/>
+      <c r="A828" s="44"/>
+      <c r="B828" s="44"/>
     </row>
     <row r="829">
-      <c r="A829" s="43"/>
-      <c r="B829" s="43"/>
+      <c r="A829" s="44"/>
+      <c r="B829" s="44"/>
     </row>
     <row r="830">
-      <c r="A830" s="43"/>
-      <c r="B830" s="43"/>
+      <c r="A830" s="44"/>
+      <c r="B830" s="44"/>
     </row>
     <row r="831">
-      <c r="A831" s="43"/>
-      <c r="B831" s="43"/>
+      <c r="A831" s="44"/>
+      <c r="B831" s="44"/>
     </row>
     <row r="832">
-      <c r="A832" s="43"/>
-      <c r="B832" s="43"/>
+      <c r="A832" s="44"/>
+      <c r="B832" s="44"/>
     </row>
     <row r="833">
-      <c r="A833" s="43"/>
-      <c r="B833" s="43"/>
+      <c r="A833" s="44"/>
+      <c r="B833" s="44"/>
     </row>
     <row r="834">
-      <c r="A834" s="43"/>
-      <c r="B834" s="43"/>
+      <c r="A834" s="44"/>
+      <c r="B834" s="44"/>
     </row>
     <row r="835">
-      <c r="A835" s="43"/>
-      <c r="B835" s="43"/>
+      <c r="A835" s="44"/>
+      <c r="B835" s="44"/>
     </row>
     <row r="836">
-      <c r="A836" s="43"/>
-      <c r="B836" s="43"/>
+      <c r="A836" s="44"/>
+      <c r="B836" s="44"/>
     </row>
     <row r="837">
-      <c r="A837" s="43"/>
-      <c r="B837" s="43"/>
+      <c r="A837" s="44"/>
+      <c r="B837" s="44"/>
     </row>
     <row r="838">
-      <c r="A838" s="43"/>
-      <c r="B838" s="43"/>
+      <c r="A838" s="44"/>
+      <c r="B838" s="44"/>
     </row>
     <row r="839">
-      <c r="A839" s="43"/>
-      <c r="B839" s="43"/>
+      <c r="A839" s="44"/>
+      <c r="B839" s="44"/>
     </row>
     <row r="840">
-      <c r="A840" s="43"/>
-      <c r="B840" s="43"/>
+      <c r="A840" s="44"/>
+      <c r="B840" s="44"/>
     </row>
     <row r="841">
-      <c r="A841" s="43"/>
-      <c r="B841" s="43"/>
+      <c r="A841" s="44"/>
+      <c r="B841" s="44"/>
     </row>
     <row r="842">
-      <c r="A842" s="43"/>
-      <c r="B842" s="43"/>
+      <c r="A842" s="44"/>
+      <c r="B842" s="44"/>
     </row>
     <row r="843">
-      <c r="A843" s="43"/>
-      <c r="B843" s="43"/>
+      <c r="A843" s="44"/>
+      <c r="B843" s="44"/>
     </row>
     <row r="844">
-      <c r="A844" s="43"/>
-      <c r="B844" s="43"/>
+      <c r="A844" s="44"/>
+      <c r="B844" s="44"/>
     </row>
     <row r="845">
-      <c r="A845" s="43"/>
-      <c r="B845" s="43"/>
+      <c r="A845" s="44"/>
+      <c r="B845" s="44"/>
     </row>
     <row r="846">
-      <c r="A846" s="43"/>
-      <c r="B846" s="43"/>
+      <c r="A846" s="44"/>
+      <c r="B846" s="44"/>
     </row>
     <row r="847">
-      <c r="A847" s="43"/>
-      <c r="B847" s="43"/>
+      <c r="A847" s="44"/>
+      <c r="B847" s="44"/>
     </row>
     <row r="848">
-      <c r="A848" s="43"/>
-      <c r="B848" s="43"/>
+      <c r="A848" s="44"/>
+      <c r="B848" s="44"/>
     </row>
     <row r="849">
-      <c r="A849" s="43"/>
-      <c r="B849" s="43"/>
+      <c r="A849" s="44"/>
+      <c r="B849" s="44"/>
     </row>
     <row r="850">
-      <c r="A850" s="43"/>
-      <c r="B850" s="43"/>
+      <c r="A850" s="44"/>
+      <c r="B850" s="44"/>
     </row>
     <row r="851">
-      <c r="A851" s="43"/>
-      <c r="B851" s="43"/>
+      <c r="A851" s="44"/>
+      <c r="B851" s="44"/>
     </row>
     <row r="852">
-      <c r="A852" s="43"/>
-      <c r="B852" s="43"/>
+      <c r="A852" s="44"/>
+      <c r="B852" s="44"/>
     </row>
     <row r="853">
-      <c r="A853" s="43"/>
-      <c r="B853" s="43"/>
+      <c r="A853" s="44"/>
+      <c r="B853" s="44"/>
     </row>
     <row r="854">
-      <c r="A854" s="43"/>
-      <c r="B854" s="43"/>
+      <c r="A854" s="44"/>
+      <c r="B854" s="44"/>
     </row>
     <row r="855">
-      <c r="A855" s="43"/>
-      <c r="B855" s="43"/>
+      <c r="A855" s="44"/>
+      <c r="B855" s="44"/>
     </row>
     <row r="856">
-      <c r="A856" s="43"/>
-      <c r="B856" s="43"/>
+      <c r="A856" s="44"/>
+      <c r="B856" s="44"/>
     </row>
     <row r="857">
-      <c r="A857" s="43"/>
-      <c r="B857" s="43"/>
+      <c r="A857" s="44"/>
+      <c r="B857" s="44"/>
     </row>
     <row r="858">
-      <c r="A858" s="43"/>
-      <c r="B858" s="43"/>
+      <c r="A858" s="44"/>
+      <c r="B858" s="44"/>
     </row>
     <row r="859">
-      <c r="A859" s="43"/>
-      <c r="B859" s="43"/>
+      <c r="A859" s="44"/>
+      <c r="B859" s="44"/>
     </row>
     <row r="860">
-      <c r="A860" s="43"/>
-      <c r="B860" s="43"/>
+      <c r="A860" s="44"/>
+      <c r="B860" s="44"/>
     </row>
     <row r="861">
-      <c r="A861" s="43"/>
-      <c r="B861" s="43"/>
+      <c r="A861" s="44"/>
+      <c r="B861" s="44"/>
     </row>
     <row r="862">
-      <c r="A862" s="43"/>
-      <c r="B862" s="43"/>
+      <c r="A862" s="44"/>
+      <c r="B862" s="44"/>
     </row>
     <row r="863">
-      <c r="A863" s="43"/>
-      <c r="B863" s="43"/>
+      <c r="A863" s="44"/>
+      <c r="B863" s="44"/>
     </row>
     <row r="864">
-      <c r="A864" s="43"/>
-      <c r="B864" s="43"/>
+      <c r="A864" s="44"/>
+      <c r="B864" s="44"/>
     </row>
     <row r="865">
-      <c r="A865" s="43"/>
-      <c r="B865" s="43"/>
+      <c r="A865" s="44"/>
+      <c r="B865" s="44"/>
     </row>
     <row r="866">
-      <c r="A866" s="43"/>
-      <c r="B866" s="43"/>
+      <c r="A866" s="44"/>
+      <c r="B866" s="44"/>
     </row>
     <row r="867">
-      <c r="A867" s="43"/>
-      <c r="B867" s="43"/>
+      <c r="A867" s="44"/>
+      <c r="B867" s="44"/>
     </row>
     <row r="868">
-      <c r="A868" s="43"/>
-      <c r="B868" s="43"/>
+      <c r="A868" s="44"/>
+      <c r="B868" s="44"/>
     </row>
     <row r="869">
-      <c r="A869" s="43"/>
-      <c r="B869" s="43"/>
+      <c r="A869" s="44"/>
+      <c r="B869" s="44"/>
     </row>
     <row r="870">
-      <c r="A870" s="43"/>
-      <c r="B870" s="43"/>
+      <c r="A870" s="44"/>
+      <c r="B870" s="44"/>
     </row>
     <row r="871">
-      <c r="A871" s="43"/>
-      <c r="B871" s="43"/>
+      <c r="A871" s="44"/>
+      <c r="B871" s="44"/>
     </row>
     <row r="872">
-      <c r="A872" s="43"/>
-      <c r="B872" s="43"/>
+      <c r="A872" s="44"/>
+      <c r="B872" s="44"/>
     </row>
     <row r="873">
-      <c r="A873" s="43"/>
-      <c r="B873" s="43"/>
+      <c r="A873" s="44"/>
+      <c r="B873" s="44"/>
     </row>
     <row r="874">
-      <c r="A874" s="43"/>
-      <c r="B874" s="43"/>
+      <c r="A874" s="44"/>
+      <c r="B874" s="44"/>
     </row>
     <row r="875">
-      <c r="A875" s="43"/>
-      <c r="B875" s="43"/>
+      <c r="A875" s="44"/>
+      <c r="B875" s="44"/>
     </row>
     <row r="876">
-      <c r="A876" s="43"/>
-      <c r="B876" s="43"/>
+      <c r="A876" s="44"/>
+      <c r="B876" s="44"/>
     </row>
     <row r="877">
-      <c r="A877" s="43"/>
-      <c r="B877" s="43"/>
+      <c r="A877" s="44"/>
+      <c r="B877" s="44"/>
     </row>
     <row r="878">
-      <c r="A878" s="43"/>
-      <c r="B878" s="43"/>
+      <c r="A878" s="44"/>
+      <c r="B878" s="44"/>
     </row>
     <row r="879">
-      <c r="A879" s="43"/>
-      <c r="B879" s="43"/>
+      <c r="A879" s="44"/>
+      <c r="B879" s="44"/>
     </row>
     <row r="880">
-      <c r="A880" s="43"/>
-      <c r="B880" s="43"/>
+      <c r="A880" s="44"/>
+      <c r="B880" s="44"/>
     </row>
     <row r="881">
-      <c r="A881" s="43"/>
-      <c r="B881" s="43"/>
+      <c r="A881" s="44"/>
+      <c r="B881" s="44"/>
     </row>
     <row r="882">
-      <c r="A882" s="43"/>
-      <c r="B882" s="43"/>
+      <c r="A882" s="44"/>
+      <c r="B882" s="44"/>
     </row>
     <row r="883">
-      <c r="A883" s="43"/>
-      <c r="B883" s="43"/>
+      <c r="A883" s="44"/>
+      <c r="B883" s="44"/>
     </row>
     <row r="884">
-      <c r="A884" s="43"/>
-      <c r="B884" s="43"/>
+      <c r="A884" s="44"/>
+      <c r="B884" s="44"/>
     </row>
     <row r="885">
-      <c r="A885" s="43"/>
-      <c r="B885" s="43"/>
+      <c r="A885" s="44"/>
+      <c r="B885" s="44"/>
     </row>
     <row r="886">
-      <c r="A886" s="43"/>
-      <c r="B886" s="43"/>
+      <c r="A886" s="44"/>
+      <c r="B886" s="44"/>
     </row>
     <row r="887">
-      <c r="A887" s="43"/>
-      <c r="B887" s="43"/>
+      <c r="A887" s="44"/>
+      <c r="B887" s="44"/>
     </row>
     <row r="888">
-      <c r="A888" s="43"/>
-      <c r="B888" s="43"/>
+      <c r="A888" s="44"/>
+      <c r="B888" s="44"/>
     </row>
     <row r="889">
-      <c r="A889" s="43"/>
-      <c r="B889" s="43"/>
+      <c r="A889" s="44"/>
+      <c r="B889" s="44"/>
     </row>
     <row r="890">
-      <c r="A890" s="43"/>
-      <c r="B890" s="43"/>
+      <c r="A890" s="44"/>
+      <c r="B890" s="44"/>
     </row>
     <row r="891">
-      <c r="A891" s="43"/>
-      <c r="B891" s="43"/>
+      <c r="A891" s="44"/>
+      <c r="B891" s="44"/>
     </row>
     <row r="892">
-      <c r="A892" s="43"/>
-      <c r="B892" s="43"/>
+      <c r="A892" s="44"/>
+      <c r="B892" s="44"/>
     </row>
     <row r="893">
-      <c r="A893" s="43"/>
-      <c r="B893" s="43"/>
+      <c r="A893" s="44"/>
+      <c r="B893" s="44"/>
     </row>
     <row r="894">
-      <c r="A894" s="43"/>
-      <c r="B894" s="43"/>
+      <c r="A894" s="44"/>
+      <c r="B894" s="44"/>
     </row>
     <row r="895">
-      <c r="A895" s="43"/>
-      <c r="B895" s="43"/>
+      <c r="A895" s="44"/>
+      <c r="B895" s="44"/>
     </row>
     <row r="896">
-      <c r="A896" s="43"/>
-      <c r="B896" s="43"/>
+      <c r="A896" s="44"/>
+      <c r="B896" s="44"/>
     </row>
     <row r="897">
-      <c r="A897" s="43"/>
-      <c r="B897" s="43"/>
+      <c r="A897" s="44"/>
+      <c r="B897" s="44"/>
     </row>
     <row r="898">
-      <c r="A898" s="43"/>
-      <c r="B898" s="43"/>
+      <c r="A898" s="44"/>
+      <c r="B898" s="44"/>
     </row>
     <row r="899">
-      <c r="A899" s="43"/>
-      <c r="B899" s="43"/>
+      <c r="A899" s="44"/>
+      <c r="B899" s="44"/>
     </row>
     <row r="900">
-      <c r="A900" s="43"/>
-      <c r="B900" s="43"/>
+      <c r="A900" s="44"/>
+      <c r="B900" s="44"/>
     </row>
     <row r="901">
-      <c r="A901" s="43"/>
-      <c r="B901" s="43"/>
+      <c r="A901" s="44"/>
+      <c r="B901" s="44"/>
     </row>
     <row r="902">
-      <c r="A902" s="43"/>
-      <c r="B902" s="43"/>
+      <c r="A902" s="44"/>
+      <c r="B902" s="44"/>
     </row>
     <row r="903">
-      <c r="A903" s="43"/>
-      <c r="B903" s="43"/>
+      <c r="A903" s="44"/>
+      <c r="B903" s="44"/>
     </row>
     <row r="904">
-      <c r="A904" s="43"/>
-      <c r="B904" s="43"/>
+      <c r="A904" s="44"/>
+      <c r="B904" s="44"/>
     </row>
     <row r="905">
-      <c r="A905" s="43"/>
-      <c r="B905" s="43"/>
+      <c r="A905" s="44"/>
+      <c r="B905" s="44"/>
     </row>
     <row r="906">
-      <c r="A906" s="43"/>
-      <c r="B906" s="43"/>
+      <c r="A906" s="44"/>
+      <c r="B906" s="44"/>
     </row>
     <row r="907">
-      <c r="A907" s="43"/>
-      <c r="B907" s="43"/>
+      <c r="A907" s="44"/>
+      <c r="B907" s="44"/>
     </row>
     <row r="908">
-      <c r="A908" s="43"/>
-      <c r="B908" s="43"/>
+      <c r="A908" s="44"/>
+      <c r="B908" s="44"/>
     </row>
     <row r="909">
-      <c r="A909" s="43"/>
-      <c r="B909" s="43"/>
+      <c r="A909" s="44"/>
+      <c r="B909" s="44"/>
     </row>
     <row r="910">
-      <c r="A910" s="43"/>
-      <c r="B910" s="43"/>
+      <c r="A910" s="44"/>
+      <c r="B910" s="44"/>
     </row>
     <row r="911">
-      <c r="A911" s="43"/>
-      <c r="B911" s="43"/>
+      <c r="A911" s="44"/>
+      <c r="B911" s="44"/>
     </row>
     <row r="912">
-      <c r="A912" s="43"/>
-      <c r="B912" s="43"/>
+      <c r="A912" s="44"/>
+      <c r="B912" s="44"/>
     </row>
     <row r="913">
-      <c r="A913" s="43"/>
-      <c r="B913" s="43"/>
+      <c r="A913" s="44"/>
+      <c r="B913" s="44"/>
     </row>
     <row r="914">
-      <c r="A914" s="43"/>
-      <c r="B914" s="43"/>
+      <c r="A914" s="44"/>
+      <c r="B914" s="44"/>
     </row>
     <row r="915">
-      <c r="A915" s="43"/>
-      <c r="B915" s="43"/>
+      <c r="A915" s="44"/>
+      <c r="B915" s="44"/>
     </row>
     <row r="916">
-      <c r="A916" s="43"/>
-      <c r="B916" s="43"/>
+      <c r="A916" s="44"/>
+      <c r="B916" s="44"/>
     </row>
     <row r="917">
-      <c r="A917" s="43"/>
-      <c r="B917" s="43"/>
+      <c r="A917" s="44"/>
+      <c r="B917" s="44"/>
     </row>
     <row r="918">
-      <c r="A918" s="43"/>
-      <c r="B918" s="43"/>
+      <c r="A918" s="44"/>
+      <c r="B918" s="44"/>
     </row>
     <row r="919">
-      <c r="A919" s="43"/>
-      <c r="B919" s="43"/>
+      <c r="A919" s="44"/>
+      <c r="B919" s="44"/>
     </row>
     <row r="920">
-      <c r="A920" s="43"/>
-      <c r="B920" s="43"/>
+      <c r="A920" s="44"/>
+      <c r="B920" s="44"/>
     </row>
     <row r="921">
-      <c r="A921" s="43"/>
-      <c r="B921" s="43"/>
+      <c r="A921" s="44"/>
+      <c r="B921" s="44"/>
     </row>
     <row r="922">
-      <c r="A922" s="43"/>
-      <c r="B922" s="43"/>
+      <c r="A922" s="44"/>
+      <c r="B922" s="44"/>
     </row>
     <row r="923">
-      <c r="A923" s="43"/>
-      <c r="B923" s="43"/>
+      <c r="A923" s="44"/>
+      <c r="B923" s="44"/>
     </row>
     <row r="924">
-      <c r="A924" s="43"/>
-      <c r="B924" s="43"/>
+      <c r="A924" s="44"/>
+      <c r="B924" s="44"/>
     </row>
     <row r="925">
-      <c r="A925" s="43"/>
-      <c r="B925" s="43"/>
+      <c r="A925" s="44"/>
+      <c r="B925" s="44"/>
     </row>
     <row r="926">
-      <c r="A926" s="43"/>
-      <c r="B926" s="43"/>
+      <c r="A926" s="44"/>
+      <c r="B926" s="44"/>
     </row>
     <row r="927">
-      <c r="A927" s="43"/>
-      <c r="B927" s="43"/>
+      <c r="A927" s="44"/>
+      <c r="B927" s="44"/>
     </row>
     <row r="928">
-      <c r="A928" s="43"/>
-      <c r="B928" s="43"/>
+      <c r="A928" s="44"/>
+      <c r="B928" s="44"/>
     </row>
     <row r="929">
-      <c r="A929" s="43"/>
-      <c r="B929" s="43"/>
+      <c r="A929" s="44"/>
+      <c r="B929" s="44"/>
     </row>
     <row r="930">
-      <c r="A930" s="43"/>
-      <c r="B930" s="43"/>
+      <c r="A930" s="44"/>
+      <c r="B930" s="44"/>
     </row>
     <row r="931">
-      <c r="A931" s="43"/>
-      <c r="B931" s="43"/>
+      <c r="A931" s="44"/>
+      <c r="B931" s="44"/>
     </row>
     <row r="932">
-      <c r="A932" s="43"/>
-      <c r="B932" s="43"/>
+      <c r="A932" s="44"/>
+      <c r="B932" s="44"/>
     </row>
     <row r="933">
-      <c r="A933" s="43"/>
-      <c r="B933" s="43"/>
+      <c r="A933" s="44"/>
+      <c r="B933" s="44"/>
     </row>
     <row r="934">
-      <c r="A934" s="43"/>
-      <c r="B934" s="43"/>
+      <c r="A934" s="44"/>
+      <c r="B934" s="44"/>
     </row>
     <row r="935">
-      <c r="A935" s="43"/>
-      <c r="B935" s="43"/>
+      <c r="A935" s="44"/>
+      <c r="B935" s="44"/>
     </row>
     <row r="936">
-      <c r="A936" s="43"/>
-      <c r="B936" s="43"/>
+      <c r="A936" s="44"/>
+      <c r="B936" s="44"/>
     </row>
     <row r="937">
-      <c r="A937" s="43"/>
-      <c r="B937" s="43"/>
+      <c r="A937" s="44"/>
+      <c r="B937" s="44"/>
     </row>
     <row r="938">
-      <c r="A938" s="43"/>
-      <c r="B938" s="43"/>
+      <c r="A938" s="44"/>
+      <c r="B938" s="44"/>
     </row>
     <row r="939">
-      <c r="A939" s="43"/>
-      <c r="B939" s="43"/>
+      <c r="A939" s="44"/>
+      <c r="B939" s="44"/>
     </row>
     <row r="940">
-      <c r="A940" s="43"/>
-      <c r="B940" s="43"/>
+      <c r="A940" s="44"/>
+      <c r="B940" s="44"/>
     </row>
     <row r="941">
-      <c r="A941" s="43"/>
-      <c r="B941" s="43"/>
+      <c r="A941" s="44"/>
+      <c r="B941" s="44"/>
     </row>
     <row r="942">
-      <c r="A942" s="43"/>
-      <c r="B942" s="43"/>
+      <c r="A942" s="44"/>
+      <c r="B942" s="44"/>
     </row>
     <row r="943">
-      <c r="A943" s="43"/>
-      <c r="B943" s="43"/>
+      <c r="A943" s="44"/>
+      <c r="B943" s="44"/>
     </row>
     <row r="944">
-      <c r="A944" s="43"/>
-      <c r="B944" s="43"/>
+      <c r="A944" s="44"/>
+      <c r="B944" s="44"/>
     </row>
     <row r="945">
-      <c r="A945" s="43"/>
-      <c r="B945" s="43"/>
+      <c r="A945" s="44"/>
+      <c r="B945" s="44"/>
     </row>
     <row r="946">
-      <c r="A946" s="43"/>
-      <c r="B946" s="43"/>
+      <c r="A946" s="44"/>
+      <c r="B946" s="44"/>
     </row>
     <row r="947">
-      <c r="A947" s="43"/>
-      <c r="B947" s="43"/>
+      <c r="A947" s="44"/>
+      <c r="B947" s="44"/>
     </row>
     <row r="948">
-      <c r="A948" s="43"/>
-      <c r="B948" s="43"/>
+      <c r="A948" s="44"/>
+      <c r="B948" s="44"/>
     </row>
     <row r="949">
-      <c r="A949" s="43"/>
-      <c r="B949" s="43"/>
+      <c r="A949" s="44"/>
+      <c r="B949" s="44"/>
     </row>
     <row r="950">
-      <c r="A950" s="43"/>
-      <c r="B950" s="43"/>
+      <c r="A950" s="44"/>
+      <c r="B950" s="44"/>
     </row>
     <row r="951">
-      <c r="A951" s="43"/>
-      <c r="B951" s="43"/>
+      <c r="A951" s="44"/>
+      <c r="B951" s="44"/>
     </row>
     <row r="952">
-      <c r="A952" s="43"/>
-      <c r="B952" s="43"/>
+      <c r="A952" s="44"/>
+      <c r="B952" s="44"/>
     </row>
     <row r="953">
-      <c r="A953" s="43"/>
-      <c r="B953" s="43"/>
+      <c r="A953" s="44"/>
+      <c r="B953" s="44"/>
     </row>
     <row r="954">
-      <c r="A954" s="43"/>
-      <c r="B954" s="43"/>
+      <c r="A954" s="44"/>
+      <c r="B954" s="44"/>
     </row>
     <row r="955">
-      <c r="A955" s="43"/>
-      <c r="B955" s="43"/>
+      <c r="A955" s="44"/>
+      <c r="B955" s="44"/>
     </row>
     <row r="956">
-      <c r="A956" s="43"/>
-      <c r="B956" s="43"/>
+      <c r="A956" s="44"/>
+      <c r="B956" s="44"/>
     </row>
     <row r="957">
-      <c r="A957" s="43"/>
-      <c r="B957" s="43"/>
+      <c r="A957" s="44"/>
+      <c r="B957" s="44"/>
     </row>
     <row r="958">
-      <c r="A958" s="43"/>
-      <c r="B958" s="43"/>
+      <c r="A958" s="44"/>
+      <c r="B958" s="44"/>
     </row>
     <row r="959">
-      <c r="A959" s="43"/>
-      <c r="B959" s="43"/>
+      <c r="A959" s="44"/>
+      <c r="B959" s="44"/>
     </row>
     <row r="960">
-      <c r="A960" s="43"/>
-      <c r="B960" s="43"/>
+      <c r="A960" s="44"/>
+      <c r="B960" s="44"/>
     </row>
     <row r="961">
-      <c r="A961" s="43"/>
-      <c r="B961" s="43"/>
+      <c r="A961" s="44"/>
+      <c r="B961" s="44"/>
     </row>
     <row r="962">
-      <c r="A962" s="43"/>
-      <c r="B962" s="43"/>
+      <c r="A962" s="44"/>
+      <c r="B962" s="44"/>
     </row>
     <row r="963">
-      <c r="A963" s="43"/>
-      <c r="B963" s="43"/>
+      <c r="A963" s="44"/>
+      <c r="B963" s="44"/>
     </row>
     <row r="964">
-      <c r="A964" s="43"/>
-      <c r="B964" s="43"/>
+      <c r="A964" s="44"/>
+      <c r="B964" s="44"/>
     </row>
     <row r="965">
-      <c r="A965" s="43"/>
-      <c r="B965" s="43"/>
+      <c r="A965" s="44"/>
+      <c r="B965" s="44"/>
     </row>
     <row r="966">
-      <c r="A966" s="43"/>
-      <c r="B966" s="43"/>
+      <c r="A966" s="44"/>
+      <c r="B966" s="44"/>
     </row>
     <row r="967">
-      <c r="A967" s="43"/>
-      <c r="B967" s="43"/>
+      <c r="A967" s="44"/>
+      <c r="B967" s="44"/>
     </row>
     <row r="968">
-      <c r="A968" s="43"/>
-      <c r="B968" s="43"/>
+      <c r="A968" s="44"/>
+      <c r="B968" s="44"/>
     </row>
     <row r="969">
-      <c r="A969" s="43"/>
-      <c r="B969" s="43"/>
+      <c r="A969" s="44"/>
+      <c r="B969" s="44"/>
     </row>
     <row r="970">
-      <c r="A970" s="43"/>
-      <c r="B970" s="43"/>
+      <c r="A970" s="44"/>
+      <c r="B970" s="44"/>
     </row>
     <row r="971">
-      <c r="A971" s="43"/>
-      <c r="B971" s="43"/>
+      <c r="A971" s="44"/>
+      <c r="B971" s="44"/>
     </row>
     <row r="972">
-      <c r="A972" s="43"/>
-      <c r="B972" s="43"/>
+      <c r="A972" s="44"/>
+      <c r="B972" s="44"/>
     </row>
     <row r="973">
-      <c r="A973" s="43"/>
-      <c r="B973" s="43"/>
+      <c r="A973" s="44"/>
+      <c r="B973" s="44"/>
     </row>
     <row r="974">
-      <c r="A974" s="43"/>
-      <c r="B974" s="43"/>
+      <c r="A974" s="44"/>
+      <c r="B974" s="44"/>
     </row>
     <row r="975">
-      <c r="A975" s="43"/>
-      <c r="B975" s="43"/>
+      <c r="A975" s="44"/>
+      <c r="B975" s="44"/>
     </row>
     <row r="976">
-      <c r="A976" s="43"/>
-      <c r="B976" s="43"/>
+      <c r="A976" s="44"/>
+      <c r="B976" s="44"/>
     </row>
     <row r="977">
-      <c r="A977" s="43"/>
-      <c r="B977" s="43"/>
+      <c r="A977" s="44"/>
+      <c r="B977" s="44"/>
     </row>
     <row r="978">
-      <c r="A978" s="43"/>
-      <c r="B978" s="43"/>
+      <c r="A978" s="44"/>
+      <c r="B978" s="44"/>
     </row>
     <row r="979">
-      <c r="A979" s="43"/>
-      <c r="B979" s="43"/>
+      <c r="A979" s="44"/>
+      <c r="B979" s="44"/>
     </row>
     <row r="980">
-      <c r="A980" s="43"/>
-      <c r="B980" s="43"/>
+      <c r="A980" s="44"/>
+      <c r="B980" s="44"/>
     </row>
     <row r="981">
-      <c r="A981" s="43"/>
-      <c r="B981" s="43"/>
+      <c r="A981" s="44"/>
+      <c r="B981" s="44"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
@@ -10320,45 +10362,45 @@
         <v>129</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="44" t="s">
+      <c r="A2" s="45" t="s">
         <v>166</v>
       </c>
-      <c r="B2" s="45" t="s">
-        <v>301</v>
-      </c>
-      <c r="C2" s="45" t="s">
-        <v>302</v>
+      <c r="B2" s="46" t="s">
+        <v>303</v>
+      </c>
+      <c r="C2" s="46" t="s">
+        <v>304</v>
       </c>
       <c r="D2" s="4"/>
       <c r="E2" s="3">
@@ -10372,14 +10414,14 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="46" t="s">
-        <v>303</v>
-      </c>
-      <c r="B3" s="45" t="s">
-        <v>304</v>
-      </c>
-      <c r="C3" s="47" t="s">
+      <c r="A3" s="47" t="s">
         <v>305</v>
+      </c>
+      <c r="B3" s="46" t="s">
+        <v>306</v>
+      </c>
+      <c r="C3" s="48" t="s">
+        <v>307</v>
       </c>
       <c r="D3" s="4"/>
       <c r="E3" s="5">
@@ -10390,24 +10432,24 @@
       </c>
       <c r="G3" s="4"/>
       <c r="H3" s="3" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>309</v>
-      </c>
-      <c r="B4" s="48" t="s">
-        <v>310</v>
-      </c>
-      <c r="C4" s="48" t="s">
         <v>311</v>
+      </c>
+      <c r="B4" s="49" t="s">
+        <v>312</v>
+      </c>
+      <c r="C4" s="49" t="s">
+        <v>313</v>
       </c>
       <c r="D4" s="4"/>
       <c r="E4" s="2">
@@ -10418,24 +10460,24 @@
       </c>
       <c r="G4" s="4"/>
       <c r="H4" s="3" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>315</v>
-      </c>
-      <c r="B5" s="49" t="s">
-        <v>316</v>
-      </c>
-      <c r="C5" s="49" t="s">
         <v>317</v>
+      </c>
+      <c r="B5" s="50" t="s">
+        <v>318</v>
+      </c>
+      <c r="C5" s="50" t="s">
+        <v>319</v>
       </c>
       <c r="E5" s="3">
         <v>-10.0</v>
@@ -10443,19 +10485,25 @@
       <c r="F5" s="3">
         <v>0.0</v>
       </c>
+      <c r="H5" s="3" t="s">
+        <v>320</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>321</v>
+      </c>
       <c r="K5" s="3" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="E6" s="3">
         <v>0.0</v>
@@ -10464,24 +10512,24 @@
         <v>-10.0</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="E7" s="3">
         <v>-10.0</v>
@@ -10490,24 +10538,24 @@
         <v>0.0</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="E8" s="3">
         <v>0.0</v>
@@ -10516,24 +10564,24 @@
         <v>-10.0</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="E9" s="3">
         <v>0.0</v>
@@ -10542,25 +10590,25 @@
         <v>0.0</v>
       </c>
       <c r="H9" s="32" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="I9" s="32" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="J9" s="32"/>
       <c r="K9" s="3" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="E10" s="3">
         <v>-10.0</v>
@@ -10569,24 +10617,24 @@
         <v>-10.0</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="K10" s="50" t="s">
-        <v>348</v>
+        <v>351</v>
+      </c>
+      <c r="K10" s="51" t="s">
+        <v>352</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="E11" s="3">
         <v>-10.0</v>
@@ -10595,13 +10643,13 @@
         <v>-10.0</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/02Script/Table/EventTable.xlsx
+++ b/Assets/02Script/Table/EventTable.xlsx
@@ -667,6 +667,10 @@
     <t>길이 잘 뚫려있네.. 여기 어딘가 열쇠가 있겠지?</t>
   </si>
   <si>
+    <t>미로 곳곳에 숨겨져 있는
+열쇠를 찾아보자!</t>
+  </si>
+  <si>
     <t>으...</t>
   </si>
   <si>
@@ -895,9 +899,6 @@
   </si>
   <si>
     <t>확인하는 게 마음이 편하겠어..</t>
-  </si>
-  <si>
-    <t>뭐...뭐야. 이소리는.</t>
   </si>
   <si>
     <t>설마.... 아까 봤던 그 괴물의 소리...?</t>
@@ -1460,7 +1461,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="D80:J150" displayName="Table_4" name="Table_4" id="4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="D81:J150" displayName="Table_4" name="Table_4" id="4">
   <tableColumns count="7">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -4718,7 +4719,7 @@
         <v>212</v>
       </c>
       <c r="E74" s="3">
-        <v>-1.0</v>
+        <v>18003.0</v>
       </c>
       <c r="F74" s="14" t="s">
         <v>133</v>
@@ -4735,19 +4736,19 @@
     </row>
     <row r="75">
       <c r="A75" s="32" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="B75" s="32" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C75" s="3">
-        <v>19001.0</v>
-      </c>
-      <c r="D75" s="3" t="s">
+        <v>18003.0</v>
+      </c>
+      <c r="D75" s="33" t="s">
         <v>213</v>
       </c>
-      <c r="E75" s="16">
-        <v>19002.0</v>
+      <c r="E75" s="3">
+        <v>-1.0</v>
       </c>
       <c r="F75" s="14" t="s">
         <v>133</v>
@@ -4756,10 +4757,10 @@
         <v>134</v>
       </c>
       <c r="I75" s="31" t="s">
-        <v>135</v>
+        <v>164</v>
       </c>
       <c r="J75" s="16">
-        <v>2.0</v>
+        <v>-1.0</v>
       </c>
     </row>
     <row r="76">
@@ -4770,13 +4771,13 @@
         <v>63</v>
       </c>
       <c r="C76" s="3">
-        <v>19002.0</v>
+        <v>19001.0</v>
       </c>
       <c r="D76" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="E76" s="3">
-        <v>19003.0</v>
+      <c r="E76" s="16">
+        <v>19002.0</v>
       </c>
       <c r="F76" s="14" t="s">
         <v>133</v>
@@ -4799,13 +4800,13 @@
         <v>63</v>
       </c>
       <c r="C77" s="3">
-        <v>19003.0</v>
+        <v>19002.0</v>
       </c>
       <c r="D77" s="3" t="s">
         <v>215</v>
       </c>
       <c r="E77" s="3">
-        <v>19004.0</v>
+        <v>19003.0</v>
       </c>
       <c r="F77" s="14" t="s">
         <v>133</v>
@@ -4816,7 +4817,7 @@
       <c r="I77" s="31" t="s">
         <v>135</v>
       </c>
-      <c r="J77" s="3">
+      <c r="J77" s="16">
         <v>2.0</v>
       </c>
     </row>
@@ -4828,21 +4829,21 @@
         <v>63</v>
       </c>
       <c r="C78" s="3">
-        <v>19004.0</v>
+        <v>19003.0</v>
       </c>
       <c r="D78" s="3" t="s">
         <v>216</v>
       </c>
       <c r="E78" s="3">
-        <v>19005.0</v>
-      </c>
-      <c r="F78" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="G78" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="I78" s="3" t="s">
+        <v>19004.0</v>
+      </c>
+      <c r="F78" s="14" t="s">
+        <v>133</v>
+      </c>
+      <c r="G78" s="11" t="s">
+        <v>134</v>
+      </c>
+      <c r="I78" s="31" t="s">
         <v>135</v>
       </c>
       <c r="J78" s="3">
@@ -4857,54 +4858,53 @@
         <v>63</v>
       </c>
       <c r="C79" s="3">
-        <v>19005.0</v>
+        <v>19004.0</v>
       </c>
       <c r="D79" s="3" t="s">
         <v>217</v>
       </c>
       <c r="E79" s="3">
+        <v>19005.0</v>
+      </c>
+      <c r="F79" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="G79" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="I79" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="J79" s="3">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="32" t="s">
+        <v>63</v>
+      </c>
+      <c r="B80" s="32" t="s">
+        <v>63</v>
+      </c>
+      <c r="C80" s="3">
+        <v>19005.0</v>
+      </c>
+      <c r="D80" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="E80" s="3">
         <v>-1.0</v>
       </c>
-      <c r="F79" s="3" t="s">
-        <v>133</v>
-      </c>
-      <c r="G79" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="I79" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="J79" s="3">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="34" t="s">
-        <v>66</v>
-      </c>
-      <c r="B80" s="34" t="s">
-        <v>66</v>
-      </c>
-      <c r="C80" s="35">
-        <v>20001.0</v>
-      </c>
-      <c r="D80" s="36" t="s">
-        <v>218</v>
-      </c>
-      <c r="E80" s="28">
-        <v>20002.0</v>
-      </c>
-      <c r="F80" s="36" t="s">
-        <v>133</v>
-      </c>
-      <c r="G80" s="37" t="s">
-        <v>134</v>
-      </c>
-      <c r="H80" s="36"/>
-      <c r="I80" s="38" t="s">
-        <v>135</v>
-      </c>
-      <c r="J80" s="28">
+      <c r="F80" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="G80" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="I80" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="J80" s="3">
         <v>0.0</v>
       </c>
     </row>
@@ -4916,25 +4916,25 @@
         <v>66</v>
       </c>
       <c r="C81" s="35">
+        <v>20001.0</v>
+      </c>
+      <c r="D81" s="36" t="s">
+        <v>219</v>
+      </c>
+      <c r="E81" s="28">
         <v>20002.0</v>
       </c>
-      <c r="D81" s="39" t="s">
-        <v>219</v>
-      </c>
-      <c r="E81" s="19">
-        <v>20003.0</v>
-      </c>
-      <c r="F81" s="39" t="s">
+      <c r="F81" s="36" t="s">
         <v>133</v>
       </c>
       <c r="G81" s="37" t="s">
         <v>134</v>
       </c>
-      <c r="H81" s="39"/>
+      <c r="H81" s="36"/>
       <c r="I81" s="38" t="s">
         <v>135</v>
       </c>
-      <c r="J81" s="19">
+      <c r="J81" s="28">
         <v>0.0</v>
       </c>
     </row>
@@ -4946,25 +4946,25 @@
         <v>66</v>
       </c>
       <c r="C82" s="35">
+        <v>20002.0</v>
+      </c>
+      <c r="D82" s="39" t="s">
+        <v>220</v>
+      </c>
+      <c r="E82" s="19">
         <v>20003.0</v>
       </c>
-      <c r="D82" s="36" t="s">
-        <v>220</v>
-      </c>
-      <c r="E82" s="28">
-        <v>20004.0</v>
-      </c>
-      <c r="F82" s="36" t="s">
+      <c r="F82" s="39" t="s">
         <v>133</v>
       </c>
       <c r="G82" s="37" t="s">
         <v>134</v>
       </c>
-      <c r="H82" s="36"/>
+      <c r="H82" s="39"/>
       <c r="I82" s="38" t="s">
         <v>135</v>
       </c>
-      <c r="J82" s="28">
+      <c r="J82" s="19">
         <v>0.0</v>
       </c>
     </row>
@@ -4976,25 +4976,25 @@
         <v>66</v>
       </c>
       <c r="C83" s="35">
+        <v>20003.0</v>
+      </c>
+      <c r="D83" s="36" t="s">
+        <v>221</v>
+      </c>
+      <c r="E83" s="28">
         <v>20004.0</v>
       </c>
-      <c r="D83" s="39" t="s">
-        <v>221</v>
-      </c>
-      <c r="E83" s="19">
-        <v>20005.0</v>
-      </c>
-      <c r="F83" s="39" t="s">
+      <c r="F83" s="36" t="s">
         <v>133</v>
       </c>
       <c r="G83" s="37" t="s">
         <v>134</v>
       </c>
-      <c r="H83" s="39"/>
+      <c r="H83" s="36"/>
       <c r="I83" s="38" t="s">
         <v>135</v>
       </c>
-      <c r="J83" s="19">
+      <c r="J83" s="28">
         <v>0.0</v>
       </c>
     </row>
@@ -5006,25 +5006,25 @@
         <v>66</v>
       </c>
       <c r="C84" s="35">
+        <v>20004.0</v>
+      </c>
+      <c r="D84" s="39" t="s">
+        <v>222</v>
+      </c>
+      <c r="E84" s="19">
         <v>20005.0</v>
       </c>
-      <c r="D84" s="36" t="s">
-        <v>222</v>
-      </c>
-      <c r="E84" s="28">
-        <v>20006.0</v>
-      </c>
-      <c r="F84" s="36" t="s">
+      <c r="F84" s="39" t="s">
         <v>133</v>
       </c>
       <c r="G84" s="37" t="s">
         <v>134</v>
       </c>
-      <c r="H84" s="36"/>
+      <c r="H84" s="39"/>
       <c r="I84" s="38" t="s">
         <v>135</v>
       </c>
-      <c r="J84" s="28">
+      <c r="J84" s="19">
         <v>0.0</v>
       </c>
     </row>
@@ -5036,85 +5036,85 @@
         <v>66</v>
       </c>
       <c r="C85" s="35">
+        <v>20005.0</v>
+      </c>
+      <c r="D85" s="36" t="s">
+        <v>223</v>
+      </c>
+      <c r="E85" s="28">
         <v>20006.0</v>
       </c>
-      <c r="D85" s="39" t="s">
-        <v>223</v>
-      </c>
-      <c r="E85" s="19">
-        <v>-1.0</v>
-      </c>
-      <c r="F85" s="39" t="s">
+      <c r="F85" s="36" t="s">
         <v>133</v>
       </c>
       <c r="G85" s="37" t="s">
         <v>134</v>
       </c>
-      <c r="H85" s="39"/>
+      <c r="H85" s="36"/>
       <c r="I85" s="38" t="s">
         <v>135</v>
       </c>
-      <c r="J85" s="19">
+      <c r="J85" s="28">
         <v>0.0</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="34" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="B86" s="34" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C86" s="35">
-        <v>21001.0</v>
-      </c>
-      <c r="D86" s="36" t="s">
+        <v>20006.0</v>
+      </c>
+      <c r="D86" s="39" t="s">
         <v>224</v>
       </c>
-      <c r="E86" s="28">
+      <c r="E86" s="19">
         <v>-1.0</v>
       </c>
-      <c r="F86" s="36" t="s">
+      <c r="F86" s="39" t="s">
         <v>133</v>
       </c>
       <c r="G86" s="37" t="s">
         <v>134</v>
       </c>
-      <c r="H86" s="36"/>
+      <c r="H86" s="39"/>
       <c r="I86" s="38" t="s">
         <v>135</v>
       </c>
-      <c r="J86" s="28">
+      <c r="J86" s="19">
         <v>0.0</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="34" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B87" s="34" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="C87" s="35">
-        <v>22001.0</v>
-      </c>
-      <c r="D87" s="39" t="s">
+        <v>21001.0</v>
+      </c>
+      <c r="D87" s="36" t="s">
         <v>225</v>
       </c>
-      <c r="E87" s="19">
-        <v>22002.0</v>
-      </c>
-      <c r="F87" s="39" t="s">
+      <c r="E87" s="28">
+        <v>-1.0</v>
+      </c>
+      <c r="F87" s="36" t="s">
         <v>133</v>
       </c>
       <c r="G87" s="37" t="s">
         <v>134</v>
       </c>
-      <c r="H87" s="39"/>
+      <c r="H87" s="36"/>
       <c r="I87" s="38" t="s">
         <v>135</v>
       </c>
-      <c r="J87" s="19">
+      <c r="J87" s="28">
         <v>0.0</v>
       </c>
     </row>
@@ -5126,55 +5126,55 @@
         <v>70</v>
       </c>
       <c r="C88" s="35">
+        <v>22001.0</v>
+      </c>
+      <c r="D88" s="39" t="s">
+        <v>226</v>
+      </c>
+      <c r="E88" s="19">
         <v>22002.0</v>
       </c>
-      <c r="D88" s="36" t="s">
-        <v>226</v>
-      </c>
-      <c r="E88" s="28">
+      <c r="F88" s="39" t="s">
+        <v>133</v>
+      </c>
+      <c r="G88" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="H88" s="39"/>
+      <c r="I88" s="38" t="s">
+        <v>135</v>
+      </c>
+      <c r="J88" s="19">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="34" t="s">
+        <v>70</v>
+      </c>
+      <c r="B89" s="34" t="s">
+        <v>70</v>
+      </c>
+      <c r="C89" s="35">
+        <v>22002.0</v>
+      </c>
+      <c r="D89" s="36" t="s">
+        <v>227</v>
+      </c>
+      <c r="E89" s="28">
         <v>22003.0</v>
       </c>
-      <c r="F88" s="36" t="s">
-        <v>133</v>
-      </c>
-      <c r="G88" s="37" t="s">
-        <v>134</v>
-      </c>
-      <c r="H88" s="36"/>
-      <c r="I88" s="38" t="s">
-        <v>135</v>
-      </c>
-      <c r="J88" s="28">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="40" t="s">
-        <v>70</v>
-      </c>
-      <c r="B89" s="40" t="s">
-        <v>70</v>
-      </c>
-      <c r="C89" s="5">
-        <v>22003.0</v>
-      </c>
-      <c r="D89" s="39" t="s">
-        <v>227</v>
-      </c>
-      <c r="E89" s="19">
-        <v>22004.0</v>
-      </c>
-      <c r="F89" s="39" t="s">
+      <c r="F89" s="36" t="s">
         <v>133</v>
       </c>
       <c r="G89" s="37" t="s">
         <v>134</v>
       </c>
-      <c r="H89" s="39"/>
+      <c r="H89" s="36"/>
       <c r="I89" s="38" t="s">
         <v>135</v>
       </c>
-      <c r="J89" s="19">
+      <c r="J89" s="28">
         <v>0.0</v>
       </c>
     </row>
@@ -5186,25 +5186,25 @@
         <v>70</v>
       </c>
       <c r="C90" s="5">
+        <v>22003.0</v>
+      </c>
+      <c r="D90" s="39" t="s">
+        <v>228</v>
+      </c>
+      <c r="E90" s="19">
         <v>22004.0</v>
       </c>
-      <c r="D90" s="36" t="s">
-        <v>228</v>
-      </c>
-      <c r="E90" s="28">
-        <v>22005.0</v>
-      </c>
-      <c r="F90" s="36" t="s">
+      <c r="F90" s="39" t="s">
         <v>133</v>
       </c>
       <c r="G90" s="37" t="s">
         <v>134</v>
       </c>
-      <c r="H90" s="36"/>
+      <c r="H90" s="39"/>
       <c r="I90" s="38" t="s">
         <v>135</v>
       </c>
-      <c r="J90" s="28">
+      <c r="J90" s="19">
         <v>0.0</v>
       </c>
     </row>
@@ -5216,55 +5216,55 @@
         <v>70</v>
       </c>
       <c r="C91" s="5">
+        <v>22004.0</v>
+      </c>
+      <c r="D91" s="36" t="s">
+        <v>229</v>
+      </c>
+      <c r="E91" s="28">
         <v>22005.0</v>
       </c>
-      <c r="D91" s="39" t="s">
-        <v>229</v>
-      </c>
-      <c r="E91" s="26">
-        <v>-1.0</v>
-      </c>
-      <c r="F91" s="39" t="s">
+      <c r="F91" s="36" t="s">
         <v>133</v>
       </c>
       <c r="G91" s="37" t="s">
         <v>134</v>
       </c>
-      <c r="H91" s="39"/>
+      <c r="H91" s="36"/>
       <c r="I91" s="38" t="s">
         <v>135</v>
       </c>
-      <c r="J91" s="19">
+      <c r="J91" s="28">
         <v>0.0</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="40" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B92" s="40" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="C92" s="5">
-        <v>23001.0</v>
-      </c>
-      <c r="D92" s="36" t="s">
+        <v>22005.0</v>
+      </c>
+      <c r="D92" s="39" t="s">
         <v>230</v>
       </c>
-      <c r="E92" s="5">
-        <v>23002.0</v>
-      </c>
-      <c r="F92" s="36" t="s">
+      <c r="E92" s="26">
+        <v>-1.0</v>
+      </c>
+      <c r="F92" s="39" t="s">
         <v>133</v>
       </c>
       <c r="G92" s="37" t="s">
         <v>134</v>
       </c>
-      <c r="H92" s="36"/>
+      <c r="H92" s="39"/>
       <c r="I92" s="38" t="s">
         <v>135</v>
       </c>
-      <c r="J92" s="28">
+      <c r="J92" s="19">
         <v>0.0</v>
       </c>
     </row>
@@ -5276,25 +5276,25 @@
         <v>72</v>
       </c>
       <c r="C93" s="5">
+        <v>23001.0</v>
+      </c>
+      <c r="D93" s="36" t="s">
+        <v>231</v>
+      </c>
+      <c r="E93" s="5">
         <v>23002.0</v>
       </c>
-      <c r="D93" s="39" t="s">
-        <v>231</v>
-      </c>
-      <c r="E93" s="5">
-        <v>23003.0</v>
-      </c>
-      <c r="F93" s="39" t="s">
+      <c r="F93" s="36" t="s">
         <v>133</v>
       </c>
       <c r="G93" s="37" t="s">
         <v>134</v>
       </c>
-      <c r="H93" s="39"/>
+      <c r="H93" s="36"/>
       <c r="I93" s="38" t="s">
         <v>135</v>
       </c>
-      <c r="J93" s="19">
+      <c r="J93" s="28">
         <v>0.0</v>
       </c>
     </row>
@@ -5306,25 +5306,25 @@
         <v>72</v>
       </c>
       <c r="C94" s="5">
+        <v>23002.0</v>
+      </c>
+      <c r="D94" s="39" t="s">
+        <v>232</v>
+      </c>
+      <c r="E94" s="5">
         <v>23003.0</v>
       </c>
-      <c r="D94" s="36" t="s">
-        <v>232</v>
-      </c>
-      <c r="E94" s="5">
-        <v>23004.0</v>
-      </c>
-      <c r="F94" s="36" t="s">
+      <c r="F94" s="39" t="s">
         <v>133</v>
       </c>
       <c r="G94" s="37" t="s">
         <v>134</v>
       </c>
-      <c r="H94" s="36"/>
+      <c r="H94" s="39"/>
       <c r="I94" s="38" t="s">
         <v>135</v>
       </c>
-      <c r="J94" s="28">
+      <c r="J94" s="19">
         <v>0.0</v>
       </c>
     </row>
@@ -5336,55 +5336,55 @@
         <v>72</v>
       </c>
       <c r="C95" s="5">
+        <v>23003.0</v>
+      </c>
+      <c r="D95" s="36" t="s">
+        <v>233</v>
+      </c>
+      <c r="E95" s="5">
         <v>23004.0</v>
       </c>
-      <c r="D95" s="39" t="s">
-        <v>233</v>
-      </c>
-      <c r="E95" s="19">
-        <v>-1.0</v>
-      </c>
-      <c r="F95" s="39" t="s">
+      <c r="F95" s="36" t="s">
         <v>133</v>
       </c>
       <c r="G95" s="37" t="s">
         <v>134</v>
       </c>
-      <c r="H95" s="39"/>
+      <c r="H95" s="36"/>
       <c r="I95" s="38" t="s">
         <v>135</v>
       </c>
-      <c r="J95" s="19">
+      <c r="J95" s="28">
         <v>0.0</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="40" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B96" s="40" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C96" s="5">
-        <v>24001.0</v>
-      </c>
-      <c r="D96" s="36" t="s">
+        <v>23004.0</v>
+      </c>
+      <c r="D96" s="39" t="s">
         <v>234</v>
       </c>
-      <c r="E96" s="28">
-        <v>24002.0</v>
-      </c>
-      <c r="F96" s="36" t="s">
+      <c r="E96" s="19">
+        <v>-1.0</v>
+      </c>
+      <c r="F96" s="39" t="s">
         <v>133</v>
       </c>
       <c r="G96" s="37" t="s">
         <v>134</v>
       </c>
-      <c r="H96" s="36"/>
+      <c r="H96" s="39"/>
       <c r="I96" s="38" t="s">
         <v>135</v>
       </c>
-      <c r="J96" s="28">
+      <c r="J96" s="19">
         <v>0.0</v>
       </c>
     </row>
@@ -5396,25 +5396,25 @@
         <v>74</v>
       </c>
       <c r="C97" s="5">
+        <v>24001.0</v>
+      </c>
+      <c r="D97" s="36" t="s">
+        <v>235</v>
+      </c>
+      <c r="E97" s="28">
         <v>24002.0</v>
       </c>
-      <c r="D97" s="39" t="s">
-        <v>235</v>
-      </c>
-      <c r="E97" s="19">
-        <v>24003.0</v>
-      </c>
-      <c r="F97" s="39" t="s">
+      <c r="F97" s="36" t="s">
         <v>133</v>
       </c>
       <c r="G97" s="37" t="s">
         <v>134</v>
       </c>
-      <c r="H97" s="39"/>
+      <c r="H97" s="36"/>
       <c r="I97" s="38" t="s">
         <v>135</v>
       </c>
-      <c r="J97" s="19">
+      <c r="J97" s="28">
         <v>0.0</v>
       </c>
     </row>
@@ -5426,25 +5426,25 @@
         <v>74</v>
       </c>
       <c r="C98" s="5">
+        <v>24002.0</v>
+      </c>
+      <c r="D98" s="39" t="s">
+        <v>236</v>
+      </c>
+      <c r="E98" s="19">
         <v>24003.0</v>
       </c>
-      <c r="D98" s="36" t="s">
-        <v>236</v>
-      </c>
-      <c r="E98" s="28">
-        <v>24004.0</v>
-      </c>
-      <c r="F98" s="36" t="s">
+      <c r="F98" s="39" t="s">
         <v>133</v>
       </c>
       <c r="G98" s="37" t="s">
         <v>134</v>
       </c>
-      <c r="H98" s="36"/>
+      <c r="H98" s="39"/>
       <c r="I98" s="38" t="s">
         <v>135</v>
       </c>
-      <c r="J98" s="28">
+      <c r="J98" s="19">
         <v>0.0</v>
       </c>
     </row>
@@ -5456,25 +5456,25 @@
         <v>74</v>
       </c>
       <c r="C99" s="5">
+        <v>24003.0</v>
+      </c>
+      <c r="D99" s="36" t="s">
+        <v>237</v>
+      </c>
+      <c r="E99" s="28">
         <v>24004.0</v>
       </c>
-      <c r="D99" s="39" t="s">
-        <v>237</v>
-      </c>
-      <c r="E99" s="19">
-        <v>24005.0</v>
-      </c>
-      <c r="F99" s="39" t="s">
+      <c r="F99" s="36" t="s">
         <v>133</v>
       </c>
       <c r="G99" s="37" t="s">
         <v>134</v>
       </c>
-      <c r="H99" s="39"/>
+      <c r="H99" s="36"/>
       <c r="I99" s="38" t="s">
         <v>135</v>
       </c>
-      <c r="J99" s="19">
+      <c r="J99" s="28">
         <v>0.0</v>
       </c>
     </row>
@@ -5486,25 +5486,25 @@
         <v>74</v>
       </c>
       <c r="C100" s="5">
+        <v>24004.0</v>
+      </c>
+      <c r="D100" s="39" t="s">
+        <v>238</v>
+      </c>
+      <c r="E100" s="19">
         <v>24005.0</v>
       </c>
-      <c r="D100" s="36" t="s">
-        <v>238</v>
-      </c>
-      <c r="E100" s="28">
-        <v>24006.0</v>
-      </c>
-      <c r="F100" s="36" t="s">
+      <c r="F100" s="39" t="s">
         <v>133</v>
       </c>
       <c r="G100" s="37" t="s">
         <v>134</v>
       </c>
-      <c r="H100" s="36"/>
+      <c r="H100" s="39"/>
       <c r="I100" s="38" t="s">
         <v>135</v>
       </c>
-      <c r="J100" s="28">
+      <c r="J100" s="19">
         <v>0.0</v>
       </c>
     </row>
@@ -5516,25 +5516,25 @@
         <v>74</v>
       </c>
       <c r="C101" s="5">
+        <v>24005.0</v>
+      </c>
+      <c r="D101" s="36" t="s">
+        <v>239</v>
+      </c>
+      <c r="E101" s="28">
         <v>24006.0</v>
       </c>
-      <c r="D101" s="39" t="s">
-        <v>239</v>
-      </c>
-      <c r="E101" s="19">
-        <v>24007.0</v>
-      </c>
-      <c r="F101" s="39" t="s">
+      <c r="F101" s="36" t="s">
         <v>133</v>
       </c>
       <c r="G101" s="37" t="s">
         <v>134</v>
       </c>
-      <c r="H101" s="39"/>
+      <c r="H101" s="36"/>
       <c r="I101" s="38" t="s">
         <v>135</v>
       </c>
-      <c r="J101" s="19">
+      <c r="J101" s="28">
         <v>0.0</v>
       </c>
     </row>
@@ -5546,25 +5546,25 @@
         <v>74</v>
       </c>
       <c r="C102" s="5">
+        <v>24006.0</v>
+      </c>
+      <c r="D102" s="39" t="s">
+        <v>240</v>
+      </c>
+      <c r="E102" s="19">
         <v>24007.0</v>
       </c>
-      <c r="D102" s="36" t="s">
-        <v>240</v>
-      </c>
-      <c r="E102" s="28">
-        <v>24008.0</v>
-      </c>
-      <c r="F102" s="36" t="s">
+      <c r="F102" s="39" t="s">
         <v>133</v>
       </c>
       <c r="G102" s="37" t="s">
         <v>134</v>
       </c>
-      <c r="H102" s="36"/>
+      <c r="H102" s="39"/>
       <c r="I102" s="38" t="s">
         <v>135</v>
       </c>
-      <c r="J102" s="28">
+      <c r="J102" s="19">
         <v>0.0</v>
       </c>
     </row>
@@ -5576,56 +5576,56 @@
         <v>74</v>
       </c>
       <c r="C103" s="5">
+        <v>24007.0</v>
+      </c>
+      <c r="D103" s="36" t="s">
+        <v>241</v>
+      </c>
+      <c r="E103" s="28">
         <v>24008.0</v>
       </c>
-      <c r="D103" s="39" t="s">
-        <v>241</v>
-      </c>
-      <c r="E103" s="19">
-        <v>-1.0</v>
-      </c>
-      <c r="F103" s="39" t="s">
+      <c r="F103" s="36" t="s">
         <v>133</v>
       </c>
       <c r="G103" s="37" t="s">
         <v>134</v>
       </c>
-      <c r="H103" s="39"/>
+      <c r="H103" s="36"/>
       <c r="I103" s="38" t="s">
         <v>135</v>
       </c>
-      <c r="J103" s="19">
+      <c r="J103" s="28">
         <v>0.0</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="40" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B104" s="40" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C104" s="5">
-        <v>25001.0</v>
-      </c>
-      <c r="D104" s="36" t="s">
+        <v>24008.0</v>
+      </c>
+      <c r="D104" s="39" t="s">
         <v>242</v>
       </c>
-      <c r="E104" s="28">
-        <v>25002.0</v>
-      </c>
-      <c r="F104" s="36" t="s">
-        <v>175</v>
-      </c>
-      <c r="G104" s="36" t="s">
-        <v>140</v>
-      </c>
-      <c r="H104" s="36"/>
-      <c r="I104" s="36" t="s">
-        <v>164</v>
-      </c>
-      <c r="J104" s="41">
+      <c r="E104" s="19">
         <v>-1.0</v>
+      </c>
+      <c r="F104" s="39" t="s">
+        <v>133</v>
+      </c>
+      <c r="G104" s="37" t="s">
+        <v>134</v>
+      </c>
+      <c r="H104" s="39"/>
+      <c r="I104" s="38" t="s">
+        <v>135</v>
+      </c>
+      <c r="J104" s="19">
+        <v>0.0</v>
       </c>
     </row>
     <row r="105">
@@ -5636,26 +5636,26 @@
         <v>76</v>
       </c>
       <c r="C105" s="5">
+        <v>25001.0</v>
+      </c>
+      <c r="D105" s="36" t="s">
+        <v>243</v>
+      </c>
+      <c r="E105" s="28">
         <v>25002.0</v>
       </c>
-      <c r="D105" s="39" t="s">
-        <v>243</v>
-      </c>
-      <c r="E105" s="19">
-        <v>25003.0</v>
-      </c>
-      <c r="F105" s="39" t="s">
-        <v>133</v>
-      </c>
-      <c r="G105" s="39" t="s">
-        <v>134</v>
-      </c>
-      <c r="H105" s="39"/>
-      <c r="I105" s="38" t="s">
-        <v>135</v>
-      </c>
-      <c r="J105" s="19">
-        <v>0.0</v>
+      <c r="F105" s="36" t="s">
+        <v>175</v>
+      </c>
+      <c r="G105" s="36" t="s">
+        <v>140</v>
+      </c>
+      <c r="H105" s="36"/>
+      <c r="I105" s="36" t="s">
+        <v>164</v>
+      </c>
+      <c r="J105" s="41">
+        <v>-1.0</v>
       </c>
     </row>
     <row r="106">
@@ -5666,26 +5666,26 @@
         <v>76</v>
       </c>
       <c r="C106" s="5">
+        <v>25002.0</v>
+      </c>
+      <c r="D106" s="39" t="s">
+        <v>244</v>
+      </c>
+      <c r="E106" s="19">
         <v>25003.0</v>
       </c>
-      <c r="D106" s="36" t="s">
-        <v>244</v>
-      </c>
-      <c r="E106" s="28">
-        <v>25004.0</v>
-      </c>
-      <c r="F106" s="36" t="s">
-        <v>175</v>
-      </c>
-      <c r="G106" s="36" t="s">
-        <v>140</v>
-      </c>
-      <c r="H106" s="36"/>
-      <c r="I106" s="36" t="s">
-        <v>164</v>
-      </c>
-      <c r="J106" s="41">
-        <v>-1.0</v>
+      <c r="F106" s="39" t="s">
+        <v>133</v>
+      </c>
+      <c r="G106" s="39" t="s">
+        <v>134</v>
+      </c>
+      <c r="H106" s="39"/>
+      <c r="I106" s="38" t="s">
+        <v>135</v>
+      </c>
+      <c r="J106" s="19">
+        <v>0.0</v>
       </c>
     </row>
     <row r="107">
@@ -5696,26 +5696,26 @@
         <v>76</v>
       </c>
       <c r="C107" s="5">
+        <v>25003.0</v>
+      </c>
+      <c r="D107" s="36" t="s">
+        <v>245</v>
+      </c>
+      <c r="E107" s="28">
         <v>25004.0</v>
       </c>
-      <c r="D107" s="39" t="s">
-        <v>245</v>
-      </c>
-      <c r="E107" s="19">
-        <v>25005.0</v>
-      </c>
-      <c r="F107" s="39" t="s">
-        <v>133</v>
-      </c>
-      <c r="G107" s="39" t="s">
-        <v>134</v>
-      </c>
-      <c r="H107" s="39"/>
-      <c r="I107" s="38" t="s">
-        <v>135</v>
-      </c>
-      <c r="J107" s="19">
-        <v>0.0</v>
+      <c r="F107" s="36" t="s">
+        <v>175</v>
+      </c>
+      <c r="G107" s="36" t="s">
+        <v>140</v>
+      </c>
+      <c r="H107" s="36"/>
+      <c r="I107" s="36" t="s">
+        <v>164</v>
+      </c>
+      <c r="J107" s="41">
+        <v>-1.0</v>
       </c>
     </row>
     <row r="108">
@@ -5726,25 +5726,25 @@
         <v>76</v>
       </c>
       <c r="C108" s="5">
+        <v>25004.0</v>
+      </c>
+      <c r="D108" s="39" t="s">
+        <v>246</v>
+      </c>
+      <c r="E108" s="19">
         <v>25005.0</v>
       </c>
-      <c r="D108" s="36" t="s">
-        <v>246</v>
-      </c>
-      <c r="E108" s="28">
-        <v>25006.0</v>
-      </c>
-      <c r="F108" s="36" t="s">
-        <v>133</v>
-      </c>
-      <c r="G108" s="36" t="s">
-        <v>134</v>
-      </c>
-      <c r="H108" s="36"/>
+      <c r="F108" s="39" t="s">
+        <v>133</v>
+      </c>
+      <c r="G108" s="39" t="s">
+        <v>134</v>
+      </c>
+      <c r="H108" s="39"/>
       <c r="I108" s="38" t="s">
         <v>135</v>
       </c>
-      <c r="J108" s="28">
+      <c r="J108" s="19">
         <v>0.0</v>
       </c>
     </row>
@@ -5756,85 +5756,85 @@
         <v>76</v>
       </c>
       <c r="C109" s="5">
+        <v>25005.0</v>
+      </c>
+      <c r="D109" s="36" t="s">
+        <v>247</v>
+      </c>
+      <c r="E109" s="28">
         <v>25006.0</v>
       </c>
-      <c r="D109" s="39" t="s">
-        <v>247</v>
-      </c>
-      <c r="E109" s="19">
-        <v>-1.0</v>
-      </c>
-      <c r="F109" s="39" t="s">
-        <v>133</v>
-      </c>
-      <c r="G109" s="39" t="s">
-        <v>134</v>
-      </c>
-      <c r="H109" s="39"/>
+      <c r="F109" s="36" t="s">
+        <v>133</v>
+      </c>
+      <c r="G109" s="36" t="s">
+        <v>134</v>
+      </c>
+      <c r="H109" s="36"/>
       <c r="I109" s="38" t="s">
         <v>135</v>
       </c>
-      <c r="J109" s="19">
+      <c r="J109" s="28">
         <v>0.0</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="40" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B110" s="40" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C110" s="5">
-        <v>26001.0</v>
-      </c>
-      <c r="D110" s="36" t="s">
+        <v>25006.0</v>
+      </c>
+      <c r="D110" s="39" t="s">
         <v>248</v>
       </c>
-      <c r="E110" s="28">
+      <c r="E110" s="19">
         <v>-1.0</v>
       </c>
-      <c r="F110" s="36" t="s">
-        <v>133</v>
-      </c>
-      <c r="G110" s="36" t="s">
-        <v>134</v>
-      </c>
-      <c r="H110" s="36"/>
-      <c r="I110" s="36" t="s">
-        <v>164</v>
-      </c>
-      <c r="J110" s="28">
+      <c r="F110" s="39" t="s">
+        <v>133</v>
+      </c>
+      <c r="G110" s="39" t="s">
+        <v>134</v>
+      </c>
+      <c r="H110" s="39"/>
+      <c r="I110" s="38" t="s">
+        <v>135</v>
+      </c>
+      <c r="J110" s="19">
         <v>0.0</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="40" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B111" s="40" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C111" s="5">
-        <v>27001.0</v>
-      </c>
-      <c r="D111" s="39" t="s">
+        <v>26001.0</v>
+      </c>
+      <c r="D111" s="36" t="s">
         <v>249</v>
       </c>
-      <c r="E111" s="19">
-        <v>27002.0</v>
-      </c>
-      <c r="F111" s="39" t="s">
-        <v>133</v>
-      </c>
-      <c r="G111" s="39" t="s">
-        <v>134</v>
-      </c>
-      <c r="H111" s="39"/>
-      <c r="I111" s="38" t="s">
-        <v>135</v>
-      </c>
-      <c r="J111" s="19">
+      <c r="E111" s="28">
+        <v>-1.0</v>
+      </c>
+      <c r="F111" s="36" t="s">
+        <v>133</v>
+      </c>
+      <c r="G111" s="36" t="s">
+        <v>134</v>
+      </c>
+      <c r="H111" s="36"/>
+      <c r="I111" s="36" t="s">
+        <v>164</v>
+      </c>
+      <c r="J111" s="28">
         <v>0.0</v>
       </c>
     </row>
@@ -5846,25 +5846,25 @@
         <v>80</v>
       </c>
       <c r="C112" s="5">
+        <v>27001.0</v>
+      </c>
+      <c r="D112" s="39" t="s">
+        <v>250</v>
+      </c>
+      <c r="E112" s="19">
         <v>27002.0</v>
       </c>
-      <c r="D112" s="36" t="s">
-        <v>250</v>
-      </c>
-      <c r="E112" s="28">
-        <v>27003.0</v>
-      </c>
-      <c r="F112" s="36" t="s">
-        <v>133</v>
-      </c>
-      <c r="G112" s="36" t="s">
-        <v>134</v>
-      </c>
-      <c r="H112" s="36"/>
+      <c r="F112" s="39" t="s">
+        <v>133</v>
+      </c>
+      <c r="G112" s="39" t="s">
+        <v>134</v>
+      </c>
+      <c r="H112" s="39"/>
       <c r="I112" s="38" t="s">
         <v>135</v>
       </c>
-      <c r="J112" s="28">
+      <c r="J112" s="19">
         <v>0.0</v>
       </c>
     </row>
@@ -5876,56 +5876,56 @@
         <v>80</v>
       </c>
       <c r="C113" s="5">
+        <v>27002.0</v>
+      </c>
+      <c r="D113" s="36" t="s">
+        <v>251</v>
+      </c>
+      <c r="E113" s="28">
         <v>27003.0</v>
       </c>
-      <c r="D113" s="39" t="s">
-        <v>251</v>
-      </c>
-      <c r="E113" s="19">
-        <v>-1.0</v>
-      </c>
-      <c r="F113" s="39" t="s">
-        <v>133</v>
-      </c>
-      <c r="G113" s="39" t="s">
-        <v>134</v>
-      </c>
-      <c r="H113" s="39"/>
+      <c r="F113" s="36" t="s">
+        <v>133</v>
+      </c>
+      <c r="G113" s="36" t="s">
+        <v>134</v>
+      </c>
+      <c r="H113" s="36"/>
       <c r="I113" s="38" t="s">
         <v>135</v>
       </c>
-      <c r="J113" s="19">
+      <c r="J113" s="28">
         <v>0.0</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="40" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B114" s="40" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C114" s="5">
-        <v>28001.0</v>
-      </c>
-      <c r="D114" s="36" t="s">
+        <v>27003.0</v>
+      </c>
+      <c r="D114" s="39" t="s">
         <v>252</v>
       </c>
-      <c r="E114" s="28">
-        <v>28002.0</v>
-      </c>
-      <c r="F114" s="36" t="s">
-        <v>175</v>
-      </c>
-      <c r="G114" s="36" t="s">
-        <v>253</v>
-      </c>
-      <c r="H114" s="36"/>
-      <c r="I114" s="36" t="s">
-        <v>164</v>
-      </c>
-      <c r="J114" s="41">
+      <c r="E114" s="19">
         <v>-1.0</v>
+      </c>
+      <c r="F114" s="39" t="s">
+        <v>133</v>
+      </c>
+      <c r="G114" s="39" t="s">
+        <v>134</v>
+      </c>
+      <c r="H114" s="39"/>
+      <c r="I114" s="38" t="s">
+        <v>135</v>
+      </c>
+      <c r="J114" s="19">
+        <v>0.0</v>
       </c>
     </row>
     <row r="115">
@@ -5936,22 +5936,22 @@
         <v>82</v>
       </c>
       <c r="C115" s="5">
+        <v>28001.0</v>
+      </c>
+      <c r="D115" s="36" t="s">
+        <v>253</v>
+      </c>
+      <c r="E115" s="28">
         <v>28002.0</v>
       </c>
-      <c r="D115" s="39" t="s">
+      <c r="F115" s="36" t="s">
+        <v>175</v>
+      </c>
+      <c r="G115" s="36" t="s">
         <v>254</v>
       </c>
-      <c r="E115" s="19">
-        <v>28003.0</v>
-      </c>
-      <c r="F115" s="39" t="s">
-        <v>175</v>
-      </c>
-      <c r="G115" s="39" t="s">
-        <v>255</v>
-      </c>
-      <c r="H115" s="39"/>
-      <c r="I115" s="39" t="s">
+      <c r="H115" s="36"/>
+      <c r="I115" s="36" t="s">
         <v>164</v>
       </c>
       <c r="J115" s="41">
@@ -5966,85 +5966,85 @@
         <v>82</v>
       </c>
       <c r="C116" s="5">
+        <v>28002.0</v>
+      </c>
+      <c r="D116" s="39" t="s">
+        <v>255</v>
+      </c>
+      <c r="E116" s="19">
         <v>28003.0</v>
       </c>
-      <c r="D116" s="36" t="s">
+      <c r="F116" s="39" t="s">
+        <v>175</v>
+      </c>
+      <c r="G116" s="39" t="s">
         <v>256</v>
       </c>
-      <c r="E116" s="28">
+      <c r="H116" s="39"/>
+      <c r="I116" s="39" t="s">
+        <v>164</v>
+      </c>
+      <c r="J116" s="41">
         <v>-1.0</v>
-      </c>
-      <c r="F116" s="36" t="s">
-        <v>133</v>
-      </c>
-      <c r="G116" s="36" t="s">
-        <v>134</v>
-      </c>
-      <c r="H116" s="36"/>
-      <c r="I116" s="38" t="s">
-        <v>135</v>
-      </c>
-      <c r="J116" s="28">
-        <v>0.0</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="40" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B117" s="40" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C117" s="5">
-        <v>29001.0</v>
-      </c>
-      <c r="D117" s="39" t="s">
+        <v>28003.0</v>
+      </c>
+      <c r="D117" s="36" t="s">
         <v>257</v>
       </c>
-      <c r="E117" s="19">
+      <c r="E117" s="28">
         <v>-1.0</v>
       </c>
-      <c r="F117" s="39" t="s">
-        <v>133</v>
-      </c>
-      <c r="G117" s="39" t="s">
-        <v>134</v>
-      </c>
-      <c r="H117" s="39"/>
+      <c r="F117" s="36" t="s">
+        <v>133</v>
+      </c>
+      <c r="G117" s="36" t="s">
+        <v>134</v>
+      </c>
+      <c r="H117" s="36"/>
       <c r="I117" s="38" t="s">
         <v>135</v>
       </c>
-      <c r="J117" s="19">
+      <c r="J117" s="28">
         <v>0.0</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="40" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B118" s="40" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="C118" s="5">
-        <v>30001.0</v>
-      </c>
-      <c r="D118" s="36" t="s">
+        <v>29001.0</v>
+      </c>
+      <c r="D118" s="39" t="s">
         <v>258</v>
       </c>
-      <c r="E118" s="28">
-        <v>30002.0</v>
-      </c>
-      <c r="F118" s="36" t="s">
-        <v>133</v>
-      </c>
-      <c r="G118" s="36" t="s">
-        <v>134</v>
-      </c>
-      <c r="H118" s="36"/>
+      <c r="E118" s="19">
+        <v>-1.0</v>
+      </c>
+      <c r="F118" s="39" t="s">
+        <v>133</v>
+      </c>
+      <c r="G118" s="39" t="s">
+        <v>134</v>
+      </c>
+      <c r="H118" s="39"/>
       <c r="I118" s="38" t="s">
         <v>135</v>
       </c>
-      <c r="J118" s="28">
+      <c r="J118" s="19">
         <v>0.0</v>
       </c>
     </row>
@@ -6056,25 +6056,25 @@
         <v>86</v>
       </c>
       <c r="C119" s="5">
+        <v>30001.0</v>
+      </c>
+      <c r="D119" s="36" t="s">
+        <v>259</v>
+      </c>
+      <c r="E119" s="28">
         <v>30002.0</v>
       </c>
-      <c r="D119" s="39" t="s">
-        <v>259</v>
-      </c>
-      <c r="E119" s="19">
-        <v>30003.0</v>
-      </c>
-      <c r="F119" s="39" t="s">
-        <v>133</v>
-      </c>
-      <c r="G119" s="39" t="s">
-        <v>134</v>
-      </c>
-      <c r="H119" s="39"/>
+      <c r="F119" s="36" t="s">
+        <v>133</v>
+      </c>
+      <c r="G119" s="36" t="s">
+        <v>134</v>
+      </c>
+      <c r="H119" s="36"/>
       <c r="I119" s="38" t="s">
         <v>135</v>
       </c>
-      <c r="J119" s="19">
+      <c r="J119" s="28">
         <v>0.0</v>
       </c>
     </row>
@@ -6086,55 +6086,55 @@
         <v>86</v>
       </c>
       <c r="C120" s="5">
+        <v>30002.0</v>
+      </c>
+      <c r="D120" s="39" t="s">
+        <v>260</v>
+      </c>
+      <c r="E120" s="19">
         <v>30003.0</v>
       </c>
-      <c r="D120" s="36" t="s">
-        <v>260</v>
-      </c>
-      <c r="E120" s="28">
-        <v>-1.0</v>
-      </c>
-      <c r="F120" s="36" t="s">
-        <v>133</v>
-      </c>
-      <c r="G120" s="36" t="s">
-        <v>134</v>
-      </c>
-      <c r="H120" s="36"/>
+      <c r="F120" s="39" t="s">
+        <v>133</v>
+      </c>
+      <c r="G120" s="39" t="s">
+        <v>134</v>
+      </c>
+      <c r="H120" s="39"/>
       <c r="I120" s="38" t="s">
         <v>135</v>
       </c>
-      <c r="J120" s="28">
+      <c r="J120" s="19">
         <v>0.0</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="40" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B121" s="40" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C121" s="5">
-        <v>31001.0</v>
-      </c>
-      <c r="D121" s="39" t="s">
+        <v>30003.0</v>
+      </c>
+      <c r="D121" s="36" t="s">
         <v>261</v>
       </c>
-      <c r="E121" s="19">
-        <v>31002.0</v>
-      </c>
-      <c r="F121" s="39" t="s">
-        <v>133</v>
-      </c>
-      <c r="G121" s="39" t="s">
-        <v>134</v>
-      </c>
-      <c r="H121" s="39"/>
+      <c r="E121" s="28">
+        <v>-1.0</v>
+      </c>
+      <c r="F121" s="36" t="s">
+        <v>133</v>
+      </c>
+      <c r="G121" s="36" t="s">
+        <v>134</v>
+      </c>
+      <c r="H121" s="36"/>
       <c r="I121" s="38" t="s">
         <v>135</v>
       </c>
-      <c r="J121" s="19">
+      <c r="J121" s="28">
         <v>0.0</v>
       </c>
     </row>
@@ -6146,56 +6146,56 @@
         <v>88</v>
       </c>
       <c r="C122" s="5">
+        <v>31001.0</v>
+      </c>
+      <c r="D122" s="39" t="s">
+        <v>262</v>
+      </c>
+      <c r="E122" s="19">
         <v>31002.0</v>
       </c>
-      <c r="D122" s="36" t="s">
-        <v>262</v>
-      </c>
-      <c r="E122" s="28">
-        <v>-1.0</v>
-      </c>
-      <c r="F122" s="36" t="s">
-        <v>133</v>
-      </c>
-      <c r="G122" s="36" t="s">
-        <v>134</v>
-      </c>
-      <c r="H122" s="36"/>
+      <c r="F122" s="39" t="s">
+        <v>133</v>
+      </c>
+      <c r="G122" s="39" t="s">
+        <v>134</v>
+      </c>
+      <c r="H122" s="39"/>
       <c r="I122" s="38" t="s">
         <v>135</v>
       </c>
-      <c r="J122" s="28">
+      <c r="J122" s="19">
         <v>0.0</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="40" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B123" s="40" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="C123" s="5">
-        <v>32001.0</v>
-      </c>
-      <c r="D123" s="39" t="s">
+        <v>31002.0</v>
+      </c>
+      <c r="D123" s="36" t="s">
         <v>263</v>
       </c>
-      <c r="E123" s="19">
-        <v>32002.0</v>
-      </c>
-      <c r="F123" s="39" t="s">
-        <v>175</v>
-      </c>
-      <c r="G123" s="39" t="s">
-        <v>140</v>
-      </c>
-      <c r="H123" s="39"/>
-      <c r="I123" s="39" t="s">
-        <v>164</v>
-      </c>
-      <c r="J123" s="41">
+      <c r="E123" s="28">
         <v>-1.0</v>
+      </c>
+      <c r="F123" s="36" t="s">
+        <v>133</v>
+      </c>
+      <c r="G123" s="36" t="s">
+        <v>134</v>
+      </c>
+      <c r="H123" s="36"/>
+      <c r="I123" s="38" t="s">
+        <v>135</v>
+      </c>
+      <c r="J123" s="28">
+        <v>0.0</v>
       </c>
     </row>
     <row r="124">
@@ -6206,22 +6206,22 @@
         <v>90</v>
       </c>
       <c r="C124" s="5">
+        <v>32001.0</v>
+      </c>
+      <c r="D124" s="39" t="s">
+        <v>264</v>
+      </c>
+      <c r="E124" s="19">
         <v>32002.0</v>
       </c>
-      <c r="D124" s="36" t="s">
-        <v>264</v>
-      </c>
-      <c r="E124" s="28">
-        <v>32003.0</v>
-      </c>
-      <c r="F124" s="36" t="s">
+      <c r="F124" s="39" t="s">
         <v>175</v>
       </c>
-      <c r="G124" s="36" t="s">
+      <c r="G124" s="39" t="s">
         <v>140</v>
       </c>
-      <c r="H124" s="36"/>
-      <c r="I124" s="36" t="s">
+      <c r="H124" s="39"/>
+      <c r="I124" s="39" t="s">
         <v>164</v>
       </c>
       <c r="J124" s="41">
@@ -6236,22 +6236,22 @@
         <v>90</v>
       </c>
       <c r="C125" s="5">
+        <v>32002.0</v>
+      </c>
+      <c r="D125" s="36" t="s">
+        <v>265</v>
+      </c>
+      <c r="E125" s="28">
         <v>32003.0</v>
       </c>
-      <c r="D125" s="39" t="s">
-        <v>265</v>
-      </c>
-      <c r="E125" s="19">
-        <v>32004.0</v>
-      </c>
-      <c r="F125" s="39" t="s">
+      <c r="F125" s="36" t="s">
         <v>175</v>
       </c>
-      <c r="G125" s="39" t="s">
+      <c r="G125" s="36" t="s">
         <v>140</v>
       </c>
-      <c r="H125" s="39"/>
-      <c r="I125" s="39" t="s">
+      <c r="H125" s="36"/>
+      <c r="I125" s="36" t="s">
         <v>164</v>
       </c>
       <c r="J125" s="41">
@@ -6266,26 +6266,26 @@
         <v>90</v>
       </c>
       <c r="C126" s="5">
+        <v>32003.0</v>
+      </c>
+      <c r="D126" s="39" t="s">
+        <v>266</v>
+      </c>
+      <c r="E126" s="19">
         <v>32004.0</v>
       </c>
-      <c r="D126" s="36" t="s">
-        <v>266</v>
-      </c>
-      <c r="E126" s="28">
-        <v>32005.0</v>
-      </c>
-      <c r="F126" s="36" t="s">
-        <v>133</v>
-      </c>
-      <c r="G126" s="36" t="s">
-        <v>134</v>
-      </c>
-      <c r="H126" s="36"/>
-      <c r="I126" s="38" t="s">
-        <v>135</v>
-      </c>
-      <c r="J126" s="28">
-        <v>0.0</v>
+      <c r="F126" s="39" t="s">
+        <v>175</v>
+      </c>
+      <c r="G126" s="39" t="s">
+        <v>140</v>
+      </c>
+      <c r="H126" s="39"/>
+      <c r="I126" s="39" t="s">
+        <v>164</v>
+      </c>
+      <c r="J126" s="41">
+        <v>-1.0</v>
       </c>
     </row>
     <row r="127">
@@ -6296,25 +6296,25 @@
         <v>90</v>
       </c>
       <c r="C127" s="5">
+        <v>32004.0</v>
+      </c>
+      <c r="D127" s="36" t="s">
+        <v>267</v>
+      </c>
+      <c r="E127" s="28">
         <v>32005.0</v>
       </c>
-      <c r="D127" s="39" t="s">
-        <v>267</v>
-      </c>
-      <c r="E127" s="19">
-        <v>32006.0</v>
-      </c>
-      <c r="F127" s="39" t="s">
-        <v>133</v>
-      </c>
-      <c r="G127" s="39" t="s">
-        <v>134</v>
-      </c>
-      <c r="H127" s="39"/>
+      <c r="F127" s="36" t="s">
+        <v>133</v>
+      </c>
+      <c r="G127" s="36" t="s">
+        <v>134</v>
+      </c>
+      <c r="H127" s="36"/>
       <c r="I127" s="38" t="s">
         <v>135</v>
       </c>
-      <c r="J127" s="19">
+      <c r="J127" s="28">
         <v>0.0</v>
       </c>
     </row>
@@ -6326,55 +6326,55 @@
         <v>90</v>
       </c>
       <c r="C128" s="5">
+        <v>32005.0</v>
+      </c>
+      <c r="D128" s="39" t="s">
+        <v>268</v>
+      </c>
+      <c r="E128" s="19">
         <v>32006.0</v>
       </c>
-      <c r="D128" s="36" t="s">
-        <v>268</v>
-      </c>
-      <c r="E128" s="28">
-        <v>-1.0</v>
-      </c>
-      <c r="F128" s="36" t="s">
-        <v>133</v>
-      </c>
-      <c r="G128" s="36" t="s">
-        <v>134</v>
-      </c>
-      <c r="H128" s="36"/>
+      <c r="F128" s="39" t="s">
+        <v>133</v>
+      </c>
+      <c r="G128" s="39" t="s">
+        <v>134</v>
+      </c>
+      <c r="H128" s="39"/>
       <c r="I128" s="38" t="s">
         <v>135</v>
       </c>
-      <c r="J128" s="28">
+      <c r="J128" s="19">
         <v>0.0</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="40" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B129" s="40" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="C129" s="5">
-        <v>33001.0</v>
-      </c>
-      <c r="D129" s="39" t="s">
+        <v>32006.0</v>
+      </c>
+      <c r="D129" s="36" t="s">
         <v>269</v>
       </c>
-      <c r="E129" s="19">
-        <v>33002.0</v>
-      </c>
-      <c r="F129" s="39" t="s">
-        <v>133</v>
-      </c>
-      <c r="G129" s="39" t="s">
-        <v>134</v>
-      </c>
-      <c r="H129" s="39"/>
+      <c r="E129" s="28">
+        <v>-1.0</v>
+      </c>
+      <c r="F129" s="36" t="s">
+        <v>133</v>
+      </c>
+      <c r="G129" s="36" t="s">
+        <v>134</v>
+      </c>
+      <c r="H129" s="36"/>
       <c r="I129" s="38" t="s">
         <v>135</v>
       </c>
-      <c r="J129" s="19">
+      <c r="J129" s="28">
         <v>0.0</v>
       </c>
     </row>
@@ -6386,56 +6386,56 @@
         <v>92</v>
       </c>
       <c r="C130" s="5">
+        <v>33001.0</v>
+      </c>
+      <c r="D130" s="39" t="s">
+        <v>270</v>
+      </c>
+      <c r="E130" s="19">
         <v>33002.0</v>
       </c>
-      <c r="D130" s="36" t="s">
-        <v>270</v>
-      </c>
-      <c r="E130" s="28">
-        <v>-1.0</v>
-      </c>
-      <c r="F130" s="36" t="s">
-        <v>133</v>
-      </c>
-      <c r="G130" s="36" t="s">
-        <v>134</v>
-      </c>
-      <c r="H130" s="36"/>
+      <c r="F130" s="39" t="s">
+        <v>133</v>
+      </c>
+      <c r="G130" s="39" t="s">
+        <v>134</v>
+      </c>
+      <c r="H130" s="39"/>
       <c r="I130" s="38" t="s">
         <v>135</v>
       </c>
-      <c r="J130" s="28">
+      <c r="J130" s="19">
         <v>0.0</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="40" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B131" s="40" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C131" s="5">
-        <v>34001.0</v>
-      </c>
-      <c r="D131" s="39" t="s">
+        <v>33002.0</v>
+      </c>
+      <c r="D131" s="36" t="s">
         <v>271</v>
       </c>
-      <c r="E131" s="19">
-        <v>34002.0</v>
-      </c>
-      <c r="F131" s="39" t="s">
-        <v>175</v>
-      </c>
-      <c r="G131" s="39" t="s">
-        <v>272</v>
-      </c>
-      <c r="H131" s="39"/>
-      <c r="I131" s="39" t="s">
-        <v>164</v>
-      </c>
-      <c r="J131" s="41">
+      <c r="E131" s="28">
         <v>-1.0</v>
+      </c>
+      <c r="F131" s="36" t="s">
+        <v>133</v>
+      </c>
+      <c r="G131" s="36" t="s">
+        <v>134</v>
+      </c>
+      <c r="H131" s="36"/>
+      <c r="I131" s="38" t="s">
+        <v>135</v>
+      </c>
+      <c r="J131" s="28">
+        <v>0.0</v>
       </c>
     </row>
     <row r="132">
@@ -6446,22 +6446,22 @@
         <v>94</v>
       </c>
       <c r="C132" s="5">
+        <v>34001.0</v>
+      </c>
+      <c r="D132" s="39" t="s">
+        <v>272</v>
+      </c>
+      <c r="E132" s="19">
         <v>34002.0</v>
       </c>
-      <c r="D132" s="36" t="s">
+      <c r="F132" s="39" t="s">
+        <v>175</v>
+      </c>
+      <c r="G132" s="39" t="s">
         <v>273</v>
       </c>
-      <c r="E132" s="28">
-        <v>34003.0</v>
-      </c>
-      <c r="F132" s="36" t="s">
-        <v>175</v>
-      </c>
-      <c r="G132" s="36" t="s">
-        <v>272</v>
-      </c>
-      <c r="H132" s="36"/>
-      <c r="I132" s="36" t="s">
+      <c r="H132" s="39"/>
+      <c r="I132" s="39" t="s">
         <v>164</v>
       </c>
       <c r="J132" s="41">
@@ -6476,85 +6476,85 @@
         <v>94</v>
       </c>
       <c r="C133" s="5">
+        <v>34002.0</v>
+      </c>
+      <c r="D133" s="36" t="s">
+        <v>274</v>
+      </c>
+      <c r="E133" s="28">
         <v>34003.0</v>
       </c>
-      <c r="D133" s="39" t="s">
-        <v>274</v>
-      </c>
-      <c r="E133" s="19">
+      <c r="F133" s="36" t="s">
+        <v>175</v>
+      </c>
+      <c r="G133" s="36" t="s">
+        <v>273</v>
+      </c>
+      <c r="H133" s="36"/>
+      <c r="I133" s="36" t="s">
+        <v>164</v>
+      </c>
+      <c r="J133" s="41">
         <v>-1.0</v>
-      </c>
-      <c r="F133" s="39" t="s">
-        <v>133</v>
-      </c>
-      <c r="G133" s="39" t="s">
-        <v>134</v>
-      </c>
-      <c r="H133" s="39"/>
-      <c r="I133" s="38" t="s">
-        <v>135</v>
-      </c>
-      <c r="J133" s="19">
-        <v>0.0</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="40" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="B134" s="40" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="C134" s="5">
-        <v>35001.0</v>
-      </c>
-      <c r="D134" s="36" t="s">
+        <v>34003.0</v>
+      </c>
+      <c r="D134" s="39" t="s">
         <v>275</v>
       </c>
-      <c r="E134" s="28">
+      <c r="E134" s="19">
         <v>-1.0</v>
       </c>
-      <c r="F134" s="36" t="s">
-        <v>133</v>
-      </c>
-      <c r="G134" s="36" t="s">
-        <v>134</v>
-      </c>
-      <c r="H134" s="36"/>
+      <c r="F134" s="39" t="s">
+        <v>133</v>
+      </c>
+      <c r="G134" s="39" t="s">
+        <v>134</v>
+      </c>
+      <c r="H134" s="39"/>
       <c r="I134" s="38" t="s">
         <v>135</v>
       </c>
-      <c r="J134" s="28">
+      <c r="J134" s="19">
         <v>0.0</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="40" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B135" s="40" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="C135" s="5">
-        <v>36001.0</v>
-      </c>
-      <c r="D135" s="39" t="s">
+        <v>35001.0</v>
+      </c>
+      <c r="D135" s="36" t="s">
         <v>276</v>
       </c>
-      <c r="E135" s="19">
-        <v>36002.0</v>
-      </c>
-      <c r="F135" s="39" t="s">
-        <v>133</v>
-      </c>
-      <c r="G135" s="39" t="s">
-        <v>134</v>
-      </c>
-      <c r="H135" s="39"/>
+      <c r="E135" s="28">
+        <v>-1.0</v>
+      </c>
+      <c r="F135" s="36" t="s">
+        <v>133</v>
+      </c>
+      <c r="G135" s="36" t="s">
+        <v>134</v>
+      </c>
+      <c r="H135" s="36"/>
       <c r="I135" s="38" t="s">
         <v>135</v>
       </c>
-      <c r="J135" s="19">
+      <c r="J135" s="28">
         <v>0.0</v>
       </c>
     </row>
@@ -6566,25 +6566,25 @@
         <v>98</v>
       </c>
       <c r="C136" s="5">
+        <v>36001.0</v>
+      </c>
+      <c r="D136" s="39" t="s">
+        <v>277</v>
+      </c>
+      <c r="E136" s="19">
         <v>36002.0</v>
       </c>
-      <c r="D136" s="36" t="s">
-        <v>277</v>
-      </c>
-      <c r="E136" s="28">
-        <v>36003.0</v>
-      </c>
-      <c r="F136" s="36" t="s">
-        <v>133</v>
-      </c>
-      <c r="G136" s="36" t="s">
-        <v>134</v>
-      </c>
-      <c r="H136" s="36"/>
+      <c r="F136" s="39" t="s">
+        <v>133</v>
+      </c>
+      <c r="G136" s="39" t="s">
+        <v>134</v>
+      </c>
+      <c r="H136" s="39"/>
       <c r="I136" s="38" t="s">
         <v>135</v>
       </c>
-      <c r="J136" s="28">
+      <c r="J136" s="19">
         <v>0.0</v>
       </c>
     </row>
@@ -6596,25 +6596,25 @@
         <v>98</v>
       </c>
       <c r="C137" s="5">
+        <v>36002.0</v>
+      </c>
+      <c r="D137" s="36" t="s">
+        <v>278</v>
+      </c>
+      <c r="E137" s="28">
         <v>36003.0</v>
       </c>
-      <c r="D137" s="39" t="s">
-        <v>278</v>
-      </c>
-      <c r="E137" s="19">
-        <v>36004.0</v>
-      </c>
-      <c r="F137" s="39" t="s">
-        <v>133</v>
-      </c>
-      <c r="G137" s="39" t="s">
-        <v>134</v>
-      </c>
-      <c r="H137" s="39"/>
+      <c r="F137" s="36" t="s">
+        <v>133</v>
+      </c>
+      <c r="G137" s="36" t="s">
+        <v>134</v>
+      </c>
+      <c r="H137" s="36"/>
       <c r="I137" s="38" t="s">
         <v>135</v>
       </c>
-      <c r="J137" s="19">
+      <c r="J137" s="28">
         <v>0.0</v>
       </c>
     </row>
@@ -6626,55 +6626,55 @@
         <v>98</v>
       </c>
       <c r="C138" s="5">
+        <v>36003.0</v>
+      </c>
+      <c r="D138" s="39" t="s">
+        <v>279</v>
+      </c>
+      <c r="E138" s="19">
         <v>36004.0</v>
       </c>
-      <c r="D138" s="36" t="s">
-        <v>279</v>
-      </c>
-      <c r="E138" s="28">
-        <v>-1.0</v>
-      </c>
-      <c r="F138" s="36" t="s">
-        <v>133</v>
-      </c>
-      <c r="G138" s="36" t="s">
-        <v>134</v>
-      </c>
-      <c r="H138" s="36"/>
+      <c r="F138" s="39" t="s">
+        <v>133</v>
+      </c>
+      <c r="G138" s="39" t="s">
+        <v>134</v>
+      </c>
+      <c r="H138" s="39"/>
       <c r="I138" s="38" t="s">
         <v>135</v>
       </c>
-      <c r="J138" s="28">
+      <c r="J138" s="19">
         <v>0.0</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="40" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B139" s="40" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C139" s="5">
-        <v>37001.0</v>
-      </c>
-      <c r="D139" s="39" t="s">
+        <v>36004.0</v>
+      </c>
+      <c r="D139" s="36" t="s">
         <v>280</v>
       </c>
-      <c r="E139" s="19">
-        <v>37002.0</v>
-      </c>
-      <c r="F139" s="39" t="s">
-        <v>133</v>
-      </c>
-      <c r="G139" s="39" t="s">
-        <v>134</v>
-      </c>
-      <c r="H139" s="39"/>
+      <c r="E139" s="28">
+        <v>-1.0</v>
+      </c>
+      <c r="F139" s="36" t="s">
+        <v>133</v>
+      </c>
+      <c r="G139" s="36" t="s">
+        <v>134</v>
+      </c>
+      <c r="H139" s="36"/>
       <c r="I139" s="38" t="s">
         <v>135</v>
       </c>
-      <c r="J139" s="19">
+      <c r="J139" s="28">
         <v>0.0</v>
       </c>
     </row>
@@ -6686,25 +6686,25 @@
         <v>100</v>
       </c>
       <c r="C140" s="5">
+        <v>37001.0</v>
+      </c>
+      <c r="D140" s="39" t="s">
+        <v>281</v>
+      </c>
+      <c r="E140" s="19">
         <v>37002.0</v>
       </c>
-      <c r="D140" s="36" t="s">
-        <v>281</v>
-      </c>
-      <c r="E140" s="28">
-        <v>37003.0</v>
-      </c>
-      <c r="F140" s="36" t="s">
-        <v>133</v>
-      </c>
-      <c r="G140" s="36" t="s">
-        <v>134</v>
-      </c>
-      <c r="H140" s="36"/>
+      <c r="F140" s="39" t="s">
+        <v>133</v>
+      </c>
+      <c r="G140" s="39" t="s">
+        <v>134</v>
+      </c>
+      <c r="H140" s="39"/>
       <c r="I140" s="38" t="s">
         <v>135</v>
       </c>
-      <c r="J140" s="28">
+      <c r="J140" s="19">
         <v>0.0</v>
       </c>
     </row>
@@ -6716,55 +6716,55 @@
         <v>100</v>
       </c>
       <c r="C141" s="5">
+        <v>37002.0</v>
+      </c>
+      <c r="D141" s="36" t="s">
+        <v>282</v>
+      </c>
+      <c r="E141" s="28">
         <v>37003.0</v>
       </c>
-      <c r="D141" s="39" t="s">
-        <v>282</v>
-      </c>
-      <c r="E141" s="19">
-        <v>-1.0</v>
-      </c>
-      <c r="F141" s="39" t="s">
-        <v>133</v>
-      </c>
-      <c r="G141" s="39" t="s">
-        <v>134</v>
-      </c>
-      <c r="H141" s="39"/>
+      <c r="F141" s="36" t="s">
+        <v>133</v>
+      </c>
+      <c r="G141" s="36" t="s">
+        <v>134</v>
+      </c>
+      <c r="H141" s="36"/>
       <c r="I141" s="38" t="s">
         <v>135</v>
       </c>
-      <c r="J141" s="19">
+      <c r="J141" s="28">
         <v>0.0</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="40" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B142" s="40" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="C142" s="5">
-        <v>38001.0</v>
-      </c>
-      <c r="D142" s="36" t="s">
+        <v>37003.0</v>
+      </c>
+      <c r="D142" s="39" t="s">
         <v>283</v>
       </c>
-      <c r="E142" s="28">
-        <v>38002.0</v>
-      </c>
-      <c r="F142" s="36" t="s">
-        <v>133</v>
-      </c>
-      <c r="G142" s="36" t="s">
-        <v>134</v>
-      </c>
-      <c r="H142" s="36"/>
+      <c r="E142" s="19">
+        <v>-1.0</v>
+      </c>
+      <c r="F142" s="39" t="s">
+        <v>133</v>
+      </c>
+      <c r="G142" s="39" t="s">
+        <v>134</v>
+      </c>
+      <c r="H142" s="39"/>
       <c r="I142" s="38" t="s">
         <v>135</v>
       </c>
-      <c r="J142" s="28">
+      <c r="J142" s="19">
         <v>0.0</v>
       </c>
     </row>
@@ -6776,25 +6776,25 @@
         <v>102</v>
       </c>
       <c r="C143" s="5">
+        <v>38001.0</v>
+      </c>
+      <c r="D143" s="36" t="s">
+        <v>284</v>
+      </c>
+      <c r="E143" s="28">
         <v>38002.0</v>
       </c>
-      <c r="D143" s="39" t="s">
-        <v>284</v>
-      </c>
-      <c r="E143" s="19">
-        <v>38003.0</v>
-      </c>
-      <c r="F143" s="39" t="s">
-        <v>133</v>
-      </c>
-      <c r="G143" s="39" t="s">
-        <v>134</v>
-      </c>
-      <c r="H143" s="39"/>
+      <c r="F143" s="36" t="s">
+        <v>133</v>
+      </c>
+      <c r="G143" s="36" t="s">
+        <v>134</v>
+      </c>
+      <c r="H143" s="36"/>
       <c r="I143" s="38" t="s">
         <v>135</v>
       </c>
-      <c r="J143" s="19">
+      <c r="J143" s="28">
         <v>0.0</v>
       </c>
     </row>
@@ -6806,25 +6806,25 @@
         <v>102</v>
       </c>
       <c r="C144" s="5">
+        <v>38002.0</v>
+      </c>
+      <c r="D144" s="39" t="s">
+        <v>285</v>
+      </c>
+      <c r="E144" s="19">
         <v>38003.0</v>
       </c>
-      <c r="D144" s="36" t="s">
-        <v>285</v>
-      </c>
-      <c r="E144" s="28">
-        <v>38004.0</v>
-      </c>
-      <c r="F144" s="36" t="s">
-        <v>133</v>
-      </c>
-      <c r="G144" s="36" t="s">
-        <v>134</v>
-      </c>
-      <c r="H144" s="36"/>
+      <c r="F144" s="39" t="s">
+        <v>133</v>
+      </c>
+      <c r="G144" s="39" t="s">
+        <v>134</v>
+      </c>
+      <c r="H144" s="39"/>
       <c r="I144" s="38" t="s">
         <v>135</v>
       </c>
-      <c r="J144" s="28">
+      <c r="J144" s="19">
         <v>0.0</v>
       </c>
     </row>
@@ -6836,73 +6836,73 @@
         <v>102</v>
       </c>
       <c r="C145" s="5">
+        <v>38003.0</v>
+      </c>
+      <c r="D145" s="36" t="s">
+        <v>286</v>
+      </c>
+      <c r="E145" s="28">
         <v>38004.0</v>
       </c>
-      <c r="D145" s="39" t="s">
-        <v>286</v>
-      </c>
-      <c r="E145" s="19">
-        <v>-1.0</v>
-      </c>
-      <c r="F145" s="39" t="s">
-        <v>133</v>
-      </c>
-      <c r="G145" s="39" t="s">
-        <v>134</v>
-      </c>
-      <c r="H145" s="39"/>
+      <c r="F145" s="36" t="s">
+        <v>133</v>
+      </c>
+      <c r="G145" s="36" t="s">
+        <v>134</v>
+      </c>
+      <c r="H145" s="36"/>
       <c r="I145" s="38" t="s">
         <v>135</v>
       </c>
-      <c r="J145" s="19">
+      <c r="J145" s="28">
         <v>0.0</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="40" t="s">
+        <v>102</v>
+      </c>
+      <c r="B146" s="40" t="s">
+        <v>102</v>
+      </c>
+      <c r="C146" s="5">
+        <v>38004.0</v>
+      </c>
+      <c r="D146" s="39" t="s">
+        <v>287</v>
+      </c>
+      <c r="E146" s="19">
+        <v>-1.0</v>
+      </c>
+      <c r="F146" s="39" t="s">
+        <v>133</v>
+      </c>
+      <c r="G146" s="39" t="s">
+        <v>134</v>
+      </c>
+      <c r="H146" s="39"/>
+      <c r="I146" s="38" t="s">
+        <v>135</v>
+      </c>
+      <c r="J146" s="19">
+        <v>0.0</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="40" t="s">
         <v>104</v>
       </c>
-      <c r="B146" s="40" t="s">
+      <c r="B147" s="40" t="s">
         <v>104</v>
       </c>
-      <c r="C146" s="5">
+      <c r="C147" s="5">
         <v>39001.0</v>
-      </c>
-      <c r="D146" s="42" t="s">
-        <v>287</v>
-      </c>
-      <c r="E146" s="28">
-        <v>-1.0</v>
-      </c>
-      <c r="F146" s="36" t="s">
-        <v>133</v>
-      </c>
-      <c r="G146" s="36" t="s">
-        <v>134</v>
-      </c>
-      <c r="H146" s="36"/>
-      <c r="I146" s="38" t="s">
-        <v>135</v>
-      </c>
-      <c r="J146" s="28">
-        <v>0.0</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" s="32" t="s">
-        <v>106</v>
-      </c>
-      <c r="B147" s="32" t="s">
-        <v>106</v>
-      </c>
-      <c r="C147" s="3">
-        <v>40000.0</v>
       </c>
       <c r="D147" s="42" t="s">
         <v>288</v>
       </c>
-      <c r="E147" s="3">
-        <v>40001.0</v>
+      <c r="E147" s="28">
+        <v>-1.0</v>
       </c>
       <c r="F147" s="36" t="s">
         <v>133</v>
@@ -6926,13 +6926,13 @@
         <v>106</v>
       </c>
       <c r="C148" s="3">
-        <v>40001.0</v>
+        <v>40000.0</v>
       </c>
       <c r="D148" s="42" t="s">
         <v>289</v>
       </c>
       <c r="E148" s="3">
-        <v>40002.0</v>
+        <v>40001.0</v>
       </c>
       <c r="F148" s="36" t="s">
         <v>133</v>
@@ -6956,7 +6956,7 @@
         <v>106</v>
       </c>
       <c r="C149" s="3">
-        <v>40002.0</v>
+        <v>40001.0</v>
       </c>
       <c r="D149" s="42" t="s">
         <v>290</v>

--- a/Assets/02Script/Table/EventTable.xlsx
+++ b/Assets/02Script/Table/EventTable.xlsx
@@ -7,6 +7,7 @@
     <sheet state="visible" name="Narration" sheetId="2" r:id="rId5"/>
     <sheet state="visible" name="Dialog" sheetId="3" r:id="rId6"/>
     <sheet state="visible" name="Choice" sheetId="4" r:id="rId7"/>
+    <sheet state="visible" name="Quest" sheetId="5" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -14,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1147" uniqueCount="359">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1271" uniqueCount="421">
   <si>
     <t>EventID</t>
   </si>
@@ -910,8 +911,7 @@
     <t>E041</t>
   </si>
   <si>
-    <t>밖에 나가기엔 늦은 시간이야..
-내일을 위해서 어서 자야 해.</t>
+    <t>열쇠를 다 찾기 전까진 돌아갈 수 없어..</t>
   </si>
   <si>
     <t>Choice0</t>
@@ -1121,6 +1121,193 @@
   </si>
   <si>
     <t>N011</t>
+  </si>
+  <si>
+    <t>C011</t>
+  </si>
+  <si>
+    <t>지금은 분명 가을인데..</t>
+  </si>
+  <si>
+    <t>봄이었던 것 같기도 하고..?
+기억이 잘 안 나네..</t>
+  </si>
+  <si>
+    <t>N014_0</t>
+  </si>
+  <si>
+    <t>N014_1</t>
+  </si>
+  <si>
+    <t>N014</t>
+  </si>
+  <si>
+    <t>QuestID</t>
+  </si>
+  <si>
+    <t>ActiveID</t>
+  </si>
+  <si>
+    <t>DeactiveID</t>
+  </si>
+  <si>
+    <t>Q001</t>
+  </si>
+  <si>
+    <t>공원 출구 찾기.</t>
+  </si>
+  <si>
+    <t>Q002</t>
+  </si>
+  <si>
+    <t>위쪽 샛길 확인하기.</t>
+  </si>
+  <si>
+    <t>Q003</t>
+  </si>
+  <si>
+    <t>N003</t>
+  </si>
+  <si>
+    <t>시루와 대화하기.</t>
+  </si>
+  <si>
+    <t>Q004</t>
+  </si>
+  <si>
+    <t>샛길 밖으로 이동하기.</t>
+  </si>
+  <si>
+    <t>Q005</t>
+  </si>
+  <si>
+    <t>Q006</t>
+  </si>
+  <si>
+    <t>Q007</t>
+  </si>
+  <si>
+    <t>풍선 확인하기.</t>
+  </si>
+  <si>
+    <t>Q008</t>
+  </si>
+  <si>
+    <t>Q009</t>
+  </si>
+  <si>
+    <t>N005</t>
+  </si>
+  <si>
+    <t>문 확인하기.</t>
+  </si>
+  <si>
+    <t>Q010</t>
+  </si>
+  <si>
+    <t>공원 한가운데 수상한 공간 확인하기.</t>
+  </si>
+  <si>
+    <t>Q011</t>
+  </si>
+  <si>
+    <t>무성해 보이는 숲길 확인하기.</t>
+  </si>
+  <si>
+    <t>Q012</t>
+  </si>
+  <si>
+    <t>미로를 탐험하며 열쇠 찾기( N / 3).</t>
+  </si>
+  <si>
+    <t>Q013</t>
+  </si>
+  <si>
+    <t>귀신을 피해 탈출하기.</t>
+  </si>
+  <si>
+    <t>Q014</t>
+  </si>
+  <si>
+    <t>열쇠를 사용해 문 열기.</t>
+  </si>
+  <si>
+    <t>Q015</t>
+  </si>
+  <si>
+    <t>교실을 나가 집으로 돌아가기.</t>
+  </si>
+  <si>
+    <t>Q016</t>
+  </si>
+  <si>
+    <t>N012</t>
+  </si>
+  <si>
+    <t>침대로 가서 잠자기.</t>
+  </si>
+  <si>
+    <t>Q017</t>
+  </si>
+  <si>
+    <t>집으로 가는 길 찾기.</t>
+  </si>
+  <si>
+    <t>Q018</t>
+  </si>
+  <si>
+    <t>골목 안 확인하기.</t>
+  </si>
+  <si>
+    <t>Q019</t>
+  </si>
+  <si>
+    <t>양아치와 대화하기.</t>
+  </si>
+  <si>
+    <t>Q020</t>
+  </si>
+  <si>
+    <t>골목 밖으로 나가기.</t>
+  </si>
+  <si>
+    <t>Q021</t>
+  </si>
+  <si>
+    <t>Q022</t>
+  </si>
+  <si>
+    <t>소리가 들리는 곳 확인하기.</t>
+  </si>
+  <si>
+    <t>Q023</t>
+  </si>
+  <si>
+    <t>Q024</t>
+  </si>
+  <si>
+    <t>Q025</t>
+  </si>
+  <si>
+    <t>Q026</t>
+  </si>
+  <si>
+    <t>Q027</t>
+  </si>
+  <si>
+    <t>N013</t>
+  </si>
+  <si>
+    <t>Q028</t>
+  </si>
+  <si>
+    <t>도로 한가운데 수상한 공간 확인하기.</t>
+  </si>
+  <si>
+    <t>Q029</t>
+  </si>
+  <si>
+    <t>터널 안쪽 확인하기.</t>
   </si>
 </sst>
 </file>
@@ -1196,7 +1383,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="53">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1351,6 +1538,9 @@
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="bottom"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
@@ -1421,6 +1611,10 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
 <table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="C2:C14" displayName="Table_1" name="Table_1" id="1">
   <tableColumns count="1">
@@ -1461,7 +1655,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="D81:J150" displayName="Table_4" name="Table_4" id="4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="D81:J152" displayName="Table_4" name="Table_4" id="4">
   <tableColumns count="7">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -6994,10 +7188,10 @@
       <c r="E150" s="41">
         <v>-1.0</v>
       </c>
-      <c r="F150" s="42" t="s">
-        <v>133</v>
-      </c>
-      <c r="G150" s="42" t="s">
+      <c r="F150" s="36" t="s">
+        <v>133</v>
+      </c>
+      <c r="G150" s="36" t="s">
         <v>134</v>
       </c>
       <c r="H150" s="36"/>
@@ -7011,10 +7205,24 @@
     <row r="151">
       <c r="A151" s="44"/>
       <c r="B151" s="44"/>
+      <c r="D151" s="42"/>
+      <c r="E151" s="18"/>
+      <c r="F151" s="36"/>
+      <c r="G151" s="36"/>
+      <c r="H151" s="36"/>
+      <c r="I151" s="38"/>
+      <c r="J151" s="28"/>
     </row>
     <row r="152">
       <c r="A152" s="44"/>
       <c r="B152" s="44"/>
+      <c r="D152" s="42"/>
+      <c r="E152" s="18"/>
+      <c r="F152" s="36"/>
+      <c r="G152" s="36"/>
+      <c r="H152" s="36"/>
+      <c r="I152" s="38"/>
+      <c r="J152" s="28"/>
     </row>
     <row r="153">
       <c r="A153" s="44"/>
@@ -10327,10 +10535,6 @@
     <row r="980">
       <c r="A980" s="44"/>
       <c r="B980" s="44"/>
-    </row>
-    <row r="981">
-      <c r="A981" s="44"/>
-      <c r="B981" s="44"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
@@ -10652,6 +10856,464 @@
         <v>358</v>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="E12" s="3">
+        <v>-10.0</v>
+      </c>
+      <c r="F12" s="3">
+        <v>0.0</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>364</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.75"/>
+  <cols>
+    <col customWidth="1" min="2" max="2" width="13.88"/>
+    <col customWidth="1" min="3" max="3" width="15.5"/>
+    <col customWidth="1" min="4" max="4" width="26.5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="3" t="s">
+        <v>368</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="C2" s="49" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2" s="52" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="s">
+        <v>370</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C3" s="49" t="s">
+        <v>30</v>
+      </c>
+      <c r="D3" s="52" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="s">
+        <v>372</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="C4" s="49" t="s">
+        <v>373</v>
+      </c>
+      <c r="D4" s="52" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="s">
+        <v>375</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>373</v>
+      </c>
+      <c r="C5" s="49" t="s">
+        <v>36</v>
+      </c>
+      <c r="D5" s="52" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="s">
+        <v>377</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C6" s="49" t="s">
+        <v>42</v>
+      </c>
+      <c r="D6" s="52" t="s">
+        <v>369</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="s">
+        <v>378</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="C7" s="49" t="s">
+        <v>48</v>
+      </c>
+      <c r="D7" s="52" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="s">
+        <v>379</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="C8" s="49" t="s">
+        <v>322</v>
+      </c>
+      <c r="D8" s="52" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="s">
+        <v>381</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>322</v>
+      </c>
+      <c r="C9" s="49" t="s">
+        <v>54</v>
+      </c>
+      <c r="D9" s="52" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="s">
+        <v>382</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="C10" s="49" t="s">
+        <v>383</v>
+      </c>
+      <c r="D10" s="52" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="s">
+        <v>385</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>383</v>
+      </c>
+      <c r="C11" s="49" t="s">
+        <v>57</v>
+      </c>
+      <c r="D11" s="52" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="s">
+        <v>387</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C12" s="49" t="s">
+        <v>60</v>
+      </c>
+      <c r="D12" s="52" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="s">
+        <v>389</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C13" s="49" t="s">
+        <v>106</v>
+      </c>
+      <c r="D13" s="52" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="s">
+        <v>391</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="C14" s="49" t="s">
+        <v>63</v>
+      </c>
+      <c r="D14" s="52" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="s">
+        <v>393</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C15" s="52"/>
+      <c r="D15" s="52" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="s">
+        <v>395</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="C16" s="49" t="s">
+        <v>70</v>
+      </c>
+      <c r="D16" s="52" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="s">
+        <v>397</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="C17" s="49" t="s">
+        <v>398</v>
+      </c>
+      <c r="D17" s="52" t="s">
+        <v>399</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="s">
+        <v>400</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C18" s="49" t="s">
+        <v>76</v>
+      </c>
+      <c r="D18" s="52" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="s">
+        <v>402</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="C19" s="49" t="s">
+        <v>80</v>
+      </c>
+      <c r="D19" s="52" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="s">
+        <v>404</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="C20" s="49" t="s">
+        <v>352</v>
+      </c>
+      <c r="D20" s="52" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="s">
+        <v>406</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="C21" s="49" t="s">
+        <v>86</v>
+      </c>
+      <c r="D21" s="52" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="s">
+        <v>408</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="C22" s="49" t="s">
+        <v>90</v>
+      </c>
+      <c r="D22" s="52" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="s">
+        <v>409</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="C23" s="49" t="s">
+        <v>92</v>
+      </c>
+      <c r="D23" s="52" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="C24" s="49" t="s">
+        <v>94</v>
+      </c>
+      <c r="D24" s="52" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="s">
+        <v>412</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="C25" s="49" t="s">
+        <v>358</v>
+      </c>
+      <c r="D25" s="52" t="s">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="C26" s="49" t="s">
+        <v>98</v>
+      </c>
+      <c r="D26" s="52" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="s">
+        <v>414</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="C27" s="49" t="s">
+        <v>100</v>
+      </c>
+      <c r="D27" s="52" t="s">
+        <v>401</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="s">
+        <v>415</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="C28" s="49" t="s">
+        <v>416</v>
+      </c>
+      <c r="D28" s="52" t="s">
+        <v>384</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="s">
+        <v>417</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>416</v>
+      </c>
+      <c r="C29" s="49" t="s">
+        <v>102</v>
+      </c>
+      <c r="D29" s="52" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="s">
+        <v>419</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="D30" s="52" t="s">
+        <v>420</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>

--- a/Assets/02Script/Table/EventTable.xlsx
+++ b/Assets/02Script/Table/EventTable.xlsx
@@ -1129,7 +1129,7 @@
     <t>지금은 분명 가을인데..</t>
   </si>
   <si>
-    <t>봄이었던 것 같기도 하고..?
+    <t>봄이었던 것 같기도하고..?
 기억이 잘 안 나네..</t>
   </si>
   <si>
@@ -11241,11 +11241,12 @@
         <v>358</v>
       </c>
       <c r="C25" s="49" t="s">
-        <v>358</v>
+        <v>98</v>
       </c>
       <c r="D25" s="52" t="s">
-        <v>405</v>
-      </c>
+        <v>407</v>
+      </c>
+      <c r="F25" s="52"/>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
@@ -11254,11 +11255,11 @@
       <c r="B26" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="C26" s="49" t="s">
-        <v>98</v>
+      <c r="C26" s="3" t="s">
+        <v>358</v>
       </c>
       <c r="D26" s="52" t="s">
-        <v>407</v>
+        <v>405</v>
       </c>
     </row>
     <row r="27">

--- a/Assets/02Script/Table/EventTable.xlsx
+++ b/Assets/02Script/Table/EventTable.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1271" uniqueCount="421">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1313" uniqueCount="433">
   <si>
     <t>EventID</t>
   </si>
@@ -339,6 +339,24 @@
   </si>
   <si>
     <t>1스테이지 1인칭 맵 귀신 나타났을 때</t>
+  </si>
+  <si>
+    <t>E041</t>
+  </si>
+  <si>
+    <t>1스테이지 1인칭 맵 열쇠 안모으고 나가려고 할 때.</t>
+  </si>
+  <si>
+    <t>E042</t>
+  </si>
+  <si>
+    <t>1스테이지 1인칭 맵 끝나고 3인칭 나온 뒤 다시 1인칭 가려고 할 때</t>
+  </si>
+  <si>
+    <t>E043</t>
+  </si>
+  <si>
+    <t>3인칭 맵에서 귀신이 등장 했을 때.</t>
   </si>
   <si>
     <t>Order</t>
@@ -908,10 +926,22 @@
     <t>도망쳐야해...!</t>
   </si>
   <si>
-    <t>E041</t>
-  </si>
-  <si>
     <t>열쇠를 다 찾기 전까진 돌아갈 수 없어..</t>
+  </si>
+  <si>
+    <t>필요한 건 다 모은 거 같으니..</t>
+  </si>
+  <si>
+    <t>다시 가지 않아도 될 거 같아...</t>
+  </si>
+  <si>
+    <t>이 소리는..?</t>
+  </si>
+  <si>
+    <t>그 괴물...?</t>
+  </si>
+  <si>
+    <t>도망가야 해...</t>
   </si>
   <si>
     <t>Choice0</t>
@@ -1308,6 +1338,12 @@
   </si>
   <si>
     <t>터널 안쪽 확인하기.</t>
+  </si>
+  <si>
+    <t>Q030</t>
+  </si>
+  <si>
+    <t>귀신을 피해 이곳을 탈출하자.</t>
   </si>
 </sst>
 </file>
@@ -1502,11 +1538,11 @@
     <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
+    <xf borderId="0" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
+    </xf>
     <xf borderId="0" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" vertical="bottom"/>
-    </xf>
-    <xf borderId="0" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="right" readingOrder="0" vertical="bottom"/>
     </xf>
     <xf borderId="0" fillId="4" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" vertical="bottom"/>
@@ -1655,7 +1691,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="D81:J152" displayName="Table_4" name="Table_4" id="4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="D81:J155" displayName="Table_4" name="Table_4" id="4">
   <tableColumns count="7">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -2396,6 +2432,39 @@
         <v>107</v>
       </c>
     </row>
+    <row r="43">
+      <c r="A43" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>113</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -2416,10 +2485,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
     </row>
     <row r="2">
@@ -2430,7 +2499,7 @@
         <v>1.0</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>110</v>
+        <v>116</v>
       </c>
     </row>
     <row r="3">
@@ -2441,7 +2510,7 @@
         <v>2.0</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>111</v>
+        <v>117</v>
       </c>
     </row>
     <row r="4">
@@ -2452,7 +2521,7 @@
         <v>3.0</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
     </row>
     <row r="5">
@@ -2463,7 +2532,7 @@
         <v>4.0</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>113</v>
+        <v>119</v>
       </c>
     </row>
     <row r="6">
@@ -2474,7 +2543,7 @@
         <v>5.0</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>114</v>
+        <v>120</v>
       </c>
     </row>
     <row r="7">
@@ -2485,7 +2554,7 @@
         <v>6.0</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>115</v>
+        <v>121</v>
       </c>
     </row>
     <row r="8">
@@ -2496,7 +2565,7 @@
         <v>7.0</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>116</v>
+        <v>122</v>
       </c>
     </row>
     <row r="9">
@@ -2507,7 +2576,7 @@
         <v>8.0</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>117</v>
+        <v>123</v>
       </c>
     </row>
     <row r="10">
@@ -2518,7 +2587,7 @@
         <v>9.0</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>118</v>
+        <v>124</v>
       </c>
     </row>
     <row r="11">
@@ -2529,7 +2598,7 @@
         <v>10.0</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>119</v>
+        <v>125</v>
       </c>
     </row>
     <row r="12">
@@ -2540,7 +2609,7 @@
         <v>11.0</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>120</v>
+        <v>126</v>
       </c>
     </row>
     <row r="13">
@@ -2551,7 +2620,7 @@
         <v>12.0</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>121</v>
+        <v>127</v>
       </c>
     </row>
     <row r="14">
@@ -2562,7 +2631,7 @@
         <v>13.0</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>122</v>
+        <v>128</v>
       </c>
     </row>
   </sheetData>
@@ -2589,31 +2658,31 @@
         <v>0</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>123</v>
+        <v>129</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>124</v>
+        <v>130</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>125</v>
+        <v>131</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>126</v>
+        <v>132</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>128</v>
+        <v>134</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>131</v>
+        <v>137</v>
       </c>
     </row>
     <row r="2">
@@ -2627,20 +2696,20 @@
         <v>2001.0</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="E2" s="12">
         <v>2002.0</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="G2" s="11" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="H2" s="13"/>
       <c r="I2" s="14" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="J2" s="14">
         <v>-1.0</v>
@@ -2658,20 +2727,20 @@
         <v>2002.0</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>136</v>
+        <v>142</v>
       </c>
       <c r="E3" s="12">
         <v>2003.0</v>
       </c>
       <c r="F3" s="11" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="G3" s="11" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="H3" s="13"/>
       <c r="I3" s="14" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="J3" s="14">
         <v>-1.0</v>
@@ -2689,20 +2758,20 @@
         <v>2003.0</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>137</v>
+        <v>143</v>
       </c>
       <c r="E4" s="12">
         <v>2004.0</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="H4" s="13"/>
       <c r="I4" s="14" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="J4" s="14">
         <v>-1.0</v>
@@ -2720,20 +2789,20 @@
         <v>2004.0</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="E5" s="12">
         <v>2005.0</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="G5" s="11" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="H5" s="13"/>
       <c r="I5" s="14" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="J5" s="14">
         <v>-1.0</v>
@@ -2751,20 +2820,20 @@
         <v>2005.0</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="E6" s="12">
         <v>2006.0</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="G6" s="11" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="H6" s="13"/>
       <c r="I6" s="14" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="J6" s="14">
         <v>-1.0</v>
@@ -2782,20 +2851,20 @@
         <v>2006.0</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="E7" s="12">
         <v>2007.0</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="G7" s="11" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="H7" s="13"/>
       <c r="I7" s="14" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="J7" s="14">
         <v>-1.0</v>
@@ -2813,20 +2882,20 @@
         <v>2007.0</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="E8" s="12">
         <v>2008.0</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="H8" s="13"/>
       <c r="I8" s="14" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="J8" s="14">
         <v>-1.0</v>
@@ -2844,20 +2913,20 @@
         <v>2008.0</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="E9" s="12">
         <v>2009.0</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="G9" s="11" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="H9" s="13"/>
       <c r="I9" s="14" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="J9" s="14">
         <v>-1.0</v>
@@ -2875,20 +2944,20 @@
         <v>2009.0</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="E10" s="12">
         <v>2010.0</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="G10" s="11" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="H10" s="13"/>
       <c r="I10" s="14" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="J10" s="14">
         <v>-1.0</v>
@@ -2906,20 +2975,20 @@
         <v>2010.0</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="E11" s="12">
         <v>2011.0</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>139</v>
+        <v>145</v>
       </c>
       <c r="G11" s="11" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="H11" s="13"/>
       <c r="I11" s="14" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="J11" s="14">
         <v>-1.0</v>
@@ -2937,20 +3006,20 @@
         <v>2011.0</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="E12" s="12">
         <v>-1.0</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="H12" s="13"/>
       <c r="I12" s="14" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="J12" s="14">
         <v>-1.0</v>
@@ -2968,20 +3037,20 @@
         <v>3001.0</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="E13" s="16">
         <v>3002.0</v>
       </c>
       <c r="F13" s="14" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="G13" s="11" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="H13" s="13"/>
       <c r="I13" s="14" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="J13" s="16">
         <v>4.0</v>
@@ -2999,20 +3068,20 @@
         <v>3002.0</v>
       </c>
       <c r="D14" s="14" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="E14" s="16">
         <v>3003.0</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="G14" s="11" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="H14" s="13"/>
       <c r="I14" s="14" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="J14" s="16">
         <v>0.0</v>
@@ -3030,20 +3099,20 @@
         <v>3003.0</v>
       </c>
       <c r="D15" s="14" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="E15" s="16">
         <v>3004.0</v>
       </c>
       <c r="F15" s="14" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="G15" s="11" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="H15" s="13"/>
       <c r="I15" s="14" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="J15" s="16">
         <v>2.0</v>
@@ -3061,20 +3130,20 @@
         <v>3004.0</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="E16" s="16">
         <v>3005.0</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="G16" s="11" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="H16" s="13"/>
       <c r="I16" s="14" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="J16" s="16">
         <v>0.0</v>
@@ -3092,20 +3161,20 @@
         <v>3005.0</v>
       </c>
       <c r="D17" s="14" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="E17" s="16">
         <v>3006.0</v>
       </c>
       <c r="F17" s="14" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="G17" s="11" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="H17" s="13"/>
       <c r="I17" s="14" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="J17" s="16">
         <v>2.0</v>
@@ -3123,20 +3192,20 @@
         <v>3006.0</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="E18" s="16">
         <v>3007.0</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="G18" s="11" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="H18" s="13"/>
       <c r="I18" s="14" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="J18" s="16">
         <v>0.0</v>
@@ -3154,20 +3223,20 @@
         <v>3007.0</v>
       </c>
       <c r="D19" s="14" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="E19" s="16">
         <v>3008.0</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="G19" s="11" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="H19" s="13"/>
       <c r="I19" s="14" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="J19" s="16">
         <v>1.0</v>
@@ -3193,20 +3262,20 @@
         <v>3008.0</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="E20" s="16">
         <v>3009.0</v>
       </c>
       <c r="F20" s="14" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="G20" s="11" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="H20" s="13"/>
       <c r="I20" s="14" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="J20" s="16">
         <v>2.0</v>
@@ -3232,20 +3301,20 @@
         <v>3009.0</v>
       </c>
       <c r="D21" s="14" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="E21" s="16">
         <v>3010.0</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="G21" s="11" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="H21" s="13"/>
       <c r="I21" s="14" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="J21" s="16">
         <v>1.0</v>
@@ -3271,20 +3340,20 @@
         <v>3010.0</v>
       </c>
       <c r="D22" s="14" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="E22" s="16">
         <v>3011.0</v>
       </c>
       <c r="F22" s="14" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="G22" s="11" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="H22" s="13"/>
       <c r="I22" s="14" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="J22" s="16">
         <v>2.0</v>
@@ -3310,20 +3379,20 @@
         <v>3011.0</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="E23" s="16">
         <v>3012.0</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="G23" s="11" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="H23" s="13"/>
       <c r="I23" s="14" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="J23" s="16">
         <v>1.0</v>
@@ -3349,19 +3418,19 @@
         <v>3012.0</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="E24" s="16">
         <v>3013.0</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="I24" s="14" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="J24" s="3">
         <v>2.0</v>
@@ -3387,19 +3456,19 @@
         <v>3013.0</v>
       </c>
       <c r="D25" s="14" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="E25" s="16">
         <v>3014.0</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="I25" s="14" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="J25" s="3">
         <v>2.0</v>
@@ -3425,19 +3494,19 @@
         <v>3014.0</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="E26" s="16">
         <v>3015.0</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="I26" s="14" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="J26" s="3">
         <v>2.0</v>
@@ -3455,20 +3524,20 @@
         <v>3015.0</v>
       </c>
       <c r="D27" s="14" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="E27" s="16">
         <v>3016.0</v>
       </c>
       <c r="F27" s="14" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="G27" s="11" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="H27" s="13"/>
       <c r="I27" s="16" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="J27" s="16">
         <v>0.0</v>
@@ -3486,22 +3555,22 @@
         <v>3016.0</v>
       </c>
       <c r="D28" s="14" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="E28" s="12">
         <v>-1.0</v>
       </c>
       <c r="F28" s="14" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="G28" s="11" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="H28" s="14" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="I28" s="16" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="J28" s="16">
         <v>0.0</v>
@@ -3519,18 +3588,18 @@
         <v>4001.0</v>
       </c>
       <c r="D29" s="14" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="E29" s="12">
         <v>4002.0</v>
       </c>
       <c r="F29" s="14" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="G29" s="21"/>
       <c r="H29" s="13"/>
       <c r="I29" s="16" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="J29" s="16">
         <v>-1.0</v>
@@ -3548,18 +3617,18 @@
         <v>4002.0</v>
       </c>
       <c r="D30" s="14" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="E30" s="12">
         <v>-1.0</v>
       </c>
       <c r="F30" s="14" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="G30" s="21"/>
       <c r="H30" s="13"/>
       <c r="I30" s="16" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="J30" s="16">
         <v>-1.0</v>
@@ -3577,23 +3646,23 @@
         <v>5001.0</v>
       </c>
       <c r="D31" s="14" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="E31" s="3">
         <v>5002.0</v>
       </c>
       <c r="F31" s="14" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="G31" s="11" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="H31" s="13"/>
       <c r="I31" s="14" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="J31" s="16">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="K31" s="17"/>
     </row>
@@ -3608,23 +3677,23 @@
         <v>5002.0</v>
       </c>
       <c r="D32" s="14" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="E32" s="3">
         <v>5003.0</v>
       </c>
       <c r="F32" s="14" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="G32" s="11" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="H32" s="13"/>
       <c r="I32" s="14" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="J32" s="16">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="K32" s="17"/>
     </row>
@@ -3639,20 +3708,20 @@
         <v>5003.0</v>
       </c>
       <c r="D33" s="14" t="s">
-        <v>132</v>
+        <v>138</v>
       </c>
       <c r="E33" s="3">
         <v>5004.0</v>
       </c>
       <c r="F33" s="14" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="G33" s="11" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="H33" s="13"/>
       <c r="I33" s="14" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="J33" s="16">
         <v>0.0</v>
@@ -3670,20 +3739,20 @@
         <v>5004.0</v>
       </c>
       <c r="D34" s="14" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="E34" s="3">
         <v>5005.0</v>
       </c>
       <c r="F34" s="14" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="G34" s="11" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="H34" s="13"/>
       <c r="I34" s="14" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="J34" s="16">
         <v>0.0</v>
@@ -3701,20 +3770,20 @@
         <v>5005.0</v>
       </c>
       <c r="D35" s="14" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="E35" s="3">
         <v>5006.0</v>
       </c>
       <c r="F35" s="14" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="G35" s="11" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="H35" s="13"/>
       <c r="I35" s="14" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="J35" s="16">
         <v>0.0</v>
@@ -3732,23 +3801,23 @@
         <v>5006.0</v>
       </c>
       <c r="D36" s="14" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="E36" s="12">
         <v>-1.0</v>
       </c>
       <c r="F36" s="14" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="G36" s="11" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="H36" s="13"/>
       <c r="I36" s="16" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="J36" s="16">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
       <c r="K36" s="17"/>
     </row>
@@ -3763,20 +3832,20 @@
         <v>6001.0</v>
       </c>
       <c r="D37" s="14" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="E37" s="16">
         <v>6002.0</v>
       </c>
       <c r="F37" s="14" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="G37" s="11" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="H37" s="13"/>
       <c r="I37" s="16" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="J37" s="16">
         <v>-1.0</v>
@@ -3794,23 +3863,23 @@
         <v>6002.0</v>
       </c>
       <c r="D38" s="14" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="E38" s="16">
         <v>6003.0</v>
       </c>
       <c r="F38" s="14" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="G38" s="11" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="H38" s="13"/>
       <c r="I38" s="14" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="J38" s="16">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
       <c r="K38" s="17"/>
     </row>
@@ -3825,20 +3894,20 @@
         <v>6003.0</v>
       </c>
       <c r="D39" s="14" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="E39" s="16">
         <v>6004.0</v>
       </c>
       <c r="F39" s="14" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="G39" s="11" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="H39" s="13"/>
       <c r="I39" s="16" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="J39" s="16">
         <v>-1.0</v>
@@ -3856,20 +3925,20 @@
         <v>6004.0</v>
       </c>
       <c r="D40" s="14" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="E40" s="16">
         <v>6005.0</v>
       </c>
       <c r="F40" s="14" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="G40" s="11" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="H40" s="13"/>
       <c r="I40" s="14" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="J40" s="16">
         <v>0.0</v>
@@ -3887,20 +3956,20 @@
         <v>6005.0</v>
       </c>
       <c r="D41" s="14" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="E41" s="16">
         <v>-1.0</v>
       </c>
       <c r="F41" s="14" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="G41" s="11" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="H41" s="13"/>
       <c r="I41" s="14" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="J41" s="16">
         <v>0.0</v>
@@ -3918,20 +3987,20 @@
         <v>7001.0</v>
       </c>
       <c r="D42" s="14" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="E42" s="16">
         <v>-1.0</v>
       </c>
       <c r="F42" s="14" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="G42" s="11" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="H42" s="13"/>
       <c r="I42" s="14" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="J42" s="16">
         <v>-1.0</v>
@@ -3949,20 +4018,20 @@
         <v>8001.0</v>
       </c>
       <c r="D43" s="14" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="E43" s="16">
         <v>8002.0</v>
       </c>
       <c r="F43" s="14" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="G43" s="11" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="H43" s="13"/>
       <c r="I43" s="14" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="J43" s="16">
         <v>-1.0</v>
@@ -3980,20 +4049,20 @@
         <v>8002.0</v>
       </c>
       <c r="D44" s="14" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="E44" s="16">
         <v>8003.0</v>
       </c>
       <c r="F44" s="14" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="G44" s="11" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="H44" s="13"/>
       <c r="I44" s="14" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="J44" s="16">
         <v>-1.0</v>
@@ -4011,20 +4080,20 @@
         <v>8003.0</v>
       </c>
       <c r="D45" s="14" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="E45" s="16">
         <v>8004.0</v>
       </c>
       <c r="F45" s="14" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="G45" s="11" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="H45" s="13"/>
       <c r="I45" s="14" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="J45" s="16">
         <v>-1.0</v>
@@ -4042,20 +4111,20 @@
         <v>8004.0</v>
       </c>
       <c r="D46" s="14" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="E46" s="16">
         <v>8005.0</v>
       </c>
       <c r="F46" s="14" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="G46" s="11" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="H46" s="13"/>
       <c r="I46" s="16" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="J46" s="16">
         <v>-1.0</v>
@@ -4073,20 +4142,20 @@
         <v>8005.0</v>
       </c>
       <c r="D47" s="14" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="E47" s="16">
         <v>-1.0</v>
       </c>
       <c r="F47" s="14" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="G47" s="11" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="H47" s="13"/>
       <c r="I47" s="14" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="J47" s="16">
         <v>-1.0</v>
@@ -4104,20 +4173,20 @@
         <v>9001.0</v>
       </c>
       <c r="D48" s="14" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="E48" s="16">
         <v>-1.0</v>
       </c>
       <c r="F48" s="14" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="G48" s="11" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="H48" s="13"/>
       <c r="I48" s="31" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="J48" s="16">
         <v>-1.0</v>
@@ -4135,23 +4204,23 @@
         <v>10001.0</v>
       </c>
       <c r="D49" s="14" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="E49" s="16">
         <v>10002.0</v>
       </c>
       <c r="F49" s="14" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="G49" s="11" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="H49" s="13"/>
       <c r="I49" s="31" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="J49" s="16">
-        <v>0.0</v>
+        <v>4.0</v>
       </c>
       <c r="K49" s="17"/>
     </row>
@@ -4166,20 +4235,20 @@
         <v>10002.0</v>
       </c>
       <c r="D50" s="14" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="E50" s="16">
         <v>10003.0</v>
       </c>
       <c r="F50" s="14" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="G50" s="11" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="H50" s="13"/>
       <c r="I50" s="31" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="J50" s="16">
         <v>0.0</v>
@@ -4197,20 +4266,20 @@
         <v>10003.0</v>
       </c>
       <c r="D51" s="14" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="E51" s="16">
         <v>10004.0</v>
       </c>
       <c r="F51" s="14" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="G51" s="11" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="H51" s="13"/>
       <c r="I51" s="31" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="J51" s="16">
         <v>0.0</v>
@@ -4228,20 +4297,20 @@
         <v>10004.0</v>
       </c>
       <c r="D52" s="14" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="E52" s="16">
         <v>-1.0</v>
       </c>
       <c r="F52" s="14" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="G52" s="11" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="H52" s="13"/>
       <c r="I52" s="16" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="J52" s="16">
         <v>0.0</v>
@@ -4259,20 +4328,20 @@
         <v>11001.0</v>
       </c>
       <c r="D53" s="14" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="E53" s="16">
         <v>-1.0</v>
       </c>
       <c r="F53" s="14" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="G53" s="11" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="H53" s="13"/>
       <c r="I53" s="16" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="J53" s="16">
         <v>-1.0</v>
@@ -4290,20 +4359,20 @@
         <v>12001.0</v>
       </c>
       <c r="D54" s="14" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="E54" s="16">
         <v>12002.0</v>
       </c>
       <c r="F54" s="14" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="G54" s="11" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="H54" s="13"/>
       <c r="I54" s="31" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="J54" s="16">
         <v>-1.0</v>
@@ -4321,23 +4390,23 @@
         <v>12002.0</v>
       </c>
       <c r="D55" s="14" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="E55" s="16">
         <v>12003.0</v>
       </c>
       <c r="F55" s="14" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="G55" s="11" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="H55" s="13"/>
       <c r="I55" s="16" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="J55" s="16">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="K55" s="17"/>
     </row>
@@ -4352,20 +4421,20 @@
         <v>12003.0</v>
       </c>
       <c r="D56" s="14" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="E56" s="16">
         <v>12004.0</v>
       </c>
       <c r="F56" s="14" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="G56" s="11" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="H56" s="13"/>
       <c r="I56" s="31" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="J56" s="16">
         <v>-1.0</v>
@@ -4383,23 +4452,23 @@
         <v>12004.0</v>
       </c>
       <c r="D57" s="14" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="E57" s="16">
         <v>12005.0</v>
       </c>
       <c r="F57" s="14" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="G57" s="11" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="H57" s="13"/>
       <c r="I57" s="31" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="J57" s="16">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
       <c r="K57" s="17"/>
     </row>
@@ -4414,20 +4483,20 @@
         <v>12005.0</v>
       </c>
       <c r="D58" s="14" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="E58" s="16">
         <v>12006.0</v>
       </c>
       <c r="F58" s="14" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="G58" s="11" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="H58" s="13"/>
       <c r="I58" s="16" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="J58" s="16">
         <v>0.0</v>
@@ -4445,20 +4514,20 @@
         <v>12006.0</v>
       </c>
       <c r="D59" s="14" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="E59" s="16">
         <v>12007.0</v>
       </c>
       <c r="F59" s="14" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="G59" s="11" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="H59" s="13"/>
       <c r="I59" s="31" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="J59" s="16">
         <v>-1.0</v>
@@ -4476,20 +4545,20 @@
         <v>12007.0</v>
       </c>
       <c r="D60" s="14" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="E60" s="16">
         <v>12008.0</v>
       </c>
       <c r="F60" s="14" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="G60" s="11" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="H60" s="13"/>
       <c r="I60" s="16" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="J60" s="16">
         <v>0.0</v>
@@ -4507,20 +4576,20 @@
         <v>12008.0</v>
       </c>
       <c r="D61" s="14" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="E61" s="16">
         <v>-1.0</v>
       </c>
       <c r="F61" s="14" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="G61" s="11" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="H61" s="13"/>
       <c r="I61" s="31" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="J61" s="16">
         <v>0.0</v>
@@ -4538,20 +4607,20 @@
         <v>13001.0</v>
       </c>
       <c r="D62" s="14" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="E62" s="16">
         <v>-1.0</v>
       </c>
       <c r="F62" s="14" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="G62" s="11" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="H62" s="13"/>
       <c r="I62" s="31" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="J62" s="16">
         <v>-1.0</v>
@@ -4569,20 +4638,20 @@
         <v>14001.0</v>
       </c>
       <c r="D63" s="14" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="E63" s="16">
         <v>14002.0</v>
       </c>
       <c r="F63" s="14" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="G63" s="11" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="H63" s="13"/>
       <c r="I63" s="31" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="J63" s="16">
         <v>-1.0</v>
@@ -4600,20 +4669,20 @@
         <v>14002.0</v>
       </c>
       <c r="D64" s="14" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="E64" s="16">
         <v>14003.0</v>
       </c>
       <c r="F64" s="14" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="G64" s="11" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="H64" s="13"/>
       <c r="I64" s="31" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="J64" s="16">
         <v>-1.0</v>
@@ -4631,20 +4700,20 @@
         <v>14003.0</v>
       </c>
       <c r="D65" s="14" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="E65" s="16">
         <v>-1.0</v>
       </c>
       <c r="F65" s="14" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="G65" s="11" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="H65" s="13"/>
       <c r="I65" s="31" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="J65" s="16">
         <v>-1.0</v>
@@ -4662,20 +4731,20 @@
         <v>15001.0</v>
       </c>
       <c r="D66" s="14" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="E66" s="16">
         <v>-1.0</v>
       </c>
       <c r="F66" s="14" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="G66" s="11" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="H66" s="13"/>
       <c r="I66" s="31" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="J66" s="16">
         <v>-1.0</v>
@@ -4693,20 +4762,20 @@
         <v>16001.0</v>
       </c>
       <c r="D67" s="14" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="E67" s="16">
         <v>16002.0</v>
       </c>
       <c r="F67" s="14" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="G67" s="11" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="H67" s="13"/>
       <c r="I67" s="31" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="J67" s="16">
         <v>0.0</v>
@@ -4724,23 +4793,23 @@
         <v>16002.0</v>
       </c>
       <c r="D68" s="14" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="E68" s="16">
         <v>-1.0</v>
       </c>
       <c r="F68" s="14" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="G68" s="11" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="H68" s="13"/>
       <c r="I68" s="31" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="J68" s="16">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
       <c r="K68" s="17"/>
     </row>
@@ -4755,20 +4824,20 @@
         <v>17001.0</v>
       </c>
       <c r="D69" s="14" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="E69" s="16">
         <v>17002.0</v>
       </c>
       <c r="F69" s="14" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="G69" s="11" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="H69" s="13"/>
       <c r="I69" s="31" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="J69" s="16">
         <v>0.0</v>
@@ -4786,23 +4855,23 @@
         <v>17002.0</v>
       </c>
       <c r="D70" s="14" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="E70" s="16">
         <v>17003.0</v>
       </c>
       <c r="F70" s="14" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="G70" s="11" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="H70" s="13"/>
       <c r="I70" s="31" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="J70" s="16">
-        <v>0.0</v>
+        <v>6.0</v>
       </c>
       <c r="K70" s="17"/>
     </row>
@@ -4817,23 +4886,23 @@
         <v>17003.0</v>
       </c>
       <c r="D71" s="14" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="E71" s="16">
         <v>17004.0</v>
       </c>
       <c r="F71" s="14" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="G71" s="11" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="H71" s="13"/>
       <c r="I71" s="31" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="J71" s="16">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
       <c r="K71" s="17"/>
     </row>
@@ -4848,20 +4917,20 @@
         <v>17004.0</v>
       </c>
       <c r="D72" s="14" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="E72" s="16">
         <v>-1.0</v>
       </c>
       <c r="F72" s="14" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="G72" s="11" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="H72" s="13"/>
       <c r="I72" s="31" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="J72" s="16">
         <v>0.0</v>
@@ -4879,23 +4948,23 @@
         <v>18001.0</v>
       </c>
       <c r="D73" s="14" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="E73" s="16">
         <v>18002.0</v>
       </c>
       <c r="F73" s="14" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="G73" s="11" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="H73" s="13"/>
       <c r="I73" s="31" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="J73" s="16">
-        <v>0.0</v>
+        <v>5.0</v>
       </c>
       <c r="K73" s="17"/>
     </row>
@@ -4910,19 +4979,19 @@
         <v>18002.0</v>
       </c>
       <c r="D74" s="33" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="E74" s="3">
         <v>18003.0</v>
       </c>
       <c r="F74" s="14" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="G74" s="11" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="I74" s="31" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="J74" s="16">
         <v>0.0</v>
@@ -4939,19 +5008,19 @@
         <v>18003.0</v>
       </c>
       <c r="D75" s="33" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="E75" s="3">
         <v>-1.0</v>
       </c>
       <c r="F75" s="14" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="G75" s="11" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="I75" s="31" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="J75" s="16">
         <v>-1.0</v>
@@ -4968,22 +5037,22 @@
         <v>19001.0</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="E76" s="16">
         <v>19002.0</v>
       </c>
       <c r="F76" s="14" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="G76" s="11" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="I76" s="31" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="J76" s="16">
-        <v>2.0</v>
+        <v>6.0</v>
       </c>
     </row>
     <row r="77">
@@ -4997,22 +5066,22 @@
         <v>19002.0</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="E77" s="3">
         <v>19003.0</v>
       </c>
       <c r="F77" s="14" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="G77" s="11" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="I77" s="31" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="J77" s="16">
-        <v>2.0</v>
+        <v>5.0</v>
       </c>
     </row>
     <row r="78">
@@ -5026,19 +5095,19 @@
         <v>19003.0</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="E78" s="3">
         <v>19004.0</v>
       </c>
       <c r="F78" s="14" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="G78" s="11" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="I78" s="31" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="J78" s="3">
         <v>2.0</v>
@@ -5055,19 +5124,19 @@
         <v>19004.0</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="E79" s="3">
         <v>19005.0</v>
       </c>
       <c r="F79" s="3" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="G79" s="3" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="J79" s="3">
         <v>2.0</v>
@@ -5084,22 +5153,22 @@
         <v>19005.0</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="E80" s="3">
         <v>-1.0</v>
       </c>
       <c r="F80" s="3" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="G80" s="3" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="J80" s="3">
-        <v>0.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="81">
@@ -5113,20 +5182,20 @@
         <v>20001.0</v>
       </c>
       <c r="D81" s="36" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="E81" s="28">
         <v>20002.0</v>
       </c>
       <c r="F81" s="36" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="G81" s="37" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="H81" s="36"/>
       <c r="I81" s="38" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="J81" s="28">
         <v>0.0</v>
@@ -5143,20 +5212,20 @@
         <v>20002.0</v>
       </c>
       <c r="D82" s="39" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="E82" s="19">
         <v>20003.0</v>
       </c>
       <c r="F82" s="39" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="G82" s="37" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="H82" s="39"/>
       <c r="I82" s="38" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="J82" s="19">
         <v>0.0</v>
@@ -5173,20 +5242,20 @@
         <v>20003.0</v>
       </c>
       <c r="D83" s="36" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="E83" s="28">
         <v>20004.0</v>
       </c>
       <c r="F83" s="36" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="G83" s="37" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="H83" s="36"/>
       <c r="I83" s="38" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="J83" s="28">
         <v>0.0</v>
@@ -5203,23 +5272,23 @@
         <v>20004.0</v>
       </c>
       <c r="D84" s="39" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="E84" s="19">
         <v>20005.0</v>
       </c>
       <c r="F84" s="39" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="G84" s="37" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="H84" s="39"/>
       <c r="I84" s="38" t="s">
-        <v>135</v>
-      </c>
-      <c r="J84" s="19">
-        <v>0.0</v>
+        <v>141</v>
+      </c>
+      <c r="J84" s="26">
+        <v>2.0</v>
       </c>
     </row>
     <row r="85">
@@ -5233,23 +5302,23 @@
         <v>20005.0</v>
       </c>
       <c r="D85" s="36" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="E85" s="28">
         <v>20006.0</v>
       </c>
       <c r="F85" s="36" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="G85" s="37" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="H85" s="36"/>
       <c r="I85" s="38" t="s">
-        <v>135</v>
-      </c>
-      <c r="J85" s="28">
-        <v>0.0</v>
+        <v>141</v>
+      </c>
+      <c r="J85" s="40">
+        <v>2.0</v>
       </c>
     </row>
     <row r="86">
@@ -5263,20 +5332,20 @@
         <v>20006.0</v>
       </c>
       <c r="D86" s="39" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="E86" s="19">
         <v>-1.0</v>
       </c>
       <c r="F86" s="39" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="G86" s="37" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="H86" s="39"/>
       <c r="I86" s="38" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="J86" s="19">
         <v>0.0</v>
@@ -5293,23 +5362,23 @@
         <v>21001.0</v>
       </c>
       <c r="D87" s="36" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="E87" s="28">
         <v>-1.0</v>
       </c>
       <c r="F87" s="36" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="G87" s="37" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="H87" s="36"/>
       <c r="I87" s="38" t="s">
-        <v>135</v>
-      </c>
-      <c r="J87" s="28">
-        <v>0.0</v>
+        <v>141</v>
+      </c>
+      <c r="J87" s="40">
+        <v>-1.0</v>
       </c>
     </row>
     <row r="88">
@@ -5323,20 +5392,20 @@
         <v>22001.0</v>
       </c>
       <c r="D88" s="39" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="E88" s="19">
         <v>22002.0</v>
       </c>
       <c r="F88" s="39" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="G88" s="37" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="H88" s="39"/>
       <c r="I88" s="38" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="J88" s="19">
         <v>0.0</v>
@@ -5353,1760 +5422,1760 @@
         <v>22002.0</v>
       </c>
       <c r="D89" s="36" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="E89" s="28">
         <v>22003.0</v>
       </c>
       <c r="F89" s="36" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="G89" s="37" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="H89" s="36"/>
       <c r="I89" s="38" t="s">
-        <v>135</v>
-      </c>
-      <c r="J89" s="28">
-        <v>0.0</v>
+        <v>141</v>
+      </c>
+      <c r="J89" s="40">
+        <v>2.0</v>
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="40" t="s">
+      <c r="A90" s="41" t="s">
         <v>70</v>
       </c>
-      <c r="B90" s="40" t="s">
+      <c r="B90" s="41" t="s">
         <v>70</v>
       </c>
       <c r="C90" s="5">
         <v>22003.0</v>
       </c>
       <c r="D90" s="39" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="E90" s="19">
         <v>22004.0</v>
       </c>
       <c r="F90" s="39" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="G90" s="37" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="H90" s="39"/>
       <c r="I90" s="38" t="s">
-        <v>135</v>
-      </c>
-      <c r="J90" s="19">
-        <v>0.0</v>
+        <v>141</v>
+      </c>
+      <c r="J90" s="26">
+        <v>2.0</v>
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="40" t="s">
+      <c r="A91" s="41" t="s">
         <v>70</v>
       </c>
-      <c r="B91" s="40" t="s">
+      <c r="B91" s="41" t="s">
         <v>70</v>
       </c>
       <c r="C91" s="5">
         <v>22004.0</v>
       </c>
       <c r="D91" s="36" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="E91" s="28">
         <v>22005.0</v>
       </c>
       <c r="F91" s="36" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="G91" s="37" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="H91" s="36"/>
       <c r="I91" s="38" t="s">
-        <v>135</v>
-      </c>
-      <c r="J91" s="28">
-        <v>0.0</v>
+        <v>141</v>
+      </c>
+      <c r="J91" s="40">
+        <v>2.0</v>
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="40" t="s">
+      <c r="A92" s="41" t="s">
         <v>70</v>
       </c>
-      <c r="B92" s="40" t="s">
+      <c r="B92" s="41" t="s">
         <v>70</v>
       </c>
       <c r="C92" s="5">
         <v>22005.0</v>
       </c>
       <c r="D92" s="39" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="E92" s="26">
         <v>-1.0</v>
       </c>
       <c r="F92" s="39" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="G92" s="37" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="H92" s="39"/>
       <c r="I92" s="38" t="s">
-        <v>135</v>
-      </c>
-      <c r="J92" s="19">
-        <v>0.0</v>
+        <v>141</v>
+      </c>
+      <c r="J92" s="26">
+        <v>1.0</v>
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="40" t="s">
+      <c r="A93" s="41" t="s">
         <v>72</v>
       </c>
-      <c r="B93" s="40" t="s">
+      <c r="B93" s="41" t="s">
         <v>72</v>
       </c>
       <c r="C93" s="5">
         <v>23001.0</v>
       </c>
       <c r="D93" s="36" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="E93" s="5">
         <v>23002.0</v>
       </c>
       <c r="F93" s="36" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="G93" s="37" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="H93" s="36"/>
       <c r="I93" s="38" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="J93" s="28">
         <v>0.0</v>
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="40" t="s">
+      <c r="A94" s="41" t="s">
         <v>72</v>
       </c>
-      <c r="B94" s="40" t="s">
+      <c r="B94" s="41" t="s">
         <v>72</v>
       </c>
       <c r="C94" s="5">
         <v>23002.0</v>
       </c>
       <c r="D94" s="39" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="E94" s="5">
         <v>23003.0</v>
       </c>
       <c r="F94" s="39" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="G94" s="37" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="H94" s="39"/>
       <c r="I94" s="38" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="J94" s="19">
         <v>0.0</v>
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="40" t="s">
+      <c r="A95" s="41" t="s">
         <v>72</v>
       </c>
-      <c r="B95" s="40" t="s">
+      <c r="B95" s="41" t="s">
         <v>72</v>
       </c>
       <c r="C95" s="5">
         <v>23003.0</v>
       </c>
       <c r="D95" s="36" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="E95" s="5">
         <v>23004.0</v>
       </c>
       <c r="F95" s="36" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="G95" s="37" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="H95" s="36"/>
       <c r="I95" s="38" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="J95" s="28">
         <v>0.0</v>
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="40" t="s">
+      <c r="A96" s="41" t="s">
         <v>72</v>
       </c>
-      <c r="B96" s="40" t="s">
+      <c r="B96" s="41" t="s">
         <v>72</v>
       </c>
       <c r="C96" s="5">
         <v>23004.0</v>
       </c>
       <c r="D96" s="39" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="E96" s="19">
         <v>-1.0</v>
       </c>
       <c r="F96" s="39" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="G96" s="37" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="H96" s="39"/>
       <c r="I96" s="38" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="J96" s="19">
         <v>0.0</v>
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="40" t="s">
+      <c r="A97" s="41" t="s">
         <v>74</v>
       </c>
-      <c r="B97" s="40" t="s">
+      <c r="B97" s="41" t="s">
         <v>74</v>
       </c>
       <c r="C97" s="5">
         <v>24001.0</v>
       </c>
       <c r="D97" s="36" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="E97" s="28">
         <v>24002.0</v>
       </c>
       <c r="F97" s="36" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="G97" s="37" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="H97" s="36"/>
       <c r="I97" s="38" t="s">
-        <v>135</v>
-      </c>
-      <c r="J97" s="28">
-        <v>0.0</v>
+        <v>141</v>
+      </c>
+      <c r="J97" s="40">
+        <v>5.0</v>
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="40" t="s">
+      <c r="A98" s="41" t="s">
         <v>74</v>
       </c>
-      <c r="B98" s="40" t="s">
+      <c r="B98" s="41" t="s">
         <v>74</v>
       </c>
       <c r="C98" s="5">
         <v>24002.0</v>
       </c>
       <c r="D98" s="39" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="E98" s="19">
         <v>24003.0</v>
       </c>
       <c r="F98" s="39" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="G98" s="37" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="H98" s="39"/>
       <c r="I98" s="38" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="J98" s="19">
         <v>0.0</v>
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="40" t="s">
+      <c r="A99" s="41" t="s">
         <v>74</v>
       </c>
-      <c r="B99" s="40" t="s">
+      <c r="B99" s="41" t="s">
         <v>74</v>
       </c>
       <c r="C99" s="5">
         <v>24003.0</v>
       </c>
       <c r="D99" s="36" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="E99" s="28">
         <v>24004.0</v>
       </c>
       <c r="F99" s="36" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="G99" s="37" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="H99" s="36"/>
       <c r="I99" s="38" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="J99" s="28">
         <v>0.0</v>
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="40" t="s">
+      <c r="A100" s="41" t="s">
         <v>74</v>
       </c>
-      <c r="B100" s="40" t="s">
+      <c r="B100" s="41" t="s">
         <v>74</v>
       </c>
       <c r="C100" s="5">
         <v>24004.0</v>
       </c>
       <c r="D100" s="39" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="E100" s="19">
         <v>24005.0</v>
       </c>
       <c r="F100" s="39" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="G100" s="37" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="H100" s="39"/>
       <c r="I100" s="38" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="J100" s="19">
         <v>0.0</v>
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="40" t="s">
+      <c r="A101" s="41" t="s">
         <v>74</v>
       </c>
-      <c r="B101" s="40" t="s">
+      <c r="B101" s="41" t="s">
         <v>74</v>
       </c>
       <c r="C101" s="5">
         <v>24005.0</v>
       </c>
       <c r="D101" s="36" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="E101" s="28">
         <v>24006.0</v>
       </c>
       <c r="F101" s="36" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="G101" s="37" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="H101" s="36"/>
       <c r="I101" s="38" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="J101" s="28">
         <v>0.0</v>
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="40" t="s">
+      <c r="A102" s="41" t="s">
         <v>74</v>
       </c>
-      <c r="B102" s="40" t="s">
+      <c r="B102" s="41" t="s">
         <v>74</v>
       </c>
       <c r="C102" s="5">
         <v>24006.0</v>
       </c>
       <c r="D102" s="39" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="E102" s="19">
         <v>24007.0</v>
       </c>
       <c r="F102" s="39" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="G102" s="37" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="H102" s="39"/>
       <c r="I102" s="38" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="J102" s="19">
         <v>0.0</v>
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="40" t="s">
+      <c r="A103" s="41" t="s">
         <v>74</v>
       </c>
-      <c r="B103" s="40" t="s">
+      <c r="B103" s="41" t="s">
         <v>74</v>
       </c>
       <c r="C103" s="5">
         <v>24007.0</v>
       </c>
       <c r="D103" s="36" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="E103" s="28">
         <v>24008.0</v>
       </c>
       <c r="F103" s="36" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="G103" s="37" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="H103" s="36"/>
       <c r="I103" s="38" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="J103" s="28">
         <v>0.0</v>
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="40" t="s">
+      <c r="A104" s="41" t="s">
         <v>74</v>
       </c>
-      <c r="B104" s="40" t="s">
+      <c r="B104" s="41" t="s">
         <v>74</v>
       </c>
       <c r="C104" s="5">
         <v>24008.0</v>
       </c>
       <c r="D104" s="39" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="E104" s="19">
         <v>-1.0</v>
       </c>
       <c r="F104" s="39" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="G104" s="37" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="H104" s="39"/>
       <c r="I104" s="38" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="J104" s="19">
         <v>0.0</v>
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="40" t="s">
+      <c r="A105" s="41" t="s">
         <v>76</v>
       </c>
-      <c r="B105" s="40" t="s">
+      <c r="B105" s="41" t="s">
         <v>76</v>
       </c>
       <c r="C105" s="5">
         <v>25001.0</v>
       </c>
       <c r="D105" s="36" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="E105" s="28">
         <v>25002.0</v>
       </c>
       <c r="F105" s="36" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="G105" s="36" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="H105" s="36"/>
       <c r="I105" s="36" t="s">
-        <v>164</v>
-      </c>
-      <c r="J105" s="41">
+        <v>170</v>
+      </c>
+      <c r="J105" s="40">
         <v>-1.0</v>
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="40" t="s">
+      <c r="A106" s="41" t="s">
         <v>76</v>
       </c>
-      <c r="B106" s="40" t="s">
+      <c r="B106" s="41" t="s">
         <v>76</v>
       </c>
       <c r="C106" s="5">
         <v>25002.0</v>
       </c>
       <c r="D106" s="39" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="E106" s="19">
         <v>25003.0</v>
       </c>
       <c r="F106" s="39" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="G106" s="39" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="H106" s="39"/>
       <c r="I106" s="38" t="s">
-        <v>135</v>
-      </c>
-      <c r="J106" s="19">
-        <v>0.0</v>
+        <v>141</v>
+      </c>
+      <c r="J106" s="26">
+        <v>5.0</v>
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="40" t="s">
+      <c r="A107" s="41" t="s">
         <v>76</v>
       </c>
-      <c r="B107" s="40" t="s">
+      <c r="B107" s="41" t="s">
         <v>76</v>
       </c>
       <c r="C107" s="5">
         <v>25003.0</v>
       </c>
       <c r="D107" s="36" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="E107" s="28">
         <v>25004.0</v>
       </c>
       <c r="F107" s="36" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="G107" s="36" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="H107" s="36"/>
       <c r="I107" s="36" t="s">
-        <v>164</v>
-      </c>
-      <c r="J107" s="41">
+        <v>170</v>
+      </c>
+      <c r="J107" s="40">
         <v>-1.0</v>
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="40" t="s">
+      <c r="A108" s="41" t="s">
         <v>76</v>
       </c>
-      <c r="B108" s="40" t="s">
+      <c r="B108" s="41" t="s">
         <v>76</v>
       </c>
       <c r="C108" s="5">
         <v>25004.0</v>
       </c>
       <c r="D108" s="39" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="E108" s="19">
         <v>25005.0</v>
       </c>
       <c r="F108" s="39" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="G108" s="39" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="H108" s="39"/>
       <c r="I108" s="38" t="s">
-        <v>135</v>
-      </c>
-      <c r="J108" s="19">
-        <v>0.0</v>
+        <v>141</v>
+      </c>
+      <c r="J108" s="26">
+        <v>5.0</v>
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="40" t="s">
+      <c r="A109" s="41" t="s">
         <v>76</v>
       </c>
-      <c r="B109" s="40" t="s">
+      <c r="B109" s="41" t="s">
         <v>76</v>
       </c>
       <c r="C109" s="5">
         <v>25005.0</v>
       </c>
       <c r="D109" s="36" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="E109" s="28">
         <v>25006.0</v>
       </c>
       <c r="F109" s="36" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="G109" s="36" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="H109" s="36"/>
       <c r="I109" s="38" t="s">
-        <v>135</v>
-      </c>
-      <c r="J109" s="28">
-        <v>0.0</v>
+        <v>141</v>
+      </c>
+      <c r="J109" s="40">
+        <v>5.0</v>
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="40" t="s">
+      <c r="A110" s="41" t="s">
         <v>76</v>
       </c>
-      <c r="B110" s="40" t="s">
+      <c r="B110" s="41" t="s">
         <v>76</v>
       </c>
       <c r="C110" s="5">
         <v>25006.0</v>
       </c>
       <c r="D110" s="39" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="E110" s="19">
         <v>-1.0</v>
       </c>
       <c r="F110" s="39" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="G110" s="39" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="H110" s="39"/>
       <c r="I110" s="38" t="s">
-        <v>135</v>
-      </c>
-      <c r="J110" s="19">
-        <v>0.0</v>
+        <v>141</v>
+      </c>
+      <c r="J110" s="26">
+        <v>5.0</v>
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="40" t="s">
+      <c r="A111" s="41" t="s">
         <v>78</v>
       </c>
-      <c r="B111" s="40" t="s">
+      <c r="B111" s="41" t="s">
         <v>78</v>
       </c>
       <c r="C111" s="5">
         <v>26001.0</v>
       </c>
       <c r="D111" s="36" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="E111" s="28">
         <v>-1.0</v>
       </c>
       <c r="F111" s="36" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="G111" s="36" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="H111" s="36"/>
       <c r="I111" s="36" t="s">
-        <v>164</v>
-      </c>
-      <c r="J111" s="28">
-        <v>0.0</v>
+        <v>170</v>
+      </c>
+      <c r="J111" s="40">
+        <v>-1.0</v>
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="40" t="s">
+      <c r="A112" s="41" t="s">
         <v>80</v>
       </c>
-      <c r="B112" s="40" t="s">
+      <c r="B112" s="41" t="s">
         <v>80</v>
       </c>
       <c r="C112" s="5">
         <v>27001.0</v>
       </c>
       <c r="D112" s="39" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="E112" s="19">
         <v>27002.0</v>
       </c>
       <c r="F112" s="39" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="G112" s="39" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="H112" s="39"/>
       <c r="I112" s="38" t="s">
-        <v>135</v>
-      </c>
-      <c r="J112" s="19">
-        <v>0.0</v>
+        <v>141</v>
+      </c>
+      <c r="J112" s="26">
+        <v>2.0</v>
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="40" t="s">
+      <c r="A113" s="41" t="s">
         <v>80</v>
       </c>
-      <c r="B113" s="40" t="s">
+      <c r="B113" s="41" t="s">
         <v>80</v>
       </c>
       <c r="C113" s="5">
         <v>27002.0</v>
       </c>
       <c r="D113" s="36" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="E113" s="28">
         <v>27003.0</v>
       </c>
       <c r="F113" s="36" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="G113" s="36" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="H113" s="36"/>
       <c r="I113" s="38" t="s">
-        <v>135</v>
-      </c>
-      <c r="J113" s="28">
-        <v>0.0</v>
+        <v>141</v>
+      </c>
+      <c r="J113" s="40">
+        <v>2.0</v>
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="40" t="s">
+      <c r="A114" s="41" t="s">
         <v>80</v>
       </c>
-      <c r="B114" s="40" t="s">
+      <c r="B114" s="41" t="s">
         <v>80</v>
       </c>
       <c r="C114" s="5">
         <v>27003.0</v>
       </c>
       <c r="D114" s="39" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="E114" s="19">
         <v>-1.0</v>
       </c>
       <c r="F114" s="39" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="G114" s="39" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="H114" s="39"/>
       <c r="I114" s="38" t="s">
-        <v>135</v>
-      </c>
-      <c r="J114" s="19">
-        <v>0.0</v>
+        <v>141</v>
+      </c>
+      <c r="J114" s="26">
+        <v>2.0</v>
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="40" t="s">
+      <c r="A115" s="41" t="s">
         <v>82</v>
       </c>
-      <c r="B115" s="40" t="s">
+      <c r="B115" s="41" t="s">
         <v>82</v>
       </c>
       <c r="C115" s="5">
         <v>28001.0</v>
       </c>
       <c r="D115" s="36" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="E115" s="28">
         <v>28002.0</v>
       </c>
       <c r="F115" s="36" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="G115" s="36" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="H115" s="36"/>
       <c r="I115" s="36" t="s">
-        <v>164</v>
-      </c>
-      <c r="J115" s="41">
+        <v>170</v>
+      </c>
+      <c r="J115" s="40">
         <v>-1.0</v>
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="40" t="s">
+      <c r="A116" s="41" t="s">
         <v>82</v>
       </c>
-      <c r="B116" s="40" t="s">
+      <c r="B116" s="41" t="s">
         <v>82</v>
       </c>
       <c r="C116" s="5">
         <v>28002.0</v>
       </c>
       <c r="D116" s="39" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="E116" s="19">
         <v>28003.0</v>
       </c>
       <c r="F116" s="39" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="G116" s="39" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="H116" s="39"/>
       <c r="I116" s="39" t="s">
-        <v>164</v>
-      </c>
-      <c r="J116" s="41">
+        <v>170</v>
+      </c>
+      <c r="J116" s="40">
         <v>-1.0</v>
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="40" t="s">
+      <c r="A117" s="41" t="s">
         <v>82</v>
       </c>
-      <c r="B117" s="40" t="s">
+      <c r="B117" s="41" t="s">
         <v>82</v>
       </c>
       <c r="C117" s="5">
         <v>28003.0</v>
       </c>
       <c r="D117" s="36" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="E117" s="28">
         <v>-1.0</v>
       </c>
       <c r="F117" s="36" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="G117" s="36" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="H117" s="36"/>
       <c r="I117" s="38" t="s">
-        <v>135</v>
-      </c>
-      <c r="J117" s="28">
-        <v>0.0</v>
+        <v>141</v>
+      </c>
+      <c r="J117" s="40">
+        <v>2.0</v>
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="40" t="s">
+      <c r="A118" s="41" t="s">
         <v>84</v>
       </c>
-      <c r="B118" s="40" t="s">
+      <c r="B118" s="41" t="s">
         <v>84</v>
       </c>
       <c r="C118" s="5">
         <v>29001.0</v>
       </c>
       <c r="D118" s="39" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="E118" s="19">
         <v>-1.0</v>
       </c>
       <c r="F118" s="39" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="G118" s="39" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="H118" s="39"/>
       <c r="I118" s="38" t="s">
-        <v>135</v>
-      </c>
-      <c r="J118" s="19">
-        <v>0.0</v>
+        <v>141</v>
+      </c>
+      <c r="J118" s="26">
+        <v>-1.0</v>
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="40" t="s">
+      <c r="A119" s="41" t="s">
         <v>86</v>
       </c>
-      <c r="B119" s="40" t="s">
+      <c r="B119" s="41" t="s">
         <v>86</v>
       </c>
       <c r="C119" s="5">
         <v>30001.0</v>
       </c>
       <c r="D119" s="36" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="E119" s="28">
         <v>30002.0</v>
       </c>
       <c r="F119" s="36" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="G119" s="36" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="H119" s="36"/>
       <c r="I119" s="38" t="s">
-        <v>135</v>
-      </c>
-      <c r="J119" s="28">
-        <v>0.0</v>
+        <v>141</v>
+      </c>
+      <c r="J119" s="40">
+        <v>2.0</v>
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="40" t="s">
+      <c r="A120" s="41" t="s">
         <v>86</v>
       </c>
-      <c r="B120" s="40" t="s">
+      <c r="B120" s="41" t="s">
         <v>86</v>
       </c>
       <c r="C120" s="5">
         <v>30002.0</v>
       </c>
       <c r="D120" s="39" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="E120" s="19">
         <v>30003.0</v>
       </c>
       <c r="F120" s="39" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="G120" s="39" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="H120" s="39"/>
       <c r="I120" s="38" t="s">
-        <v>135</v>
-      </c>
-      <c r="J120" s="19">
-        <v>0.0</v>
+        <v>141</v>
+      </c>
+      <c r="J120" s="26">
+        <v>1.0</v>
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="40" t="s">
+      <c r="A121" s="41" t="s">
         <v>86</v>
       </c>
-      <c r="B121" s="40" t="s">
+      <c r="B121" s="41" t="s">
         <v>86</v>
       </c>
       <c r="C121" s="5">
         <v>30003.0</v>
       </c>
       <c r="D121" s="36" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="E121" s="28">
         <v>-1.0</v>
       </c>
       <c r="F121" s="36" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="G121" s="36" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="H121" s="36"/>
       <c r="I121" s="38" t="s">
-        <v>135</v>
-      </c>
-      <c r="J121" s="28">
-        <v>0.0</v>
+        <v>141</v>
+      </c>
+      <c r="J121" s="40">
+        <v>2.0</v>
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="40" t="s">
+      <c r="A122" s="41" t="s">
         <v>88</v>
       </c>
-      <c r="B122" s="40" t="s">
+      <c r="B122" s="41" t="s">
         <v>88</v>
       </c>
       <c r="C122" s="5">
         <v>31001.0</v>
       </c>
       <c r="D122" s="39" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="E122" s="19">
         <v>31002.0</v>
       </c>
       <c r="F122" s="39" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="G122" s="39" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="H122" s="39"/>
       <c r="I122" s="38" t="s">
-        <v>135</v>
-      </c>
-      <c r="J122" s="19">
-        <v>0.0</v>
+        <v>141</v>
+      </c>
+      <c r="J122" s="26">
+        <v>5.0</v>
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="40" t="s">
+      <c r="A123" s="41" t="s">
         <v>88</v>
       </c>
-      <c r="B123" s="40" t="s">
+      <c r="B123" s="41" t="s">
         <v>88</v>
       </c>
       <c r="C123" s="5">
         <v>31002.0</v>
       </c>
       <c r="D123" s="36" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="E123" s="28">
         <v>-1.0</v>
       </c>
       <c r="F123" s="36" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="G123" s="36" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="H123" s="36"/>
       <c r="I123" s="38" t="s">
-        <v>135</v>
-      </c>
-      <c r="J123" s="28">
-        <v>0.0</v>
+        <v>141</v>
+      </c>
+      <c r="J123" s="40">
+        <v>6.0</v>
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="40" t="s">
+      <c r="A124" s="41" t="s">
         <v>90</v>
       </c>
-      <c r="B124" s="40" t="s">
+      <c r="B124" s="41" t="s">
         <v>90</v>
       </c>
       <c r="C124" s="5">
         <v>32001.0</v>
       </c>
       <c r="D124" s="39" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="E124" s="19">
         <v>32002.0</v>
       </c>
       <c r="F124" s="39" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="G124" s="39" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="H124" s="39"/>
       <c r="I124" s="39" t="s">
-        <v>164</v>
-      </c>
-      <c r="J124" s="41">
+        <v>170</v>
+      </c>
+      <c r="J124" s="40">
         <v>-1.0</v>
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="40" t="s">
+      <c r="A125" s="41" t="s">
         <v>90</v>
       </c>
-      <c r="B125" s="40" t="s">
+      <c r="B125" s="41" t="s">
         <v>90</v>
       </c>
       <c r="C125" s="5">
         <v>32002.0</v>
       </c>
       <c r="D125" s="36" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="E125" s="28">
         <v>32003.0</v>
       </c>
       <c r="F125" s="36" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="G125" s="36" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="H125" s="36"/>
       <c r="I125" s="36" t="s">
-        <v>164</v>
-      </c>
-      <c r="J125" s="41">
+        <v>170</v>
+      </c>
+      <c r="J125" s="40">
         <v>-1.0</v>
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="40" t="s">
+      <c r="A126" s="41" t="s">
         <v>90</v>
       </c>
-      <c r="B126" s="40" t="s">
+      <c r="B126" s="41" t="s">
         <v>90</v>
       </c>
       <c r="C126" s="5">
         <v>32003.0</v>
       </c>
       <c r="D126" s="39" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="E126" s="19">
         <v>32004.0</v>
       </c>
       <c r="F126" s="39" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="G126" s="39" t="s">
-        <v>140</v>
+        <v>146</v>
       </c>
       <c r="H126" s="39"/>
       <c r="I126" s="39" t="s">
-        <v>164</v>
-      </c>
-      <c r="J126" s="41">
+        <v>170</v>
+      </c>
+      <c r="J126" s="40">
         <v>-1.0</v>
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="40" t="s">
+      <c r="A127" s="41" t="s">
         <v>90</v>
       </c>
-      <c r="B127" s="40" t="s">
+      <c r="B127" s="41" t="s">
         <v>90</v>
       </c>
       <c r="C127" s="5">
         <v>32004.0</v>
       </c>
       <c r="D127" s="36" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="E127" s="28">
         <v>32005.0</v>
       </c>
       <c r="F127" s="36" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="G127" s="36" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="H127" s="36"/>
       <c r="I127" s="38" t="s">
-        <v>135</v>
-      </c>
-      <c r="J127" s="28">
-        <v>0.0</v>
+        <v>141</v>
+      </c>
+      <c r="J127" s="40">
+        <v>5.0</v>
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="40" t="s">
+      <c r="A128" s="41" t="s">
         <v>90</v>
       </c>
-      <c r="B128" s="40" t="s">
+      <c r="B128" s="41" t="s">
         <v>90</v>
       </c>
       <c r="C128" s="5">
         <v>32005.0</v>
       </c>
       <c r="D128" s="39" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="E128" s="19">
         <v>32006.0</v>
       </c>
       <c r="F128" s="39" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="G128" s="39" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="H128" s="39"/>
       <c r="I128" s="38" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="J128" s="19">
         <v>0.0</v>
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="40" t="s">
+      <c r="A129" s="41" t="s">
         <v>90</v>
       </c>
-      <c r="B129" s="40" t="s">
+      <c r="B129" s="41" t="s">
         <v>90</v>
       </c>
       <c r="C129" s="5">
         <v>32006.0</v>
       </c>
       <c r="D129" s="36" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="E129" s="28">
         <v>-1.0</v>
       </c>
       <c r="F129" s="36" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="G129" s="36" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="H129" s="36"/>
       <c r="I129" s="38" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="J129" s="28">
         <v>0.0</v>
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="40" t="s">
+      <c r="A130" s="41" t="s">
         <v>92</v>
       </c>
-      <c r="B130" s="40" t="s">
+      <c r="B130" s="41" t="s">
         <v>92</v>
       </c>
       <c r="C130" s="5">
         <v>33001.0</v>
       </c>
       <c r="D130" s="39" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="E130" s="19">
         <v>33002.0</v>
       </c>
       <c r="F130" s="39" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="G130" s="39" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="H130" s="39"/>
       <c r="I130" s="38" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="J130" s="19">
         <v>0.0</v>
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="40" t="s">
+      <c r="A131" s="41" t="s">
         <v>92</v>
       </c>
-      <c r="B131" s="40" t="s">
+      <c r="B131" s="41" t="s">
         <v>92</v>
       </c>
       <c r="C131" s="5">
         <v>33002.0</v>
       </c>
       <c r="D131" s="36" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="E131" s="28">
         <v>-1.0</v>
       </c>
       <c r="F131" s="36" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="G131" s="36" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="H131" s="36"/>
       <c r="I131" s="38" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="J131" s="28">
         <v>0.0</v>
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="40" t="s">
+      <c r="A132" s="41" t="s">
         <v>94</v>
       </c>
-      <c r="B132" s="40" t="s">
+      <c r="B132" s="41" t="s">
         <v>94</v>
       </c>
       <c r="C132" s="5">
         <v>34001.0</v>
       </c>
       <c r="D132" s="39" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="E132" s="19">
         <v>34002.0</v>
       </c>
       <c r="F132" s="39" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="G132" s="39" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="H132" s="39"/>
       <c r="I132" s="39" t="s">
-        <v>164</v>
-      </c>
-      <c r="J132" s="41">
+        <v>170</v>
+      </c>
+      <c r="J132" s="40">
         <v>-1.0</v>
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="40" t="s">
+      <c r="A133" s="41" t="s">
         <v>94</v>
       </c>
-      <c r="B133" s="40" t="s">
+      <c r="B133" s="41" t="s">
         <v>94</v>
       </c>
       <c r="C133" s="5">
         <v>34002.0</v>
       </c>
       <c r="D133" s="36" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="E133" s="28">
         <v>34003.0</v>
       </c>
       <c r="F133" s="36" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="G133" s="36" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="H133" s="36"/>
       <c r="I133" s="36" t="s">
-        <v>164</v>
-      </c>
-      <c r="J133" s="41">
+        <v>170</v>
+      </c>
+      <c r="J133" s="40">
         <v>-1.0</v>
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="40" t="s">
+      <c r="A134" s="41" t="s">
         <v>94</v>
       </c>
-      <c r="B134" s="40" t="s">
+      <c r="B134" s="41" t="s">
         <v>94</v>
       </c>
       <c r="C134" s="5">
         <v>34003.0</v>
       </c>
       <c r="D134" s="39" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="E134" s="19">
         <v>-1.0</v>
       </c>
       <c r="F134" s="39" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="G134" s="39" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="H134" s="39"/>
       <c r="I134" s="38" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="J134" s="19">
         <v>0.0</v>
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="40" t="s">
+      <c r="A135" s="41" t="s">
         <v>96</v>
       </c>
-      <c r="B135" s="40" t="s">
+      <c r="B135" s="41" t="s">
         <v>96</v>
       </c>
       <c r="C135" s="5">
         <v>35001.0</v>
       </c>
       <c r="D135" s="36" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="E135" s="28">
         <v>-1.0</v>
       </c>
       <c r="F135" s="36" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="G135" s="36" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="H135" s="36"/>
       <c r="I135" s="38" t="s">
-        <v>135</v>
-      </c>
-      <c r="J135" s="28">
-        <v>0.0</v>
+        <v>141</v>
+      </c>
+      <c r="J135" s="40">
+        <v>-1.0</v>
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="40" t="s">
+      <c r="A136" s="41" t="s">
         <v>98</v>
       </c>
-      <c r="B136" s="40" t="s">
+      <c r="B136" s="41" t="s">
         <v>98</v>
       </c>
       <c r="C136" s="5">
         <v>36001.0</v>
       </c>
       <c r="D136" s="39" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="E136" s="19">
         <v>36002.0</v>
       </c>
       <c r="F136" s="39" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="G136" s="39" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="H136" s="39"/>
       <c r="I136" s="38" t="s">
-        <v>135</v>
-      </c>
-      <c r="J136" s="19">
-        <v>0.0</v>
+        <v>141</v>
+      </c>
+      <c r="J136" s="26">
+        <v>1.0</v>
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="40" t="s">
+      <c r="A137" s="41" t="s">
         <v>98</v>
       </c>
-      <c r="B137" s="40" t="s">
+      <c r="B137" s="41" t="s">
         <v>98</v>
       </c>
       <c r="C137" s="5">
         <v>36002.0</v>
       </c>
       <c r="D137" s="36" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="E137" s="28">
         <v>36003.0</v>
       </c>
       <c r="F137" s="36" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="G137" s="36" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="H137" s="36"/>
       <c r="I137" s="38" t="s">
-        <v>135</v>
-      </c>
-      <c r="J137" s="28">
-        <v>0.0</v>
+        <v>141</v>
+      </c>
+      <c r="J137" s="40">
+        <v>2.0</v>
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="40" t="s">
+      <c r="A138" s="41" t="s">
         <v>98</v>
       </c>
-      <c r="B138" s="40" t="s">
+      <c r="B138" s="41" t="s">
         <v>98</v>
       </c>
       <c r="C138" s="5">
         <v>36003.0</v>
       </c>
       <c r="D138" s="39" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="E138" s="19">
         <v>36004.0</v>
       </c>
       <c r="F138" s="39" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="G138" s="39" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="H138" s="39"/>
       <c r="I138" s="38" t="s">
-        <v>135</v>
-      </c>
-      <c r="J138" s="19">
-        <v>0.0</v>
+        <v>141</v>
+      </c>
+      <c r="J138" s="26">
+        <v>2.0</v>
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="40" t="s">
+      <c r="A139" s="41" t="s">
         <v>98</v>
       </c>
-      <c r="B139" s="40" t="s">
+      <c r="B139" s="41" t="s">
         <v>98</v>
       </c>
       <c r="C139" s="5">
         <v>36004.0</v>
       </c>
       <c r="D139" s="36" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="E139" s="28">
         <v>-1.0</v>
       </c>
       <c r="F139" s="36" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="G139" s="36" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="H139" s="36"/>
       <c r="I139" s="38" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="J139" s="28">
         <v>0.0</v>
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="40" t="s">
+      <c r="A140" s="41" t="s">
         <v>100</v>
       </c>
-      <c r="B140" s="40" t="s">
+      <c r="B140" s="41" t="s">
         <v>100</v>
       </c>
       <c r="C140" s="5">
         <v>37001.0</v>
       </c>
       <c r="D140" s="39" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="E140" s="19">
         <v>37002.0</v>
       </c>
       <c r="F140" s="39" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="G140" s="39" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="H140" s="39"/>
       <c r="I140" s="38" t="s">
-        <v>135</v>
-      </c>
-      <c r="J140" s="19">
-        <v>0.0</v>
+        <v>141</v>
+      </c>
+      <c r="J140" s="26">
+        <v>5.0</v>
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="40" t="s">
+      <c r="A141" s="41" t="s">
         <v>100</v>
       </c>
-      <c r="B141" s="40" t="s">
+      <c r="B141" s="41" t="s">
         <v>100</v>
       </c>
       <c r="C141" s="5">
         <v>37002.0</v>
       </c>
       <c r="D141" s="36" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="E141" s="28">
         <v>37003.0</v>
       </c>
       <c r="F141" s="36" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="G141" s="36" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="H141" s="36"/>
       <c r="I141" s="38" t="s">
-        <v>135</v>
-      </c>
-      <c r="J141" s="28">
-        <v>0.0</v>
+        <v>141</v>
+      </c>
+      <c r="J141" s="40">
+        <v>6.0</v>
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="40" t="s">
+      <c r="A142" s="41" t="s">
         <v>100</v>
       </c>
-      <c r="B142" s="40" t="s">
+      <c r="B142" s="41" t="s">
         <v>100</v>
       </c>
       <c r="C142" s="5">
         <v>37003.0</v>
       </c>
       <c r="D142" s="39" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="E142" s="19">
         <v>-1.0</v>
       </c>
       <c r="F142" s="39" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="G142" s="39" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="H142" s="39"/>
       <c r="I142" s="38" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="J142" s="19">
         <v>0.0</v>
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="40" t="s">
+      <c r="A143" s="41" t="s">
         <v>102</v>
       </c>
-      <c r="B143" s="40" t="s">
+      <c r="B143" s="41" t="s">
         <v>102</v>
       </c>
       <c r="C143" s="5">
         <v>38001.0</v>
       </c>
       <c r="D143" s="36" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="E143" s="28">
         <v>38002.0</v>
       </c>
       <c r="F143" s="36" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="G143" s="36" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="H143" s="36"/>
       <c r="I143" s="38" t="s">
-        <v>135</v>
-      </c>
-      <c r="J143" s="28">
-        <v>0.0</v>
+        <v>141</v>
+      </c>
+      <c r="J143" s="40">
+        <v>6.0</v>
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="40" t="s">
+      <c r="A144" s="41" t="s">
         <v>102</v>
       </c>
-      <c r="B144" s="40" t="s">
+      <c r="B144" s="41" t="s">
         <v>102</v>
       </c>
       <c r="C144" s="5">
         <v>38002.0</v>
       </c>
       <c r="D144" s="39" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="E144" s="19">
         <v>38003.0</v>
       </c>
       <c r="F144" s="39" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="G144" s="39" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="H144" s="39"/>
       <c r="I144" s="38" t="s">
-        <v>135</v>
-      </c>
-      <c r="J144" s="19">
-        <v>0.0</v>
+        <v>141</v>
+      </c>
+      <c r="J144" s="26">
+        <v>5.0</v>
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="40" t="s">
+      <c r="A145" s="41" t="s">
         <v>102</v>
       </c>
-      <c r="B145" s="40" t="s">
+      <c r="B145" s="41" t="s">
         <v>102</v>
       </c>
       <c r="C145" s="5">
         <v>38003.0</v>
       </c>
       <c r="D145" s="36" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="E145" s="28">
         <v>38004.0</v>
       </c>
       <c r="F145" s="36" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="G145" s="36" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="H145" s="36"/>
       <c r="I145" s="38" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="J145" s="28">
         <v>0.0</v>
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="40" t="s">
+      <c r="A146" s="41" t="s">
         <v>102</v>
       </c>
-      <c r="B146" s="40" t="s">
+      <c r="B146" s="41" t="s">
         <v>102</v>
       </c>
       <c r="C146" s="5">
         <v>38004.0</v>
       </c>
       <c r="D146" s="39" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="E146" s="19">
         <v>-1.0</v>
       </c>
       <c r="F146" s="39" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="G146" s="39" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="H146" s="39"/>
       <c r="I146" s="38" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="J146" s="19">
         <v>0.0</v>
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="40" t="s">
+      <c r="A147" s="41" t="s">
         <v>104</v>
       </c>
-      <c r="B147" s="40" t="s">
+      <c r="B147" s="41" t="s">
         <v>104</v>
       </c>
       <c r="C147" s="5">
         <v>39001.0</v>
       </c>
       <c r="D147" s="42" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="E147" s="28">
         <v>-1.0</v>
       </c>
       <c r="F147" s="36" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="G147" s="36" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="H147" s="36"/>
       <c r="I147" s="38" t="s">
-        <v>135</v>
+        <v>141</v>
       </c>
       <c r="J147" s="28">
         <v>0.0</v>
@@ -7123,23 +7192,23 @@
         <v>40000.0</v>
       </c>
       <c r="D148" s="42" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="E148" s="3">
         <v>40001.0</v>
       </c>
       <c r="F148" s="36" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="G148" s="36" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="H148" s="36"/>
       <c r="I148" s="38" t="s">
-        <v>135</v>
-      </c>
-      <c r="J148" s="28">
-        <v>0.0</v>
+        <v>141</v>
+      </c>
+      <c r="J148" s="40">
+        <v>6.0</v>
       </c>
     </row>
     <row r="149">
@@ -7153,88 +7222,204 @@
         <v>40001.0</v>
       </c>
       <c r="D149" s="42" t="s">
-        <v>290</v>
-      </c>
-      <c r="E149" s="41">
+        <v>296</v>
+      </c>
+      <c r="E149" s="40">
         <v>-1.0</v>
       </c>
       <c r="F149" s="36" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="G149" s="36" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="H149" s="36"/>
       <c r="I149" s="38" t="s">
-        <v>135</v>
-      </c>
-      <c r="J149" s="28">
-        <v>0.0</v>
+        <v>141</v>
+      </c>
+      <c r="J149" s="40">
+        <v>5.0</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="32" t="s">
-        <v>291</v>
+        <v>108</v>
       </c>
       <c r="B150" s="32" t="s">
-        <v>291</v>
+        <v>108</v>
       </c>
       <c r="C150" s="3">
         <v>41001.0</v>
       </c>
       <c r="D150" s="42" t="s">
-        <v>292</v>
-      </c>
-      <c r="E150" s="41">
+        <v>297</v>
+      </c>
+      <c r="E150" s="40">
         <v>-1.0</v>
       </c>
       <c r="F150" s="36" t="s">
-        <v>133</v>
+        <v>139</v>
       </c>
       <c r="G150" s="36" t="s">
-        <v>134</v>
+        <v>140</v>
       </c>
       <c r="H150" s="36"/>
       <c r="I150" s="43" t="s">
-        <v>164</v>
-      </c>
-      <c r="J150" s="41">
+        <v>170</v>
+      </c>
+      <c r="J150" s="40">
         <v>-1.0</v>
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="44"/>
-      <c r="B151" s="44"/>
-      <c r="D151" s="42"/>
-      <c r="E151" s="18"/>
-      <c r="F151" s="36"/>
-      <c r="G151" s="36"/>
+      <c r="A151" s="32" t="s">
+        <v>110</v>
+      </c>
+      <c r="B151" s="32" t="s">
+        <v>110</v>
+      </c>
+      <c r="C151" s="3">
+        <v>42001.0</v>
+      </c>
+      <c r="D151" s="42" t="s">
+        <v>298</v>
+      </c>
+      <c r="E151" s="40">
+        <v>42002.0</v>
+      </c>
+      <c r="F151" s="42" t="s">
+        <v>139</v>
+      </c>
+      <c r="G151" s="42" t="s">
+        <v>140</v>
+      </c>
       <c r="H151" s="36"/>
-      <c r="I151" s="38"/>
-      <c r="J151" s="28"/>
+      <c r="I151" s="43" t="s">
+        <v>141</v>
+      </c>
+      <c r="J151" s="40">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="152">
-      <c r="A152" s="44"/>
-      <c r="B152" s="44"/>
-      <c r="D152" s="42"/>
-      <c r="E152" s="18"/>
-      <c r="F152" s="36"/>
-      <c r="G152" s="36"/>
+      <c r="A152" s="32" t="s">
+        <v>110</v>
+      </c>
+      <c r="B152" s="32" t="s">
+        <v>110</v>
+      </c>
+      <c r="C152" s="3">
+        <v>42002.0</v>
+      </c>
+      <c r="D152" s="42" t="s">
+        <v>299</v>
+      </c>
+      <c r="E152" s="40">
+        <v>-1.0</v>
+      </c>
+      <c r="F152" s="42" t="s">
+        <v>139</v>
+      </c>
+      <c r="G152" s="42" t="s">
+        <v>140</v>
+      </c>
       <c r="H152" s="36"/>
-      <c r="I152" s="38"/>
-      <c r="J152" s="28"/>
+      <c r="I152" s="43" t="s">
+        <v>141</v>
+      </c>
+      <c r="J152" s="40">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="153">
-      <c r="A153" s="44"/>
-      <c r="B153" s="44"/>
+      <c r="A153" s="32" t="s">
+        <v>112</v>
+      </c>
+      <c r="B153" s="32" t="s">
+        <v>112</v>
+      </c>
+      <c r="C153" s="3">
+        <v>43001.0</v>
+      </c>
+      <c r="D153" s="42" t="s">
+        <v>300</v>
+      </c>
+      <c r="E153" s="40">
+        <v>43002.0</v>
+      </c>
+      <c r="F153" s="42" t="s">
+        <v>139</v>
+      </c>
+      <c r="G153" s="42" t="s">
+        <v>140</v>
+      </c>
+      <c r="H153" s="36"/>
+      <c r="I153" s="43" t="s">
+        <v>141</v>
+      </c>
+      <c r="J153" s="40">
+        <v>6.0</v>
+      </c>
     </row>
     <row r="154">
-      <c r="A154" s="44"/>
-      <c r="B154" s="44"/>
+      <c r="A154" s="32" t="s">
+        <v>112</v>
+      </c>
+      <c r="B154" s="32" t="s">
+        <v>112</v>
+      </c>
+      <c r="C154" s="3">
+        <v>43002.0</v>
+      </c>
+      <c r="D154" s="42" t="s">
+        <v>301</v>
+      </c>
+      <c r="E154" s="40">
+        <v>43003.0</v>
+      </c>
+      <c r="F154" s="42" t="s">
+        <v>139</v>
+      </c>
+      <c r="G154" s="42" t="s">
+        <v>140</v>
+      </c>
+      <c r="H154" s="36"/>
+      <c r="I154" s="43" t="s">
+        <v>141</v>
+      </c>
+      <c r="J154" s="40">
+        <v>5.0</v>
+      </c>
     </row>
     <row r="155">
-      <c r="A155" s="44"/>
-      <c r="B155" s="44"/>
+      <c r="A155" s="32" t="s">
+        <v>112</v>
+      </c>
+      <c r="B155" s="32" t="s">
+        <v>112</v>
+      </c>
+      <c r="C155" s="3">
+        <v>43003.0</v>
+      </c>
+      <c r="D155" s="42" t="s">
+        <v>302</v>
+      </c>
+      <c r="E155" s="40">
+        <v>-1.0</v>
+      </c>
+      <c r="F155" s="42" t="s">
+        <v>139</v>
+      </c>
+      <c r="G155" s="42" t="s">
+        <v>140</v>
+      </c>
+      <c r="H155" s="36"/>
+      <c r="I155" s="43" t="s">
+        <v>141</v>
+      </c>
+      <c r="J155" s="40">
+        <v>5.0</v>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="44"/>
@@ -10563,48 +10748,48 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="4" t="s">
-        <v>129</v>
+        <v>135</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>293</v>
+        <v>303</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>294</v>
+        <v>304</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>295</v>
+        <v>305</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>296</v>
+        <v>306</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>297</v>
+        <v>307</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>298</v>
+        <v>308</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>299</v>
+        <v>309</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>301</v>
+        <v>311</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>302</v>
+        <v>312</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="45" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="B2" s="46" t="s">
-        <v>303</v>
+        <v>313</v>
       </c>
       <c r="C2" s="46" t="s">
-        <v>304</v>
+        <v>314</v>
       </c>
       <c r="D2" s="4"/>
       <c r="E2" s="3">
@@ -10619,13 +10804,13 @@
     </row>
     <row r="3">
       <c r="A3" s="47" t="s">
-        <v>305</v>
+        <v>315</v>
       </c>
       <c r="B3" s="46" t="s">
-        <v>306</v>
+        <v>316</v>
       </c>
       <c r="C3" s="48" t="s">
-        <v>307</v>
+        <v>317</v>
       </c>
       <c r="D3" s="4"/>
       <c r="E3" s="5">
@@ -10636,24 +10821,24 @@
       </c>
       <c r="G3" s="4"/>
       <c r="H3" s="3" t="s">
-        <v>308</v>
+        <v>318</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>309</v>
+        <v>319</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>310</v>
+        <v>320</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>311</v>
+        <v>321</v>
       </c>
       <c r="B4" s="49" t="s">
-        <v>312</v>
+        <v>322</v>
       </c>
       <c r="C4" s="49" t="s">
-        <v>313</v>
+        <v>323</v>
       </c>
       <c r="D4" s="4"/>
       <c r="E4" s="2">
@@ -10664,24 +10849,24 @@
       </c>
       <c r="G4" s="4"/>
       <c r="H4" s="3" t="s">
-        <v>314</v>
+        <v>324</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>315</v>
+        <v>325</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>316</v>
+        <v>326</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>317</v>
+        <v>327</v>
       </c>
       <c r="B5" s="50" t="s">
-        <v>318</v>
+        <v>328</v>
       </c>
       <c r="C5" s="50" t="s">
-        <v>319</v>
+        <v>329</v>
       </c>
       <c r="E5" s="3">
         <v>-10.0</v>
@@ -10690,24 +10875,24 @@
         <v>0.0</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>320</v>
+        <v>330</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>321</v>
+        <v>331</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>322</v>
+        <v>332</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>323</v>
+        <v>333</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>324</v>
+        <v>334</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>325</v>
+        <v>335</v>
       </c>
       <c r="E6" s="3">
         <v>0.0</v>
@@ -10716,24 +10901,24 @@
         <v>-10.0</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>326</v>
+        <v>336</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>327</v>
+        <v>337</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>328</v>
+        <v>338</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>329</v>
+        <v>339</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>330</v>
+        <v>340</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>331</v>
+        <v>341</v>
       </c>
       <c r="E7" s="3">
         <v>-10.0</v>
@@ -10742,24 +10927,24 @@
         <v>0.0</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>332</v>
+        <v>342</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>333</v>
+        <v>343</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>334</v>
+        <v>344</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>335</v>
+        <v>345</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>336</v>
+        <v>346</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>337</v>
+        <v>347</v>
       </c>
       <c r="E8" s="3">
         <v>0.0</v>
@@ -10768,24 +10953,24 @@
         <v>-10.0</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>338</v>
+        <v>348</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>339</v>
+        <v>349</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>340</v>
+        <v>350</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>342</v>
+        <v>352</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>343</v>
+        <v>353</v>
       </c>
       <c r="E9" s="3">
         <v>0.0</v>
@@ -10794,25 +10979,25 @@
         <v>0.0</v>
       </c>
       <c r="H9" s="32" t="s">
-        <v>344</v>
+        <v>354</v>
       </c>
       <c r="I9" s="32" t="s">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="J9" s="32"/>
       <c r="K9" s="3" t="s">
-        <v>346</v>
+        <v>356</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>347</v>
+        <v>357</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>348</v>
+        <v>358</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>349</v>
+        <v>359</v>
       </c>
       <c r="E10" s="3">
         <v>-10.0</v>
@@ -10821,24 +11006,24 @@
         <v>-10.0</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>350</v>
+        <v>360</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>351</v>
+        <v>361</v>
       </c>
       <c r="K10" s="51" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>353</v>
+        <v>363</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>354</v>
+        <v>364</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>355</v>
+        <v>365</v>
       </c>
       <c r="E11" s="3">
         <v>-10.0</v>
@@ -10847,24 +11032,24 @@
         <v>-10.0</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>356</v>
+        <v>366</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>357</v>
+        <v>367</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>358</v>
+        <v>368</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>359</v>
+        <v>369</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>360</v>
+        <v>370</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="E12" s="3">
         <v>-10.0</v>
@@ -10873,13 +11058,13 @@
         <v>0.0</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>362</v>
+        <v>372</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>363</v>
+        <v>373</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>364</v>
+        <v>374</v>
       </c>
     </row>
   </sheetData>
@@ -10901,21 +11086,21 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="3" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>366</v>
+        <v>376</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>367</v>
+        <v>377</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>109</v>
+        <v>115</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>368</v>
+        <v>378</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>21</v>
@@ -10924,12 +11109,12 @@
         <v>24</v>
       </c>
       <c r="D2" s="52" t="s">
-        <v>369</v>
+        <v>379</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>370</v>
+        <v>380</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>24</v>
@@ -10938,40 +11123,40 @@
         <v>30</v>
       </c>
       <c r="D3" s="52" t="s">
-        <v>371</v>
+        <v>381</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>372</v>
+        <v>382</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>30</v>
       </c>
       <c r="C4" s="49" t="s">
-        <v>373</v>
+        <v>383</v>
       </c>
       <c r="D4" s="52" t="s">
-        <v>374</v>
+        <v>384</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>375</v>
+        <v>385</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>373</v>
+        <v>383</v>
       </c>
       <c r="C5" s="49" t="s">
         <v>36</v>
       </c>
       <c r="D5" s="52" t="s">
-        <v>376</v>
+        <v>386</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>377</v>
+        <v>387</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>36</v>
@@ -10980,12 +11165,12 @@
         <v>42</v>
       </c>
       <c r="D6" s="52" t="s">
-        <v>369</v>
+        <v>379</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>378</v>
+        <v>388</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>42</v>
@@ -10994,68 +11179,68 @@
         <v>48</v>
       </c>
       <c r="D7" s="52" t="s">
-        <v>371</v>
+        <v>381</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>379</v>
+        <v>389</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>48</v>
       </c>
       <c r="C8" s="49" t="s">
-        <v>322</v>
+        <v>332</v>
       </c>
       <c r="D8" s="52" t="s">
-        <v>380</v>
+        <v>390</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>381</v>
+        <v>391</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>322</v>
+        <v>332</v>
       </c>
       <c r="C9" s="49" t="s">
         <v>54</v>
       </c>
       <c r="D9" s="52" t="s">
-        <v>376</v>
+        <v>386</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>382</v>
+        <v>392</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>54</v>
       </c>
       <c r="C10" s="49" t="s">
-        <v>383</v>
+        <v>393</v>
       </c>
       <c r="D10" s="52" t="s">
-        <v>384</v>
+        <v>394</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>385</v>
+        <v>395</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>383</v>
+        <v>393</v>
       </c>
       <c r="C11" s="49" t="s">
         <v>57</v>
       </c>
       <c r="D11" s="52" t="s">
-        <v>386</v>
+        <v>396</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>387</v>
+        <v>397</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>57</v>
@@ -11064,12 +11249,12 @@
         <v>60</v>
       </c>
       <c r="D12" s="52" t="s">
-        <v>388</v>
+        <v>398</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>389</v>
+        <v>399</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>60</v>
@@ -11078,12 +11263,12 @@
         <v>106</v>
       </c>
       <c r="D13" s="52" t="s">
-        <v>390</v>
+        <v>400</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>391</v>
+        <v>401</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>106</v>
@@ -11092,24 +11277,24 @@
         <v>63</v>
       </c>
       <c r="D14" s="52" t="s">
-        <v>392</v>
+        <v>402</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>393</v>
+        <v>403</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>63</v>
       </c>
       <c r="C15" s="52"/>
       <c r="D15" s="52" t="s">
-        <v>394</v>
+        <v>404</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>395</v>
+        <v>405</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>66</v>
@@ -11118,26 +11303,26 @@
         <v>70</v>
       </c>
       <c r="D16" s="52" t="s">
-        <v>396</v>
+        <v>406</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>397</v>
+        <v>407</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>70</v>
       </c>
       <c r="C17" s="49" t="s">
-        <v>398</v>
+        <v>408</v>
       </c>
       <c r="D17" s="52" t="s">
-        <v>399</v>
+        <v>409</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>400</v>
+        <v>410</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>74</v>
@@ -11146,12 +11331,12 @@
         <v>76</v>
       </c>
       <c r="D18" s="52" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>402</v>
+        <v>412</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>76</v>
@@ -11160,40 +11345,40 @@
         <v>80</v>
       </c>
       <c r="D19" s="52" t="s">
-        <v>403</v>
+        <v>413</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>404</v>
+        <v>414</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>80</v>
       </c>
       <c r="C20" s="49" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="D20" s="52" t="s">
-        <v>405</v>
+        <v>415</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>406</v>
+        <v>416</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="C21" s="49" t="s">
         <v>86</v>
       </c>
       <c r="D21" s="52" t="s">
-        <v>407</v>
+        <v>417</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>408</v>
+        <v>418</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>86</v>
@@ -11202,12 +11387,12 @@
         <v>90</v>
       </c>
       <c r="D22" s="52" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>409</v>
+        <v>419</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>90</v>
@@ -11216,12 +11401,12 @@
         <v>92</v>
       </c>
       <c r="D23" s="52" t="s">
-        <v>410</v>
+        <v>420</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>411</v>
+        <v>421</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>92</v>
@@ -11230,41 +11415,41 @@
         <v>94</v>
       </c>
       <c r="D24" s="52" t="s">
-        <v>403</v>
+        <v>413</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>412</v>
+        <v>422</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>358</v>
+        <v>368</v>
       </c>
       <c r="C25" s="49" t="s">
         <v>98</v>
       </c>
       <c r="D25" s="52" t="s">
-        <v>407</v>
+        <v>417</v>
       </c>
       <c r="F25" s="52"/>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>413</v>
+        <v>423</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>94</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>358</v>
+        <v>368</v>
       </c>
       <c r="D26" s="52" t="s">
-        <v>405</v>
+        <v>415</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>414</v>
+        <v>424</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>98</v>
@@ -11273,46 +11458,57 @@
         <v>100</v>
       </c>
       <c r="D27" s="52" t="s">
-        <v>401</v>
+        <v>411</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>415</v>
+        <v>425</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>100</v>
       </c>
       <c r="C28" s="49" t="s">
-        <v>416</v>
+        <v>426</v>
       </c>
       <c r="D28" s="52" t="s">
-        <v>384</v>
+        <v>394</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>417</v>
+        <v>427</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>416</v>
+        <v>426</v>
       </c>
       <c r="C29" s="49" t="s">
         <v>102</v>
       </c>
       <c r="D29" s="52" t="s">
-        <v>418</v>
+        <v>428</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>419</v>
+        <v>429</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>102</v>
       </c>
       <c r="D30" s="52" t="s">
-        <v>420</v>
+        <v>430</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="s">
+        <v>431</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="D31" s="50" t="s">
+        <v>432</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/02Script/Table/EventTable.xlsx
+++ b/Assets/02Script/Table/EventTable.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1313" uniqueCount="433">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1523" uniqueCount="480">
   <si>
     <t>EventID</t>
   </si>
@@ -357,6 +357,54 @@
   </si>
   <si>
     <t>3인칭 맵에서 귀신이 등장 했을 때.</t>
+  </si>
+  <si>
+    <t>E044</t>
+  </si>
+  <si>
+    <t>2스테이지 1인칭 맵 입장 했을 때</t>
+  </si>
+  <si>
+    <t>E045</t>
+  </si>
+  <si>
+    <t>2스테이지 1인칭 맵 터널 중간 부분에서</t>
+  </si>
+  <si>
+    <t>E046</t>
+  </si>
+  <si>
+    <t>2스테이지 1인칭 맵 터널 끝부분, 일러스트와 함께</t>
+  </si>
+  <si>
+    <t>E047</t>
+  </si>
+  <si>
+    <t>사고 현장 앞에서 귀신 효과음과 함께 등장</t>
+  </si>
+  <si>
+    <t>E048</t>
+  </si>
+  <si>
+    <t>귀신 이벤트 진행 뒤</t>
+  </si>
+  <si>
+    <t>E049</t>
+  </si>
+  <si>
+    <t>가로등 근처 갔을 때</t>
+  </si>
+  <si>
+    <t>E050</t>
+  </si>
+  <si>
+    <t>자동차 근처 갔을 때</t>
+  </si>
+  <si>
+    <t>E051</t>
+  </si>
+  <si>
+    <t>1인칭맵 그냥 나가려고 할 때</t>
   </si>
   <si>
     <t>Order</t>
@@ -942,6 +990,99 @@
   </si>
   <si>
     <t>도망가야 해...</t>
+  </si>
+  <si>
+    <t>처음 보는 터널인데..</t>
+  </si>
+  <si>
+    <t>우리 동네에 이런 터널이 있었나?</t>
+  </si>
+  <si>
+    <t>너무 어두워서 앞이 잘 안보이네..</t>
+  </si>
+  <si>
+    <t>일단 앞으로 가봐야겠다..</t>
+  </si>
+  <si>
+    <t>저기가 터널 출구인가?</t>
+  </si>
+  <si>
+    <t>조금만 더 가면 되겠다.</t>
+  </si>
+  <si>
+    <t>어..?</t>
+  </si>
+  <si>
+    <t>설마.....저긴?</t>
+  </si>
+  <si>
+    <t>아니겠지..?</t>
+  </si>
+  <si>
+    <t>내가 어떻게 잊고 살았는데...</t>
+  </si>
+  <si>
+    <t>왜 여기로 오게 된거야...</t>
+  </si>
+  <si>
+    <t>엄마....아빠....</t>
+  </si>
+  <si>
+    <t>다 나 때문이야...</t>
+  </si>
+  <si>
+    <t>미안해....</t>
+  </si>
+  <si>
+    <t>이게 무슨 소리지..?</t>
+  </si>
+  <si>
+    <t>ㄷ...ㅏ....ㄴ....ㅔ.....ㅈ...ㅏ...ㄹ...ㅁ...ㅗ..ㅅ..ㅇ....ㅑ...</t>
+  </si>
+  <si>
+    <t>방금 그건 뭐였지..?</t>
+  </si>
+  <si>
+    <t>그래 맞아...</t>
+  </si>
+  <si>
+    <t>기억났어..</t>
+  </si>
+  <si>
+    <t>아까 학교에서 꾼 꿈..</t>
+  </si>
+  <si>
+    <t>그곳에서도  저녀석을 봤었어..</t>
+  </si>
+  <si>
+    <t>혹시....</t>
+  </si>
+  <si>
+    <t>엄마의 일기장에 쓰여있던 몽령이 바로 저 녀석인가..?</t>
+  </si>
+  <si>
+    <t>소름끼쳐....</t>
+  </si>
+  <si>
+    <t>어서 빨리 비밀번호를 찾고 여기서 도망쳐야겠다..</t>
+  </si>
+  <si>
+    <t>저 가로등... 뭔가 이상한데..</t>
+  </si>
+  <si>
+    <t>한번 확인 해볼까...</t>
+  </si>
+  <si>
+    <t>자동차 안에 뭔가 있을거같은데...</t>
+  </si>
+  <si>
+    <t>문이 열리려나..?</t>
+  </si>
+  <si>
+    <t>한번 확인 해봐야겠다..</t>
+  </si>
+  <si>
+    <t>비밀번호를 찾기 전까진 돌아갈 수 없어..</t>
   </si>
   <si>
     <t>Choice0</t>
@@ -1691,7 +1832,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="D81:J155" displayName="Table_4" name="Table_4" id="4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="D81:J186" displayName="Table_4" name="Table_4" id="4">
   <tableColumns count="7">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -2465,6 +2606,94 @@
         <v>113</v>
       </c>
     </row>
+    <row r="46">
+      <c r="A46" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D47" s="3" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D48" s="3" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D49" s="3" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D50" s="3" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C51" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D51" s="3" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="C52" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D52" s="3" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="C53" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D53" s="3" t="s">
+        <v>129</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -2485,10 +2714,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>114</v>
+        <v>130</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>115</v>
+        <v>131</v>
       </c>
     </row>
     <row r="2">
@@ -2499,7 +2728,7 @@
         <v>1.0</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>116</v>
+        <v>132</v>
       </c>
     </row>
     <row r="3">
@@ -2510,7 +2739,7 @@
         <v>2.0</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>117</v>
+        <v>133</v>
       </c>
     </row>
     <row r="4">
@@ -2521,7 +2750,7 @@
         <v>3.0</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>118</v>
+        <v>134</v>
       </c>
     </row>
     <row r="5">
@@ -2532,7 +2761,7 @@
         <v>4.0</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>119</v>
+        <v>135</v>
       </c>
     </row>
     <row r="6">
@@ -2543,7 +2772,7 @@
         <v>5.0</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>120</v>
+        <v>136</v>
       </c>
     </row>
     <row r="7">
@@ -2554,7 +2783,7 @@
         <v>6.0</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>121</v>
+        <v>137</v>
       </c>
     </row>
     <row r="8">
@@ -2565,7 +2794,7 @@
         <v>7.0</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>122</v>
+        <v>138</v>
       </c>
     </row>
     <row r="9">
@@ -2576,7 +2805,7 @@
         <v>8.0</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>123</v>
+        <v>139</v>
       </c>
     </row>
     <row r="10">
@@ -2587,7 +2816,7 @@
         <v>9.0</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>124</v>
+        <v>140</v>
       </c>
     </row>
     <row r="11">
@@ -2598,7 +2827,7 @@
         <v>10.0</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>125</v>
+        <v>141</v>
       </c>
     </row>
     <row r="12">
@@ -2609,7 +2838,7 @@
         <v>11.0</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>126</v>
+        <v>142</v>
       </c>
     </row>
     <row r="13">
@@ -2620,7 +2849,7 @@
         <v>12.0</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>127</v>
+        <v>143</v>
       </c>
     </row>
     <row r="14">
@@ -2631,7 +2860,7 @@
         <v>13.0</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>128</v>
+        <v>144</v>
       </c>
     </row>
   </sheetData>
@@ -2658,31 +2887,31 @@
         <v>0</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>129</v>
+        <v>145</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>130</v>
+        <v>146</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>131</v>
+        <v>147</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>132</v>
+        <v>148</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>133</v>
+        <v>149</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>134</v>
+        <v>150</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>135</v>
+        <v>151</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>136</v>
+        <v>152</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>137</v>
+        <v>153</v>
       </c>
     </row>
     <row r="2">
@@ -2696,20 +2925,20 @@
         <v>2001.0</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>138</v>
+        <v>154</v>
       </c>
       <c r="E2" s="12">
         <v>2002.0</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="G2" s="11" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="H2" s="13"/>
       <c r="I2" s="14" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="J2" s="14">
         <v>-1.0</v>
@@ -2727,20 +2956,20 @@
         <v>2002.0</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>142</v>
+        <v>158</v>
       </c>
       <c r="E3" s="12">
         <v>2003.0</v>
       </c>
       <c r="F3" s="11" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="G3" s="11" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="H3" s="13"/>
       <c r="I3" s="14" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="J3" s="14">
         <v>-1.0</v>
@@ -2758,20 +2987,20 @@
         <v>2003.0</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>143</v>
+        <v>159</v>
       </c>
       <c r="E4" s="12">
         <v>2004.0</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="H4" s="13"/>
       <c r="I4" s="14" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="J4" s="14">
         <v>-1.0</v>
@@ -2789,20 +3018,20 @@
         <v>2004.0</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>144</v>
+        <v>160</v>
       </c>
       <c r="E5" s="12">
         <v>2005.0</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>145</v>
+        <v>161</v>
       </c>
       <c r="G5" s="11" t="s">
-        <v>146</v>
+        <v>162</v>
       </c>
       <c r="H5" s="13"/>
       <c r="I5" s="14" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="J5" s="14">
         <v>-1.0</v>
@@ -2820,20 +3049,20 @@
         <v>2005.0</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>147</v>
+        <v>163</v>
       </c>
       <c r="E6" s="12">
         <v>2006.0</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="G6" s="11" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="H6" s="13"/>
       <c r="I6" s="14" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="J6" s="14">
         <v>-1.0</v>
@@ -2851,20 +3080,20 @@
         <v>2006.0</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>144</v>
+        <v>160</v>
       </c>
       <c r="E7" s="12">
         <v>2007.0</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>145</v>
+        <v>161</v>
       </c>
       <c r="G7" s="11" t="s">
-        <v>146</v>
+        <v>162</v>
       </c>
       <c r="H7" s="13"/>
       <c r="I7" s="14" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="J7" s="14">
         <v>-1.0</v>
@@ -2882,20 +3111,20 @@
         <v>2007.0</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>148</v>
+        <v>164</v>
       </c>
       <c r="E8" s="12">
         <v>2008.0</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="H8" s="13"/>
       <c r="I8" s="14" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="J8" s="14">
         <v>-1.0</v>
@@ -2913,20 +3142,20 @@
         <v>2008.0</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>149</v>
+        <v>165</v>
       </c>
       <c r="E9" s="12">
         <v>2009.0</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>145</v>
+        <v>161</v>
       </c>
       <c r="G9" s="11" t="s">
-        <v>146</v>
+        <v>162</v>
       </c>
       <c r="H9" s="13"/>
       <c r="I9" s="14" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="J9" s="14">
         <v>-1.0</v>
@@ -2944,20 +3173,20 @@
         <v>2009.0</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>150</v>
+        <v>166</v>
       </c>
       <c r="E10" s="12">
         <v>2010.0</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="G10" s="11" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="H10" s="13"/>
       <c r="I10" s="14" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="J10" s="14">
         <v>-1.0</v>
@@ -2975,20 +3204,20 @@
         <v>2010.0</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>151</v>
+        <v>167</v>
       </c>
       <c r="E11" s="12">
         <v>2011.0</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>145</v>
+        <v>161</v>
       </c>
       <c r="G11" s="11" t="s">
-        <v>152</v>
+        <v>168</v>
       </c>
       <c r="H11" s="13"/>
       <c r="I11" s="14" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="J11" s="14">
         <v>-1.0</v>
@@ -3006,20 +3235,20 @@
         <v>2011.0</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>153</v>
+        <v>169</v>
       </c>
       <c r="E12" s="12">
         <v>-1.0</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="H12" s="13"/>
       <c r="I12" s="14" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="J12" s="14">
         <v>-1.0</v>
@@ -3037,20 +3266,20 @@
         <v>3001.0</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>154</v>
+        <v>170</v>
       </c>
       <c r="E13" s="16">
         <v>3002.0</v>
       </c>
       <c r="F13" s="14" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="G13" s="11" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="H13" s="13"/>
       <c r="I13" s="14" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="J13" s="16">
         <v>4.0</v>
@@ -3068,20 +3297,20 @@
         <v>3002.0</v>
       </c>
       <c r="D14" s="14" t="s">
-        <v>155</v>
+        <v>171</v>
       </c>
       <c r="E14" s="16">
         <v>3003.0</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>156</v>
+        <v>172</v>
       </c>
       <c r="G14" s="11" t="s">
-        <v>152</v>
+        <v>168</v>
       </c>
       <c r="H14" s="13"/>
       <c r="I14" s="14" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="J14" s="16">
         <v>0.0</v>
@@ -3099,20 +3328,20 @@
         <v>3003.0</v>
       </c>
       <c r="D15" s="14" t="s">
-        <v>157</v>
+        <v>173</v>
       </c>
       <c r="E15" s="16">
         <v>3004.0</v>
       </c>
       <c r="F15" s="14" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="G15" s="11" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="H15" s="13"/>
       <c r="I15" s="14" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="J15" s="16">
         <v>2.0</v>
@@ -3130,20 +3359,20 @@
         <v>3004.0</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>158</v>
+        <v>174</v>
       </c>
       <c r="E16" s="16">
         <v>3005.0</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>156</v>
+        <v>172</v>
       </c>
       <c r="G16" s="11" t="s">
-        <v>152</v>
+        <v>168</v>
       </c>
       <c r="H16" s="13"/>
       <c r="I16" s="14" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="J16" s="16">
         <v>0.0</v>
@@ -3161,20 +3390,20 @@
         <v>3005.0</v>
       </c>
       <c r="D17" s="14" t="s">
-        <v>159</v>
+        <v>175</v>
       </c>
       <c r="E17" s="16">
         <v>3006.0</v>
       </c>
       <c r="F17" s="14" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="G17" s="11" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="H17" s="13"/>
       <c r="I17" s="14" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="J17" s="16">
         <v>2.0</v>
@@ -3192,20 +3421,20 @@
         <v>3006.0</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>160</v>
+        <v>176</v>
       </c>
       <c r="E18" s="16">
         <v>3007.0</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>156</v>
+        <v>172</v>
       </c>
       <c r="G18" s="11" t="s">
-        <v>152</v>
+        <v>168</v>
       </c>
       <c r="H18" s="13"/>
       <c r="I18" s="14" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="J18" s="16">
         <v>0.0</v>
@@ -3223,20 +3452,20 @@
         <v>3007.0</v>
       </c>
       <c r="D19" s="14" t="s">
-        <v>161</v>
+        <v>177</v>
       </c>
       <c r="E19" s="16">
         <v>3008.0</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>156</v>
+        <v>172</v>
       </c>
       <c r="G19" s="11" t="s">
-        <v>152</v>
+        <v>168</v>
       </c>
       <c r="H19" s="13"/>
       <c r="I19" s="14" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="J19" s="16">
         <v>1.0</v>
@@ -3262,20 +3491,20 @@
         <v>3008.0</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>162</v>
+        <v>178</v>
       </c>
       <c r="E20" s="16">
         <v>3009.0</v>
       </c>
       <c r="F20" s="14" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="G20" s="11" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="H20" s="13"/>
       <c r="I20" s="14" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="J20" s="16">
         <v>2.0</v>
@@ -3301,20 +3530,20 @@
         <v>3009.0</v>
       </c>
       <c r="D21" s="14" t="s">
-        <v>163</v>
+        <v>179</v>
       </c>
       <c r="E21" s="16">
         <v>3010.0</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>156</v>
+        <v>172</v>
       </c>
       <c r="G21" s="11" t="s">
-        <v>152</v>
+        <v>168</v>
       </c>
       <c r="H21" s="13"/>
       <c r="I21" s="14" t="s">
-        <v>164</v>
+        <v>180</v>
       </c>
       <c r="J21" s="16">
         <v>1.0</v>
@@ -3340,20 +3569,20 @@
         <v>3010.0</v>
       </c>
       <c r="D22" s="14" t="s">
-        <v>165</v>
+        <v>181</v>
       </c>
       <c r="E22" s="16">
         <v>3011.0</v>
       </c>
       <c r="F22" s="14" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="G22" s="11" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="H22" s="13"/>
       <c r="I22" s="14" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="J22" s="16">
         <v>2.0</v>
@@ -3379,20 +3608,20 @@
         <v>3011.0</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>160</v>
+        <v>176</v>
       </c>
       <c r="E23" s="16">
         <v>3012.0</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>156</v>
+        <v>172</v>
       </c>
       <c r="G23" s="11" t="s">
-        <v>152</v>
+        <v>168</v>
       </c>
       <c r="H23" s="13"/>
       <c r="I23" s="14" t="s">
-        <v>164</v>
+        <v>180</v>
       </c>
       <c r="J23" s="16">
         <v>1.0</v>
@@ -3418,19 +3647,19 @@
         <v>3012.0</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>166</v>
+        <v>182</v>
       </c>
       <c r="E24" s="16">
         <v>3013.0</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="I24" s="14" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="J24" s="3">
         <v>2.0</v>
@@ -3456,19 +3685,19 @@
         <v>3013.0</v>
       </c>
       <c r="D25" s="14" t="s">
-        <v>167</v>
+        <v>183</v>
       </c>
       <c r="E25" s="16">
         <v>3014.0</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>156</v>
+        <v>172</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>152</v>
+        <v>168</v>
       </c>
       <c r="I25" s="14" t="s">
-        <v>164</v>
+        <v>180</v>
       </c>
       <c r="J25" s="3">
         <v>2.0</v>
@@ -3494,19 +3723,19 @@
         <v>3014.0</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>168</v>
+        <v>184</v>
       </c>
       <c r="E26" s="16">
         <v>3015.0</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="I26" s="14" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="J26" s="3">
         <v>2.0</v>
@@ -3524,20 +3753,20 @@
         <v>3015.0</v>
       </c>
       <c r="D27" s="14" t="s">
-        <v>169</v>
+        <v>185</v>
       </c>
       <c r="E27" s="16">
         <v>3016.0</v>
       </c>
       <c r="F27" s="14" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="G27" s="11" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="H27" s="13"/>
       <c r="I27" s="16" t="s">
-        <v>170</v>
+        <v>186</v>
       </c>
       <c r="J27" s="16">
         <v>0.0</v>
@@ -3555,22 +3784,22 @@
         <v>3016.0</v>
       </c>
       <c r="D28" s="14" t="s">
-        <v>171</v>
+        <v>187</v>
       </c>
       <c r="E28" s="12">
         <v>-1.0</v>
       </c>
       <c r="F28" s="14" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="G28" s="11" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="H28" s="14" t="s">
-        <v>172</v>
+        <v>188</v>
       </c>
       <c r="I28" s="16" t="s">
-        <v>170</v>
+        <v>186</v>
       </c>
       <c r="J28" s="16">
         <v>0.0</v>
@@ -3588,18 +3817,18 @@
         <v>4001.0</v>
       </c>
       <c r="D29" s="14" t="s">
-        <v>173</v>
+        <v>189</v>
       </c>
       <c r="E29" s="12">
         <v>4002.0</v>
       </c>
       <c r="F29" s="14" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="G29" s="21"/>
       <c r="H29" s="13"/>
       <c r="I29" s="16" t="s">
-        <v>170</v>
+        <v>186</v>
       </c>
       <c r="J29" s="16">
         <v>-1.0</v>
@@ -3617,18 +3846,18 @@
         <v>4002.0</v>
       </c>
       <c r="D30" s="14" t="s">
-        <v>174</v>
+        <v>190</v>
       </c>
       <c r="E30" s="12">
         <v>-1.0</v>
       </c>
       <c r="F30" s="14" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="G30" s="21"/>
       <c r="H30" s="13"/>
       <c r="I30" s="16" t="s">
-        <v>170</v>
+        <v>186</v>
       </c>
       <c r="J30" s="16">
         <v>-1.0</v>
@@ -3646,20 +3875,20 @@
         <v>5001.0</v>
       </c>
       <c r="D31" s="14" t="s">
-        <v>175</v>
+        <v>191</v>
       </c>
       <c r="E31" s="3">
         <v>5002.0</v>
       </c>
       <c r="F31" s="14" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="G31" s="11" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="H31" s="13"/>
       <c r="I31" s="14" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="J31" s="16">
         <v>5.0</v>
@@ -3677,20 +3906,20 @@
         <v>5002.0</v>
       </c>
       <c r="D32" s="14" t="s">
-        <v>176</v>
+        <v>192</v>
       </c>
       <c r="E32" s="3">
         <v>5003.0</v>
       </c>
       <c r="F32" s="14" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="G32" s="11" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="H32" s="13"/>
       <c r="I32" s="14" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="J32" s="16">
         <v>5.0</v>
@@ -3708,20 +3937,20 @@
         <v>5003.0</v>
       </c>
       <c r="D33" s="14" t="s">
-        <v>138</v>
+        <v>154</v>
       </c>
       <c r="E33" s="3">
         <v>5004.0</v>
       </c>
       <c r="F33" s="14" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="G33" s="11" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="H33" s="13"/>
       <c r="I33" s="14" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="J33" s="16">
         <v>0.0</v>
@@ -3739,20 +3968,20 @@
         <v>5004.0</v>
       </c>
       <c r="D34" s="14" t="s">
-        <v>177</v>
+        <v>193</v>
       </c>
       <c r="E34" s="3">
         <v>5005.0</v>
       </c>
       <c r="F34" s="14" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="G34" s="11" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="H34" s="13"/>
       <c r="I34" s="14" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="J34" s="16">
         <v>0.0</v>
@@ -3770,20 +3999,20 @@
         <v>5005.0</v>
       </c>
       <c r="D35" s="14" t="s">
-        <v>178</v>
+        <v>194</v>
       </c>
       <c r="E35" s="3">
         <v>5006.0</v>
       </c>
       <c r="F35" s="14" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="G35" s="11" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="H35" s="13"/>
       <c r="I35" s="14" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="J35" s="16">
         <v>0.0</v>
@@ -3801,20 +4030,20 @@
         <v>5006.0</v>
       </c>
       <c r="D36" s="14" t="s">
-        <v>179</v>
+        <v>195</v>
       </c>
       <c r="E36" s="12">
         <v>-1.0</v>
       </c>
       <c r="F36" s="14" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="G36" s="11" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="H36" s="13"/>
       <c r="I36" s="16" t="s">
-        <v>170</v>
+        <v>186</v>
       </c>
       <c r="J36" s="16">
         <v>-1.0</v>
@@ -3832,20 +4061,20 @@
         <v>6001.0</v>
       </c>
       <c r="D37" s="14" t="s">
-        <v>180</v>
+        <v>196</v>
       </c>
       <c r="E37" s="16">
         <v>6002.0</v>
       </c>
       <c r="F37" s="14" t="s">
-        <v>181</v>
+        <v>197</v>
       </c>
       <c r="G37" s="11" t="s">
-        <v>146</v>
+        <v>162</v>
       </c>
       <c r="H37" s="13"/>
       <c r="I37" s="16" t="s">
-        <v>170</v>
+        <v>186</v>
       </c>
       <c r="J37" s="16">
         <v>-1.0</v>
@@ -3863,20 +4092,20 @@
         <v>6002.0</v>
       </c>
       <c r="D38" s="14" t="s">
-        <v>182</v>
+        <v>198</v>
       </c>
       <c r="E38" s="16">
         <v>6003.0</v>
       </c>
       <c r="F38" s="14" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="G38" s="11" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="H38" s="13"/>
       <c r="I38" s="14" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="J38" s="16">
         <v>5.0</v>
@@ -3894,20 +4123,20 @@
         <v>6003.0</v>
       </c>
       <c r="D39" s="14" t="s">
-        <v>183</v>
+        <v>199</v>
       </c>
       <c r="E39" s="16">
         <v>6004.0</v>
       </c>
       <c r="F39" s="14" t="s">
-        <v>181</v>
+        <v>197</v>
       </c>
       <c r="G39" s="11" t="s">
-        <v>146</v>
+        <v>162</v>
       </c>
       <c r="H39" s="13"/>
       <c r="I39" s="16" t="s">
-        <v>170</v>
+        <v>186</v>
       </c>
       <c r="J39" s="16">
         <v>-1.0</v>
@@ -3925,20 +4154,20 @@
         <v>6004.0</v>
       </c>
       <c r="D40" s="14" t="s">
-        <v>184</v>
+        <v>200</v>
       </c>
       <c r="E40" s="16">
         <v>6005.0</v>
       </c>
       <c r="F40" s="14" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="G40" s="11" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="H40" s="13"/>
       <c r="I40" s="14" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="J40" s="16">
         <v>0.0</v>
@@ -3956,20 +4185,20 @@
         <v>6005.0</v>
       </c>
       <c r="D41" s="14" t="s">
-        <v>185</v>
+        <v>201</v>
       </c>
       <c r="E41" s="16">
         <v>-1.0</v>
       </c>
       <c r="F41" s="14" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="G41" s="11" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="H41" s="13"/>
       <c r="I41" s="14" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="J41" s="16">
         <v>0.0</v>
@@ -3987,20 +4216,20 @@
         <v>7001.0</v>
       </c>
       <c r="D42" s="14" t="s">
-        <v>186</v>
+        <v>202</v>
       </c>
       <c r="E42" s="16">
         <v>-1.0</v>
       </c>
       <c r="F42" s="14" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="G42" s="11" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="H42" s="13"/>
       <c r="I42" s="14" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="J42" s="16">
         <v>-1.0</v>
@@ -4018,20 +4247,20 @@
         <v>8001.0</v>
       </c>
       <c r="D43" s="14" t="s">
-        <v>187</v>
+        <v>203</v>
       </c>
       <c r="E43" s="16">
         <v>8002.0</v>
       </c>
       <c r="F43" s="14" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="G43" s="11" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="H43" s="13"/>
       <c r="I43" s="14" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="J43" s="16">
         <v>-1.0</v>
@@ -4049,20 +4278,20 @@
         <v>8002.0</v>
       </c>
       <c r="D44" s="14" t="s">
-        <v>188</v>
+        <v>204</v>
       </c>
       <c r="E44" s="16">
         <v>8003.0</v>
       </c>
       <c r="F44" s="14" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="G44" s="11" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="H44" s="13"/>
       <c r="I44" s="14" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="J44" s="16">
         <v>-1.0</v>
@@ -4080,20 +4309,20 @@
         <v>8003.0</v>
       </c>
       <c r="D45" s="14" t="s">
-        <v>189</v>
+        <v>205</v>
       </c>
       <c r="E45" s="16">
         <v>8004.0</v>
       </c>
       <c r="F45" s="14" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="G45" s="11" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="H45" s="13"/>
       <c r="I45" s="14" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="J45" s="16">
         <v>-1.0</v>
@@ -4111,20 +4340,20 @@
         <v>8004.0</v>
       </c>
       <c r="D46" s="14" t="s">
-        <v>190</v>
+        <v>206</v>
       </c>
       <c r="E46" s="16">
         <v>8005.0</v>
       </c>
       <c r="F46" s="14" t="s">
-        <v>181</v>
+        <v>197</v>
       </c>
       <c r="G46" s="11" t="s">
-        <v>146</v>
+        <v>162</v>
       </c>
       <c r="H46" s="13"/>
       <c r="I46" s="16" t="s">
-        <v>170</v>
+        <v>186</v>
       </c>
       <c r="J46" s="16">
         <v>-1.0</v>
@@ -4142,20 +4371,20 @@
         <v>8005.0</v>
       </c>
       <c r="D47" s="14" t="s">
-        <v>191</v>
+        <v>207</v>
       </c>
       <c r="E47" s="16">
         <v>-1.0</v>
       </c>
       <c r="F47" s="14" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="G47" s="11" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="H47" s="13"/>
       <c r="I47" s="14" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="J47" s="16">
         <v>-1.0</v>
@@ -4173,20 +4402,20 @@
         <v>9001.0</v>
       </c>
       <c r="D48" s="14" t="s">
-        <v>192</v>
+        <v>208</v>
       </c>
       <c r="E48" s="16">
         <v>-1.0</v>
       </c>
       <c r="F48" s="14" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="G48" s="11" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="H48" s="13"/>
       <c r="I48" s="31" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="J48" s="16">
         <v>-1.0</v>
@@ -4204,20 +4433,20 @@
         <v>10001.0</v>
       </c>
       <c r="D49" s="14" t="s">
-        <v>193</v>
+        <v>209</v>
       </c>
       <c r="E49" s="16">
         <v>10002.0</v>
       </c>
       <c r="F49" s="14" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="G49" s="11" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="H49" s="13"/>
       <c r="I49" s="31" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="J49" s="16">
         <v>4.0</v>
@@ -4235,20 +4464,20 @@
         <v>10002.0</v>
       </c>
       <c r="D50" s="14" t="s">
-        <v>194</v>
+        <v>210</v>
       </c>
       <c r="E50" s="16">
         <v>10003.0</v>
       </c>
       <c r="F50" s="14" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="G50" s="11" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="H50" s="13"/>
       <c r="I50" s="31" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="J50" s="16">
         <v>0.0</v>
@@ -4266,20 +4495,20 @@
         <v>10003.0</v>
       </c>
       <c r="D51" s="14" t="s">
-        <v>195</v>
+        <v>211</v>
       </c>
       <c r="E51" s="16">
         <v>10004.0</v>
       </c>
       <c r="F51" s="14" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="G51" s="11" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="H51" s="13"/>
       <c r="I51" s="31" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="J51" s="16">
         <v>0.0</v>
@@ -4297,20 +4526,20 @@
         <v>10004.0</v>
       </c>
       <c r="D52" s="14" t="s">
-        <v>196</v>
+        <v>212</v>
       </c>
       <c r="E52" s="16">
         <v>-1.0</v>
       </c>
       <c r="F52" s="14" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="G52" s="11" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="H52" s="13"/>
       <c r="I52" s="16" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="J52" s="16">
         <v>0.0</v>
@@ -4328,20 +4557,20 @@
         <v>11001.0</v>
       </c>
       <c r="D53" s="14" t="s">
-        <v>197</v>
+        <v>213</v>
       </c>
       <c r="E53" s="16">
         <v>-1.0</v>
       </c>
       <c r="F53" s="14" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="G53" s="11" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="H53" s="13"/>
       <c r="I53" s="16" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="J53" s="16">
         <v>-1.0</v>
@@ -4359,20 +4588,20 @@
         <v>12001.0</v>
       </c>
       <c r="D54" s="14" t="s">
-        <v>198</v>
+        <v>214</v>
       </c>
       <c r="E54" s="16">
         <v>12002.0</v>
       </c>
       <c r="F54" s="14" t="s">
-        <v>181</v>
+        <v>197</v>
       </c>
       <c r="G54" s="11" t="s">
-        <v>146</v>
+        <v>162</v>
       </c>
       <c r="H54" s="13"/>
       <c r="I54" s="31" t="s">
-        <v>170</v>
+        <v>186</v>
       </c>
       <c r="J54" s="16">
         <v>-1.0</v>
@@ -4390,20 +4619,20 @@
         <v>12002.0</v>
       </c>
       <c r="D55" s="14" t="s">
-        <v>199</v>
+        <v>215</v>
       </c>
       <c r="E55" s="16">
         <v>12003.0</v>
       </c>
       <c r="F55" s="14" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="G55" s="11" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="H55" s="13"/>
       <c r="I55" s="16" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="J55" s="16">
         <v>0.0</v>
@@ -4421,20 +4650,20 @@
         <v>12003.0</v>
       </c>
       <c r="D56" s="14" t="s">
-        <v>200</v>
+        <v>216</v>
       </c>
       <c r="E56" s="16">
         <v>12004.0</v>
       </c>
       <c r="F56" s="14" t="s">
-        <v>181</v>
+        <v>197</v>
       </c>
       <c r="G56" s="11" t="s">
-        <v>146</v>
+        <v>162</v>
       </c>
       <c r="H56" s="13"/>
       <c r="I56" s="31" t="s">
-        <v>170</v>
+        <v>186</v>
       </c>
       <c r="J56" s="16">
         <v>-1.0</v>
@@ -4452,20 +4681,20 @@
         <v>12004.0</v>
       </c>
       <c r="D57" s="14" t="s">
-        <v>201</v>
+        <v>217</v>
       </c>
       <c r="E57" s="16">
         <v>12005.0</v>
       </c>
       <c r="F57" s="14" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="G57" s="11" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="H57" s="13"/>
       <c r="I57" s="31" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="J57" s="16">
         <v>5.0</v>
@@ -4483,20 +4712,20 @@
         <v>12005.0</v>
       </c>
       <c r="D58" s="14" t="s">
-        <v>202</v>
+        <v>218</v>
       </c>
       <c r="E58" s="16">
         <v>12006.0</v>
       </c>
       <c r="F58" s="14" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="G58" s="11" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="H58" s="13"/>
       <c r="I58" s="16" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="J58" s="16">
         <v>0.0</v>
@@ -4514,20 +4743,20 @@
         <v>12006.0</v>
       </c>
       <c r="D59" s="14" t="s">
-        <v>203</v>
+        <v>219</v>
       </c>
       <c r="E59" s="16">
         <v>12007.0</v>
       </c>
       <c r="F59" s="14" t="s">
-        <v>181</v>
+        <v>197</v>
       </c>
       <c r="G59" s="11" t="s">
-        <v>146</v>
+        <v>162</v>
       </c>
       <c r="H59" s="13"/>
       <c r="I59" s="31" t="s">
-        <v>170</v>
+        <v>186</v>
       </c>
       <c r="J59" s="16">
         <v>-1.0</v>
@@ -4545,20 +4774,20 @@
         <v>12007.0</v>
       </c>
       <c r="D60" s="14" t="s">
-        <v>204</v>
+        <v>220</v>
       </c>
       <c r="E60" s="16">
         <v>12008.0</v>
       </c>
       <c r="F60" s="14" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="G60" s="11" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="H60" s="13"/>
       <c r="I60" s="16" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="J60" s="16">
         <v>0.0</v>
@@ -4576,20 +4805,20 @@
         <v>12008.0</v>
       </c>
       <c r="D61" s="14" t="s">
-        <v>205</v>
+        <v>221</v>
       </c>
       <c r="E61" s="16">
         <v>-1.0</v>
       </c>
       <c r="F61" s="14" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="G61" s="11" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="H61" s="13"/>
       <c r="I61" s="31" t="s">
-        <v>170</v>
+        <v>186</v>
       </c>
       <c r="J61" s="16">
         <v>0.0</v>
@@ -4607,20 +4836,20 @@
         <v>13001.0</v>
       </c>
       <c r="D62" s="14" t="s">
-        <v>206</v>
+        <v>222</v>
       </c>
       <c r="E62" s="16">
         <v>-1.0</v>
       </c>
       <c r="F62" s="14" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="G62" s="11" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="H62" s="13"/>
       <c r="I62" s="31" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="J62" s="16">
         <v>-1.0</v>
@@ -4638,20 +4867,20 @@
         <v>14001.0</v>
       </c>
       <c r="D63" s="14" t="s">
-        <v>207</v>
+        <v>223</v>
       </c>
       <c r="E63" s="16">
         <v>14002.0</v>
       </c>
       <c r="F63" s="14" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="G63" s="11" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="H63" s="13"/>
       <c r="I63" s="31" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="J63" s="16">
         <v>-1.0</v>
@@ -4669,20 +4898,20 @@
         <v>14002.0</v>
       </c>
       <c r="D64" s="14" t="s">
-        <v>208</v>
+        <v>224</v>
       </c>
       <c r="E64" s="16">
         <v>14003.0</v>
       </c>
       <c r="F64" s="14" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="G64" s="11" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="H64" s="13"/>
       <c r="I64" s="31" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="J64" s="16">
         <v>-1.0</v>
@@ -4700,20 +4929,20 @@
         <v>14003.0</v>
       </c>
       <c r="D65" s="14" t="s">
-        <v>209</v>
+        <v>225</v>
       </c>
       <c r="E65" s="16">
         <v>-1.0</v>
       </c>
       <c r="F65" s="14" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="G65" s="11" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="H65" s="13"/>
       <c r="I65" s="31" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="J65" s="16">
         <v>-1.0</v>
@@ -4731,20 +4960,20 @@
         <v>15001.0</v>
       </c>
       <c r="D66" s="14" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="E66" s="16">
         <v>-1.0</v>
       </c>
       <c r="F66" s="14" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="G66" s="11" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="H66" s="13"/>
       <c r="I66" s="31" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="J66" s="16">
         <v>-1.0</v>
@@ -4762,20 +4991,20 @@
         <v>16001.0</v>
       </c>
       <c r="D67" s="14" t="s">
-        <v>211</v>
+        <v>227</v>
       </c>
       <c r="E67" s="16">
         <v>16002.0</v>
       </c>
       <c r="F67" s="14" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="G67" s="11" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="H67" s="13"/>
       <c r="I67" s="31" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="J67" s="16">
         <v>0.0</v>
@@ -4793,20 +5022,20 @@
         <v>16002.0</v>
       </c>
       <c r="D68" s="14" t="s">
-        <v>212</v>
+        <v>228</v>
       </c>
       <c r="E68" s="16">
         <v>-1.0</v>
       </c>
       <c r="F68" s="14" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="G68" s="11" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="H68" s="13"/>
       <c r="I68" s="31" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="J68" s="16">
         <v>5.0</v>
@@ -4824,20 +5053,20 @@
         <v>17001.0</v>
       </c>
       <c r="D69" s="14" t="s">
-        <v>213</v>
+        <v>229</v>
       </c>
       <c r="E69" s="16">
         <v>17002.0</v>
       </c>
       <c r="F69" s="14" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="G69" s="11" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="H69" s="13"/>
       <c r="I69" s="31" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="J69" s="16">
         <v>0.0</v>
@@ -4855,20 +5084,20 @@
         <v>17002.0</v>
       </c>
       <c r="D70" s="14" t="s">
-        <v>214</v>
+        <v>230</v>
       </c>
       <c r="E70" s="16">
         <v>17003.0</v>
       </c>
       <c r="F70" s="14" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="G70" s="11" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="H70" s="13"/>
       <c r="I70" s="31" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="J70" s="16">
         <v>6.0</v>
@@ -4886,20 +5115,20 @@
         <v>17003.0</v>
       </c>
       <c r="D71" s="14" t="s">
-        <v>215</v>
+        <v>231</v>
       </c>
       <c r="E71" s="16">
         <v>17004.0</v>
       </c>
       <c r="F71" s="14" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="G71" s="11" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="H71" s="13"/>
       <c r="I71" s="31" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="J71" s="16">
         <v>5.0</v>
@@ -4917,20 +5146,20 @@
         <v>17004.0</v>
       </c>
       <c r="D72" s="14" t="s">
-        <v>216</v>
+        <v>232</v>
       </c>
       <c r="E72" s="16">
         <v>-1.0</v>
       </c>
       <c r="F72" s="14" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="G72" s="11" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="H72" s="13"/>
       <c r="I72" s="31" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="J72" s="16">
         <v>0.0</v>
@@ -4948,20 +5177,20 @@
         <v>18001.0</v>
       </c>
       <c r="D73" s="14" t="s">
-        <v>217</v>
+        <v>233</v>
       </c>
       <c r="E73" s="16">
         <v>18002.0</v>
       </c>
       <c r="F73" s="14" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="G73" s="11" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="H73" s="13"/>
       <c r="I73" s="31" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="J73" s="16">
         <v>5.0</v>
@@ -4979,19 +5208,19 @@
         <v>18002.0</v>
       </c>
       <c r="D74" s="33" t="s">
-        <v>218</v>
+        <v>234</v>
       </c>
       <c r="E74" s="3">
         <v>18003.0</v>
       </c>
       <c r="F74" s="14" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="G74" s="11" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="I74" s="31" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="J74" s="16">
         <v>0.0</v>
@@ -5008,19 +5237,19 @@
         <v>18003.0</v>
       </c>
       <c r="D75" s="33" t="s">
-        <v>219</v>
+        <v>235</v>
       </c>
       <c r="E75" s="3">
         <v>-1.0</v>
       </c>
       <c r="F75" s="14" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="G75" s="11" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="I75" s="31" t="s">
-        <v>170</v>
+        <v>186</v>
       </c>
       <c r="J75" s="16">
         <v>-1.0</v>
@@ -5037,19 +5266,19 @@
         <v>19001.0</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>220</v>
+        <v>236</v>
       </c>
       <c r="E76" s="16">
         <v>19002.0</v>
       </c>
       <c r="F76" s="14" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="G76" s="11" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="I76" s="31" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="J76" s="16">
         <v>6.0</v>
@@ -5066,19 +5295,19 @@
         <v>19002.0</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>221</v>
+        <v>237</v>
       </c>
       <c r="E77" s="3">
         <v>19003.0</v>
       </c>
       <c r="F77" s="14" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="G77" s="11" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="I77" s="31" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="J77" s="16">
         <v>5.0</v>
@@ -5095,19 +5324,19 @@
         <v>19003.0</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>222</v>
+        <v>238</v>
       </c>
       <c r="E78" s="3">
         <v>19004.0</v>
       </c>
       <c r="F78" s="14" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="G78" s="11" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="I78" s="31" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="J78" s="3">
         <v>2.0</v>
@@ -5124,19 +5353,19 @@
         <v>19004.0</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>223</v>
+        <v>239</v>
       </c>
       <c r="E79" s="3">
         <v>19005.0</v>
       </c>
       <c r="F79" s="3" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="G79" s="3" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="J79" s="3">
         <v>2.0</v>
@@ -5153,19 +5382,19 @@
         <v>19005.0</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>224</v>
+        <v>240</v>
       </c>
       <c r="E80" s="3">
         <v>-1.0</v>
       </c>
       <c r="F80" s="3" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="G80" s="3" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="J80" s="3">
         <v>2.0</v>
@@ -5182,20 +5411,20 @@
         <v>20001.0</v>
       </c>
       <c r="D81" s="36" t="s">
-        <v>225</v>
+        <v>241</v>
       </c>
       <c r="E81" s="28">
         <v>20002.0</v>
       </c>
       <c r="F81" s="36" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="G81" s="37" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="H81" s="36"/>
       <c r="I81" s="38" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="J81" s="28">
         <v>0.0</v>
@@ -5212,20 +5441,20 @@
         <v>20002.0</v>
       </c>
       <c r="D82" s="39" t="s">
-        <v>226</v>
+        <v>242</v>
       </c>
       <c r="E82" s="19">
         <v>20003.0</v>
       </c>
       <c r="F82" s="39" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="G82" s="37" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="H82" s="39"/>
       <c r="I82" s="38" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="J82" s="19">
         <v>0.0</v>
@@ -5242,20 +5471,20 @@
         <v>20003.0</v>
       </c>
       <c r="D83" s="36" t="s">
-        <v>227</v>
+        <v>243</v>
       </c>
       <c r="E83" s="28">
         <v>20004.0</v>
       </c>
       <c r="F83" s="36" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="G83" s="37" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="H83" s="36"/>
       <c r="I83" s="38" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="J83" s="28">
         <v>0.0</v>
@@ -5272,20 +5501,20 @@
         <v>20004.0</v>
       </c>
       <c r="D84" s="39" t="s">
-        <v>228</v>
+        <v>244</v>
       </c>
       <c r="E84" s="19">
         <v>20005.0</v>
       </c>
       <c r="F84" s="39" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="G84" s="37" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="H84" s="39"/>
       <c r="I84" s="38" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="J84" s="26">
         <v>2.0</v>
@@ -5302,20 +5531,20 @@
         <v>20005.0</v>
       </c>
       <c r="D85" s="36" t="s">
-        <v>229</v>
+        <v>245</v>
       </c>
       <c r="E85" s="28">
         <v>20006.0</v>
       </c>
       <c r="F85" s="36" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="G85" s="37" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="H85" s="36"/>
       <c r="I85" s="38" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="J85" s="40">
         <v>2.0</v>
@@ -5332,20 +5561,20 @@
         <v>20006.0</v>
       </c>
       <c r="D86" s="39" t="s">
-        <v>230</v>
+        <v>246</v>
       </c>
       <c r="E86" s="19">
         <v>-1.0</v>
       </c>
       <c r="F86" s="39" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="G86" s="37" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="H86" s="39"/>
       <c r="I86" s="38" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="J86" s="19">
         <v>0.0</v>
@@ -5362,20 +5591,20 @@
         <v>21001.0</v>
       </c>
       <c r="D87" s="36" t="s">
-        <v>231</v>
+        <v>247</v>
       </c>
       <c r="E87" s="28">
         <v>-1.0</v>
       </c>
       <c r="F87" s="36" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="G87" s="37" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="H87" s="36"/>
       <c r="I87" s="38" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="J87" s="40">
         <v>-1.0</v>
@@ -5392,20 +5621,20 @@
         <v>22001.0</v>
       </c>
       <c r="D88" s="39" t="s">
-        <v>232</v>
+        <v>248</v>
       </c>
       <c r="E88" s="19">
         <v>22002.0</v>
       </c>
       <c r="F88" s="39" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="G88" s="37" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="H88" s="39"/>
       <c r="I88" s="38" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="J88" s="19">
         <v>0.0</v>
@@ -5422,20 +5651,20 @@
         <v>22002.0</v>
       </c>
       <c r="D89" s="36" t="s">
-        <v>233</v>
+        <v>249</v>
       </c>
       <c r="E89" s="28">
         <v>22003.0</v>
       </c>
       <c r="F89" s="36" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="G89" s="37" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="H89" s="36"/>
       <c r="I89" s="38" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="J89" s="40">
         <v>2.0</v>
@@ -5452,20 +5681,20 @@
         <v>22003.0</v>
       </c>
       <c r="D90" s="39" t="s">
-        <v>234</v>
+        <v>250</v>
       </c>
       <c r="E90" s="19">
         <v>22004.0</v>
       </c>
       <c r="F90" s="39" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="G90" s="37" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="H90" s="39"/>
       <c r="I90" s="38" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="J90" s="26">
         <v>2.0</v>
@@ -5482,20 +5711,20 @@
         <v>22004.0</v>
       </c>
       <c r="D91" s="36" t="s">
-        <v>235</v>
+        <v>251</v>
       </c>
       <c r="E91" s="28">
         <v>22005.0</v>
       </c>
       <c r="F91" s="36" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="G91" s="37" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="H91" s="36"/>
       <c r="I91" s="38" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="J91" s="40">
         <v>2.0</v>
@@ -5512,20 +5741,20 @@
         <v>22005.0</v>
       </c>
       <c r="D92" s="39" t="s">
-        <v>236</v>
+        <v>252</v>
       </c>
       <c r="E92" s="26">
         <v>-1.0</v>
       </c>
       <c r="F92" s="39" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="G92" s="37" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="H92" s="39"/>
       <c r="I92" s="38" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="J92" s="26">
         <v>1.0</v>
@@ -5542,20 +5771,20 @@
         <v>23001.0</v>
       </c>
       <c r="D93" s="36" t="s">
-        <v>237</v>
+        <v>253</v>
       </c>
       <c r="E93" s="5">
         <v>23002.0</v>
       </c>
       <c r="F93" s="36" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="G93" s="37" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="H93" s="36"/>
       <c r="I93" s="38" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="J93" s="28">
         <v>0.0</v>
@@ -5572,20 +5801,20 @@
         <v>23002.0</v>
       </c>
       <c r="D94" s="39" t="s">
-        <v>238</v>
+        <v>254</v>
       </c>
       <c r="E94" s="5">
         <v>23003.0</v>
       </c>
       <c r="F94" s="39" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="G94" s="37" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="H94" s="39"/>
       <c r="I94" s="38" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="J94" s="19">
         <v>0.0</v>
@@ -5602,20 +5831,20 @@
         <v>23003.0</v>
       </c>
       <c r="D95" s="36" t="s">
-        <v>239</v>
+        <v>255</v>
       </c>
       <c r="E95" s="5">
         <v>23004.0</v>
       </c>
       <c r="F95" s="36" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="G95" s="37" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="H95" s="36"/>
       <c r="I95" s="38" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="J95" s="28">
         <v>0.0</v>
@@ -5632,20 +5861,20 @@
         <v>23004.0</v>
       </c>
       <c r="D96" s="39" t="s">
-        <v>240</v>
+        <v>256</v>
       </c>
       <c r="E96" s="19">
         <v>-1.0</v>
       </c>
       <c r="F96" s="39" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="G96" s="37" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="H96" s="39"/>
       <c r="I96" s="38" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="J96" s="19">
         <v>0.0</v>
@@ -5662,20 +5891,20 @@
         <v>24001.0</v>
       </c>
       <c r="D97" s="36" t="s">
-        <v>241</v>
+        <v>257</v>
       </c>
       <c r="E97" s="28">
         <v>24002.0</v>
       </c>
       <c r="F97" s="36" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="G97" s="37" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="H97" s="36"/>
       <c r="I97" s="38" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="J97" s="40">
         <v>5.0</v>
@@ -5692,20 +5921,20 @@
         <v>24002.0</v>
       </c>
       <c r="D98" s="39" t="s">
-        <v>242</v>
+        <v>258</v>
       </c>
       <c r="E98" s="19">
         <v>24003.0</v>
       </c>
       <c r="F98" s="39" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="G98" s="37" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="H98" s="39"/>
       <c r="I98" s="38" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="J98" s="19">
         <v>0.0</v>
@@ -5722,20 +5951,20 @@
         <v>24003.0</v>
       </c>
       <c r="D99" s="36" t="s">
-        <v>243</v>
+        <v>259</v>
       </c>
       <c r="E99" s="28">
         <v>24004.0</v>
       </c>
       <c r="F99" s="36" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="G99" s="37" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="H99" s="36"/>
       <c r="I99" s="38" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="J99" s="28">
         <v>0.0</v>
@@ -5752,20 +5981,20 @@
         <v>24004.0</v>
       </c>
       <c r="D100" s="39" t="s">
-        <v>244</v>
+        <v>260</v>
       </c>
       <c r="E100" s="19">
         <v>24005.0</v>
       </c>
       <c r="F100" s="39" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="G100" s="37" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="H100" s="39"/>
       <c r="I100" s="38" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="J100" s="19">
         <v>0.0</v>
@@ -5782,20 +6011,20 @@
         <v>24005.0</v>
       </c>
       <c r="D101" s="36" t="s">
-        <v>245</v>
+        <v>261</v>
       </c>
       <c r="E101" s="28">
         <v>24006.0</v>
       </c>
       <c r="F101" s="36" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="G101" s="37" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="H101" s="36"/>
       <c r="I101" s="38" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="J101" s="28">
         <v>0.0</v>
@@ -5812,20 +6041,20 @@
         <v>24006.0</v>
       </c>
       <c r="D102" s="39" t="s">
-        <v>246</v>
+        <v>262</v>
       </c>
       <c r="E102" s="19">
         <v>24007.0</v>
       </c>
       <c r="F102" s="39" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="G102" s="37" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="H102" s="39"/>
       <c r="I102" s="38" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="J102" s="19">
         <v>0.0</v>
@@ -5842,20 +6071,20 @@
         <v>24007.0</v>
       </c>
       <c r="D103" s="36" t="s">
-        <v>247</v>
+        <v>263</v>
       </c>
       <c r="E103" s="28">
         <v>24008.0</v>
       </c>
       <c r="F103" s="36" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="G103" s="37" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="H103" s="36"/>
       <c r="I103" s="38" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="J103" s="28">
         <v>0.0</v>
@@ -5872,20 +6101,20 @@
         <v>24008.0</v>
       </c>
       <c r="D104" s="39" t="s">
-        <v>248</v>
+        <v>264</v>
       </c>
       <c r="E104" s="19">
         <v>-1.0</v>
       </c>
       <c r="F104" s="39" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="G104" s="37" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="H104" s="39"/>
       <c r="I104" s="38" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="J104" s="19">
         <v>0.0</v>
@@ -5902,20 +6131,20 @@
         <v>25001.0</v>
       </c>
       <c r="D105" s="36" t="s">
-        <v>249</v>
+        <v>265</v>
       </c>
       <c r="E105" s="28">
         <v>25002.0</v>
       </c>
       <c r="F105" s="36" t="s">
-        <v>181</v>
+        <v>197</v>
       </c>
       <c r="G105" s="36" t="s">
-        <v>146</v>
+        <v>162</v>
       </c>
       <c r="H105" s="36"/>
       <c r="I105" s="36" t="s">
-        <v>170</v>
+        <v>186</v>
       </c>
       <c r="J105" s="40">
         <v>-1.0</v>
@@ -5932,20 +6161,20 @@
         <v>25002.0</v>
       </c>
       <c r="D106" s="39" t="s">
-        <v>250</v>
+        <v>266</v>
       </c>
       <c r="E106" s="19">
         <v>25003.0</v>
       </c>
       <c r="F106" s="39" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="G106" s="39" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="H106" s="39"/>
       <c r="I106" s="38" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="J106" s="26">
         <v>5.0</v>
@@ -5962,20 +6191,20 @@
         <v>25003.0</v>
       </c>
       <c r="D107" s="36" t="s">
-        <v>251</v>
+        <v>267</v>
       </c>
       <c r="E107" s="28">
         <v>25004.0</v>
       </c>
       <c r="F107" s="36" t="s">
-        <v>181</v>
+        <v>197</v>
       </c>
       <c r="G107" s="36" t="s">
-        <v>146</v>
+        <v>162</v>
       </c>
       <c r="H107" s="36"/>
       <c r="I107" s="36" t="s">
-        <v>170</v>
+        <v>186</v>
       </c>
       <c r="J107" s="40">
         <v>-1.0</v>
@@ -5992,20 +6221,20 @@
         <v>25004.0</v>
       </c>
       <c r="D108" s="39" t="s">
-        <v>252</v>
+        <v>268</v>
       </c>
       <c r="E108" s="19">
         <v>25005.0</v>
       </c>
       <c r="F108" s="39" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="G108" s="39" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="H108" s="39"/>
       <c r="I108" s="38" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="J108" s="26">
         <v>5.0</v>
@@ -6022,20 +6251,20 @@
         <v>25005.0</v>
       </c>
       <c r="D109" s="36" t="s">
-        <v>253</v>
+        <v>269</v>
       </c>
       <c r="E109" s="28">
         <v>25006.0</v>
       </c>
       <c r="F109" s="36" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="G109" s="36" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="H109" s="36"/>
       <c r="I109" s="38" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="J109" s="40">
         <v>5.0</v>
@@ -6052,20 +6281,20 @@
         <v>25006.0</v>
       </c>
       <c r="D110" s="39" t="s">
-        <v>254</v>
+        <v>270</v>
       </c>
       <c r="E110" s="19">
         <v>-1.0</v>
       </c>
       <c r="F110" s="39" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="G110" s="39" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="H110" s="39"/>
       <c r="I110" s="38" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="J110" s="26">
         <v>5.0</v>
@@ -6082,20 +6311,20 @@
         <v>26001.0</v>
       </c>
       <c r="D111" s="36" t="s">
-        <v>255</v>
+        <v>271</v>
       </c>
       <c r="E111" s="28">
         <v>-1.0</v>
       </c>
       <c r="F111" s="36" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="G111" s="36" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="H111" s="36"/>
       <c r="I111" s="36" t="s">
-        <v>170</v>
+        <v>186</v>
       </c>
       <c r="J111" s="40">
         <v>-1.0</v>
@@ -6112,20 +6341,20 @@
         <v>27001.0</v>
       </c>
       <c r="D112" s="39" t="s">
-        <v>256</v>
+        <v>272</v>
       </c>
       <c r="E112" s="19">
         <v>27002.0</v>
       </c>
       <c r="F112" s="39" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="G112" s="39" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="H112" s="39"/>
       <c r="I112" s="38" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="J112" s="26">
         <v>2.0</v>
@@ -6142,20 +6371,20 @@
         <v>27002.0</v>
       </c>
       <c r="D113" s="36" t="s">
-        <v>257</v>
+        <v>273</v>
       </c>
       <c r="E113" s="28">
         <v>27003.0</v>
       </c>
       <c r="F113" s="36" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="G113" s="36" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="H113" s="36"/>
       <c r="I113" s="38" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="J113" s="40">
         <v>2.0</v>
@@ -6172,20 +6401,20 @@
         <v>27003.0</v>
       </c>
       <c r="D114" s="39" t="s">
-        <v>258</v>
+        <v>274</v>
       </c>
       <c r="E114" s="19">
         <v>-1.0</v>
       </c>
       <c r="F114" s="39" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="G114" s="39" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="H114" s="39"/>
       <c r="I114" s="38" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="J114" s="26">
         <v>2.0</v>
@@ -6202,20 +6431,20 @@
         <v>28001.0</v>
       </c>
       <c r="D115" s="36" t="s">
-        <v>259</v>
+        <v>275</v>
       </c>
       <c r="E115" s="28">
         <v>28002.0</v>
       </c>
       <c r="F115" s="36" t="s">
-        <v>181</v>
+        <v>197</v>
       </c>
       <c r="G115" s="36" t="s">
-        <v>260</v>
+        <v>276</v>
       </c>
       <c r="H115" s="36"/>
       <c r="I115" s="36" t="s">
-        <v>170</v>
+        <v>186</v>
       </c>
       <c r="J115" s="40">
         <v>-1.0</v>
@@ -6232,20 +6461,20 @@
         <v>28002.0</v>
       </c>
       <c r="D116" s="39" t="s">
-        <v>261</v>
+        <v>277</v>
       </c>
       <c r="E116" s="19">
         <v>28003.0</v>
       </c>
       <c r="F116" s="39" t="s">
-        <v>181</v>
+        <v>197</v>
       </c>
       <c r="G116" s="39" t="s">
-        <v>262</v>
+        <v>278</v>
       </c>
       <c r="H116" s="39"/>
       <c r="I116" s="39" t="s">
-        <v>170</v>
+        <v>186</v>
       </c>
       <c r="J116" s="40">
         <v>-1.0</v>
@@ -6262,20 +6491,20 @@
         <v>28003.0</v>
       </c>
       <c r="D117" s="36" t="s">
-        <v>263</v>
+        <v>279</v>
       </c>
       <c r="E117" s="28">
         <v>-1.0</v>
       </c>
       <c r="F117" s="36" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="G117" s="36" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="H117" s="36"/>
       <c r="I117" s="38" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="J117" s="40">
         <v>2.0</v>
@@ -6292,20 +6521,20 @@
         <v>29001.0</v>
       </c>
       <c r="D118" s="39" t="s">
-        <v>264</v>
+        <v>280</v>
       </c>
       <c r="E118" s="19">
         <v>-1.0</v>
       </c>
       <c r="F118" s="39" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="G118" s="39" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="H118" s="39"/>
       <c r="I118" s="38" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="J118" s="26">
         <v>-1.0</v>
@@ -6322,20 +6551,20 @@
         <v>30001.0</v>
       </c>
       <c r="D119" s="36" t="s">
-        <v>265</v>
+        <v>281</v>
       </c>
       <c r="E119" s="28">
         <v>30002.0</v>
       </c>
       <c r="F119" s="36" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="G119" s="36" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="H119" s="36"/>
       <c r="I119" s="38" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="J119" s="40">
         <v>2.0</v>
@@ -6352,20 +6581,20 @@
         <v>30002.0</v>
       </c>
       <c r="D120" s="39" t="s">
-        <v>266</v>
+        <v>282</v>
       </c>
       <c r="E120" s="19">
         <v>30003.0</v>
       </c>
       <c r="F120" s="39" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="G120" s="39" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="H120" s="39"/>
       <c r="I120" s="38" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="J120" s="26">
         <v>1.0</v>
@@ -6382,20 +6611,20 @@
         <v>30003.0</v>
       </c>
       <c r="D121" s="36" t="s">
-        <v>267</v>
+        <v>283</v>
       </c>
       <c r="E121" s="28">
         <v>-1.0</v>
       </c>
       <c r="F121" s="36" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="G121" s="36" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="H121" s="36"/>
       <c r="I121" s="38" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="J121" s="40">
         <v>2.0</v>
@@ -6412,20 +6641,20 @@
         <v>31001.0</v>
       </c>
       <c r="D122" s="39" t="s">
-        <v>268</v>
+        <v>284</v>
       </c>
       <c r="E122" s="19">
         <v>31002.0</v>
       </c>
       <c r="F122" s="39" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="G122" s="39" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="H122" s="39"/>
       <c r="I122" s="38" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="J122" s="26">
         <v>5.0</v>
@@ -6442,20 +6671,20 @@
         <v>31002.0</v>
       </c>
       <c r="D123" s="36" t="s">
-        <v>269</v>
+        <v>285</v>
       </c>
       <c r="E123" s="28">
         <v>-1.0</v>
       </c>
       <c r="F123" s="36" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="G123" s="36" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="H123" s="36"/>
       <c r="I123" s="38" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="J123" s="40">
         <v>6.0</v>
@@ -6472,20 +6701,20 @@
         <v>32001.0</v>
       </c>
       <c r="D124" s="39" t="s">
-        <v>270</v>
+        <v>286</v>
       </c>
       <c r="E124" s="19">
         <v>32002.0</v>
       </c>
       <c r="F124" s="39" t="s">
-        <v>181</v>
+        <v>197</v>
       </c>
       <c r="G124" s="39" t="s">
-        <v>146</v>
+        <v>162</v>
       </c>
       <c r="H124" s="39"/>
       <c r="I124" s="39" t="s">
-        <v>170</v>
+        <v>186</v>
       </c>
       <c r="J124" s="40">
         <v>-1.0</v>
@@ -6502,20 +6731,20 @@
         <v>32002.0</v>
       </c>
       <c r="D125" s="36" t="s">
-        <v>271</v>
+        <v>287</v>
       </c>
       <c r="E125" s="28">
         <v>32003.0</v>
       </c>
       <c r="F125" s="36" t="s">
-        <v>181</v>
+        <v>197</v>
       </c>
       <c r="G125" s="36" t="s">
-        <v>146</v>
+        <v>162</v>
       </c>
       <c r="H125" s="36"/>
       <c r="I125" s="36" t="s">
-        <v>170</v>
+        <v>186</v>
       </c>
       <c r="J125" s="40">
         <v>-1.0</v>
@@ -6532,20 +6761,20 @@
         <v>32003.0</v>
       </c>
       <c r="D126" s="39" t="s">
-        <v>272</v>
+        <v>288</v>
       </c>
       <c r="E126" s="19">
         <v>32004.0</v>
       </c>
       <c r="F126" s="39" t="s">
-        <v>181</v>
+        <v>197</v>
       </c>
       <c r="G126" s="39" t="s">
-        <v>146</v>
+        <v>162</v>
       </c>
       <c r="H126" s="39"/>
       <c r="I126" s="39" t="s">
-        <v>170</v>
+        <v>186</v>
       </c>
       <c r="J126" s="40">
         <v>-1.0</v>
@@ -6562,20 +6791,20 @@
         <v>32004.0</v>
       </c>
       <c r="D127" s="36" t="s">
-        <v>273</v>
+        <v>289</v>
       </c>
       <c r="E127" s="28">
         <v>32005.0</v>
       </c>
       <c r="F127" s="36" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="G127" s="36" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="H127" s="36"/>
       <c r="I127" s="38" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="J127" s="40">
         <v>5.0</v>
@@ -6592,20 +6821,20 @@
         <v>32005.0</v>
       </c>
       <c r="D128" s="39" t="s">
-        <v>274</v>
+        <v>290</v>
       </c>
       <c r="E128" s="19">
         <v>32006.0</v>
       </c>
       <c r="F128" s="39" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="G128" s="39" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="H128" s="39"/>
       <c r="I128" s="38" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="J128" s="19">
         <v>0.0</v>
@@ -6622,20 +6851,20 @@
         <v>32006.0</v>
       </c>
       <c r="D129" s="36" t="s">
-        <v>275</v>
+        <v>291</v>
       </c>
       <c r="E129" s="28">
         <v>-1.0</v>
       </c>
       <c r="F129" s="36" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="G129" s="36" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="H129" s="36"/>
       <c r="I129" s="38" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="J129" s="28">
         <v>0.0</v>
@@ -6652,20 +6881,20 @@
         <v>33001.0</v>
       </c>
       <c r="D130" s="39" t="s">
-        <v>276</v>
+        <v>292</v>
       </c>
       <c r="E130" s="19">
         <v>33002.0</v>
       </c>
       <c r="F130" s="39" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="G130" s="39" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="H130" s="39"/>
       <c r="I130" s="38" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="J130" s="19">
         <v>0.0</v>
@@ -6682,20 +6911,20 @@
         <v>33002.0</v>
       </c>
       <c r="D131" s="36" t="s">
-        <v>277</v>
+        <v>293</v>
       </c>
       <c r="E131" s="28">
         <v>-1.0</v>
       </c>
       <c r="F131" s="36" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="G131" s="36" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="H131" s="36"/>
       <c r="I131" s="38" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="J131" s="28">
         <v>0.0</v>
@@ -6712,20 +6941,20 @@
         <v>34001.0</v>
       </c>
       <c r="D132" s="39" t="s">
-        <v>278</v>
+        <v>294</v>
       </c>
       <c r="E132" s="19">
         <v>34002.0</v>
       </c>
       <c r="F132" s="39" t="s">
-        <v>181</v>
+        <v>197</v>
       </c>
       <c r="G132" s="39" t="s">
-        <v>279</v>
+        <v>295</v>
       </c>
       <c r="H132" s="39"/>
       <c r="I132" s="39" t="s">
-        <v>170</v>
+        <v>186</v>
       </c>
       <c r="J132" s="40">
         <v>-1.0</v>
@@ -6742,20 +6971,20 @@
         <v>34002.0</v>
       </c>
       <c r="D133" s="36" t="s">
-        <v>280</v>
+        <v>296</v>
       </c>
       <c r="E133" s="28">
         <v>34003.0</v>
       </c>
       <c r="F133" s="36" t="s">
-        <v>181</v>
+        <v>197</v>
       </c>
       <c r="G133" s="36" t="s">
-        <v>279</v>
+        <v>295</v>
       </c>
       <c r="H133" s="36"/>
       <c r="I133" s="36" t="s">
-        <v>170</v>
+        <v>186</v>
       </c>
       <c r="J133" s="40">
         <v>-1.0</v>
@@ -6772,20 +7001,20 @@
         <v>34003.0</v>
       </c>
       <c r="D134" s="39" t="s">
-        <v>281</v>
+        <v>297</v>
       </c>
       <c r="E134" s="19">
         <v>-1.0</v>
       </c>
       <c r="F134" s="39" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="G134" s="39" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="H134" s="39"/>
       <c r="I134" s="38" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="J134" s="19">
         <v>0.0</v>
@@ -6802,20 +7031,20 @@
         <v>35001.0</v>
       </c>
       <c r="D135" s="36" t="s">
-        <v>282</v>
+        <v>298</v>
       </c>
       <c r="E135" s="28">
         <v>-1.0</v>
       </c>
       <c r="F135" s="36" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="G135" s="36" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="H135" s="36"/>
       <c r="I135" s="38" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="J135" s="40">
         <v>-1.0</v>
@@ -6832,20 +7061,20 @@
         <v>36001.0</v>
       </c>
       <c r="D136" s="39" t="s">
-        <v>283</v>
+        <v>299</v>
       </c>
       <c r="E136" s="19">
         <v>36002.0</v>
       </c>
       <c r="F136" s="39" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="G136" s="39" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="H136" s="39"/>
       <c r="I136" s="38" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="J136" s="26">
         <v>1.0</v>
@@ -6862,20 +7091,20 @@
         <v>36002.0</v>
       </c>
       <c r="D137" s="36" t="s">
-        <v>284</v>
+        <v>300</v>
       </c>
       <c r="E137" s="28">
         <v>36003.0</v>
       </c>
       <c r="F137" s="36" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="G137" s="36" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="H137" s="36"/>
       <c r="I137" s="38" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="J137" s="40">
         <v>2.0</v>
@@ -6892,20 +7121,20 @@
         <v>36003.0</v>
       </c>
       <c r="D138" s="39" t="s">
-        <v>285</v>
+        <v>301</v>
       </c>
       <c r="E138" s="19">
         <v>36004.0</v>
       </c>
       <c r="F138" s="39" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="G138" s="39" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="H138" s="39"/>
       <c r="I138" s="38" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="J138" s="26">
         <v>2.0</v>
@@ -6922,20 +7151,20 @@
         <v>36004.0</v>
       </c>
       <c r="D139" s="36" t="s">
-        <v>286</v>
+        <v>302</v>
       </c>
       <c r="E139" s="28">
         <v>-1.0</v>
       </c>
       <c r="F139" s="36" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="G139" s="36" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="H139" s="36"/>
       <c r="I139" s="38" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="J139" s="28">
         <v>0.0</v>
@@ -6952,20 +7181,20 @@
         <v>37001.0</v>
       </c>
       <c r="D140" s="39" t="s">
-        <v>287</v>
+        <v>303</v>
       </c>
       <c r="E140" s="19">
         <v>37002.0</v>
       </c>
       <c r="F140" s="39" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="G140" s="39" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="H140" s="39"/>
       <c r="I140" s="38" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="J140" s="26">
         <v>5.0</v>
@@ -6982,20 +7211,20 @@
         <v>37002.0</v>
       </c>
       <c r="D141" s="36" t="s">
-        <v>288</v>
+        <v>304</v>
       </c>
       <c r="E141" s="28">
         <v>37003.0</v>
       </c>
       <c r="F141" s="36" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="G141" s="36" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="H141" s="36"/>
       <c r="I141" s="38" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="J141" s="40">
         <v>6.0</v>
@@ -7012,20 +7241,20 @@
         <v>37003.0</v>
       </c>
       <c r="D142" s="39" t="s">
-        <v>289</v>
+        <v>305</v>
       </c>
       <c r="E142" s="19">
         <v>-1.0</v>
       </c>
       <c r="F142" s="39" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="G142" s="39" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="H142" s="39"/>
       <c r="I142" s="38" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="J142" s="19">
         <v>0.0</v>
@@ -7042,20 +7271,20 @@
         <v>38001.0</v>
       </c>
       <c r="D143" s="36" t="s">
-        <v>290</v>
+        <v>306</v>
       </c>
       <c r="E143" s="28">
         <v>38002.0</v>
       </c>
       <c r="F143" s="36" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="G143" s="36" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="H143" s="36"/>
       <c r="I143" s="38" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="J143" s="40">
         <v>6.0</v>
@@ -7072,20 +7301,20 @@
         <v>38002.0</v>
       </c>
       <c r="D144" s="39" t="s">
-        <v>291</v>
+        <v>307</v>
       </c>
       <c r="E144" s="19">
         <v>38003.0</v>
       </c>
       <c r="F144" s="39" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="G144" s="39" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="H144" s="39"/>
       <c r="I144" s="38" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="J144" s="26">
         <v>5.0</v>
@@ -7102,20 +7331,20 @@
         <v>38003.0</v>
       </c>
       <c r="D145" s="36" t="s">
-        <v>292</v>
+        <v>308</v>
       </c>
       <c r="E145" s="28">
         <v>38004.0</v>
       </c>
       <c r="F145" s="36" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="G145" s="36" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="H145" s="36"/>
       <c r="I145" s="38" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="J145" s="28">
         <v>0.0</v>
@@ -7132,20 +7361,20 @@
         <v>38004.0</v>
       </c>
       <c r="D146" s="39" t="s">
-        <v>293</v>
+        <v>309</v>
       </c>
       <c r="E146" s="19">
         <v>-1.0</v>
       </c>
       <c r="F146" s="39" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="G146" s="39" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="H146" s="39"/>
       <c r="I146" s="38" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="J146" s="19">
         <v>0.0</v>
@@ -7162,20 +7391,20 @@
         <v>39001.0</v>
       </c>
       <c r="D147" s="42" t="s">
-        <v>294</v>
+        <v>310</v>
       </c>
       <c r="E147" s="28">
         <v>-1.0</v>
       </c>
       <c r="F147" s="36" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="G147" s="36" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="H147" s="36"/>
       <c r="I147" s="38" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="J147" s="28">
         <v>0.0</v>
@@ -7189,23 +7418,23 @@
         <v>106</v>
       </c>
       <c r="C148" s="3">
-        <v>40000.0</v>
+        <v>40001.0</v>
       </c>
       <c r="D148" s="42" t="s">
-        <v>295</v>
+        <v>311</v>
       </c>
       <c r="E148" s="3">
-        <v>40001.0</v>
+        <v>40002.0</v>
       </c>
       <c r="F148" s="36" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="G148" s="36" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="H148" s="36"/>
       <c r="I148" s="38" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="J148" s="40">
         <v>6.0</v>
@@ -7219,23 +7448,23 @@
         <v>106</v>
       </c>
       <c r="C149" s="3">
-        <v>40001.0</v>
+        <v>40002.0</v>
       </c>
       <c r="D149" s="42" t="s">
-        <v>296</v>
+        <v>312</v>
       </c>
       <c r="E149" s="40">
         <v>-1.0</v>
       </c>
       <c r="F149" s="36" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="G149" s="36" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="H149" s="36"/>
       <c r="I149" s="38" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="J149" s="40">
         <v>5.0</v>
@@ -7252,20 +7481,20 @@
         <v>41001.0</v>
       </c>
       <c r="D150" s="42" t="s">
-        <v>297</v>
+        <v>313</v>
       </c>
       <c r="E150" s="40">
         <v>-1.0</v>
       </c>
       <c r="F150" s="36" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="G150" s="36" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="H150" s="36"/>
       <c r="I150" s="43" t="s">
-        <v>170</v>
+        <v>186</v>
       </c>
       <c r="J150" s="40">
         <v>-1.0</v>
@@ -7282,20 +7511,20 @@
         <v>42001.0</v>
       </c>
       <c r="D151" s="42" t="s">
-        <v>298</v>
+        <v>314</v>
       </c>
       <c r="E151" s="40">
         <v>42002.0</v>
       </c>
       <c r="F151" s="42" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="G151" s="42" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="H151" s="36"/>
       <c r="I151" s="43" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="J151" s="40">
         <v>0.0</v>
@@ -7312,20 +7541,20 @@
         <v>42002.0</v>
       </c>
       <c r="D152" s="42" t="s">
-        <v>299</v>
+        <v>315</v>
       </c>
       <c r="E152" s="40">
         <v>-1.0</v>
       </c>
       <c r="F152" s="42" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="G152" s="42" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="H152" s="36"/>
       <c r="I152" s="43" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="J152" s="40">
         <v>0.0</v>
@@ -7342,20 +7571,20 @@
         <v>43001.0</v>
       </c>
       <c r="D153" s="42" t="s">
-        <v>300</v>
+        <v>316</v>
       </c>
       <c r="E153" s="40">
         <v>43002.0</v>
       </c>
       <c r="F153" s="42" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="G153" s="42" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="H153" s="36"/>
       <c r="I153" s="43" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="J153" s="40">
         <v>6.0</v>
@@ -7372,20 +7601,20 @@
         <v>43002.0</v>
       </c>
       <c r="D154" s="42" t="s">
-        <v>301</v>
+        <v>317</v>
       </c>
       <c r="E154" s="40">
         <v>43003.0</v>
       </c>
       <c r="F154" s="42" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="G154" s="42" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="H154" s="36"/>
       <c r="I154" s="43" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="J154" s="40">
         <v>5.0</v>
@@ -7402,148 +7631,953 @@
         <v>43003.0</v>
       </c>
       <c r="D155" s="42" t="s">
-        <v>302</v>
+        <v>318</v>
       </c>
       <c r="E155" s="40">
         <v>-1.0</v>
       </c>
       <c r="F155" s="42" t="s">
-        <v>139</v>
+        <v>155</v>
       </c>
       <c r="G155" s="42" t="s">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="H155" s="36"/>
       <c r="I155" s="43" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="J155" s="40">
         <v>5.0</v>
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="44"/>
-      <c r="B156" s="44"/>
+      <c r="A156" s="32" t="s">
+        <v>114</v>
+      </c>
+      <c r="B156" s="32" t="s">
+        <v>114</v>
+      </c>
+      <c r="C156" s="3">
+        <v>44001.0</v>
+      </c>
+      <c r="D156" s="3" t="s">
+        <v>319</v>
+      </c>
+      <c r="E156" s="40">
+        <v>44002.0</v>
+      </c>
+      <c r="F156" s="42" t="s">
+        <v>155</v>
+      </c>
+      <c r="G156" s="42" t="s">
+        <v>156</v>
+      </c>
+      <c r="H156" s="36"/>
+      <c r="I156" s="43" t="s">
+        <v>157</v>
+      </c>
+      <c r="J156" s="19">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="157">
-      <c r="A157" s="44"/>
-      <c r="B157" s="44"/>
+      <c r="A157" s="32" t="s">
+        <v>114</v>
+      </c>
+      <c r="B157" s="32" t="s">
+        <v>114</v>
+      </c>
+      <c r="C157" s="3">
+        <v>44002.0</v>
+      </c>
+      <c r="D157" s="42" t="s">
+        <v>320</v>
+      </c>
+      <c r="E157" s="40">
+        <v>44003.0</v>
+      </c>
+      <c r="F157" s="42" t="s">
+        <v>155</v>
+      </c>
+      <c r="G157" s="42" t="s">
+        <v>156</v>
+      </c>
+      <c r="H157" s="36"/>
+      <c r="I157" s="43" t="s">
+        <v>157</v>
+      </c>
+      <c r="J157" s="28">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="158">
-      <c r="A158" s="44"/>
-      <c r="B158" s="44"/>
+      <c r="A158" s="32" t="s">
+        <v>114</v>
+      </c>
+      <c r="B158" s="32" t="s">
+        <v>114</v>
+      </c>
+      <c r="C158" s="3">
+        <v>44003.0</v>
+      </c>
+      <c r="D158" s="42" t="s">
+        <v>321</v>
+      </c>
+      <c r="E158" s="40">
+        <v>44004.0</v>
+      </c>
+      <c r="F158" s="42" t="s">
+        <v>155</v>
+      </c>
+      <c r="G158" s="42" t="s">
+        <v>156</v>
+      </c>
+      <c r="H158" s="36"/>
+      <c r="I158" s="43" t="s">
+        <v>157</v>
+      </c>
+      <c r="J158" s="19">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="159">
-      <c r="A159" s="44"/>
-      <c r="B159" s="44"/>
+      <c r="A159" s="32" t="s">
+        <v>114</v>
+      </c>
+      <c r="B159" s="32" t="s">
+        <v>114</v>
+      </c>
+      <c r="C159" s="3">
+        <v>44004.0</v>
+      </c>
+      <c r="D159" s="42" t="s">
+        <v>322</v>
+      </c>
+      <c r="E159" s="40">
+        <v>-1.0</v>
+      </c>
+      <c r="F159" s="42" t="s">
+        <v>155</v>
+      </c>
+      <c r="G159" s="42" t="s">
+        <v>156</v>
+      </c>
+      <c r="H159" s="36"/>
+      <c r="I159" s="43" t="s">
+        <v>157</v>
+      </c>
+      <c r="J159" s="28">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="160">
-      <c r="A160" s="44"/>
-      <c r="B160" s="44"/>
+      <c r="A160" s="32" t="s">
+        <v>116</v>
+      </c>
+      <c r="B160" s="32" t="s">
+        <v>116</v>
+      </c>
+      <c r="C160" s="3">
+        <v>45001.0</v>
+      </c>
+      <c r="D160" s="42" t="s">
+        <v>323</v>
+      </c>
+      <c r="E160" s="40">
+        <v>45002.0</v>
+      </c>
+      <c r="F160" s="42" t="s">
+        <v>155</v>
+      </c>
+      <c r="G160" s="42" t="s">
+        <v>156</v>
+      </c>
+      <c r="H160" s="36"/>
+      <c r="I160" s="43" t="s">
+        <v>157</v>
+      </c>
+      <c r="J160" s="19">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="161">
-      <c r="A161" s="44"/>
-      <c r="B161" s="44"/>
+      <c r="A161" s="32" t="s">
+        <v>116</v>
+      </c>
+      <c r="B161" s="32" t="s">
+        <v>116</v>
+      </c>
+      <c r="C161" s="3">
+        <v>45002.0</v>
+      </c>
+      <c r="D161" s="42" t="s">
+        <v>324</v>
+      </c>
+      <c r="E161" s="40">
+        <v>45003.0</v>
+      </c>
+      <c r="F161" s="42" t="s">
+        <v>155</v>
+      </c>
+      <c r="G161" s="42" t="s">
+        <v>156</v>
+      </c>
+      <c r="H161" s="36"/>
+      <c r="I161" s="43" t="s">
+        <v>157</v>
+      </c>
+      <c r="J161" s="28">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="162">
-      <c r="A162" s="44"/>
-      <c r="B162" s="44"/>
+      <c r="A162" s="32" t="s">
+        <v>116</v>
+      </c>
+      <c r="B162" s="32" t="s">
+        <v>116</v>
+      </c>
+      <c r="C162" s="3">
+        <v>45003.0</v>
+      </c>
+      <c r="D162" s="42" t="s">
+        <v>325</v>
+      </c>
+      <c r="E162" s="40">
+        <v>45004.0</v>
+      </c>
+      <c r="F162" s="42" t="s">
+        <v>155</v>
+      </c>
+      <c r="G162" s="42" t="s">
+        <v>156</v>
+      </c>
+      <c r="H162" s="36"/>
+      <c r="I162" s="43" t="s">
+        <v>157</v>
+      </c>
+      <c r="J162" s="19">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="163">
-      <c r="A163" s="44"/>
-      <c r="B163" s="44"/>
+      <c r="A163" s="32" t="s">
+        <v>116</v>
+      </c>
+      <c r="B163" s="32" t="s">
+        <v>116</v>
+      </c>
+      <c r="C163" s="3">
+        <v>45004.0</v>
+      </c>
+      <c r="D163" s="42" t="s">
+        <v>326</v>
+      </c>
+      <c r="E163" s="40">
+        <v>45005.0</v>
+      </c>
+      <c r="F163" s="42" t="s">
+        <v>155</v>
+      </c>
+      <c r="G163" s="42" t="s">
+        <v>156</v>
+      </c>
+      <c r="H163" s="36"/>
+      <c r="I163" s="43" t="s">
+        <v>157</v>
+      </c>
+      <c r="J163" s="28">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="164">
-      <c r="A164" s="44"/>
-      <c r="B164" s="44"/>
+      <c r="A164" s="32" t="s">
+        <v>116</v>
+      </c>
+      <c r="B164" s="32" t="s">
+        <v>116</v>
+      </c>
+      <c r="C164" s="3">
+        <v>45005.0</v>
+      </c>
+      <c r="D164" s="42" t="s">
+        <v>327</v>
+      </c>
+      <c r="E164" s="40">
+        <v>-1.0</v>
+      </c>
+      <c r="F164" s="42" t="s">
+        <v>155</v>
+      </c>
+      <c r="G164" s="42" t="s">
+        <v>156</v>
+      </c>
+      <c r="H164" s="36"/>
+      <c r="I164" s="43" t="s">
+        <v>157</v>
+      </c>
+      <c r="J164" s="19">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="165">
-      <c r="A165" s="44"/>
-      <c r="B165" s="44"/>
+      <c r="A165" s="32" t="s">
+        <v>118</v>
+      </c>
+      <c r="B165" s="32" t="s">
+        <v>118</v>
+      </c>
+      <c r="C165" s="3">
+        <v>46001.0</v>
+      </c>
+      <c r="D165" s="42" t="s">
+        <v>328</v>
+      </c>
+      <c r="E165" s="40">
+        <v>46002.0</v>
+      </c>
+      <c r="F165" s="42" t="s">
+        <v>155</v>
+      </c>
+      <c r="G165" s="42" t="s">
+        <v>156</v>
+      </c>
+      <c r="H165" s="36"/>
+      <c r="I165" s="43" t="s">
+        <v>157</v>
+      </c>
+      <c r="J165" s="28">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="166">
-      <c r="A166" s="44"/>
-      <c r="B166" s="44"/>
+      <c r="A166" s="32" t="s">
+        <v>118</v>
+      </c>
+      <c r="B166" s="32" t="s">
+        <v>118</v>
+      </c>
+      <c r="C166" s="3">
+        <v>46002.0</v>
+      </c>
+      <c r="D166" s="42" t="s">
+        <v>329</v>
+      </c>
+      <c r="E166" s="40">
+        <v>46003.0</v>
+      </c>
+      <c r="F166" s="42" t="s">
+        <v>155</v>
+      </c>
+      <c r="G166" s="42" t="s">
+        <v>156</v>
+      </c>
+      <c r="H166" s="36"/>
+      <c r="I166" s="43" t="s">
+        <v>157</v>
+      </c>
+      <c r="J166" s="19">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="167">
-      <c r="A167" s="44"/>
-      <c r="B167" s="44"/>
+      <c r="A167" s="32" t="s">
+        <v>118</v>
+      </c>
+      <c r="B167" s="32" t="s">
+        <v>118</v>
+      </c>
+      <c r="C167" s="3">
+        <v>46003.0</v>
+      </c>
+      <c r="D167" s="42" t="s">
+        <v>330</v>
+      </c>
+      <c r="E167" s="40">
+        <v>46004.0</v>
+      </c>
+      <c r="F167" s="42" t="s">
+        <v>155</v>
+      </c>
+      <c r="G167" s="42" t="s">
+        <v>156</v>
+      </c>
+      <c r="H167" s="36"/>
+      <c r="I167" s="43" t="s">
+        <v>157</v>
+      </c>
+      <c r="J167" s="28">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="168">
-      <c r="A168" s="44"/>
-      <c r="B168" s="44"/>
+      <c r="A168" s="32" t="s">
+        <v>118</v>
+      </c>
+      <c r="B168" s="32" t="s">
+        <v>118</v>
+      </c>
+      <c r="C168" s="3">
+        <v>46004.0</v>
+      </c>
+      <c r="D168" s="42" t="s">
+        <v>331</v>
+      </c>
+      <c r="E168" s="40">
+        <v>46005.0</v>
+      </c>
+      <c r="F168" s="42" t="s">
+        <v>155</v>
+      </c>
+      <c r="G168" s="42" t="s">
+        <v>156</v>
+      </c>
+      <c r="H168" s="36"/>
+      <c r="I168" s="43" t="s">
+        <v>157</v>
+      </c>
+      <c r="J168" s="19">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="169">
-      <c r="A169" s="44"/>
-      <c r="B169" s="44"/>
+      <c r="A169" s="32" t="s">
+        <v>118</v>
+      </c>
+      <c r="B169" s="32" t="s">
+        <v>118</v>
+      </c>
+      <c r="C169" s="3">
+        <v>46005.0</v>
+      </c>
+      <c r="D169" s="42" t="s">
+        <v>332</v>
+      </c>
+      <c r="E169" s="40">
+        <v>-1.0</v>
+      </c>
+      <c r="F169" s="42" t="s">
+        <v>155</v>
+      </c>
+      <c r="G169" s="42" t="s">
+        <v>156</v>
+      </c>
+      <c r="H169" s="36"/>
+      <c r="I169" s="43" t="s">
+        <v>157</v>
+      </c>
+      <c r="J169" s="28">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="170">
-      <c r="A170" s="44"/>
-      <c r="B170" s="44"/>
+      <c r="A170" s="32" t="s">
+        <v>120</v>
+      </c>
+      <c r="B170" s="32" t="s">
+        <v>120</v>
+      </c>
+      <c r="C170" s="3">
+        <v>47001.0</v>
+      </c>
+      <c r="D170" s="3" t="s">
+        <v>333</v>
+      </c>
+      <c r="E170" s="3">
+        <v>47002.0</v>
+      </c>
+      <c r="F170" s="42" t="s">
+        <v>155</v>
+      </c>
+      <c r="G170" s="42" t="s">
+        <v>156</v>
+      </c>
+      <c r="I170" s="43" t="s">
+        <v>157</v>
+      </c>
+      <c r="J170" s="19">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="171">
-      <c r="A171" s="44"/>
-      <c r="B171" s="44"/>
+      <c r="A171" s="32" t="s">
+        <v>120</v>
+      </c>
+      <c r="B171" s="32" t="s">
+        <v>120</v>
+      </c>
+      <c r="C171" s="3">
+        <v>47002.0</v>
+      </c>
+      <c r="D171" s="42" t="s">
+        <v>334</v>
+      </c>
+      <c r="E171" s="40">
+        <v>-1.0</v>
+      </c>
+      <c r="F171" s="42" t="s">
+        <v>197</v>
+      </c>
+      <c r="G171" s="42" t="s">
+        <v>162</v>
+      </c>
+      <c r="H171" s="36"/>
+      <c r="I171" s="43" t="s">
+        <v>180</v>
+      </c>
+      <c r="J171" s="28">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="172">
-      <c r="A172" s="44"/>
-      <c r="B172" s="44"/>
+      <c r="A172" s="32" t="s">
+        <v>122</v>
+      </c>
+      <c r="B172" s="32" t="s">
+        <v>122</v>
+      </c>
+      <c r="C172" s="3">
+        <v>48001.0</v>
+      </c>
+      <c r="D172" s="42" t="s">
+        <v>335</v>
+      </c>
+      <c r="E172" s="40">
+        <v>48002.0</v>
+      </c>
+      <c r="F172" s="42" t="s">
+        <v>155</v>
+      </c>
+      <c r="G172" s="42" t="s">
+        <v>156</v>
+      </c>
+      <c r="H172" s="36"/>
+      <c r="I172" s="43" t="s">
+        <v>157</v>
+      </c>
+      <c r="J172" s="19">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="173">
-      <c r="A173" s="44"/>
-      <c r="B173" s="44"/>
+      <c r="A173" s="32" t="s">
+        <v>122</v>
+      </c>
+      <c r="B173" s="32" t="s">
+        <v>122</v>
+      </c>
+      <c r="C173" s="3">
+        <v>48002.0</v>
+      </c>
+      <c r="D173" s="42" t="s">
+        <v>336</v>
+      </c>
+      <c r="E173" s="40">
+        <v>48003.0</v>
+      </c>
+      <c r="F173" s="42" t="s">
+        <v>155</v>
+      </c>
+      <c r="G173" s="42" t="s">
+        <v>156</v>
+      </c>
+      <c r="H173" s="36"/>
+      <c r="I173" s="43" t="s">
+        <v>157</v>
+      </c>
+      <c r="J173" s="28">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="174">
-      <c r="A174" s="44"/>
-      <c r="B174" s="44"/>
+      <c r="A174" s="32" t="s">
+        <v>122</v>
+      </c>
+      <c r="B174" s="32" t="s">
+        <v>122</v>
+      </c>
+      <c r="C174" s="3">
+        <v>48003.0</v>
+      </c>
+      <c r="D174" s="42" t="s">
+        <v>337</v>
+      </c>
+      <c r="E174" s="40">
+        <v>48004.0</v>
+      </c>
+      <c r="F174" s="42" t="s">
+        <v>155</v>
+      </c>
+      <c r="G174" s="42" t="s">
+        <v>156</v>
+      </c>
+      <c r="H174" s="36"/>
+      <c r="I174" s="43" t="s">
+        <v>157</v>
+      </c>
+      <c r="J174" s="19">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="175">
-      <c r="A175" s="44"/>
-      <c r="B175" s="44"/>
+      <c r="A175" s="32" t="s">
+        <v>122</v>
+      </c>
+      <c r="B175" s="32" t="s">
+        <v>122</v>
+      </c>
+      <c r="C175" s="3">
+        <v>48004.0</v>
+      </c>
+      <c r="D175" s="42" t="s">
+        <v>338</v>
+      </c>
+      <c r="E175" s="40">
+        <v>48005.0</v>
+      </c>
+      <c r="F175" s="42" t="s">
+        <v>155</v>
+      </c>
+      <c r="G175" s="42" t="s">
+        <v>156</v>
+      </c>
+      <c r="H175" s="36"/>
+      <c r="I175" s="43" t="s">
+        <v>157</v>
+      </c>
+      <c r="J175" s="28">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="176">
-      <c r="A176" s="44"/>
-      <c r="B176" s="44"/>
+      <c r="A176" s="32" t="s">
+        <v>122</v>
+      </c>
+      <c r="B176" s="32" t="s">
+        <v>122</v>
+      </c>
+      <c r="C176" s="3">
+        <v>48005.0</v>
+      </c>
+      <c r="D176" s="42" t="s">
+        <v>339</v>
+      </c>
+      <c r="E176" s="40">
+        <v>48006.0</v>
+      </c>
+      <c r="F176" s="42" t="s">
+        <v>155</v>
+      </c>
+      <c r="G176" s="42" t="s">
+        <v>156</v>
+      </c>
+      <c r="H176" s="36"/>
+      <c r="I176" s="43" t="s">
+        <v>157</v>
+      </c>
+      <c r="J176" s="19">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="177">
-      <c r="A177" s="44"/>
-      <c r="B177" s="44"/>
+      <c r="A177" s="32" t="s">
+        <v>122</v>
+      </c>
+      <c r="B177" s="32" t="s">
+        <v>122</v>
+      </c>
+      <c r="C177" s="3">
+        <v>48006.0</v>
+      </c>
+      <c r="D177" s="42" t="s">
+        <v>340</v>
+      </c>
+      <c r="E177" s="40">
+        <v>48007.0</v>
+      </c>
+      <c r="F177" s="42" t="s">
+        <v>155</v>
+      </c>
+      <c r="G177" s="42" t="s">
+        <v>156</v>
+      </c>
+      <c r="H177" s="36"/>
+      <c r="I177" s="43" t="s">
+        <v>157</v>
+      </c>
+      <c r="J177" s="28">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="178">
-      <c r="A178" s="44"/>
-      <c r="B178" s="44"/>
+      <c r="A178" s="32" t="s">
+        <v>122</v>
+      </c>
+      <c r="B178" s="32" t="s">
+        <v>122</v>
+      </c>
+      <c r="C178" s="3">
+        <v>48007.0</v>
+      </c>
+      <c r="D178" s="42" t="s">
+        <v>341</v>
+      </c>
+      <c r="E178" s="40">
+        <v>48008.0</v>
+      </c>
+      <c r="F178" s="42" t="s">
+        <v>155</v>
+      </c>
+      <c r="G178" s="42" t="s">
+        <v>156</v>
+      </c>
+      <c r="H178" s="36"/>
+      <c r="I178" s="43" t="s">
+        <v>157</v>
+      </c>
+      <c r="J178" s="19">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="179">
-      <c r="A179" s="44"/>
-      <c r="B179" s="44"/>
+      <c r="A179" s="32" t="s">
+        <v>122</v>
+      </c>
+      <c r="B179" s="32" t="s">
+        <v>122</v>
+      </c>
+      <c r="C179" s="3">
+        <v>48008.0</v>
+      </c>
+      <c r="D179" s="42" t="s">
+        <v>342</v>
+      </c>
+      <c r="E179" s="40">
+        <v>48009.0</v>
+      </c>
+      <c r="F179" s="42" t="s">
+        <v>155</v>
+      </c>
+      <c r="G179" s="42" t="s">
+        <v>156</v>
+      </c>
+      <c r="H179" s="36"/>
+      <c r="I179" s="43" t="s">
+        <v>157</v>
+      </c>
+      <c r="J179" s="28">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="180">
-      <c r="A180" s="44"/>
-      <c r="B180" s="44"/>
+      <c r="A180" s="32" t="s">
+        <v>122</v>
+      </c>
+      <c r="B180" s="32" t="s">
+        <v>122</v>
+      </c>
+      <c r="C180" s="3">
+        <v>48009.0</v>
+      </c>
+      <c r="D180" s="42" t="s">
+        <v>343</v>
+      </c>
+      <c r="E180" s="40">
+        <v>-1.0</v>
+      </c>
+      <c r="F180" s="42" t="s">
+        <v>155</v>
+      </c>
+      <c r="G180" s="42" t="s">
+        <v>156</v>
+      </c>
+      <c r="H180" s="36"/>
+      <c r="I180" s="43" t="s">
+        <v>157</v>
+      </c>
+      <c r="J180" s="19">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="181">
-      <c r="A181" s="44"/>
-      <c r="B181" s="44"/>
+      <c r="A181" s="32" t="s">
+        <v>124</v>
+      </c>
+      <c r="B181" s="32" t="s">
+        <v>124</v>
+      </c>
+      <c r="C181" s="3">
+        <v>49001.0</v>
+      </c>
+      <c r="D181" s="42" t="s">
+        <v>344</v>
+      </c>
+      <c r="E181" s="40">
+        <v>49002.0</v>
+      </c>
+      <c r="F181" s="42" t="s">
+        <v>155</v>
+      </c>
+      <c r="G181" s="42" t="s">
+        <v>156</v>
+      </c>
+      <c r="H181" s="36"/>
+      <c r="I181" s="43" t="s">
+        <v>157</v>
+      </c>
+      <c r="J181" s="28">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="182">
-      <c r="A182" s="44"/>
-      <c r="B182" s="44"/>
+      <c r="A182" s="32" t="s">
+        <v>124</v>
+      </c>
+      <c r="B182" s="32" t="s">
+        <v>124</v>
+      </c>
+      <c r="C182" s="3">
+        <v>49002.0</v>
+      </c>
+      <c r="D182" s="42" t="s">
+        <v>345</v>
+      </c>
+      <c r="E182" s="40">
+        <v>-1.0</v>
+      </c>
+      <c r="F182" s="42" t="s">
+        <v>155</v>
+      </c>
+      <c r="G182" s="42" t="s">
+        <v>156</v>
+      </c>
+      <c r="H182" s="36"/>
+      <c r="I182" s="43" t="s">
+        <v>157</v>
+      </c>
+      <c r="J182" s="19">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="183">
-      <c r="A183" s="44"/>
-      <c r="B183" s="44"/>
+      <c r="A183" s="32" t="s">
+        <v>126</v>
+      </c>
+      <c r="B183" s="32" t="s">
+        <v>126</v>
+      </c>
+      <c r="C183" s="3">
+        <v>50001.0</v>
+      </c>
+      <c r="D183" s="42" t="s">
+        <v>346</v>
+      </c>
+      <c r="E183" s="40">
+        <v>50002.0</v>
+      </c>
+      <c r="F183" s="42" t="s">
+        <v>155</v>
+      </c>
+      <c r="G183" s="42" t="s">
+        <v>156</v>
+      </c>
+      <c r="H183" s="36"/>
+      <c r="I183" s="43" t="s">
+        <v>157</v>
+      </c>
+      <c r="J183" s="28">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="184">
-      <c r="A184" s="44"/>
-      <c r="B184" s="44"/>
+      <c r="A184" s="32" t="s">
+        <v>126</v>
+      </c>
+      <c r="B184" s="32" t="s">
+        <v>126</v>
+      </c>
+      <c r="C184" s="3">
+        <v>50002.0</v>
+      </c>
+      <c r="D184" s="42" t="s">
+        <v>347</v>
+      </c>
+      <c r="E184" s="40">
+        <v>50003.0</v>
+      </c>
+      <c r="F184" s="42" t="s">
+        <v>155</v>
+      </c>
+      <c r="G184" s="42" t="s">
+        <v>156</v>
+      </c>
+      <c r="H184" s="36"/>
+      <c r="I184" s="43" t="s">
+        <v>157</v>
+      </c>
+      <c r="J184" s="19">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="185">
-      <c r="A185" s="44"/>
-      <c r="B185" s="44"/>
+      <c r="A185" s="32" t="s">
+        <v>126</v>
+      </c>
+      <c r="B185" s="32" t="s">
+        <v>126</v>
+      </c>
+      <c r="C185" s="3">
+        <v>50003.0</v>
+      </c>
+      <c r="D185" s="42" t="s">
+        <v>348</v>
+      </c>
+      <c r="E185" s="40">
+        <v>-1.0</v>
+      </c>
+      <c r="F185" s="42" t="s">
+        <v>155</v>
+      </c>
+      <c r="G185" s="42" t="s">
+        <v>156</v>
+      </c>
+      <c r="H185" s="36"/>
+      <c r="I185" s="43" t="s">
+        <v>157</v>
+      </c>
+      <c r="J185" s="28">
+        <v>0.0</v>
+      </c>
     </row>
     <row r="186">
-      <c r="A186" s="44"/>
-      <c r="B186" s="44"/>
+      <c r="A186" s="32" t="s">
+        <v>128</v>
+      </c>
+      <c r="B186" s="32" t="s">
+        <v>128</v>
+      </c>
+      <c r="C186" s="3">
+        <v>51001.0</v>
+      </c>
+      <c r="D186" s="42" t="s">
+        <v>349</v>
+      </c>
+      <c r="E186" s="40">
+        <v>-1.0</v>
+      </c>
+      <c r="F186" s="42" t="s">
+        <v>155</v>
+      </c>
+      <c r="G186" s="42" t="s">
+        <v>156</v>
+      </c>
+      <c r="H186" s="36"/>
+      <c r="I186" s="43" t="s">
+        <v>186</v>
+      </c>
+      <c r="J186" s="40">
+        <v>-1.0</v>
+      </c>
     </row>
     <row r="187">
       <c r="A187" s="44"/>
@@ -10720,6 +11754,10 @@
     <row r="980">
       <c r="A980" s="44"/>
       <c r="B980" s="44"/>
+    </row>
+    <row r="981">
+      <c r="A981" s="44"/>
+      <c r="B981" s="44"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
@@ -10748,48 +11786,48 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="4" t="s">
-        <v>135</v>
+        <v>151</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>303</v>
+        <v>350</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>304</v>
+        <v>351</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>305</v>
+        <v>352</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>306</v>
+        <v>353</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>307</v>
+        <v>354</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>308</v>
+        <v>355</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>309</v>
+        <v>356</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>310</v>
+        <v>357</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>311</v>
+        <v>358</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>312</v>
+        <v>359</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="45" t="s">
-        <v>172</v>
+        <v>188</v>
       </c>
       <c r="B2" s="46" t="s">
-        <v>313</v>
+        <v>360</v>
       </c>
       <c r="C2" s="46" t="s">
-        <v>314</v>
+        <v>361</v>
       </c>
       <c r="D2" s="4"/>
       <c r="E2" s="3">
@@ -10804,13 +11842,13 @@
     </row>
     <row r="3">
       <c r="A3" s="47" t="s">
-        <v>315</v>
+        <v>362</v>
       </c>
       <c r="B3" s="46" t="s">
-        <v>316</v>
+        <v>363</v>
       </c>
       <c r="C3" s="48" t="s">
-        <v>317</v>
+        <v>364</v>
       </c>
       <c r="D3" s="4"/>
       <c r="E3" s="5">
@@ -10821,24 +11859,24 @@
       </c>
       <c r="G3" s="4"/>
       <c r="H3" s="3" t="s">
-        <v>318</v>
+        <v>365</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>319</v>
+        <v>366</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>320</v>
+        <v>367</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>321</v>
+        <v>368</v>
       </c>
       <c r="B4" s="49" t="s">
-        <v>322</v>
+        <v>369</v>
       </c>
       <c r="C4" s="49" t="s">
-        <v>323</v>
+        <v>370</v>
       </c>
       <c r="D4" s="4"/>
       <c r="E4" s="2">
@@ -10849,24 +11887,24 @@
       </c>
       <c r="G4" s="4"/>
       <c r="H4" s="3" t="s">
-        <v>324</v>
+        <v>371</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>325</v>
+        <v>372</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>326</v>
+        <v>373</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>327</v>
+        <v>374</v>
       </c>
       <c r="B5" s="50" t="s">
-        <v>328</v>
+        <v>375</v>
       </c>
       <c r="C5" s="50" t="s">
-        <v>329</v>
+        <v>376</v>
       </c>
       <c r="E5" s="3">
         <v>-10.0</v>
@@ -10875,24 +11913,24 @@
         <v>0.0</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>330</v>
+        <v>377</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>331</v>
+        <v>378</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>332</v>
+        <v>379</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>333</v>
+        <v>380</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>334</v>
+        <v>381</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>335</v>
+        <v>382</v>
       </c>
       <c r="E6" s="3">
         <v>0.0</v>
@@ -10901,24 +11939,24 @@
         <v>-10.0</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>336</v>
+        <v>383</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>337</v>
+        <v>384</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>338</v>
+        <v>385</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>339</v>
+        <v>386</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>340</v>
+        <v>387</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>341</v>
+        <v>388</v>
       </c>
       <c r="E7" s="3">
         <v>-10.0</v>
@@ -10927,24 +11965,24 @@
         <v>0.0</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>342</v>
+        <v>389</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>343</v>
+        <v>390</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>344</v>
+        <v>391</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>345</v>
+        <v>392</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>346</v>
+        <v>393</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>347</v>
+        <v>394</v>
       </c>
       <c r="E8" s="3">
         <v>0.0</v>
@@ -10953,24 +11991,24 @@
         <v>-10.0</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>348</v>
+        <v>395</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>349</v>
+        <v>396</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>350</v>
+        <v>397</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>351</v>
+        <v>398</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>352</v>
+        <v>399</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>353</v>
+        <v>400</v>
       </c>
       <c r="E9" s="3">
         <v>0.0</v>
@@ -10979,25 +12017,25 @@
         <v>0.0</v>
       </c>
       <c r="H9" s="32" t="s">
-        <v>354</v>
+        <v>401</v>
       </c>
       <c r="I9" s="32" t="s">
-        <v>355</v>
+        <v>402</v>
       </c>
       <c r="J9" s="32"/>
       <c r="K9" s="3" t="s">
-        <v>356</v>
+        <v>403</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>357</v>
+        <v>404</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>358</v>
+        <v>405</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>359</v>
+        <v>406</v>
       </c>
       <c r="E10" s="3">
         <v>-10.0</v>
@@ -11006,24 +12044,24 @@
         <v>-10.0</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>360</v>
+        <v>407</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>361</v>
+        <v>408</v>
       </c>
       <c r="K10" s="51" t="s">
-        <v>362</v>
+        <v>409</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>363</v>
+        <v>410</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>364</v>
+        <v>411</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>365</v>
+        <v>412</v>
       </c>
       <c r="E11" s="3">
         <v>-10.0</v>
@@ -11032,24 +12070,24 @@
         <v>-10.0</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>366</v>
+        <v>413</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>367</v>
+        <v>414</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>368</v>
+        <v>415</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>369</v>
+        <v>416</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>370</v>
+        <v>417</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>371</v>
+        <v>418</v>
       </c>
       <c r="E12" s="3">
         <v>-10.0</v>
@@ -11058,13 +12096,13 @@
         <v>0.0</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>372</v>
+        <v>419</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>373</v>
+        <v>420</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>374</v>
+        <v>421</v>
       </c>
     </row>
   </sheetData>
@@ -11086,21 +12124,21 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="3" t="s">
-        <v>375</v>
+        <v>422</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>376</v>
+        <v>423</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>377</v>
+        <v>424</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>115</v>
+        <v>131</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>378</v>
+        <v>425</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>21</v>
@@ -11109,12 +12147,12 @@
         <v>24</v>
       </c>
       <c r="D2" s="52" t="s">
-        <v>379</v>
+        <v>426</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>380</v>
+        <v>427</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>24</v>
@@ -11123,40 +12161,40 @@
         <v>30</v>
       </c>
       <c r="D3" s="52" t="s">
-        <v>381</v>
+        <v>428</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>382</v>
+        <v>429</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>30</v>
       </c>
       <c r="C4" s="49" t="s">
-        <v>383</v>
+        <v>430</v>
       </c>
       <c r="D4" s="52" t="s">
-        <v>384</v>
+        <v>431</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>385</v>
+        <v>432</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>383</v>
+        <v>430</v>
       </c>
       <c r="C5" s="49" t="s">
         <v>36</v>
       </c>
       <c r="D5" s="52" t="s">
-        <v>386</v>
+        <v>433</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>387</v>
+        <v>434</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>36</v>
@@ -11165,12 +12203,12 @@
         <v>42</v>
       </c>
       <c r="D6" s="52" t="s">
-        <v>379</v>
+        <v>426</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>388</v>
+        <v>435</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>42</v>
@@ -11179,68 +12217,68 @@
         <v>48</v>
       </c>
       <c r="D7" s="52" t="s">
-        <v>381</v>
+        <v>428</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>389</v>
+        <v>436</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>48</v>
       </c>
       <c r="C8" s="49" t="s">
-        <v>332</v>
+        <v>379</v>
       </c>
       <c r="D8" s="52" t="s">
-        <v>390</v>
+        <v>437</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>391</v>
+        <v>438</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>332</v>
+        <v>379</v>
       </c>
       <c r="C9" s="49" t="s">
         <v>54</v>
       </c>
       <c r="D9" s="52" t="s">
-        <v>386</v>
+        <v>433</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>392</v>
+        <v>439</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>54</v>
       </c>
       <c r="C10" s="49" t="s">
-        <v>393</v>
+        <v>440</v>
       </c>
       <c r="D10" s="52" t="s">
-        <v>394</v>
+        <v>441</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>395</v>
+        <v>442</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>393</v>
+        <v>440</v>
       </c>
       <c r="C11" s="49" t="s">
         <v>57</v>
       </c>
       <c r="D11" s="52" t="s">
-        <v>396</v>
+        <v>443</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>397</v>
+        <v>444</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>57</v>
@@ -11249,12 +12287,12 @@
         <v>60</v>
       </c>
       <c r="D12" s="52" t="s">
-        <v>398</v>
+        <v>445</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>399</v>
+        <v>446</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>60</v>
@@ -11263,12 +12301,12 @@
         <v>106</v>
       </c>
       <c r="D13" s="52" t="s">
-        <v>400</v>
+        <v>447</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>401</v>
+        <v>448</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>106</v>
@@ -11277,24 +12315,24 @@
         <v>63</v>
       </c>
       <c r="D14" s="52" t="s">
-        <v>402</v>
+        <v>449</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>403</v>
+        <v>450</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>63</v>
       </c>
       <c r="C15" s="52"/>
       <c r="D15" s="52" t="s">
-        <v>404</v>
+        <v>451</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>405</v>
+        <v>452</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>66</v>
@@ -11303,26 +12341,26 @@
         <v>70</v>
       </c>
       <c r="D16" s="52" t="s">
-        <v>406</v>
+        <v>453</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>407</v>
+        <v>454</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>70</v>
       </c>
       <c r="C17" s="49" t="s">
-        <v>408</v>
+        <v>455</v>
       </c>
       <c r="D17" s="52" t="s">
-        <v>409</v>
+        <v>456</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>410</v>
+        <v>457</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>74</v>
@@ -11331,12 +12369,12 @@
         <v>76</v>
       </c>
       <c r="D18" s="52" t="s">
-        <v>411</v>
+        <v>458</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>412</v>
+        <v>459</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>76</v>
@@ -11345,40 +12383,40 @@
         <v>80</v>
       </c>
       <c r="D19" s="52" t="s">
-        <v>413</v>
+        <v>460</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>414</v>
+        <v>461</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>80</v>
       </c>
       <c r="C20" s="49" t="s">
-        <v>362</v>
+        <v>409</v>
       </c>
       <c r="D20" s="52" t="s">
-        <v>415</v>
+        <v>462</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>416</v>
+        <v>463</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>362</v>
+        <v>409</v>
       </c>
       <c r="C21" s="49" t="s">
         <v>86</v>
       </c>
       <c r="D21" s="52" t="s">
-        <v>417</v>
+        <v>464</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>418</v>
+        <v>465</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>86</v>
@@ -11387,12 +12425,12 @@
         <v>90</v>
       </c>
       <c r="D22" s="52" t="s">
-        <v>411</v>
+        <v>458</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>419</v>
+        <v>466</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>90</v>
@@ -11401,12 +12439,12 @@
         <v>92</v>
       </c>
       <c r="D23" s="52" t="s">
-        <v>420</v>
+        <v>467</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>421</v>
+        <v>468</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>92</v>
@@ -11415,41 +12453,41 @@
         <v>94</v>
       </c>
       <c r="D24" s="52" t="s">
-        <v>413</v>
+        <v>460</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>422</v>
+        <v>469</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>368</v>
+        <v>415</v>
       </c>
       <c r="C25" s="49" t="s">
         <v>98</v>
       </c>
       <c r="D25" s="52" t="s">
-        <v>417</v>
+        <v>464</v>
       </c>
       <c r="F25" s="52"/>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>423</v>
+        <v>470</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>94</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>368</v>
+        <v>415</v>
       </c>
       <c r="D26" s="52" t="s">
-        <v>415</v>
+        <v>462</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>424</v>
+        <v>471</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>98</v>
@@ -11458,57 +12496,57 @@
         <v>100</v>
       </c>
       <c r="D27" s="52" t="s">
-        <v>411</v>
+        <v>458</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>425</v>
+        <v>472</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>100</v>
       </c>
       <c r="C28" s="49" t="s">
-        <v>426</v>
+        <v>473</v>
       </c>
       <c r="D28" s="52" t="s">
-        <v>394</v>
+        <v>441</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>427</v>
+        <v>474</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>426</v>
+        <v>473</v>
       </c>
       <c r="C29" s="49" t="s">
         <v>102</v>
       </c>
       <c r="D29" s="52" t="s">
-        <v>428</v>
+        <v>475</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>429</v>
+        <v>476</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>102</v>
       </c>
       <c r="D30" s="52" t="s">
-        <v>430</v>
+        <v>477</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>431</v>
+        <v>478</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>112</v>
       </c>
       <c r="D31" s="50" t="s">
-        <v>432</v>
+        <v>479</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/02Script/Table/EventTable.xlsx
+++ b/Assets/02Script/Table/EventTable.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2435" uniqueCount="672">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2381" uniqueCount="688">
   <si>
     <t>EventID</t>
   </si>
@@ -570,6 +570,12 @@
   </si>
   <si>
     <t>해피 엔딩</t>
+  </si>
+  <si>
+    <t>E080</t>
+  </si>
+  <si>
+    <t>2스테이지 1인칭에서 나온 후 다시 가려고 할 때</t>
   </si>
   <si>
     <t>Order</t>
@@ -1561,51 +1567,6 @@
     <t>일단... 앞으로 나아가 볼까...</t>
   </si>
   <si>
-    <t>어..? 저기 문이... 있잖아...?</t>
-  </si>
-  <si>
-    <t>저기가 나가는 곳인가...? 다행이다...</t>
-  </si>
-  <si>
-    <t>어..딜...가..려..고...</t>
-  </si>
-  <si>
-    <t>또... 너구나...</t>
-  </si>
-  <si>
-    <t>왜 자꾸 날 괴롭히는 거야...</t>
-  </si>
-  <si>
-    <t>넌...원래....살고..싶지..않..았잖아...</t>
-  </si>
-  <si>
-    <t>너의...소원을...이루어...주려는...거다...</t>
-  </si>
-  <si>
-    <t>아니야..... 난....</t>
-  </si>
-  <si>
-    <t>난.... 살고 싶어!!!</t>
-  </si>
-  <si>
-    <t>이미.... 늦었다...</t>
-  </si>
-  <si>
-    <t>그냥... 포기하고... 네... 몸을... 넘겨라...</t>
-  </si>
-  <si>
-    <t>시... 싫어....</t>
-  </si>
-  <si>
-    <t>누가... 좀... 도와줘....</t>
-  </si>
-  <si>
-    <t>죽어!!!!!!!!!!!!!!!!!!!!!!!!!!!!!!!!!</t>
-  </si>
-  <si>
-    <t>그만둬!!!!</t>
-  </si>
-  <si>
     <t>방해... 하지... 마라....!!!</t>
   </si>
   <si>
@@ -1639,28 +1600,7 @@
     <t>그렇지만 지금은 살아서 여길 나가는 게 우선이야...</t>
   </si>
   <si>
-    <t>저녀석은 엄마가 막을 테니깐 넌 어서 문으로 달려가렴</t>
-  </si>
-  <si>
-    <t>엄마가... 꼭 다시 갈게... 알겠지...?</t>
-  </si>
-  <si>
-    <t>네.... 알겠어요... 꼭이에요....</t>
-  </si>
-  <si>
-    <t>그럼... 당연하지... 약속할게...</t>
-  </si>
-  <si>
-    <t>그럼 엄마가 신호하면 문으로 달려가 알겠지?</t>
-  </si>
-  <si>
-    <t>네... 알겠어요..!!</t>
-  </si>
-  <si>
-    <t>지금이야!!!!!!</t>
-  </si>
-  <si>
-    <t>네 이놈!!!!!!!!!!!!!!!!!!!!!!!!!!!!!!!!!!!!!!!!!!!!!</t>
+    <t>녀석이 쫓아올지도 모르니까 어서 가서 문을 열어야겠어..</t>
   </si>
   <si>
     <t>Choice0</t>
@@ -2063,6 +2003,114 @@
   </si>
   <si>
     <t>귀신을 피해 이곳을 탈출하자.</t>
+  </si>
+  <si>
+    <t>Q031</t>
+  </si>
+  <si>
+    <t>터널 밖으로 이동하기.</t>
+  </si>
+  <si>
+    <t>Q032</t>
+  </si>
+  <si>
+    <t>사고 현장 확인하기.</t>
+  </si>
+  <si>
+    <t>Q033</t>
+  </si>
+  <si>
+    <t>사고 현장에서 비밀번호 찾기.</t>
+  </si>
+  <si>
+    <t>Q034</t>
+  </si>
+  <si>
+    <t>귀신을 피해 도망치기.</t>
+  </si>
+  <si>
+    <t>Q035</t>
+  </si>
+  <si>
+    <t>제한 시간동안 살아남기.</t>
+  </si>
+  <si>
+    <t>Q036</t>
+  </si>
+  <si>
+    <t>골목길로 돌아가기.</t>
+  </si>
+  <si>
+    <t>Q037</t>
+  </si>
+  <si>
+    <t>비밀번호 : 375</t>
+  </si>
+  <si>
+    <t>Q038</t>
+  </si>
+  <si>
+    <t>밖으로 나가기.</t>
+  </si>
+  <si>
+    <t>Q039</t>
+  </si>
+  <si>
+    <t>엄마의 일기장 찾기.</t>
+  </si>
+  <si>
+    <t>Q040</t>
+  </si>
+  <si>
+    <t>학교로 가기.</t>
+  </si>
+  <si>
+    <t>Q041</t>
+  </si>
+  <si>
+    <t>비밀번호 찾기.</t>
+  </si>
+  <si>
+    <t>Q042</t>
+  </si>
+  <si>
+    <t>비밀번호 입력하기.</t>
+  </si>
+  <si>
+    <t>Q043</t>
+  </si>
+  <si>
+    <t>Q044</t>
+  </si>
+  <si>
+    <t>전기를 연결해 불 켜기.</t>
+  </si>
+  <si>
+    <t>Q045</t>
+  </si>
+  <si>
+    <t>귀신을 피해 숨기.</t>
+  </si>
+  <si>
+    <t>Q046</t>
+  </si>
+  <si>
+    <t>Q047</t>
+  </si>
+  <si>
+    <t>교실로 향하기.</t>
+  </si>
+  <si>
+    <t>Q048</t>
+  </si>
+  <si>
+    <t>귀신에게서 살아남기.</t>
+  </si>
+  <si>
+    <t>Q049</t>
+  </si>
+  <si>
+    <t>일기장 확인하기.</t>
   </si>
 </sst>
 </file>
@@ -2431,7 +2479,7 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="D81:J324" displayName="Table_4" name="Table_4" id="4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" headerRowCount="0" ref="D81:J302" displayName="Table_4" name="Table_4" id="4">
   <tableColumns count="7">
     <tableColumn name="Column1" id="1"/>
     <tableColumn name="Column2" id="2"/>
@@ -3601,6 +3649,17 @@
         <v>184</v>
       </c>
     </row>
+    <row r="82">
+      <c r="A82" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="C82" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D82" s="3" t="s">
+        <v>186</v>
+      </c>
+    </row>
   </sheetData>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -3621,10 +3680,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="2">
@@ -3635,7 +3694,7 @@
         <v>1.0</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="3">
@@ -3646,7 +3705,7 @@
         <v>2.0</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="4">
@@ -3657,7 +3716,7 @@
         <v>3.0</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="5">
@@ -3668,7 +3727,7 @@
         <v>4.0</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="6">
@@ -3679,7 +3738,7 @@
         <v>5.0</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="7">
@@ -3690,7 +3749,7 @@
         <v>6.0</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
     </row>
     <row r="8">
@@ -3701,7 +3760,7 @@
         <v>7.0</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
     </row>
     <row r="9">
@@ -3712,7 +3771,7 @@
         <v>8.0</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="10">
@@ -3723,7 +3782,7 @@
         <v>9.0</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
     </row>
     <row r="11">
@@ -3734,7 +3793,7 @@
         <v>10.0</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
     </row>
     <row r="12">
@@ -3745,7 +3804,7 @@
         <v>11.0</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
     </row>
     <row r="13">
@@ -3756,7 +3815,7 @@
         <v>12.0</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="14">
@@ -3767,7 +3826,7 @@
         <v>13.0</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
     </row>
   </sheetData>
@@ -3794,31 +3853,31 @@
         <v>0</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="2">
@@ -3832,20 +3891,20 @@
         <v>2001.0</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="E2" s="12">
         <v>2002.0</v>
       </c>
       <c r="F2" s="11" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G2" s="11" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H2" s="13"/>
       <c r="I2" s="14" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J2" s="14">
         <v>-1.0</v>
@@ -3863,20 +3922,20 @@
         <v>2002.0</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="E3" s="12">
         <v>2003.0</v>
       </c>
       <c r="F3" s="11" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G3" s="11" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H3" s="13"/>
       <c r="I3" s="14" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J3" s="14">
         <v>-1.0</v>
@@ -3894,20 +3953,20 @@
         <v>2003.0</v>
       </c>
       <c r="D4" s="11" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="E4" s="12">
         <v>2004.0</v>
       </c>
       <c r="F4" s="11" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G4" s="11" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H4" s="13"/>
       <c r="I4" s="14" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J4" s="14">
         <v>-1.0</v>
@@ -3925,20 +3984,20 @@
         <v>2004.0</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="E5" s="12">
         <v>2005.0</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="G5" s="11" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="H5" s="13"/>
       <c r="I5" s="14" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J5" s="14">
         <v>-1.0</v>
@@ -3956,20 +4015,20 @@
         <v>2005.0</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="E6" s="12">
         <v>2006.0</v>
       </c>
       <c r="F6" s="11" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G6" s="11" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H6" s="13"/>
       <c r="I6" s="14" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J6" s="14">
         <v>-1.0</v>
@@ -3987,20 +4046,20 @@
         <v>2006.0</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="E7" s="12">
         <v>2007.0</v>
       </c>
       <c r="F7" s="11" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="G7" s="11" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="H7" s="13"/>
       <c r="I7" s="14" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J7" s="14">
         <v>-1.0</v>
@@ -4018,20 +4077,20 @@
         <v>2007.0</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E8" s="12">
         <v>2008.0</v>
       </c>
       <c r="F8" s="11" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G8" s="11" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H8" s="13"/>
       <c r="I8" s="14" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J8" s="14">
         <v>-1.0</v>
@@ -4049,20 +4108,20 @@
         <v>2008.0</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="E9" s="12">
         <v>2009.0</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="G9" s="11" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="H9" s="13"/>
       <c r="I9" s="14" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J9" s="14">
         <v>-1.0</v>
@@ -4080,20 +4139,20 @@
         <v>2009.0</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="E10" s="12">
         <v>2010.0</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G10" s="11" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H10" s="13"/>
       <c r="I10" s="14" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J10" s="14">
         <v>-1.0</v>
@@ -4111,20 +4170,20 @@
         <v>2010.0</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="E11" s="12">
         <v>2011.0</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="G11" s="11" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="H11" s="13"/>
       <c r="I11" s="14" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J11" s="14">
         <v>-1.0</v>
@@ -4142,20 +4201,20 @@
         <v>2011.0</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="E12" s="12">
         <v>-1.0</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H12" s="13"/>
       <c r="I12" s="14" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J12" s="14">
         <v>-1.0</v>
@@ -4173,20 +4232,20 @@
         <v>3001.0</v>
       </c>
       <c r="D13" s="14" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="E13" s="16">
         <v>3002.0</v>
       </c>
       <c r="F13" s="14" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G13" s="11" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H13" s="13"/>
       <c r="I13" s="14" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J13" s="16">
         <v>4.0</v>
@@ -4204,20 +4263,20 @@
         <v>3002.0</v>
       </c>
       <c r="D14" s="14" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="E14" s="16">
         <v>3003.0</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="G14" s="11" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="H14" s="13"/>
       <c r="I14" s="14" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J14" s="16">
         <v>0.0</v>
@@ -4235,20 +4294,20 @@
         <v>3003.0</v>
       </c>
       <c r="D15" s="14" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="E15" s="16">
         <v>3004.0</v>
       </c>
       <c r="F15" s="14" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G15" s="11" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H15" s="13"/>
       <c r="I15" s="14" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J15" s="16">
         <v>2.0</v>
@@ -4266,20 +4325,20 @@
         <v>3004.0</v>
       </c>
       <c r="D16" s="14" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="E16" s="16">
         <v>3005.0</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="G16" s="11" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="H16" s="13"/>
       <c r="I16" s="14" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J16" s="16">
         <v>0.0</v>
@@ -4297,20 +4356,20 @@
         <v>3005.0</v>
       </c>
       <c r="D17" s="14" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="E17" s="16">
         <v>3006.0</v>
       </c>
       <c r="F17" s="14" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G17" s="11" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H17" s="13"/>
       <c r="I17" s="14" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J17" s="16">
         <v>2.0</v>
@@ -4328,20 +4387,20 @@
         <v>3006.0</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="E18" s="16">
         <v>3007.0</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="G18" s="11" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="H18" s="13"/>
       <c r="I18" s="14" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J18" s="16">
         <v>0.0</v>
@@ -4359,20 +4418,20 @@
         <v>3007.0</v>
       </c>
       <c r="D19" s="14" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="E19" s="16">
         <v>3008.0</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="G19" s="11" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="H19" s="13"/>
       <c r="I19" s="14" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J19" s="16">
         <v>1.0</v>
@@ -4398,20 +4457,20 @@
         <v>3008.0</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="E20" s="16">
         <v>3009.0</v>
       </c>
       <c r="F20" s="14" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G20" s="11" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H20" s="13"/>
       <c r="I20" s="14" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J20" s="16">
         <v>2.0</v>
@@ -4437,20 +4496,20 @@
         <v>3009.0</v>
       </c>
       <c r="D21" s="14" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="E21" s="16">
         <v>3010.0</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="G21" s="11" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="H21" s="13"/>
       <c r="I21" s="14" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="J21" s="16">
         <v>1.0</v>
@@ -4476,20 +4535,20 @@
         <v>3010.0</v>
       </c>
       <c r="D22" s="14" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="E22" s="16">
         <v>3011.0</v>
       </c>
       <c r="F22" s="14" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G22" s="11" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H22" s="13"/>
       <c r="I22" s="14" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J22" s="16">
         <v>2.0</v>
@@ -4515,20 +4574,20 @@
         <v>3011.0</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="E23" s="16">
         <v>3012.0</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="G23" s="11" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="H23" s="13"/>
       <c r="I23" s="14" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="J23" s="16">
         <v>1.0</v>
@@ -4554,19 +4613,19 @@
         <v>3012.0</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="E24" s="16">
         <v>3013.0</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="I24" s="14" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J24" s="3">
         <v>2.0</v>
@@ -4592,19 +4651,19 @@
         <v>3013.0</v>
       </c>
       <c r="D25" s="14" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="E25" s="16">
         <v>3014.0</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="I25" s="14" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="J25" s="3">
         <v>2.0</v>
@@ -4630,19 +4689,19 @@
         <v>3014.0</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="E26" s="16">
         <v>3015.0</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="I26" s="14" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J26" s="3">
         <v>2.0</v>
@@ -4660,20 +4719,20 @@
         <v>3015.0</v>
       </c>
       <c r="D27" s="14" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="E27" s="16">
         <v>3016.0</v>
       </c>
       <c r="F27" s="14" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G27" s="11" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H27" s="13"/>
       <c r="I27" s="16" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="J27" s="16">
         <v>0.0</v>
@@ -4691,22 +4750,22 @@
         <v>3016.0</v>
       </c>
       <c r="D28" s="14" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="E28" s="12">
         <v>-1.0</v>
       </c>
       <c r="F28" s="14" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G28" s="11" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H28" s="14" t="s">
+        <v>245</v>
+      </c>
+      <c r="I28" s="16" t="s">
         <v>243</v>
-      </c>
-      <c r="I28" s="16" t="s">
-        <v>241</v>
       </c>
       <c r="J28" s="16">
         <v>0.0</v>
@@ -4724,18 +4783,18 @@
         <v>4001.0</v>
       </c>
       <c r="D29" s="14" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="E29" s="12">
         <v>4002.0</v>
       </c>
       <c r="F29" s="14" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G29" s="21"/>
       <c r="H29" s="13"/>
       <c r="I29" s="16" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="J29" s="16">
         <v>-1.0</v>
@@ -4753,18 +4812,18 @@
         <v>4002.0</v>
       </c>
       <c r="D30" s="14" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="E30" s="12">
         <v>-1.0</v>
       </c>
       <c r="F30" s="14" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G30" s="21"/>
       <c r="H30" s="13"/>
       <c r="I30" s="16" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="J30" s="16">
         <v>-1.0</v>
@@ -4782,20 +4841,20 @@
         <v>5001.0</v>
       </c>
       <c r="D31" s="14" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="E31" s="3">
         <v>5002.0</v>
       </c>
       <c r="F31" s="14" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G31" s="11" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H31" s="13"/>
       <c r="I31" s="14" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J31" s="16">
         <v>5.0</v>
@@ -4813,20 +4872,20 @@
         <v>5002.0</v>
       </c>
       <c r="D32" s="14" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="E32" s="3">
         <v>5003.0</v>
       </c>
       <c r="F32" s="14" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G32" s="11" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H32" s="13"/>
       <c r="I32" s="14" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J32" s="16">
         <v>5.0</v>
@@ -4844,20 +4903,20 @@
         <v>5003.0</v>
       </c>
       <c r="D33" s="14" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="E33" s="3">
         <v>5004.0</v>
       </c>
       <c r="F33" s="14" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G33" s="11" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H33" s="13"/>
       <c r="I33" s="14" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J33" s="16">
         <v>0.0</v>
@@ -4875,20 +4934,20 @@
         <v>5004.0</v>
       </c>
       <c r="D34" s="14" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="E34" s="3">
         <v>5005.0</v>
       </c>
       <c r="F34" s="14" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G34" s="11" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H34" s="13"/>
       <c r="I34" s="14" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J34" s="16">
         <v>0.0</v>
@@ -4906,20 +4965,20 @@
         <v>5005.0</v>
       </c>
       <c r="D35" s="14" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="E35" s="3">
         <v>5006.0</v>
       </c>
       <c r="F35" s="14" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G35" s="11" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H35" s="13"/>
       <c r="I35" s="14" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J35" s="16">
         <v>0.0</v>
@@ -4937,20 +4996,20 @@
         <v>5006.0</v>
       </c>
       <c r="D36" s="14" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="E36" s="12">
         <v>-1.0</v>
       </c>
       <c r="F36" s="14" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G36" s="11" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H36" s="13"/>
       <c r="I36" s="16" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="J36" s="16">
         <v>-1.0</v>
@@ -4968,20 +5027,20 @@
         <v>6001.0</v>
       </c>
       <c r="D37" s="14" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="E37" s="16">
         <v>6002.0</v>
       </c>
       <c r="F37" s="14" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="G37" s="11" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="H37" s="13"/>
       <c r="I37" s="16" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="J37" s="16">
         <v>-1.0</v>
@@ -4999,20 +5058,20 @@
         <v>6002.0</v>
       </c>
       <c r="D38" s="14" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="E38" s="16">
         <v>6003.0</v>
       </c>
       <c r="F38" s="14" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G38" s="11" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H38" s="13"/>
       <c r="I38" s="14" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J38" s="16">
         <v>5.0</v>
@@ -5030,20 +5089,20 @@
         <v>6003.0</v>
       </c>
       <c r="D39" s="14" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="E39" s="16">
         <v>6004.0</v>
       </c>
       <c r="F39" s="14" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="G39" s="11" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="H39" s="13"/>
       <c r="I39" s="16" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="J39" s="16">
         <v>-1.0</v>
@@ -5061,20 +5120,20 @@
         <v>6004.0</v>
       </c>
       <c r="D40" s="14" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="E40" s="16">
         <v>6005.0</v>
       </c>
       <c r="F40" s="14" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G40" s="11" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H40" s="13"/>
       <c r="I40" s="14" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J40" s="16">
         <v>0.0</v>
@@ -5092,20 +5151,20 @@
         <v>6005.0</v>
       </c>
       <c r="D41" s="14" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="E41" s="16">
         <v>-1.0</v>
       </c>
       <c r="F41" s="14" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G41" s="11" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H41" s="13"/>
       <c r="I41" s="14" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J41" s="16">
         <v>0.0</v>
@@ -5123,20 +5182,20 @@
         <v>7001.0</v>
       </c>
       <c r="D42" s="14" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="E42" s="16">
         <v>-1.0</v>
       </c>
       <c r="F42" s="14" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G42" s="11" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H42" s="13"/>
       <c r="I42" s="14" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J42" s="16">
         <v>-1.0</v>
@@ -5154,20 +5213,20 @@
         <v>8001.0</v>
       </c>
       <c r="D43" s="14" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="E43" s="16">
         <v>8002.0</v>
       </c>
       <c r="F43" s="14" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G43" s="11" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H43" s="13"/>
       <c r="I43" s="14" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J43" s="16">
         <v>-1.0</v>
@@ -5185,20 +5244,20 @@
         <v>8002.0</v>
       </c>
       <c r="D44" s="14" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="E44" s="16">
         <v>8003.0</v>
       </c>
       <c r="F44" s="14" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G44" s="11" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H44" s="13"/>
       <c r="I44" s="14" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J44" s="16">
         <v>-1.0</v>
@@ -5216,20 +5275,20 @@
         <v>8003.0</v>
       </c>
       <c r="D45" s="14" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="E45" s="16">
         <v>8004.0</v>
       </c>
       <c r="F45" s="14" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G45" s="11" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H45" s="13"/>
       <c r="I45" s="14" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J45" s="16">
         <v>-1.0</v>
@@ -5247,20 +5306,20 @@
         <v>8004.0</v>
       </c>
       <c r="D46" s="14" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="E46" s="16">
         <v>8005.0</v>
       </c>
       <c r="F46" s="14" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="G46" s="11" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="H46" s="13"/>
       <c r="I46" s="16" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="J46" s="16">
         <v>-1.0</v>
@@ -5278,20 +5337,20 @@
         <v>8005.0</v>
       </c>
       <c r="D47" s="14" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="E47" s="16">
         <v>-1.0</v>
       </c>
       <c r="F47" s="14" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G47" s="11" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H47" s="13"/>
       <c r="I47" s="14" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J47" s="16">
         <v>-1.0</v>
@@ -5309,20 +5368,20 @@
         <v>9001.0</v>
       </c>
       <c r="D48" s="14" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="E48" s="16">
         <v>-1.0</v>
       </c>
       <c r="F48" s="14" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G48" s="11" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H48" s="13"/>
       <c r="I48" s="31" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J48" s="16">
         <v>-1.0</v>
@@ -5340,20 +5399,20 @@
         <v>10001.0</v>
       </c>
       <c r="D49" s="14" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="E49" s="16">
         <v>10002.0</v>
       </c>
       <c r="F49" s="14" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G49" s="11" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H49" s="13"/>
       <c r="I49" s="31" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J49" s="16">
         <v>4.0</v>
@@ -5371,20 +5430,20 @@
         <v>10002.0</v>
       </c>
       <c r="D50" s="14" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="E50" s="16">
         <v>10003.0</v>
       </c>
       <c r="F50" s="14" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G50" s="11" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H50" s="13"/>
       <c r="I50" s="31" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J50" s="16">
         <v>0.0</v>
@@ -5402,20 +5461,20 @@
         <v>10003.0</v>
       </c>
       <c r="D51" s="14" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="E51" s="16">
         <v>10004.0</v>
       </c>
       <c r="F51" s="14" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G51" s="11" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H51" s="13"/>
       <c r="I51" s="31" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J51" s="16">
         <v>0.0</v>
@@ -5433,20 +5492,20 @@
         <v>10004.0</v>
       </c>
       <c r="D52" s="14" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="E52" s="16">
         <v>-1.0</v>
       </c>
       <c r="F52" s="14" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G52" s="11" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H52" s="13"/>
       <c r="I52" s="16" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J52" s="16">
         <v>0.0</v>
@@ -5464,20 +5523,20 @@
         <v>11001.0</v>
       </c>
       <c r="D53" s="14" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="E53" s="16">
         <v>-1.0</v>
       </c>
       <c r="F53" s="14" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G53" s="11" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H53" s="13"/>
       <c r="I53" s="16" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J53" s="16">
         <v>-1.0</v>
@@ -5495,20 +5554,20 @@
         <v>12001.0</v>
       </c>
       <c r="D54" s="14" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="E54" s="16">
         <v>12002.0</v>
       </c>
       <c r="F54" s="14" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="G54" s="11" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="H54" s="13"/>
       <c r="I54" s="31" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="J54" s="16">
         <v>-1.0</v>
@@ -5526,20 +5585,20 @@
         <v>12002.0</v>
       </c>
       <c r="D55" s="14" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="E55" s="16">
         <v>12003.0</v>
       </c>
       <c r="F55" s="14" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G55" s="11" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H55" s="13"/>
       <c r="I55" s="16" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J55" s="16">
         <v>0.0</v>
@@ -5557,20 +5616,20 @@
         <v>12003.0</v>
       </c>
       <c r="D56" s="14" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="E56" s="16">
         <v>12004.0</v>
       </c>
       <c r="F56" s="14" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="G56" s="11" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="H56" s="13"/>
       <c r="I56" s="31" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="J56" s="16">
         <v>-1.0</v>
@@ -5588,20 +5647,20 @@
         <v>12004.0</v>
       </c>
       <c r="D57" s="14" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="E57" s="16">
         <v>12005.0</v>
       </c>
       <c r="F57" s="14" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G57" s="11" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H57" s="13"/>
       <c r="I57" s="31" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J57" s="16">
         <v>5.0</v>
@@ -5619,20 +5678,20 @@
         <v>12005.0</v>
       </c>
       <c r="D58" s="14" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="E58" s="16">
         <v>12006.0</v>
       </c>
       <c r="F58" s="14" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G58" s="11" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H58" s="13"/>
       <c r="I58" s="16" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J58" s="16">
         <v>0.0</v>
@@ -5650,20 +5709,20 @@
         <v>12006.0</v>
       </c>
       <c r="D59" s="14" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="E59" s="16">
         <v>12007.0</v>
       </c>
       <c r="F59" s="14" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="G59" s="11" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="H59" s="13"/>
       <c r="I59" s="31" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="J59" s="16">
         <v>-1.0</v>
@@ -5681,20 +5740,20 @@
         <v>12007.0</v>
       </c>
       <c r="D60" s="14" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="E60" s="16">
         <v>12008.0</v>
       </c>
       <c r="F60" s="14" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G60" s="11" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H60" s="13"/>
       <c r="I60" s="16" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J60" s="16">
         <v>0.0</v>
@@ -5712,20 +5771,20 @@
         <v>12008.0</v>
       </c>
       <c r="D61" s="14" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="E61" s="16">
         <v>-1.0</v>
       </c>
       <c r="F61" s="14" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G61" s="11" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H61" s="13"/>
       <c r="I61" s="31" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="J61" s="16">
         <v>0.0</v>
@@ -5743,20 +5802,20 @@
         <v>13001.0</v>
       </c>
       <c r="D62" s="14" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E62" s="16">
         <v>-1.0</v>
       </c>
       <c r="F62" s="14" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G62" s="11" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H62" s="13"/>
       <c r="I62" s="31" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J62" s="16">
         <v>-1.0</v>
@@ -5774,20 +5833,20 @@
         <v>14001.0</v>
       </c>
       <c r="D63" s="14" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="E63" s="16">
         <v>14002.0</v>
       </c>
       <c r="F63" s="14" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G63" s="11" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H63" s="13"/>
       <c r="I63" s="31" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J63" s="16">
         <v>-1.0</v>
@@ -5805,20 +5864,20 @@
         <v>14002.0</v>
       </c>
       <c r="D64" s="14" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="E64" s="16">
         <v>14003.0</v>
       </c>
       <c r="F64" s="14" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G64" s="11" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H64" s="13"/>
       <c r="I64" s="31" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J64" s="16">
         <v>-1.0</v>
@@ -5836,20 +5895,20 @@
         <v>14003.0</v>
       </c>
       <c r="D65" s="14" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="E65" s="16">
         <v>-1.0</v>
       </c>
       <c r="F65" s="14" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G65" s="11" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H65" s="13"/>
       <c r="I65" s="31" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J65" s="16">
         <v>-1.0</v>
@@ -5867,20 +5926,20 @@
         <v>15001.0</v>
       </c>
       <c r="D66" s="14" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="E66" s="16">
         <v>-1.0</v>
       </c>
       <c r="F66" s="14" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G66" s="11" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H66" s="13"/>
       <c r="I66" s="31" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J66" s="16">
         <v>-1.0</v>
@@ -5898,20 +5957,20 @@
         <v>16001.0</v>
       </c>
       <c r="D67" s="14" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="E67" s="16">
         <v>16002.0</v>
       </c>
       <c r="F67" s="14" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G67" s="11" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H67" s="13"/>
       <c r="I67" s="31" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J67" s="16">
         <v>0.0</v>
@@ -5929,20 +5988,20 @@
         <v>16002.0</v>
       </c>
       <c r="D68" s="14" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="E68" s="16">
         <v>-1.0</v>
       </c>
       <c r="F68" s="14" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G68" s="11" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H68" s="13"/>
       <c r="I68" s="31" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J68" s="16">
         <v>5.0</v>
@@ -5960,20 +6019,20 @@
         <v>17001.0</v>
       </c>
       <c r="D69" s="14" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="E69" s="16">
         <v>17002.0</v>
       </c>
       <c r="F69" s="14" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G69" s="11" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H69" s="13"/>
       <c r="I69" s="31" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J69" s="16">
         <v>0.0</v>
@@ -5991,20 +6050,20 @@
         <v>17002.0</v>
       </c>
       <c r="D70" s="14" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="E70" s="16">
         <v>17003.0</v>
       </c>
       <c r="F70" s="14" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G70" s="11" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H70" s="13"/>
       <c r="I70" s="31" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J70" s="16">
         <v>6.0</v>
@@ -6022,20 +6081,20 @@
         <v>17003.0</v>
       </c>
       <c r="D71" s="14" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="E71" s="16">
         <v>17004.0</v>
       </c>
       <c r="F71" s="14" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G71" s="11" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H71" s="13"/>
       <c r="I71" s="31" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J71" s="16">
         <v>5.0</v>
@@ -6053,20 +6112,20 @@
         <v>17004.0</v>
       </c>
       <c r="D72" s="14" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="E72" s="16">
         <v>-1.0</v>
       </c>
       <c r="F72" s="14" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G72" s="11" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H72" s="13"/>
       <c r="I72" s="31" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J72" s="16">
         <v>0.0</v>
@@ -6084,20 +6143,20 @@
         <v>18001.0</v>
       </c>
       <c r="D73" s="14" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="E73" s="16">
         <v>18002.0</v>
       </c>
       <c r="F73" s="14" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G73" s="11" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H73" s="13"/>
       <c r="I73" s="31" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J73" s="16">
         <v>5.0</v>
@@ -6115,19 +6174,19 @@
         <v>18002.0</v>
       </c>
       <c r="D74" s="33" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="E74" s="3">
         <v>18003.0</v>
       </c>
       <c r="F74" s="14" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G74" s="11" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="I74" s="31" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J74" s="16">
         <v>0.0</v>
@@ -6144,19 +6203,19 @@
         <v>18003.0</v>
       </c>
       <c r="D75" s="33" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="E75" s="3">
         <v>-1.0</v>
       </c>
       <c r="F75" s="14" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G75" s="11" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="I75" s="31" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="J75" s="16">
         <v>-1.0</v>
@@ -6173,19 +6232,19 @@
         <v>19001.0</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="E76" s="16">
         <v>19002.0</v>
       </c>
       <c r="F76" s="14" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G76" s="11" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="I76" s="31" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J76" s="16">
         <v>6.0</v>
@@ -6202,19 +6261,19 @@
         <v>19002.0</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="E77" s="3">
         <v>19003.0</v>
       </c>
       <c r="F77" s="14" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G77" s="11" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="I77" s="31" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J77" s="16">
         <v>5.0</v>
@@ -6231,19 +6290,19 @@
         <v>19003.0</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="E78" s="3">
         <v>19004.0</v>
       </c>
       <c r="F78" s="14" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G78" s="11" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="I78" s="31" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J78" s="3">
         <v>2.0</v>
@@ -6260,19 +6319,19 @@
         <v>19004.0</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="E79" s="3">
         <v>19005.0</v>
       </c>
       <c r="F79" s="3" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G79" s="3" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J79" s="3">
         <v>2.0</v>
@@ -6289,19 +6348,19 @@
         <v>19005.0</v>
       </c>
       <c r="D80" s="3" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="E80" s="3">
         <v>-1.0</v>
       </c>
       <c r="F80" s="3" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G80" s="3" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J80" s="3">
         <v>2.0</v>
@@ -6318,20 +6377,20 @@
         <v>20001.0</v>
       </c>
       <c r="D81" s="36" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="E81" s="28">
         <v>20002.0</v>
       </c>
       <c r="F81" s="36" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G81" s="37" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H81" s="36"/>
       <c r="I81" s="38" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J81" s="28">
         <v>0.0</v>
@@ -6348,20 +6407,20 @@
         <v>20002.0</v>
       </c>
       <c r="D82" s="39" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="E82" s="19">
         <v>20003.0</v>
       </c>
       <c r="F82" s="39" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G82" s="37" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H82" s="39"/>
       <c r="I82" s="38" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J82" s="19">
         <v>0.0</v>
@@ -6378,20 +6437,20 @@
         <v>20003.0</v>
       </c>
       <c r="D83" s="36" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="E83" s="28">
         <v>20004.0</v>
       </c>
       <c r="F83" s="36" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G83" s="37" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H83" s="36"/>
       <c r="I83" s="38" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J83" s="28">
         <v>0.0</v>
@@ -6408,20 +6467,20 @@
         <v>20004.0</v>
       </c>
       <c r="D84" s="39" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="E84" s="19">
         <v>20005.0</v>
       </c>
       <c r="F84" s="39" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G84" s="37" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H84" s="39"/>
       <c r="I84" s="38" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J84" s="26">
         <v>2.0</v>
@@ -6438,20 +6497,20 @@
         <v>20005.0</v>
       </c>
       <c r="D85" s="36" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="E85" s="28">
         <v>20006.0</v>
       </c>
       <c r="F85" s="36" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G85" s="37" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H85" s="36"/>
       <c r="I85" s="38" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J85" s="40">
         <v>2.0</v>
@@ -6468,20 +6527,20 @@
         <v>20006.0</v>
       </c>
       <c r="D86" s="39" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="E86" s="19">
         <v>-1.0</v>
       </c>
       <c r="F86" s="39" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G86" s="37" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H86" s="39"/>
       <c r="I86" s="38" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J86" s="19">
         <v>0.0</v>
@@ -6498,20 +6557,20 @@
         <v>21001.0</v>
       </c>
       <c r="D87" s="36" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="E87" s="28">
         <v>-1.0</v>
       </c>
       <c r="F87" s="36" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G87" s="37" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H87" s="36"/>
       <c r="I87" s="38" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J87" s="40">
         <v>-1.0</v>
@@ -6528,20 +6587,20 @@
         <v>22001.0</v>
       </c>
       <c r="D88" s="39" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="E88" s="19">
         <v>22002.0</v>
       </c>
       <c r="F88" s="39" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G88" s="37" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H88" s="39"/>
       <c r="I88" s="38" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J88" s="19">
         <v>0.0</v>
@@ -6558,20 +6617,20 @@
         <v>22002.0</v>
       </c>
       <c r="D89" s="36" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="E89" s="28">
         <v>22003.0</v>
       </c>
       <c r="F89" s="36" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G89" s="37" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H89" s="36"/>
       <c r="I89" s="38" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J89" s="40">
         <v>2.0</v>
@@ -6588,20 +6647,20 @@
         <v>22003.0</v>
       </c>
       <c r="D90" s="39" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="E90" s="19">
         <v>22004.0</v>
       </c>
       <c r="F90" s="39" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G90" s="37" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H90" s="39"/>
       <c r="I90" s="38" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J90" s="26">
         <v>2.0</v>
@@ -6618,20 +6677,20 @@
         <v>22004.0</v>
       </c>
       <c r="D91" s="36" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="E91" s="28">
         <v>22005.0</v>
       </c>
       <c r="F91" s="36" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G91" s="37" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H91" s="36"/>
       <c r="I91" s="38" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J91" s="40">
         <v>2.0</v>
@@ -6648,20 +6707,20 @@
         <v>22005.0</v>
       </c>
       <c r="D92" s="39" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="E92" s="26">
         <v>-1.0</v>
       </c>
       <c r="F92" s="39" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G92" s="37" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H92" s="39"/>
       <c r="I92" s="38" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J92" s="26">
         <v>1.0</v>
@@ -6678,20 +6737,20 @@
         <v>23001.0</v>
       </c>
       <c r="D93" s="36" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="E93" s="5">
         <v>23002.0</v>
       </c>
       <c r="F93" s="36" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G93" s="37" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H93" s="36"/>
       <c r="I93" s="38" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J93" s="28">
         <v>0.0</v>
@@ -6708,20 +6767,20 @@
         <v>23002.0</v>
       </c>
       <c r="D94" s="39" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="E94" s="5">
         <v>23003.0</v>
       </c>
       <c r="F94" s="39" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G94" s="37" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H94" s="39"/>
       <c r="I94" s="38" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J94" s="19">
         <v>0.0</v>
@@ -6738,20 +6797,20 @@
         <v>23003.0</v>
       </c>
       <c r="D95" s="36" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="E95" s="5">
         <v>23004.0</v>
       </c>
       <c r="F95" s="36" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G95" s="37" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H95" s="36"/>
       <c r="I95" s="38" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J95" s="28">
         <v>0.0</v>
@@ -6768,20 +6827,20 @@
         <v>23004.0</v>
       </c>
       <c r="D96" s="39" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="E96" s="19">
         <v>-1.0</v>
       </c>
       <c r="F96" s="39" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G96" s="37" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H96" s="39"/>
       <c r="I96" s="38" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J96" s="19">
         <v>0.0</v>
@@ -6798,20 +6857,20 @@
         <v>24001.0</v>
       </c>
       <c r="D97" s="36" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="E97" s="28">
         <v>24002.0</v>
       </c>
       <c r="F97" s="36" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G97" s="37" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H97" s="36"/>
       <c r="I97" s="38" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J97" s="40">
         <v>5.0</v>
@@ -6828,20 +6887,20 @@
         <v>24002.0</v>
       </c>
       <c r="D98" s="39" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="E98" s="19">
         <v>24003.0</v>
       </c>
       <c r="F98" s="39" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G98" s="37" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H98" s="39"/>
       <c r="I98" s="38" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J98" s="19">
         <v>0.0</v>
@@ -6858,20 +6917,20 @@
         <v>24003.0</v>
       </c>
       <c r="D99" s="36" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="E99" s="28">
         <v>24004.0</v>
       </c>
       <c r="F99" s="36" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G99" s="37" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H99" s="36"/>
       <c r="I99" s="38" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J99" s="28">
         <v>0.0</v>
@@ -6888,20 +6947,20 @@
         <v>24004.0</v>
       </c>
       <c r="D100" s="39" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="E100" s="19">
         <v>24005.0</v>
       </c>
       <c r="F100" s="39" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G100" s="37" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H100" s="39"/>
       <c r="I100" s="38" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J100" s="19">
         <v>0.0</v>
@@ -6918,20 +6977,20 @@
         <v>24005.0</v>
       </c>
       <c r="D101" s="36" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="E101" s="28">
         <v>24006.0</v>
       </c>
       <c r="F101" s="36" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G101" s="37" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H101" s="36"/>
       <c r="I101" s="38" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J101" s="28">
         <v>0.0</v>
@@ -6948,20 +7007,20 @@
         <v>24006.0</v>
       </c>
       <c r="D102" s="39" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="E102" s="19">
         <v>24007.0</v>
       </c>
       <c r="F102" s="39" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G102" s="37" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H102" s="39"/>
       <c r="I102" s="38" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J102" s="19">
         <v>0.0</v>
@@ -6978,20 +7037,20 @@
         <v>24007.0</v>
       </c>
       <c r="D103" s="36" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="E103" s="28">
         <v>24008.0</v>
       </c>
       <c r="F103" s="36" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G103" s="37" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H103" s="36"/>
       <c r="I103" s="38" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J103" s="28">
         <v>0.0</v>
@@ -7008,20 +7067,20 @@
         <v>24008.0</v>
       </c>
       <c r="D104" s="39" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="E104" s="19">
         <v>-1.0</v>
       </c>
       <c r="F104" s="39" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G104" s="37" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H104" s="39"/>
       <c r="I104" s="38" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J104" s="19">
         <v>0.0</v>
@@ -7038,20 +7097,20 @@
         <v>25001.0</v>
       </c>
       <c r="D105" s="36" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="E105" s="28">
         <v>25002.0</v>
       </c>
       <c r="F105" s="36" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="G105" s="36" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="H105" s="36"/>
       <c r="I105" s="36" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="J105" s="40">
         <v>-1.0</v>
@@ -7068,20 +7127,20 @@
         <v>25002.0</v>
       </c>
       <c r="D106" s="39" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="E106" s="19">
         <v>25003.0</v>
       </c>
       <c r="F106" s="39" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G106" s="39" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H106" s="39"/>
       <c r="I106" s="38" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J106" s="26">
         <v>5.0</v>
@@ -7098,20 +7157,20 @@
         <v>25003.0</v>
       </c>
       <c r="D107" s="36" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="E107" s="28">
         <v>25004.0</v>
       </c>
       <c r="F107" s="36" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="G107" s="36" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="H107" s="36"/>
       <c r="I107" s="36" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="J107" s="40">
         <v>-1.0</v>
@@ -7128,20 +7187,20 @@
         <v>25004.0</v>
       </c>
       <c r="D108" s="39" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="E108" s="19">
         <v>25005.0</v>
       </c>
       <c r="F108" s="39" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G108" s="39" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H108" s="39"/>
       <c r="I108" s="38" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J108" s="26">
         <v>5.0</v>
@@ -7158,20 +7217,20 @@
         <v>25005.0</v>
       </c>
       <c r="D109" s="36" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="E109" s="28">
         <v>25006.0</v>
       </c>
       <c r="F109" s="36" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G109" s="36" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H109" s="36"/>
       <c r="I109" s="38" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J109" s="40">
         <v>5.0</v>
@@ -7188,20 +7247,20 @@
         <v>25006.0</v>
       </c>
       <c r="D110" s="39" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="E110" s="19">
         <v>-1.0</v>
       </c>
       <c r="F110" s="39" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G110" s="39" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H110" s="39"/>
       <c r="I110" s="38" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J110" s="26">
         <v>5.0</v>
@@ -7218,20 +7277,20 @@
         <v>26001.0</v>
       </c>
       <c r="D111" s="36" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="E111" s="28">
         <v>-1.0</v>
       </c>
       <c r="F111" s="36" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G111" s="36" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H111" s="36"/>
       <c r="I111" s="36" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="J111" s="40">
         <v>-1.0</v>
@@ -7248,20 +7307,20 @@
         <v>27001.0</v>
       </c>
       <c r="D112" s="39" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="E112" s="19">
         <v>27002.0</v>
       </c>
       <c r="F112" s="39" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G112" s="39" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H112" s="39"/>
       <c r="I112" s="38" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J112" s="26">
         <v>2.0</v>
@@ -7278,20 +7337,20 @@
         <v>27002.0</v>
       </c>
       <c r="D113" s="36" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="E113" s="28">
         <v>27003.0</v>
       </c>
       <c r="F113" s="36" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G113" s="36" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H113" s="36"/>
       <c r="I113" s="38" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J113" s="40">
         <v>2.0</v>
@@ -7308,20 +7367,20 @@
         <v>27003.0</v>
       </c>
       <c r="D114" s="39" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="E114" s="19">
         <v>-1.0</v>
       </c>
       <c r="F114" s="39" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G114" s="39" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H114" s="39"/>
       <c r="I114" s="38" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J114" s="26">
         <v>2.0</v>
@@ -7338,20 +7397,20 @@
         <v>28001.0</v>
       </c>
       <c r="D115" s="36" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="E115" s="28">
         <v>28002.0</v>
       </c>
       <c r="F115" s="36" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="G115" s="36" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="H115" s="36"/>
       <c r="I115" s="36" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="J115" s="40">
         <v>-1.0</v>
@@ -7368,20 +7427,20 @@
         <v>28002.0</v>
       </c>
       <c r="D116" s="39" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="E116" s="19">
         <v>28003.0</v>
       </c>
       <c r="F116" s="39" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="G116" s="39" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="H116" s="39"/>
       <c r="I116" s="39" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="J116" s="40">
         <v>-1.0</v>
@@ -7398,20 +7457,20 @@
         <v>28003.0</v>
       </c>
       <c r="D117" s="36" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="E117" s="28">
         <v>-1.0</v>
       </c>
       <c r="F117" s="36" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G117" s="36" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H117" s="36"/>
       <c r="I117" s="38" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J117" s="40">
         <v>2.0</v>
@@ -7428,20 +7487,20 @@
         <v>29001.0</v>
       </c>
       <c r="D118" s="39" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="E118" s="19">
         <v>-1.0</v>
       </c>
       <c r="F118" s="39" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G118" s="39" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H118" s="39"/>
       <c r="I118" s="38" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J118" s="26">
         <v>-1.0</v>
@@ -7458,20 +7517,20 @@
         <v>30001.0</v>
       </c>
       <c r="D119" s="36" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="E119" s="28">
         <v>30002.0</v>
       </c>
       <c r="F119" s="36" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G119" s="36" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H119" s="36"/>
       <c r="I119" s="38" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J119" s="40">
         <v>2.0</v>
@@ -7488,20 +7547,20 @@
         <v>30002.0</v>
       </c>
       <c r="D120" s="39" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="E120" s="19">
         <v>30003.0</v>
       </c>
       <c r="F120" s="39" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G120" s="39" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H120" s="39"/>
       <c r="I120" s="38" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J120" s="26">
         <v>1.0</v>
@@ -7518,20 +7577,20 @@
         <v>30003.0</v>
       </c>
       <c r="D121" s="36" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="E121" s="28">
         <v>-1.0</v>
       </c>
       <c r="F121" s="36" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G121" s="36" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H121" s="36"/>
       <c r="I121" s="38" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J121" s="40">
         <v>2.0</v>
@@ -7548,20 +7607,20 @@
         <v>31001.0</v>
       </c>
       <c r="D122" s="39" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="E122" s="19">
         <v>31002.0</v>
       </c>
       <c r="F122" s="39" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G122" s="39" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H122" s="39"/>
       <c r="I122" s="38" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J122" s="26">
         <v>5.0</v>
@@ -7578,20 +7637,20 @@
         <v>31002.0</v>
       </c>
       <c r="D123" s="36" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="E123" s="28">
         <v>-1.0</v>
       </c>
       <c r="F123" s="36" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G123" s="36" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H123" s="36"/>
       <c r="I123" s="38" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J123" s="40">
         <v>6.0</v>
@@ -7608,20 +7667,20 @@
         <v>32001.0</v>
       </c>
       <c r="D124" s="39" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="E124" s="19">
         <v>32002.0</v>
       </c>
       <c r="F124" s="39" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="G124" s="39" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="H124" s="39"/>
       <c r="I124" s="39" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="J124" s="40">
         <v>-1.0</v>
@@ -7638,20 +7697,20 @@
         <v>32002.0</v>
       </c>
       <c r="D125" s="36" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="E125" s="28">
         <v>32003.0</v>
       </c>
       <c r="F125" s="36" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="G125" s="36" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="H125" s="36"/>
       <c r="I125" s="36" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="J125" s="40">
         <v>-1.0</v>
@@ -7668,20 +7727,20 @@
         <v>32003.0</v>
       </c>
       <c r="D126" s="39" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="E126" s="19">
         <v>32004.0</v>
       </c>
       <c r="F126" s="39" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="G126" s="39" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="H126" s="39"/>
       <c r="I126" s="39" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="J126" s="40">
         <v>-1.0</v>
@@ -7698,20 +7757,20 @@
         <v>32004.0</v>
       </c>
       <c r="D127" s="36" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="E127" s="28">
         <v>32005.0</v>
       </c>
       <c r="F127" s="36" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G127" s="36" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H127" s="36"/>
       <c r="I127" s="38" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J127" s="40">
         <v>5.0</v>
@@ -7728,20 +7787,20 @@
         <v>32005.0</v>
       </c>
       <c r="D128" s="39" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="E128" s="19">
         <v>32006.0</v>
       </c>
       <c r="F128" s="39" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G128" s="39" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H128" s="39"/>
       <c r="I128" s="38" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J128" s="19">
         <v>0.0</v>
@@ -7758,20 +7817,20 @@
         <v>32006.0</v>
       </c>
       <c r="D129" s="36" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="E129" s="28">
         <v>-1.0</v>
       </c>
       <c r="F129" s="36" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G129" s="36" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H129" s="36"/>
       <c r="I129" s="38" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J129" s="28">
         <v>0.0</v>
@@ -7788,20 +7847,20 @@
         <v>33001.0</v>
       </c>
       <c r="D130" s="39" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="E130" s="19">
         <v>33002.0</v>
       </c>
       <c r="F130" s="39" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G130" s="39" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H130" s="39"/>
       <c r="I130" s="38" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J130" s="19">
         <v>0.0</v>
@@ -7818,20 +7877,20 @@
         <v>33002.0</v>
       </c>
       <c r="D131" s="36" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="E131" s="28">
         <v>-1.0</v>
       </c>
       <c r="F131" s="36" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G131" s="36" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H131" s="36"/>
       <c r="I131" s="38" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J131" s="28">
         <v>0.0</v>
@@ -7848,20 +7907,20 @@
         <v>34001.0</v>
       </c>
       <c r="D132" s="39" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="E132" s="19">
         <v>34002.0</v>
       </c>
       <c r="F132" s="39" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="G132" s="39" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="H132" s="39"/>
       <c r="I132" s="39" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="J132" s="40">
         <v>-1.0</v>
@@ -7878,20 +7937,20 @@
         <v>34002.0</v>
       </c>
       <c r="D133" s="36" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="E133" s="28">
         <v>34003.0</v>
       </c>
       <c r="F133" s="36" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="G133" s="36" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="H133" s="36"/>
       <c r="I133" s="36" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="J133" s="40">
         <v>-1.0</v>
@@ -7908,20 +7967,20 @@
         <v>34003.0</v>
       </c>
       <c r="D134" s="39" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="E134" s="19">
         <v>-1.0</v>
       </c>
       <c r="F134" s="39" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G134" s="39" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H134" s="39"/>
       <c r="I134" s="38" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J134" s="19">
         <v>0.0</v>
@@ -7938,20 +7997,20 @@
         <v>35001.0</v>
       </c>
       <c r="D135" s="36" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="E135" s="28">
         <v>-1.0</v>
       </c>
       <c r="F135" s="36" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G135" s="36" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H135" s="36"/>
       <c r="I135" s="38" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J135" s="40">
         <v>-1.0</v>
@@ -7968,20 +8027,20 @@
         <v>36001.0</v>
       </c>
       <c r="D136" s="39" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="E136" s="19">
         <v>36002.0</v>
       </c>
       <c r="F136" s="39" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G136" s="39" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H136" s="39"/>
       <c r="I136" s="38" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J136" s="26">
         <v>1.0</v>
@@ -7998,20 +8057,20 @@
         <v>36002.0</v>
       </c>
       <c r="D137" s="36" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="E137" s="28">
         <v>36003.0</v>
       </c>
       <c r="F137" s="36" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G137" s="36" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H137" s="36"/>
       <c r="I137" s="38" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J137" s="40">
         <v>2.0</v>
@@ -8028,20 +8087,20 @@
         <v>36003.0</v>
       </c>
       <c r="D138" s="39" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="E138" s="19">
         <v>36004.0</v>
       </c>
       <c r="F138" s="39" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G138" s="39" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H138" s="39"/>
       <c r="I138" s="38" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J138" s="26">
         <v>2.0</v>
@@ -8058,20 +8117,20 @@
         <v>36004.0</v>
       </c>
       <c r="D139" s="36" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="E139" s="28">
         <v>-1.0</v>
       </c>
       <c r="F139" s="36" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G139" s="36" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H139" s="36"/>
       <c r="I139" s="38" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J139" s="28">
         <v>0.0</v>
@@ -8088,20 +8147,20 @@
         <v>37001.0</v>
       </c>
       <c r="D140" s="39" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="E140" s="19">
         <v>37002.0</v>
       </c>
       <c r="F140" s="39" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G140" s="39" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H140" s="39"/>
       <c r="I140" s="38" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J140" s="26">
         <v>5.0</v>
@@ -8118,20 +8177,20 @@
         <v>37002.0</v>
       </c>
       <c r="D141" s="36" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="E141" s="28">
         <v>37003.0</v>
       </c>
       <c r="F141" s="36" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G141" s="36" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H141" s="36"/>
       <c r="I141" s="38" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J141" s="40">
         <v>6.0</v>
@@ -8148,20 +8207,20 @@
         <v>37003.0</v>
       </c>
       <c r="D142" s="39" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="E142" s="19">
         <v>-1.0</v>
       </c>
       <c r="F142" s="39" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G142" s="39" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H142" s="39"/>
       <c r="I142" s="38" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J142" s="19">
         <v>0.0</v>
@@ -8178,20 +8237,20 @@
         <v>38001.0</v>
       </c>
       <c r="D143" s="36" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="E143" s="28">
         <v>38002.0</v>
       </c>
       <c r="F143" s="36" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G143" s="36" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H143" s="36"/>
       <c r="I143" s="38" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J143" s="40">
         <v>6.0</v>
@@ -8208,20 +8267,20 @@
         <v>38002.0</v>
       </c>
       <c r="D144" s="39" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="E144" s="19">
         <v>38003.0</v>
       </c>
       <c r="F144" s="39" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G144" s="39" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H144" s="39"/>
       <c r="I144" s="38" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J144" s="26">
         <v>5.0</v>
@@ -8238,20 +8297,20 @@
         <v>38003.0</v>
       </c>
       <c r="D145" s="36" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="E145" s="28">
         <v>38004.0</v>
       </c>
       <c r="F145" s="36" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G145" s="36" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H145" s="36"/>
       <c r="I145" s="38" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J145" s="28">
         <v>0.0</v>
@@ -8268,20 +8327,20 @@
         <v>38004.0</v>
       </c>
       <c r="D146" s="39" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="E146" s="19">
         <v>-1.0</v>
       </c>
       <c r="F146" s="39" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G146" s="39" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H146" s="39"/>
       <c r="I146" s="38" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J146" s="19">
         <v>0.0</v>
@@ -8298,20 +8357,20 @@
         <v>39001.0</v>
       </c>
       <c r="D147" s="42" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="E147" s="28">
         <v>-1.0</v>
       </c>
       <c r="F147" s="36" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G147" s="36" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H147" s="36"/>
       <c r="I147" s="38" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J147" s="28">
         <v>0.0</v>
@@ -8328,20 +8387,20 @@
         <v>40001.0</v>
       </c>
       <c r="D148" s="42" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="E148" s="3">
         <v>40002.0</v>
       </c>
       <c r="F148" s="36" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G148" s="36" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H148" s="36"/>
       <c r="I148" s="38" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J148" s="40">
         <v>6.0</v>
@@ -8358,20 +8417,20 @@
         <v>40002.0</v>
       </c>
       <c r="D149" s="42" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="E149" s="40">
         <v>-1.0</v>
       </c>
       <c r="F149" s="36" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G149" s="36" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H149" s="36"/>
       <c r="I149" s="38" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J149" s="40">
         <v>5.0</v>
@@ -8388,20 +8447,20 @@
         <v>41001.0</v>
       </c>
       <c r="D150" s="42" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="E150" s="40">
         <v>-1.0</v>
       </c>
       <c r="F150" s="36" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G150" s="36" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H150" s="36"/>
       <c r="I150" s="43" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="J150" s="40">
         <v>-1.0</v>
@@ -8418,20 +8477,20 @@
         <v>42001.0</v>
       </c>
       <c r="D151" s="42" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="E151" s="40">
         <v>42002.0</v>
       </c>
       <c r="F151" s="42" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G151" s="42" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H151" s="36"/>
       <c r="I151" s="43" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J151" s="40">
         <v>0.0</v>
@@ -8448,20 +8507,20 @@
         <v>42002.0</v>
       </c>
       <c r="D152" s="42" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="E152" s="40">
         <v>-1.0</v>
       </c>
       <c r="F152" s="42" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G152" s="42" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H152" s="36"/>
       <c r="I152" s="43" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J152" s="40">
         <v>0.0</v>
@@ -8478,20 +8537,20 @@
         <v>43001.0</v>
       </c>
       <c r="D153" s="42" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="E153" s="40">
         <v>43002.0</v>
       </c>
       <c r="F153" s="42" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G153" s="42" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H153" s="36"/>
       <c r="I153" s="43" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J153" s="40">
         <v>6.0</v>
@@ -8508,20 +8567,20 @@
         <v>43002.0</v>
       </c>
       <c r="D154" s="42" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="E154" s="40">
         <v>43003.0</v>
       </c>
       <c r="F154" s="42" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G154" s="42" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H154" s="36"/>
       <c r="I154" s="43" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J154" s="40">
         <v>5.0</v>
@@ -8538,20 +8597,20 @@
         <v>43003.0</v>
       </c>
       <c r="D155" s="42" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="E155" s="40">
         <v>-1.0</v>
       </c>
       <c r="F155" s="42" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G155" s="42" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H155" s="36"/>
       <c r="I155" s="43" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J155" s="40">
         <v>5.0</v>
@@ -8568,20 +8627,20 @@
         <v>44001.0</v>
       </c>
       <c r="D156" s="3" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="E156" s="40">
         <v>44002.0</v>
       </c>
       <c r="F156" s="42" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G156" s="42" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H156" s="36"/>
       <c r="I156" s="43" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J156" s="19">
         <v>0.0</v>
@@ -8598,20 +8657,20 @@
         <v>44002.0</v>
       </c>
       <c r="D157" s="42" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="E157" s="40">
         <v>44003.0</v>
       </c>
       <c r="F157" s="42" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G157" s="42" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H157" s="36"/>
       <c r="I157" s="43" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J157" s="28">
         <v>0.0</v>
@@ -8628,20 +8687,20 @@
         <v>44003.0</v>
       </c>
       <c r="D158" s="42" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="E158" s="40">
         <v>44004.0</v>
       </c>
       <c r="F158" s="42" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G158" s="42" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H158" s="36"/>
       <c r="I158" s="43" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J158" s="19">
         <v>0.0</v>
@@ -8658,20 +8717,20 @@
         <v>44004.0</v>
       </c>
       <c r="D159" s="42" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="E159" s="40">
         <v>-1.0</v>
       </c>
       <c r="F159" s="42" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G159" s="42" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H159" s="36"/>
       <c r="I159" s="43" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J159" s="28">
         <v>0.0</v>
@@ -8688,20 +8747,20 @@
         <v>45001.0</v>
       </c>
       <c r="D160" s="42" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="E160" s="40">
         <v>45002.0</v>
       </c>
       <c r="F160" s="42" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G160" s="42" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H160" s="36"/>
       <c r="I160" s="43" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J160" s="19">
         <v>0.0</v>
@@ -8718,20 +8777,20 @@
         <v>45002.0</v>
       </c>
       <c r="D161" s="42" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="E161" s="40">
         <v>45003.0</v>
       </c>
       <c r="F161" s="42" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G161" s="42" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H161" s="36"/>
       <c r="I161" s="43" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J161" s="28">
         <v>0.0</v>
@@ -8748,20 +8807,20 @@
         <v>45003.0</v>
       </c>
       <c r="D162" s="42" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="E162" s="40">
         <v>45004.0</v>
       </c>
       <c r="F162" s="42" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G162" s="42" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H162" s="36"/>
       <c r="I162" s="43" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J162" s="19">
         <v>0.0</v>
@@ -8778,20 +8837,20 @@
         <v>45004.0</v>
       </c>
       <c r="D163" s="42" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="E163" s="40">
         <v>45005.0</v>
       </c>
       <c r="F163" s="42" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G163" s="42" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H163" s="36"/>
       <c r="I163" s="43" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J163" s="28">
         <v>0.0</v>
@@ -8808,20 +8867,20 @@
         <v>45005.0</v>
       </c>
       <c r="D164" s="42" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="E164" s="40">
         <v>-1.0</v>
       </c>
       <c r="F164" s="42" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G164" s="42" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H164" s="36"/>
       <c r="I164" s="43" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J164" s="19">
         <v>0.0</v>
@@ -8838,20 +8897,20 @@
         <v>46001.0</v>
       </c>
       <c r="D165" s="42" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="E165" s="40">
         <v>46002.0</v>
       </c>
       <c r="F165" s="42" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G165" s="42" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H165" s="36"/>
       <c r="I165" s="43" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J165" s="28">
         <v>0.0</v>
@@ -8868,20 +8927,20 @@
         <v>46002.0</v>
       </c>
       <c r="D166" s="42" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="E166" s="40">
         <v>46003.0</v>
       </c>
       <c r="F166" s="42" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G166" s="42" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H166" s="36"/>
       <c r="I166" s="43" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J166" s="19">
         <v>0.0</v>
@@ -8898,20 +8957,20 @@
         <v>46003.0</v>
       </c>
       <c r="D167" s="42" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="E167" s="40">
         <v>46004.0</v>
       </c>
       <c r="F167" s="42" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G167" s="42" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H167" s="36"/>
       <c r="I167" s="43" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J167" s="28">
         <v>0.0</v>
@@ -8928,20 +8987,20 @@
         <v>46004.0</v>
       </c>
       <c r="D168" s="42" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="E168" s="40">
         <v>46005.0</v>
       </c>
       <c r="F168" s="42" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G168" s="42" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H168" s="36"/>
       <c r="I168" s="43" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J168" s="19">
         <v>0.0</v>
@@ -8958,20 +9017,20 @@
         <v>46005.0</v>
       </c>
       <c r="D169" s="42" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="E169" s="40">
         <v>-1.0</v>
       </c>
       <c r="F169" s="42" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G169" s="42" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H169" s="36"/>
       <c r="I169" s="43" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J169" s="28">
         <v>0.0</v>
@@ -8988,19 +9047,19 @@
         <v>47001.0</v>
       </c>
       <c r="D170" s="3" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="E170" s="3">
         <v>47002.0</v>
       </c>
       <c r="F170" s="42" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G170" s="42" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="I170" s="43" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J170" s="19">
         <v>0.0</v>
@@ -9017,20 +9076,20 @@
         <v>47002.0</v>
       </c>
       <c r="D171" s="42" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="E171" s="40">
         <v>-1.0</v>
       </c>
       <c r="F171" s="42" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="G171" s="42" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="H171" s="36"/>
       <c r="I171" s="43" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="J171" s="28">
         <v>0.0</v>
@@ -9047,20 +9106,20 @@
         <v>48001.0</v>
       </c>
       <c r="D172" s="42" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="E172" s="40">
         <v>48002.0</v>
       </c>
       <c r="F172" s="42" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G172" s="42" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H172" s="36"/>
       <c r="I172" s="43" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J172" s="19">
         <v>0.0</v>
@@ -9077,20 +9136,20 @@
         <v>48002.0</v>
       </c>
       <c r="D173" s="42" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="E173" s="40">
         <v>48003.0</v>
       </c>
       <c r="F173" s="42" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G173" s="42" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H173" s="36"/>
       <c r="I173" s="43" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J173" s="28">
         <v>0.0</v>
@@ -9107,20 +9166,20 @@
         <v>48003.0</v>
       </c>
       <c r="D174" s="42" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="E174" s="40">
         <v>48004.0</v>
       </c>
       <c r="F174" s="42" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G174" s="42" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H174" s="36"/>
       <c r="I174" s="43" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J174" s="19">
         <v>0.0</v>
@@ -9137,20 +9196,20 @@
         <v>48004.0</v>
       </c>
       <c r="D175" s="42" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="E175" s="40">
         <v>48005.0</v>
       </c>
       <c r="F175" s="42" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G175" s="42" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H175" s="36"/>
       <c r="I175" s="43" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J175" s="28">
         <v>0.0</v>
@@ -9167,20 +9226,20 @@
         <v>48005.0</v>
       </c>
       <c r="D176" s="42" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="E176" s="40">
         <v>48006.0</v>
       </c>
       <c r="F176" s="42" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G176" s="42" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H176" s="36"/>
       <c r="I176" s="43" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J176" s="19">
         <v>0.0</v>
@@ -9197,20 +9256,20 @@
         <v>48006.0</v>
       </c>
       <c r="D177" s="42" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="E177" s="40">
         <v>48007.0</v>
       </c>
       <c r="F177" s="42" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G177" s="42" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H177" s="36"/>
       <c r="I177" s="43" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J177" s="28">
         <v>0.0</v>
@@ -9227,20 +9286,20 @@
         <v>48007.0</v>
       </c>
       <c r="D178" s="42" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="E178" s="40">
         <v>48008.0</v>
       </c>
       <c r="F178" s="42" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G178" s="42" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H178" s="36"/>
       <c r="I178" s="43" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J178" s="19">
         <v>0.0</v>
@@ -9257,20 +9316,20 @@
         <v>48008.0</v>
       </c>
       <c r="D179" s="42" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="E179" s="40">
         <v>48009.0</v>
       </c>
       <c r="F179" s="42" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G179" s="42" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H179" s="36"/>
       <c r="I179" s="43" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J179" s="28">
         <v>0.0</v>
@@ -9287,20 +9346,20 @@
         <v>48009.0</v>
       </c>
       <c r="D180" s="42" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="E180" s="40">
         <v>-1.0</v>
       </c>
       <c r="F180" s="42" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G180" s="42" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H180" s="36"/>
       <c r="I180" s="43" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J180" s="19">
         <v>0.0</v>
@@ -9317,20 +9376,20 @@
         <v>49001.0</v>
       </c>
       <c r="D181" s="42" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="E181" s="40">
         <v>49002.0</v>
       </c>
       <c r="F181" s="42" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G181" s="42" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H181" s="36"/>
       <c r="I181" s="43" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J181" s="28">
         <v>0.0</v>
@@ -9347,20 +9406,20 @@
         <v>49002.0</v>
       </c>
       <c r="D182" s="42" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="E182" s="40">
         <v>-1.0</v>
       </c>
       <c r="F182" s="42" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G182" s="42" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H182" s="36"/>
       <c r="I182" s="43" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J182" s="19">
         <v>0.0</v>
@@ -9377,20 +9436,20 @@
         <v>50001.0</v>
       </c>
       <c r="D183" s="42" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="E183" s="40">
         <v>50002.0</v>
       </c>
       <c r="F183" s="42" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G183" s="42" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H183" s="36"/>
       <c r="I183" s="43" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J183" s="28">
         <v>0.0</v>
@@ -9407,20 +9466,20 @@
         <v>50002.0</v>
       </c>
       <c r="D184" s="42" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="E184" s="40">
         <v>50003.0</v>
       </c>
       <c r="F184" s="42" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G184" s="42" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H184" s="36"/>
       <c r="I184" s="43" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J184" s="19">
         <v>0.0</v>
@@ -9437,20 +9496,20 @@
         <v>50003.0</v>
       </c>
       <c r="D185" s="42" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="E185" s="40">
         <v>-1.0</v>
       </c>
       <c r="F185" s="42" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G185" s="42" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H185" s="36"/>
       <c r="I185" s="43" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J185" s="28">
         <v>0.0</v>
@@ -9467,20 +9526,20 @@
         <v>51001.0</v>
       </c>
       <c r="D186" s="42" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="E186" s="40">
         <v>-1.0</v>
       </c>
       <c r="F186" s="42" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G186" s="42" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H186" s="36"/>
       <c r="I186" s="43" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="J186" s="40">
         <v>-1.0</v>
@@ -9497,20 +9556,20 @@
         <v>52001.0</v>
       </c>
       <c r="D187" s="44" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="E187" s="40">
         <v>52002.0</v>
       </c>
       <c r="F187" s="42" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G187" s="42" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H187" s="36"/>
       <c r="I187" s="43" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J187" s="40">
         <v>0.0</v>
@@ -9527,20 +9586,20 @@
         <v>52002.0</v>
       </c>
       <c r="D188" s="45" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="E188" s="40">
         <v>52003.0</v>
       </c>
       <c r="F188" s="42" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G188" s="42" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H188" s="36"/>
       <c r="I188" s="43" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J188" s="40">
         <v>0.0</v>
@@ -9557,20 +9616,20 @@
         <v>52003.0</v>
       </c>
       <c r="D189" s="44" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="E189" s="40">
         <v>52004.0</v>
       </c>
       <c r="F189" s="42" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G189" s="42" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H189" s="36"/>
       <c r="I189" s="43" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J189" s="40">
         <v>0.0</v>
@@ -9587,20 +9646,20 @@
         <v>52004.0</v>
       </c>
       <c r="D190" s="44" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="E190" s="40">
         <v>52005.0</v>
       </c>
       <c r="F190" s="42" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G190" s="42" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H190" s="36"/>
       <c r="I190" s="43" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J190" s="40">
         <v>0.0</v>
@@ -9617,20 +9676,20 @@
         <v>52005.0</v>
       </c>
       <c r="D191" s="3" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="E191" s="40">
         <v>-1.0</v>
       </c>
       <c r="F191" s="42" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G191" s="42" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H191" s="36"/>
       <c r="I191" s="43" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J191" s="40">
         <v>0.0</v>
@@ -9647,20 +9706,20 @@
         <v>53001.0</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="E192" s="40">
         <v>53002.0</v>
       </c>
       <c r="F192" s="42" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G192" s="42" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H192" s="36"/>
       <c r="I192" s="43" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J192" s="40">
         <v>0.0</v>
@@ -9677,20 +9736,20 @@
         <v>53002.0</v>
       </c>
       <c r="D193" s="14" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="E193" s="40">
         <v>53003.0</v>
       </c>
       <c r="F193" s="42" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G193" s="42" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H193" s="36"/>
       <c r="I193" s="43" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J193" s="40">
         <v>0.0</v>
@@ -9707,20 +9766,20 @@
         <v>53003.0</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="E194" s="40">
         <v>53004.0</v>
       </c>
       <c r="F194" s="42" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G194" s="42" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H194" s="36"/>
       <c r="I194" s="43" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J194" s="40">
         <v>0.0</v>
@@ -9737,20 +9796,20 @@
         <v>53004.0</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="E195" s="40">
         <v>-1.0</v>
       </c>
       <c r="F195" s="42" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G195" s="42" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H195" s="36"/>
       <c r="I195" s="43" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J195" s="40">
         <v>0.0</v>
@@ -9767,20 +9826,20 @@
         <v>54001.0</v>
       </c>
       <c r="D196" s="14" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="E196" s="40">
         <v>54002.0</v>
       </c>
       <c r="F196" s="42" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G196" s="42" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H196" s="36"/>
       <c r="I196" s="43" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J196" s="40">
         <v>0.0</v>
@@ -9797,20 +9856,20 @@
         <v>54002.0</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="E197" s="40">
         <v>54003.0</v>
       </c>
       <c r="F197" s="42" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G197" s="42" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H197" s="36"/>
       <c r="I197" s="43" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J197" s="40">
         <v>0.0</v>
@@ -9827,20 +9886,20 @@
         <v>54003.0</v>
       </c>
       <c r="D198" s="14" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="E198" s="40">
         <v>54004.0</v>
       </c>
       <c r="F198" s="42" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G198" s="42" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H198" s="36"/>
       <c r="I198" s="43" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J198" s="40">
         <v>0.0</v>
@@ -9857,20 +9916,20 @@
         <v>54004.0</v>
       </c>
       <c r="D199" s="1" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="E199" s="40">
         <v>-1.0</v>
       </c>
       <c r="F199" s="42" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G199" s="42" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H199" s="36"/>
       <c r="I199" s="43" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J199" s="40">
         <v>0.0</v>
@@ -9887,20 +9946,20 @@
         <v>55001.0</v>
       </c>
       <c r="D200" s="1" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="E200" s="40">
         <v>55002.0</v>
       </c>
       <c r="F200" s="42" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G200" s="42" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H200" s="36"/>
       <c r="I200" s="43" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J200" s="40">
         <v>0.0</v>
@@ -9917,20 +9976,20 @@
         <v>55002.0</v>
       </c>
       <c r="D201" s="14" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="E201" s="40">
         <v>-1.0</v>
       </c>
       <c r="F201" s="42" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G201" s="42" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H201" s="36"/>
       <c r="I201" s="43" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J201" s="40">
         <v>0.0</v>
@@ -9947,20 +10006,20 @@
         <v>56001.0</v>
       </c>
       <c r="D202" s="14" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="E202" s="40">
         <v>56002.0</v>
       </c>
       <c r="F202" s="42" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G202" s="42" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H202" s="36"/>
       <c r="I202" s="43" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J202" s="40">
         <v>0.0</v>
@@ -9977,20 +10036,20 @@
         <v>56002.0</v>
       </c>
       <c r="D203" s="14" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="E203" s="40">
         <v>-1.0</v>
       </c>
       <c r="F203" s="42" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G203" s="42" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H203" s="36"/>
       <c r="I203" s="43" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J203" s="40">
         <v>0.0</v>
@@ -10007,20 +10066,20 @@
         <v>57001.0</v>
       </c>
       <c r="D204" s="14" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="E204" s="40">
         <v>57002.0</v>
       </c>
       <c r="F204" s="42" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G204" s="42" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H204" s="36"/>
       <c r="I204" s="43" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J204" s="40">
         <v>0.0</v>
@@ -10037,20 +10096,20 @@
         <v>57002.0</v>
       </c>
       <c r="D205" s="14" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="E205" s="40">
         <v>-1.0</v>
       </c>
       <c r="F205" s="42" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G205" s="42" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H205" s="36"/>
       <c r="I205" s="43" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J205" s="40">
         <v>0.0</v>
@@ -10067,20 +10126,20 @@
         <v>58001.0</v>
       </c>
       <c r="D206" s="1" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="E206" s="40">
         <v>58002.0</v>
       </c>
       <c r="F206" s="42" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G206" s="42" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H206" s="36"/>
       <c r="I206" s="43" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J206" s="40">
         <v>0.0</v>
@@ -10097,20 +10156,20 @@
         <v>58002.0</v>
       </c>
       <c r="D207" s="1" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="E207" s="40">
         <v>58003.0</v>
       </c>
       <c r="F207" s="42" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G207" s="42" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H207" s="36"/>
       <c r="I207" s="43" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J207" s="40">
         <v>0.0</v>
@@ -10127,20 +10186,20 @@
         <v>58003.0</v>
       </c>
       <c r="D208" s="1" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="E208" s="40">
         <v>58004.0</v>
       </c>
       <c r="F208" s="42" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G208" s="42" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H208" s="36"/>
       <c r="I208" s="43" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J208" s="40">
         <v>0.0</v>
@@ -10157,20 +10216,20 @@
         <v>58004.0</v>
       </c>
       <c r="D209" s="14" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="E209" s="40">
         <v>58005.0</v>
       </c>
       <c r="F209" s="42" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G209" s="42" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H209" s="36"/>
       <c r="I209" s="43" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J209" s="40">
         <v>0.0</v>
@@ -10187,20 +10246,20 @@
         <v>58005.0</v>
       </c>
       <c r="D210" s="14" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="E210" s="40">
         <v>58006.0</v>
       </c>
       <c r="F210" s="42" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G210" s="42" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H210" s="36"/>
       <c r="I210" s="43" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J210" s="40">
         <v>0.0</v>
@@ -10217,20 +10276,20 @@
         <v>58006.0</v>
       </c>
       <c r="D211" s="14" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="E211" s="40">
         <v>-1.0</v>
       </c>
       <c r="F211" s="42" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G211" s="42" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H211" s="36"/>
       <c r="I211" s="43" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J211" s="40">
         <v>0.0</v>
@@ -10247,20 +10306,20 @@
         <v>59001.0</v>
       </c>
       <c r="D212" s="1" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="E212" s="40">
         <v>59002.0</v>
       </c>
       <c r="F212" s="42" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G212" s="42" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H212" s="36"/>
       <c r="I212" s="43" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J212" s="40">
         <v>0.0</v>
@@ -10277,20 +10336,20 @@
         <v>59002.0</v>
       </c>
       <c r="D213" s="1" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="E213" s="40">
         <v>59003.0</v>
       </c>
       <c r="F213" s="42" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G213" s="42" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H213" s="36"/>
       <c r="I213" s="43" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J213" s="40">
         <v>0.0</v>
@@ -10307,20 +10366,20 @@
         <v>59003.0</v>
       </c>
       <c r="D214" s="14" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="E214" s="40">
         <v>59004.0</v>
       </c>
       <c r="F214" s="42" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G214" s="42" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H214" s="36"/>
       <c r="I214" s="43" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J214" s="40">
         <v>0.0</v>
@@ -10337,20 +10396,20 @@
         <v>59004.0</v>
       </c>
       <c r="D215" s="1" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="E215" s="40">
         <v>59005.0</v>
       </c>
       <c r="F215" s="42" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G215" s="42" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H215" s="36"/>
       <c r="I215" s="43" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J215" s="40">
         <v>0.0</v>
@@ -10367,20 +10426,20 @@
         <v>59005.0</v>
       </c>
       <c r="D216" s="14" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="E216" s="40">
         <v>59006.0</v>
       </c>
       <c r="F216" s="42" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G216" s="42" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H216" s="36"/>
       <c r="I216" s="43" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J216" s="40">
         <v>0.0</v>
@@ -10397,20 +10456,20 @@
         <v>59006.0</v>
       </c>
       <c r="D217" s="14" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="E217" s="40">
         <v>-1.0</v>
       </c>
       <c r="F217" s="42" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G217" s="42" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H217" s="36"/>
       <c r="I217" s="43" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J217" s="40">
         <v>0.0</v>
@@ -10427,20 +10486,20 @@
         <v>60001.0</v>
       </c>
       <c r="D218" s="1" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="E218" s="40">
         <v>60002.0</v>
       </c>
       <c r="F218" s="42" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G218" s="42" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H218" s="36"/>
       <c r="I218" s="43" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J218" s="40">
         <v>0.0</v>
@@ -10457,20 +10516,20 @@
         <v>60002.0</v>
       </c>
       <c r="D219" s="14" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="E219" s="40">
         <v>60003.0</v>
       </c>
       <c r="F219" s="42" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G219" s="42" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H219" s="36"/>
       <c r="I219" s="43" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J219" s="40">
         <v>0.0</v>
@@ -10487,20 +10546,20 @@
         <v>60003.0</v>
       </c>
       <c r="D220" s="14" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="E220" s="40">
         <v>60004.0</v>
       </c>
       <c r="F220" s="42" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G220" s="42" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H220" s="36"/>
       <c r="I220" s="43" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J220" s="40">
         <v>0.0</v>
@@ -10517,20 +10576,20 @@
         <v>60004.0</v>
       </c>
       <c r="D221" s="14" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="E221" s="40">
         <v>60005.0</v>
       </c>
       <c r="F221" s="42" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G221" s="42" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H221" s="36"/>
       <c r="I221" s="43" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J221" s="40">
         <v>0.0</v>
@@ -10547,20 +10606,20 @@
         <v>60005.0</v>
       </c>
       <c r="D222" s="14" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="E222" s="40">
         <v>60006.0</v>
       </c>
       <c r="F222" s="42" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G222" s="42" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H222" s="36"/>
       <c r="I222" s="43" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J222" s="40">
         <v>0.0</v>
@@ -10577,20 +10636,20 @@
         <v>60006.0</v>
       </c>
       <c r="D223" s="14" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="E223" s="40">
         <v>60007.0</v>
       </c>
       <c r="F223" s="42" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G223" s="42" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H223" s="36"/>
       <c r="I223" s="43" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J223" s="40">
         <v>0.0</v>
@@ -10607,20 +10666,20 @@
         <v>60007.0</v>
       </c>
       <c r="D224" s="1" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="E224" s="40">
         <v>-1.0</v>
       </c>
       <c r="F224" s="42" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G224" s="42" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H224" s="36"/>
       <c r="I224" s="43" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J224" s="40">
         <v>0.0</v>
@@ -10637,20 +10696,20 @@
         <v>61001.0</v>
       </c>
       <c r="D225" s="1" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="E225" s="3">
         <v>61002.0</v>
       </c>
       <c r="F225" s="42" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G225" s="42" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H225" s="36"/>
       <c r="I225" s="43" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J225" s="40">
         <v>0.0</v>
@@ -10667,20 +10726,20 @@
         <v>61002.0</v>
       </c>
       <c r="D226" s="1" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E226" s="3">
         <v>61003.0</v>
       </c>
       <c r="F226" s="42" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G226" s="42" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H226" s="36"/>
       <c r="I226" s="43" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J226" s="40">
         <v>0.0</v>
@@ -10697,20 +10756,20 @@
         <v>61003.0</v>
       </c>
       <c r="D227" s="3" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="E227" s="3">
         <v>61004.0</v>
       </c>
       <c r="F227" s="42" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G227" s="42" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H227" s="36"/>
       <c r="I227" s="43" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J227" s="40">
         <v>0.0</v>
@@ -10727,20 +10786,20 @@
         <v>61004.0</v>
       </c>
       <c r="D228" s="46" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="E228" s="3">
         <v>61005.0</v>
       </c>
       <c r="F228" s="42" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G228" s="42" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H228" s="36"/>
       <c r="I228" s="43" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J228" s="40">
         <v>0.0</v>
@@ -10757,20 +10816,20 @@
         <v>61005.0</v>
       </c>
       <c r="D229" s="46" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="E229" s="3">
         <v>61006.0</v>
       </c>
       <c r="F229" s="42" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G229" s="42" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H229" s="36"/>
       <c r="I229" s="43" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J229" s="40">
         <v>0.0</v>
@@ -10787,20 +10846,20 @@
         <v>61006.0</v>
       </c>
       <c r="D230" s="46" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="E230" s="3">
         <v>61007.0</v>
       </c>
       <c r="F230" s="42" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G230" s="42" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H230" s="36"/>
       <c r="I230" s="43" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J230" s="40">
         <v>0.0</v>
@@ -10817,20 +10876,20 @@
         <v>61007.0</v>
       </c>
       <c r="D231" s="46" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="E231" s="40">
         <v>-1.0</v>
       </c>
       <c r="F231" s="42" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G231" s="42" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H231" s="36"/>
       <c r="I231" s="43" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J231" s="40">
         <v>0.0</v>
@@ -10847,20 +10906,20 @@
         <v>62001.0</v>
       </c>
       <c r="D232" s="1" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="E232" s="40">
         <v>62002.0</v>
       </c>
       <c r="F232" s="42" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G232" s="42" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H232" s="36"/>
       <c r="I232" s="43" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J232" s="40">
         <v>0.0</v>
@@ -10877,20 +10936,20 @@
         <v>62002.0</v>
       </c>
       <c r="D233" s="1" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="E233" s="40">
         <v>62003.0</v>
       </c>
       <c r="F233" s="42" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G233" s="42" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H233" s="36"/>
       <c r="I233" s="43" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J233" s="40">
         <v>0.0</v>
@@ -10907,20 +10966,20 @@
         <v>62003.0</v>
       </c>
       <c r="D234" s="14" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="E234" s="40">
         <v>-1.0</v>
       </c>
       <c r="F234" s="42" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G234" s="42" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H234" s="36"/>
       <c r="I234" s="43" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J234" s="40">
         <v>0.0</v>
@@ -10937,20 +10996,20 @@
         <v>63001.0</v>
       </c>
       <c r="D235" s="14" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="E235" s="3">
         <v>63002.0</v>
       </c>
       <c r="F235" s="42" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G235" s="42" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H235" s="36"/>
       <c r="I235" s="43" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J235" s="40">
         <v>0.0</v>
@@ -10967,20 +11026,20 @@
         <v>63002.0</v>
       </c>
       <c r="D236" s="1" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="E236" s="3">
         <v>63003.0</v>
       </c>
       <c r="F236" s="42" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G236" s="42" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H236" s="36"/>
       <c r="I236" s="43" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J236" s="40">
         <v>0.0</v>
@@ -10997,20 +11056,20 @@
         <v>63003.0</v>
       </c>
       <c r="D237" s="1" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="E237" s="3">
         <v>63004.0</v>
       </c>
       <c r="F237" s="42" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G237" s="42" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H237" s="36"/>
       <c r="I237" s="43" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J237" s="40">
         <v>0.0</v>
@@ -11027,20 +11086,20 @@
         <v>63004.0</v>
       </c>
       <c r="D238" s="1" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="E238" s="3">
         <v>63005.0</v>
       </c>
       <c r="F238" s="42" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G238" s="42" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H238" s="36"/>
       <c r="I238" s="43" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J238" s="40">
         <v>0.0</v>
@@ -11057,20 +11116,20 @@
         <v>63005.0</v>
       </c>
       <c r="D239" s="1" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="E239" s="3">
         <v>63006.0</v>
       </c>
       <c r="F239" s="42" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G239" s="42" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H239" s="36"/>
       <c r="I239" s="43" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J239" s="40">
         <v>0.0</v>
@@ -11087,20 +11146,20 @@
         <v>63006.0</v>
       </c>
       <c r="D240" s="1" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="E240" s="3">
         <v>63007.0</v>
       </c>
       <c r="F240" s="42" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G240" s="42" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H240" s="36"/>
       <c r="I240" s="43" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J240" s="40">
         <v>0.0</v>
@@ -11117,20 +11176,20 @@
         <v>63007.0</v>
       </c>
       <c r="D241" s="14" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="E241" s="3">
         <v>63008.0</v>
       </c>
       <c r="F241" s="42" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G241" s="42" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H241" s="36"/>
       <c r="I241" s="43" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J241" s="40">
         <v>0.0</v>
@@ -11147,20 +11206,20 @@
         <v>63008.0</v>
       </c>
       <c r="D242" s="14" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="E242" s="3">
         <v>63009.0</v>
       </c>
       <c r="F242" s="42" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G242" s="42" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H242" s="36"/>
       <c r="I242" s="43" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J242" s="40">
         <v>0.0</v>
@@ -11177,20 +11236,20 @@
         <v>63009.0</v>
       </c>
       <c r="D243" s="14" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="E243" s="3">
         <v>63010.0</v>
       </c>
       <c r="F243" s="42" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G243" s="42" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H243" s="36"/>
       <c r="I243" s="43" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J243" s="40">
         <v>0.0</v>
@@ -11207,20 +11266,20 @@
         <v>63010.0</v>
       </c>
       <c r="D244" s="14" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="E244" s="40">
         <v>-1.0</v>
       </c>
       <c r="F244" s="42" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G244" s="42" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H244" s="36"/>
       <c r="I244" s="43" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J244" s="40">
         <v>0.0</v>
@@ -11237,20 +11296,20 @@
         <v>64001.0</v>
       </c>
       <c r="D245" s="14" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="E245" s="40">
         <v>-1.0</v>
       </c>
       <c r="F245" s="42" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G245" s="42" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H245" s="36"/>
       <c r="I245" s="43" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="J245" s="40">
         <v>-1.0</v>
@@ -11267,20 +11326,20 @@
         <v>65001.0</v>
       </c>
       <c r="D246" s="1" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="E246" s="40">
         <v>65002.0</v>
       </c>
       <c r="F246" s="42" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G246" s="42" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H246" s="36"/>
       <c r="I246" s="43" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J246" s="40">
         <v>0.0</v>
@@ -11297,20 +11356,20 @@
         <v>65002.0</v>
       </c>
       <c r="D247" s="14" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="E247" s="40">
         <v>65003.0</v>
       </c>
       <c r="F247" s="42" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G247" s="42" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H247" s="36"/>
       <c r="I247" s="43" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J247" s="40">
         <v>0.0</v>
@@ -11327,20 +11386,20 @@
         <v>65003.0</v>
       </c>
       <c r="D248" s="14" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="E248" s="40">
         <v>-1.0</v>
       </c>
       <c r="F248" s="42" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G248" s="42" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H248" s="36"/>
       <c r="I248" s="43" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J248" s="40">
         <v>0.0</v>
@@ -11357,20 +11416,20 @@
         <v>66001.0</v>
       </c>
       <c r="D249" s="1" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="E249" s="40">
         <v>66002.0</v>
       </c>
       <c r="F249" s="42" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G249" s="42" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H249" s="36"/>
       <c r="I249" s="43" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J249" s="40">
         <v>0.0</v>
@@ -11387,20 +11446,20 @@
         <v>66002.0</v>
       </c>
       <c r="D250" s="14" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="E250" s="40">
         <v>66003.0</v>
       </c>
       <c r="F250" s="42" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G250" s="42" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H250" s="36"/>
       <c r="I250" s="43" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J250" s="40">
         <v>0.0</v>
@@ -11417,20 +11476,20 @@
         <v>66003.0</v>
       </c>
       <c r="D251" s="14" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="E251" s="40">
         <v>66004.0</v>
       </c>
       <c r="F251" s="42" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G251" s="42" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H251" s="36"/>
       <c r="I251" s="43" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J251" s="40">
         <v>0.0</v>
@@ -11447,20 +11506,20 @@
         <v>66004.0</v>
       </c>
       <c r="D252" s="1" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="E252" s="40">
         <v>66005.0</v>
       </c>
       <c r="F252" s="42" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G252" s="42" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H252" s="36"/>
       <c r="I252" s="43" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J252" s="40">
         <v>0.0</v>
@@ -11477,20 +11536,20 @@
         <v>66005.0</v>
       </c>
       <c r="D253" s="1" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="E253" s="40">
         <v>-1.0</v>
       </c>
       <c r="F253" s="42" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G253" s="42" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H253" s="36"/>
       <c r="I253" s="43" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J253" s="40">
         <v>0.0</v>
@@ -11507,20 +11566,20 @@
         <v>67001.0</v>
       </c>
       <c r="D254" s="1" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="E254" s="40">
         <v>67002.0</v>
       </c>
       <c r="F254" s="42" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G254" s="42" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H254" s="36"/>
       <c r="I254" s="43" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J254" s="40">
         <v>0.0</v>
@@ -11537,20 +11596,20 @@
         <v>67002.0</v>
       </c>
       <c r="D255" s="1" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="E255" s="40">
         <v>67003.0</v>
       </c>
       <c r="F255" s="42" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G255" s="42" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H255" s="36"/>
       <c r="I255" s="43" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J255" s="40">
         <v>0.0</v>
@@ -11567,20 +11626,20 @@
         <v>67003.0</v>
       </c>
       <c r="D256" s="14" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="E256" s="40">
         <v>67004.0</v>
       </c>
       <c r="F256" s="42" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G256" s="42" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H256" s="36"/>
       <c r="I256" s="43" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J256" s="40">
         <v>0.0</v>
@@ -11597,20 +11656,20 @@
         <v>67004.0</v>
       </c>
       <c r="D257" s="14" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="E257" s="40">
         <v>67005.0</v>
       </c>
       <c r="F257" s="42" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G257" s="42" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H257" s="36"/>
       <c r="I257" s="43" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J257" s="40">
         <v>0.0</v>
@@ -11627,20 +11686,20 @@
         <v>67005.0</v>
       </c>
       <c r="D258" s="1" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="E258" s="40">
         <v>-1.0</v>
       </c>
       <c r="F258" s="42" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G258" s="42" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H258" s="36"/>
       <c r="I258" s="43" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J258" s="40">
         <v>0.0</v>
@@ -11657,20 +11716,20 @@
         <v>68001.0</v>
       </c>
       <c r="D259" s="3" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="E259" s="40">
         <v>68002.0</v>
       </c>
       <c r="F259" s="42" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G259" s="42" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H259" s="36"/>
       <c r="I259" s="43" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J259" s="40">
         <v>0.0</v>
@@ -11687,20 +11746,20 @@
         <v>68002.0</v>
       </c>
       <c r="D260" s="3" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="E260" s="40">
         <v>-1.0</v>
       </c>
       <c r="F260" s="42" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G260" s="42" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H260" s="36"/>
       <c r="I260" s="43" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J260" s="40">
         <v>0.0</v>
@@ -11717,20 +11776,20 @@
         <v>69001.0</v>
       </c>
       <c r="D261" s="1" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="E261" s="40">
         <v>69002.0</v>
       </c>
       <c r="F261" s="42" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G261" s="42" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H261" s="36"/>
       <c r="I261" s="43" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J261" s="40">
         <v>0.0</v>
@@ -11747,20 +11806,20 @@
         <v>69002.0</v>
       </c>
       <c r="D262" s="1" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="E262" s="40">
         <v>69003.0</v>
       </c>
       <c r="F262" s="42" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G262" s="42" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H262" s="36"/>
       <c r="I262" s="43" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J262" s="40">
         <v>0.0</v>
@@ -11777,20 +11836,20 @@
         <v>69003.0</v>
       </c>
       <c r="D263" s="1" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="E263" s="40">
         <v>-1.0</v>
       </c>
       <c r="F263" s="42" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G263" s="42" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H263" s="36"/>
       <c r="I263" s="43" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J263" s="40">
         <v>0.0</v>
@@ -11807,20 +11866,20 @@
         <v>70001.0</v>
       </c>
       <c r="D264" s="3" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="E264" s="40">
         <v>-1.0</v>
       </c>
       <c r="F264" s="42" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G264" s="42" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H264" s="36"/>
       <c r="I264" s="43" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J264" s="40">
         <v>0.0</v>
@@ -11837,20 +11896,20 @@
         <v>71001.0</v>
       </c>
       <c r="D265" s="1" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="E265" s="3">
         <v>71002.0</v>
       </c>
       <c r="F265" s="42" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G265" s="42" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H265" s="36"/>
       <c r="I265" s="43" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J265" s="40">
         <v>0.0</v>
@@ -11867,20 +11926,20 @@
         <v>71002.0</v>
       </c>
       <c r="D266" s="1" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="E266" s="3">
         <v>71003.0</v>
       </c>
       <c r="F266" s="42" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G266" s="42" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H266" s="36"/>
       <c r="I266" s="43" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J266" s="40">
         <v>0.0</v>
@@ -11897,20 +11956,20 @@
         <v>71003.0</v>
       </c>
       <c r="D267" s="1" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="E267" s="3">
         <v>71004.0</v>
       </c>
       <c r="F267" s="42" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G267" s="42" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H267" s="36"/>
       <c r="I267" s="43" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J267" s="40">
         <v>0.0</v>
@@ -11927,20 +11986,20 @@
         <v>71004.0</v>
       </c>
       <c r="D268" s="14" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="E268" s="40">
         <v>-1.0</v>
       </c>
       <c r="F268" s="42" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G268" s="42" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H268" s="36"/>
       <c r="I268" s="43" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J268" s="40">
         <v>0.0</v>
@@ -11957,20 +12016,20 @@
         <v>72001.0</v>
       </c>
       <c r="D269" s="3" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="E269" s="3">
         <v>72002.0</v>
       </c>
       <c r="F269" s="42" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G269" s="42" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H269" s="36"/>
       <c r="I269" s="43" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J269" s="40">
         <v>0.0</v>
@@ -11987,20 +12046,20 @@
         <v>72002.0</v>
       </c>
       <c r="D270" s="46" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="E270" s="3">
         <v>72003.0</v>
       </c>
       <c r="F270" s="42" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G270" s="42" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H270" s="36"/>
       <c r="I270" s="43" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J270" s="40">
         <v>0.0</v>
@@ -12017,20 +12076,20 @@
         <v>72003.0</v>
       </c>
       <c r="D271" s="4" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="E271" s="3">
         <v>72004.0</v>
       </c>
       <c r="F271" s="42" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G271" s="42" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H271" s="36"/>
       <c r="I271" s="43" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J271" s="40">
         <v>0.0</v>
@@ -12047,20 +12106,20 @@
         <v>72004.0</v>
       </c>
       <c r="D272" s="1" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="E272" s="3">
         <v>72005.0</v>
       </c>
       <c r="F272" s="42" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G272" s="42" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H272" s="36"/>
       <c r="I272" s="43" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J272" s="40">
         <v>0.0</v>
@@ -12077,20 +12136,20 @@
         <v>72005.0</v>
       </c>
       <c r="D273" s="1" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="E273" s="40">
         <v>-1.0</v>
       </c>
       <c r="F273" s="42" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G273" s="42" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H273" s="36"/>
       <c r="I273" s="43" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J273" s="40">
         <v>0.0</v>
@@ -12107,20 +12166,20 @@
         <v>73001.0</v>
       </c>
       <c r="D274" s="1" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="E274" s="3">
         <v>73002.0</v>
       </c>
       <c r="F274" s="42" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G274" s="42" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H274" s="36"/>
       <c r="I274" s="43" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J274" s="40">
         <v>0.0</v>
@@ -12137,20 +12196,20 @@
         <v>73002.0</v>
       </c>
       <c r="D275" s="1" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="E275" s="3">
         <v>73003.0</v>
       </c>
       <c r="F275" s="42" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G275" s="42" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H275" s="36"/>
       <c r="I275" s="43" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J275" s="40">
         <v>0.0</v>
@@ -12167,20 +12226,20 @@
         <v>73003.0</v>
       </c>
       <c r="D276" s="1" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="E276" s="40">
         <v>-1.0</v>
       </c>
       <c r="F276" s="42" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G276" s="42" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H276" s="36"/>
       <c r="I276" s="43" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J276" s="40">
         <v>0.0</v>
@@ -12197,20 +12256,20 @@
         <v>74001.0</v>
       </c>
       <c r="D277" s="1" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="E277" s="3">
         <v>74002.0</v>
       </c>
       <c r="F277" s="42" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G277" s="42" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H277" s="36"/>
       <c r="I277" s="43" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J277" s="40">
         <v>0.0</v>
@@ -12227,20 +12286,20 @@
         <v>74002.0</v>
       </c>
       <c r="D278" s="4" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="E278" s="40">
         <v>-1.0</v>
       </c>
       <c r="F278" s="42" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G278" s="42" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H278" s="36"/>
       <c r="I278" s="43" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J278" s="40">
         <v>0.0</v>
@@ -12257,20 +12316,20 @@
         <v>75001.0</v>
       </c>
       <c r="D279" s="4" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="E279" s="40">
         <v>75002.0</v>
       </c>
       <c r="F279" s="42" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G279" s="42" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H279" s="36"/>
       <c r="I279" s="43" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J279" s="40">
         <v>0.0</v>
@@ -12287,20 +12346,20 @@
         <v>75002.0</v>
       </c>
       <c r="D280" s="1" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="E280" s="40">
         <v>-1.0</v>
       </c>
       <c r="F280" s="42" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G280" s="42" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H280" s="36"/>
       <c r="I280" s="43" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J280" s="40">
         <v>0.0</v>
@@ -12317,23 +12376,23 @@
         <v>76001.0</v>
       </c>
       <c r="D281" s="4" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="E281" s="3">
         <v>76002.0</v>
       </c>
-      <c r="F281" s="42" t="s">
-        <v>252</v>
+      <c r="F281" s="11" t="s">
+        <v>218</v>
       </c>
       <c r="G281" s="42" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="H281" s="36"/>
       <c r="I281" s="43" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="J281" s="40">
-        <v>1.0</v>
+        <v>-1.0</v>
       </c>
     </row>
     <row r="282">
@@ -12347,20 +12406,20 @@
         <v>76002.0</v>
       </c>
       <c r="D282" s="4" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="E282" s="3">
         <v>76003.0</v>
       </c>
       <c r="F282" s="42" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G282" s="42" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H282" s="36"/>
       <c r="I282" s="43" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J282" s="40">
         <v>0.0</v>
@@ -12377,20 +12436,20 @@
         <v>76003.0</v>
       </c>
       <c r="D283" s="1" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="E283" s="3">
         <v>76004.0</v>
       </c>
       <c r="F283" s="42" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G283" s="42" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H283" s="36"/>
       <c r="I283" s="43" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J283" s="40">
         <v>0.0</v>
@@ -12407,20 +12466,20 @@
         <v>76004.0</v>
       </c>
       <c r="D284" s="1" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="E284" s="40">
         <v>-1.0</v>
       </c>
       <c r="F284" s="42" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G284" s="42" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H284" s="36"/>
       <c r="I284" s="43" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J284" s="40">
         <v>0.0</v>
@@ -12437,20 +12496,20 @@
         <v>77001.0</v>
       </c>
       <c r="D285" s="1" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="E285" s="3">
         <v>77002.0</v>
       </c>
       <c r="F285" s="42" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G285" s="42" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H285" s="36"/>
       <c r="I285" s="43" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J285" s="40">
         <v>0.0</v>
@@ -12467,20 +12526,20 @@
         <v>77002.0</v>
       </c>
       <c r="D286" s="4" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="E286" s="3">
         <v>77003.0</v>
       </c>
       <c r="F286" s="42" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G286" s="42" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H286" s="36"/>
       <c r="I286" s="43" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J286" s="40">
         <v>0.0</v>
@@ -12497,20 +12556,20 @@
         <v>77003.0</v>
       </c>
       <c r="D287" s="1" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="E287" s="40">
         <v>-1.0</v>
       </c>
       <c r="F287" s="42" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G287" s="42" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H287" s="36"/>
       <c r="I287" s="43" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J287" s="40">
         <v>0.0</v>
@@ -12527,20 +12586,20 @@
         <v>78001.0</v>
       </c>
       <c r="D288" s="1" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="E288" s="3">
         <v>78002.0</v>
       </c>
       <c r="F288" s="42" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G288" s="42" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H288" s="36"/>
       <c r="I288" s="43" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J288" s="40">
         <v>0.0</v>
@@ -12557,20 +12616,20 @@
         <v>78002.0</v>
       </c>
       <c r="D289" s="1" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="E289" s="3">
         <v>78003.0</v>
       </c>
       <c r="F289" s="42" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G289" s="42" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H289" s="36"/>
       <c r="I289" s="43" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J289" s="40">
         <v>0.0</v>
@@ -12587,20 +12646,20 @@
         <v>78003.0</v>
       </c>
       <c r="D290" s="1" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="E290" s="40">
         <v>-1.0</v>
       </c>
       <c r="F290" s="42" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="G290" s="42" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="H290" s="36"/>
       <c r="I290" s="43" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J290" s="40">
         <v>0.0</v>
@@ -12616,24 +12675,24 @@
       <c r="C291" s="3">
         <v>79001.0</v>
       </c>
-      <c r="D291" s="14" t="s">
-        <v>508</v>
+      <c r="D291" s="1" t="s">
+        <v>510</v>
       </c>
       <c r="E291" s="3">
         <v>79002.0</v>
       </c>
-      <c r="F291" s="42" t="s">
-        <v>210</v>
-      </c>
-      <c r="G291" s="42" t="s">
-        <v>211</v>
+      <c r="F291" s="11" t="s">
+        <v>218</v>
+      </c>
+      <c r="G291" s="1" t="s">
+        <v>501</v>
       </c>
       <c r="H291" s="36"/>
       <c r="I291" s="43" t="s">
-        <v>212</v>
+        <v>237</v>
       </c>
       <c r="J291" s="40">
-        <v>0.0</v>
+        <v>-1.0</v>
       </c>
     </row>
     <row r="292">
@@ -12646,21 +12705,21 @@
       <c r="C292" s="3">
         <v>79002.0</v>
       </c>
-      <c r="D292" s="4" t="s">
-        <v>509</v>
+      <c r="D292" s="1" t="s">
+        <v>511</v>
       </c>
       <c r="E292" s="3">
         <v>79003.0</v>
       </c>
       <c r="F292" s="42" t="s">
-        <v>210</v>
-      </c>
-      <c r="G292" s="42" t="s">
-        <v>211</v>
+        <v>229</v>
+      </c>
+      <c r="G292" s="47" t="s">
+        <v>225</v>
       </c>
       <c r="H292" s="36"/>
       <c r="I292" s="43" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J292" s="40">
         <v>0.0</v>
@@ -12677,23 +12736,23 @@
         <v>79003.0</v>
       </c>
       <c r="D293" s="1" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="E293" s="3">
         <v>79004.0</v>
       </c>
       <c r="F293" s="42" t="s">
-        <v>252</v>
-      </c>
-      <c r="G293" s="42" t="s">
-        <v>499</v>
+        <v>229</v>
+      </c>
+      <c r="G293" s="4" t="s">
+        <v>225</v>
       </c>
       <c r="H293" s="36"/>
       <c r="I293" s="43" t="s">
-        <v>235</v>
+        <v>214</v>
       </c>
       <c r="J293" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="294">
@@ -12706,21 +12765,21 @@
       <c r="C294" s="3">
         <v>79004.0</v>
       </c>
-      <c r="D294" s="1" t="s">
-        <v>511</v>
+      <c r="D294" s="4" t="s">
+        <v>513</v>
       </c>
       <c r="E294" s="3">
         <v>79005.0</v>
       </c>
       <c r="F294" s="42" t="s">
-        <v>210</v>
-      </c>
-      <c r="G294" s="42" t="s">
-        <v>211</v>
+        <v>212</v>
+      </c>
+      <c r="G294" s="4" t="s">
+        <v>213</v>
       </c>
       <c r="H294" s="36"/>
       <c r="I294" s="43" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J294" s="40">
         <v>0.0</v>
@@ -12737,20 +12796,20 @@
         <v>79005.0</v>
       </c>
       <c r="D295" s="1" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="E295" s="3">
         <v>79006.0</v>
       </c>
       <c r="F295" s="42" t="s">
-        <v>210</v>
-      </c>
-      <c r="G295" s="42" t="s">
-        <v>211</v>
+        <v>229</v>
+      </c>
+      <c r="G295" s="4" t="s">
+        <v>225</v>
       </c>
       <c r="H295" s="36"/>
       <c r="I295" s="43" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J295" s="40">
         <v>0.0</v>
@@ -12767,23 +12826,23 @@
         <v>79006.0</v>
       </c>
       <c r="D296" s="4" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="E296" s="3">
         <v>79007.0</v>
       </c>
       <c r="F296" s="42" t="s">
-        <v>252</v>
-      </c>
-      <c r="G296" s="42" t="s">
-        <v>499</v>
+        <v>229</v>
+      </c>
+      <c r="G296" s="4" t="s">
+        <v>225</v>
       </c>
       <c r="H296" s="36"/>
       <c r="I296" s="43" t="s">
-        <v>235</v>
+        <v>214</v>
       </c>
       <c r="J296" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="297">
@@ -12797,23 +12856,23 @@
         <v>79007.0</v>
       </c>
       <c r="D297" s="4" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="E297" s="3">
         <v>79008.0</v>
       </c>
       <c r="F297" s="42" t="s">
-        <v>252</v>
-      </c>
-      <c r="G297" s="42" t="s">
-        <v>499</v>
+        <v>229</v>
+      </c>
+      <c r="G297" s="4" t="s">
+        <v>225</v>
       </c>
       <c r="H297" s="36"/>
       <c r="I297" s="43" t="s">
-        <v>235</v>
+        <v>214</v>
       </c>
       <c r="J297" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="298">
@@ -12827,20 +12886,20 @@
         <v>79008.0</v>
       </c>
       <c r="D298" s="1" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="E298" s="3">
         <v>79009.0</v>
       </c>
       <c r="F298" s="42" t="s">
-        <v>210</v>
-      </c>
-      <c r="G298" s="42" t="s">
-        <v>211</v>
+        <v>212</v>
+      </c>
+      <c r="G298" s="4" t="s">
+        <v>213</v>
       </c>
       <c r="H298" s="36"/>
       <c r="I298" s="43" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J298" s="40">
         <v>0.0</v>
@@ -12857,20 +12916,20 @@
         <v>79009.0</v>
       </c>
       <c r="D299" s="1" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="E299" s="3">
         <v>79010.0</v>
       </c>
       <c r="F299" s="42" t="s">
-        <v>210</v>
-      </c>
-      <c r="G299" s="42" t="s">
-        <v>211</v>
+        <v>212</v>
+      </c>
+      <c r="G299" s="4" t="s">
+        <v>213</v>
       </c>
       <c r="H299" s="36"/>
       <c r="I299" s="43" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J299" s="40">
         <v>0.0</v>
@@ -12886,24 +12945,24 @@
       <c r="C300" s="3">
         <v>79010.0</v>
       </c>
-      <c r="D300" s="1" t="s">
-        <v>517</v>
+      <c r="D300" s="4" t="s">
+        <v>519</v>
       </c>
       <c r="E300" s="3">
         <v>79011.0</v>
       </c>
       <c r="F300" s="42" t="s">
-        <v>252</v>
-      </c>
-      <c r="G300" s="42" t="s">
-        <v>499</v>
+        <v>229</v>
+      </c>
+      <c r="G300" s="4" t="s">
+        <v>225</v>
       </c>
       <c r="H300" s="36"/>
       <c r="I300" s="43" t="s">
-        <v>235</v>
+        <v>214</v>
       </c>
       <c r="J300" s="40">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
     </row>
     <row r="301">
@@ -12917,20 +12976,20 @@
         <v>79011.0</v>
       </c>
       <c r="D301" s="1" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="E301" s="3">
-        <v>79012.0</v>
+        <v>-1.0</v>
       </c>
       <c r="F301" s="42" t="s">
-        <v>252</v>
-      </c>
-      <c r="G301" s="42" t="s">
-        <v>499</v>
+        <v>229</v>
+      </c>
+      <c r="G301" s="4" t="s">
+        <v>225</v>
       </c>
       <c r="H301" s="36"/>
       <c r="I301" s="43" t="s">
-        <v>235</v>
+        <v>214</v>
       </c>
       <c r="J301" s="40">
         <v>0.0</v>
@@ -12938,693 +12997,121 @@
     </row>
     <row r="302">
       <c r="A302" s="32" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="B302" s="32" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C302" s="3">
-        <v>79012.0</v>
-      </c>
-      <c r="D302" s="1" t="s">
-        <v>519</v>
-      </c>
-      <c r="E302" s="3">
-        <v>79013.0</v>
+        <v>80001.0</v>
+      </c>
+      <c r="D302" s="14" t="s">
+        <v>521</v>
+      </c>
+      <c r="E302" s="40">
+        <v>-1.0</v>
       </c>
       <c r="F302" s="42" t="s">
-        <v>210</v>
-      </c>
-      <c r="G302" s="42" t="s">
-        <v>211</v>
+        <v>212</v>
+      </c>
+      <c r="G302" s="14" t="s">
+        <v>213</v>
       </c>
       <c r="H302" s="36"/>
       <c r="I302" s="43" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="J302" s="40">
         <v>0.0</v>
       </c>
     </row>
     <row r="303">
-      <c r="A303" s="32" t="s">
-        <v>183</v>
-      </c>
-      <c r="B303" s="32" t="s">
-        <v>183</v>
-      </c>
-      <c r="C303" s="3">
-        <v>79013.0</v>
-      </c>
-      <c r="D303" s="1" t="s">
-        <v>520</v>
-      </c>
-      <c r="E303" s="3">
-        <v>79014.0</v>
-      </c>
-      <c r="F303" s="42" t="s">
-        <v>210</v>
-      </c>
-      <c r="G303" s="42" t="s">
-        <v>211</v>
-      </c>
-      <c r="H303" s="36"/>
-      <c r="I303" s="43" t="s">
-        <v>212</v>
-      </c>
-      <c r="J303" s="40">
-        <v>0.0</v>
-      </c>
+      <c r="A303" s="48"/>
+      <c r="B303" s="48"/>
     </row>
     <row r="304">
-      <c r="A304" s="32" t="s">
-        <v>183</v>
-      </c>
-      <c r="B304" s="32" t="s">
-        <v>183</v>
-      </c>
-      <c r="C304" s="3">
-        <v>79014.0</v>
-      </c>
-      <c r="D304" s="4" t="s">
-        <v>521</v>
-      </c>
-      <c r="E304" s="3">
-        <v>79015.0</v>
-      </c>
-      <c r="F304" s="42" t="s">
-        <v>252</v>
-      </c>
-      <c r="G304" s="1" t="s">
-        <v>499</v>
-      </c>
-      <c r="H304" s="36"/>
-      <c r="I304" s="43" t="s">
-        <v>235</v>
-      </c>
-      <c r="J304" s="40">
-        <v>1.0</v>
-      </c>
+      <c r="A304" s="48"/>
+      <c r="B304" s="48"/>
     </row>
     <row r="305">
-      <c r="A305" s="32" t="s">
-        <v>183</v>
-      </c>
-      <c r="B305" s="32" t="s">
-        <v>183</v>
-      </c>
-      <c r="C305" s="3">
-        <v>79015.0</v>
-      </c>
-      <c r="D305" s="1" t="s">
-        <v>522</v>
-      </c>
-      <c r="E305" s="3">
-        <v>79016.0</v>
-      </c>
-      <c r="F305" s="42" t="s">
-        <v>227</v>
-      </c>
-      <c r="G305" s="47" t="s">
-        <v>223</v>
-      </c>
-      <c r="H305" s="36"/>
-      <c r="I305" s="43" t="s">
-        <v>241</v>
-      </c>
-      <c r="J305" s="40">
-        <v>0.0</v>
-      </c>
+      <c r="A305" s="48"/>
+      <c r="B305" s="48"/>
     </row>
     <row r="306">
-      <c r="A306" s="32" t="s">
-        <v>183</v>
-      </c>
-      <c r="B306" s="32" t="s">
-        <v>183</v>
-      </c>
-      <c r="C306" s="3">
-        <v>79016.0</v>
-      </c>
-      <c r="D306" s="1" t="s">
-        <v>523</v>
-      </c>
-      <c r="E306" s="3">
-        <v>79017.0</v>
-      </c>
-      <c r="F306" s="42" t="s">
-        <v>252</v>
-      </c>
-      <c r="G306" s="1" t="s">
-        <v>499</v>
-      </c>
-      <c r="H306" s="36"/>
-      <c r="I306" s="43" t="s">
-        <v>235</v>
-      </c>
-      <c r="J306" s="40">
-        <v>1.0</v>
-      </c>
+      <c r="A306" s="48"/>
+      <c r="B306" s="48"/>
     </row>
     <row r="307">
-      <c r="A307" s="32" t="s">
-        <v>183</v>
-      </c>
-      <c r="B307" s="32" t="s">
-        <v>183</v>
-      </c>
-      <c r="C307" s="3">
-        <v>79017.0</v>
-      </c>
-      <c r="D307" s="1" t="s">
-        <v>524</v>
-      </c>
-      <c r="E307" s="3">
-        <v>79018.0</v>
-      </c>
-      <c r="F307" s="42" t="s">
-        <v>227</v>
-      </c>
-      <c r="G307" s="47" t="s">
-        <v>223</v>
-      </c>
-      <c r="H307" s="36"/>
-      <c r="I307" s="43" t="s">
-        <v>241</v>
-      </c>
-      <c r="J307" s="40">
-        <v>0.0</v>
-      </c>
+      <c r="A307" s="48"/>
+      <c r="B307" s="48"/>
     </row>
     <row r="308">
-      <c r="A308" s="32" t="s">
-        <v>183</v>
-      </c>
-      <c r="B308" s="32" t="s">
-        <v>183</v>
-      </c>
-      <c r="C308" s="3">
-        <v>79018.0</v>
-      </c>
-      <c r="D308" s="1" t="s">
-        <v>525</v>
-      </c>
-      <c r="E308" s="3">
-        <v>79019.0</v>
-      </c>
-      <c r="F308" s="42" t="s">
-        <v>227</v>
-      </c>
-      <c r="G308" s="4" t="s">
-        <v>223</v>
-      </c>
-      <c r="H308" s="36"/>
-      <c r="I308" s="43" t="s">
-        <v>241</v>
-      </c>
-      <c r="J308" s="40">
-        <v>0.0</v>
-      </c>
+      <c r="A308" s="48"/>
+      <c r="B308" s="48"/>
     </row>
     <row r="309">
-      <c r="A309" s="32" t="s">
-        <v>183</v>
-      </c>
-      <c r="B309" s="32" t="s">
-        <v>183</v>
-      </c>
-      <c r="C309" s="3">
-        <v>79019.0</v>
-      </c>
-      <c r="D309" s="4" t="s">
-        <v>526</v>
-      </c>
-      <c r="E309" s="3">
-        <v>79020.0</v>
-      </c>
-      <c r="F309" s="42" t="s">
-        <v>210</v>
-      </c>
-      <c r="G309" s="4" t="s">
-        <v>211</v>
-      </c>
-      <c r="H309" s="36"/>
-      <c r="I309" s="43" t="s">
-        <v>212</v>
-      </c>
-      <c r="J309" s="40">
-        <v>0.0</v>
-      </c>
+      <c r="A309" s="48"/>
+      <c r="B309" s="48"/>
     </row>
     <row r="310">
-      <c r="A310" s="32" t="s">
-        <v>183</v>
-      </c>
-      <c r="B310" s="32" t="s">
-        <v>183</v>
-      </c>
-      <c r="C310" s="3">
-        <v>79020.0</v>
-      </c>
-      <c r="D310" s="1" t="s">
-        <v>527</v>
-      </c>
-      <c r="E310" s="3">
-        <v>79021.0</v>
-      </c>
-      <c r="F310" s="42" t="s">
-        <v>227</v>
-      </c>
-      <c r="G310" s="4" t="s">
-        <v>223</v>
-      </c>
-      <c r="H310" s="36"/>
-      <c r="I310" s="43" t="s">
-        <v>241</v>
-      </c>
-      <c r="J310" s="40">
-        <v>0.0</v>
-      </c>
+      <c r="A310" s="48"/>
+      <c r="B310" s="48"/>
     </row>
     <row r="311">
-      <c r="A311" s="32" t="s">
-        <v>183</v>
-      </c>
-      <c r="B311" s="32" t="s">
-        <v>183</v>
-      </c>
-      <c r="C311" s="3">
-        <v>79021.0</v>
-      </c>
-      <c r="D311" s="4" t="s">
-        <v>528</v>
-      </c>
-      <c r="E311" s="3">
-        <v>79022.0</v>
-      </c>
-      <c r="F311" s="42" t="s">
-        <v>227</v>
-      </c>
-      <c r="G311" s="4" t="s">
-        <v>223</v>
-      </c>
-      <c r="H311" s="36"/>
-      <c r="I311" s="43" t="s">
-        <v>241</v>
-      </c>
-      <c r="J311" s="40">
-        <v>0.0</v>
-      </c>
+      <c r="A311" s="48"/>
+      <c r="B311" s="48"/>
     </row>
     <row r="312">
-      <c r="A312" s="32" t="s">
-        <v>183</v>
-      </c>
-      <c r="B312" s="32" t="s">
-        <v>183</v>
-      </c>
-      <c r="C312" s="3">
-        <v>79022.0</v>
-      </c>
-      <c r="D312" s="4" t="s">
-        <v>529</v>
-      </c>
-      <c r="E312" s="3">
-        <v>79023.0</v>
-      </c>
-      <c r="F312" s="42" t="s">
-        <v>227</v>
-      </c>
-      <c r="G312" s="4" t="s">
-        <v>223</v>
-      </c>
-      <c r="H312" s="36"/>
-      <c r="I312" s="43" t="s">
-        <v>241</v>
-      </c>
-      <c r="J312" s="40">
-        <v>0.0</v>
-      </c>
+      <c r="A312" s="48"/>
+      <c r="B312" s="48"/>
     </row>
     <row r="313">
-      <c r="A313" s="32" t="s">
-        <v>183</v>
-      </c>
-      <c r="B313" s="32" t="s">
-        <v>183</v>
-      </c>
-      <c r="C313" s="3">
-        <v>79023.0</v>
-      </c>
-      <c r="D313" s="1" t="s">
-        <v>530</v>
-      </c>
-      <c r="E313" s="3">
-        <v>79024.0</v>
-      </c>
-      <c r="F313" s="42" t="s">
-        <v>210</v>
-      </c>
-      <c r="G313" s="4" t="s">
-        <v>211</v>
-      </c>
-      <c r="H313" s="36"/>
-      <c r="I313" s="43" t="s">
-        <v>212</v>
-      </c>
-      <c r="J313" s="40">
-        <v>0.0</v>
-      </c>
+      <c r="A313" s="48"/>
+      <c r="B313" s="48"/>
     </row>
     <row r="314">
-      <c r="A314" s="32" t="s">
-        <v>183</v>
-      </c>
-      <c r="B314" s="32" t="s">
-        <v>183</v>
-      </c>
-      <c r="C314" s="3">
-        <v>79024.0</v>
-      </c>
-      <c r="D314" s="1" t="s">
-        <v>531</v>
-      </c>
-      <c r="E314" s="3">
-        <v>79025.0</v>
-      </c>
-      <c r="F314" s="42" t="s">
-        <v>210</v>
-      </c>
-      <c r="G314" s="4" t="s">
-        <v>211</v>
-      </c>
-      <c r="H314" s="36"/>
-      <c r="I314" s="43" t="s">
-        <v>212</v>
-      </c>
-      <c r="J314" s="40">
-        <v>0.0</v>
-      </c>
+      <c r="A314" s="48"/>
+      <c r="B314" s="48"/>
     </row>
     <row r="315">
-      <c r="A315" s="32" t="s">
-        <v>183</v>
-      </c>
-      <c r="B315" s="32" t="s">
-        <v>183</v>
-      </c>
-      <c r="C315" s="3">
-        <v>79025.0</v>
-      </c>
-      <c r="D315" s="4" t="s">
-        <v>532</v>
-      </c>
-      <c r="E315" s="3">
-        <v>79026.0</v>
-      </c>
-      <c r="F315" s="42" t="s">
-        <v>227</v>
-      </c>
-      <c r="G315" s="4" t="s">
-        <v>223</v>
-      </c>
-      <c r="H315" s="36"/>
-      <c r="I315" s="43" t="s">
-        <v>241</v>
-      </c>
-      <c r="J315" s="40">
-        <v>0.0</v>
-      </c>
+      <c r="A315" s="48"/>
+      <c r="B315" s="48"/>
     </row>
     <row r="316">
-      <c r="A316" s="32" t="s">
-        <v>183</v>
-      </c>
-      <c r="B316" s="32" t="s">
-        <v>183</v>
-      </c>
-      <c r="C316" s="3">
-        <v>79026.0</v>
-      </c>
-      <c r="D316" s="1" t="s">
-        <v>533</v>
-      </c>
-      <c r="E316" s="3">
-        <v>79027.0</v>
-      </c>
-      <c r="F316" s="42" t="s">
-        <v>227</v>
-      </c>
-      <c r="G316" s="4" t="s">
-        <v>223</v>
-      </c>
-      <c r="H316" s="36"/>
-      <c r="I316" s="43" t="s">
-        <v>241</v>
-      </c>
-      <c r="J316" s="40">
-        <v>0.0</v>
-      </c>
+      <c r="A316" s="48"/>
+      <c r="B316" s="48"/>
     </row>
     <row r="317">
-      <c r="A317" s="32" t="s">
-        <v>183</v>
-      </c>
-      <c r="B317" s="32" t="s">
-        <v>183</v>
-      </c>
-      <c r="C317" s="3">
-        <v>79027.0</v>
-      </c>
-      <c r="D317" s="1" t="s">
-        <v>534</v>
-      </c>
-      <c r="E317" s="3">
-        <v>79028.0</v>
-      </c>
-      <c r="F317" s="42" t="s">
-        <v>227</v>
-      </c>
-      <c r="G317" s="4" t="s">
-        <v>223</v>
-      </c>
-      <c r="H317" s="36"/>
-      <c r="I317" s="43" t="s">
-        <v>241</v>
-      </c>
-      <c r="J317" s="40">
-        <v>0.0</v>
-      </c>
+      <c r="A317" s="48"/>
+      <c r="B317" s="48"/>
     </row>
     <row r="318">
-      <c r="A318" s="32" t="s">
-        <v>183</v>
-      </c>
-      <c r="B318" s="32" t="s">
-        <v>183</v>
-      </c>
-      <c r="C318" s="3">
-        <v>79028.0</v>
-      </c>
-      <c r="D318" s="1" t="s">
-        <v>535</v>
-      </c>
-      <c r="E318" s="3">
-        <v>79029.0</v>
-      </c>
-      <c r="F318" s="42" t="s">
-        <v>227</v>
-      </c>
-      <c r="G318" s="1" t="s">
-        <v>223</v>
-      </c>
-      <c r="H318" s="36"/>
-      <c r="I318" s="43" t="s">
-        <v>241</v>
-      </c>
-      <c r="J318" s="40">
-        <v>0.0</v>
-      </c>
+      <c r="A318" s="48"/>
+      <c r="B318" s="48"/>
     </row>
     <row r="319">
-      <c r="A319" s="32" t="s">
-        <v>183</v>
-      </c>
-      <c r="B319" s="32" t="s">
-        <v>183</v>
-      </c>
-      <c r="C319" s="3">
-        <v>79029.0</v>
-      </c>
-      <c r="D319" s="1" t="s">
-        <v>536</v>
-      </c>
-      <c r="E319" s="3">
-        <v>79030.0</v>
-      </c>
-      <c r="F319" s="42" t="s">
-        <v>210</v>
-      </c>
-      <c r="G319" s="4" t="s">
-        <v>211</v>
-      </c>
-      <c r="H319" s="36"/>
-      <c r="I319" s="43" t="s">
-        <v>212</v>
-      </c>
-      <c r="J319" s="40">
-        <v>0.0</v>
-      </c>
+      <c r="A319" s="48"/>
+      <c r="B319" s="48"/>
     </row>
     <row r="320">
-      <c r="A320" s="32" t="s">
-        <v>183</v>
-      </c>
-      <c r="B320" s="32" t="s">
-        <v>183</v>
-      </c>
-      <c r="C320" s="3">
-        <v>79030.0</v>
-      </c>
-      <c r="D320" s="1" t="s">
-        <v>537</v>
-      </c>
-      <c r="E320" s="3">
-        <v>79031.0</v>
-      </c>
-      <c r="F320" s="42" t="s">
-        <v>227</v>
-      </c>
-      <c r="G320" s="4" t="s">
-        <v>223</v>
-      </c>
-      <c r="H320" s="36"/>
-      <c r="I320" s="43" t="s">
-        <v>241</v>
-      </c>
-      <c r="J320" s="40">
-        <v>0.0</v>
-      </c>
+      <c r="A320" s="48"/>
+      <c r="B320" s="48"/>
     </row>
     <row r="321">
-      <c r="A321" s="32" t="s">
-        <v>183</v>
-      </c>
-      <c r="B321" s="32" t="s">
-        <v>183</v>
-      </c>
-      <c r="C321" s="3">
-        <v>79031.0</v>
-      </c>
-      <c r="D321" s="4" t="s">
-        <v>538</v>
-      </c>
-      <c r="E321" s="3">
-        <v>79032.0</v>
-      </c>
-      <c r="F321" s="42" t="s">
-        <v>227</v>
-      </c>
-      <c r="G321" s="4" t="s">
-        <v>223</v>
-      </c>
-      <c r="H321" s="36"/>
-      <c r="I321" s="43" t="s">
-        <v>241</v>
-      </c>
-      <c r="J321" s="40">
-        <v>0.0</v>
-      </c>
+      <c r="A321" s="48"/>
+      <c r="B321" s="48"/>
     </row>
     <row r="322">
-      <c r="A322" s="32" t="s">
-        <v>183</v>
-      </c>
-      <c r="B322" s="32" t="s">
-        <v>183</v>
-      </c>
-      <c r="C322" s="3">
-        <v>79032.0</v>
-      </c>
-      <c r="D322" s="4" t="s">
-        <v>539</v>
-      </c>
-      <c r="E322" s="3">
-        <v>79033.0</v>
-      </c>
-      <c r="F322" s="42" t="s">
-        <v>210</v>
-      </c>
-      <c r="G322" s="4" t="s">
-        <v>211</v>
-      </c>
-      <c r="H322" s="36"/>
-      <c r="I322" s="43" t="s">
-        <v>212</v>
-      </c>
-      <c r="J322" s="40">
-        <v>0.0</v>
-      </c>
+      <c r="A322" s="48"/>
+      <c r="B322" s="48"/>
     </row>
     <row r="323">
-      <c r="A323" s="32" t="s">
-        <v>183</v>
-      </c>
-      <c r="B323" s="32" t="s">
-        <v>183</v>
-      </c>
-      <c r="C323" s="3">
-        <v>79033.0</v>
-      </c>
-      <c r="D323" s="4" t="s">
-        <v>540</v>
-      </c>
-      <c r="E323" s="3">
-        <v>79034.0</v>
-      </c>
-      <c r="F323" s="42" t="s">
-        <v>227</v>
-      </c>
-      <c r="G323" s="4" t="s">
-        <v>223</v>
-      </c>
-      <c r="H323" s="36"/>
-      <c r="I323" s="43" t="s">
-        <v>241</v>
-      </c>
-      <c r="J323" s="40">
-        <v>0.0</v>
-      </c>
+      <c r="A323" s="48"/>
+      <c r="B323" s="48"/>
     </row>
     <row r="324">
-      <c r="A324" s="32" t="s">
-        <v>183</v>
-      </c>
-      <c r="B324" s="32" t="s">
-        <v>183</v>
-      </c>
-      <c r="C324" s="3">
-        <v>79034.0</v>
-      </c>
-      <c r="D324" s="4" t="s">
-        <v>541</v>
-      </c>
-      <c r="E324" s="40">
-        <v>-1.0</v>
-      </c>
-      <c r="F324" s="42" t="s">
-        <v>252</v>
-      </c>
-      <c r="G324" s="1" t="s">
-        <v>499</v>
-      </c>
-      <c r="H324" s="36"/>
-      <c r="I324" s="43" t="s">
-        <v>235</v>
-      </c>
-      <c r="J324" s="40">
-        <v>1.0</v>
-      </c>
+      <c r="A324" s="48"/>
+      <c r="B324" s="48"/>
     </row>
     <row r="325">
       <c r="A325" s="48"/>
@@ -16161,98 +15648,6 @@
     <row r="958">
       <c r="A958" s="48"/>
       <c r="B958" s="48"/>
-    </row>
-    <row r="959">
-      <c r="A959" s="48"/>
-      <c r="B959" s="48"/>
-    </row>
-    <row r="960">
-      <c r="A960" s="48"/>
-      <c r="B960" s="48"/>
-    </row>
-    <row r="961">
-      <c r="A961" s="48"/>
-      <c r="B961" s="48"/>
-    </row>
-    <row r="962">
-      <c r="A962" s="48"/>
-      <c r="B962" s="48"/>
-    </row>
-    <row r="963">
-      <c r="A963" s="48"/>
-      <c r="B963" s="48"/>
-    </row>
-    <row r="964">
-      <c r="A964" s="48"/>
-      <c r="B964" s="48"/>
-    </row>
-    <row r="965">
-      <c r="A965" s="48"/>
-      <c r="B965" s="48"/>
-    </row>
-    <row r="966">
-      <c r="A966" s="48"/>
-      <c r="B966" s="48"/>
-    </row>
-    <row r="967">
-      <c r="A967" s="48"/>
-      <c r="B967" s="48"/>
-    </row>
-    <row r="968">
-      <c r="A968" s="48"/>
-      <c r="B968" s="48"/>
-    </row>
-    <row r="969">
-      <c r="A969" s="48"/>
-      <c r="B969" s="48"/>
-    </row>
-    <row r="970">
-      <c r="A970" s="48"/>
-      <c r="B970" s="48"/>
-    </row>
-    <row r="971">
-      <c r="A971" s="48"/>
-      <c r="B971" s="48"/>
-    </row>
-    <row r="972">
-      <c r="A972" s="48"/>
-      <c r="B972" s="48"/>
-    </row>
-    <row r="973">
-      <c r="A973" s="48"/>
-      <c r="B973" s="48"/>
-    </row>
-    <row r="974">
-      <c r="A974" s="48"/>
-      <c r="B974" s="48"/>
-    </row>
-    <row r="975">
-      <c r="A975" s="48"/>
-      <c r="B975" s="48"/>
-    </row>
-    <row r="976">
-      <c r="A976" s="48"/>
-      <c r="B976" s="48"/>
-    </row>
-    <row r="977">
-      <c r="A977" s="48"/>
-      <c r="B977" s="48"/>
-    </row>
-    <row r="978">
-      <c r="A978" s="48"/>
-      <c r="B978" s="48"/>
-    </row>
-    <row r="979">
-      <c r="A979" s="48"/>
-      <c r="B979" s="48"/>
-    </row>
-    <row r="980">
-      <c r="A980" s="48"/>
-      <c r="B980" s="48"/>
-    </row>
-    <row r="981">
-      <c r="A981" s="48"/>
-      <c r="B981" s="48"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>
@@ -16281,48 +15676,48 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="4" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>542</v>
+        <v>522</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>543</v>
+        <v>523</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>544</v>
+        <v>524</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>545</v>
+        <v>525</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>546</v>
+        <v>526</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>547</v>
+        <v>527</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>548</v>
+        <v>528</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>549</v>
+        <v>529</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>550</v>
+        <v>530</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>551</v>
+        <v>531</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="49" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B2" s="50" t="s">
-        <v>552</v>
+        <v>532</v>
       </c>
       <c r="C2" s="50" t="s">
-        <v>553</v>
+        <v>533</v>
       </c>
       <c r="D2" s="4"/>
       <c r="E2" s="3">
@@ -16337,13 +15732,13 @@
     </row>
     <row r="3">
       <c r="A3" s="51" t="s">
-        <v>554</v>
+        <v>534</v>
       </c>
       <c r="B3" s="50" t="s">
-        <v>555</v>
+        <v>535</v>
       </c>
       <c r="C3" s="52" t="s">
-        <v>556</v>
+        <v>536</v>
       </c>
       <c r="D3" s="4"/>
       <c r="E3" s="5">
@@ -16354,24 +15749,24 @@
       </c>
       <c r="G3" s="4"/>
       <c r="H3" s="3" t="s">
-        <v>557</v>
+        <v>537</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>558</v>
+        <v>538</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>559</v>
+        <v>539</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="s">
-        <v>560</v>
+        <v>540</v>
       </c>
       <c r="B4" s="53" t="s">
-        <v>561</v>
+        <v>541</v>
       </c>
       <c r="C4" s="53" t="s">
-        <v>562</v>
+        <v>542</v>
       </c>
       <c r="D4" s="4"/>
       <c r="E4" s="2">
@@ -16382,24 +15777,24 @@
       </c>
       <c r="G4" s="4"/>
       <c r="H4" s="3" t="s">
-        <v>563</v>
+        <v>543</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>564</v>
+        <v>544</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>565</v>
+        <v>545</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>566</v>
+        <v>546</v>
       </c>
       <c r="B5" s="54" t="s">
-        <v>567</v>
+        <v>547</v>
       </c>
       <c r="C5" s="54" t="s">
-        <v>568</v>
+        <v>548</v>
       </c>
       <c r="E5" s="3">
         <v>-10.0</v>
@@ -16408,24 +15803,24 @@
         <v>0.0</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>569</v>
+        <v>549</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>570</v>
+        <v>550</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>571</v>
+        <v>551</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>572</v>
+        <v>552</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>573</v>
+        <v>553</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>574</v>
+        <v>554</v>
       </c>
       <c r="E6" s="3">
         <v>0.0</v>
@@ -16434,24 +15829,24 @@
         <v>-10.0</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>575</v>
+        <v>555</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>576</v>
+        <v>556</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>577</v>
+        <v>557</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>578</v>
+        <v>558</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>579</v>
+        <v>559</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>580</v>
+        <v>560</v>
       </c>
       <c r="E7" s="3">
         <v>-10.0</v>
@@ -16460,24 +15855,24 @@
         <v>0.0</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>581</v>
+        <v>561</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>582</v>
+        <v>562</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>583</v>
+        <v>563</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>584</v>
+        <v>564</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>585</v>
+        <v>565</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>586</v>
+        <v>566</v>
       </c>
       <c r="E8" s="3">
         <v>0.0</v>
@@ -16486,24 +15881,24 @@
         <v>-10.0</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>587</v>
+        <v>567</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>588</v>
+        <v>568</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>589</v>
+        <v>569</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>590</v>
+        <v>570</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>591</v>
+        <v>571</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>592</v>
+        <v>572</v>
       </c>
       <c r="E9" s="3">
         <v>0.0</v>
@@ -16512,25 +15907,25 @@
         <v>0.0</v>
       </c>
       <c r="H9" s="32" t="s">
-        <v>593</v>
+        <v>573</v>
       </c>
       <c r="I9" s="32" t="s">
-        <v>594</v>
+        <v>574</v>
       </c>
       <c r="J9" s="32"/>
       <c r="K9" s="3" t="s">
-        <v>595</v>
+        <v>575</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>596</v>
+        <v>576</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>597</v>
+        <v>577</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>598</v>
+        <v>578</v>
       </c>
       <c r="E10" s="3">
         <v>-10.0</v>
@@ -16539,24 +15934,24 @@
         <v>-10.0</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>599</v>
+        <v>579</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>600</v>
+        <v>580</v>
       </c>
       <c r="K10" s="55" t="s">
-        <v>601</v>
+        <v>581</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>602</v>
+        <v>582</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>603</v>
+        <v>583</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>604</v>
+        <v>584</v>
       </c>
       <c r="E11" s="3">
         <v>-10.0</v>
@@ -16565,24 +15960,24 @@
         <v>-10.0</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>605</v>
+        <v>585</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>606</v>
+        <v>586</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>607</v>
+        <v>587</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>608</v>
+        <v>588</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>609</v>
+        <v>589</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>610</v>
+        <v>590</v>
       </c>
       <c r="E12" s="3">
         <v>-10.0</v>
@@ -16591,13 +15986,13 @@
         <v>0.0</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>611</v>
+        <v>591</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>612</v>
+        <v>592</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>613</v>
+        <v>593</v>
       </c>
     </row>
   </sheetData>
@@ -16619,21 +16014,21 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="3" t="s">
-        <v>614</v>
+        <v>594</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>615</v>
+        <v>595</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>616</v>
+        <v>596</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>617</v>
+        <v>597</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>21</v>
@@ -16642,12 +16037,12 @@
         <v>24</v>
       </c>
       <c r="D2" s="56" t="s">
-        <v>618</v>
+        <v>598</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>619</v>
+        <v>599</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>24</v>
@@ -16656,40 +16051,40 @@
         <v>30</v>
       </c>
       <c r="D3" s="56" t="s">
-        <v>620</v>
+        <v>600</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>621</v>
+        <v>601</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>30</v>
       </c>
       <c r="C4" s="53" t="s">
-        <v>622</v>
+        <v>602</v>
       </c>
       <c r="D4" s="56" t="s">
-        <v>623</v>
+        <v>603</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>624</v>
+        <v>604</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>622</v>
+        <v>602</v>
       </c>
       <c r="C5" s="53" t="s">
         <v>36</v>
       </c>
       <c r="D5" s="56" t="s">
-        <v>625</v>
+        <v>605</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>626</v>
+        <v>606</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>36</v>
@@ -16698,12 +16093,12 @@
         <v>42</v>
       </c>
       <c r="D6" s="56" t="s">
-        <v>618</v>
+        <v>598</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>627</v>
+        <v>607</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>42</v>
@@ -16712,68 +16107,68 @@
         <v>48</v>
       </c>
       <c r="D7" s="56" t="s">
-        <v>620</v>
+        <v>600</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>628</v>
+        <v>608</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>48</v>
       </c>
       <c r="C8" s="53" t="s">
-        <v>571</v>
+        <v>551</v>
       </c>
       <c r="D8" s="56" t="s">
-        <v>629</v>
+        <v>609</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>630</v>
+        <v>610</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>571</v>
+        <v>551</v>
       </c>
       <c r="C9" s="53" t="s">
         <v>54</v>
       </c>
       <c r="D9" s="56" t="s">
-        <v>625</v>
+        <v>605</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>631</v>
+        <v>611</v>
       </c>
       <c r="B10" s="3" t="s">
         <v>54</v>
       </c>
       <c r="C10" s="53" t="s">
-        <v>632</v>
+        <v>612</v>
       </c>
       <c r="D10" s="56" t="s">
-        <v>633</v>
+        <v>613</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>634</v>
+        <v>614</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>632</v>
+        <v>612</v>
       </c>
       <c r="C11" s="53" t="s">
         <v>57</v>
       </c>
       <c r="D11" s="56" t="s">
-        <v>635</v>
+        <v>615</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>636</v>
+        <v>616</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>57</v>
@@ -16782,12 +16177,12 @@
         <v>60</v>
       </c>
       <c r="D12" s="56" t="s">
-        <v>637</v>
+        <v>617</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>638</v>
+        <v>618</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>60</v>
@@ -16796,12 +16191,12 @@
         <v>106</v>
       </c>
       <c r="D13" s="56" t="s">
-        <v>639</v>
+        <v>619</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>640</v>
+        <v>620</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>106</v>
@@ -16810,24 +16205,24 @@
         <v>63</v>
       </c>
       <c r="D14" s="56" t="s">
-        <v>641</v>
+        <v>621</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>642</v>
+        <v>622</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>63</v>
       </c>
       <c r="C15" s="56"/>
       <c r="D15" s="56" t="s">
-        <v>643</v>
+        <v>623</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>644</v>
+        <v>624</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>66</v>
@@ -16836,26 +16231,26 @@
         <v>70</v>
       </c>
       <c r="D16" s="56" t="s">
-        <v>645</v>
+        <v>625</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>646</v>
+        <v>626</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>70</v>
       </c>
       <c r="C17" s="53" t="s">
-        <v>647</v>
+        <v>627</v>
       </c>
       <c r="D17" s="56" t="s">
-        <v>648</v>
+        <v>628</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>649</v>
+        <v>629</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>74</v>
@@ -16864,12 +16259,12 @@
         <v>76</v>
       </c>
       <c r="D18" s="56" t="s">
-        <v>650</v>
+        <v>630</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>651</v>
+        <v>631</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>76</v>
@@ -16878,40 +16273,40 @@
         <v>80</v>
       </c>
       <c r="D19" s="56" t="s">
-        <v>652</v>
+        <v>632</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>653</v>
+        <v>633</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>80</v>
       </c>
       <c r="C20" s="53" t="s">
-        <v>601</v>
+        <v>581</v>
       </c>
       <c r="D20" s="56" t="s">
-        <v>654</v>
+        <v>634</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>655</v>
+        <v>635</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>601</v>
+        <v>581</v>
       </c>
       <c r="C21" s="53" t="s">
         <v>86</v>
       </c>
       <c r="D21" s="56" t="s">
-        <v>656</v>
+        <v>636</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>657</v>
+        <v>637</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>86</v>
@@ -16920,12 +16315,12 @@
         <v>90</v>
       </c>
       <c r="D22" s="56" t="s">
-        <v>650</v>
+        <v>630</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>658</v>
+        <v>638</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>90</v>
@@ -16934,12 +16329,12 @@
         <v>92</v>
       </c>
       <c r="D23" s="56" t="s">
-        <v>659</v>
+        <v>639</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>660</v>
+        <v>640</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>92</v>
@@ -16948,41 +16343,41 @@
         <v>94</v>
       </c>
       <c r="D24" s="56" t="s">
-        <v>652</v>
+        <v>632</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>661</v>
+        <v>641</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>607</v>
+        <v>587</v>
       </c>
       <c r="C25" s="53" t="s">
         <v>98</v>
       </c>
       <c r="D25" s="56" t="s">
-        <v>656</v>
+        <v>636</v>
       </c>
       <c r="F25" s="56"/>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>662</v>
+        <v>642</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>94</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>607</v>
+        <v>587</v>
       </c>
       <c r="D26" s="56" t="s">
-        <v>654</v>
+        <v>634</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>663</v>
+        <v>643</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>98</v>
@@ -16991,57 +16386,320 @@
         <v>100</v>
       </c>
       <c r="D27" s="56" t="s">
-        <v>650</v>
+        <v>630</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>664</v>
+        <v>644</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>100</v>
       </c>
       <c r="C28" s="53" t="s">
-        <v>665</v>
+        <v>645</v>
       </c>
       <c r="D28" s="56" t="s">
-        <v>633</v>
+        <v>613</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>666</v>
+        <v>646</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>665</v>
+        <v>645</v>
       </c>
       <c r="C29" s="53" t="s">
         <v>102</v>
       </c>
       <c r="D29" s="56" t="s">
-        <v>667</v>
+        <v>647</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>668</v>
+        <v>648</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>102</v>
       </c>
       <c r="D30" s="56" t="s">
-        <v>669</v>
+        <v>649</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>670</v>
+        <v>650</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>112</v>
       </c>
       <c r="D31" s="54" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="s">
+        <v>652</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="C32" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="D32" s="54" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="s">
+        <v>654</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="C33" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="D33" s="54" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="s">
+        <v>656</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="D34" s="54" t="s">
+        <v>657</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="s">
+        <v>658</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>132</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="D35" s="54" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="s">
+        <v>660</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="D36" s="54" t="s">
+        <v>661</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="s">
+        <v>662</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="D37" s="54" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="s">
+        <v>664</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="C38" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="D38" s="54" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="s">
+        <v>666</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="C39" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="D39" s="54" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="s">
+        <v>668</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="D40" s="54" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="s">
+        <v>670</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="D41" s="54" t="s">
         <v>671</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="s">
+        <v>672</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="D42" s="54" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="s">
+        <v>674</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="D43" s="54" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="s">
+        <v>676</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="D44" s="54" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="s">
+        <v>677</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="D45" s="54" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="3" t="s">
+        <v>679</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="C46" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="D46" s="54" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="3" t="s">
+        <v>681</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>173</v>
+      </c>
+      <c r="C47" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="D47" s="54" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="s">
+        <v>682</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>175</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="D48" s="54" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="3" t="s">
+        <v>684</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="D49" s="54" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="3" t="s">
+        <v>686</v>
+      </c>
+      <c r="B50" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="D50" s="54" t="s">
+        <v>687</v>
       </c>
     </row>
   </sheetData>
